--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{930CABF5-B21E-482D-8F15-2C61F5CAF6E7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{867B78F5-3A76-414E-85CC-EE97F846E210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1547" uniqueCount="1003">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1560" uniqueCount="1016">
   <si>
     <t>Ramazzotti Spritz</t>
   </si>
@@ -4244,10 +4244,6 @@
 En el mismo ensayo de MacElhone de 1927 aparece también el Old Pal, un cóctel estrechamente relacionado. En su versión original, el Old Pal se diferenciaba solo por emplear whisky de centeno, en particular Canadian Club, en lugar de bourbon, manteniendo partes iguales de Campari y vermú italiano dulce. Con el tiempo, su estándar contemporáneo evolucionó hacia una mezcla a partes iguales de whisky de centeno, vermú francés seco y Campari, dando lugar a un perfil más seco y austero que el del Boulevardier.</t>
   </si>
   <si>
-    <t>El Old Pal es un cóctel clásico emparentado directamente con el Negroni y el Boulevardier, documentado —al igual que este último— en Barflies and Cocktails (1927) de Harry MacElhone. Ambos aparecen en el mismo ensayo de Arthur Moss y forman parte del repertorio de tragos asociados a la vida bohemia del París de entreguerras.
-En su versión original, el Old Pal se diferenciaba del Boulevardier únicamente por el uso de whisky de centeno, en particular Canadian Club, manteniendo partes iguales de Campari, vermú italiano dulce y whisky. Con el tiempo, la receta evolucionó hacia su estándar contemporáneo, que emplea partes iguales de whisky de centeno, vermú francés seco y Campari, dando como resultado un cóctel más seco y herbal.</t>
-  </si>
-  <si>
     <t>Boulevardier</t>
   </si>
   <si>
@@ -4723,6 +4719,69 @@
   <si>
     <t>strummer.jpg
 Joe Strummer bebiendo un schop Cristal en Copiapó, Chile, durante su visita en 1996 para filmar Docteur Chance, película francesa de corte experimental escrita y dirigida por F. J. Ossang, en la que también participó el actor chileno Francisco Reyes.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federico García Lorca, Salvador Dalí y una botella de ron
+Federico García Lorca y Salvador Dalí se conocieron en 1923 en la Residencia de Estudiantes de Madrid, uno de los centros más vibrantes de la vida intelectual española de la época. Lorca ya destacaba como poeta y músico; Dalí era un joven pintor inquieto, todavía en búsqueda de su propio lenguaje. Entre ambos surgió rápidamente una afinidad profunda, alimentada por largas conversaciones, lecturas compartidas y una curiosidad común por las vanguardias artísticas. Aquella amistad, intensa y compleja, marcaría de manera decisiva la obra y la sensibilidad de ambos.
+En ese clima de complicidad artística y emocional surgió también un imaginario común en el que el alcohol aparecía más como símbolo que como hábito. El bodegón Naturaleza muerta con botella de ron, que Dalí regaló a Lorca hacia 1924 y que el poeta conservó hasta su muerte, es un buen ejemplo de ello. No hay evidencia de que Lorca fuera particularmente aficionado al ron; sin embargo, para ambos esta bebida evocaba un mundo que los fascinaba: el de los puertos, los marineros, las tabernas y los viajes imaginados, un territorio de aventura y misterio que dialogaba con la sensibilidad poética de Lorca y con la imaginación visual de Dalí.
+Está documentado que Dalí regaló este cuadro a Lorca como un gesto de amistad profunda y de intimidad artística, en los años en que su relación fue especialmente intensa. La correspondencia que se conserva deja entrever un vínculo cargado de afecto y admiración, que muchos estudiosos han interpretado también con matices eróticos y sentimentales. Los testimonios posteriores sugieren que Lorca desarrolló sentimientos amorosos más explícitos hacia Dalí, mientras que Dalí mantuvo una posición ambigua y finalmente tomó distancia. Esa asimetría afectiva parece haber generado tensiones y un cierto dolor en Lorca, perceptible en algunas cartas y en el tono de ciertos textos de la época.
+Hacia fines de la década de 1920, varios factores contribuyeron a que la relación se debilitara. Dalí estrechó su vínculo con Luis Buñuel y con el grupo surrealista de París, y su mundo artístico cambió con rapidez. El guion de la película Un chien andalou (1929), escrito por Dalí y Buñuel, incluyó elementos que Lorca interpretó como alusiones críticas o burlas hacia él, lo que aumentó la distancia emocional entre ambos. Al mismo tiempo, Lorca se concentró cada vez más en el teatro y la poesía, y su viaje a Nueva York en 1929 transformó profundamente su obra. Sus trayectorias comenzaron así a separarse de manera natural.
+Con el paso de los años la relación se fue enfriando hasta desvanecerse, pero el cuadro permaneció colgado sobre la cama de Lorca en su habitación de la Residencia, como un vestigio silencioso de aquella amistad intensa, en la que la pintura, la poesía y hasta una botella de ron formaron parte del amor compartido. </t>
+  </si>
+  <si>
+    <t>naturaleza_ron.jpg
+Título: Naturaleza muerta con botella de ron (también conocida como Sifón y botella de ron)
+Autor: Salvador Dalí
+Técnica: Óleo sobre lienzo
+Año: 1924</t>
+  </si>
+  <si>
+    <t>La_Bodeguita_Ernest_Hemingway.jpg
+Frase atribuida a Ernest Hemingway, escrita en una pared de La Bodeguita del Medio, en La Habana, Cuba.</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=yaPEkSRf6Vg</t>
+  </si>
+  <si>
+    <t>Joan Manuel Serrat cantando el poema "Herido de amor" de Federico Garcia Lorca (2003).</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=mYuGb4uPqVw</t>
+  </si>
+  <si>
+    <t>Hoy el noble y el villano/El prohombre y el gusano/Bailan y se dan la mano/Sin importarles la facha/Juntos los encuentra el sol/A la sombra de un farol/Empapados en alcohol/Magreando a una muchacha/Y con la resaca a cuestas/Vuelve el pobre a su pobreza/Vuelve el rico a su riqueza/Y el señor cura a sus misas</t>
+  </si>
+  <si>
+    <t>El Old Pal es un cóctel clásico emparentado directamente con el Negroni y el Boulevardier, documentado, al igual que este último, en Barflies and Cocktails (1927) de Harry MacElhone. Ambos aparecen en el mismo ensayo de Arthur Moss y forman parte del repertorio de tragos asociados a la vida bohemia del París de entreguerras.
+En su versión original, el Old Pal se diferenciaba del Boulevardier únicamente por el uso de whisky de centeno, en particular Canadian Club, manteniendo partes iguales de Campari, vermú italiano dulce y whisky. Con el tiempo, la receta evolucionó hacia su estándar contemporáneo, que emplea partes iguales de whisky de centeno, vermú francés seco y Campari, dando como resultado un cóctel más seco y herbal.</t>
+  </si>
+  <si>
+    <t>Joan Manuel Serrat - Fiesta (TVE, 1975)</t>
+  </si>
+  <si>
+    <t>Trepo por el/Tallo del lúpulo/Al cielo iré/Tu espuma en cúmulos/Atravesaré/Somos los tres/Junto a tu hermano pan/La agrupación/Perfecta, inmortal</t>
+  </si>
+  <si>
+    <t>Antonio_Machado_por_Leandro_Oroz_(1925).jpg
+Título: Retrato de Antonio Machado (1875 - 1939)
+Autor: Leandro Oroz Lacalle
+Técnica: Sanguina
+Año: 1925</t>
+  </si>
+  <si>
+    <t>AlcProfSummerPenn19351.jpg
+Afiche publicitario de Penn Maryland De Luxe Rye Whiskey, 1935.</t>
+  </si>
+  <si>
+    <t>El descubrimiento de la penicilina
+En 1928, el bacteriólogo escocés Alexander Fleming observó algo inesperado en su laboratorio de Londres: en una placa de cultivo contaminada por un moho del género Penicillium, las bacterias habían desaparecido alrededor del hongo. Comprendió entonces que aquel moho producía una sustancia capaz de destruirlas, a la que llamó penicilina.
+Sin embargo, el hallazgo casi no fue valorado en su momento. Fleming logró demostrar el efecto antibacteriano, pero no consiguió aislar ni producir la sustancia en forma estable, y la penicilina se degradaba con facilidad, lo que hacía muy difícil estudiarla o utilizarla como medicamento. Durante varios años, su descubrimiento quedó prácticamente olvidado.
+Recién a fines de la década de 1930, los científicos Howard Florey, Ernst Chain y su equipo en la Universidad de Oxford, con un papel clave también del químico Norman Heatley, lograron purificarla y producirla en cantidades suficientes. Así comenzó la era de los antibióticos, que transformó para siempre la medicina.
+La historia suele recordarse como un ejemplo clásico de descubrimiento por azar, pero también de la importancia de observar con atención lo inesperado y perseverar hasta que una idea encuentre su momento.</t>
+  </si>
+  <si>
+    <t>whisky.jpg
+Aviso publicitario de Ballantine’s Scotch de 1935, que alude al tradicional partido de fútbol americano Harvard–Yale, conocido como The Game, una de las rivalidades universitarias más antiguas de Estados Unidos.</t>
   </si>
 </sst>
 </file>
@@ -5442,10 +5501,10 @@
         <v>829</v>
       </c>
       <c r="AC1" s="27" t="s">
+        <v>905</v>
+      </c>
+      <c r="AD1" s="27" t="s">
         <v>906</v>
-      </c>
-      <c r="AD1" s="27" t="s">
-        <v>907</v>
       </c>
       <c r="AE1" s="27" t="s">
         <v>82</v>
@@ -35244,7 +35303,7 @@
     </row>
     <row r="167" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>53</v>
@@ -35596,7 +35655,7 @@
     </row>
     <row r="169" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>55</v>
@@ -35774,7 +35833,7 @@
     </row>
     <row r="170" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>53</v>
@@ -35950,7 +36009,7 @@
     </row>
     <row r="171" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>55</v>
@@ -57926,7 +57985,7 @@
         <v>315</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>316</v>
@@ -57941,7 +58000,7 @@
         <v>768</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="M1" s="7" t="s">
         <v>816</v>
@@ -57972,7 +58031,7 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="4" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58018,7 +58077,7 @@
         <v>239</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="5"/>
@@ -58054,7 +58113,7 @@
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
       <c r="M5" s="4" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="270" x14ac:dyDescent="0.25">
@@ -58082,7 +58141,7 @@
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="4" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="270" x14ac:dyDescent="0.25">
@@ -58108,7 +58167,7 @@
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="4" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="210" x14ac:dyDescent="0.25">
@@ -58160,7 +58219,7 @@
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
       <c r="M9" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="210" x14ac:dyDescent="0.25">
@@ -58206,7 +58265,7 @@
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="4" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58233,7 +58292,7 @@
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
-    <row r="13" spans="1:13" ht="210" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="195" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="str">
         <f>IF(receta!A13="","",receta!A13)</f>
         <v>Bellini</v>
@@ -58254,7 +58313,7 @@
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="4" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58282,7 +58341,7 @@
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="4" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58316,13 +58375,13 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -58408,7 +58467,7 @@
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="4" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -58460,7 +58519,7 @@
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="4" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="375" x14ac:dyDescent="0.25">
@@ -58508,7 +58567,7 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="4" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="345" x14ac:dyDescent="0.25">
@@ -58556,7 +58615,7 @@
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="4" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58584,7 +58643,7 @@
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="4" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="375" x14ac:dyDescent="0.25">
@@ -58610,7 +58669,7 @@
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="4" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58636,7 +58695,7 @@
       <c r="K28" s="5"/>
       <c r="L28" s="5"/>
       <c r="M28" s="4" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="360" x14ac:dyDescent="0.25">
@@ -58662,7 +58721,7 @@
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="4" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58677,7 +58736,7 @@
         <v>672</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
@@ -58688,7 +58747,7 @@
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="4" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58705,19 +58764,25 @@
       <c r="D31" s="4" t="s">
         <v>426</v>
       </c>
-      <c r="E31" s="1"/>
-      <c r="F31" s="1"/>
-      <c r="G31" s="1"/>
+      <c r="E31" s="1" t="s">
+        <v>1010</v>
+      </c>
+      <c r="F31" s="5" t="s">
+        <v>1007</v>
+      </c>
+      <c r="G31" s="4" t="s">
+        <v>1008</v>
+      </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
       <c r="J31" s="1"/>
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="4" t="s">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="255" x14ac:dyDescent="0.25">
+        <v>985</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="240" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="str">
         <f>IF(receta!A32="","",receta!A32)</f>
         <v>Cléry Durazno</v>
@@ -58796,7 +58861,7 @@
       <c r="K34" s="5"/>
       <c r="L34" s="5"/>
       <c r="M34" s="4" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -58840,7 +58905,7 @@
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -58868,7 +58933,7 @@
       <c r="K37" s="5"/>
       <c r="L37" s="5"/>
       <c r="M37" s="4" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="255" x14ac:dyDescent="0.25">
@@ -58894,7 +58959,7 @@
       <c r="K38" s="5"/>
       <c r="L38" s="5"/>
       <c r="M38" s="4" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="75" x14ac:dyDescent="0.25">
@@ -58935,16 +59000,16 @@
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="1" t="s">
+        <v>931</v>
+      </c>
+      <c r="I40" s="5" t="s">
         <v>932</v>
-      </c>
-      <c r="I40" s="5" t="s">
-        <v>933</v>
       </c>
       <c r="J40" s="4"/>
       <c r="K40" s="5"/>
       <c r="L40" s="5"/>
       <c r="M40" s="4" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="210" x14ac:dyDescent="0.25">
@@ -58992,7 +59057,7 @@
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="M42" s="4" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="270" x14ac:dyDescent="0.25">
@@ -59020,7 +59085,7 @@
       <c r="K43" s="5"/>
       <c r="L43" s="5"/>
       <c r="M43" s="4" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -59077,7 +59142,7 @@
       </c>
       <c r="C46" s="4"/>
       <c r="D46" s="4" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>185</v>
@@ -59092,7 +59157,7 @@
       <c r="K46" s="5"/>
       <c r="L46" s="5"/>
       <c r="M46" s="4" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -59120,7 +59185,7 @@
       <c r="K47" s="5"/>
       <c r="L47" s="5"/>
       <c r="M47" s="4" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="315" x14ac:dyDescent="0.25">
@@ -59168,14 +59233,16 @@
         <v>773</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
       <c r="J49" s="1"/>
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
-      <c r="M49" s="1"/>
+      <c r="M49" s="4" t="s">
+        <v>1012</v>
+      </c>
     </row>
     <row r="50" spans="1:13" ht="255" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="str">
@@ -59194,7 +59261,7 @@
         <v>484</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>326</v>
@@ -59206,10 +59273,10 @@
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
       <c r="M50" s="4" t="s">
-        <v>968</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="str">
         <f>IF(receta!A51="","",receta!A51)</f>
         <v>Espresso Martini</v>
@@ -59228,7 +59295,7 @@
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
       <c r="M51" s="1" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="150" x14ac:dyDescent="0.25">
@@ -59260,7 +59327,7 @@
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
       <c r="M52" s="4" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="390" x14ac:dyDescent="0.25">
@@ -59281,7 +59348,9 @@
       <c r="F53" s="1" t="s">
         <v>405</v>
       </c>
-      <c r="G53" s="1"/>
+      <c r="G53" s="4" t="s">
+        <v>1011</v>
+      </c>
       <c r="H53" s="1" t="s">
         <v>385</v>
       </c>
@@ -59292,7 +59361,7 @@
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="4" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59318,7 +59387,7 @@
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
       <c r="M54" s="4" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
@@ -59364,7 +59433,7 @@
         <v>475</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -59372,7 +59441,7 @@
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
       <c r="M56" s="4" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59400,7 +59469,7 @@
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
       <c r="M57" s="4" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="150" x14ac:dyDescent="0.25">
@@ -59424,7 +59493,7 @@
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="4" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59454,7 +59523,7 @@
       <c r="K59" s="5"/>
       <c r="L59" s="5"/>
       <c r="M59" s="4" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -59476,7 +59545,7 @@
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
       <c r="M60" s="4" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="165" x14ac:dyDescent="0.25">
@@ -59492,10 +59561,10 @@
         <v>389</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="4"/>
@@ -59504,7 +59573,7 @@
       <c r="K61" s="1"/>
       <c r="L61" s="1"/>
       <c r="M61" s="4" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="345" x14ac:dyDescent="0.25">
@@ -59530,7 +59599,7 @@
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
       <c r="M62" s="4" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59563,10 +59632,10 @@
         <v>770</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="M63" s="4" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -59588,7 +59657,7 @@
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
       <c r="M64" s="4" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59612,7 +59681,7 @@
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
       <c r="M65" s="1" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="375" x14ac:dyDescent="0.25">
@@ -59660,7 +59729,7 @@
       <c r="K67" s="5"/>
       <c r="L67" s="5"/>
       <c r="M67" s="4" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="68" spans="1:13" ht="330" x14ac:dyDescent="0.25">
@@ -59670,7 +59739,7 @@
       </c>
       <c r="B68" s="1"/>
       <c r="C68" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>598</v>
@@ -59688,7 +59757,7 @@
       <c r="K68" s="5"/>
       <c r="L68" s="5"/>
       <c r="M68" s="4" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="69" spans="1:13" ht="300" x14ac:dyDescent="0.25">
@@ -59716,7 +59785,7 @@
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
       <c r="M69" s="4" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -59744,7 +59813,7 @@
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
       <c r="M70" s="4" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -59770,7 +59839,7 @@
       <c r="K71" s="5"/>
       <c r="L71" s="5"/>
       <c r="M71" s="4" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="72" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60090,7 +60159,7 @@
       <c r="K84" s="1"/>
       <c r="L84" s="1"/>
       <c r="M84" s="4" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -60120,7 +60189,7 @@
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
       <c r="M85" s="4" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -60170,7 +60239,7 @@
       <c r="K87" s="5"/>
       <c r="L87" s="5"/>
       <c r="M87" s="4" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="88" spans="1:13" ht="360" x14ac:dyDescent="0.25">
@@ -60359,7 +60428,9 @@
       <c r="J95" s="1"/>
       <c r="K95" s="1"/>
       <c r="L95" s="1"/>
-      <c r="M95" s="1"/>
+      <c r="M95" s="4" t="s">
+        <v>1004</v>
+      </c>
     </row>
     <row r="96" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="str">
@@ -60381,7 +60452,7 @@
       <c r="L96" s="1"/>
       <c r="M96" s="1"/>
     </row>
-    <row r="97" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="str">
         <f>IF(receta!A97="","",receta!A97)</f>
         <v>Mojito Maracuyá</v>
@@ -60390,16 +60461,24 @@
       <c r="C97" s="4" t="s">
         <v>582</v>
       </c>
-      <c r="D97" s="4"/>
-      <c r="E97" s="1"/>
-      <c r="F97" s="1"/>
+      <c r="D97" s="4" t="s">
+        <v>1002</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>1006</v>
+      </c>
+      <c r="F97" s="5" t="s">
+        <v>1005</v>
+      </c>
       <c r="G97" s="1"/>
       <c r="H97" s="4"/>
       <c r="I97" s="1"/>
       <c r="J97" s="1"/>
       <c r="K97" s="1"/>
       <c r="L97" s="1"/>
-      <c r="M97" s="1"/>
+      <c r="M97" s="4" t="s">
+        <v>1003</v>
+      </c>
     </row>
     <row r="98" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="str">
@@ -60444,7 +60523,7 @@
       <c r="K99" s="5"/>
       <c r="L99" s="5"/>
       <c r="M99" s="4" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="100" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -60518,7 +60597,7 @@
       <c r="K102" s="1"/>
       <c r="L102" s="1"/>
       <c r="M102" s="4" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="103" spans="1:13" ht="150" x14ac:dyDescent="0.25">
@@ -60592,7 +60671,7 @@
       <c r="K105" s="1"/>
       <c r="L105" s="1"/>
       <c r="M105" s="4" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="106" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -60657,7 +60736,7 @@
       </c>
       <c r="G108" s="1"/>
       <c r="H108" s="1" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="I108" s="5" t="s">
         <v>256</v>
@@ -60666,7 +60745,7 @@
       <c r="K108" s="1"/>
       <c r="L108" s="1"/>
       <c r="M108" s="4" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="109" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -60689,7 +60768,7 @@
       <c r="L109" s="1"/>
       <c r="M109" s="1"/>
     </row>
-    <row r="110" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" ht="330" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="str">
         <f>IF(receta!A110="","",receta!A110)</f>
         <v>Penicilina</v>
@@ -60700,7 +60779,9 @@
       <c r="C110" s="4" t="s">
         <v>677</v>
       </c>
-      <c r="D110" s="1"/>
+      <c r="D110" s="4" t="s">
+        <v>1014</v>
+      </c>
       <c r="E110" s="4" t="s">
         <v>587</v>
       </c>
@@ -60713,7 +60794,9 @@
       <c r="J110" s="4"/>
       <c r="K110" s="5"/>
       <c r="L110" s="5"/>
-      <c r="M110" s="1"/>
+      <c r="M110" s="4" t="s">
+        <v>1015</v>
+      </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="str">
@@ -60786,7 +60869,7 @@
       <c r="K113" s="5"/>
       <c r="L113" s="5"/>
       <c r="M113" s="4" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.25">
@@ -60880,7 +60963,7 @@
       <c r="K117" s="5"/>
       <c r="L117" s="5"/>
       <c r="M117" s="4" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="118" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -61028,7 +61111,7 @@
       <c r="K123" s="5"/>
       <c r="L123" s="5"/>
       <c r="M123" s="4" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="124" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -61155,7 +61238,7 @@
         <v>370</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="E129" s="1"/>
       <c r="F129" s="1"/>
@@ -61166,7 +61249,7 @@
       <c r="K129" s="1"/>
       <c r="L129" s="1"/>
       <c r="M129" s="4" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="130" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -61278,7 +61361,7 @@
       <c r="K134" s="5"/>
       <c r="L134" s="5"/>
       <c r="M134" s="4" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="135" spans="1:13" ht="300" x14ac:dyDescent="0.25">
@@ -61290,25 +61373,25 @@
         <v>656</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="E135" s="1"/>
       <c r="F135" s="1"/>
       <c r="G135" s="1"/>
       <c r="H135" s="1" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="I135" s="5" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="J135" s="1"/>
       <c r="K135" s="1"/>
       <c r="L135" s="1"/>
       <c r="M135" s="4" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="136" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -61376,7 +61459,7 @@
       <c r="K138" s="1"/>
       <c r="L138" s="1"/>
       <c r="M138" s="4" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="139" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -61443,7 +61526,7 @@
         <v>688</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="E141" s="4" t="s">
         <v>615</v>
@@ -61510,7 +61593,7 @@
       <c r="K143" s="1"/>
       <c r="L143" s="1"/>
       <c r="M143" s="4" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="144" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -61538,7 +61621,7 @@
       <c r="K144" s="1"/>
       <c r="L144" s="1"/>
       <c r="M144" s="4" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="145" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -61612,7 +61695,7 @@
       <c r="K147" s="5"/>
       <c r="L147" s="5"/>
       <c r="M147" s="4" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="148" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -61692,7 +61775,7 @@
       <c r="K150" s="1"/>
       <c r="L150" s="1"/>
       <c r="M150" s="4" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="151" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -61803,7 +61886,7 @@
         <v>775</v>
       </c>
       <c r="L154" s="26" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="M154" s="1"/>
     </row>
@@ -61942,7 +62025,7 @@
       <c r="K159" s="1"/>
       <c r="L159" s="1"/>
       <c r="M159" s="4" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="160" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -62040,7 +62123,7 @@
       <c r="K163" s="1"/>
       <c r="L163" s="1"/>
       <c r="M163" s="4" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="164" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62098,7 +62181,7 @@
       <c r="K165" s="1"/>
       <c r="L165" s="1"/>
       <c r="M165" s="4" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="166" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62158,7 +62241,7 @@
       </c>
       <c r="B168" s="1"/>
       <c r="C168" s="4" t="s">
-        <v>896</v>
+        <v>1009</v>
       </c>
       <c r="D168" s="4"/>
       <c r="E168" s="1"/>
@@ -62169,7 +62252,9 @@
       <c r="J168" s="1"/>
       <c r="K168" s="1"/>
       <c r="L168" s="1"/>
-      <c r="M168" s="1"/>
+      <c r="M168" s="4" t="s">
+        <v>1013</v>
+      </c>
     </row>
     <row r="169" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="str">
@@ -62177,10 +62262,10 @@
         <v>Chardonnay Sour</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="D169" s="4"/>
       <c r="E169" s="1"/>
@@ -62199,13 +62284,13 @@
         <v>Carmenere Sour</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>472</v>
@@ -62220,7 +62305,7 @@
       <c r="K170" s="1"/>
       <c r="L170" s="1"/>
       <c r="M170" s="4" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="171" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62229,10 +62314,10 @@
         <v>Jerez Sour</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="D171" s="4" t="s">
         <v>892</v>
@@ -62246,7 +62331,7 @@
       <c r="K171" s="1"/>
       <c r="L171" s="1"/>
       <c r="M171" s="4" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="172" spans="1:13" x14ac:dyDescent="0.25">
@@ -63744,9 +63829,11 @@
     <hyperlink ref="I40" r:id="rId67" xr:uid="{18514F5E-18F5-44D8-BD76-F70D6B1E8FC6}"/>
     <hyperlink ref="I135" r:id="rId68" xr:uid="{6B3689A7-4101-496D-821F-20A52B38FF72}"/>
     <hyperlink ref="F16" r:id="rId69" xr:uid="{816C87E7-4A29-4F45-8BD1-D79076FE292E}"/>
+    <hyperlink ref="F97" r:id="rId70" xr:uid="{B4B59D4D-272B-4AEE-820B-4D18D5925638}"/>
+    <hyperlink ref="F31" r:id="rId71" xr:uid="{295A8609-0926-4F9B-85D6-EFECD8ABD350}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId70"/>
+  <pageSetup orientation="portrait" r:id="rId72"/>
 </worksheet>
 </file>
 

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{867B78F5-3A76-414E-85CC-EE97F846E210}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B50E5487-5DF1-4FA8-AC83-69AA240CCCBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1560" uniqueCount="1016">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1562" uniqueCount="1018">
   <si>
     <t>Ramazzotti Spritz</t>
   </si>
@@ -4782,6 +4782,14 @@
   <si>
     <t>whisky.jpg
 Aviso publicitario de Ballantine’s Scotch de 1935, que alude al tradicional partido de fútbol americano Harvard–Yale, conocido como The Game, una de las rivalidades universitarias más antiguas de Estados Unidos.</t>
+  </si>
+  <si>
+    <t>Aberfan.jpg
+Vista aérea de Aberfan, Gales, tras el desastre del 21 de octubre de 1966.</t>
+  </si>
+  <si>
+    <t>Papaya.jpg
+Papayas chilenas (Vasconcellea pubescens). A diferencia de la papaya tropical común (Carica papaya), la papaya chilena es más pequeña y aromática.</t>
   </si>
 </sst>
 </file>
@@ -60646,7 +60654,9 @@
       <c r="J104" s="1"/>
       <c r="K104" s="5"/>
       <c r="L104" s="5"/>
-      <c r="M104" s="1"/>
+      <c r="M104" s="4" t="s">
+        <v>1016</v>
+      </c>
     </row>
     <row r="105" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="str">
@@ -61226,7 +61236,9 @@
       <c r="J128" s="1"/>
       <c r="K128" s="1"/>
       <c r="L128" s="1"/>
-      <c r="M128" s="1"/>
+      <c r="M128" s="4" t="s">
+        <v>1017</v>
+      </c>
     </row>
     <row r="129" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="str">

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B50E5487-5DF1-4FA8-AC83-69AA240CCCBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09CC4E2A-B402-45B0-B3FF-75FE32EFC56F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1562" uniqueCount="1018">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1563" uniqueCount="1019">
   <si>
     <t>Ramazzotti Spritz</t>
   </si>
@@ -4790,6 +4790,10 @@
   <si>
     <t>Papaya.jpg
 Papayas chilenas (Vasconcellea pubescens). A diferencia de la papaya tropical común (Carica papaya), la papaya chilena es más pequeña y aromática.</t>
+  </si>
+  <si>
+    <t>tree_cat.jpg
+Дерево и кошка (The Tree and the Cat, 1983) es un cortometraje de animación soviético dirigido por Evgeniy (Yevgeniy) Sivokon y producido en el estudio Kievnauchfilm.</t>
   </si>
 </sst>
 </file>
@@ -61026,7 +61030,9 @@
       <c r="J119" s="1"/>
       <c r="K119" s="5"/>
       <c r="L119" s="5"/>
-      <c r="M119" s="1"/>
+      <c r="M119" s="4" t="s">
+        <v>1018</v>
+      </c>
     </row>
     <row r="120" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="str">

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{09CC4E2A-B402-45B0-B3FF-75FE32EFC56F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70ACF0BF-4039-46A2-BF03-D7CF942B9D42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
@@ -4793,7 +4793,7 @@
   </si>
   <si>
     <t>tree_cat.jpg
-Дерево и кошка (The Tree and the Cat, 1983) es un cortometraje de animación soviético dirigido por Evgeniy (Yevgeniy) Sivokon y producido en el estudio Kievnauchfilm.</t>
+Дерево и кошка (El Árbol y la Gata, 1983) es un cortometraje de animación soviético dirigido por Evgeniy Sivokon y producido en el estudio Kievnauchfilm.</t>
   </si>
 </sst>
 </file>

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70ACF0BF-4039-46A2-BF03-D7CF942B9D42}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB442779-3323-48FE-AC20-6ACD8268D68B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1563" uniqueCount="1019">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1566" uniqueCount="1022">
   <si>
     <t>Ramazzotti Spritz</t>
   </si>
@@ -2431,9 +2431,6 @@
 Originalmente, se preparaba con gin seco (London Dry), en contraposición al Tom Collins, que usaba Old Tom Gin, una versión más dulce. Sin embargo, con el paso del tiempo, especialmente en Estados Unidos y Sudamérica, el John Collins comenzó a prepararse también con whiskey, lo que ha generado cierta ambigüedad. Por ello, en bares contemporáneos conviene especificar el destilado al pedirlo, ya que puede servirse tanto con gin como con whiskey, según la interpretación del bartender.</t>
   </si>
   <si>
-    <t>El Laguna Azul (Blue Lagoon, en inglés) es un cóctel vistoso y refrescante, reconocido por su color azul intenso y su perfil cítrico y dulce. Es popular en fiestas, barras veraniegas y cartas de coctelería por su atractivo visual y su sencillez de preparación. Existen variantes que se preparan solo con jugo de limón, mientras que otras incorporan gaseosas de limón, como Sprite o 7Up, para añadir efervescencia y un toque más suave.</t>
-  </si>
-  <si>
     <t>El London Mule es una variante del clásico Moscow Mule, pero reemplazando el vodka por gin, lo que le da un perfil más aromático y herbal.</t>
   </si>
   <si>
@@ -4478,10 +4475,6 @@
 Retrato juvenil de Luis Alberto Spinetta, realizado a comienzos de los años setenta.</t>
   </si>
   <si>
-    <t>briceño.jpg
-Cristóbal Briceño, reconocido cantante, compositor y guitarrista chileno. Vocalista y líder de proyectos musicales como Ases Falsos, Fother Muckers, Los Mil Jinetes y Las Chaquetas Amarillas, entre otros.</t>
-  </si>
-  <si>
     <t>garcia.jpg
 Charly García fotografiado por Hilda Lizarazu (1986)</t>
   </si>
@@ -4794,6 +4787,32 @@
   <si>
     <t>tree_cat.jpg
 Дерево и кошка (El Árbol y la Gata, 1983) es un cortometraje de animación soviético dirigido por Evgeniy Sivokon y producido en el estudio Kievnauchfilm.</t>
+  </si>
+  <si>
+    <t>tropezon.jpg
+Micro Tropezón en Pudahuel, año 1978. Fotografía análoga en color. Donante: Mirta Guerrero. Archivo de la Biblioteca Pública N° 11 “Jaime Quilán”, Pudahuel.</t>
+  </si>
+  <si>
+    <t>piscolero.jpg
+Ilustración contemporánea de estilo retro, creada como pieza decorativa o humorística inspirada en la gráfica publicitaria de mediados del siglo XX.</t>
+  </si>
+  <si>
+    <t>laguna.jpg
+Afiche ilustrado del cóctel Laguna Azul.</t>
+  </si>
+  <si>
+    <t>El mar en un vaso
+Durante siglos, los cócteles tuvieron los colores de la tierra: ámbar, rojo, dorado, transparente. El azul parecía imposible, porque casi no existe en la naturaleza comestible.
+Todo cambió cuando el curaçao, un licor de naranja del Caribe, comenzó a teñirse de azul a mediados del siglo XX. El sabor seguía siendo el mismo, pero el efecto era completamente nuevo, el bartender podía servir algo que parecía agua de mar.
+La época estaba lista para ese color. En los años 50 y 60, la moda tropical y los bares tiki invitaron a beber paisajes. Surgieron entonces cócteles como el Blue Hawaiian, el Swimming Pool y el Laguna Azul. Su nombre evocaba simplemente una laguna luminosa, una postal líquida.
+Décadas más tarde, el cine reforzó ese imaginario. Películas como La laguna azul terminaron de fijar la asociación entre el azul brillante y la idea de paraíso. El cóctel no nació de la película, pero ambos compartían el mismo sueño: el de una isla lejana, suspendida en el tiempo.
+Hubo años en que los tragos azules perdieron prestigio, víctimas del exceso de azúcar y de la coctelería descuidada. Pero hoy han vuelto, redescubiertos con mejores técnicas y nuevos equilibrios.
+Y tal vez esa sea la razón de su encanto: porque en el fondo, un cóctel azul sigue siendo lo mismo que fue desde el principio, la ilusión, breve y luminosa, de sostener el mar entre las manos.</t>
+  </si>
+  <si>
+    <t>El Laguna Azul (Blue Lagoon, en inglés) es un cóctel vistoso y refrescante, reconocido por su color azul intenso y su perfil cítrico y dulce. Es popular en fiestas, barras veraniegas y cartas de coctelería por su atractivo visual y su sencillez de preparación.
+La versión más aceptada sitúa su creación en la década de 1960, cuando el bartender Andy MacElhone, del Harry’s New York Bar de París, buscó un trago que evocara el color luminoso de una laguna tropical. El resultado fue una bebida que no solo destacaba por su sabor, sino también por su apariencia, algo poco habitual en la coctelería de la época.
+Existen variantes que se preparan solo con jugo de limón, mientras que otras incorporan gaseosas de limón, como Sprite o 7Up, para añadir efervescencia y un carácter más suave.</t>
   </si>
 </sst>
 </file>
@@ -5471,10 +5490,10 @@
         <v>78</v>
       </c>
       <c r="O1" s="27" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="P1" s="27" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="Q1" s="27" t="s">
         <v>79</v>
@@ -5486,13 +5505,13 @@
         <v>265</v>
       </c>
       <c r="T1" s="27" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="U1" s="27" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="V1" s="27" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="W1" s="27" t="s">
         <v>80</v>
@@ -5507,16 +5526,16 @@
         <v>196</v>
       </c>
       <c r="AA1" s="27" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="AB1" s="27" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="AC1" s="27" t="s">
+        <v>904</v>
+      </c>
+      <c r="AD1" s="27" t="s">
         <v>905</v>
-      </c>
-      <c r="AD1" s="27" t="s">
-        <v>906</v>
       </c>
       <c r="AE1" s="27" t="s">
         <v>82</v>
@@ -5543,7 +5562,7 @@
         <v>87</v>
       </c>
       <c r="AM1" s="27" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="AN1" s="27" t="s">
         <v>223</v>
@@ -5570,13 +5589,13 @@
         <v>200</v>
       </c>
       <c r="AV1" s="27" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="AW1" s="27" t="s">
         <v>209</v>
       </c>
       <c r="AX1" s="27" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="AY1" s="27" t="s">
         <v>230</v>
@@ -5666,16 +5685,16 @@
         <v>152</v>
       </c>
       <c r="CB1" s="8" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="CC1" s="8" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="CD1" s="7" t="s">
         <v>280</v>
       </c>
       <c r="CE1" s="7" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="CF1" s="8" t="s">
         <v>198</v>
@@ -5708,10 +5727,10 @@
         <v>215</v>
       </c>
       <c r="CP1" s="8" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="CQ1" s="8" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="CR1" s="7" t="s">
         <v>95</v>
@@ -5723,7 +5742,7 @@
         <v>97</v>
       </c>
       <c r="CU1" s="7" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="CV1" s="7" t="s">
         <v>386</v>
@@ -5732,7 +5751,7 @@
         <v>98</v>
       </c>
       <c r="CX1" s="7" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="CY1" s="7" t="s">
         <v>99</v>
@@ -5747,22 +5766,22 @@
         <v>154</v>
       </c>
       <c r="DC1" s="8" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="DD1" s="18" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="DE1" s="18" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="DF1" s="18" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="DG1" s="18" t="s">
+        <v>847</v>
+      </c>
+      <c r="DH1" s="18" t="s">
         <v>848</v>
-      </c>
-      <c r="DH1" s="18" t="s">
-        <v>849</v>
       </c>
       <c r="DI1" s="15" t="s">
         <v>136</v>
@@ -5771,31 +5790,31 @@
         <v>135</v>
       </c>
       <c r="DK1" s="15" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="DL1" s="15" t="s">
+        <v>570</v>
+      </c>
+      <c r="DM1" s="15" t="s">
         <v>571</v>
       </c>
-      <c r="DM1" s="15" t="s">
-        <v>572</v>
-      </c>
       <c r="DN1" s="15" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="DO1" s="15" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="DP1" s="15" t="s">
+        <v>608</v>
+      </c>
+      <c r="DQ1" s="15" t="s">
+        <v>818</v>
+      </c>
+      <c r="DR1" s="15" t="s">
         <v>609</v>
       </c>
-      <c r="DQ1" s="15" t="s">
-        <v>819</v>
-      </c>
-      <c r="DR1" s="15" t="s">
-        <v>610</v>
-      </c>
       <c r="DS1" s="15" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="DT1" s="15" t="s">
         <v>141</v>
@@ -5804,43 +5823,43 @@
         <v>237</v>
       </c>
       <c r="DV1" s="15" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="DW1" s="15" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="DX1" s="15" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="DY1" s="15" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="DZ1" s="15" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="EA1" s="15" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="EB1" s="21" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="EC1" s="21" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="ED1" s="25" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="EE1" s="12" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="EF1" s="14" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="EG1" s="12" t="s">
         <v>234</v>
       </c>
       <c r="EH1" s="12" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="EI1" s="12" t="s">
         <v>286</v>
@@ -5855,19 +5874,19 @@
         <v>125</v>
       </c>
       <c r="EM1" s="17" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="EN1" s="17" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="EO1" s="17" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="EP1" s="19" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="EQ1" s="19" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="ER1" s="19" t="s">
         <v>126</v>
@@ -5882,7 +5901,7 @@
         <v>231</v>
       </c>
       <c r="EV1" s="20" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="EW1" s="20" t="s">
         <v>232</v>
@@ -7320,13 +7339,13 @@
     </row>
     <row r="10" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>51</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D10" s="2">
         <v>300</v>
@@ -7680,13 +7699,13 @@
     </row>
     <row r="12" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>55</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D12" s="2">
         <v>200</v>
@@ -8388,7 +8407,7 @@
     </row>
     <row r="16" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>278</v>
@@ -9472,7 +9491,7 @@
     </row>
     <row r="22" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>53</v>
@@ -10180,7 +10199,7 @@
     </row>
     <row r="26" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>50</v>
@@ -10358,7 +10377,7 @@
     </row>
     <row r="27" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>51</v>
@@ -10890,7 +10909,7 @@
     </row>
     <row r="30" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>278</v>
@@ -11068,7 +11087,7 @@
     </row>
     <row r="31" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>278</v>
@@ -11246,7 +11265,7 @@
     </row>
     <row r="32" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>278</v>
@@ -11424,7 +11443,7 @@
     </row>
     <row r="33" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>55</v>
@@ -11958,7 +11977,7 @@
     </row>
     <row r="36" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>54</v>
@@ -12134,13 +12153,13 @@
     </row>
     <row r="37" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D37" s="2">
         <v>300</v>
@@ -12316,7 +12335,7 @@
     </row>
     <row r="38" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>50</v>
@@ -14442,7 +14461,7 @@
     </row>
     <row r="50" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>53</v>
@@ -14622,7 +14641,7 @@
     </row>
     <row r="51" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>55</v>
@@ -16930,7 +16949,7 @@
     </row>
     <row r="64" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>50</v>
@@ -17286,7 +17305,7 @@
     </row>
     <row r="66" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>49</v>
@@ -18536,10 +18555,10 @@
     </row>
     <row r="73" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>562</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>563</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>564</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>69</v>
@@ -18716,7 +18735,7 @@
     </row>
     <row r="74" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>51</v>
@@ -19968,7 +19987,7 @@
     </row>
     <row r="81" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>51</v>
@@ -20146,7 +20165,7 @@
     </row>
     <row r="82" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>50</v>
@@ -20510,7 +20529,7 @@
     </row>
     <row r="84" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>51</v>
@@ -20686,7 +20705,7 @@
     </row>
     <row r="85" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>51</v>
@@ -21740,10 +21759,10 @@
     </row>
     <row r="91" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>682</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>683</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>684</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>63</v>
@@ -22100,7 +22119,7 @@
     </row>
     <row r="93" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>53</v>
@@ -22990,7 +23009,7 @@
     </row>
     <row r="98" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>49</v>
@@ -24428,7 +24447,7 @@
     </row>
     <row r="106" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>53</v>
@@ -24784,7 +24803,7 @@
     </row>
     <row r="108" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>50</v>
@@ -25152,13 +25171,13 @@
     </row>
     <row r="110" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D110" s="2">
         <v>300</v>
@@ -25332,7 +25351,7 @@
     </row>
     <row r="111" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>50</v>
@@ -26572,7 +26591,7 @@
     </row>
     <row r="118" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>50</v>
@@ -27286,7 +27305,7 @@
     </row>
     <row r="122" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>50</v>
@@ -27816,7 +27835,7 @@
     </row>
     <row r="125" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A125" s="13" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>278</v>
@@ -28000,7 +28019,7 @@
     </row>
     <row r="126" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>278</v>
@@ -28716,7 +28735,7 @@
     </row>
     <row r="130" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>151</v>
@@ -29954,7 +29973,7 @@
     </row>
     <row r="137" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A137" s="13" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>278</v>
@@ -30312,7 +30331,7 @@
     </row>
     <row r="139" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>52</v>
@@ -30674,7 +30693,7 @@
     </row>
     <row r="141" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>55</v>
@@ -31032,7 +31051,7 @@
     </row>
     <row r="143" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>51</v>
@@ -31396,7 +31415,7 @@
     </row>
     <row r="145" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>53</v>
@@ -31748,7 +31767,7 @@
     </row>
     <row r="147" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>51</v>
@@ -31924,7 +31943,7 @@
     </row>
     <row r="148" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>51</v>
@@ -32100,7 +32119,7 @@
     </row>
     <row r="149" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>50</v>
@@ -32454,13 +32473,13 @@
     </row>
     <row r="151" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D151" s="2">
         <v>300</v>
@@ -32634,7 +32653,7 @@
     </row>
     <row r="152" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>53</v>
@@ -32813,13 +32832,13 @@
     </row>
     <row r="153" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D153" s="2">
         <v>300</v>
@@ -32993,7 +33012,7 @@
     </row>
     <row r="154" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>51</v>
@@ -33169,7 +33188,7 @@
     </row>
     <row r="155" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>54</v>
@@ -33345,7 +33364,7 @@
     </row>
     <row r="156" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>53</v>
@@ -33523,7 +33542,7 @@
     </row>
     <row r="157" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>278</v>
@@ -33697,13 +33716,13 @@
     </row>
     <row r="158" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>278</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="D158" s="2">
         <v>1500</v>
@@ -33877,13 +33896,13 @@
     </row>
     <row r="159" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>278</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="D159" s="2">
         <v>1500</v>
@@ -34067,7 +34086,7 @@
     </row>
     <row r="160" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>197</v>
@@ -34239,7 +34258,7 @@
     </row>
     <row r="161" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>51</v>
@@ -34423,7 +34442,7 @@
     </row>
     <row r="162" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>51</v>
@@ -34599,7 +34618,7 @@
     </row>
     <row r="163" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>51</v>
@@ -34779,7 +34798,7 @@
     </row>
     <row r="164" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>53</v>
@@ -34957,7 +34976,7 @@
     </row>
     <row r="165" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>51</v>
@@ -35133,7 +35152,7 @@
     </row>
     <row r="166" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>50</v>
@@ -35315,7 +35334,7 @@
     </row>
     <row r="167" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>53</v>
@@ -35493,7 +35512,7 @@
     </row>
     <row r="168" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>55</v>
@@ -35667,7 +35686,7 @@
     </row>
     <row r="169" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>55</v>
@@ -35845,7 +35864,7 @@
     </row>
     <row r="170" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>53</v>
@@ -36021,7 +36040,7 @@
     </row>
     <row r="171" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>55</v>
@@ -48505,16 +48524,16 @@
         <v>129</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>141</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="J1" s="8" t="s">
         <v>237</v>
@@ -48529,10 +48548,10 @@
         <v>283</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="P1" s="8" t="s">
         <v>132</v>
@@ -48568,7 +48587,7 @@
         <v>131</v>
       </c>
       <c r="AA1" s="7" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AB1" s="7" t="s">
         <v>199</v>
@@ -57959,6 +57978,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43DB3A21-6E97-43C0-9768-D0796C62C1D9}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:M250"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -57982,7 +58002,7 @@
         <v>72</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>318</v>
@@ -57997,7 +58017,7 @@
         <v>315</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>316</v>
@@ -58006,19 +58026,19 @@
         <v>317</v>
       </c>
       <c r="J1" s="7" t="s">
+        <v>766</v>
+      </c>
+      <c r="K1" s="7" t="s">
         <v>767</v>
       </c>
-      <c r="K1" s="7" t="s">
-        <v>768</v>
-      </c>
       <c r="L1" s="7" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>816</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="270" x14ac:dyDescent="0.25">
+        <v>815</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="270" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="str">
         <f>IF(receta!A2="","",receta!A2)</f>
         <v>Agua de Valencia</v>
@@ -58043,16 +58063,16 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="4" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="3" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="str">
         <f>IF(receta!A3="","",receta!A3)</f>
         <v>Alejandra</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>367</v>
@@ -58070,7 +58090,7 @@
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:13" ht="180" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="180" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="str">
         <f>IF(receta!A4="","",receta!A4)</f>
         <v>Alevosía</v>
@@ -58089,7 +58109,7 @@
         <v>239</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="5"/>
@@ -58098,19 +58118,19 @@
       <c r="L4" s="5"/>
       <c r="M4" s="1"/>
     </row>
-    <row r="5" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="str">
         <f>IF(receta!A5="","",receta!A5)</f>
         <v>Alexander</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>449</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>366</v>
@@ -58125,16 +58145,16 @@
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
       <c r="M5" s="4" t="s">
-        <v>920</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="270" x14ac:dyDescent="0.25">
+        <v>919</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="270" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="str">
         <f>IF(receta!A6="","",receta!A6)</f>
         <v>Amaretto Sour</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>353</v>
@@ -58153,10 +58173,10 @@
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="4" t="s">
-        <v>960</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="270" x14ac:dyDescent="0.25">
+        <v>958</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="270" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="str">
         <f>IF(receta!A7="","",receta!A7)</f>
         <v>Amaretto Spritz</v>
@@ -58179,10 +58199,10 @@
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="4" t="s">
-        <v>961</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="210" x14ac:dyDescent="0.25">
+        <v>959</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="210" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="str">
         <f>IF(receta!A8="","",receta!A8)</f>
         <v>Americano</v>
@@ -58206,7 +58226,7 @@
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
     </row>
-    <row r="9" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="str">
         <f>IF(receta!A9="","",receta!A9)</f>
         <v>Amiga Mía</v>
@@ -58231,19 +58251,19 @@
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
       <c r="M9" s="1" t="s">
-        <v>921</v>
-      </c>
-    </row>
-    <row r="10" spans="1:13" ht="210" x14ac:dyDescent="0.25">
+        <v>920</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="210" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="str">
         <f>IF(receta!A10="","",receta!A10)</f>
         <v>Andes Refresh</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="11"/>
@@ -58256,17 +58276,17 @@
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
     </row>
-    <row r="11" spans="1:13" ht="390" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="390" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="str">
         <f>IF(receta!A11="","",receta!A11)</f>
         <v>Aperol Spritz</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="4" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -58277,22 +58297,22 @@
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="4" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="12" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>976</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="str">
         <f>IF(receta!A12="","",receta!A12)</f>
         <v>Arándano Sour</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
@@ -58304,7 +58324,7 @@
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
-    <row r="13" spans="1:13" ht="195" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="195" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="str">
         <f>IF(receta!A13="","",receta!A13)</f>
         <v>Bellini</v>
@@ -58325,10 +58345,10 @@
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="4" t="s">
-        <v>980</v>
-      </c>
-    </row>
-    <row r="14" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>978</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="str">
         <f>IF(receta!A14="","",receta!A14)</f>
         <v>Bello Barrio</v>
@@ -58353,17 +58373,17 @@
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="4" t="s">
-        <v>922</v>
-      </c>
-    </row>
-    <row r="15" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>921</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="str">
         <f>IF(receta!A15="","",receta!A15)</f>
         <v>Bitter Batido</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="4" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>379</v>
@@ -58378,7 +58398,7 @@
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
     </row>
-    <row r="16" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="str">
         <f>IF(receta!A16="","",receta!A16)</f>
         <v>Blanco de Verano</v>
@@ -58387,13 +58407,13 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -58402,7 +58422,7 @@
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
     </row>
-    <row r="17" spans="1:13" ht="390" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="390" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="str">
         <f>IF(receta!A17="","",receta!A17)</f>
         <v>Bloody Mary</v>
@@ -58432,7 +58452,7 @@
       <c r="L17" s="10"/>
       <c r="M17" s="1"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="str">
         <f>IF(receta!A18="","",receta!A18)</f>
         <v>Bloody Mary (Sin Alcohol)</v>
@@ -58456,7 +58476,7 @@
       <c r="L18" s="5"/>
       <c r="M18" s="1"/>
     </row>
-    <row r="19" spans="1:13" ht="180" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="180" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="str">
         <f>IF(receta!A19="","",receta!A19)</f>
         <v>Blue Hawaii</v>
@@ -58479,10 +58499,10 @@
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="4" t="s">
-        <v>981</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="str">
         <f>IF(receta!A20="","",receta!A20)</f>
         <v>Blue Hawaiian</v>
@@ -58506,16 +58526,16 @@
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
     </row>
-    <row r="21" spans="1:13" ht="135" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="str">
         <f>IF(receta!A21="","",receta!A21)</f>
         <v>Borgoña</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="1"/>
@@ -58531,26 +58551,26 @@
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="4" t="s">
-        <v>924</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="375" x14ac:dyDescent="0.25">
+        <v>923</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="375" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="str">
         <f>IF(receta!A22="","",receta!A22)</f>
         <v>Caipiriña</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1" t="s">
+        <v>573</v>
+      </c>
+      <c r="F22" s="5" t="s">
         <v>574</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>575</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="1"/>
@@ -58560,7 +58580,7 @@
       <c r="L22" s="5"/>
       <c r="M22" s="1"/>
     </row>
-    <row r="23" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="str">
         <f>IF(receta!A23="","",receta!A23)</f>
         <v>Campari &amp; Vermouth Tonic</v>
@@ -58579,17 +58599,17 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="4" t="s">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="345" x14ac:dyDescent="0.25">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="str">
         <f>IF(receta!A24="","",receta!A24)</f>
         <v>Carajillo</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="4" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1" t="s">
@@ -58606,7 +58626,7 @@
       <c r="L24" s="5"/>
       <c r="M24" s="1"/>
     </row>
-    <row r="25" spans="1:13" ht="360" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" ht="360" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="str">
         <f>IF(receta!A25="","",receta!A25)</f>
         <v>Chilcano</v>
@@ -58627,50 +58647,50 @@
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="4" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="26" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="26" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="str">
         <f>IF(receta!A26="","",receta!A26)</f>
         <v>Chuflay</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="4" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="4" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="375" x14ac:dyDescent="0.25">
+        <v>998</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="375" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="str">
         <f>IF(receta!A27="","",receta!A27)</f>
         <v>Chupilca</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
@@ -58681,10 +58701,10 @@
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="4" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="str">
         <f>IF(receta!A28="","",receta!A28)</f>
         <v>Cimarrón</v>
@@ -58707,24 +58727,24 @@
       <c r="K28" s="5"/>
       <c r="L28" s="5"/>
       <c r="M28" s="4" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="360" x14ac:dyDescent="0.25">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="360" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="str">
         <f>IF(receta!A29="","",receta!A29)</f>
         <v>Clavo Oxidado</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="4" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
@@ -58733,22 +58753,22 @@
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="4" t="s">
-        <v>935</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>934</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="str">
         <f>IF(receta!A30="","",receta!A30)</f>
         <v>Cléry</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
@@ -58759,31 +58779,31 @@
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="4" t="s">
-        <v>936</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>935</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="str">
         <f>IF(receta!A31="","",receta!A31)</f>
         <v>Cléry Chirimoya</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>426</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -58791,19 +58811,19 @@
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="4" t="s">
-        <v>985</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="240" x14ac:dyDescent="0.25">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="240" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="str">
         <f>IF(receta!A32="","",receta!A32)</f>
         <v>Cléry Durazno</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1" t="s">
@@ -58820,25 +58840,25 @@
       <c r="L32" s="5"/>
       <c r="M32" s="1"/>
     </row>
-    <row r="33" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="str">
         <f>IF(receta!A33="","",receta!A33)</f>
         <v>Clover Club</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="D33" s="4" t="s">
+        <v>550</v>
+      </c>
+      <c r="E33" s="4" t="s">
         <v>551</v>
       </c>
-      <c r="E33" s="4" t="s">
-        <v>552</v>
-      </c>
       <c r="F33" s="1" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
@@ -58847,17 +58867,17 @@
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="4" t="s">
-        <v>886</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="255" x14ac:dyDescent="0.25">
+        <v>885</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="255" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="str">
         <f>IF(receta!A34="","",receta!A34)</f>
         <v>Cordillera</v>
       </c>
       <c r="B34" s="1"/>
       <c r="C34" s="4" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="1" t="s">
@@ -58873,19 +58893,19 @@
       <c r="K34" s="5"/>
       <c r="L34" s="5"/>
       <c r="M34" s="4" t="s">
-        <v>986</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="str">
         <f>IF(receta!A35="","",receta!A35)</f>
         <v>Cosmo Patagonia</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="1"/>
@@ -58898,14 +58918,14 @@
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
     </row>
-    <row r="36" spans="1:13" ht="165" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" ht="165" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="str">
         <f>IF(receta!A36="","",receta!A36)</f>
         <v>Cosmopolitan</v>
       </c>
       <c r="B36" s="1"/>
       <c r="C36" s="4" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
@@ -58917,19 +58937,19 @@
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1" t="s">
-        <v>965</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+        <v>963</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="str">
         <f>IF(receta!A37="","",receta!A37)</f>
         <v>Crepúsculo</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="4" t="s">
@@ -58945,24 +58965,24 @@
       <c r="K37" s="5"/>
       <c r="L37" s="5"/>
       <c r="M37" s="4" t="s">
-        <v>948</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="255" x14ac:dyDescent="0.25">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="255" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="str">
         <f>IF(receta!A38="","",receta!A38)</f>
         <v>Cuba Libre</v>
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="4" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D38" s="1"/>
       <c r="E38" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="1"/>
@@ -58971,10 +58991,10 @@
       <c r="K38" s="5"/>
       <c r="L38" s="5"/>
       <c r="M38" s="4" t="s">
-        <v>997</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+        <v>995</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="str">
         <f>IF(receta!A39="","",receta!A39)</f>
         <v>Cynar Spritz</v>
@@ -58994,7 +59014,7 @@
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
     </row>
-    <row r="40" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="str">
         <f>IF(receta!A40="","",receta!A40)</f>
         <v>Daiquiri</v>
@@ -59012,28 +59032,28 @@
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="1" t="s">
+        <v>930</v>
+      </c>
+      <c r="I40" s="5" t="s">
         <v>931</v>
-      </c>
-      <c r="I40" s="5" t="s">
-        <v>932</v>
       </c>
       <c r="J40" s="4"/>
       <c r="K40" s="5"/>
       <c r="L40" s="5"/>
       <c r="M40" s="4" t="s">
-        <v>945</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="210" x14ac:dyDescent="0.25">
+        <v>943</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="210" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="str">
         <f>IF(receta!A41="","",receta!A41)</f>
         <v>Dama Blanca</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="1"/>
@@ -59046,7 +59066,7 @@
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
     </row>
-    <row r="42" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="str">
         <f>IF(receta!A42="","",receta!A42)</f>
         <v>Dark &amp; Stormy</v>
@@ -59069,20 +59089,20 @@
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="M42" s="4" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="43" spans="1:13" ht="270" x14ac:dyDescent="0.25">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="43" spans="1:13" ht="270" hidden="1" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="str">
         <f>IF(receta!A43="","",receta!A43)</f>
         <v>Destornillador</v>
       </c>
       <c r="B43" s="1"/>
       <c r="C43" s="4" t="s">
+        <v>593</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>594</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>595</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="5"/>
@@ -59097,10 +59117,10 @@
       <c r="K43" s="5"/>
       <c r="L43" s="5"/>
       <c r="M43" s="4" t="s">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="44" spans="1:13" ht="135" x14ac:dyDescent="0.25">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="44" spans="1:13" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="str">
         <f>IF(receta!A44="","",receta!A44)</f>
         <v>Doug's Death</v>
@@ -59120,16 +59140,16 @@
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
     </row>
-    <row r="45" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="str">
         <f>IF(receta!A45="","",receta!A45)</f>
         <v>Dry Martini</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>393</v>
@@ -59144,17 +59164,17 @@
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
     </row>
-    <row r="46" spans="1:13" ht="285" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" ht="285" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="str">
         <f>IF(receta!A46="","",receta!A46)</f>
         <v>El Amor en los Tiempos del Covid</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="C46" s="4"/>
       <c r="D46" s="4" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>185</v>
@@ -59169,10 +59189,10 @@
       <c r="K46" s="5"/>
       <c r="L46" s="5"/>
       <c r="M46" s="4" t="s">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" ht="240" x14ac:dyDescent="0.25">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="240" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="str">
         <f>IF(receta!A47="","",receta!A47)</f>
         <v>Enemigo Íntimo</v>
@@ -59197,10 +59217,10 @@
       <c r="K47" s="5"/>
       <c r="L47" s="5"/>
       <c r="M47" s="4" t="s">
-        <v>944</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" ht="315" x14ac:dyDescent="0.25">
+        <v>942</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="315" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="str">
         <f>IF(receta!A48="","",receta!A48)</f>
         <v>Escarabajo</v>
@@ -59210,13 +59230,13 @@
         <v>381</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E48" s="1" t="s">
+        <v>599</v>
+      </c>
+      <c r="F48" s="5" t="s">
         <v>600</v>
-      </c>
-      <c r="F48" s="5" t="s">
-        <v>601</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="1"/>
@@ -59226,26 +59246,26 @@
       <c r="L48" s="5"/>
       <c r="M48" s="1"/>
     </row>
-    <row r="49" spans="1:13" ht="270" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" ht="270" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="str">
         <f>IF(receta!A49="","",receta!A49)</f>
         <v>Española</v>
       </c>
       <c r="B49" s="1"/>
       <c r="C49" s="4" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>373</v>
       </c>
       <c r="E49" s="1" t="s">
+        <v>771</v>
+      </c>
+      <c r="F49" s="5" t="s">
         <v>772</v>
       </c>
-      <c r="F49" s="5" t="s">
-        <v>773</v>
-      </c>
       <c r="G49" s="4" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -59253,27 +59273,27 @@
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
       <c r="M49" s="4" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" ht="255" x14ac:dyDescent="0.25">
+        <v>1010</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="255" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="str">
         <f>IF(receta!A50="","",receta!A50)</f>
         <v>Espiral</v>
       </c>
       <c r="B50" s="1"/>
       <c r="C50" s="4" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="4" t="s">
+        <v>482</v>
+      </c>
+      <c r="F50" s="5" t="s">
         <v>483</v>
       </c>
-      <c r="F50" s="5" t="s">
-        <v>484</v>
-      </c>
       <c r="G50" s="4" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>326</v>
@@ -59285,17 +59305,17 @@
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
       <c r="M50" s="4" t="s">
-        <v>967</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+        <v>965</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="str">
         <f>IF(receta!A51="","",receta!A51)</f>
         <v>Espresso Martini</v>
       </c>
       <c r="B51" s="1"/>
       <c r="C51" s="4" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -59307,10 +59327,10 @@
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
       <c r="M51" s="1" t="s">
-        <v>962</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" ht="150" x14ac:dyDescent="0.25">
+        <v>960</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="str">
         <f>IF(receta!A52="","",receta!A52)</f>
         <v>Estoy Verde</v>
@@ -59320,7 +59340,7 @@
         <v>372</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>193</v>
@@ -59330,19 +59350,19 @@
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
       <c r="M52" s="4" t="s">
-        <v>942</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" ht="390" x14ac:dyDescent="0.25">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="390" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="str">
         <f>IF(receta!A53="","",receta!A53)</f>
         <v>Fanshop</v>
@@ -59361,7 +59381,7 @@
         <v>405</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>385</v>
@@ -59373,17 +59393,17 @@
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="4" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="54" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="str">
         <f>IF(receta!A54="","",receta!A54)</f>
         <v>Faro</v>
       </c>
       <c r="B54" s="1"/>
       <c r="C54" s="4" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="1"/>
@@ -59399,10 +59419,10 @@
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
       <c r="M54" s="4" t="s">
-        <v>918</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="str">
         <f>IF(receta!A55="","",receta!A55)</f>
         <v>Feria Libre</v>
@@ -59426,26 +59446,26 @@
       <c r="L55" s="5"/>
       <c r="M55" s="1"/>
     </row>
-    <row r="56" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="str">
         <f>IF(receta!A56="","",receta!A56)</f>
         <v>Fernet con Coca</v>
       </c>
       <c r="B56" s="1"/>
       <c r="C56" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="D56" s="4" t="s">
         <v>396</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -59453,10 +59473,10 @@
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
       <c r="M56" s="4" t="s">
-        <v>963</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="str">
         <f>IF(receta!A57="","",receta!A57)</f>
         <v>Ferroviario</v>
@@ -59481,16 +59501,16 @@
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
       <c r="M57" s="4" t="s">
-        <v>969</v>
-      </c>
-    </row>
-    <row r="58" spans="1:13" ht="150" x14ac:dyDescent="0.25">
+        <v>967</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="str">
         <f>IF(receta!A58="","",receta!A58)</f>
         <v>Frangelico Sour</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>338</v>
@@ -59505,19 +59525,19 @@
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="4" t="s">
-        <v>966</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>964</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="str">
         <f>IF(receta!A59="","",receta!A59)</f>
         <v>French 75</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>359</v>
@@ -59535,10 +59555,10 @@
       <c r="K59" s="5"/>
       <c r="L59" s="5"/>
       <c r="M59" s="4" t="s">
-        <v>964</v>
-      </c>
-    </row>
-    <row r="60" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+        <v>962</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="str">
         <f>IF(receta!A60="","",receta!A60)</f>
         <v>Garibaldi</v>
@@ -59557,10 +59577,10 @@
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
       <c r="M60" s="4" t="s">
-        <v>990</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" ht="165" x14ac:dyDescent="0.25">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="165" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="str">
         <f>IF(receta!A61="","",receta!A61)</f>
         <v>Gimlet</v>
@@ -59573,10 +59593,10 @@
         <v>389</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="4"/>
@@ -59585,17 +59605,17 @@
       <c r="K61" s="1"/>
       <c r="L61" s="1"/>
       <c r="M61" s="4" t="s">
-        <v>914</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" ht="345" x14ac:dyDescent="0.25">
+        <v>913</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="str">
         <f>IF(receta!A62="","",receta!A62)</f>
         <v>Gin con Gin</v>
       </c>
       <c r="B62" s="1"/>
       <c r="C62" s="4" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D62" s="1"/>
       <c r="E62" s="4" t="s">
@@ -59611,10 +59631,10 @@
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
       <c r="M62" s="4" t="s">
-        <v>999</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>997</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="str">
         <f>IF(receta!A63="","",receta!A63)</f>
         <v>Gin Tonic</v>
@@ -59638,26 +59658,26 @@
         <v>337</v>
       </c>
       <c r="J63" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="K63" s="5" t="s">
         <v>769</v>
       </c>
-      <c r="K63" s="5" t="s">
-        <v>770</v>
-      </c>
       <c r="L63" s="4" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
       <c r="M63" s="4" t="s">
-        <v>934</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" ht="135" x14ac:dyDescent="0.25">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="str">
         <f>IF(receta!A64="","",receta!A64)</f>
         <v>Ginger Fire</v>
       </c>
       <c r="B64" s="1"/>
       <c r="C64" s="4" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
@@ -59669,17 +59689,17 @@
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
       <c r="M64" s="4" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="65" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="str">
         <f>IF(receta!A65="","",receta!A65)</f>
         <v>Hemingway Daiquiri</v>
       </c>
       <c r="B65" s="1"/>
       <c r="C65" s="4" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>169</v>
@@ -59693,20 +59713,20 @@
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
       <c r="M65" s="1" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="66" spans="1:13" ht="375" x14ac:dyDescent="0.25">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" ht="375" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="str">
         <f>IF(receta!A66="","",receta!A66)</f>
         <v>Hugo</v>
       </c>
       <c r="B66" s="1"/>
       <c r="C66" s="4" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
@@ -59718,7 +59738,7 @@
       <c r="L66" s="1"/>
       <c r="M66" s="1"/>
     </row>
-    <row r="67" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="str">
         <f>IF(receta!A67="","",receta!A67)</f>
         <v>Incendio</v>
@@ -59741,20 +59761,20 @@
       <c r="K67" s="5"/>
       <c r="L67" s="5"/>
       <c r="M67" s="4" t="s">
-        <v>959</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" ht="330" x14ac:dyDescent="0.25">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="330" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="str">
         <f>IF(receta!A68="","",receta!A68)</f>
         <v>Ingrata</v>
       </c>
       <c r="B68" s="1"/>
       <c r="C68" s="1" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>165</v>
@@ -59769,10 +59789,10 @@
       <c r="K68" s="5"/>
       <c r="L68" s="5"/>
       <c r="M68" s="4" t="s">
-        <v>952</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" ht="300" x14ac:dyDescent="0.25">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="300" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="str">
         <f>IF(receta!A69="","",receta!A69)</f>
         <v>Isla Negra</v>
@@ -59797,10 +59817,10 @@
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
       <c r="M69" s="4" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" ht="195" x14ac:dyDescent="0.25">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" ht="195" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="str">
         <f>IF(receta!A70="","",receta!A70)</f>
         <v>Jardín</v>
@@ -59825,10 +59845,10 @@
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
       <c r="M70" s="4" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13" ht="225" x14ac:dyDescent="0.25">
+        <v>947</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" ht="225" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="str">
         <f>IF(receta!A71="","",receta!A71)</f>
         <v>John Collins</v>
@@ -59839,10 +59859,10 @@
       </c>
       <c r="D71" s="1"/>
       <c r="E71" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="1"/>
@@ -59851,22 +59871,22 @@
       <c r="K71" s="5"/>
       <c r="L71" s="5"/>
       <c r="M71" s="4" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="str">
         <f>IF(receta!A72="","",receta!A72)</f>
         <v>Jote</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="E72" s="1"/>
       <c r="F72" s="5"/>
@@ -59881,20 +59901,20 @@
       <c r="K72" s="5"/>
       <c r="L72" s="5"/>
       <c r="M72" s="4" t="s">
-        <v>875</v>
-      </c>
-    </row>
-    <row r="73" spans="1:13" ht="225" x14ac:dyDescent="0.25">
+        <v>874</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" ht="225" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="str">
         <f>IF(receta!A73="","",receta!A73)</f>
         <v>Julepe de Menta</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="C73" s="4"/>
       <c r="D73" s="4" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
@@ -59906,39 +59926,39 @@
       <c r="L73" s="1"/>
       <c r="M73" s="1"/>
     </row>
-    <row r="74" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="str">
         <f>IF(receta!A74="","",receta!A74)</f>
         <v>Julieta Flowers</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E74" s="1" t="s">
+        <v>730</v>
+      </c>
+      <c r="F74" s="5" t="s">
         <v>731</v>
-      </c>
-      <c r="F74" s="5" t="s">
-        <v>732</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="1" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="J74" s="1"/>
       <c r="K74" s="5"/>
       <c r="L74" s="5"/>
       <c r="M74" s="1"/>
     </row>
-    <row r="75" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="str">
         <f>IF(receta!A75="","",receta!A75)</f>
         <v>Kir Royal</v>
@@ -59958,7 +59978,7 @@
       <c r="L75" s="1"/>
       <c r="M75" s="1"/>
     </row>
-    <row r="76" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="str">
         <f>IF(receta!A76="","",receta!A76)</f>
         <v>Kokomo</v>
@@ -59984,16 +60004,18 @@
       <c r="L76" s="5"/>
       <c r="M76" s="1"/>
     </row>
-    <row r="77" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="str">
         <f>IF(receta!A77="","",receta!A77)</f>
         <v>Laguna Azul</v>
       </c>
       <c r="B77" s="1"/>
       <c r="C77" s="4" t="s">
-        <v>464</v>
-      </c>
-      <c r="D77" s="1"/>
+        <v>1021</v>
+      </c>
+      <c r="D77" s="4" t="s">
+        <v>1020</v>
+      </c>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
       <c r="G77" s="1"/>
@@ -60002,37 +60024,39 @@
       <c r="J77" s="1"/>
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
-      <c r="M77" s="1"/>
-    </row>
-    <row r="78" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+      <c r="M77" s="4" t="s">
+        <v>1019</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="str">
         <f>IF(receta!A78="","",receta!A78)</f>
         <v>London Mule</v>
       </c>
       <c r="B78" s="1"/>
       <c r="C78" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D78" s="1"/>
       <c r="E78" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="G78" s="5"/>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
       <c r="J78" s="1" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="K78" s="5" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="L78" s="5"/>
       <c r="M78" s="1"/>
     </row>
-    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="str">
         <f>IF(receta!A79="","",receta!A79)</f>
         <v>Luisito</v>
@@ -60050,7 +60074,7 @@
       <c r="L79" s="1"/>
       <c r="M79" s="1"/>
     </row>
-    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="str">
         <f>IF(receta!A80="","",receta!A80)</f>
         <v>Luisito (Sin Alcohol)</v>
@@ -60070,14 +60094,14 @@
       <c r="L80" s="1"/>
       <c r="M80" s="1"/>
     </row>
-    <row r="81" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="str">
         <f>IF(receta!A81="","",receta!A81)</f>
         <v>Madras</v>
       </c>
       <c r="B81" s="1"/>
       <c r="C81" s="4" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="D81" s="4"/>
       <c r="E81" s="1"/>
@@ -60090,40 +60114,40 @@
       <c r="L81" s="1"/>
       <c r="M81" s="1"/>
     </row>
-    <row r="82" spans="1:13" ht="240" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" ht="240" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="str">
         <f>IF(receta!A82="","",receta!A82)</f>
         <v>Mai Tai Piña</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D82" s="4"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
       <c r="G82" s="1"/>
       <c r="H82" s="1" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="I82" s="5" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="J82" s="1"/>
       <c r="K82" s="1"/>
       <c r="L82" s="1"/>
       <c r="M82" s="1"/>
     </row>
-    <row r="83" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="str">
         <f>IF(receta!A83="","",receta!A83)</f>
         <v>Mala Reputación</v>
       </c>
       <c r="B83" s="1"/>
       <c r="C83" s="4" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>304</v>
@@ -60141,76 +60165,76 @@
       <c r="K83" s="5"/>
       <c r="L83" s="5"/>
       <c r="M83" s="4" t="s">
-        <v>887</v>
-      </c>
-    </row>
-    <row r="84" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>886</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="str">
         <f>IF(receta!A84="","",receta!A84)</f>
         <v>Malta con Huevo</v>
       </c>
       <c r="B84" s="4" t="s">
+        <v>662</v>
+      </c>
+      <c r="C84" s="4" t="s">
         <v>663</v>
       </c>
-      <c r="C84" s="4" t="s">
-        <v>664</v>
-      </c>
       <c r="D84" s="4" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
       <c r="H84" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="J84" s="1"/>
       <c r="K84" s="1"/>
       <c r="L84" s="1"/>
       <c r="M84" s="4" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="85" spans="1:13" ht="240" x14ac:dyDescent="0.25">
+        <v>990</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" ht="240" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="str">
         <f>IF(receta!A85="","",receta!A85)</f>
         <v>Malta con Leche Condensada</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
       <c r="H85" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="J85" s="1"/>
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
       <c r="M85" s="4" t="s">
-        <v>993</v>
-      </c>
-    </row>
-    <row r="86" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>991</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="str">
         <f>IF(receta!A86="","",receta!A86)</f>
         <v>Mango Sour</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C86" s="4"/>
       <c r="D86" s="1"/>
@@ -60224,25 +60248,25 @@
       <c r="L86" s="1"/>
       <c r="M86" s="1"/>
     </row>
-    <row r="87" spans="1:13" ht="165" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" ht="165" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="str">
         <f>IF(receta!A87="","",receta!A87)</f>
         <v>Manhattan</v>
       </c>
       <c r="B87" s="1"/>
       <c r="C87" s="4" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="D87" s="1"/>
       <c r="E87" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="G87" s="5"/>
       <c r="H87" s="1" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="I87" s="5" t="s">
         <v>374</v>
@@ -60251,22 +60275,22 @@
       <c r="K87" s="5"/>
       <c r="L87" s="5"/>
       <c r="M87" s="4" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="88" spans="1:13" ht="360" x14ac:dyDescent="0.25">
+        <v>945</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" ht="360" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="str">
         <f>IF(receta!A88="","",receta!A88)</f>
         <v>Maqui Sour</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
@@ -60278,16 +60302,16 @@
       <c r="L88" s="1"/>
       <c r="M88" s="1"/>
     </row>
-    <row r="89" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="str">
         <f>IF(receta!A89="","",receta!A89)</f>
         <v>Margarita</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D89" s="1"/>
       <c r="E89" s="1" t="s">
@@ -60304,7 +60328,7 @@
       <c r="L89" s="5"/>
       <c r="M89" s="1"/>
     </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="str">
         <f>IF(receta!A90="","",receta!A90)</f>
         <v>Margarita Maracuyá</v>
@@ -60313,7 +60337,7 @@
       <c r="C90" s="1"/>
       <c r="D90" s="1"/>
       <c r="E90" s="1" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="F90" s="5" t="s">
         <v>411</v>
@@ -60326,16 +60350,16 @@
       <c r="L90" s="5"/>
       <c r="M90" s="1"/>
     </row>
-    <row r="91" spans="1:13" ht="225" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" ht="225" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="str">
         <f>IF(receta!A91="","",receta!A91)</f>
         <v>Melón con Vino</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="D91" s="1"/>
       <c r="E91" s="1" t="s">
@@ -60352,16 +60376,16 @@
       <c r="L91" s="5"/>
       <c r="M91" s="1"/>
     </row>
-    <row r="92" spans="1:13" ht="375" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" ht="375" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="str">
         <f>IF(receta!A92="","",receta!A92)</f>
         <v>Michelada</v>
       </c>
       <c r="B92" s="4" t="s">
+        <v>845</v>
+      </c>
+      <c r="C92" s="4" t="s">
         <v>846</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>847</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>402</v>
@@ -60380,14 +60404,14 @@
       <c r="L92" s="5"/>
       <c r="M92" s="1"/>
     </row>
-    <row r="93" spans="1:13" ht="150" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="str">
         <f>IF(receta!A93="","",receta!A93)</f>
         <v>Milano Torino</v>
       </c>
       <c r="B93" s="1"/>
       <c r="C93" s="4" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
@@ -60400,7 +60424,7 @@
       <c r="L93" s="1"/>
       <c r="M93" s="1"/>
     </row>
-    <row r="94" spans="1:13" ht="180" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" ht="180" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="str">
         <f>IF(receta!A94="","",receta!A94)</f>
         <v>Mimosa</v>
@@ -60420,16 +60444,16 @@
       <c r="L94" s="1"/>
       <c r="M94" s="1"/>
     </row>
-    <row r="95" spans="1:13" ht="225" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" ht="225" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="str">
         <f>IF(receta!A95="","",receta!A95)</f>
         <v>Mojito</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D95" s="4"/>
       <c r="E95" s="1"/>
@@ -60441,17 +60465,17 @@
       <c r="K95" s="1"/>
       <c r="L95" s="1"/>
       <c r="M95" s="4" t="s">
-        <v>1004</v>
-      </c>
-    </row>
-    <row r="96" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="str">
         <f>IF(receta!A96="","",receta!A96)</f>
         <v>Mojito (Sin Alcohol)</v>
       </c>
       <c r="B96" s="1"/>
       <c r="C96" s="4" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D96" s="4"/>
       <c r="E96" s="1"/>
@@ -60464,23 +60488,23 @@
       <c r="L96" s="1"/>
       <c r="M96" s="1"/>
     </row>
-    <row r="97" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="str">
         <f>IF(receta!A97="","",receta!A97)</f>
         <v>Mojito Maracuyá</v>
       </c>
       <c r="B97" s="1"/>
       <c r="C97" s="4" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="G97" s="1"/>
       <c r="H97" s="4"/>
@@ -60489,17 +60513,17 @@
       <c r="K97" s="1"/>
       <c r="L97" s="1"/>
       <c r="M97" s="4" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="98" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+        <v>1001</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="str">
         <f>IF(receta!A98="","",receta!A98)</f>
         <v>Mojito Spritz</v>
       </c>
       <c r="B98" s="1"/>
       <c r="C98" s="4" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D98" s="4"/>
       <c r="E98" s="1"/>
@@ -60512,7 +60536,7 @@
       <c r="L98" s="1"/>
       <c r="M98" s="1"/>
     </row>
-    <row r="99" spans="1:13" ht="375" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" ht="375" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="str">
         <f>IF(receta!A99="","",receta!A99)</f>
         <v>Moscow Mule</v>
@@ -60535,16 +60559,16 @@
       <c r="K99" s="5"/>
       <c r="L99" s="5"/>
       <c r="M99" s="4" t="s">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="100" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="str">
         <f>IF(receta!A100="","",receta!A100)</f>
         <v>Naranja Sour</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>372</v>
@@ -60564,14 +60588,14 @@
       <c r="L100" s="5"/>
       <c r="M100" s="1"/>
     </row>
-    <row r="101" spans="1:13" ht="195" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" ht="195" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="str">
         <f>IF(receta!A101="","",receta!A101)</f>
         <v>Negativismo Lógico</v>
       </c>
       <c r="B101" s="1"/>
       <c r="C101" s="4" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D101" s="4"/>
       <c r="E101" s="4"/>
@@ -60588,7 +60612,7 @@
       <c r="L101" s="1"/>
       <c r="M101" s="1"/>
     </row>
-    <row r="102" spans="1:13" ht="210" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" ht="210" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="str">
         <f>IF(receta!A102="","",receta!A102)</f>
         <v>Negroni</v>
@@ -60609,17 +60633,17 @@
       <c r="K102" s="1"/>
       <c r="L102" s="1"/>
       <c r="M102" s="4" t="s">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="103" spans="1:13" ht="150" x14ac:dyDescent="0.25">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="str">
         <f>IF(receta!A103="","",receta!A103)</f>
         <v>Negroni Sbagliato</v>
       </c>
       <c r="B103" s="1"/>
       <c r="C103" s="4" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="D103" s="1"/>
       <c r="E103" s="1"/>
@@ -60632,25 +60656,25 @@
       <c r="L103" s="1"/>
       <c r="M103" s="1"/>
     </row>
-    <row r="104" spans="1:13" ht="345" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="str">
         <f>IF(receta!A104="","",receta!A104)</f>
         <v>New York Sour</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="G104" s="5"/>
       <c r="H104" s="1"/>
@@ -60659,10 +60683,10 @@
       <c r="K104" s="5"/>
       <c r="L104" s="5"/>
       <c r="M104" s="4" t="s">
-        <v>1016</v>
-      </c>
-    </row>
-    <row r="105" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+        <v>1014</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="str">
         <f>IF(receta!A105="","",receta!A105)</f>
         <v>No Me Falles</v>
@@ -60685,20 +60709,20 @@
       <c r="K105" s="1"/>
       <c r="L105" s="1"/>
       <c r="M105" s="4" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="106" spans="1:13" ht="240" x14ac:dyDescent="0.25">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" ht="240" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="str">
         <f>IF(receta!A106="","",receta!A106)</f>
         <v>Old Fashioned</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C106" s="4"/>
       <c r="D106" s="4" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="E106" s="1"/>
       <c r="F106" s="1"/>
@@ -60710,7 +60734,7 @@
       <c r="L106" s="1"/>
       <c r="M106" s="1"/>
     </row>
-    <row r="107" spans="1:13" ht="192" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" ht="192" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="str">
         <f>IF(receta!A107="","",receta!A107)</f>
         <v>Padrino</v>
@@ -60730,27 +60754,27 @@
       <c r="L107" s="1"/>
       <c r="M107" s="1"/>
     </row>
-    <row r="108" spans="1:13" ht="195" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" ht="195" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="str">
         <f>IF(receta!A108="","",receta!A108)</f>
         <v>Paloma</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D108" s="1"/>
       <c r="E108" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="G108" s="1"/>
       <c r="H108" s="1" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="I108" s="5" t="s">
         <v>256</v>
@@ -60759,16 +60783,16 @@
       <c r="K108" s="1"/>
       <c r="L108" s="1"/>
       <c r="M108" s="4" t="s">
-        <v>970</v>
-      </c>
-    </row>
-    <row r="109" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="str">
         <f>IF(receta!A109="","",receta!A109)</f>
         <v>Parrón</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="C109" s="4"/>
       <c r="D109" s="4"/>
@@ -60782,25 +60806,25 @@
       <c r="L109" s="1"/>
       <c r="M109" s="1"/>
     </row>
-    <row r="110" spans="1:13" ht="330" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" ht="330" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="str">
         <f>IF(receta!A110="","",receta!A110)</f>
         <v>Penicilina</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="G110" s="5"/>
       <c r="H110" s="1"/>
@@ -60809,24 +60833,24 @@
       <c r="K110" s="5"/>
       <c r="L110" s="5"/>
       <c r="M110" s="4" t="s">
-        <v>1015</v>
-      </c>
-    </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1013</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="str">
         <f>IF(receta!A111="","",receta!A111)</f>
         <v>Phil Collins</v>
       </c>
       <c r="B111" s="1"/>
       <c r="C111" s="4" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D111" s="1"/>
       <c r="E111" s="1" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="G111" s="5"/>
       <c r="H111" s="1"/>
@@ -60836,7 +60860,7 @@
       <c r="L111" s="5"/>
       <c r="M111" s="1"/>
     </row>
-    <row r="112" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="str">
         <f>IF(receta!A112="","",receta!A112)</f>
         <v>Pichuncho</v>
@@ -60847,10 +60871,10 @@
       </c>
       <c r="D112" s="1"/>
       <c r="E112" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="G112" s="5"/>
       <c r="H112" s="1"/>
@@ -60860,14 +60884,14 @@
       <c r="L112" s="5"/>
       <c r="M112" s="1"/>
     </row>
-    <row r="113" spans="1:13" ht="195" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" ht="195" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="str">
         <f>IF(receta!A113="","",receta!A113)</f>
         <v>Piña Colada</v>
       </c>
       <c r="B113" s="1"/>
       <c r="C113" s="4" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D113" s="5"/>
       <c r="E113" s="6" t="s">
@@ -60883,10 +60907,10 @@
       <c r="K113" s="5"/>
       <c r="L113" s="5"/>
       <c r="M113" s="4" t="s">
-        <v>937</v>
-      </c>
-    </row>
-    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+        <v>936</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="str">
         <f>IF(receta!A114="","",receta!A114)</f>
         <v>Piña Colada (Sin Alcohol)</v>
@@ -60906,7 +60930,7 @@
       <c r="L114" s="1"/>
       <c r="M114" s="1"/>
     </row>
-    <row r="115" spans="1:13" ht="195" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" ht="195" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="str">
         <f>IF(receta!A115="","",receta!A115)</f>
         <v>Pisco Punch</v>
@@ -60926,7 +60950,7 @@
       <c r="L115" s="1"/>
       <c r="M115" s="1"/>
     </row>
-    <row r="116" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="str">
         <f>IF(receta!A116="","",receta!A116)</f>
         <v>Pisco Sour</v>
@@ -60952,16 +60976,16 @@
       <c r="L116" s="5"/>
       <c r="M116" s="1"/>
     </row>
-    <row r="117" spans="1:13" ht="210" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" ht="210" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="str">
         <f>IF(receta!A117="","",receta!A117)</f>
         <v>Piscola</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D117" s="5"/>
       <c r="E117" s="1" t="s">
@@ -60977,26 +61001,26 @@
       <c r="K117" s="5"/>
       <c r="L117" s="5"/>
       <c r="M117" s="4" t="s">
-        <v>941</v>
-      </c>
-    </row>
-    <row r="118" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+        <v>1018</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="str">
         <f>IF(receta!A118="","",receta!A118)</f>
         <v>Pistón</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D118" s="1"/>
       <c r="E118" s="1" t="s">
+        <v>502</v>
+      </c>
+      <c r="F118" s="5" t="s">
         <v>503</v>
-      </c>
-      <c r="F118" s="5" t="s">
-        <v>504</v>
       </c>
       <c r="G118" s="5"/>
       <c r="H118" s="1"/>
@@ -61006,7 +61030,7 @@
       <c r="L118" s="5"/>
       <c r="M118" s="1"/>
     </row>
-    <row r="119" spans="1:13" ht="375" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" ht="375" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="str">
         <f>IF(receta!A119="","",receta!A119)</f>
         <v>Quédate</v>
@@ -61031,10 +61055,10 @@
       <c r="K119" s="5"/>
       <c r="L119" s="5"/>
       <c r="M119" s="4" t="s">
-        <v>1018</v>
-      </c>
-    </row>
-    <row r="120" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+        <v>1016</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="str">
         <f>IF(receta!A120="","",receta!A120)</f>
         <v>Ramazzotti Spritz</v>
@@ -61058,14 +61082,14 @@
       <c r="L120" s="5"/>
       <c r="M120" s="1"/>
     </row>
-    <row r="121" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="str">
         <f>IF(receta!A121="","",receta!A121)</f>
         <v>Ramazzotti Violetto Spritz</v>
       </c>
       <c r="B121" s="1"/>
       <c r="C121" s="4" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D121" s="1"/>
       <c r="E121" s="1"/>
@@ -61078,21 +61102,21 @@
       <c r="L121" s="1"/>
       <c r="M121" s="1"/>
     </row>
-    <row r="122" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="str">
         <f>IF(receta!A122="","",receta!A122)</f>
         <v>Ron Cola</v>
       </c>
       <c r="B122" s="1"/>
       <c r="C122" s="4" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D122" s="1"/>
       <c r="E122" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="G122" s="1"/>
       <c r="H122" s="1"/>
@@ -61102,14 +61126,14 @@
       <c r="L122" s="1"/>
       <c r="M122" s="1"/>
     </row>
-    <row r="123" spans="1:13" ht="135" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="str">
         <f>IF(receta!A123="","",receta!A123)</f>
         <v>Ruso Blanco</v>
       </c>
       <c r="B123" s="1"/>
       <c r="C123" s="4" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D123" s="4" t="s">
         <v>252</v>
@@ -61127,17 +61151,17 @@
       <c r="K123" s="5"/>
       <c r="L123" s="5"/>
       <c r="M123" s="4" t="s">
-        <v>929</v>
-      </c>
-    </row>
-    <row r="124" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>928</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="str">
         <f>IF(receta!A124="","",receta!A124)</f>
         <v>Ruso Negro</v>
       </c>
       <c r="B124" s="1"/>
       <c r="C124" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D124" s="4" t="s">
         <v>357</v>
@@ -61152,16 +61176,16 @@
       <c r="L124" s="1"/>
       <c r="M124" s="1"/>
     </row>
-    <row r="125" spans="1:13" ht="330" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" ht="330" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="str">
         <f>IF(receta!A125="","",receta!A125)</f>
         <v>Sangría</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D125" s="4" t="s">
         <v>394</v>
@@ -61180,14 +61204,14 @@
       <c r="L125" s="1"/>
       <c r="M125" s="1"/>
     </row>
-    <row r="126" spans="1:13" ht="255" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" ht="255" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="str">
         <f>IF(receta!A126="","",receta!A126)</f>
         <v>Sangrita</v>
       </c>
       <c r="B126" s="1"/>
       <c r="C126" s="4" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D126" s="1"/>
       <c r="E126" s="1"/>
@@ -61200,21 +61224,21 @@
       <c r="L126" s="1"/>
       <c r="M126" s="1"/>
     </row>
-    <row r="127" spans="1:13" ht="165" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" ht="165" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="str">
         <f>IF(receta!A127="","",receta!A127)</f>
         <v>Sea Breeze</v>
       </c>
       <c r="B127" s="1"/>
       <c r="C127" s="4" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D127" s="1"/>
       <c r="E127" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="G127" s="1"/>
       <c r="H127" s="1"/>
@@ -61224,7 +61248,7 @@
       <c r="L127" s="1"/>
       <c r="M127" s="1"/>
     </row>
-    <row r="128" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="str">
         <f>IF(receta!A128="","",receta!A128)</f>
         <v>Serena Libre</v>
@@ -61243,10 +61267,10 @@
       <c r="K128" s="1"/>
       <c r="L128" s="1"/>
       <c r="M128" s="4" t="s">
-        <v>1017</v>
-      </c>
-    </row>
-    <row r="129" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>1015</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="str">
         <f>IF(receta!A129="","",receta!A129)</f>
         <v>Sexo en la Playa</v>
@@ -61256,7 +61280,7 @@
         <v>370</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="E129" s="1"/>
       <c r="F129" s="1"/>
@@ -61267,10 +61291,10 @@
       <c r="K129" s="1"/>
       <c r="L129" s="1"/>
       <c r="M129" s="4" t="s">
-        <v>915</v>
-      </c>
-    </row>
-    <row r="130" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>914</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="str">
         <f>IF(receta!A130="","",receta!A130)</f>
         <v>Sexo Seguro en la Playa</v>
@@ -61290,14 +61314,14 @@
       <c r="L130" s="1"/>
       <c r="M130" s="1"/>
     </row>
-    <row r="131" spans="1:13" ht="210" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" ht="210" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="str">
         <f>IF(receta!A131="","",receta!A131)</f>
         <v>Sidecar</v>
       </c>
       <c r="B131" s="1"/>
       <c r="C131" s="4" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="D131" s="4"/>
       <c r="E131" s="1"/>
@@ -61310,7 +61334,7 @@
       <c r="L131" s="1"/>
       <c r="M131" s="1"/>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="str">
         <f>IF(receta!A132="","",receta!A132)</f>
         <v>Síndrome Impostor</v>
@@ -61334,7 +61358,7 @@
       <c r="L132" s="5"/>
       <c r="M132" s="1"/>
     </row>
-    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="str">
         <f>IF(receta!A133="","",receta!A133)</f>
         <v>Sour (Sin Alcohol)</v>
@@ -61354,23 +61378,23 @@
       <c r="L133" s="1"/>
       <c r="M133" s="1"/>
     </row>
-    <row r="134" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="str">
         <f>IF(receta!A134="","",receta!A134)</f>
         <v>Tequila Sunrise</v>
       </c>
       <c r="B134" s="1"/>
       <c r="C134" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="D134" s="4" t="s">
+        <v>598</v>
+      </c>
+      <c r="E134" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="F134" s="5" t="s">
         <v>590</v>
-      </c>
-      <c r="D134" s="4" t="s">
-        <v>599</v>
-      </c>
-      <c r="E134" s="4" t="s">
-        <v>592</v>
-      </c>
-      <c r="F134" s="5" t="s">
-        <v>591</v>
       </c>
       <c r="G134" s="5"/>
       <c r="H134" s="4"/>
@@ -61379,49 +61403,49 @@
       <c r="K134" s="5"/>
       <c r="L134" s="5"/>
       <c r="M134" s="4" t="s">
-        <v>946</v>
-      </c>
-    </row>
-    <row r="135" spans="1:13" ht="300" x14ac:dyDescent="0.25">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" ht="300" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="str">
         <f>IF(receta!A135="","",receta!A135)</f>
         <v>Terremoto</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="E135" s="1"/>
       <c r="F135" s="1"/>
       <c r="G135" s="1"/>
       <c r="H135" s="1" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="I135" s="5" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="J135" s="1"/>
       <c r="K135" s="1"/>
       <c r="L135" s="1"/>
       <c r="M135" s="4" t="s">
-        <v>957</v>
-      </c>
-    </row>
-    <row r="136" spans="1:13" ht="180" x14ac:dyDescent="0.25">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" ht="180" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="str">
         <f>IF(receta!A136="","",receta!A136)</f>
         <v>Terremoto (Sin Alcohol)</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D136" s="4"/>
       <c r="E136" s="1" t="s">
@@ -61438,7 +61462,7 @@
       <c r="L136" s="5"/>
       <c r="M136" s="1"/>
     </row>
-    <row r="137" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="str">
         <f>IF(receta!A137="","",receta!A137)</f>
         <v>Tinto de Verano</v>
@@ -61458,14 +61482,14 @@
       <c r="L137" s="1"/>
       <c r="M137" s="1"/>
     </row>
-    <row r="138" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="str">
         <f>IF(receta!A138="","",receta!A138)</f>
         <v>Tom Collins</v>
       </c>
       <c r="B138" s="4"/>
       <c r="C138" s="4" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D138" s="1"/>
       <c r="E138" s="1"/>
@@ -61477,17 +61501,17 @@
       <c r="K138" s="1"/>
       <c r="L138" s="1"/>
       <c r="M138" s="4" t="s">
-        <v>938</v>
-      </c>
-    </row>
-    <row r="139" spans="1:13" ht="195" x14ac:dyDescent="0.25">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" ht="195" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="str">
         <f>IF(receta!A139="","",receta!A139)</f>
         <v>Trikahue</v>
       </c>
       <c r="B139" s="1"/>
       <c r="C139" s="4" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D139" s="4"/>
       <c r="E139" s="1"/>
@@ -61504,16 +61528,16 @@
       <c r="L139" s="1"/>
       <c r="M139" s="1"/>
     </row>
-    <row r="140" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="str">
         <f>IF(receta!A140="","",receta!A140)</f>
         <v>Tropezón</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="D140" s="4" t="s">
         <v>345</v>
@@ -61530,27 +61554,29 @@
       <c r="J140" s="1"/>
       <c r="K140" s="5"/>
       <c r="L140" s="5"/>
-      <c r="M140" s="1"/>
-    </row>
-    <row r="141" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+      <c r="M140" s="4" t="s">
+        <v>1017</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="str">
         <f>IF(receta!A141="","",receta!A141)</f>
         <v>Vaina</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="E141" s="4" t="s">
+        <v>614</v>
+      </c>
+      <c r="F141" s="4" t="s">
         <v>615</v>
-      </c>
-      <c r="F141" s="4" t="s">
-        <v>616</v>
       </c>
       <c r="G141" s="4"/>
       <c r="H141" s="1"/>
@@ -61560,14 +61586,14 @@
       <c r="L141" s="4"/>
       <c r="M141" s="1"/>
     </row>
-    <row r="142" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="str">
         <f>IF(receta!A142="","",receta!A142)</f>
         <v>Valentín</v>
       </c>
       <c r="B142" s="1"/>
       <c r="C142" s="4" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D142" s="4"/>
       <c r="E142" s="4" t="s">
@@ -61584,25 +61610,25 @@
       <c r="L142" s="5"/>
       <c r="M142" s="1"/>
     </row>
-    <row r="143" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="str">
         <f>IF(receta!A143="","",receta!A143)</f>
         <v>Vampiro</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="E143" s="1" t="s">
+        <v>540</v>
+      </c>
+      <c r="F143" s="1" t="s">
         <v>541</v>
-      </c>
-      <c r="F143" s="1" t="s">
-        <v>542</v>
       </c>
       <c r="G143" s="1"/>
       <c r="H143" s="1"/>
@@ -61611,10 +61637,10 @@
       <c r="K143" s="1"/>
       <c r="L143" s="1"/>
       <c r="M143" s="4" t="s">
-        <v>943</v>
-      </c>
-    </row>
-    <row r="144" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="str">
         <f>IF(receta!A144="","",receta!A144)</f>
         <v>Venganza</v>
@@ -61639,28 +61665,28 @@
       <c r="K144" s="1"/>
       <c r="L144" s="1"/>
       <c r="M144" s="4" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="145" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="str">
         <f>IF(receta!A145="","",receta!A145)</f>
         <v>Vermouth con Soda</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G145" s="1"/>
       <c r="H145" s="1"/>
@@ -61670,14 +61696,14 @@
       <c r="L145" s="1"/>
       <c r="M145" s="1"/>
     </row>
-    <row r="146" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="str">
         <f>IF(receta!A146="","",receta!A146)</f>
         <v>Violetto Tonic</v>
       </c>
       <c r="B146" s="1"/>
       <c r="C146" s="4" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D146" s="1"/>
       <c r="E146" s="1"/>
@@ -61690,21 +61716,21 @@
       <c r="L146" s="1"/>
       <c r="M146" s="1"/>
     </row>
-    <row r="147" spans="1:13" ht="240" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:13" ht="240" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="str">
         <f>IF(receta!A147="","",receta!A147)</f>
         <v>Vodka Cranberry</v>
       </c>
       <c r="B147" s="1"/>
       <c r="C147" s="4" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D147" s="4"/>
       <c r="E147" s="1" t="s">
+        <v>715</v>
+      </c>
+      <c r="F147" s="5" t="s">
         <v>716</v>
-      </c>
-      <c r="F147" s="5" t="s">
-        <v>717</v>
       </c>
       <c r="G147" s="5"/>
       <c r="H147" s="1"/>
@@ -61713,24 +61739,24 @@
       <c r="K147" s="5"/>
       <c r="L147" s="5"/>
       <c r="M147" s="4" t="s">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="148" spans="1:13" ht="225" x14ac:dyDescent="0.25">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13" ht="225" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="str">
         <f>IF(receta!A148="","",receta!A148)</f>
         <v>Whiscola</v>
       </c>
       <c r="B148" s="1"/>
       <c r="C148" s="4" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="D148" s="1"/>
       <c r="E148" s="1" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="G148" s="5"/>
       <c r="H148" s="1"/>
@@ -61740,23 +61766,23 @@
       <c r="L148" s="5"/>
       <c r="M148" s="1"/>
     </row>
-    <row r="149" spans="1:13" ht="324" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:13" ht="324" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="str">
         <f>IF(receta!A149="","",receta!A149)</f>
         <v>Whiskey Highball</v>
       </c>
       <c r="B149" s="1"/>
       <c r="C149" s="4" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="E149" s="1" t="s">
+        <v>709</v>
+      </c>
+      <c r="F149" s="5" t="s">
         <v>710</v>
-      </c>
-      <c r="F149" s="5" t="s">
-        <v>711</v>
       </c>
       <c r="G149" s="5"/>
       <c r="H149" s="1"/>
@@ -61766,13 +61792,13 @@
       <c r="L149" s="5"/>
       <c r="M149" s="1"/>
     </row>
-    <row r="150" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="str">
         <f>IF(receta!A150="","",receta!A150)</f>
         <v>Whisky Sour</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C150" s="4" t="s">
         <v>361</v>
@@ -61781,10 +61807,10 @@
         <v>356</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="G150" s="1"/>
       <c r="H150" s="1"/>
@@ -61793,28 +61819,28 @@
       <c r="K150" s="1"/>
       <c r="L150" s="1"/>
       <c r="M150" s="4" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="151" spans="1:13" ht="180" x14ac:dyDescent="0.25">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" ht="180" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="str">
         <f>IF(receta!A151="","",receta!A151)</f>
         <v>Bramble</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="D151" s="4" t="s">
+        <v>792</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>794</v>
+      </c>
+      <c r="F151" s="1" t="s">
         <v>793</v>
-      </c>
-      <c r="E151" s="1" t="s">
-        <v>795</v>
-      </c>
-      <c r="F151" s="1" t="s">
-        <v>794</v>
       </c>
       <c r="G151" s="1"/>
       <c r="H151" s="1"/>
@@ -61824,21 +61850,21 @@
       <c r="L151" s="1"/>
       <c r="M151" s="1"/>
     </row>
-    <row r="152" spans="1:13" ht="180" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:13" ht="180" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="str">
         <f>IF(receta!A152="","",receta!A152)</f>
         <v>Pantera Rosa</v>
       </c>
       <c r="B152" s="1"/>
       <c r="C152" s="4" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D152" s="4"/>
       <c r="E152" s="1" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="G152" s="1"/>
       <c r="H152" s="1"/>
@@ -61848,25 +61874,25 @@
       <c r="L152" s="1"/>
       <c r="M152" s="1"/>
     </row>
-    <row r="153" spans="1:13" ht="240" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:13" ht="240" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="str">
         <f>IF(receta!A153="","",receta!A153)</f>
         <v>Gin Basil Smash</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="E153" s="4" t="s">
+        <v>796</v>
+      </c>
+      <c r="F153" s="1" t="s">
         <v>797</v>
-      </c>
-      <c r="F153" s="1" t="s">
-        <v>798</v>
       </c>
       <c r="G153" s="1"/>
       <c r="H153" s="1"/>
@@ -61876,48 +61902,48 @@
       <c r="L153" s="1"/>
       <c r="M153" s="1"/>
     </row>
-    <row r="154" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="str">
         <f>IF(receta!A154="","",receta!A154)</f>
         <v>Vodka Tonic</v>
       </c>
       <c r="B154" s="1"/>
       <c r="C154" s="4" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="D154" s="26" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="E154" s="1" t="s">
+        <v>785</v>
+      </c>
+      <c r="F154" s="5" t="s">
         <v>786</v>
-      </c>
-      <c r="F154" s="5" t="s">
-        <v>787</v>
       </c>
       <c r="G154" s="5"/>
       <c r="H154" s="1"/>
       <c r="I154" s="5"/>
       <c r="J154" s="1" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="K154" s="5" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="L154" s="26" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
       <c r="M154" s="1"/>
     </row>
-    <row r="155" spans="1:13" ht="240" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:13" ht="240" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="str">
         <f>IF(receta!A155="","",receta!A155)</f>
         <v>Medias de Seda</v>
       </c>
       <c r="B155" s="4" t="s">
+        <v>801</v>
+      </c>
+      <c r="C155" s="4" t="s">
         <v>802</v>
-      </c>
-      <c r="C155" s="4" t="s">
-        <v>803</v>
       </c>
       <c r="D155" s="4"/>
       <c r="E155" s="1"/>
@@ -61930,23 +61956,23 @@
       <c r="L155" s="1"/>
       <c r="M155" s="1"/>
     </row>
-    <row r="156" spans="1:13" ht="255" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:13" ht="255" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="str">
         <f>IF(receta!A156="","",receta!A156)</f>
         <v>Brandy Sour</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="D156" s="4"/>
       <c r="E156" s="1" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="G156" s="5"/>
       <c r="H156" s="1"/>
@@ -61956,16 +61982,16 @@
       <c r="L156" s="1"/>
       <c r="M156" s="1"/>
     </row>
-    <row r="157" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="str">
         <f>IF(receta!A157="","",receta!A157)</f>
         <v>Juanito Rosado</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="D157" s="4" t="s">
         <v>435</v>
@@ -61984,23 +62010,23 @@
       <c r="L157" s="1"/>
       <c r="M157" s="4"/>
     </row>
-    <row r="158" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="str">
         <f>IF(receta!A158="","",receta!A158)</f>
         <v>Vino Navegado</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="D158" s="10"/>
       <c r="E158" s="1" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="G158" s="1"/>
       <c r="H158" s="1"/>
@@ -62009,53 +62035,53 @@
       <c r="K158" s="1"/>
       <c r="L158" s="1"/>
       <c r="M158" s="10" t="s">
-        <v>818</v>
-      </c>
-    </row>
-    <row r="159" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="str">
         <f>IF(receta!A159="","",receta!A159)</f>
         <v>Cola de Mono</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="G159" s="5"/>
       <c r="H159" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="I159" s="10" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="J159" s="1"/>
       <c r="K159" s="1"/>
       <c r="L159" s="1"/>
       <c r="M159" s="4" t="s">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="160" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="str">
         <f>IF(receta!A160="","",receta!A160)</f>
         <v>Chichón</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="D160" s="4"/>
       <c r="E160" s="1"/>
@@ -62068,16 +62094,16 @@
       <c r="L160" s="1"/>
       <c r="M160" s="1"/>
     </row>
-    <row r="161" spans="1:13" ht="195" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:13" ht="195" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="str">
         <f>IF(receta!A161="","",receta!A161)</f>
         <v>Ramos Fizz</v>
       </c>
       <c r="B161" s="4" t="s">
+        <v>842</v>
+      </c>
+      <c r="C161" s="4" t="s">
         <v>843</v>
-      </c>
-      <c r="C161" s="4" t="s">
-        <v>844</v>
       </c>
       <c r="D161" s="4"/>
       <c r="E161" s="1"/>
@@ -62090,23 +62116,23 @@
       <c r="L161" s="1"/>
       <c r="M161" s="1"/>
     </row>
-    <row r="162" spans="1:13" ht="195" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:13" ht="195" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="str">
         <f>IF(receta!A162="","",receta!A162)</f>
         <v>Gin Fizz</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="D162" s="4"/>
       <c r="E162" s="1" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="G162" s="5"/>
       <c r="H162" s="5"/>
@@ -62116,23 +62142,23 @@
       <c r="L162" s="1"/>
       <c r="M162" s="1"/>
     </row>
-    <row r="163" spans="1:13" ht="255" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:13" ht="255" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="str">
         <f>IF(receta!A163="","",receta!A163)</f>
         <v>Carta Breve</v>
       </c>
       <c r="B163" s="1"/>
       <c r="C163" s="4" t="s">
+        <v>855</v>
+      </c>
+      <c r="D163" s="4" t="s">
+        <v>854</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>857</v>
+      </c>
+      <c r="F163" s="5" t="s">
         <v>856</v>
-      </c>
-      <c r="D163" s="4" t="s">
-        <v>855</v>
-      </c>
-      <c r="E163" s="1" t="s">
-        <v>858</v>
-      </c>
-      <c r="F163" s="5" t="s">
-        <v>857</v>
       </c>
       <c r="G163" s="5"/>
       <c r="H163" s="1"/>
@@ -62141,54 +62167,54 @@
       <c r="K163" s="1"/>
       <c r="L163" s="1"/>
       <c r="M163" s="4" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="164" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>980</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="str">
         <f>IF(receta!A164="","",receta!A164)</f>
         <v>Orgasmo</v>
       </c>
       <c r="B164" s="4"/>
       <c r="C164" s="4" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="G164" s="5"/>
       <c r="H164" s="1"/>
       <c r="I164" s="5"/>
       <c r="J164" s="1" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="K164" s="1" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="L164" s="1"/>
       <c r="M164" s="4" t="s">
-        <v>863</v>
-      </c>
-    </row>
-    <row r="165" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>862</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="str">
         <f>IF(receta!A165="","",receta!A165)</f>
         <v>Pihuelo</v>
       </c>
       <c r="B165" s="4" t="s">
+        <v>871</v>
+      </c>
+      <c r="C165" s="4" t="s">
         <v>872</v>
       </c>
-      <c r="C165" s="4" t="s">
-        <v>873</v>
-      </c>
       <c r="D165" s="4" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="E165" s="1"/>
       <c r="F165" s="1"/>
@@ -62199,28 +62225,28 @@
       <c r="K165" s="1"/>
       <c r="L165" s="1"/>
       <c r="M165" s="4" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="166" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="166" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="str">
         <f>IF(receta!A166="","",receta!A166)</f>
         <v>Mojito Sandía</v>
       </c>
       <c r="B166" s="4" t="s">
+        <v>883</v>
+      </c>
+      <c r="C166" s="4" t="s">
         <v>884</v>
       </c>
-      <c r="C166" s="4" t="s">
-        <v>885</v>
-      </c>
       <c r="D166" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="E166" s="1" t="s">
+        <v>881</v>
+      </c>
+      <c r="F166" s="5" t="s">
         <v>882</v>
-      </c>
-      <c r="F166" s="5" t="s">
-        <v>883</v>
       </c>
       <c r="G166" s="5"/>
       <c r="H166" s="1"/>
@@ -62229,17 +62255,17 @@
       <c r="K166" s="1"/>
       <c r="L166" s="1"/>
       <c r="M166" s="4" t="s">
-        <v>890</v>
-      </c>
-    </row>
-    <row r="167" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>889</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="str">
         <f>IF(receta!A167="","",receta!A167)</f>
         <v>Boulevardier</v>
       </c>
       <c r="B167" s="1"/>
       <c r="C167" s="4" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="D167" s="4"/>
       <c r="E167" s="1"/>
@@ -62252,14 +62278,14 @@
       <c r="L167" s="1"/>
       <c r="M167" s="1"/>
     </row>
-    <row r="168" spans="1:13" ht="180" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:13" ht="180" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="str">
         <f>IF(receta!A168="","",receta!A168)</f>
         <v>Old Pal</v>
       </c>
       <c r="B168" s="1"/>
       <c r="C168" s="4" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
       <c r="D168" s="4"/>
       <c r="E168" s="1"/>
@@ -62271,19 +62297,19 @@
       <c r="K168" s="1"/>
       <c r="L168" s="1"/>
       <c r="M168" s="4" t="s">
-        <v>1013</v>
-      </c>
-    </row>
-    <row r="169" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="169" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="str">
         <f>IF(receta!A169="","",receta!A169)</f>
         <v>Chardonnay Sour</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="D169" s="4"/>
       <c r="E169" s="1"/>
@@ -62296,25 +62322,25 @@
       <c r="L169" s="1"/>
       <c r="M169" s="1"/>
     </row>
-    <row r="170" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="str">
         <f>IF(receta!A170="","",receta!A170)</f>
         <v>Carmenere Sour</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="G170" s="1"/>
       <c r="H170" s="1"/>
@@ -62323,22 +62349,22 @@
       <c r="K170" s="1"/>
       <c r="L170" s="1"/>
       <c r="M170" s="4" t="s">
-        <v>902</v>
-      </c>
-    </row>
-    <row r="171" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>901</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="str">
         <f>IF(receta!A171="","",receta!A171)</f>
         <v>Jerez Sour</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="E171" s="1"/>
       <c r="F171" s="1"/>
@@ -62349,10 +62375,10 @@
       <c r="K171" s="1"/>
       <c r="L171" s="1"/>
       <c r="M171" s="4" t="s">
-        <v>907</v>
-      </c>
-    </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="172" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="str">
         <f>IF(receta!A172="","",receta!A172)</f>
         <v/>
@@ -62370,7 +62396,7 @@
       <c r="L172" s="1"/>
       <c r="M172" s="1"/>
     </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="str">
         <f>IF(receta!A173="","",receta!A173)</f>
         <v/>
@@ -62388,7 +62414,7 @@
       <c r="L173" s="1"/>
       <c r="M173" s="1"/>
     </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="str">
         <f>IF(receta!A174="","",receta!A174)</f>
         <v/>
@@ -62406,7 +62432,7 @@
       <c r="L174" s="1"/>
       <c r="M174" s="1"/>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="str">
         <f>IF(receta!A175="","",receta!A175)</f>
         <v/>
@@ -62424,7 +62450,7 @@
       <c r="L175" s="1"/>
       <c r="M175" s="1"/>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="str">
         <f>IF(receta!A176="","",receta!A176)</f>
         <v/>
@@ -62442,7 +62468,7 @@
       <c r="L176" s="1"/>
       <c r="M176" s="1"/>
     </row>
-    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="str">
         <f>IF(receta!A177="","",receta!A177)</f>
         <v/>
@@ -62460,7 +62486,7 @@
       <c r="L177" s="1"/>
       <c r="M177" s="1"/>
     </row>
-    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="str">
         <f>IF(receta!A178="","",receta!A178)</f>
         <v/>
@@ -62478,7 +62504,7 @@
       <c r="L178" s="1"/>
       <c r="M178" s="1"/>
     </row>
-    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="str">
         <f>IF(receta!A179="","",receta!A179)</f>
         <v/>
@@ -62496,7 +62522,7 @@
       <c r="L179" s="1"/>
       <c r="M179" s="1"/>
     </row>
-    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="str">
         <f>IF(receta!A180="","",receta!A180)</f>
         <v/>
@@ -62514,7 +62540,7 @@
       <c r="L180" s="1"/>
       <c r="M180" s="1"/>
     </row>
-    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="str">
         <f>IF(receta!A181="","",receta!A181)</f>
         <v/>
@@ -62532,7 +62558,7 @@
       <c r="L181" s="1"/>
       <c r="M181" s="1"/>
     </row>
-    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="str">
         <f>IF(receta!A182="","",receta!A182)</f>
         <v/>
@@ -62550,7 +62576,7 @@
       <c r="L182" s="1"/>
       <c r="M182" s="1"/>
     </row>
-    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="str">
         <f>IF(receta!A183="","",receta!A183)</f>
         <v/>
@@ -62568,7 +62594,7 @@
       <c r="L183" s="1"/>
       <c r="M183" s="1"/>
     </row>
-    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="str">
         <f>IF(receta!A184="","",receta!A184)</f>
         <v/>
@@ -62586,7 +62612,7 @@
       <c r="L184" s="1"/>
       <c r="M184" s="1"/>
     </row>
-    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="str">
         <f>IF(receta!A185="","",receta!A185)</f>
         <v/>
@@ -62604,7 +62630,7 @@
       <c r="L185" s="1"/>
       <c r="M185" s="1"/>
     </row>
-    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="str">
         <f>IF(receta!A186="","",receta!A186)</f>
         <v/>
@@ -62622,7 +62648,7 @@
       <c r="L186" s="1"/>
       <c r="M186" s="1"/>
     </row>
-    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="str">
         <f>IF(receta!A187="","",receta!A187)</f>
         <v/>
@@ -62640,7 +62666,7 @@
       <c r="L187" s="1"/>
       <c r="M187" s="1"/>
     </row>
-    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="str">
         <f>IF(receta!A188="","",receta!A188)</f>
         <v/>
@@ -62658,7 +62684,7 @@
       <c r="L188" s="1"/>
       <c r="M188" s="1"/>
     </row>
-    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="str">
         <f>IF(receta!A189="","",receta!A189)</f>
         <v/>
@@ -62676,7 +62702,7 @@
       <c r="L189" s="1"/>
       <c r="M189" s="1"/>
     </row>
-    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="str">
         <f>IF(receta!A190="","",receta!A190)</f>
         <v/>
@@ -62694,7 +62720,7 @@
       <c r="L190" s="1"/>
       <c r="M190" s="1"/>
     </row>
-    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="str">
         <f>IF(receta!A191="","",receta!A191)</f>
         <v/>
@@ -62712,7 +62738,7 @@
       <c r="L191" s="1"/>
       <c r="M191" s="1"/>
     </row>
-    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="str">
         <f>IF(receta!A192="","",receta!A192)</f>
         <v/>
@@ -62730,7 +62756,7 @@
       <c r="L192" s="1"/>
       <c r="M192" s="1"/>
     </row>
-    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="str">
         <f>IF(receta!A193="","",receta!A193)</f>
         <v/>
@@ -62748,7 +62774,7 @@
       <c r="L193" s="1"/>
       <c r="M193" s="1"/>
     </row>
-    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="str">
         <f>IF(receta!A194="","",receta!A194)</f>
         <v/>
@@ -62766,7 +62792,7 @@
       <c r="L194" s="1"/>
       <c r="M194" s="1"/>
     </row>
-    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="str">
         <f>IF(receta!A195="","",receta!A195)</f>
         <v/>
@@ -62784,7 +62810,7 @@
       <c r="L195" s="1"/>
       <c r="M195" s="1"/>
     </row>
-    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="str">
         <f>IF(receta!A196="","",receta!A196)</f>
         <v/>
@@ -62802,7 +62828,7 @@
       <c r="L196" s="1"/>
       <c r="M196" s="1"/>
     </row>
-    <row r="197" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="str">
         <f>IF(receta!A197="","",receta!A197)</f>
         <v/>
@@ -62820,7 +62846,7 @@
       <c r="L197" s="1"/>
       <c r="M197" s="1"/>
     </row>
-    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="str">
         <f>IF(receta!A198="","",receta!A198)</f>
         <v/>
@@ -62838,7 +62864,7 @@
       <c r="L198" s="1"/>
       <c r="M198" s="1"/>
     </row>
-    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="str">
         <f>IF(receta!A199="","",receta!A199)</f>
         <v/>
@@ -62856,7 +62882,7 @@
       <c r="L199" s="1"/>
       <c r="M199" s="1"/>
     </row>
-    <row r="200" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="str">
         <f>IF(receta!A200="","",receta!A200)</f>
         <v/>
@@ -62874,7 +62900,7 @@
       <c r="L200" s="1"/>
       <c r="M200" s="1"/>
     </row>
-    <row r="201" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="str">
         <f>IF(receta!A201="","",receta!A201)</f>
         <v/>
@@ -62892,7 +62918,7 @@
       <c r="L201" s="1"/>
       <c r="M201" s="1"/>
     </row>
-    <row r="202" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="str">
         <f>IF(receta!A202="","",receta!A202)</f>
         <v/>
@@ -62910,7 +62936,7 @@
       <c r="L202" s="1"/>
       <c r="M202" s="1"/>
     </row>
-    <row r="203" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="str">
         <f>IF(receta!A203="","",receta!A203)</f>
         <v/>
@@ -62928,7 +62954,7 @@
       <c r="L203" s="1"/>
       <c r="M203" s="1"/>
     </row>
-    <row r="204" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="str">
         <f>IF(receta!A204="","",receta!A204)</f>
         <v/>
@@ -62946,7 +62972,7 @@
       <c r="L204" s="1"/>
       <c r="M204" s="1"/>
     </row>
-    <row r="205" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="str">
         <f>IF(receta!A205="","",receta!A205)</f>
         <v/>
@@ -62964,7 +62990,7 @@
       <c r="L205" s="1"/>
       <c r="M205" s="1"/>
     </row>
-    <row r="206" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="str">
         <f>IF(receta!A206="","",receta!A206)</f>
         <v/>
@@ -62982,7 +63008,7 @@
       <c r="L206" s="1"/>
       <c r="M206" s="1"/>
     </row>
-    <row r="207" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="str">
         <f>IF(receta!A207="","",receta!A207)</f>
         <v/>
@@ -63000,7 +63026,7 @@
       <c r="L207" s="1"/>
       <c r="M207" s="1"/>
     </row>
-    <row r="208" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="str">
         <f>IF(receta!A208="","",receta!A208)</f>
         <v/>
@@ -63018,7 +63044,7 @@
       <c r="L208" s="1"/>
       <c r="M208" s="1"/>
     </row>
-    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="str">
         <f>IF(receta!A209="","",receta!A209)</f>
         <v/>
@@ -63036,7 +63062,7 @@
       <c r="L209" s="1"/>
       <c r="M209" s="1"/>
     </row>
-    <row r="210" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="str">
         <f>IF(receta!A210="","",receta!A210)</f>
         <v/>
@@ -63054,7 +63080,7 @@
       <c r="L210" s="1"/>
       <c r="M210" s="1"/>
     </row>
-    <row r="211" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="str">
         <f>IF(receta!A211="","",receta!A211)</f>
         <v/>
@@ -63072,7 +63098,7 @@
       <c r="L211" s="1"/>
       <c r="M211" s="1"/>
     </row>
-    <row r="212" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="str">
         <f>IF(receta!A212="","",receta!A212)</f>
         <v/>
@@ -63090,7 +63116,7 @@
       <c r="L212" s="1"/>
       <c r="M212" s="1"/>
     </row>
-    <row r="213" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="str">
         <f>IF(receta!A213="","",receta!A213)</f>
         <v/>
@@ -63108,7 +63134,7 @@
       <c r="L213" s="1"/>
       <c r="M213" s="1"/>
     </row>
-    <row r="214" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="str">
         <f>IF(receta!A214="","",receta!A214)</f>
         <v/>
@@ -63126,7 +63152,7 @@
       <c r="L214" s="1"/>
       <c r="M214" s="1"/>
     </row>
-    <row r="215" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="str">
         <f>IF(receta!A215="","",receta!A215)</f>
         <v/>
@@ -63144,7 +63170,7 @@
       <c r="L215" s="1"/>
       <c r="M215" s="1"/>
     </row>
-    <row r="216" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="str">
         <f>IF(receta!A216="","",receta!A216)</f>
         <v/>
@@ -63162,7 +63188,7 @@
       <c r="L216" s="1"/>
       <c r="M216" s="1"/>
     </row>
-    <row r="217" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="str">
         <f>IF(receta!A217="","",receta!A217)</f>
         <v/>
@@ -63180,7 +63206,7 @@
       <c r="L217" s="1"/>
       <c r="M217" s="1"/>
     </row>
-    <row r="218" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="str">
         <f>IF(receta!A218="","",receta!A218)</f>
         <v/>
@@ -63198,7 +63224,7 @@
       <c r="L218" s="1"/>
       <c r="M218" s="1"/>
     </row>
-    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="str">
         <f>IF(receta!A219="","",receta!A219)</f>
         <v/>
@@ -63216,7 +63242,7 @@
       <c r="L219" s="1"/>
       <c r="M219" s="1"/>
     </row>
-    <row r="220" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="str">
         <f>IF(receta!A220="","",receta!A220)</f>
         <v/>
@@ -63234,7 +63260,7 @@
       <c r="L220" s="1"/>
       <c r="M220" s="1"/>
     </row>
-    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="str">
         <f>IF(receta!A221="","",receta!A221)</f>
         <v/>
@@ -63252,7 +63278,7 @@
       <c r="L221" s="1"/>
       <c r="M221" s="1"/>
     </row>
-    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="str">
         <f>IF(receta!A222="","",receta!A222)</f>
         <v/>
@@ -63270,7 +63296,7 @@
       <c r="L222" s="1"/>
       <c r="M222" s="1"/>
     </row>
-    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="str">
         <f>IF(receta!A223="","",receta!A223)</f>
         <v/>
@@ -63288,7 +63314,7 @@
       <c r="L223" s="1"/>
       <c r="M223" s="1"/>
     </row>
-    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="str">
         <f>IF(receta!A224="","",receta!A224)</f>
         <v/>
@@ -63306,7 +63332,7 @@
       <c r="L224" s="1"/>
       <c r="M224" s="1"/>
     </row>
-    <row r="225" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="str">
         <f>IF(receta!A225="","",receta!A225)</f>
         <v/>
@@ -63324,7 +63350,7 @@
       <c r="L225" s="1"/>
       <c r="M225" s="1"/>
     </row>
-    <row r="226" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="str">
         <f>IF(receta!A226="","",receta!A226)</f>
         <v/>
@@ -63342,7 +63368,7 @@
       <c r="L226" s="1"/>
       <c r="M226" s="1"/>
     </row>
-    <row r="227" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="str">
         <f>IF(receta!A227="","",receta!A227)</f>
         <v/>
@@ -63360,7 +63386,7 @@
       <c r="L227" s="1"/>
       <c r="M227" s="1"/>
     </row>
-    <row r="228" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="str">
         <f>IF(receta!A228="","",receta!A228)</f>
         <v/>
@@ -63378,7 +63404,7 @@
       <c r="L228" s="1"/>
       <c r="M228" s="1"/>
     </row>
-    <row r="229" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="str">
         <f>IF(receta!A229="","",receta!A229)</f>
         <v/>
@@ -63396,7 +63422,7 @@
       <c r="L229" s="1"/>
       <c r="M229" s="1"/>
     </row>
-    <row r="230" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="str">
         <f>IF(receta!A230="","",receta!A230)</f>
         <v/>
@@ -63414,7 +63440,7 @@
       <c r="L230" s="1"/>
       <c r="M230" s="1"/>
     </row>
-    <row r="231" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="str">
         <f>IF(receta!A231="","",receta!A231)</f>
         <v/>
@@ -63432,7 +63458,7 @@
       <c r="L231" s="1"/>
       <c r="M231" s="1"/>
     </row>
-    <row r="232" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="str">
         <f>IF(receta!A232="","",receta!A232)</f>
         <v/>
@@ -63450,7 +63476,7 @@
       <c r="L232" s="1"/>
       <c r="M232" s="1"/>
     </row>
-    <row r="233" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="str">
         <f>IF(receta!A233="","",receta!A233)</f>
         <v/>
@@ -63468,7 +63494,7 @@
       <c r="L233" s="1"/>
       <c r="M233" s="1"/>
     </row>
-    <row r="234" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="str">
         <f>IF(receta!A234="","",receta!A234)</f>
         <v/>
@@ -63486,7 +63512,7 @@
       <c r="L234" s="1"/>
       <c r="M234" s="1"/>
     </row>
-    <row r="235" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="str">
         <f>IF(receta!A235="","",receta!A235)</f>
         <v/>
@@ -63504,7 +63530,7 @@
       <c r="L235" s="1"/>
       <c r="M235" s="1"/>
     </row>
-    <row r="236" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="str">
         <f>IF(receta!A236="","",receta!A236)</f>
         <v/>
@@ -63522,7 +63548,7 @@
       <c r="L236" s="1"/>
       <c r="M236" s="1"/>
     </row>
-    <row r="237" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="str">
         <f>IF(receta!A237="","",receta!A237)</f>
         <v/>
@@ -63540,7 +63566,7 @@
       <c r="L237" s="1"/>
       <c r="M237" s="1"/>
     </row>
-    <row r="238" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="str">
         <f>IF(receta!A238="","",receta!A238)</f>
         <v/>
@@ -63558,7 +63584,7 @@
       <c r="L238" s="1"/>
       <c r="M238" s="1"/>
     </row>
-    <row r="239" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="str">
         <f>IF(receta!A239="","",receta!A239)</f>
         <v/>
@@ -63576,7 +63602,7 @@
       <c r="L239" s="1"/>
       <c r="M239" s="1"/>
     </row>
-    <row r="240" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="str">
         <f>IF(receta!A240="","",receta!A240)</f>
         <v/>
@@ -63594,7 +63620,7 @@
       <c r="L240" s="1"/>
       <c r="M240" s="1"/>
     </row>
-    <row r="241" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="str">
         <f>IF(receta!A241="","",receta!A241)</f>
         <v/>
@@ -63612,7 +63638,7 @@
       <c r="L241" s="1"/>
       <c r="M241" s="1"/>
     </row>
-    <row r="242" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="str">
         <f>IF(receta!A242="","",receta!A242)</f>
         <v/>
@@ -63630,7 +63656,7 @@
       <c r="L242" s="1"/>
       <c r="M242" s="1"/>
     </row>
-    <row r="243" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="str">
         <f>IF(receta!A243="","",receta!A243)</f>
         <v/>
@@ -63648,7 +63674,7 @@
       <c r="L243" s="1"/>
       <c r="M243" s="1"/>
     </row>
-    <row r="244" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="str">
         <f>IF(receta!A244="","",receta!A244)</f>
         <v/>
@@ -63666,7 +63692,7 @@
       <c r="L244" s="1"/>
       <c r="M244" s="1"/>
     </row>
-    <row r="245" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="str">
         <f>IF(receta!A245="","",receta!A245)</f>
         <v/>
@@ -63684,7 +63710,7 @@
       <c r="L245" s="1"/>
       <c r="M245" s="1"/>
     </row>
-    <row r="246" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="str">
         <f>IF(receta!A246="","",receta!A246)</f>
         <v/>
@@ -63702,7 +63728,7 @@
       <c r="L246" s="1"/>
       <c r="M246" s="1"/>
     </row>
-    <row r="247" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="str">
         <f>IF(receta!A247="","",receta!A247)</f>
         <v/>
@@ -63720,7 +63746,7 @@
       <c r="L247" s="1"/>
       <c r="M247" s="1"/>
     </row>
-    <row r="248" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="str">
         <f>IF(receta!A248="","",receta!A248)</f>
         <v/>
@@ -63738,7 +63764,7 @@
       <c r="L248" s="1"/>
       <c r="M248" s="1"/>
     </row>
-    <row r="249" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="str">
         <f>IF(receta!A249="","",receta!A249)</f>
         <v/>
@@ -63756,7 +63782,7 @@
       <c r="L249" s="1"/>
       <c r="M249" s="1"/>
     </row>
-    <row r="250" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="str">
         <f>IF(receta!A250="","",receta!A250)</f>
         <v/>
@@ -63775,7 +63801,13 @@
       <c r="M250" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M250" xr:uid="{43DB3A21-6E97-43C0-9768-D0796C62C1D9}"/>
+  <autoFilter ref="A1:M250" xr:uid="{43DB3A21-6E97-43C0-9768-D0796C62C1D9}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Laguna Azul"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="F63" r:id="rId1" xr:uid="{F4C5002B-4D4E-44DF-92F8-067F77645455}"/>
@@ -63880,10 +63912,10 @@
         <v>62</v>
       </c>
       <c r="B2" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C2" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -63891,7 +63923,7 @@
         <v>67</v>
       </c>
       <c r="B3" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C3" t="s">
         <v>202</v>
@@ -63902,10 +63934,10 @@
         <v>68</v>
       </c>
       <c r="B4" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C4" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -63913,7 +63945,7 @@
         <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C5" t="s">
         <v>203</v>
@@ -63924,10 +63956,10 @@
         <v>69</v>
       </c>
       <c r="B6" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C6" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -63935,7 +63967,7 @@
         <v>70</v>
       </c>
       <c r="B7" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C7" t="s">
         <v>71</v>
@@ -63943,24 +63975,24 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="B8" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C8" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>810</v>
+      </c>
+      <c r="B9" t="s">
         <v>811</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>812</v>
-      </c>
-      <c r="C9" t="s">
-        <v>813</v>
       </c>
     </row>
   </sheetData>
@@ -63990,7 +64022,7 @@
         <v>115</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -63998,7 +64030,7 @@
         <v>116</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -64006,7 +64038,7 @@
         <v>117</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -64014,7 +64046,7 @@
         <v>118</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -64022,7 +64054,7 @@
         <v>119</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -64030,7 +64062,7 @@
         <v>120</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -64038,7 +64070,7 @@
         <v>215</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -64046,23 +64078,23 @@
         <v>429</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="23" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="23" t="s">
+        <v>704</v>
+      </c>
+      <c r="B11" s="23" t="s">
         <v>705</v>
-      </c>
-      <c r="B11" s="23" t="s">
-        <v>706</v>
       </c>
     </row>
   </sheetData>

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB442779-3323-48FE-AC20-6ACD8268D68B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2247699-EE40-43AD-BF2F-9309D16E2B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
@@ -57978,7 +57978,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43DB3A21-6E97-43C0-9768-D0796C62C1D9}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:M250"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -58038,7 +58037,7 @@
         <v>815</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="270" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="270" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="str">
         <f>IF(receta!A2="","",receta!A2)</f>
         <v>Agua de Valencia</v>
@@ -58066,7 +58065,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="3" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="str">
         <f>IF(receta!A3="","",receta!A3)</f>
         <v>Alejandra</v>
@@ -58090,7 +58089,7 @@
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:13" ht="180" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="180" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="str">
         <f>IF(receta!A4="","",receta!A4)</f>
         <v>Alevosía</v>
@@ -58118,7 +58117,7 @@
       <c r="L4" s="5"/>
       <c r="M4" s="1"/>
     </row>
-    <row r="5" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="str">
         <f>IF(receta!A5="","",receta!A5)</f>
         <v>Alexander</v>
@@ -58148,7 +58147,7 @@
         <v>919</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="270" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="270" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="str">
         <f>IF(receta!A6="","",receta!A6)</f>
         <v>Amaretto Sour</v>
@@ -58176,7 +58175,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="270" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="270" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="str">
         <f>IF(receta!A7="","",receta!A7)</f>
         <v>Amaretto Spritz</v>
@@ -58202,7 +58201,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="210" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="210" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="str">
         <f>IF(receta!A8="","",receta!A8)</f>
         <v>Americano</v>
@@ -58226,7 +58225,7 @@
       <c r="L8" s="1"/>
       <c r="M8" s="1"/>
     </row>
-    <row r="9" spans="1:13" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="str">
         <f>IF(receta!A9="","",receta!A9)</f>
         <v>Amiga Mía</v>
@@ -58254,7 +58253,7 @@
         <v>920</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="210" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" ht="210" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="str">
         <f>IF(receta!A10="","",receta!A10)</f>
         <v>Andes Refresh</v>
@@ -58276,7 +58275,7 @@
       <c r="L10" s="1"/>
       <c r="M10" s="1"/>
     </row>
-    <row r="11" spans="1:13" ht="390" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:13" ht="390" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="str">
         <f>IF(receta!A11="","",receta!A11)</f>
         <v>Aperol Spritz</v>
@@ -58300,7 +58299,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="str">
         <f>IF(receta!A12="","",receta!A12)</f>
         <v>Arándano Sour</v>
@@ -58324,7 +58323,7 @@
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
-    <row r="13" spans="1:13" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="195" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="str">
         <f>IF(receta!A13="","",receta!A13)</f>
         <v>Bellini</v>
@@ -58348,7 +58347,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="str">
         <f>IF(receta!A14="","",receta!A14)</f>
         <v>Bello Barrio</v>
@@ -58376,7 +58375,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="15" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="str">
         <f>IF(receta!A15="","",receta!A15)</f>
         <v>Bitter Batido</v>
@@ -58398,7 +58397,7 @@
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
     </row>
-    <row r="16" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="str">
         <f>IF(receta!A16="","",receta!A16)</f>
         <v>Blanco de Verano</v>
@@ -58422,7 +58421,7 @@
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
     </row>
-    <row r="17" spans="1:13" ht="390" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="390" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="str">
         <f>IF(receta!A17="","",receta!A17)</f>
         <v>Bloody Mary</v>
@@ -58452,7 +58451,7 @@
       <c r="L17" s="10"/>
       <c r="M17" s="1"/>
     </row>
-    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="str">
         <f>IF(receta!A18="","",receta!A18)</f>
         <v>Bloody Mary (Sin Alcohol)</v>
@@ -58476,7 +58475,7 @@
       <c r="L18" s="5"/>
       <c r="M18" s="1"/>
     </row>
-    <row r="19" spans="1:13" ht="180" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="180" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="str">
         <f>IF(receta!A19="","",receta!A19)</f>
         <v>Blue Hawaii</v>
@@ -58502,7 +58501,7 @@
         <v>979</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="str">
         <f>IF(receta!A20="","",receta!A20)</f>
         <v>Blue Hawaiian</v>
@@ -58526,7 +58525,7 @@
       <c r="L20" s="1"/>
       <c r="M20" s="1"/>
     </row>
-    <row r="21" spans="1:13" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="str">
         <f>IF(receta!A21="","",receta!A21)</f>
         <v>Borgoña</v>
@@ -58554,7 +58553,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="375" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="375" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="str">
         <f>IF(receta!A22="","",receta!A22)</f>
         <v>Caipiriña</v>
@@ -58580,7 +58579,7 @@
       <c r="L22" s="5"/>
       <c r="M22" s="1"/>
     </row>
-    <row r="23" spans="1:13" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="str">
         <f>IF(receta!A23="","",receta!A23)</f>
         <v>Campari &amp; Vermouth Tonic</v>
@@ -58602,7 +58601,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="345" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="str">
         <f>IF(receta!A24="","",receta!A24)</f>
         <v>Carajillo</v>
@@ -58626,7 +58625,7 @@
       <c r="L24" s="5"/>
       <c r="M24" s="1"/>
     </row>
-    <row r="25" spans="1:13" ht="360" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:13" ht="360" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="str">
         <f>IF(receta!A25="","",receta!A25)</f>
         <v>Chilcano</v>
@@ -58650,7 +58649,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="str">
         <f>IF(receta!A26="","",receta!A26)</f>
         <v>Chuflay</v>
@@ -58678,7 +58677,7 @@
         <v>998</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="375" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" ht="375" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="str">
         <f>IF(receta!A27="","",receta!A27)</f>
         <v>Chupilca</v>
@@ -58704,7 +58703,7 @@
         <v>982</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="str">
         <f>IF(receta!A28="","",receta!A28)</f>
         <v>Cimarrón</v>
@@ -58730,7 +58729,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="360" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" ht="360" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="str">
         <f>IF(receta!A29="","",receta!A29)</f>
         <v>Clavo Oxidado</v>
@@ -58756,7 +58755,7 @@
         <v>934</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="str">
         <f>IF(receta!A30="","",receta!A30)</f>
         <v>Cléry</v>
@@ -58782,7 +58781,7 @@
         <v>935</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="str">
         <f>IF(receta!A31="","",receta!A31)</f>
         <v>Cléry Chirimoya</v>
@@ -58814,7 +58813,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="240" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" ht="240" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="str">
         <f>IF(receta!A32="","",receta!A32)</f>
         <v>Cléry Durazno</v>
@@ -58840,7 +58839,7 @@
       <c r="L32" s="5"/>
       <c r="M32" s="1"/>
     </row>
-    <row r="33" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="str">
         <f>IF(receta!A33="","",receta!A33)</f>
         <v>Clover Club</v>
@@ -58870,7 +58869,7 @@
         <v>885</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="255" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" ht="255" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="str">
         <f>IF(receta!A34="","",receta!A34)</f>
         <v>Cordillera</v>
@@ -58896,7 +58895,7 @@
         <v>984</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="str">
         <f>IF(receta!A35="","",receta!A35)</f>
         <v>Cosmo Patagonia</v>
@@ -58918,7 +58917,7 @@
       <c r="L35" s="1"/>
       <c r="M35" s="1"/>
     </row>
-    <row r="36" spans="1:13" ht="165" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:13" ht="165" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="str">
         <f>IF(receta!A36="","",receta!A36)</f>
         <v>Cosmopolitan</v>
@@ -58940,7 +58939,7 @@
         <v>963</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="str">
         <f>IF(receta!A37="","",receta!A37)</f>
         <v>Crepúsculo</v>
@@ -58968,7 +58967,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="255" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" ht="255" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="str">
         <f>IF(receta!A38="","",receta!A38)</f>
         <v>Cuba Libre</v>
@@ -58994,7 +58993,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="39" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="str">
         <f>IF(receta!A39="","",receta!A39)</f>
         <v>Cynar Spritz</v>
@@ -59014,7 +59013,7 @@
       <c r="L39" s="1"/>
       <c r="M39" s="1"/>
     </row>
-    <row r="40" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="str">
         <f>IF(receta!A40="","",receta!A40)</f>
         <v>Daiquiri</v>
@@ -59044,7 +59043,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="210" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:13" ht="210" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="str">
         <f>IF(receta!A41="","",receta!A41)</f>
         <v>Dama Blanca</v>
@@ -59066,7 +59065,7 @@
       <c r="L41" s="1"/>
       <c r="M41" s="1"/>
     </row>
-    <row r="42" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="str">
         <f>IF(receta!A42="","",receta!A42)</f>
         <v>Dark &amp; Stormy</v>
@@ -59092,7 +59091,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="270" hidden="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:13" ht="270" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="str">
         <f>IF(receta!A43="","",receta!A43)</f>
         <v>Destornillador</v>
@@ -59120,7 +59119,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="str">
         <f>IF(receta!A44="","",receta!A44)</f>
         <v>Doug's Death</v>
@@ -59140,7 +59139,7 @@
       <c r="L44" s="1"/>
       <c r="M44" s="1"/>
     </row>
-    <row r="45" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="str">
         <f>IF(receta!A45="","",receta!A45)</f>
         <v>Dry Martini</v>
@@ -59164,7 +59163,7 @@
       <c r="L45" s="1"/>
       <c r="M45" s="1"/>
     </row>
-    <row r="46" spans="1:13" ht="285" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" ht="285" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="str">
         <f>IF(receta!A46="","",receta!A46)</f>
         <v>El Amor en los Tiempos del Covid</v>
@@ -59192,7 +59191,7 @@
         <v>992</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="240" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" ht="240" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="str">
         <f>IF(receta!A47="","",receta!A47)</f>
         <v>Enemigo Íntimo</v>
@@ -59220,7 +59219,7 @@
         <v>942</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="315" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" ht="315" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="str">
         <f>IF(receta!A48="","",receta!A48)</f>
         <v>Escarabajo</v>
@@ -59246,7 +59245,7 @@
       <c r="L48" s="5"/>
       <c r="M48" s="1"/>
     </row>
-    <row r="49" spans="1:13" ht="270" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" ht="270" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="str">
         <f>IF(receta!A49="","",receta!A49)</f>
         <v>Española</v>
@@ -59276,7 +59275,7 @@
         <v>1010</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="255" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" ht="255" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="str">
         <f>IF(receta!A50="","",receta!A50)</f>
         <v>Espiral</v>
@@ -59308,7 +59307,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="str">
         <f>IF(receta!A51="","",receta!A51)</f>
         <v>Espresso Martini</v>
@@ -59330,7 +59329,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" ht="150" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="str">
         <f>IF(receta!A52="","",receta!A52)</f>
         <v>Estoy Verde</v>
@@ -59362,7 +59361,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="390" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" ht="390" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="str">
         <f>IF(receta!A53="","",receta!A53)</f>
         <v>Fanshop</v>
@@ -59396,7 +59395,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="54" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="str">
         <f>IF(receta!A54="","",receta!A54)</f>
         <v>Faro</v>
@@ -59422,7 +59421,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="55" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="str">
         <f>IF(receta!A55="","",receta!A55)</f>
         <v>Feria Libre</v>
@@ -59446,7 +59445,7 @@
       <c r="L55" s="5"/>
       <c r="M55" s="1"/>
     </row>
-    <row r="56" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="str">
         <f>IF(receta!A56="","",receta!A56)</f>
         <v>Fernet con Coca</v>
@@ -59476,7 +59475,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="57" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="str">
         <f>IF(receta!A57="","",receta!A57)</f>
         <v>Ferroviario</v>
@@ -59504,7 +59503,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="58" spans="1:13" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" ht="150" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="str">
         <f>IF(receta!A58="","",receta!A58)</f>
         <v>Frangelico Sour</v>
@@ -59528,7 +59527,7 @@
         <v>964</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="str">
         <f>IF(receta!A59="","",receta!A59)</f>
         <v>French 75</v>
@@ -59558,7 +59557,7 @@
         <v>962</v>
       </c>
     </row>
-    <row r="60" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="str">
         <f>IF(receta!A60="","",receta!A60)</f>
         <v>Garibaldi</v>
@@ -59580,7 +59579,7 @@
         <v>988</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="165" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" ht="165" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="str">
         <f>IF(receta!A61="","",receta!A61)</f>
         <v>Gimlet</v>
@@ -59608,7 +59607,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" ht="345" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="str">
         <f>IF(receta!A62="","",receta!A62)</f>
         <v>Gin con Gin</v>
@@ -59634,7 +59633,7 @@
         <v>997</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="str">
         <f>IF(receta!A63="","",receta!A63)</f>
         <v>Gin Tonic</v>
@@ -59670,7 +59669,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="str">
         <f>IF(receta!A64="","",receta!A64)</f>
         <v>Ginger Fire</v>
@@ -59692,7 +59691,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="65" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="str">
         <f>IF(receta!A65="","",receta!A65)</f>
         <v>Hemingway Daiquiri</v>
@@ -59716,7 +59715,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="66" spans="1:13" ht="375" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:13" ht="375" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="str">
         <f>IF(receta!A66="","",receta!A66)</f>
         <v>Hugo</v>
@@ -59738,7 +59737,7 @@
       <c r="L66" s="1"/>
       <c r="M66" s="1"/>
     </row>
-    <row r="67" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="str">
         <f>IF(receta!A67="","",receta!A67)</f>
         <v>Incendio</v>
@@ -59764,7 +59763,7 @@
         <v>957</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" ht="330" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="str">
         <f>IF(receta!A68="","",receta!A68)</f>
         <v>Ingrata</v>
@@ -59792,7 +59791,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="300" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" ht="300" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="str">
         <f>IF(receta!A69="","",receta!A69)</f>
         <v>Isla Negra</v>
@@ -59820,7 +59819,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" ht="195" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="str">
         <f>IF(receta!A70="","",receta!A70)</f>
         <v>Jardín</v>
@@ -59848,7 +59847,7 @@
         <v>947</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="225" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" ht="225" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="str">
         <f>IF(receta!A71="","",receta!A71)</f>
         <v>John Collins</v>
@@ -59874,7 +59873,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="str">
         <f>IF(receta!A72="","",receta!A72)</f>
         <v>Jote</v>
@@ -59904,7 +59903,7 @@
         <v>874</v>
       </c>
     </row>
-    <row r="73" spans="1:13" ht="225" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:13" ht="225" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="str">
         <f>IF(receta!A73="","",receta!A73)</f>
         <v>Julepe de Menta</v>
@@ -59926,7 +59925,7 @@
       <c r="L73" s="1"/>
       <c r="M73" s="1"/>
     </row>
-    <row r="74" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="str">
         <f>IF(receta!A74="","",receta!A74)</f>
         <v>Julieta Flowers</v>
@@ -59958,7 +59957,7 @@
       <c r="L74" s="5"/>
       <c r="M74" s="1"/>
     </row>
-    <row r="75" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="str">
         <f>IF(receta!A75="","",receta!A75)</f>
         <v>Kir Royal</v>
@@ -59978,7 +59977,7 @@
       <c r="L75" s="1"/>
       <c r="M75" s="1"/>
     </row>
-    <row r="76" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="str">
         <f>IF(receta!A76="","",receta!A76)</f>
         <v>Kokomo</v>
@@ -60028,7 +60027,7 @@
         <v>1019</v>
       </c>
     </row>
-    <row r="78" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="str">
         <f>IF(receta!A78="","",receta!A78)</f>
         <v>London Mule</v>
@@ -60056,7 +60055,7 @@
       <c r="L78" s="5"/>
       <c r="M78" s="1"/>
     </row>
-    <row r="79" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A79" s="1" t="str">
         <f>IF(receta!A79="","",receta!A79)</f>
         <v>Luisito</v>
@@ -60074,7 +60073,7 @@
       <c r="L79" s="1"/>
       <c r="M79" s="1"/>
     </row>
-    <row r="80" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="str">
         <f>IF(receta!A80="","",receta!A80)</f>
         <v>Luisito (Sin Alcohol)</v>
@@ -60094,7 +60093,7 @@
       <c r="L80" s="1"/>
       <c r="M80" s="1"/>
     </row>
-    <row r="81" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="str">
         <f>IF(receta!A81="","",receta!A81)</f>
         <v>Madras</v>
@@ -60114,7 +60113,7 @@
       <c r="L81" s="1"/>
       <c r="M81" s="1"/>
     </row>
-    <row r="82" spans="1:13" ht="240" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:13" ht="240" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="str">
         <f>IF(receta!A82="","",receta!A82)</f>
         <v>Mai Tai Piña</v>
@@ -60140,7 +60139,7 @@
       <c r="L82" s="1"/>
       <c r="M82" s="1"/>
     </row>
-    <row r="83" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="str">
         <f>IF(receta!A83="","",receta!A83)</f>
         <v>Mala Reputación</v>
@@ -60168,7 +60167,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="84" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="str">
         <f>IF(receta!A84="","",receta!A84)</f>
         <v>Malta con Huevo</v>
@@ -60198,7 +60197,7 @@
         <v>990</v>
       </c>
     </row>
-    <row r="85" spans="1:13" ht="240" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:13" ht="240" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="str">
         <f>IF(receta!A85="","",receta!A85)</f>
         <v>Malta con Leche Condensada</v>
@@ -60228,7 +60227,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="86" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="str">
         <f>IF(receta!A86="","",receta!A86)</f>
         <v>Mango Sour</v>
@@ -60248,7 +60247,7 @@
       <c r="L86" s="1"/>
       <c r="M86" s="1"/>
     </row>
-    <row r="87" spans="1:13" ht="165" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" ht="165" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="str">
         <f>IF(receta!A87="","",receta!A87)</f>
         <v>Manhattan</v>
@@ -60278,7 +60277,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="88" spans="1:13" ht="360" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:13" ht="360" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="str">
         <f>IF(receta!A88="","",receta!A88)</f>
         <v>Maqui Sour</v>
@@ -60302,7 +60301,7 @@
       <c r="L88" s="1"/>
       <c r="M88" s="1"/>
     </row>
-    <row r="89" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="str">
         <f>IF(receta!A89="","",receta!A89)</f>
         <v>Margarita</v>
@@ -60328,7 +60327,7 @@
       <c r="L89" s="5"/>
       <c r="M89" s="1"/>
     </row>
-    <row r="90" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="str">
         <f>IF(receta!A90="","",receta!A90)</f>
         <v>Margarita Maracuyá</v>
@@ -60350,7 +60349,7 @@
       <c r="L90" s="5"/>
       <c r="M90" s="1"/>
     </row>
-    <row r="91" spans="1:13" ht="225" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" ht="225" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="str">
         <f>IF(receta!A91="","",receta!A91)</f>
         <v>Melón con Vino</v>
@@ -60376,7 +60375,7 @@
       <c r="L91" s="5"/>
       <c r="M91" s="1"/>
     </row>
-    <row r="92" spans="1:13" ht="375" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" ht="375" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="str">
         <f>IF(receta!A92="","",receta!A92)</f>
         <v>Michelada</v>
@@ -60404,7 +60403,7 @@
       <c r="L92" s="5"/>
       <c r="M92" s="1"/>
     </row>
-    <row r="93" spans="1:13" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" ht="150" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="str">
         <f>IF(receta!A93="","",receta!A93)</f>
         <v>Milano Torino</v>
@@ -60424,7 +60423,7 @@
       <c r="L93" s="1"/>
       <c r="M93" s="1"/>
     </row>
-    <row r="94" spans="1:13" ht="180" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" ht="180" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="str">
         <f>IF(receta!A94="","",receta!A94)</f>
         <v>Mimosa</v>
@@ -60444,7 +60443,7 @@
       <c r="L94" s="1"/>
       <c r="M94" s="1"/>
     </row>
-    <row r="95" spans="1:13" ht="225" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:13" ht="225" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="str">
         <f>IF(receta!A95="","",receta!A95)</f>
         <v>Mojito</v>
@@ -60468,7 +60467,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="96" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="str">
         <f>IF(receta!A96="","",receta!A96)</f>
         <v>Mojito (Sin Alcohol)</v>
@@ -60488,7 +60487,7 @@
       <c r="L96" s="1"/>
       <c r="M96" s="1"/>
     </row>
-    <row r="97" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="str">
         <f>IF(receta!A97="","",receta!A97)</f>
         <v>Mojito Maracuyá</v>
@@ -60516,7 +60515,7 @@
         <v>1001</v>
       </c>
     </row>
-    <row r="98" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="str">
         <f>IF(receta!A98="","",receta!A98)</f>
         <v>Mojito Spritz</v>
@@ -60536,7 +60535,7 @@
       <c r="L98" s="1"/>
       <c r="M98" s="1"/>
     </row>
-    <row r="99" spans="1:13" ht="375" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" ht="375" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="str">
         <f>IF(receta!A99="","",receta!A99)</f>
         <v>Moscow Mule</v>
@@ -60562,7 +60561,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="100" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="str">
         <f>IF(receta!A100="","",receta!A100)</f>
         <v>Naranja Sour</v>
@@ -60588,7 +60587,7 @@
       <c r="L100" s="5"/>
       <c r="M100" s="1"/>
     </row>
-    <row r="101" spans="1:13" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:13" ht="195" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="str">
         <f>IF(receta!A101="","",receta!A101)</f>
         <v>Negativismo Lógico</v>
@@ -60612,7 +60611,7 @@
       <c r="L101" s="1"/>
       <c r="M101" s="1"/>
     </row>
-    <row r="102" spans="1:13" ht="210" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:13" ht="210" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="str">
         <f>IF(receta!A102="","",receta!A102)</f>
         <v>Negroni</v>
@@ -60636,7 +60635,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="103" spans="1:13" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" ht="150" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="str">
         <f>IF(receta!A103="","",receta!A103)</f>
         <v>Negroni Sbagliato</v>
@@ -60656,7 +60655,7 @@
       <c r="L103" s="1"/>
       <c r="M103" s="1"/>
     </row>
-    <row r="104" spans="1:13" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" ht="345" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="str">
         <f>IF(receta!A104="","",receta!A104)</f>
         <v>New York Sour</v>
@@ -60686,7 +60685,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="105" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="str">
         <f>IF(receta!A105="","",receta!A105)</f>
         <v>No Me Falles</v>
@@ -60712,7 +60711,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="106" spans="1:13" ht="240" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" ht="240" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="str">
         <f>IF(receta!A106="","",receta!A106)</f>
         <v>Old Fashioned</v>
@@ -60734,7 +60733,7 @@
       <c r="L106" s="1"/>
       <c r="M106" s="1"/>
     </row>
-    <row r="107" spans="1:13" ht="192" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:13" ht="192" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="str">
         <f>IF(receta!A107="","",receta!A107)</f>
         <v>Padrino</v>
@@ -60754,7 +60753,7 @@
       <c r="L107" s="1"/>
       <c r="M107" s="1"/>
     </row>
-    <row r="108" spans="1:13" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:13" ht="195" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="str">
         <f>IF(receta!A108="","",receta!A108)</f>
         <v>Paloma</v>
@@ -60786,7 +60785,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="109" spans="1:13" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="str">
         <f>IF(receta!A109="","",receta!A109)</f>
         <v>Parrón</v>
@@ -60806,7 +60805,7 @@
       <c r="L109" s="1"/>
       <c r="M109" s="1"/>
     </row>
-    <row r="110" spans="1:13" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" ht="330" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="str">
         <f>IF(receta!A110="","",receta!A110)</f>
         <v>Penicilina</v>
@@ -60836,7 +60835,7 @@
         <v>1013</v>
       </c>
     </row>
-    <row r="111" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="str">
         <f>IF(receta!A111="","",receta!A111)</f>
         <v>Phil Collins</v>
@@ -60860,7 +60859,7 @@
       <c r="L111" s="5"/>
       <c r="M111" s="1"/>
     </row>
-    <row r="112" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="str">
         <f>IF(receta!A112="","",receta!A112)</f>
         <v>Pichuncho</v>
@@ -60884,7 +60883,7 @@
       <c r="L112" s="5"/>
       <c r="M112" s="1"/>
     </row>
-    <row r="113" spans="1:13" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" ht="195" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="str">
         <f>IF(receta!A113="","",receta!A113)</f>
         <v>Piña Colada</v>
@@ -60910,7 +60909,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="114" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="str">
         <f>IF(receta!A114="","",receta!A114)</f>
         <v>Piña Colada (Sin Alcohol)</v>
@@ -60930,7 +60929,7 @@
       <c r="L114" s="1"/>
       <c r="M114" s="1"/>
     </row>
-    <row r="115" spans="1:13" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" ht="195" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="str">
         <f>IF(receta!A115="","",receta!A115)</f>
         <v>Pisco Punch</v>
@@ -60950,7 +60949,7 @@
       <c r="L115" s="1"/>
       <c r="M115" s="1"/>
     </row>
-    <row r="116" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="str">
         <f>IF(receta!A116="","",receta!A116)</f>
         <v>Pisco Sour</v>
@@ -60976,7 +60975,7 @@
       <c r="L116" s="5"/>
       <c r="M116" s="1"/>
     </row>
-    <row r="117" spans="1:13" ht="210" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" ht="210" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="str">
         <f>IF(receta!A117="","",receta!A117)</f>
         <v>Piscola</v>
@@ -61004,7 +61003,7 @@
         <v>1018</v>
       </c>
     </row>
-    <row r="118" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="str">
         <f>IF(receta!A118="","",receta!A118)</f>
         <v>Pistón</v>
@@ -61030,7 +61029,7 @@
       <c r="L118" s="5"/>
       <c r="M118" s="1"/>
     </row>
-    <row r="119" spans="1:13" ht="375" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:13" ht="375" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="str">
         <f>IF(receta!A119="","",receta!A119)</f>
         <v>Quédate</v>
@@ -61058,7 +61057,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="120" spans="1:13" ht="75" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" ht="75" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="str">
         <f>IF(receta!A120="","",receta!A120)</f>
         <v>Ramazzotti Spritz</v>
@@ -61082,7 +61081,7 @@
       <c r="L120" s="5"/>
       <c r="M120" s="1"/>
     </row>
-    <row r="121" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="str">
         <f>IF(receta!A121="","",receta!A121)</f>
         <v>Ramazzotti Violetto Spritz</v>
@@ -61102,7 +61101,7 @@
       <c r="L121" s="1"/>
       <c r="M121" s="1"/>
     </row>
-    <row r="122" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="str">
         <f>IF(receta!A122="","",receta!A122)</f>
         <v>Ron Cola</v>
@@ -61126,7 +61125,7 @@
       <c r="L122" s="1"/>
       <c r="M122" s="1"/>
     </row>
-    <row r="123" spans="1:13" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="str">
         <f>IF(receta!A123="","",receta!A123)</f>
         <v>Ruso Blanco</v>
@@ -61154,7 +61153,7 @@
         <v>928</v>
       </c>
     </row>
-    <row r="124" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="str">
         <f>IF(receta!A124="","",receta!A124)</f>
         <v>Ruso Negro</v>
@@ -61176,7 +61175,7 @@
       <c r="L124" s="1"/>
       <c r="M124" s="1"/>
     </row>
-    <row r="125" spans="1:13" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" ht="330" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="str">
         <f>IF(receta!A125="","",receta!A125)</f>
         <v>Sangría</v>
@@ -61204,7 +61203,7 @@
       <c r="L125" s="1"/>
       <c r="M125" s="1"/>
     </row>
-    <row r="126" spans="1:13" ht="255" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:13" ht="255" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="str">
         <f>IF(receta!A126="","",receta!A126)</f>
         <v>Sangrita</v>
@@ -61224,7 +61223,7 @@
       <c r="L126" s="1"/>
       <c r="M126" s="1"/>
     </row>
-    <row r="127" spans="1:13" ht="165" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" ht="165" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="str">
         <f>IF(receta!A127="","",receta!A127)</f>
         <v>Sea Breeze</v>
@@ -61248,7 +61247,7 @@
       <c r="L127" s="1"/>
       <c r="M127" s="1"/>
     </row>
-    <row r="128" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="str">
         <f>IF(receta!A128="","",receta!A128)</f>
         <v>Serena Libre</v>
@@ -61270,7 +61269,7 @@
         <v>1015</v>
       </c>
     </row>
-    <row r="129" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="str">
         <f>IF(receta!A129="","",receta!A129)</f>
         <v>Sexo en la Playa</v>
@@ -61294,7 +61293,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="130" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="str">
         <f>IF(receta!A130="","",receta!A130)</f>
         <v>Sexo Seguro en la Playa</v>
@@ -61314,7 +61313,7 @@
       <c r="L130" s="1"/>
       <c r="M130" s="1"/>
     </row>
-    <row r="131" spans="1:13" ht="210" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" ht="210" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="str">
         <f>IF(receta!A131="","",receta!A131)</f>
         <v>Sidecar</v>
@@ -61334,7 +61333,7 @@
       <c r="L131" s="1"/>
       <c r="M131" s="1"/>
     </row>
-    <row r="132" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="str">
         <f>IF(receta!A132="","",receta!A132)</f>
         <v>Síndrome Impostor</v>
@@ -61358,7 +61357,7 @@
       <c r="L132" s="5"/>
       <c r="M132" s="1"/>
     </row>
-    <row r="133" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="str">
         <f>IF(receta!A133="","",receta!A133)</f>
         <v>Sour (Sin Alcohol)</v>
@@ -61378,7 +61377,7 @@
       <c r="L133" s="1"/>
       <c r="M133" s="1"/>
     </row>
-    <row r="134" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="str">
         <f>IF(receta!A134="","",receta!A134)</f>
         <v>Tequila Sunrise</v>
@@ -61406,7 +61405,7 @@
         <v>944</v>
       </c>
     </row>
-    <row r="135" spans="1:13" ht="300" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:13" ht="300" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="str">
         <f>IF(receta!A135="","",receta!A135)</f>
         <v>Terremoto</v>
@@ -61436,7 +61435,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="136" spans="1:13" ht="180" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" ht="180" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="str">
         <f>IF(receta!A136="","",receta!A136)</f>
         <v>Terremoto (Sin Alcohol)</v>
@@ -61462,7 +61461,7 @@
       <c r="L136" s="5"/>
       <c r="M136" s="1"/>
     </row>
-    <row r="137" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="str">
         <f>IF(receta!A137="","",receta!A137)</f>
         <v>Tinto de Verano</v>
@@ -61482,7 +61481,7 @@
       <c r="L137" s="1"/>
       <c r="M137" s="1"/>
     </row>
-    <row r="138" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="str">
         <f>IF(receta!A138="","",receta!A138)</f>
         <v>Tom Collins</v>
@@ -61504,7 +61503,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="139" spans="1:13" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:13" ht="195" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="str">
         <f>IF(receta!A139="","",receta!A139)</f>
         <v>Trikahue</v>
@@ -61528,7 +61527,7 @@
       <c r="L139" s="1"/>
       <c r="M139" s="1"/>
     </row>
-    <row r="140" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="str">
         <f>IF(receta!A140="","",receta!A140)</f>
         <v>Tropezón</v>
@@ -61558,7 +61557,7 @@
         <v>1017</v>
       </c>
     </row>
-    <row r="141" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="str">
         <f>IF(receta!A141="","",receta!A141)</f>
         <v>Vaina</v>
@@ -61586,7 +61585,7 @@
       <c r="L141" s="4"/>
       <c r="M141" s="1"/>
     </row>
-    <row r="142" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="str">
         <f>IF(receta!A142="","",receta!A142)</f>
         <v>Valentín</v>
@@ -61610,7 +61609,7 @@
       <c r="L142" s="5"/>
       <c r="M142" s="1"/>
     </row>
-    <row r="143" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="str">
         <f>IF(receta!A143="","",receta!A143)</f>
         <v>Vampiro</v>
@@ -61640,7 +61639,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="144" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="str">
         <f>IF(receta!A144="","",receta!A144)</f>
         <v>Venganza</v>
@@ -61668,7 +61667,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="145" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="str">
         <f>IF(receta!A145="","",receta!A145)</f>
         <v>Vermouth con Soda</v>
@@ -61696,7 +61695,7 @@
       <c r="L145" s="1"/>
       <c r="M145" s="1"/>
     </row>
-    <row r="146" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="str">
         <f>IF(receta!A146="","",receta!A146)</f>
         <v>Violetto Tonic</v>
@@ -61716,7 +61715,7 @@
       <c r="L146" s="1"/>
       <c r="M146" s="1"/>
     </row>
-    <row r="147" spans="1:13" ht="240" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:13" ht="240" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="str">
         <f>IF(receta!A147="","",receta!A147)</f>
         <v>Vodka Cranberry</v>
@@ -61742,7 +61741,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="148" spans="1:13" ht="225" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:13" ht="225" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="str">
         <f>IF(receta!A148="","",receta!A148)</f>
         <v>Whiscola</v>
@@ -61766,7 +61765,7 @@
       <c r="L148" s="5"/>
       <c r="M148" s="1"/>
     </row>
-    <row r="149" spans="1:13" ht="324" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:13" ht="324" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="str">
         <f>IF(receta!A149="","",receta!A149)</f>
         <v>Whiskey Highball</v>
@@ -61792,7 +61791,7 @@
       <c r="L149" s="5"/>
       <c r="M149" s="1"/>
     </row>
-    <row r="150" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="str">
         <f>IF(receta!A150="","",receta!A150)</f>
         <v>Whisky Sour</v>
@@ -61822,7 +61821,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="151" spans="1:13" ht="180" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:13" ht="180" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="str">
         <f>IF(receta!A151="","",receta!A151)</f>
         <v>Bramble</v>
@@ -61850,7 +61849,7 @@
       <c r="L151" s="1"/>
       <c r="M151" s="1"/>
     </row>
-    <row r="152" spans="1:13" ht="180" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:13" ht="180" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="str">
         <f>IF(receta!A152="","",receta!A152)</f>
         <v>Pantera Rosa</v>
@@ -61874,7 +61873,7 @@
       <c r="L152" s="1"/>
       <c r="M152" s="1"/>
     </row>
-    <row r="153" spans="1:13" ht="240" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:13" ht="240" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="str">
         <f>IF(receta!A153="","",receta!A153)</f>
         <v>Gin Basil Smash</v>
@@ -61902,7 +61901,7 @@
       <c r="L153" s="1"/>
       <c r="M153" s="1"/>
     </row>
-    <row r="154" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="str">
         <f>IF(receta!A154="","",receta!A154)</f>
         <v>Vodka Tonic</v>
@@ -61934,7 +61933,7 @@
       </c>
       <c r="M154" s="1"/>
     </row>
-    <row r="155" spans="1:13" ht="240" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:13" ht="240" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="str">
         <f>IF(receta!A155="","",receta!A155)</f>
         <v>Medias de Seda</v>
@@ -61956,7 +61955,7 @@
       <c r="L155" s="1"/>
       <c r="M155" s="1"/>
     </row>
-    <row r="156" spans="1:13" ht="255" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:13" ht="255" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="str">
         <f>IF(receta!A156="","",receta!A156)</f>
         <v>Brandy Sour</v>
@@ -61982,7 +61981,7 @@
       <c r="L156" s="1"/>
       <c r="M156" s="1"/>
     </row>
-    <row r="157" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="str">
         <f>IF(receta!A157="","",receta!A157)</f>
         <v>Juanito Rosado</v>
@@ -62010,7 +62009,7 @@
       <c r="L157" s="1"/>
       <c r="M157" s="4"/>
     </row>
-    <row r="158" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="str">
         <f>IF(receta!A158="","",receta!A158)</f>
         <v>Vino Navegado</v>
@@ -62038,7 +62037,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="159" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="str">
         <f>IF(receta!A159="","",receta!A159)</f>
         <v>Cola de Mono</v>
@@ -62072,7 +62071,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="160" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="str">
         <f>IF(receta!A160="","",receta!A160)</f>
         <v>Chichón</v>
@@ -62094,7 +62093,7 @@
       <c r="L160" s="1"/>
       <c r="M160" s="1"/>
     </row>
-    <row r="161" spans="1:13" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:13" ht="195" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="str">
         <f>IF(receta!A161="","",receta!A161)</f>
         <v>Ramos Fizz</v>
@@ -62116,7 +62115,7 @@
       <c r="L161" s="1"/>
       <c r="M161" s="1"/>
     </row>
-    <row r="162" spans="1:13" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:13" ht="195" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="str">
         <f>IF(receta!A162="","",receta!A162)</f>
         <v>Gin Fizz</v>
@@ -62142,7 +62141,7 @@
       <c r="L162" s="1"/>
       <c r="M162" s="1"/>
     </row>
-    <row r="163" spans="1:13" ht="255" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:13" ht="255" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="str">
         <f>IF(receta!A163="","",receta!A163)</f>
         <v>Carta Breve</v>
@@ -62170,7 +62169,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="164" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="str">
         <f>IF(receta!A164="","",receta!A164)</f>
         <v>Orgasmo</v>
@@ -62202,7 +62201,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="165" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="str">
         <f>IF(receta!A165="","",receta!A165)</f>
         <v>Pihuelo</v>
@@ -62228,7 +62227,7 @@
         <v>994</v>
       </c>
     </row>
-    <row r="166" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="str">
         <f>IF(receta!A166="","",receta!A166)</f>
         <v>Mojito Sandía</v>
@@ -62258,7 +62257,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="167" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="str">
         <f>IF(receta!A167="","",receta!A167)</f>
         <v>Boulevardier</v>
@@ -62278,7 +62277,7 @@
       <c r="L167" s="1"/>
       <c r="M167" s="1"/>
     </row>
-    <row r="168" spans="1:13" ht="180" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:13" ht="180" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="str">
         <f>IF(receta!A168="","",receta!A168)</f>
         <v>Old Pal</v>
@@ -62300,7 +62299,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="169" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="str">
         <f>IF(receta!A169="","",receta!A169)</f>
         <v>Chardonnay Sour</v>
@@ -62322,7 +62321,7 @@
       <c r="L169" s="1"/>
       <c r="M169" s="1"/>
     </row>
-    <row r="170" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="str">
         <f>IF(receta!A170="","",receta!A170)</f>
         <v>Carmenere Sour</v>
@@ -62352,7 +62351,7 @@
         <v>901</v>
       </c>
     </row>
-    <row r="171" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="str">
         <f>IF(receta!A171="","",receta!A171)</f>
         <v>Jerez Sour</v>
@@ -62378,7 +62377,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="172" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="str">
         <f>IF(receta!A172="","",receta!A172)</f>
         <v/>
@@ -62396,7 +62395,7 @@
       <c r="L172" s="1"/>
       <c r="M172" s="1"/>
     </row>
-    <row r="173" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="str">
         <f>IF(receta!A173="","",receta!A173)</f>
         <v/>
@@ -62414,7 +62413,7 @@
       <c r="L173" s="1"/>
       <c r="M173" s="1"/>
     </row>
-    <row r="174" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="str">
         <f>IF(receta!A174="","",receta!A174)</f>
         <v/>
@@ -62432,7 +62431,7 @@
       <c r="L174" s="1"/>
       <c r="M174" s="1"/>
     </row>
-    <row r="175" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="str">
         <f>IF(receta!A175="","",receta!A175)</f>
         <v/>
@@ -62450,7 +62449,7 @@
       <c r="L175" s="1"/>
       <c r="M175" s="1"/>
     </row>
-    <row r="176" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="str">
         <f>IF(receta!A176="","",receta!A176)</f>
         <v/>
@@ -62468,7 +62467,7 @@
       <c r="L176" s="1"/>
       <c r="M176" s="1"/>
     </row>
-    <row r="177" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="177" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="str">
         <f>IF(receta!A177="","",receta!A177)</f>
         <v/>
@@ -62486,7 +62485,7 @@
       <c r="L177" s="1"/>
       <c r="M177" s="1"/>
     </row>
-    <row r="178" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="178" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A178" s="1" t="str">
         <f>IF(receta!A178="","",receta!A178)</f>
         <v/>
@@ -62504,7 +62503,7 @@
       <c r="L178" s="1"/>
       <c r="M178" s="1"/>
     </row>
-    <row r="179" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="179" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A179" s="1" t="str">
         <f>IF(receta!A179="","",receta!A179)</f>
         <v/>
@@ -62522,7 +62521,7 @@
       <c r="L179" s="1"/>
       <c r="M179" s="1"/>
     </row>
-    <row r="180" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="180" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A180" s="1" t="str">
         <f>IF(receta!A180="","",receta!A180)</f>
         <v/>
@@ -62540,7 +62539,7 @@
       <c r="L180" s="1"/>
       <c r="M180" s="1"/>
     </row>
-    <row r="181" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="181" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A181" s="1" t="str">
         <f>IF(receta!A181="","",receta!A181)</f>
         <v/>
@@ -62558,7 +62557,7 @@
       <c r="L181" s="1"/>
       <c r="M181" s="1"/>
     </row>
-    <row r="182" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="182" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A182" s="1" t="str">
         <f>IF(receta!A182="","",receta!A182)</f>
         <v/>
@@ -62576,7 +62575,7 @@
       <c r="L182" s="1"/>
       <c r="M182" s="1"/>
     </row>
-    <row r="183" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="183" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A183" s="1" t="str">
         <f>IF(receta!A183="","",receta!A183)</f>
         <v/>
@@ -62594,7 +62593,7 @@
       <c r="L183" s="1"/>
       <c r="M183" s="1"/>
     </row>
-    <row r="184" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="184" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A184" s="1" t="str">
         <f>IF(receta!A184="","",receta!A184)</f>
         <v/>
@@ -62612,7 +62611,7 @@
       <c r="L184" s="1"/>
       <c r="M184" s="1"/>
     </row>
-    <row r="185" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="185" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A185" s="1" t="str">
         <f>IF(receta!A185="","",receta!A185)</f>
         <v/>
@@ -62630,7 +62629,7 @@
       <c r="L185" s="1"/>
       <c r="M185" s="1"/>
     </row>
-    <row r="186" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="186" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A186" s="1" t="str">
         <f>IF(receta!A186="","",receta!A186)</f>
         <v/>
@@ -62648,7 +62647,7 @@
       <c r="L186" s="1"/>
       <c r="M186" s="1"/>
     </row>
-    <row r="187" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="187" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A187" s="1" t="str">
         <f>IF(receta!A187="","",receta!A187)</f>
         <v/>
@@ -62666,7 +62665,7 @@
       <c r="L187" s="1"/>
       <c r="M187" s="1"/>
     </row>
-    <row r="188" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="188" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A188" s="1" t="str">
         <f>IF(receta!A188="","",receta!A188)</f>
         <v/>
@@ -62684,7 +62683,7 @@
       <c r="L188" s="1"/>
       <c r="M188" s="1"/>
     </row>
-    <row r="189" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="189" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A189" s="1" t="str">
         <f>IF(receta!A189="","",receta!A189)</f>
         <v/>
@@ -62702,7 +62701,7 @@
       <c r="L189" s="1"/>
       <c r="M189" s="1"/>
     </row>
-    <row r="190" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="190" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A190" s="1" t="str">
         <f>IF(receta!A190="","",receta!A190)</f>
         <v/>
@@ -62720,7 +62719,7 @@
       <c r="L190" s="1"/>
       <c r="M190" s="1"/>
     </row>
-    <row r="191" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="191" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A191" s="1" t="str">
         <f>IF(receta!A191="","",receta!A191)</f>
         <v/>
@@ -62738,7 +62737,7 @@
       <c r="L191" s="1"/>
       <c r="M191" s="1"/>
     </row>
-    <row r="192" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="192" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A192" s="1" t="str">
         <f>IF(receta!A192="","",receta!A192)</f>
         <v/>
@@ -62756,7 +62755,7 @@
       <c r="L192" s="1"/>
       <c r="M192" s="1"/>
     </row>
-    <row r="193" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="193" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A193" s="1" t="str">
         <f>IF(receta!A193="","",receta!A193)</f>
         <v/>
@@ -62774,7 +62773,7 @@
       <c r="L193" s="1"/>
       <c r="M193" s="1"/>
     </row>
-    <row r="194" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="194" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A194" s="1" t="str">
         <f>IF(receta!A194="","",receta!A194)</f>
         <v/>
@@ -62792,7 +62791,7 @@
       <c r="L194" s="1"/>
       <c r="M194" s="1"/>
     </row>
-    <row r="195" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="195" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A195" s="1" t="str">
         <f>IF(receta!A195="","",receta!A195)</f>
         <v/>
@@ -62810,7 +62809,7 @@
       <c r="L195" s="1"/>
       <c r="M195" s="1"/>
     </row>
-    <row r="196" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="196" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A196" s="1" t="str">
         <f>IF(receta!A196="","",receta!A196)</f>
         <v/>
@@ -62828,7 +62827,7 @@
       <c r="L196" s="1"/>
       <c r="M196" s="1"/>
     </row>
-    <row r="197" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="197" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A197" s="1" t="str">
         <f>IF(receta!A197="","",receta!A197)</f>
         <v/>
@@ -62846,7 +62845,7 @@
       <c r="L197" s="1"/>
       <c r="M197" s="1"/>
     </row>
-    <row r="198" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="198" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A198" s="1" t="str">
         <f>IF(receta!A198="","",receta!A198)</f>
         <v/>
@@ -62864,7 +62863,7 @@
       <c r="L198" s="1"/>
       <c r="M198" s="1"/>
     </row>
-    <row r="199" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="199" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A199" s="1" t="str">
         <f>IF(receta!A199="","",receta!A199)</f>
         <v/>
@@ -62882,7 +62881,7 @@
       <c r="L199" s="1"/>
       <c r="M199" s="1"/>
     </row>
-    <row r="200" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="200" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A200" s="1" t="str">
         <f>IF(receta!A200="","",receta!A200)</f>
         <v/>
@@ -62900,7 +62899,7 @@
       <c r="L200" s="1"/>
       <c r="M200" s="1"/>
     </row>
-    <row r="201" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="201" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A201" s="1" t="str">
         <f>IF(receta!A201="","",receta!A201)</f>
         <v/>
@@ -62918,7 +62917,7 @@
       <c r="L201" s="1"/>
       <c r="M201" s="1"/>
     </row>
-    <row r="202" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="202" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A202" s="1" t="str">
         <f>IF(receta!A202="","",receta!A202)</f>
         <v/>
@@ -62936,7 +62935,7 @@
       <c r="L202" s="1"/>
       <c r="M202" s="1"/>
     </row>
-    <row r="203" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="203" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A203" s="1" t="str">
         <f>IF(receta!A203="","",receta!A203)</f>
         <v/>
@@ -62954,7 +62953,7 @@
       <c r="L203" s="1"/>
       <c r="M203" s="1"/>
     </row>
-    <row r="204" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="204" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A204" s="1" t="str">
         <f>IF(receta!A204="","",receta!A204)</f>
         <v/>
@@ -62972,7 +62971,7 @@
       <c r="L204" s="1"/>
       <c r="M204" s="1"/>
     </row>
-    <row r="205" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="205" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A205" s="1" t="str">
         <f>IF(receta!A205="","",receta!A205)</f>
         <v/>
@@ -62990,7 +62989,7 @@
       <c r="L205" s="1"/>
       <c r="M205" s="1"/>
     </row>
-    <row r="206" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="206" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A206" s="1" t="str">
         <f>IF(receta!A206="","",receta!A206)</f>
         <v/>
@@ -63008,7 +63007,7 @@
       <c r="L206" s="1"/>
       <c r="M206" s="1"/>
     </row>
-    <row r="207" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="207" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A207" s="1" t="str">
         <f>IF(receta!A207="","",receta!A207)</f>
         <v/>
@@ -63026,7 +63025,7 @@
       <c r="L207" s="1"/>
       <c r="M207" s="1"/>
     </row>
-    <row r="208" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="208" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A208" s="1" t="str">
         <f>IF(receta!A208="","",receta!A208)</f>
         <v/>
@@ -63044,7 +63043,7 @@
       <c r="L208" s="1"/>
       <c r="M208" s="1"/>
     </row>
-    <row r="209" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="209" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A209" s="1" t="str">
         <f>IF(receta!A209="","",receta!A209)</f>
         <v/>
@@ -63062,7 +63061,7 @@
       <c r="L209" s="1"/>
       <c r="M209" s="1"/>
     </row>
-    <row r="210" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="210" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A210" s="1" t="str">
         <f>IF(receta!A210="","",receta!A210)</f>
         <v/>
@@ -63080,7 +63079,7 @@
       <c r="L210" s="1"/>
       <c r="M210" s="1"/>
     </row>
-    <row r="211" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="211" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A211" s="1" t="str">
         <f>IF(receta!A211="","",receta!A211)</f>
         <v/>
@@ -63098,7 +63097,7 @@
       <c r="L211" s="1"/>
       <c r="M211" s="1"/>
     </row>
-    <row r="212" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="212" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A212" s="1" t="str">
         <f>IF(receta!A212="","",receta!A212)</f>
         <v/>
@@ -63116,7 +63115,7 @@
       <c r="L212" s="1"/>
       <c r="M212" s="1"/>
     </row>
-    <row r="213" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="213" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A213" s="1" t="str">
         <f>IF(receta!A213="","",receta!A213)</f>
         <v/>
@@ -63134,7 +63133,7 @@
       <c r="L213" s="1"/>
       <c r="M213" s="1"/>
     </row>
-    <row r="214" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="214" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A214" s="1" t="str">
         <f>IF(receta!A214="","",receta!A214)</f>
         <v/>
@@ -63152,7 +63151,7 @@
       <c r="L214" s="1"/>
       <c r="M214" s="1"/>
     </row>
-    <row r="215" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="215" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A215" s="1" t="str">
         <f>IF(receta!A215="","",receta!A215)</f>
         <v/>
@@ -63170,7 +63169,7 @@
       <c r="L215" s="1"/>
       <c r="M215" s="1"/>
     </row>
-    <row r="216" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="216" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A216" s="1" t="str">
         <f>IF(receta!A216="","",receta!A216)</f>
         <v/>
@@ -63188,7 +63187,7 @@
       <c r="L216" s="1"/>
       <c r="M216" s="1"/>
     </row>
-    <row r="217" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="217" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A217" s="1" t="str">
         <f>IF(receta!A217="","",receta!A217)</f>
         <v/>
@@ -63206,7 +63205,7 @@
       <c r="L217" s="1"/>
       <c r="M217" s="1"/>
     </row>
-    <row r="218" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="218" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A218" s="1" t="str">
         <f>IF(receta!A218="","",receta!A218)</f>
         <v/>
@@ -63224,7 +63223,7 @@
       <c r="L218" s="1"/>
       <c r="M218" s="1"/>
     </row>
-    <row r="219" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="219" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A219" s="1" t="str">
         <f>IF(receta!A219="","",receta!A219)</f>
         <v/>
@@ -63242,7 +63241,7 @@
       <c r="L219" s="1"/>
       <c r="M219" s="1"/>
     </row>
-    <row r="220" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="220" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A220" s="1" t="str">
         <f>IF(receta!A220="","",receta!A220)</f>
         <v/>
@@ -63260,7 +63259,7 @@
       <c r="L220" s="1"/>
       <c r="M220" s="1"/>
     </row>
-    <row r="221" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="221" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A221" s="1" t="str">
         <f>IF(receta!A221="","",receta!A221)</f>
         <v/>
@@ -63278,7 +63277,7 @@
       <c r="L221" s="1"/>
       <c r="M221" s="1"/>
     </row>
-    <row r="222" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="222" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A222" s="1" t="str">
         <f>IF(receta!A222="","",receta!A222)</f>
         <v/>
@@ -63296,7 +63295,7 @@
       <c r="L222" s="1"/>
       <c r="M222" s="1"/>
     </row>
-    <row r="223" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="223" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A223" s="1" t="str">
         <f>IF(receta!A223="","",receta!A223)</f>
         <v/>
@@ -63314,7 +63313,7 @@
       <c r="L223" s="1"/>
       <c r="M223" s="1"/>
     </row>
-    <row r="224" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="224" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A224" s="1" t="str">
         <f>IF(receta!A224="","",receta!A224)</f>
         <v/>
@@ -63332,7 +63331,7 @@
       <c r="L224" s="1"/>
       <c r="M224" s="1"/>
     </row>
-    <row r="225" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="225" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A225" s="1" t="str">
         <f>IF(receta!A225="","",receta!A225)</f>
         <v/>
@@ -63350,7 +63349,7 @@
       <c r="L225" s="1"/>
       <c r="M225" s="1"/>
     </row>
-    <row r="226" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="226" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A226" s="1" t="str">
         <f>IF(receta!A226="","",receta!A226)</f>
         <v/>
@@ -63368,7 +63367,7 @@
       <c r="L226" s="1"/>
       <c r="M226" s="1"/>
     </row>
-    <row r="227" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="227" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A227" s="1" t="str">
         <f>IF(receta!A227="","",receta!A227)</f>
         <v/>
@@ -63386,7 +63385,7 @@
       <c r="L227" s="1"/>
       <c r="M227" s="1"/>
     </row>
-    <row r="228" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="228" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A228" s="1" t="str">
         <f>IF(receta!A228="","",receta!A228)</f>
         <v/>
@@ -63404,7 +63403,7 @@
       <c r="L228" s="1"/>
       <c r="M228" s="1"/>
     </row>
-    <row r="229" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="229" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A229" s="1" t="str">
         <f>IF(receta!A229="","",receta!A229)</f>
         <v/>
@@ -63422,7 +63421,7 @@
       <c r="L229" s="1"/>
       <c r="M229" s="1"/>
     </row>
-    <row r="230" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="230" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A230" s="1" t="str">
         <f>IF(receta!A230="","",receta!A230)</f>
         <v/>
@@ -63440,7 +63439,7 @@
       <c r="L230" s="1"/>
       <c r="M230" s="1"/>
     </row>
-    <row r="231" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="231" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A231" s="1" t="str">
         <f>IF(receta!A231="","",receta!A231)</f>
         <v/>
@@ -63458,7 +63457,7 @@
       <c r="L231" s="1"/>
       <c r="M231" s="1"/>
     </row>
-    <row r="232" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="232" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A232" s="1" t="str">
         <f>IF(receta!A232="","",receta!A232)</f>
         <v/>
@@ -63476,7 +63475,7 @@
       <c r="L232" s="1"/>
       <c r="M232" s="1"/>
     </row>
-    <row r="233" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="233" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A233" s="1" t="str">
         <f>IF(receta!A233="","",receta!A233)</f>
         <v/>
@@ -63494,7 +63493,7 @@
       <c r="L233" s="1"/>
       <c r="M233" s="1"/>
     </row>
-    <row r="234" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="234" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A234" s="1" t="str">
         <f>IF(receta!A234="","",receta!A234)</f>
         <v/>
@@ -63512,7 +63511,7 @@
       <c r="L234" s="1"/>
       <c r="M234" s="1"/>
     </row>
-    <row r="235" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="235" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A235" s="1" t="str">
         <f>IF(receta!A235="","",receta!A235)</f>
         <v/>
@@ -63530,7 +63529,7 @@
       <c r="L235" s="1"/>
       <c r="M235" s="1"/>
     </row>
-    <row r="236" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="236" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A236" s="1" t="str">
         <f>IF(receta!A236="","",receta!A236)</f>
         <v/>
@@ -63548,7 +63547,7 @@
       <c r="L236" s="1"/>
       <c r="M236" s="1"/>
     </row>
-    <row r="237" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="237" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A237" s="1" t="str">
         <f>IF(receta!A237="","",receta!A237)</f>
         <v/>
@@ -63566,7 +63565,7 @@
       <c r="L237" s="1"/>
       <c r="M237" s="1"/>
     </row>
-    <row r="238" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="238" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A238" s="1" t="str">
         <f>IF(receta!A238="","",receta!A238)</f>
         <v/>
@@ -63584,7 +63583,7 @@
       <c r="L238" s="1"/>
       <c r="M238" s="1"/>
     </row>
-    <row r="239" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="239" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A239" s="1" t="str">
         <f>IF(receta!A239="","",receta!A239)</f>
         <v/>
@@ -63602,7 +63601,7 @@
       <c r="L239" s="1"/>
       <c r="M239" s="1"/>
     </row>
-    <row r="240" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="240" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A240" s="1" t="str">
         <f>IF(receta!A240="","",receta!A240)</f>
         <v/>
@@ -63620,7 +63619,7 @@
       <c r="L240" s="1"/>
       <c r="M240" s="1"/>
     </row>
-    <row r="241" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="241" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A241" s="1" t="str">
         <f>IF(receta!A241="","",receta!A241)</f>
         <v/>
@@ -63638,7 +63637,7 @@
       <c r="L241" s="1"/>
       <c r="M241" s="1"/>
     </row>
-    <row r="242" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="242" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A242" s="1" t="str">
         <f>IF(receta!A242="","",receta!A242)</f>
         <v/>
@@ -63656,7 +63655,7 @@
       <c r="L242" s="1"/>
       <c r="M242" s="1"/>
     </row>
-    <row r="243" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="243" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A243" s="1" t="str">
         <f>IF(receta!A243="","",receta!A243)</f>
         <v/>
@@ -63674,7 +63673,7 @@
       <c r="L243" s="1"/>
       <c r="M243" s="1"/>
     </row>
-    <row r="244" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="244" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A244" s="1" t="str">
         <f>IF(receta!A244="","",receta!A244)</f>
         <v/>
@@ -63692,7 +63691,7 @@
       <c r="L244" s="1"/>
       <c r="M244" s="1"/>
     </row>
-    <row r="245" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="245" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A245" s="1" t="str">
         <f>IF(receta!A245="","",receta!A245)</f>
         <v/>
@@ -63710,7 +63709,7 @@
       <c r="L245" s="1"/>
       <c r="M245" s="1"/>
     </row>
-    <row r="246" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="246" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A246" s="1" t="str">
         <f>IF(receta!A246="","",receta!A246)</f>
         <v/>
@@ -63728,7 +63727,7 @@
       <c r="L246" s="1"/>
       <c r="M246" s="1"/>
     </row>
-    <row r="247" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="247" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A247" s="1" t="str">
         <f>IF(receta!A247="","",receta!A247)</f>
         <v/>
@@ -63746,7 +63745,7 @@
       <c r="L247" s="1"/>
       <c r="M247" s="1"/>
     </row>
-    <row r="248" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="248" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A248" s="1" t="str">
         <f>IF(receta!A248="","",receta!A248)</f>
         <v/>
@@ -63764,7 +63763,7 @@
       <c r="L248" s="1"/>
       <c r="M248" s="1"/>
     </row>
-    <row r="249" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="249" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A249" s="1" t="str">
         <f>IF(receta!A249="","",receta!A249)</f>
         <v/>
@@ -63782,7 +63781,7 @@
       <c r="L249" s="1"/>
       <c r="M249" s="1"/>
     </row>
-    <row r="250" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="250" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A250" s="1" t="str">
         <f>IF(receta!A250="","",receta!A250)</f>
         <v/>
@@ -63801,13 +63800,7 @@
       <c r="M250" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M250" xr:uid="{43DB3A21-6E97-43C0-9768-D0796C62C1D9}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Laguna Azul"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:M250" xr:uid="{43DB3A21-6E97-43C0-9768-D0796C62C1D9}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="F63" r:id="rId1" xr:uid="{F4C5002B-4D4E-44DF-92F8-067F77645455}"/>

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2247699-EE40-43AD-BF2F-9309D16E2B5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB79B956-3DE6-45CD-B050-9D20885A6BB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
@@ -4801,18 +4801,17 @@
 Afiche ilustrado del cóctel Laguna Azul.</t>
   </si>
   <si>
-    <t>El mar en un vaso
-Durante siglos, los cócteles tuvieron los colores de la tierra: ámbar, rojo, dorado, transparente. El azul parecía imposible, porque casi no existe en la naturaleza comestible.
-Todo cambió cuando el curaçao, un licor de naranja del Caribe, comenzó a teñirse de azul a mediados del siglo XX. El sabor seguía siendo el mismo, pero el efecto era completamente nuevo, el bartender podía servir algo que parecía agua de mar.
-La época estaba lista para ese color. En los años 50 y 60, la moda tropical y los bares tiki invitaron a beber paisajes. Surgieron entonces cócteles como el Blue Hawaiian, el Swimming Pool y el Laguna Azul. Su nombre evocaba simplemente una laguna luminosa, una postal líquida.
-Décadas más tarde, el cine reforzó ese imaginario. Películas como La laguna azul terminaron de fijar la asociación entre el azul brillante y la idea de paraíso. El cóctel no nació de la película, pero ambos compartían el mismo sueño: el de una isla lejana, suspendida en el tiempo.
-Hubo años en que los tragos azules perdieron prestigio, víctimas del exceso de azúcar y de la coctelería descuidada. Pero hoy han vuelto, redescubiertos con mejores técnicas y nuevos equilibrios.
-Y tal vez esa sea la razón de su encanto: porque en el fondo, un cóctel azul sigue siendo lo mismo que fue desde el principio, la ilusión, breve y luminosa, de sostener el mar entre las manos.</t>
-  </si>
-  <si>
     <t>El Laguna Azul (Blue Lagoon, en inglés) es un cóctel vistoso y refrescante, reconocido por su color azul intenso y su perfil cítrico y dulce. Es popular en fiestas, barras veraniegas y cartas de coctelería por su atractivo visual y su sencillez de preparación.
 La versión más aceptada sitúa su creación en la década de 1960, cuando el bartender Andy MacElhone, del Harry’s New York Bar de París, buscó un trago que evocara el color luminoso de una laguna tropical. El resultado fue una bebida que no solo destacaba por su sabor, sino también por su apariencia, algo poco habitual en la coctelería de la época.
 Existen variantes que se preparan solo con jugo de limón, mientras que otras incorporan gaseosas de limón, como Sprite o 7Up, para añadir efervescencia y un carácter más suave.</t>
+  </si>
+  <si>
+    <t>El mar en un vaso
+Durante siglos, los cócteles tuvieron los colores de la tierra, la madera y las frutas. El azul parecía imposible, porque casi no existe en la naturaleza de lo comestible.
+Todo cambió cuando el curaçao, un licor de naranja del Caribe, comenzó a teñirse artificialmente de azul a mediados del siglo XX. El sabor seguía siendo el mismo, pero el efecto era completamente nuevo, el bartender podía servir algo que parecía agua de una playa paradisiaca.
+En los años 50 y 60, la moda tropical y los bares tiki invitaron a beber paisajes, surgieron entonces cócteles como el Blue Hawaiian y el Laguna Azul. El cóctel podía ser una postal del trópico.
+Décadas más tarde, el cine reforzó ese imaginario. Películas como La laguna azul, estrenada en 1980, filmada en Fiyi, protagonizada con Brooke Shields y Christopher Atkins, terminaron por fijar la asociación entre el azul brillante y la idea de paraíso. El cóctel no nació de la película, de hecho es anterior, pero ambos compartían el mismo sueño: el de una isla lejana, suspendida en el tiempo.
+Posteriormente los tragos azules perdieron prestigio y popularidad, víctimas del exceso de azúcar y de la coctelería descuidada. Pero hoy han vuelto, redescubiertos con mejores técnicas y nuevos equilibrios, manteniendo su encanto original: la ilusión, breve y luminosa, de sostener el mar entre las manos.</t>
   </si>
 </sst>
 </file>
@@ -60003,17 +60002,17 @@
       <c r="L76" s="5"/>
       <c r="M76" s="1"/>
     </row>
-    <row r="77" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:13" ht="405" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="str">
         <f>IF(receta!A77="","",receta!A77)</f>
         <v>Laguna Azul</v>
       </c>
       <c r="B77" s="1"/>
       <c r="C77" s="4" t="s">
+        <v>1020</v>
+      </c>
+      <c r="D77" s="4" t="s">
         <v>1021</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>1020</v>
       </c>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB79B956-3DE6-45CD-B050-9D20885A6BB9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7391569-4975-41DF-BEAF-F900050F4D90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1566" uniqueCount="1022">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="1023">
   <si>
     <t>Ramazzotti Spritz</t>
   </si>
@@ -4812,6 +4812,13 @@
 En los años 50 y 60, la moda tropical y los bares tiki invitaron a beber paisajes, surgieron entonces cócteles como el Blue Hawaiian y el Laguna Azul. El cóctel podía ser una postal del trópico.
 Décadas más tarde, el cine reforzó ese imaginario. Películas como La laguna azul, estrenada en 1980, filmada en Fiyi, protagonizada con Brooke Shields y Christopher Atkins, terminaron por fijar la asociación entre el azul brillante y la idea de paraíso. El cóctel no nació de la película, de hecho es anterior, pero ambos compartían el mismo sueño: el de una isla lejana, suspendida en el tiempo.
 Posteriormente los tragos azules perdieron prestigio y popularidad, víctimas del exceso de azúcar y de la coctelería descuidada. Pero hoy han vuelto, redescubiertos con mejores técnicas y nuevos equilibrios, manteniendo su encanto original: la ilusión, breve y luminosa, de sostener el mar entre las manos.</t>
+  </si>
+  <si>
+    <t>pink.jpg
+Título: The Pink Panther 03
+Autora: Crys (Cristina Tichitoli)
+Técnica: Acrílico y técnica mixta sobre papel 
+Año: 2023</t>
   </si>
 </sst>
 </file>
@@ -61870,7 +61877,9 @@
       <c r="J152" s="1"/>
       <c r="K152" s="1"/>
       <c r="L152" s="1"/>
-      <c r="M152" s="1"/>
+      <c r="M152" s="4" t="s">
+        <v>1022</v>
+      </c>
     </row>
     <row r="153" spans="1:13" ht="240" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="str">

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D7391569-4975-41DF-BEAF-F900050F4D90}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB3A6C55-1625-4973-9CD7-F2F8C9453FE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1567" uniqueCount="1023">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1571" uniqueCount="1027">
   <si>
     <t>Ramazzotti Spritz</t>
   </si>
@@ -4819,6 +4819,23 @@
 Autora: Crys (Cristina Tichitoli)
 Técnica: Acrílico y técnica mixta sobre papel 
 Año: 2023</t>
+  </si>
+  <si>
+    <t>En el jardín del edén/Suspira Santa Teresa/Con una copa en la mano,/Parece que de cerveza./De lejos sentía el amo/Fragancia de chicha cru'a,/Pa' sus adentros pensaba/"qué fiesta tan macanú'a".</t>
+  </si>
+  <si>
+    <t>Un Domingo en el Cielo - Isabel Parra</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=MYXpEs72fmc</t>
+  </si>
+  <si>
+    <t>Fragmento
+Paula Miranda Herrera
+Nicanor la detuvo o la estimuló en momentos muy claves de su vida. Cántame una canción más, una canción siquiera, le dijo su hermano-padre el día sábado. Pero su voz destemplada y violenta, se apagó bajo un seco balazo el domingo 5 de febrero de 1967. No fue capaz de ingresar al espesor universal y explosivo del 68, estaba muy cansada, había “recorrido a pie toda la geografía fúnebre de la música de su país” y tenía que parar. Chillaneja desgarrada en medio del torbellino de la modernidad, se enredó en las cosas. Compuso, cantó, recopiló, tejió, bordó, bailó, actuó, amó, parió, escribió, pero no podía hacerlo todo, por lo menos no con la intensidad que lo hizo y tuvo que parar. El suicidio no es sólo la anécdota trágica (y vaya que lo es), sino que su sentido tiñe todas sus composiciones y artesanías, en ellas está siempre la muerte y la tristeza acechando, como mantos que todo lo maldicen. Se mató porque estaba muy cansada, porque lo de Gilbert Favré, porque lo de la Carpa de La Reina, porque los hijos, porque no se puede ir en contra de todas las corrientes, porque sí.
+Violeta nació a la vida muchas veces y pereció otras tantas. Muchos suicidios habían precedido al de Febrero, ninguno tan duro como el que ocurrió esa tarde de domingo. Cuando los santiaguinos se aprestaban a dormir una siesta y esperaban resignados el re-inicio de semana, Violeta escribía convulsionada cartas y más cartas, para luego desaparecer. De alguna manera “Gracias a la vida” es el gesto más fúnebre y trágico que yo conozca, su agradecimiento es un lamento, su canto una letanía, su oración una condena. Cuando Violeta estaba casi sin aliento en sus “Últimas composiciones” está plenamente consciente que nada más queda por hacer, su agradecimiento es una despedida. Nicanor y la gente que estuvo más cerca de ella el último tiempo trataron de impedir el desenlace trágico, le habían inventado un viaje a Argentina y Nicanor le había propuesto que escribiera LA NOVELA de Chile. El suicidio se emparenta con el canto, con su canción y su saturación. Gilbert (o Zapiola o Rodríguez, el nombre da lo mismo) y la Carpa de La Reina desencadenan la escena final, pero en ellos están personificadas las fuerzas incontrolables de una modernidad que no paró jamás de remecerla y fragmentarla. La cobardía y la ignorancia no permiten dimensionar la mucha falta que hoy nos hace la Violeta. Necesito su choreza, su rareza, su marginalidad, su desenfado, su misterio. Si hubiese logrado cruzar el 68 y todo lo que vino después, probablemente cantaría con los raperos jóvenes y con los cantores de Aculeo, pero prefirió cantar “Día domingo en el cielo”, y parar su marcha el 67.
+Extraído de:
+Miranda, Paula. “Pienso cantar día domingo en el cielo, a 32 años del suicidio de Violeta Parra”. Baquiana, números 1–2, 1999.</t>
   </si>
 </sst>
 </file>
@@ -62079,7 +62096,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="160" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="str">
         <f>IF(receta!A160="","",receta!A160)</f>
         <v>Chichón</v>
@@ -62090,10 +62107,18 @@
       <c r="C160" s="4" t="s">
         <v>830</v>
       </c>
-      <c r="D160" s="4"/>
-      <c r="E160" s="1"/>
-      <c r="F160" s="1"/>
-      <c r="G160" s="1"/>
+      <c r="D160" s="4" t="s">
+        <v>1026</v>
+      </c>
+      <c r="E160" s="1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F160" s="5" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G160" s="4" t="s">
+        <v>1023</v>
+      </c>
       <c r="H160" s="1"/>
       <c r="I160" s="5"/>
       <c r="J160" s="1"/>
@@ -63882,9 +63907,10 @@
     <hyperlink ref="F16" r:id="rId69" xr:uid="{816C87E7-4A29-4F45-8BD1-D79076FE292E}"/>
     <hyperlink ref="F97" r:id="rId70" xr:uid="{B4B59D4D-272B-4AEE-820B-4D18D5925638}"/>
     <hyperlink ref="F31" r:id="rId71" xr:uid="{295A8609-0926-4F9B-85D6-EFECD8ABD350}"/>
+    <hyperlink ref="F160" r:id="rId72" xr:uid="{4AF06AA3-B56D-4EF1-A3DA-0A54500AAB46}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId72"/>
+  <pageSetup orientation="portrait" r:id="rId73"/>
 </worksheet>
 </file>
 

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB3A6C55-1625-4973-9CD7-F2F8C9453FE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{604D615E-5C69-4586-866B-F04013CDD6B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1571" uniqueCount="1027">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="1030">
   <si>
     <t>Ramazzotti Spritz</t>
   </si>
@@ -4836,6 +4836,15 @@
 Violeta nació a la vida muchas veces y pereció otras tantas. Muchos suicidios habían precedido al de Febrero, ninguno tan duro como el que ocurrió esa tarde de domingo. Cuando los santiaguinos se aprestaban a dormir una siesta y esperaban resignados el re-inicio de semana, Violeta escribía convulsionada cartas y más cartas, para luego desaparecer. De alguna manera “Gracias a la vida” es el gesto más fúnebre y trágico que yo conozca, su agradecimiento es un lamento, su canto una letanía, su oración una condena. Cuando Violeta estaba casi sin aliento en sus “Últimas composiciones” está plenamente consciente que nada más queda por hacer, su agradecimiento es una despedida. Nicanor y la gente que estuvo más cerca de ella el último tiempo trataron de impedir el desenlace trágico, le habían inventado un viaje a Argentina y Nicanor le había propuesto que escribiera LA NOVELA de Chile. El suicidio se emparenta con el canto, con su canción y su saturación. Gilbert (o Zapiola o Rodríguez, el nombre da lo mismo) y la Carpa de La Reina desencadenan la escena final, pero en ellos están personificadas las fuerzas incontrolables de una modernidad que no paró jamás de remecerla y fragmentarla. La cobardía y la ignorancia no permiten dimensionar la mucha falta que hoy nos hace la Violeta. Necesito su choreza, su rareza, su marginalidad, su desenfado, su misterio. Si hubiese logrado cruzar el 68 y todo lo que vino después, probablemente cantaría con los raperos jóvenes y con los cantores de Aculeo, pero prefirió cantar “Día domingo en el cielo”, y parar su marcha el 67.
 Extraído de:
 Miranda, Paula. “Pienso cantar día domingo en el cielo, a 32 años del suicidio de Violeta Parra”. Baquiana, números 1–2, 1999.</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=5n624chcEDo</t>
+  </si>
+  <si>
+    <t>Los Corrigüela - Cuando chico en una liebre</t>
+  </si>
+  <si>
+    <t>Cuando chico en una liebre/tirame pa' Franklin Matadero-Palma, de Tropezón a Ñuñoa/tirame pa' Franklin Matadero-Palma, de Tropezón a Ñuñoa/la Carrascal-Santa Julia/tirame pa' Franklin Matadero-Palma, de mil colores eran to'as/tirame pa' Franklin Matadero-Palma, cuando chico en una liebre.</t>
   </si>
 </sst>
 </file>
@@ -61565,16 +61574,22 @@
         <v>345</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>420</v>
+        <v>1028</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>419</v>
-      </c>
-      <c r="G140" s="5"/>
+        <v>1027</v>
+      </c>
+      <c r="G140" s="4" t="s">
+        <v>1029</v>
+      </c>
       <c r="H140" s="1"/>
       <c r="I140" s="1"/>
-      <c r="J140" s="1"/>
-      <c r="K140" s="5"/>
+      <c r="J140" s="1" t="s">
+        <v>420</v>
+      </c>
+      <c r="K140" s="5" t="s">
+        <v>419</v>
+      </c>
       <c r="L140" s="5"/>
       <c r="M140" s="4" t="s">
         <v>1017</v>
@@ -63871,46 +63886,47 @@
     <hyperlink ref="I119" r:id="rId33" xr:uid="{2CC1FD11-45F7-4E90-8180-4808569A466E}"/>
     <hyperlink ref="I72" r:id="rId34" xr:uid="{716EB464-A291-40E8-95EF-4C1BEB94A9E9}"/>
     <hyperlink ref="F117" r:id="rId35" xr:uid="{6A2CA4F1-AB09-430D-9DDC-D0B22E47A043}"/>
-    <hyperlink ref="F140" r:id="rId36" xr:uid="{ACB1AE2E-AD8F-44A3-9167-37C0CFC2B153}"/>
-    <hyperlink ref="F71" r:id="rId37" xr:uid="{A0310311-45B1-42AB-B4D5-454C1A2F857A}"/>
-    <hyperlink ref="F104" r:id="rId38" xr:uid="{5F1FE064-20CD-4CD0-BFCD-2A29DCE05378}"/>
-    <hyperlink ref="F50" r:id="rId39" xr:uid="{B9029BDE-2CF2-4C7F-8412-0C40AE11F68F}"/>
-    <hyperlink ref="F112" r:id="rId40" xr:uid="{9D0D4CC8-CC22-44E2-B264-DD6DC0AAB856}"/>
-    <hyperlink ref="F118" r:id="rId41" xr:uid="{D0F5E38C-8D61-4A45-9420-0674EA07BF30}"/>
-    <hyperlink ref="F38" r:id="rId42" xr:uid="{262EA65B-7E4E-40E7-83C0-33F10D141492}"/>
-    <hyperlink ref="I108" r:id="rId43" xr:uid="{D354F0C5-47C3-4AC8-89C3-72A923D81147}"/>
-    <hyperlink ref="F143" r:id="rId44" xr:uid="{F8159653-E06F-48AC-B06F-F96FF8FAC6FB}"/>
-    <hyperlink ref="F22" r:id="rId45" xr:uid="{D5C24302-111F-4DD4-B671-45B434C1F272}"/>
-    <hyperlink ref="F37" r:id="rId46" xr:uid="{BC8299D9-94A5-4297-8A97-2305D757D1DF}"/>
-    <hyperlink ref="F110" r:id="rId47" xr:uid="{D9F12F69-7825-432C-8F17-8179F5ACB838}"/>
-    <hyperlink ref="F90" r:id="rId48" xr:uid="{05CA1CBC-8ECD-4A48-9B49-7B0A090F5B0A}"/>
-    <hyperlink ref="F48" r:id="rId49" xr:uid="{5B202746-9CD3-4DEA-86F6-B02FBFECC9BD}"/>
-    <hyperlink ref="F141" r:id="rId50" xr:uid="{75E0E620-EEE7-456F-8B1D-E144584094F6}"/>
-    <hyperlink ref="F91" r:id="rId51" xr:uid="{FAD199C6-5901-4269-B73C-7936FE7D51A0}"/>
-    <hyperlink ref="F148" r:id="rId52" xr:uid="{A5AAC270-3690-4B95-8FC8-A8FD0A109532}"/>
-    <hyperlink ref="F32" r:id="rId53" xr:uid="{04E04D75-704C-4FE6-A3DA-E28677DD7E74}"/>
-    <hyperlink ref="F147" r:id="rId54" xr:uid="{DEED7687-3797-41E5-8622-295B72CFDA25}"/>
-    <hyperlink ref="I74" r:id="rId55" xr:uid="{92BCF14D-68BF-4577-A968-400B7094B7EC}"/>
-    <hyperlink ref="F49" r:id="rId56" xr:uid="{2147548B-F6F7-4EB8-9101-1DF8578426C8}"/>
-    <hyperlink ref="K154" r:id="rId57" xr:uid="{159A8B66-145C-4FBD-93E9-54444710C298}"/>
-    <hyperlink ref="F78" r:id="rId58" xr:uid="{160BFB4E-F52C-4586-9551-1CC63AFC8DC9}"/>
-    <hyperlink ref="K78" r:id="rId59" xr:uid="{9CF2EC77-5892-4BF7-8320-49B85E7226D1}"/>
-    <hyperlink ref="F156" r:id="rId60" xr:uid="{E88376AE-94E5-45C8-B9C6-C745DAA369F1}"/>
-    <hyperlink ref="M158" r:id="rId61" display="https://blogger.googleusercontent.com/img/b/R29vZ2xl/AVvXsEgo9MT1901v1qHy4lzjVuGMhhUkNsOHrn2_qd_JQYznroS1AvlrM1oWLC4_YQA0e4SXQa-PTptjibmZC7gGZsFz_fzaFzkBvhgvXAzOB4F4L2Cf4pEZ211OR3aIufsSPMQg526vHvJ3Csc/s1600/vino-navegado_pati-aguilera.jpg_x000a_Créditos: Ilustración de Pati Aguilera y Fito Holloway (AJíCOLOR)" xr:uid="{436ED537-67EF-4A46-B4F4-10BD6ADA7FCC}"/>
-    <hyperlink ref="F159" r:id="rId62" xr:uid="{5E921682-2244-4A8F-895D-0E726F507E4B}"/>
-    <hyperlink ref="F162" r:id="rId63" xr:uid="{EF657F86-A49C-4DF5-9318-9BE891FDC415}"/>
-    <hyperlink ref="F163" r:id="rId64" xr:uid="{8B571519-9B2E-4DBD-AB73-A1220F412D75}"/>
-    <hyperlink ref="F125" r:id="rId65" xr:uid="{B8E5BCD6-A355-47CC-A5DA-2F0E1F25AE0F}"/>
-    <hyperlink ref="F61" r:id="rId66" xr:uid="{24079934-3DB4-47C7-A4F6-EB34761E8517}"/>
-    <hyperlink ref="I40" r:id="rId67" xr:uid="{18514F5E-18F5-44D8-BD76-F70D6B1E8FC6}"/>
-    <hyperlink ref="I135" r:id="rId68" xr:uid="{6B3689A7-4101-496D-821F-20A52B38FF72}"/>
-    <hyperlink ref="F16" r:id="rId69" xr:uid="{816C87E7-4A29-4F45-8BD1-D79076FE292E}"/>
-    <hyperlink ref="F97" r:id="rId70" xr:uid="{B4B59D4D-272B-4AEE-820B-4D18D5925638}"/>
-    <hyperlink ref="F31" r:id="rId71" xr:uid="{295A8609-0926-4F9B-85D6-EFECD8ABD350}"/>
-    <hyperlink ref="F160" r:id="rId72" xr:uid="{4AF06AA3-B56D-4EF1-A3DA-0A54500AAB46}"/>
+    <hyperlink ref="F71" r:id="rId36" xr:uid="{A0310311-45B1-42AB-B4D5-454C1A2F857A}"/>
+    <hyperlink ref="F104" r:id="rId37" xr:uid="{5F1FE064-20CD-4CD0-BFCD-2A29DCE05378}"/>
+    <hyperlink ref="F50" r:id="rId38" xr:uid="{B9029BDE-2CF2-4C7F-8412-0C40AE11F68F}"/>
+    <hyperlink ref="F112" r:id="rId39" xr:uid="{9D0D4CC8-CC22-44E2-B264-DD6DC0AAB856}"/>
+    <hyperlink ref="F118" r:id="rId40" xr:uid="{D0F5E38C-8D61-4A45-9420-0674EA07BF30}"/>
+    <hyperlink ref="F38" r:id="rId41" xr:uid="{262EA65B-7E4E-40E7-83C0-33F10D141492}"/>
+    <hyperlink ref="I108" r:id="rId42" xr:uid="{D354F0C5-47C3-4AC8-89C3-72A923D81147}"/>
+    <hyperlink ref="F143" r:id="rId43" xr:uid="{F8159653-E06F-48AC-B06F-F96FF8FAC6FB}"/>
+    <hyperlink ref="F22" r:id="rId44" xr:uid="{D5C24302-111F-4DD4-B671-45B434C1F272}"/>
+    <hyperlink ref="F37" r:id="rId45" xr:uid="{BC8299D9-94A5-4297-8A97-2305D757D1DF}"/>
+    <hyperlink ref="F110" r:id="rId46" xr:uid="{D9F12F69-7825-432C-8F17-8179F5ACB838}"/>
+    <hyperlink ref="F90" r:id="rId47" xr:uid="{05CA1CBC-8ECD-4A48-9B49-7B0A090F5B0A}"/>
+    <hyperlink ref="F48" r:id="rId48" xr:uid="{5B202746-9CD3-4DEA-86F6-B02FBFECC9BD}"/>
+    <hyperlink ref="F141" r:id="rId49" xr:uid="{75E0E620-EEE7-456F-8B1D-E144584094F6}"/>
+    <hyperlink ref="F91" r:id="rId50" xr:uid="{FAD199C6-5901-4269-B73C-7936FE7D51A0}"/>
+    <hyperlink ref="F148" r:id="rId51" xr:uid="{A5AAC270-3690-4B95-8FC8-A8FD0A109532}"/>
+    <hyperlink ref="F32" r:id="rId52" xr:uid="{04E04D75-704C-4FE6-A3DA-E28677DD7E74}"/>
+    <hyperlink ref="F147" r:id="rId53" xr:uid="{DEED7687-3797-41E5-8622-295B72CFDA25}"/>
+    <hyperlink ref="I74" r:id="rId54" xr:uid="{92BCF14D-68BF-4577-A968-400B7094B7EC}"/>
+    <hyperlink ref="F49" r:id="rId55" xr:uid="{2147548B-F6F7-4EB8-9101-1DF8578426C8}"/>
+    <hyperlink ref="K154" r:id="rId56" xr:uid="{159A8B66-145C-4FBD-93E9-54444710C298}"/>
+    <hyperlink ref="F78" r:id="rId57" xr:uid="{160BFB4E-F52C-4586-9551-1CC63AFC8DC9}"/>
+    <hyperlink ref="K78" r:id="rId58" xr:uid="{9CF2EC77-5892-4BF7-8320-49B85E7226D1}"/>
+    <hyperlink ref="F156" r:id="rId59" xr:uid="{E88376AE-94E5-45C8-B9C6-C745DAA369F1}"/>
+    <hyperlink ref="M158" r:id="rId60" display="https://blogger.googleusercontent.com/img/b/R29vZ2xl/AVvXsEgo9MT1901v1qHy4lzjVuGMhhUkNsOHrn2_qd_JQYznroS1AvlrM1oWLC4_YQA0e4SXQa-PTptjibmZC7gGZsFz_fzaFzkBvhgvXAzOB4F4L2Cf4pEZ211OR3aIufsSPMQg526vHvJ3Csc/s1600/vino-navegado_pati-aguilera.jpg_x000a_Créditos: Ilustración de Pati Aguilera y Fito Holloway (AJíCOLOR)" xr:uid="{436ED537-67EF-4A46-B4F4-10BD6ADA7FCC}"/>
+    <hyperlink ref="F159" r:id="rId61" xr:uid="{5E921682-2244-4A8F-895D-0E726F507E4B}"/>
+    <hyperlink ref="F162" r:id="rId62" xr:uid="{EF657F86-A49C-4DF5-9318-9BE891FDC415}"/>
+    <hyperlink ref="F163" r:id="rId63" xr:uid="{8B571519-9B2E-4DBD-AB73-A1220F412D75}"/>
+    <hyperlink ref="F125" r:id="rId64" xr:uid="{B8E5BCD6-A355-47CC-A5DA-2F0E1F25AE0F}"/>
+    <hyperlink ref="F61" r:id="rId65" xr:uid="{24079934-3DB4-47C7-A4F6-EB34761E8517}"/>
+    <hyperlink ref="I40" r:id="rId66" xr:uid="{18514F5E-18F5-44D8-BD76-F70D6B1E8FC6}"/>
+    <hyperlink ref="I135" r:id="rId67" xr:uid="{6B3689A7-4101-496D-821F-20A52B38FF72}"/>
+    <hyperlink ref="F16" r:id="rId68" xr:uid="{816C87E7-4A29-4F45-8BD1-D79076FE292E}"/>
+    <hyperlink ref="F97" r:id="rId69" xr:uid="{B4B59D4D-272B-4AEE-820B-4D18D5925638}"/>
+    <hyperlink ref="F31" r:id="rId70" xr:uid="{295A8609-0926-4F9B-85D6-EFECD8ABD350}"/>
+    <hyperlink ref="F160" r:id="rId71" xr:uid="{4AF06AA3-B56D-4EF1-A3DA-0A54500AAB46}"/>
+    <hyperlink ref="K140" r:id="rId72" xr:uid="{2AAF686C-BD90-49C7-BF1A-AD5D0EEB2ADE}"/>
+    <hyperlink ref="F140" r:id="rId73" xr:uid="{40736A97-19E9-43FF-9714-87C9BEC14957}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId73"/>
+  <pageSetup orientation="portrait" r:id="rId74"/>
 </worksheet>
 </file>
 

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{604D615E-5C69-4586-866B-F04013CDD6B0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E62B0D6-DA2E-4F96-B058-C308C37EC94E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1574" uniqueCount="1030">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="1031">
   <si>
     <t>Ramazzotti Spritz</t>
   </si>
@@ -4845,6 +4845,10 @@
   </si>
   <si>
     <t>Cuando chico en una liebre/tirame pa' Franklin Matadero-Palma, de Tropezón a Ñuñoa/tirame pa' Franklin Matadero-Palma, de Tropezón a Ñuñoa/la Carrascal-Santa Julia/tirame pa' Franklin Matadero-Palma, de mil colores eran to'as/tirame pa' Franklin Matadero-Palma, cuando chico en una liebre.</t>
+  </si>
+  <si>
+    <t>violetanicanor.jpg
+Violeta Parra y Nicanor. Fotografía del Archivo de la Fundación Violeta Parra.</t>
   </si>
 </sst>
 </file>
@@ -62139,7 +62143,9 @@
       <c r="J160" s="1"/>
       <c r="K160" s="1"/>
       <c r="L160" s="1"/>
-      <c r="M160" s="1"/>
+      <c r="M160" s="4" t="s">
+        <v>1030</v>
+      </c>
     </row>
     <row r="161" spans="1:13" ht="195" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="str">

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4E62B0D6-DA2E-4F96-B058-C308C37EC94E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2DC101A-9453-43BB-85CD-02CAFBA185DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
@@ -4848,7 +4848,7 @@
   </si>
   <si>
     <t>violetanicanor.jpg
-Violeta Parra y Nicanor. Fotografía del Archivo de la Fundación Violeta Parra.</t>
+Violeta Parra compartiendo un vino caliente junto a su hermano Nicanor, en "La carpa de La Reina" (1966). Fotografía del Archivo de la Fundación Violeta Parra.</t>
   </si>
 </sst>
 </file>

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2DC101A-9453-43BB-85CD-02CAFBA185DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F63329E1-2FFB-48F5-9E08-1C569E0C2A51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1575" uniqueCount="1031">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1602" uniqueCount="1058">
   <si>
     <t>Ramazzotti Spritz</t>
   </si>
@@ -4849,6 +4849,96 @@
   <si>
     <t>violetanicanor.jpg
 Violeta Parra compartiendo un vino caliente junto a su hermano Nicanor, en "La carpa de La Reina" (1966). Fotografía del Archivo de la Fundación Violeta Parra.</t>
+  </si>
+  <si>
+    <t>Quilapayún - Canción final de la Cantata Santa María de Iquique (en vivo 1972)</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=LiPS_WRgrAE</t>
+  </si>
+  <si>
+    <t>Quilapayún - Cantata Santa María de Iquique (Luis Advis)</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=fVX_c54xA5U</t>
+  </si>
+  <si>
+    <t xml:space="preserve">
+Inti Illimani - Señora Chichera</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=3BKR5TeR59k</t>
+  </si>
+  <si>
+    <t>Señora chichera/Véndeme chichita/Señora chichera/Véndeme chichita/Si no tiene chicha/Cualquiera cosita</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=d6kmaZA3Dl0</t>
+  </si>
+  <si>
+    <t>Illapu - El Loco del Puerto</t>
+  </si>
+  <si>
+    <t>La gente lo miraba/se caía al caminar/colgaba de los faros/su sonrisa era de sal.</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=OdZHhRTmLHo</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pibes Chorros - Que calor </t>
+  </si>
+  <si>
+    <t>Que levante la mano/El que quiera tomar/Que la caja de vino va a empezar a pasar</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=MUUrW7xJSw4</t>
+  </si>
+  <si>
+    <t>Yerba Brava - La Cumbia de los Trapos</t>
+  </si>
+  <si>
+    <t>Borracho, yo voy cantando/Con mis amigos, voy festejando un triunfo más/Loco soy por mi trapo/Te sigo a muerte, por donde vas/Porque la vuelta queremos dar/Queremos dar</t>
+  </si>
+  <si>
+    <t>Me pondré por los hombros/De abrigo toda el alba/Mi penúltimo whisky/Quedará sin beber/Llegará tangamente/Mi muerte enamorada/Yo estaré muerta en punto/Cuando sean las seis</t>
+  </si>
+  <si>
+    <t>Elena Roger &amp; Escalandrum - Balada para Mi Muerte</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=NDVneLzlaxE</t>
+  </si>
+  <si>
+    <t>Cinzano.jpg
+Afiche publicitario de Cinzano, diseñado por el ilustrador italiano Leonetto Cappiello hacia comienzos del siglo XX, que simboliza el carácter festivo y ligero del vermut y los vinos espumantes de la casa Cinzano, fundada en Turín en 1757.</t>
+  </si>
+  <si>
+    <t>cinzano bitter.jpg
+Afiche publicitario de Cinzano para su Bitter Aperitif, realizado a mediados del siglo XX, cuando el aperitivo italiano se consolidaba como parte del ritual social previo a la comida. El bitter, una bebida aromatizada con hierbas y especias, de sabor amargo, se popularizó especialmente en Europa desde el siglo XIX, asociado a la costumbre del aperitivo y al desarrollo de la cultura del bar.</t>
+  </si>
+  <si>
+    <t>campari2.jpg
+Afiche publicitario de Campari Group, inspirado en el estilo gráfico moderno asociado a la tradición del cartel italiano del siglo XX.</t>
+  </si>
+  <si>
+    <t>campari-cocktail-poster.jpg
+Afiche publicitario de Campari Group, inspirado en el lenguaje visual de la gráfica italiana de entreguerras.</t>
+  </si>
+  <si>
+    <t>dirty.jpg
+Afiche contemporáneo inspirado en el Dirty Martini, una variante del Martini (cocktail) en la que se añade salmuera de aceitunas, lo que le da un carácter más salino y opaco que la versión clásica.</t>
+  </si>
+  <si>
+    <t>vermouth-bianco-martini-rossi.jpg
+Afiche publicitario de Martini &amp; Rossi, realizado a comienzos del siglo XX para promocionar su Vermouth Bianco, una variedad más clara y aromática del vermut tradicional.</t>
+  </si>
+  <si>
+    <t>martini-torino-4.jpg
+Afiche publicitario de Martini &amp; Rossi, realizado en las primeras décadas del siglo XX, cuando el vermut italiano se difundía ampliamente en Europa y América como bebida de aperitivo.</t>
+  </si>
+  <si>
+    <t>martini_vermouth.jpg
+Afiche publicitario de Martini &amp; Rossi, difundido a mediados del siglo XX, en el que se presentan dos de sus variedades más conocidas de vermut: Rosso y Dry.</t>
   </si>
 </sst>
 </file>
@@ -58259,7 +58349,9 @@
       <c r="J8" s="1"/>
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
+      <c r="M8" s="4" t="s">
+        <v>1052</v>
+      </c>
     </row>
     <row r="9" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="str">
@@ -58359,7 +58451,7 @@
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
-    <row r="13" spans="1:13" ht="195" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="210" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="str">
         <f>IF(receta!A13="","",receta!A13)</f>
         <v>Bellini</v>
@@ -58431,7 +58523,9 @@
       <c r="J15" s="1"/>
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
+      <c r="M15" s="4" t="s">
+        <v>1051</v>
+      </c>
     </row>
     <row r="16" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="str">
@@ -58849,7 +58943,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="240" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" ht="255" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="str">
         <f>IF(receta!A32="","",receta!A32)</f>
         <v>Cléry Durazno</v>
@@ -59197,7 +59291,9 @@
       <c r="J45" s="1"/>
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
-      <c r="M45" s="1"/>
+      <c r="M45" s="4" t="s">
+        <v>1054</v>
+      </c>
     </row>
     <row r="46" spans="1:13" ht="285" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="str">
@@ -59220,9 +59316,15 @@
       <c r="G46" s="5"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
-      <c r="J46" s="4"/>
-      <c r="K46" s="5"/>
-      <c r="L46" s="5"/>
+      <c r="J46" s="4" t="s">
+        <v>1042</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>1041</v>
+      </c>
+      <c r="L46" s="4" t="s">
+        <v>1043</v>
+      </c>
       <c r="M46" s="4" t="s">
         <v>992</v>
       </c>
@@ -59343,7 +59445,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="str">
         <f>IF(receta!A51="","",receta!A51)</f>
         <v>Espresso Martini</v>
@@ -59441,9 +59543,15 @@
         <v>684</v>
       </c>
       <c r="D54" s="4"/>
-      <c r="E54" s="1"/>
-      <c r="F54" s="5"/>
-      <c r="G54" s="5"/>
+      <c r="E54" s="1" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F54" s="5" t="s">
+        <v>1038</v>
+      </c>
+      <c r="G54" s="4" t="s">
+        <v>1040</v>
+      </c>
       <c r="H54" s="1" t="s">
         <v>352</v>
       </c>
@@ -60439,7 +60547,7 @@
       <c r="L92" s="5"/>
       <c r="M92" s="1"/>
     </row>
-    <row r="93" spans="1:13" ht="150" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" ht="180" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="str">
         <f>IF(receta!A93="","",receta!A93)</f>
         <v>Milano Torino</v>
@@ -60457,7 +60565,9 @@
       <c r="J93" s="1"/>
       <c r="K93" s="1"/>
       <c r="L93" s="1"/>
-      <c r="M93" s="1"/>
+      <c r="M93" s="4" t="s">
+        <v>1056</v>
+      </c>
     </row>
     <row r="94" spans="1:13" ht="180" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="str">
@@ -60671,7 +60781,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="103" spans="1:13" ht="150" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:13" ht="210" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="str">
         <f>IF(receta!A103="","",receta!A103)</f>
         <v>Negroni Sbagliato</v>
@@ -60689,7 +60799,9 @@
       <c r="J103" s="1"/>
       <c r="K103" s="1"/>
       <c r="L103" s="1"/>
-      <c r="M103" s="1"/>
+      <c r="M103" s="4" t="s">
+        <v>1050</v>
+      </c>
     </row>
     <row r="104" spans="1:13" ht="345" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="str">
@@ -60759,9 +60871,15 @@
       <c r="D106" s="4" t="s">
         <v>566</v>
       </c>
-      <c r="E106" s="1"/>
-      <c r="F106" s="1"/>
-      <c r="G106" s="1"/>
+      <c r="E106" s="1" t="s">
+        <v>1048</v>
+      </c>
+      <c r="F106" s="5" t="s">
+        <v>1049</v>
+      </c>
+      <c r="G106" s="4" t="s">
+        <v>1047</v>
+      </c>
       <c r="H106" s="1"/>
       <c r="I106" s="1"/>
       <c r="J106" s="1"/>
@@ -61369,7 +61487,7 @@
       <c r="L131" s="1"/>
       <c r="M131" s="1"/>
     </row>
-    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" ht="165" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="str">
         <f>IF(receta!A132="","",receta!A132)</f>
         <v>Síndrome Impostor</v>
@@ -61391,7 +61509,9 @@
       <c r="J132" s="1"/>
       <c r="K132" s="5"/>
       <c r="L132" s="5"/>
-      <c r="M132" s="1"/>
+      <c r="M132" s="4" t="s">
+        <v>1055</v>
+      </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="str">
@@ -61507,9 +61627,15 @@
       <c r="D137" s="4" t="s">
         <v>434</v>
       </c>
-      <c r="E137" s="1"/>
-      <c r="F137" s="1"/>
-      <c r="G137" s="1"/>
+      <c r="E137" s="1" t="s">
+        <v>1045</v>
+      </c>
+      <c r="F137" s="5" t="s">
+        <v>1044</v>
+      </c>
+      <c r="G137" s="4" t="s">
+        <v>1046</v>
+      </c>
       <c r="H137" s="1"/>
       <c r="I137" s="1"/>
       <c r="J137" s="1"/>
@@ -61700,10 +61826,18 @@
         <v>310</v>
       </c>
       <c r="G144" s="1"/>
-      <c r="H144" s="1"/>
-      <c r="I144" s="1"/>
-      <c r="J144" s="1"/>
-      <c r="K144" s="1"/>
+      <c r="H144" s="1" t="s">
+        <v>1033</v>
+      </c>
+      <c r="I144" s="5" t="s">
+        <v>1034</v>
+      </c>
+      <c r="J144" s="1" t="s">
+        <v>1031</v>
+      </c>
+      <c r="K144" s="5" t="s">
+        <v>1032</v>
+      </c>
       <c r="L144" s="1"/>
       <c r="M144" s="4" t="s">
         <v>925</v>
@@ -61735,7 +61869,9 @@
       <c r="J145" s="1"/>
       <c r="K145" s="1"/>
       <c r="L145" s="1"/>
-      <c r="M145" s="1"/>
+      <c r="M145" s="4" t="s">
+        <v>1057</v>
+      </c>
     </row>
     <row r="146" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="str">
@@ -62269,9 +62405,15 @@
       <c r="D165" s="4" t="s">
         <v>875</v>
       </c>
-      <c r="E165" s="1"/>
-      <c r="F165" s="1"/>
-      <c r="G165" s="1"/>
+      <c r="E165" s="4" t="s">
+        <v>1035</v>
+      </c>
+      <c r="F165" s="5" t="s">
+        <v>1036</v>
+      </c>
+      <c r="G165" s="1" t="s">
+        <v>1037</v>
+      </c>
       <c r="H165" s="1"/>
       <c r="I165" s="5"/>
       <c r="J165" s="1"/>
@@ -62329,7 +62471,9 @@
       <c r="J167" s="1"/>
       <c r="K167" s="1"/>
       <c r="L167" s="1"/>
-      <c r="M167" s="1"/>
+      <c r="M167" s="4" t="s">
+        <v>1053</v>
+      </c>
     </row>
     <row r="168" spans="1:13" ht="180" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="str">
@@ -63930,9 +64074,16 @@
     <hyperlink ref="F160" r:id="rId71" xr:uid="{4AF06AA3-B56D-4EF1-A3DA-0A54500AAB46}"/>
     <hyperlink ref="K140" r:id="rId72" xr:uid="{2AAF686C-BD90-49C7-BF1A-AD5D0EEB2ADE}"/>
     <hyperlink ref="F140" r:id="rId73" xr:uid="{40736A97-19E9-43FF-9714-87C9BEC14957}"/>
+    <hyperlink ref="K144" r:id="rId74" xr:uid="{53B80412-D30A-4E61-B7C0-84FAEE3C9B8F}"/>
+    <hyperlink ref="I144" r:id="rId75" xr:uid="{51307B8A-9D3C-440A-95F6-7FAB063FC58B}"/>
+    <hyperlink ref="F165" r:id="rId76" xr:uid="{31D85646-B6D0-4064-847B-6A91577D6D6C}"/>
+    <hyperlink ref="F54" r:id="rId77" xr:uid="{62AB4C70-4B08-403C-9DAD-3742BCB54E51}"/>
+    <hyperlink ref="K46" r:id="rId78" xr:uid="{BD04903A-05E0-4F1C-B9C8-226D01E9B9F0}"/>
+    <hyperlink ref="F137" r:id="rId79" xr:uid="{5F4B6BA8-9C2D-4FA6-9E30-3405A5456BC9}"/>
+    <hyperlink ref="F106" r:id="rId80" xr:uid="{ABCFAB17-7667-4D61-879E-A320868B2202}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId74"/>
+  <pageSetup orientation="portrait" r:id="rId81"/>
 </worksheet>
 </file>
 

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F63329E1-2FFB-48F5-9E08-1C569E0C2A51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A83BE708-6FCC-468D-8445-89E575A172DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
   <sheets>
     <sheet name="receta" sheetId="1" r:id="rId1"/>
@@ -4594,10 +4594,6 @@
 Año: 2015?</t>
   </si>
   <si>
-    <t>la-vieille-dame-et-les-pigeons.jpg
-Fotorama de  "La vieja dama y las palomas" (La vieille dame et les pigeons, 1997), cortometraje de animación dirigido por Sylvain Chomet.</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=wUDRIC5RSX4</t>
   </si>
   <si>
@@ -4873,15 +4869,6 @@
     <t>Señora chichera/Véndeme chichita/Señora chichera/Véndeme chichita/Si no tiene chicha/Cualquiera cosita</t>
   </si>
   <si>
-    <t>https://www.youtube.com/watch?v=d6kmaZA3Dl0</t>
-  </si>
-  <si>
-    <t>Illapu - El Loco del Puerto</t>
-  </si>
-  <si>
-    <t>La gente lo miraba/se caía al caminar/colgaba de los faros/su sonrisa era de sal.</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=OdZHhRTmLHo</t>
   </si>
   <si>
@@ -4939,6 +4926,21 @@
   <si>
     <t>martini_vermouth.jpg
 Afiche publicitario de Martini &amp; Rossi, difundido a mediados del siglo XX, en el que se presentan dos de sus variedades más conocidas de vermut: Rosso y Dry.</t>
+  </si>
+  <si>
+    <t>https://euvs-vintage-cocktail-books.cld.bz/</t>
+  </si>
+  <si>
+    <t>Biblioteca vintage de coctelería de la EUVS (Exposition Universelle des Vins et Spiritueux), una organización dedicada a la difusión de la cultura y la historia de los vinos, destilados y la coctelería. Dentro de sus proyectos mantienen esta biblioteca digital, donde han reunido y digitalizado libros antiguos de cócteles, muchos de ellos de fines del siglo XIX y comienzos del XX, provenientes de colecciones privadas e investigadores.
+Permite hojearlos en línea y ver cómo se preparaban los tragos en otras épocas, qué ingredientes se usaban y cómo ha evolucionado la coctelería a lo largo del tiempo.</t>
+  </si>
+  <si>
+    <t>20200202_092625.jpg
+Portada del folleto publicitario Cocktail Memoirs of Fresco Lime, publicado en Nueva York hacia 1935 por la American Lime Corporation. Este cuadernillo promocional, editado poco después del fin de la Ley Seca en Estados Unidos, difundía recetas de cócteles, postres y preparaciones con lima, reflejando el auge de la coctelería y el interés comercial por promover el consumo de cítricos procedentes del Caribe, entonces conocidos como “West Indies”.</t>
+  </si>
+  <si>
+    <t>la-vieille-dame-et-les-pigeons.jpg
+Fotograma de  "La vieja dama y las palomas" (La vieille dame et les pigeons, 1997), cortometraje de animación dirigido por Sylvain Chomet.</t>
   </si>
 </sst>
 </file>
@@ -58142,7 +58144,7 @@
         <v>315</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>316</v>
@@ -58157,7 +58159,7 @@
         <v>767</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="M1" s="7" t="s">
         <v>815</v>
@@ -58234,7 +58236,7 @@
         <v>239</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="5"/>
@@ -58350,7 +58352,7 @@
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="4" t="s">
-        <v>1052</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -58424,7 +58426,7 @@
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="4" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58451,7 +58453,7 @@
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
-    <row r="13" spans="1:13" ht="210" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="195" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="str">
         <f>IF(receta!A13="","",receta!A13)</f>
         <v>Bellini</v>
@@ -58472,7 +58474,7 @@
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="4" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58524,7 +58526,7 @@
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="4" t="s">
-        <v>1051</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -58536,13 +58538,13 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -58628,7 +58630,7 @@
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="4" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -58728,7 +58730,7 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="4" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="345" x14ac:dyDescent="0.25">
@@ -58776,7 +58778,7 @@
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="4" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58804,7 +58806,7 @@
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="4" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="375" x14ac:dyDescent="0.25">
@@ -58830,7 +58832,7 @@
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="4" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58926,13 +58928,13 @@
         <v>426</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="F31" s="5" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G31" s="4" t="s">
         <v>1005</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>1006</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -58940,10 +58942,10 @@
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="4" t="s">
-        <v>983</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="255" x14ac:dyDescent="0.25">
+        <v>982</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="240" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="str">
         <f>IF(receta!A32="","",receta!A32)</f>
         <v>Cléry Durazno</v>
@@ -59022,7 +59024,7 @@
       <c r="K34" s="5"/>
       <c r="L34" s="5"/>
       <c r="M34" s="4" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -59120,7 +59122,7 @@
       <c r="K38" s="5"/>
       <c r="L38" s="5"/>
       <c r="M38" s="4" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="75" x14ac:dyDescent="0.25">
@@ -59292,7 +59294,7 @@
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
       <c r="M45" s="4" t="s">
-        <v>1054</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="285" x14ac:dyDescent="0.25">
@@ -59305,7 +59307,7 @@
       </c>
       <c r="C46" s="4"/>
       <c r="D46" s="4" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>185</v>
@@ -59317,16 +59319,16 @@
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
       <c r="J46" s="4" t="s">
-        <v>1042</v>
+        <v>1038</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>1041</v>
+        <v>1037</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>1043</v>
+        <v>1039</v>
       </c>
       <c r="M46" s="4" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -59402,7 +59404,7 @@
         <v>772</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -59410,7 +59412,7 @@
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
       <c r="M49" s="4" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="255" x14ac:dyDescent="0.25">
@@ -59430,7 +59432,7 @@
         <v>483</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>326</v>
@@ -59445,7 +59447,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="str">
         <f>IF(receta!A51="","",receta!A51)</f>
         <v>Espresso Martini</v>
@@ -59518,7 +59520,7 @@
         <v>405</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>385</v>
@@ -59530,7 +59532,7 @@
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="4" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59543,15 +59545,9 @@
         <v>684</v>
       </c>
       <c r="D54" s="4"/>
-      <c r="E54" s="1" t="s">
-        <v>1039</v>
-      </c>
-      <c r="F54" s="5" t="s">
-        <v>1038</v>
-      </c>
-      <c r="G54" s="4" t="s">
-        <v>1040</v>
-      </c>
+      <c r="E54" s="1"/>
+      <c r="F54" s="5"/>
+      <c r="G54" s="4"/>
       <c r="H54" s="1" t="s">
         <v>352</v>
       </c>
@@ -59608,7 +59604,7 @@
         <v>474</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -59714,13 +59710,13 @@
       <c r="E60" s="1"/>
       <c r="F60" s="1"/>
       <c r="G60" s="1"/>
-      <c r="H60" s="1"/>
+      <c r="H60" s="4"/>
       <c r="I60" s="1"/>
       <c r="J60" s="1"/>
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
       <c r="M60" s="4" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="165" x14ac:dyDescent="0.25">
@@ -59774,7 +59770,7 @@
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
       <c r="M62" s="4" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59807,7 +59803,7 @@
         <v>769</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="M63" s="4" t="s">
         <v>933</v>
@@ -59832,7 +59828,7 @@
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
       <c r="M64" s="4" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60154,10 +60150,10 @@
       </c>
       <c r="B77" s="1"/>
       <c r="C77" s="4" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D77" s="4" t="s">
         <v>1020</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>1021</v>
       </c>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
@@ -60168,7 +60164,7 @@
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
       <c r="M77" s="4" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="78" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -60338,7 +60334,7 @@
       <c r="K84" s="1"/>
       <c r="L84" s="1"/>
       <c r="M84" s="4" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -60368,7 +60364,7 @@
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
       <c r="M85" s="4" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -60566,7 +60562,7 @@
       <c r="K93" s="1"/>
       <c r="L93" s="1"/>
       <c r="M93" s="4" t="s">
-        <v>1056</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="94" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -60610,7 +60606,7 @@
       <c r="K95" s="1"/>
       <c r="L95" s="1"/>
       <c r="M95" s="4" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="96" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -60643,13 +60639,13 @@
         <v>581</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="G97" s="1"/>
       <c r="H97" s="4"/>
@@ -60658,7 +60654,7 @@
       <c r="K97" s="1"/>
       <c r="L97" s="1"/>
       <c r="M97" s="4" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="98" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -60778,7 +60774,7 @@
       <c r="K102" s="1"/>
       <c r="L102" s="1"/>
       <c r="M102" s="4" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="103" spans="1:13" ht="210" x14ac:dyDescent="0.25">
@@ -60800,7 +60796,7 @@
       <c r="K103" s="1"/>
       <c r="L103" s="1"/>
       <c r="M103" s="4" t="s">
-        <v>1050</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="104" spans="1:13" ht="345" x14ac:dyDescent="0.25">
@@ -60830,7 +60826,7 @@
       <c r="K104" s="5"/>
       <c r="L104" s="5"/>
       <c r="M104" s="4" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="105" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -60859,7 +60855,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="106" spans="1:13" ht="240" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" ht="375" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="str">
         <f>IF(receta!A106="","",receta!A106)</f>
         <v>Old Fashioned</v>
@@ -60872,20 +60868,26 @@
         <v>566</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>1048</v>
+        <v>1044</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>1049</v>
+        <v>1045</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>1047</v>
-      </c>
-      <c r="H106" s="1"/>
-      <c r="I106" s="1"/>
+        <v>1043</v>
+      </c>
+      <c r="H106" s="4" t="s">
+        <v>1055</v>
+      </c>
+      <c r="I106" s="5" t="s">
+        <v>1054</v>
+      </c>
       <c r="J106" s="1"/>
       <c r="K106" s="1"/>
       <c r="L106" s="1"/>
-      <c r="M106" s="1"/>
+      <c r="M106" s="4" t="s">
+        <v>1056</v>
+      </c>
     </row>
     <row r="107" spans="1:13" ht="192" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="str">
@@ -60936,7 +60938,7 @@
       <c r="K108" s="1"/>
       <c r="L108" s="1"/>
       <c r="M108" s="4" t="s">
-        <v>968</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="109" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -60971,7 +60973,7 @@
         <v>676</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="E110" s="4" t="s">
         <v>586</v>
@@ -60986,7 +60988,7 @@
       <c r="K110" s="5"/>
       <c r="L110" s="5"/>
       <c r="M110" s="4" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.25">
@@ -61154,7 +61156,7 @@
       <c r="K117" s="5"/>
       <c r="L117" s="5"/>
       <c r="M117" s="4" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="118" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -61208,7 +61210,7 @@
       <c r="K119" s="5"/>
       <c r="L119" s="5"/>
       <c r="M119" s="4" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="120" spans="1:13" ht="75" x14ac:dyDescent="0.25">
@@ -61420,7 +61422,7 @@
       <c r="K128" s="1"/>
       <c r="L128" s="1"/>
       <c r="M128" s="4" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="129" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -61510,7 +61512,7 @@
       <c r="K132" s="5"/>
       <c r="L132" s="5"/>
       <c r="M132" s="4" t="s">
-        <v>1055</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.25">
@@ -61628,13 +61630,13 @@
         <v>434</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>1045</v>
+        <v>1041</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>1044</v>
+        <v>1040</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>1046</v>
+        <v>1042</v>
       </c>
       <c r="H137" s="1"/>
       <c r="I137" s="1"/>
@@ -61704,13 +61706,13 @@
         <v>345</v>
       </c>
       <c r="E140" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="F140" s="5" t="s">
+        <v>1026</v>
+      </c>
+      <c r="G140" s="4" t="s">
         <v>1028</v>
-      </c>
-      <c r="F140" s="5" t="s">
-        <v>1027</v>
-      </c>
-      <c r="G140" s="4" t="s">
-        <v>1029</v>
       </c>
       <c r="H140" s="1"/>
       <c r="I140" s="1"/>
@@ -61722,7 +61724,7 @@
       </c>
       <c r="L140" s="5"/>
       <c r="M140" s="4" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="141" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -61827,16 +61829,16 @@
       </c>
       <c r="G144" s="1"/>
       <c r="H144" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="I144" s="5" t="s">
         <v>1033</v>
       </c>
-      <c r="I144" s="5" t="s">
-        <v>1034</v>
-      </c>
       <c r="J144" s="1" t="s">
+        <v>1030</v>
+      </c>
+      <c r="K144" s="5" t="s">
         <v>1031</v>
-      </c>
-      <c r="K144" s="5" t="s">
-        <v>1032</v>
       </c>
       <c r="L144" s="1"/>
       <c r="M144" s="4" t="s">
@@ -61870,7 +61872,7 @@
       <c r="K145" s="1"/>
       <c r="L145" s="1"/>
       <c r="M145" s="4" t="s">
-        <v>1057</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="146" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -62050,7 +62052,7 @@
       <c r="K152" s="1"/>
       <c r="L152" s="1"/>
       <c r="M152" s="4" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="153" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -62109,7 +62111,7 @@
         <v>774</v>
       </c>
       <c r="L154" s="26" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="M154" s="1"/>
     </row>
@@ -62263,16 +62265,16 @@
         <v>830</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="E160" s="1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="F160" s="5" t="s">
         <v>1024</v>
       </c>
-      <c r="F160" s="5" t="s">
-        <v>1025</v>
-      </c>
       <c r="G160" s="4" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="H160" s="1"/>
       <c r="I160" s="5"/>
@@ -62280,7 +62282,7 @@
       <c r="K160" s="1"/>
       <c r="L160" s="1"/>
       <c r="M160" s="4" t="s">
-        <v>1030</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="161" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -62356,7 +62358,7 @@
       <c r="K163" s="1"/>
       <c r="L163" s="1"/>
       <c r="M163" s="4" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="164" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62406,13 +62408,13 @@
         <v>875</v>
       </c>
       <c r="E165" s="4" t="s">
+        <v>1034</v>
+      </c>
+      <c r="F165" s="5" t="s">
         <v>1035</v>
       </c>
-      <c r="F165" s="5" t="s">
+      <c r="G165" s="1" t="s">
         <v>1036</v>
-      </c>
-      <c r="G165" s="1" t="s">
-        <v>1037</v>
       </c>
       <c r="H165" s="1"/>
       <c r="I165" s="5"/>
@@ -62420,7 +62422,7 @@
       <c r="K165" s="1"/>
       <c r="L165" s="1"/>
       <c r="M165" s="4" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="166" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62472,7 +62474,7 @@
       <c r="K167" s="1"/>
       <c r="L167" s="1"/>
       <c r="M167" s="4" t="s">
-        <v>1053</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="168" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -62482,7 +62484,7 @@
       </c>
       <c r="B168" s="1"/>
       <c r="C168" s="4" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="D168" s="4"/>
       <c r="E168" s="1"/>
@@ -62494,7 +62496,7 @@
       <c r="K168" s="1"/>
       <c r="L168" s="1"/>
       <c r="M168" s="4" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="169" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -64077,10 +64079,10 @@
     <hyperlink ref="K144" r:id="rId74" xr:uid="{53B80412-D30A-4E61-B7C0-84FAEE3C9B8F}"/>
     <hyperlink ref="I144" r:id="rId75" xr:uid="{51307B8A-9D3C-440A-95F6-7FAB063FC58B}"/>
     <hyperlink ref="F165" r:id="rId76" xr:uid="{31D85646-B6D0-4064-847B-6A91577D6D6C}"/>
-    <hyperlink ref="F54" r:id="rId77" xr:uid="{62AB4C70-4B08-403C-9DAD-3742BCB54E51}"/>
-    <hyperlink ref="K46" r:id="rId78" xr:uid="{BD04903A-05E0-4F1C-B9C8-226D01E9B9F0}"/>
-    <hyperlink ref="F137" r:id="rId79" xr:uid="{5F4B6BA8-9C2D-4FA6-9E30-3405A5456BC9}"/>
-    <hyperlink ref="F106" r:id="rId80" xr:uid="{ABCFAB17-7667-4D61-879E-A320868B2202}"/>
+    <hyperlink ref="K46" r:id="rId77" xr:uid="{BD04903A-05E0-4F1C-B9C8-226D01E9B9F0}"/>
+    <hyperlink ref="F137" r:id="rId78" xr:uid="{5F4B6BA8-9C2D-4FA6-9E30-3405A5456BC9}"/>
+    <hyperlink ref="F106" r:id="rId79" xr:uid="{ABCFAB17-7667-4D61-879E-A320868B2202}"/>
+    <hyperlink ref="I106" r:id="rId80" xr:uid="{4BF12877-B808-4EA1-A6A9-B6AAB5F55B13}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId81"/>

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A83BE708-6FCC-468D-8445-89E575A172DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A74465D-0CAE-4A67-A06A-5A602A0461F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
@@ -4931,16 +4931,15 @@
     <t>https://euvs-vintage-cocktail-books.cld.bz/</t>
   </si>
   <si>
-    <t>Biblioteca vintage de coctelería de la EUVS (Exposition Universelle des Vins et Spiritueux), una organización dedicada a la difusión de la cultura y la historia de los vinos, destilados y la coctelería. Dentro de sus proyectos mantienen esta biblioteca digital, donde han reunido y digitalizado libros antiguos de cócteles, muchos de ellos de fines del siglo XIX y comienzos del XX, provenientes de colecciones privadas e investigadores.
-Permite hojearlos en línea y ver cómo se preparaban los tragos en otras épocas, qué ingredientes se usaban y cómo ha evolucionado la coctelería a lo largo del tiempo.</t>
-  </si>
-  <si>
     <t>20200202_092625.jpg
 Portada del folleto publicitario Cocktail Memoirs of Fresco Lime, publicado en Nueva York hacia 1935 por la American Lime Corporation. Este cuadernillo promocional, editado poco después del fin de la Ley Seca en Estados Unidos, difundía recetas de cócteles, postres y preparaciones con lima, reflejando el auge de la coctelería y el interés comercial por promover el consumo de cítricos procedentes del Caribe, entonces conocidos como “West Indies”.</t>
   </si>
   <si>
     <t>la-vieille-dame-et-les-pigeons.jpg
 Fotograma de  "La vieja dama y las palomas" (La vieille dame et les pigeons, 1997), cortometraje de animación dirigido por Sylvain Chomet.</t>
+  </si>
+  <si>
+    <t>Biblioteca vintage de coctelería de la EUVS (Exposition Universelle des Vins et Spiritueux).</t>
   </si>
 </sst>
 </file>
@@ -60877,7 +60876,7 @@
         <v>1043</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="I106" s="5" t="s">
         <v>1054</v>
@@ -60886,7 +60885,7 @@
       <c r="K106" s="1"/>
       <c r="L106" s="1"/>
       <c r="M106" s="4" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="107" spans="1:13" ht="192" customHeight="1" x14ac:dyDescent="0.25">
@@ -60938,7 +60937,7 @@
       <c r="K108" s="1"/>
       <c r="L108" s="1"/>
       <c r="M108" s="4" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="109" spans="1:13" ht="105" x14ac:dyDescent="0.25">

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7A74465D-0CAE-4A67-A06A-5A602A0461F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEF7FC5A-6DFB-4840-AC5B-28896947810E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
+    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
   <sheets>
     <sheet name="receta" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1602" uniqueCount="1058">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1603" uniqueCount="1059">
   <si>
     <t>Ramazzotti Spritz</t>
   </si>
@@ -4940,6 +4940,24 @@
   </si>
   <si>
     <t>Biblioteca vintage de coctelería de la EUVS (Exposition Universelle des Vins et Spiritueux).</t>
+  </si>
+  <si>
+    <t>Que no encuentre ni el rocío
+Anónimo (harawi, canto lírico quechua).
+Vicuña de los cerros, venado de los montes:
+decidme si pasó por aquí la ingrata paloma,
+la paloma que dejó su nido
+que olvidó a su amado.
+Vicuña de los cerros, taruka de los montes,
+venid a ver cómo lloran mis ojos;
+así me dejó, con los ojos llorando,
+así me dejó, con el corazón herido.
+¡Oh, que tenga sed en el camino!
+y que no encuentre ni la escarcha de los pajonales
+que no encuentre ni el rocío en las yerbas
+¡Que tenga sed en todos los caminos
+la paloma que olvidó a su amado!
+Extraído de: José María Arguedas, Cantos y cuentos quechuas I. Municipalidad de Lima Metropolitana, Secretaría de Educación y Cultura, 1986.</t>
   </si>
 </sst>
 </file>
@@ -58843,7 +58861,9 @@
       <c r="C28" s="4" t="s">
         <v>459</v>
       </c>
-      <c r="D28" s="4"/>
+      <c r="D28" s="4" t="s">
+        <v>1058</v>
+      </c>
       <c r="E28" s="1"/>
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EEF7FC5A-6DFB-4840-AC5B-28896947810E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8AD8B7-9EB4-4F82-A28F-F3C227C8A7DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1603" uniqueCount="1059">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1601" uniqueCount="1058">
   <si>
     <t>Ramazzotti Spritz</t>
   </si>
@@ -1436,9 +1436,6 @@
   </si>
   <si>
     <t xml:space="preserve"> Georges Brassens - La Mauvaise Réputation</t>
-  </si>
-  <si>
-    <t>La Viejecita y las Palomas  (Cortometraje francés 1997)</t>
   </si>
   <si>
     <t>El Cíclope del Mar (Cortometraje francés 1999)</t>
@@ -5635,10 +5632,10 @@
         <v>78</v>
       </c>
       <c r="O1" s="27" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="P1" s="27" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="Q1" s="27" t="s">
         <v>79</v>
@@ -5650,13 +5647,13 @@
         <v>265</v>
       </c>
       <c r="T1" s="27" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="U1" s="27" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="V1" s="27" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="W1" s="27" t="s">
         <v>80</v>
@@ -5671,16 +5668,16 @@
         <v>196</v>
       </c>
       <c r="AA1" s="27" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="AB1" s="27" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="AC1" s="27" t="s">
+        <v>903</v>
+      </c>
+      <c r="AD1" s="27" t="s">
         <v>904</v>
-      </c>
-      <c r="AD1" s="27" t="s">
-        <v>905</v>
       </c>
       <c r="AE1" s="27" t="s">
         <v>82</v>
@@ -5707,7 +5704,7 @@
         <v>87</v>
       </c>
       <c r="AM1" s="27" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="AN1" s="27" t="s">
         <v>223</v>
@@ -5734,13 +5731,13 @@
         <v>200</v>
       </c>
       <c r="AV1" s="27" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="AW1" s="27" t="s">
         <v>209</v>
       </c>
       <c r="AX1" s="27" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="AY1" s="27" t="s">
         <v>230</v>
@@ -5830,16 +5827,16 @@
         <v>152</v>
       </c>
       <c r="CB1" s="8" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="CC1" s="8" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="CD1" s="7" t="s">
         <v>280</v>
       </c>
       <c r="CE1" s="7" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="CF1" s="8" t="s">
         <v>198</v>
@@ -5866,16 +5863,16 @@
         <v>120</v>
       </c>
       <c r="CN1" s="8" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="CO1" s="8" t="s">
         <v>215</v>
       </c>
       <c r="CP1" s="8" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="CQ1" s="8" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="CR1" s="7" t="s">
         <v>95</v>
@@ -5887,16 +5884,16 @@
         <v>97</v>
       </c>
       <c r="CU1" s="7" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="CV1" s="7" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="CW1" s="7" t="s">
         <v>98</v>
       </c>
       <c r="CX1" s="7" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="CY1" s="7" t="s">
         <v>99</v>
@@ -5911,22 +5908,22 @@
         <v>154</v>
       </c>
       <c r="DC1" s="8" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="DD1" s="18" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="DE1" s="18" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="DF1" s="18" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="DG1" s="18" t="s">
+        <v>846</v>
+      </c>
+      <c r="DH1" s="18" t="s">
         <v>847</v>
-      </c>
-      <c r="DH1" s="18" t="s">
-        <v>848</v>
       </c>
       <c r="DI1" s="15" t="s">
         <v>136</v>
@@ -5935,31 +5932,31 @@
         <v>135</v>
       </c>
       <c r="DK1" s="15" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="DL1" s="15" t="s">
+        <v>569</v>
+      </c>
+      <c r="DM1" s="15" t="s">
         <v>570</v>
       </c>
-      <c r="DM1" s="15" t="s">
-        <v>571</v>
-      </c>
       <c r="DN1" s="15" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="DO1" s="15" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="DP1" s="15" t="s">
+        <v>607</v>
+      </c>
+      <c r="DQ1" s="15" t="s">
+        <v>817</v>
+      </c>
+      <c r="DR1" s="15" t="s">
         <v>608</v>
       </c>
-      <c r="DQ1" s="15" t="s">
-        <v>818</v>
-      </c>
-      <c r="DR1" s="15" t="s">
-        <v>609</v>
-      </c>
       <c r="DS1" s="15" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="DT1" s="15" t="s">
         <v>141</v>
@@ -5968,43 +5965,43 @@
         <v>237</v>
       </c>
       <c r="DV1" s="15" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="DW1" s="15" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="DX1" s="15" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="DY1" s="15" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="DZ1" s="15" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="EA1" s="15" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="EB1" s="21" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="EC1" s="21" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="ED1" s="25" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="EE1" s="12" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="EF1" s="14" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="EG1" s="12" t="s">
         <v>234</v>
       </c>
       <c r="EH1" s="12" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="EI1" s="12" t="s">
         <v>286</v>
@@ -6019,19 +6016,19 @@
         <v>125</v>
       </c>
       <c r="EM1" s="17" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="EN1" s="17" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="EO1" s="17" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="EP1" s="19" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="EQ1" s="19" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="ER1" s="19" t="s">
         <v>126</v>
@@ -6046,7 +6043,7 @@
         <v>231</v>
       </c>
       <c r="EV1" s="20" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="EW1" s="20" t="s">
         <v>232</v>
@@ -7484,13 +7481,13 @@
     </row>
     <row r="10" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>51</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D10" s="2">
         <v>300</v>
@@ -7844,13 +7841,13 @@
     </row>
     <row r="12" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>55</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D12" s="2">
         <v>200</v>
@@ -8552,7 +8549,7 @@
     </row>
     <row r="16" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>278</v>
@@ -9280,7 +9277,7 @@
     </row>
     <row r="20" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>151</v>
@@ -9636,7 +9633,7 @@
     </row>
     <row r="22" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>53</v>
@@ -10344,7 +10341,7 @@
     </row>
     <row r="26" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>50</v>
@@ -10522,7 +10519,7 @@
     </row>
     <row r="27" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>51</v>
@@ -11054,7 +11051,7 @@
     </row>
     <row r="30" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>278</v>
@@ -11232,7 +11229,7 @@
     </row>
     <row r="31" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>278</v>
@@ -11410,7 +11407,7 @@
     </row>
     <row r="32" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>278</v>
@@ -11588,7 +11585,7 @@
     </row>
     <row r="33" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>55</v>
@@ -12122,7 +12119,7 @@
     </row>
     <row r="36" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>54</v>
@@ -12298,13 +12295,13 @@
     </row>
     <row r="37" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D37" s="2">
         <v>300</v>
@@ -12480,7 +12477,7 @@
     </row>
     <row r="38" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>50</v>
@@ -14606,7 +14603,7 @@
     </row>
     <row r="50" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>53</v>
@@ -14786,7 +14783,7 @@
     </row>
     <row r="51" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>55</v>
@@ -15146,7 +15143,7 @@
     </row>
     <row r="53" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>56</v>
@@ -15680,7 +15677,7 @@
     </row>
     <row r="56" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>51</v>
@@ -16214,7 +16211,7 @@
     </row>
     <row r="59" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>55</v>
@@ -17094,7 +17091,7 @@
     </row>
     <row r="64" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>50</v>
@@ -17450,7 +17447,7 @@
     </row>
     <row r="66" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>49</v>
@@ -17986,7 +17983,7 @@
     </row>
     <row r="69" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>430</v>
+        <v>429</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>55</v>
@@ -18162,7 +18159,7 @@
     </row>
     <row r="70" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>398</v>
+        <v>397</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>51</v>
@@ -18524,7 +18521,7 @@
     </row>
     <row r="72" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>50</v>
@@ -18700,10 +18697,10 @@
     </row>
     <row r="73" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>561</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>562</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>563</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>69</v>
@@ -18880,7 +18877,7 @@
     </row>
     <row r="74" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>51</v>
@@ -20132,7 +20129,7 @@
     </row>
     <row r="81" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>51</v>
@@ -20310,7 +20307,7 @@
     </row>
     <row r="82" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>50</v>
@@ -20674,7 +20671,7 @@
     </row>
     <row r="84" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>51</v>
@@ -20850,7 +20847,7 @@
     </row>
     <row r="85" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>51</v>
@@ -21904,10 +21901,10 @@
     </row>
     <row r="91" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>681</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>682</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>683</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>63</v>
@@ -22264,7 +22261,7 @@
     </row>
     <row r="93" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>53</v>
@@ -23154,7 +23151,7 @@
     </row>
     <row r="98" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>49</v>
@@ -24592,7 +24589,7 @@
     </row>
     <row r="106" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>53</v>
@@ -24948,7 +24945,7 @@
     </row>
     <row r="108" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>50</v>
@@ -25316,13 +25313,13 @@
     </row>
     <row r="110" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D110" s="2">
         <v>300</v>
@@ -25496,7 +25493,7 @@
     </row>
     <row r="111" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>50</v>
@@ -26736,7 +26733,7 @@
     </row>
     <row r="118" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>50</v>
@@ -27450,7 +27447,7 @@
     </row>
     <row r="122" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>50</v>
@@ -27980,7 +27977,7 @@
     </row>
     <row r="125" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A125" s="13" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>278</v>
@@ -28164,7 +28161,7 @@
     </row>
     <row r="126" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>278</v>
@@ -28880,7 +28877,7 @@
     </row>
     <row r="130" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>151</v>
@@ -30118,7 +30115,7 @@
     </row>
     <row r="137" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A137" s="13" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>278</v>
@@ -30476,7 +30473,7 @@
     </row>
     <row r="139" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>52</v>
@@ -30656,7 +30653,7 @@
     </row>
     <row r="140" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>50</v>
@@ -30838,7 +30835,7 @@
     </row>
     <row r="141" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>55</v>
@@ -31196,7 +31193,7 @@
     </row>
     <row r="143" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>51</v>
@@ -31560,7 +31557,7 @@
     </row>
     <row r="145" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>53</v>
@@ -31912,7 +31909,7 @@
     </row>
     <row r="147" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>51</v>
@@ -32088,7 +32085,7 @@
     </row>
     <row r="148" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>51</v>
@@ -32264,7 +32261,7 @@
     </row>
     <row r="149" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>50</v>
@@ -32618,13 +32615,13 @@
     </row>
     <row r="151" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D151" s="2">
         <v>300</v>
@@ -32798,7 +32795,7 @@
     </row>
     <row r="152" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>53</v>
@@ -32977,13 +32974,13 @@
     </row>
     <row r="153" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D153" s="2">
         <v>300</v>
@@ -33157,7 +33154,7 @@
     </row>
     <row r="154" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>51</v>
@@ -33333,7 +33330,7 @@
     </row>
     <row r="155" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>54</v>
@@ -33509,7 +33506,7 @@
     </row>
     <row r="156" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>53</v>
@@ -33687,7 +33684,7 @@
     </row>
     <row r="157" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>278</v>
@@ -33861,13 +33858,13 @@
     </row>
     <row r="158" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>278</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="D158" s="2">
         <v>1500</v>
@@ -34041,13 +34038,13 @@
     </row>
     <row r="159" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>278</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="D159" s="2">
         <v>1500</v>
@@ -34231,7 +34228,7 @@
     </row>
     <row r="160" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>197</v>
@@ -34403,7 +34400,7 @@
     </row>
     <row r="161" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>51</v>
@@ -34587,7 +34584,7 @@
     </row>
     <row r="162" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>51</v>
@@ -34763,7 +34760,7 @@
     </row>
     <row r="163" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>51</v>
@@ -34943,7 +34940,7 @@
     </row>
     <row r="164" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>53</v>
@@ -35121,7 +35118,7 @@
     </row>
     <row r="165" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>51</v>
@@ -35297,7 +35294,7 @@
     </row>
     <row r="166" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>50</v>
@@ -35479,7 +35476,7 @@
     </row>
     <row r="167" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>53</v>
@@ -35657,7 +35654,7 @@
     </row>
     <row r="168" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>55</v>
@@ -35831,7 +35828,7 @@
     </row>
     <row r="169" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>55</v>
@@ -36009,7 +36006,7 @@
     </row>
     <row r="170" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>53</v>
@@ -36185,7 +36182,7 @@
     </row>
     <row r="171" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>55</v>
@@ -48669,16 +48666,16 @@
         <v>129</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>141</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="J1" s="8" t="s">
         <v>237</v>
@@ -48693,10 +48690,10 @@
         <v>283</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="P1" s="8" t="s">
         <v>132</v>
@@ -48732,7 +48729,7 @@
         <v>131</v>
       </c>
       <c r="AA1" s="7" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="AB1" s="7" t="s">
         <v>199</v>
@@ -58146,7 +58143,7 @@
         <v>72</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>318</v>
@@ -58161,7 +58158,7 @@
         <v>315</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>316</v>
@@ -58170,16 +58167,16 @@
         <v>317</v>
       </c>
       <c r="J1" s="7" t="s">
+        <v>765</v>
+      </c>
+      <c r="K1" s="7" t="s">
         <v>766</v>
       </c>
-      <c r="K1" s="7" t="s">
-        <v>767</v>
-      </c>
       <c r="L1" s="7" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="270" x14ac:dyDescent="0.25">
@@ -58189,7 +58186,7 @@
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>309</v>
@@ -58207,7 +58204,7 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="4" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58216,10 +58213,10 @@
         <v>Alejandra</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>235</v>
@@ -58241,10 +58238,10 @@
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>238</v>
@@ -58253,7 +58250,7 @@
         <v>239</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="5"/>
@@ -58268,19 +58265,19 @@
         <v>Alexander</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="1"/>
@@ -58289,7 +58286,7 @@
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
       <c r="M5" s="4" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="270" x14ac:dyDescent="0.25">
@@ -58298,17 +58295,17 @@
         <v>Amaretto Sour</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
@@ -58317,7 +58314,7 @@
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="4" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="270" x14ac:dyDescent="0.25">
@@ -58327,14 +58324,14 @@
       </c>
       <c r="B7" s="1"/>
       <c r="C7" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
@@ -58343,7 +58340,7 @@
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="4" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="210" x14ac:dyDescent="0.25">
@@ -58353,7 +58350,7 @@
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
@@ -58369,7 +58366,7 @@
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="4" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -58379,10 +58376,10 @@
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>188</v>
@@ -58397,7 +58394,7 @@
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
       <c r="M9" s="1" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="210" x14ac:dyDescent="0.25">
@@ -58406,10 +58403,10 @@
         <v>Andes Refresh</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="11"/>
@@ -58429,10 +58426,10 @@
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="4" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -58443,7 +58440,7 @@
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="4" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58452,13 +58449,13 @@
         <v>Arándano Sour</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
@@ -58477,10 +58474,10 @@
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
@@ -58491,7 +58488,7 @@
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="4" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58501,10 +58498,10 @@
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
@@ -58519,7 +58516,7 @@
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="4" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58529,10 +58526,10 @@
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="4" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
@@ -58543,7 +58540,7 @@
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="4" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -58555,13 +58552,13 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -58577,16 +58574,16 @@
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="4" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>157</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="G17" s="10"/>
       <c r="H17" s="4" t="s">
@@ -58631,14 +58628,14 @@
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="4" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="1" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
@@ -58647,7 +58644,7 @@
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="4" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -58657,7 +58654,7 @@
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="1" t="s">
@@ -58680,26 +58677,26 @@
         <v>Borgoña</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="4" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="375" x14ac:dyDescent="0.25">
@@ -58708,17 +58705,17 @@
         <v>Caipiriña</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1" t="s">
+        <v>572</v>
+      </c>
+      <c r="F22" s="5" t="s">
         <v>573</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>574</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="1"/>
@@ -58736,7 +58733,7 @@
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
@@ -58747,7 +58744,7 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="4" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="345" x14ac:dyDescent="0.25">
@@ -58757,7 +58754,7 @@
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="4" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1" t="s">
@@ -58781,10 +58778,10 @@
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
@@ -58795,7 +58792,7 @@
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="4" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58805,25 +58802,25 @@
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="4" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="4" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="4" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="375" x14ac:dyDescent="0.25">
@@ -58832,13 +58829,13 @@
         <v>Chupilca</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
@@ -58849,7 +58846,7 @@
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="4" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58859,25 +58856,25 @@
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>1058</v>
-      </c>
-      <c r="E28" s="1"/>
-      <c r="F28" s="5"/>
+        <v>1057</v>
+      </c>
+      <c r="E28" s="1" t="s">
+        <v>529</v>
+      </c>
+      <c r="F28" s="1" t="s">
+        <v>528</v>
+      </c>
       <c r="G28" s="5"/>
-      <c r="H28" s="1" t="s">
-        <v>351</v>
-      </c>
-      <c r="I28" s="5" t="s">
-        <v>256</v>
-      </c>
+      <c r="H28" s="1"/>
+      <c r="I28" s="5"/>
       <c r="J28" s="1"/>
       <c r="K28" s="5"/>
       <c r="L28" s="5"/>
       <c r="M28" s="4" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="360" x14ac:dyDescent="0.25">
@@ -58887,14 +58884,14 @@
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="4" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
@@ -58903,7 +58900,7 @@
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="4" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58912,13 +58909,13 @@
         <v>Cléry</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
@@ -58929,7 +58926,7 @@
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="4" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58938,22 +58935,22 @@
         <v>Cléry Chirimoya</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="F31" s="5" t="s">
+        <v>1003</v>
+      </c>
+      <c r="G31" s="4" t="s">
         <v>1004</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>1005</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -58961,7 +58958,7 @@
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="4" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -58970,10 +58967,10 @@
         <v>Cléry Durazno</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1" t="s">
@@ -58996,19 +58993,19 @@
         <v>Clover Club</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="D33" s="4" t="s">
+        <v>549</v>
+      </c>
+      <c r="E33" s="4" t="s">
         <v>550</v>
       </c>
-      <c r="E33" s="4" t="s">
-        <v>551</v>
-      </c>
       <c r="F33" s="1" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
@@ -59017,7 +59014,7 @@
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="4" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="255" x14ac:dyDescent="0.25">
@@ -59027,7 +59024,7 @@
       </c>
       <c r="B34" s="1"/>
       <c r="C34" s="4" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="1" t="s">
@@ -59043,7 +59040,7 @@
       <c r="K34" s="5"/>
       <c r="L34" s="5"/>
       <c r="M34" s="4" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -59052,10 +59049,10 @@
         <v>Cosmo Patagonia</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="1"/>
@@ -59075,7 +59072,7 @@
       </c>
       <c r="B36" s="1"/>
       <c r="C36" s="4" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
@@ -59087,7 +59084,7 @@
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59096,10 +59093,10 @@
         <v>Crepúsculo</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="4" t="s">
@@ -59115,7 +59112,7 @@
       <c r="K37" s="5"/>
       <c r="L37" s="5"/>
       <c r="M37" s="4" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="255" x14ac:dyDescent="0.25">
@@ -59125,14 +59122,14 @@
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="4" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D38" s="1"/>
       <c r="E38" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="1"/>
@@ -59141,7 +59138,7 @@
       <c r="K38" s="5"/>
       <c r="L38" s="5"/>
       <c r="M38" s="4" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="75" x14ac:dyDescent="0.25">
@@ -59175,23 +59172,23 @@
       </c>
       <c r="D40" s="1"/>
       <c r="E40" s="4" t="s">
-        <v>407</v>
+        <v>406</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="1" t="s">
+        <v>929</v>
+      </c>
+      <c r="I40" s="5" t="s">
         <v>930</v>
-      </c>
-      <c r="I40" s="5" t="s">
-        <v>931</v>
       </c>
       <c r="J40" s="4"/>
       <c r="K40" s="5"/>
       <c r="L40" s="5"/>
       <c r="M40" s="4" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="210" x14ac:dyDescent="0.25">
@@ -59200,10 +59197,10 @@
         <v>Dama Blanca</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="1"/>
@@ -59223,14 +59220,14 @@
       </c>
       <c r="B42" s="1"/>
       <c r="C42" s="4" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
@@ -59239,7 +59236,7 @@
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="M42" s="4" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="270" x14ac:dyDescent="0.25">
@@ -59249,10 +59246,10 @@
       </c>
       <c r="B43" s="1"/>
       <c r="C43" s="4" t="s">
+        <v>592</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>593</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>594</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="5"/>
@@ -59267,7 +59264,7 @@
       <c r="K43" s="5"/>
       <c r="L43" s="5"/>
       <c r="M43" s="4" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -59277,7 +59274,7 @@
       </c>
       <c r="B44" s="1"/>
       <c r="C44" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
@@ -59296,13 +59293,13 @@
         <v>Dry Martini</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
@@ -59313,7 +59310,7 @@
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
       <c r="M45" s="4" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="285" x14ac:dyDescent="0.25">
@@ -59322,11 +59319,11 @@
         <v>El Amor en los Tiempos del Covid</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C46" s="4"/>
       <c r="D46" s="4" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>185</v>
@@ -59338,16 +59335,16 @@
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
       <c r="J46" s="4" t="s">
+        <v>1037</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>1036</v>
+      </c>
+      <c r="L46" s="4" t="s">
         <v>1038</v>
       </c>
-      <c r="K46" s="5" t="s">
-        <v>1037</v>
-      </c>
-      <c r="L46" s="4" t="s">
-        <v>1039</v>
-      </c>
       <c r="M46" s="4" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -59357,7 +59354,7 @@
       </c>
       <c r="B47" s="1"/>
       <c r="C47" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>306</v>
@@ -59375,7 +59372,7 @@
       <c r="K47" s="5"/>
       <c r="L47" s="5"/>
       <c r="M47" s="4" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="315" x14ac:dyDescent="0.25">
@@ -59385,16 +59382,16 @@
       </c>
       <c r="B48" s="1"/>
       <c r="C48" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E48" s="1" t="s">
+        <v>598</v>
+      </c>
+      <c r="F48" s="5" t="s">
         <v>599</v>
-      </c>
-      <c r="F48" s="5" t="s">
-        <v>600</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="1"/>
@@ -59411,19 +59408,19 @@
       </c>
       <c r="B49" s="1"/>
       <c r="C49" s="4" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="E49" s="1" t="s">
+        <v>770</v>
+      </c>
+      <c r="F49" s="5" t="s">
         <v>771</v>
       </c>
-      <c r="F49" s="5" t="s">
-        <v>772</v>
-      </c>
       <c r="G49" s="4" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -59431,7 +59428,7 @@
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
       <c r="M49" s="4" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="255" x14ac:dyDescent="0.25">
@@ -59441,17 +59438,17 @@
       </c>
       <c r="B50" s="1"/>
       <c r="C50" s="4" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="4" t="s">
+        <v>481</v>
+      </c>
+      <c r="F50" s="5" t="s">
         <v>482</v>
       </c>
-      <c r="F50" s="5" t="s">
-        <v>483</v>
-      </c>
       <c r="G50" s="4" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>326</v>
@@ -59463,7 +59460,7 @@
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
       <c r="M50" s="4" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -59473,7 +59470,7 @@
       </c>
       <c r="B51" s="1"/>
       <c r="C51" s="4" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -59485,7 +59482,7 @@
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
       <c r="M51" s="1" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="150" x14ac:dyDescent="0.25">
@@ -59495,10 +59492,10 @@
       </c>
       <c r="B52" s="1"/>
       <c r="C52" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>193</v>
@@ -59508,16 +59505,16 @@
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
       <c r="M52" s="4" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="390" x14ac:dyDescent="0.25">
@@ -59527,31 +59524,31 @@
       </c>
       <c r="B53" s="1"/>
       <c r="C53" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D53" s="4" t="s">
+        <v>402</v>
+      </c>
+      <c r="E53" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="F53" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="F53" s="1" t="s">
-        <v>405</v>
-      </c>
       <c r="G53" s="4" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="J53" s="1"/>
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="4" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59561,14 +59558,14 @@
       </c>
       <c r="B54" s="1"/>
       <c r="C54" s="4" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="1"/>
       <c r="F54" s="5"/>
       <c r="G54" s="4"/>
       <c r="H54" s="1" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="I54" s="5" t="s">
         <v>290</v>
@@ -59577,7 +59574,7 @@
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
       <c r="M54" s="4" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
@@ -59587,7 +59584,7 @@
       </c>
       <c r="B55" s="1"/>
       <c r="C55" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D55" s="1"/>
       <c r="E55" s="1" t="s">
@@ -59611,19 +59608,19 @@
       </c>
       <c r="B56" s="1"/>
       <c r="C56" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -59631,7 +59628,7 @@
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
       <c r="M56" s="4" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59641,10 +59638,10 @@
       </c>
       <c r="B57" s="1"/>
       <c r="C57" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E57" s="11" t="s">
         <v>172</v>
@@ -59659,7 +59656,7 @@
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
       <c r="M57" s="4" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="150" x14ac:dyDescent="0.25">
@@ -59668,7 +59665,7 @@
         <v>Frangelico Sour</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>338</v>
@@ -59683,7 +59680,7 @@
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="4" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59692,19 +59689,19 @@
         <v>French 75</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E59" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="G59" s="5"/>
       <c r="H59" s="1"/>
@@ -59713,7 +59710,7 @@
       <c r="K59" s="5"/>
       <c r="L59" s="5"/>
       <c r="M59" s="4" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -59735,7 +59732,7 @@
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
       <c r="M60" s="4" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="165" x14ac:dyDescent="0.25">
@@ -59748,13 +59745,13 @@
         <v>336</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="4"/>
@@ -59763,7 +59760,7 @@
       <c r="K61" s="1"/>
       <c r="L61" s="1"/>
       <c r="M61" s="4" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="345" x14ac:dyDescent="0.25">
@@ -59773,14 +59770,14 @@
       </c>
       <c r="B62" s="1"/>
       <c r="C62" s="4" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D62" s="1"/>
       <c r="E62" s="4" t="s">
+        <v>407</v>
+      </c>
+      <c r="F62" s="5" t="s">
         <v>408</v>
-      </c>
-      <c r="F62" s="5" t="s">
-        <v>409</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="4"/>
@@ -59789,7 +59786,7 @@
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
       <c r="M62" s="4" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59800,7 +59797,7 @@
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>159</v>
@@ -59810,22 +59807,22 @@
       </c>
       <c r="G63" s="4"/>
       <c r="H63" s="4" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="I63" s="5" t="s">
         <v>337</v>
       </c>
       <c r="J63" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="K63" s="5" t="s">
         <v>768</v>
       </c>
-      <c r="K63" s="5" t="s">
-        <v>769</v>
-      </c>
       <c r="L63" s="4" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="M63" s="4" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -59835,7 +59832,7 @@
       </c>
       <c r="B64" s="1"/>
       <c r="C64" s="4" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
@@ -59847,7 +59844,7 @@
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
       <c r="M64" s="4" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59857,7 +59854,7 @@
       </c>
       <c r="B65" s="1"/>
       <c r="C65" s="4" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>169</v>
@@ -59871,7 +59868,7 @@
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
       <c r="M65" s="1" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="375" x14ac:dyDescent="0.25">
@@ -59881,10 +59878,10 @@
       </c>
       <c r="B66" s="1"/>
       <c r="C66" s="4" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
@@ -59903,7 +59900,7 @@
       </c>
       <c r="B67" s="1"/>
       <c r="C67" s="4" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="D67" s="4"/>
       <c r="E67" s="1" t="s">
@@ -59919,7 +59916,7 @@
       <c r="K67" s="5"/>
       <c r="L67" s="5"/>
       <c r="M67" s="4" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="68" spans="1:13" ht="330" x14ac:dyDescent="0.25">
@@ -59929,10 +59926,10 @@
       </c>
       <c r="B68" s="1"/>
       <c r="C68" s="1" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>165</v>
@@ -59947,7 +59944,7 @@
       <c r="K68" s="5"/>
       <c r="L68" s="5"/>
       <c r="M68" s="4" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="69" spans="1:13" ht="300" x14ac:dyDescent="0.25">
@@ -59957,16 +59954,16 @@
       </c>
       <c r="B69" s="1"/>
       <c r="C69" s="4" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="D69" s="4" t="s">
+        <v>430</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>432</v>
+      </c>
+      <c r="F69" s="1" t="s">
         <v>431</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>433</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>432</v>
       </c>
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
@@ -59975,7 +59972,7 @@
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
       <c r="M69" s="4" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -59985,16 +59982,16 @@
       </c>
       <c r="B70" s="1"/>
       <c r="C70" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E70" s="1" t="s">
+        <v>398</v>
+      </c>
+      <c r="F70" s="1" t="s">
         <v>399</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>400</v>
       </c>
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
@@ -60003,7 +60000,7 @@
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
       <c r="M70" s="4" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -60013,14 +60010,14 @@
       </c>
       <c r="B71" s="1"/>
       <c r="C71" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D71" s="1"/>
       <c r="E71" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="1"/>
@@ -60029,7 +60026,7 @@
       <c r="K71" s="5"/>
       <c r="L71" s="5"/>
       <c r="M71" s="4" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="72" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60038,28 +60035,28 @@
         <v>Jote</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="E72" s="1"/>
       <c r="F72" s="5"/>
       <c r="G72" s="5"/>
       <c r="H72" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="J72" s="1"/>
       <c r="K72" s="5"/>
       <c r="L72" s="5"/>
       <c r="M72" s="4" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
     </row>
     <row r="73" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -60068,11 +60065,11 @@
         <v>Julepe de Menta</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C73" s="4"/>
       <c r="D73" s="4" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
@@ -60090,26 +60087,26 @@
         <v>Julieta Flowers</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="E74" s="1" t="s">
+        <v>729</v>
+      </c>
+      <c r="F74" s="5" t="s">
         <v>730</v>
-      </c>
-      <c r="F74" s="5" t="s">
-        <v>731</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="1" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="J74" s="1"/>
       <c r="K74" s="5"/>
@@ -60143,7 +60140,7 @@
       </c>
       <c r="B76" s="1"/>
       <c r="C76" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D76" s="4" t="s">
         <v>270</v>
@@ -60169,10 +60166,10 @@
       </c>
       <c r="B77" s="1"/>
       <c r="C77" s="4" t="s">
+        <v>1018</v>
+      </c>
+      <c r="D77" s="4" t="s">
         <v>1019</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>1020</v>
       </c>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
@@ -60183,7 +60180,7 @@
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
       <c r="M77" s="4" t="s">
-        <v>1018</v>
+        <v>1017</v>
       </c>
     </row>
     <row r="78" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -60193,23 +60190,23 @@
       </c>
       <c r="B78" s="1"/>
       <c r="C78" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D78" s="1"/>
       <c r="E78" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="G78" s="5"/>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
       <c r="J78" s="1" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="K78" s="5" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="L78" s="5"/>
       <c r="M78" s="1"/>
@@ -60259,7 +60256,7 @@
       </c>
       <c r="B81" s="1"/>
       <c r="C81" s="4" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D81" s="4"/>
       <c r="E81" s="1"/>
@@ -60278,20 +60275,20 @@
         <v>Mai Tai Piña</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D82" s="4"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
       <c r="G82" s="1"/>
       <c r="H82" s="1" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="I82" s="5" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="J82" s="1"/>
       <c r="K82" s="1"/>
@@ -60305,7 +60302,7 @@
       </c>
       <c r="B83" s="1"/>
       <c r="C83" s="4" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>304</v>
@@ -60323,7 +60320,7 @@
       <c r="K83" s="5"/>
       <c r="L83" s="5"/>
       <c r="M83" s="4" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="84" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60332,28 +60329,28 @@
         <v>Malta con Huevo</v>
       </c>
       <c r="B84" s="4" t="s">
+        <v>661</v>
+      </c>
+      <c r="C84" s="4" t="s">
         <v>662</v>
       </c>
-      <c r="C84" s="4" t="s">
-        <v>663</v>
-      </c>
       <c r="D84" s="4" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
       <c r="H84" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="J84" s="1"/>
       <c r="K84" s="1"/>
       <c r="L84" s="1"/>
       <c r="M84" s="4" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -60362,28 +60359,28 @@
         <v>Malta con Leche Condensada</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
       <c r="H85" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="J85" s="1"/>
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
       <c r="M85" s="4" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -60392,7 +60389,7 @@
         <v>Mango Sour</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C86" s="4"/>
       <c r="D86" s="1"/>
@@ -60413,27 +60410,27 @@
       </c>
       <c r="B87" s="1"/>
       <c r="C87" s="4" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="D87" s="1"/>
       <c r="E87" s="1" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="G87" s="5"/>
       <c r="H87" s="1" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="I87" s="5" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="J87" s="1"/>
       <c r="K87" s="5"/>
       <c r="L87" s="5"/>
       <c r="M87" s="4" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="88" spans="1:13" ht="360" x14ac:dyDescent="0.25">
@@ -60442,13 +60439,13 @@
         <v>Maqui Sour</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
@@ -60466,10 +60463,10 @@
         <v>Margarita</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D89" s="1"/>
       <c r="E89" s="1" t="s">
@@ -60495,10 +60492,10 @@
       <c r="C90" s="1"/>
       <c r="D90" s="1"/>
       <c r="E90" s="1" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="G90" s="5"/>
       <c r="H90" s="1"/>
@@ -60514,10 +60511,10 @@
         <v>Melón con Vino</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D91" s="1"/>
       <c r="E91" s="1" t="s">
@@ -60540,13 +60537,13 @@
         <v>Michelada</v>
       </c>
       <c r="B92" s="4" t="s">
+        <v>844</v>
+      </c>
+      <c r="C92" s="4" t="s">
         <v>845</v>
       </c>
-      <c r="C92" s="4" t="s">
-        <v>846</v>
-      </c>
       <c r="D92" s="4" t="s">
-        <v>402</v>
+        <v>401</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>178</v>
@@ -60569,7 +60566,7 @@
       </c>
       <c r="B93" s="1"/>
       <c r="C93" s="4" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
@@ -60581,7 +60578,7 @@
       <c r="K93" s="1"/>
       <c r="L93" s="1"/>
       <c r="M93" s="4" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="94" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -60591,7 +60588,7 @@
       </c>
       <c r="B94" s="1"/>
       <c r="C94" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="D94" s="1"/>
       <c r="E94" s="1"/>
@@ -60610,10 +60607,10 @@
         <v>Mojito</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D95" s="4"/>
       <c r="E95" s="1"/>
@@ -60625,7 +60622,7 @@
       <c r="K95" s="1"/>
       <c r="L95" s="1"/>
       <c r="M95" s="4" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="96" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -60635,7 +60632,7 @@
       </c>
       <c r="B96" s="1"/>
       <c r="C96" s="4" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D96" s="4"/>
       <c r="E96" s="1"/>
@@ -60655,16 +60652,16 @@
       </c>
       <c r="B97" s="1"/>
       <c r="C97" s="4" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="G97" s="1"/>
       <c r="H97" s="4"/>
@@ -60673,7 +60670,7 @@
       <c r="K97" s="1"/>
       <c r="L97" s="1"/>
       <c r="M97" s="4" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="98" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -60683,7 +60680,7 @@
       </c>
       <c r="B98" s="1"/>
       <c r="C98" s="4" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="D98" s="4"/>
       <c r="E98" s="1"/>
@@ -60719,7 +60716,7 @@
       <c r="K99" s="5"/>
       <c r="L99" s="5"/>
       <c r="M99" s="4" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="100" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -60728,10 +60725,10 @@
         <v>Naranja Sour</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D100" s="4"/>
       <c r="E100" s="1" t="s">
@@ -60755,7 +60752,7 @@
       </c>
       <c r="B101" s="1"/>
       <c r="C101" s="4" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="D101" s="4"/>
       <c r="E101" s="4"/>
@@ -60779,7 +60776,7 @@
       </c>
       <c r="B102" s="1"/>
       <c r="C102" s="4" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="D102" s="4" t="s">
         <v>224</v>
@@ -60793,7 +60790,7 @@
       <c r="K102" s="1"/>
       <c r="L102" s="1"/>
       <c r="M102" s="4" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="103" spans="1:13" ht="210" x14ac:dyDescent="0.25">
@@ -60803,7 +60800,7 @@
       </c>
       <c r="B103" s="1"/>
       <c r="C103" s="4" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="D103" s="1"/>
       <c r="E103" s="1"/>
@@ -60815,7 +60812,7 @@
       <c r="K103" s="1"/>
       <c r="L103" s="1"/>
       <c r="M103" s="4" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="104" spans="1:13" ht="345" x14ac:dyDescent="0.25">
@@ -60824,19 +60821,19 @@
         <v>New York Sour</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="G104" s="5"/>
       <c r="H104" s="1"/>
@@ -60845,7 +60842,7 @@
       <c r="K104" s="5"/>
       <c r="L104" s="5"/>
       <c r="M104" s="4" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="105" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -60855,7 +60852,7 @@
       </c>
       <c r="B105" s="1"/>
       <c r="C105" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D105" s="1"/>
       <c r="E105" s="1" t="s">
@@ -60871,7 +60868,7 @@
       <c r="K105" s="1"/>
       <c r="L105" s="1"/>
       <c r="M105" s="4" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="106" spans="1:13" ht="375" x14ac:dyDescent="0.25">
@@ -60880,32 +60877,32 @@
         <v>Old Fashioned</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C106" s="4"/>
       <c r="D106" s="4" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="E106" s="1" t="s">
+        <v>1043</v>
+      </c>
+      <c r="F106" s="5" t="s">
         <v>1044</v>
       </c>
-      <c r="F106" s="5" t="s">
-        <v>1045</v>
-      </c>
       <c r="G106" s="4" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="I106" s="5" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="J106" s="1"/>
       <c r="K106" s="1"/>
       <c r="L106" s="1"/>
       <c r="M106" s="4" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="107" spans="1:13" ht="192" customHeight="1" x14ac:dyDescent="0.25">
@@ -60934,21 +60931,17 @@
         <v>Paloma</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="D108" s="1"/>
-      <c r="E108" s="1" t="s">
-        <v>530</v>
-      </c>
-      <c r="F108" s="1" t="s">
-        <v>529</v>
-      </c>
+      <c r="E108" s="1"/>
+      <c r="F108" s="1"/>
       <c r="G108" s="1"/>
       <c r="H108" s="1" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="I108" s="5" t="s">
         <v>256</v>
@@ -60957,7 +60950,7 @@
       <c r="K108" s="1"/>
       <c r="L108" s="1"/>
       <c r="M108" s="4" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="109" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -60966,7 +60959,7 @@
         <v>Parrón</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="C109" s="4"/>
       <c r="D109" s="4"/>
@@ -60986,19 +60979,19 @@
         <v>Penicilina</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="G110" s="5"/>
       <c r="H110" s="1"/>
@@ -61007,7 +61000,7 @@
       <c r="K110" s="5"/>
       <c r="L110" s="5"/>
       <c r="M110" s="4" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.25">
@@ -61017,14 +61010,14 @@
       </c>
       <c r="B111" s="1"/>
       <c r="C111" s="4" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="D111" s="1"/>
       <c r="E111" s="1" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="G111" s="5"/>
       <c r="H111" s="1"/>
@@ -61041,14 +61034,14 @@
       </c>
       <c r="B112" s="1"/>
       <c r="C112" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D112" s="1"/>
       <c r="E112" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="G112" s="5"/>
       <c r="H112" s="1"/>
@@ -61065,11 +61058,11 @@
       </c>
       <c r="B113" s="1"/>
       <c r="C113" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D113" s="5"/>
       <c r="E113" s="6" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="F113" s="5" t="s">
         <v>158</v>
@@ -61081,7 +61074,7 @@
       <c r="K113" s="5"/>
       <c r="L113" s="5"/>
       <c r="M113" s="4" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.25">
@@ -61130,11 +61123,11 @@
         <v>Pisco Sour</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="C116" s="4"/>
       <c r="D116" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>161</v>
@@ -61156,17 +61149,17 @@
         <v>Piscola</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D117" s="5"/>
       <c r="E117" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="G117" s="5"/>
       <c r="H117" s="1"/>
@@ -61175,7 +61168,7 @@
       <c r="K117" s="5"/>
       <c r="L117" s="5"/>
       <c r="M117" s="4" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="118" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -61184,17 +61177,17 @@
         <v>Pistón</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D118" s="1"/>
       <c r="E118" s="1" t="s">
+        <v>501</v>
+      </c>
+      <c r="F118" s="5" t="s">
         <v>502</v>
-      </c>
-      <c r="F118" s="5" t="s">
-        <v>503</v>
       </c>
       <c r="G118" s="5"/>
       <c r="H118" s="1"/>
@@ -61211,10 +61204,10 @@
       </c>
       <c r="B119" s="1"/>
       <c r="C119" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E119" s="1"/>
       <c r="F119" s="5"/>
@@ -61229,7 +61222,7 @@
       <c r="K119" s="5"/>
       <c r="L119" s="5"/>
       <c r="M119" s="4" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="120" spans="1:13" ht="75" x14ac:dyDescent="0.25">
@@ -61239,14 +61232,14 @@
       </c>
       <c r="B120" s="1"/>
       <c r="C120" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D120" s="1"/>
       <c r="E120" s="1" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="G120" s="5"/>
       <c r="H120" s="1"/>
@@ -61263,7 +61256,7 @@
       </c>
       <c r="B121" s="1"/>
       <c r="C121" s="4" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D121" s="1"/>
       <c r="E121" s="1"/>
@@ -61283,14 +61276,14 @@
       </c>
       <c r="B122" s="1"/>
       <c r="C122" s="4" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D122" s="1"/>
       <c r="E122" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="G122" s="1"/>
       <c r="H122" s="1"/>
@@ -61307,7 +61300,7 @@
       </c>
       <c r="B123" s="1"/>
       <c r="C123" s="4" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D123" s="4" t="s">
         <v>252</v>
@@ -61325,7 +61318,7 @@
       <c r="K123" s="5"/>
       <c r="L123" s="5"/>
       <c r="M123" s="4" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="124" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -61335,10 +61328,10 @@
       </c>
       <c r="B124" s="1"/>
       <c r="C124" s="4" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E124" s="1"/>
       <c r="F124" s="1"/>
@@ -61356,19 +61349,19 @@
         <v>Sangría</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="G125" s="5"/>
       <c r="H125" s="1"/>
@@ -61385,7 +61378,7 @@
       </c>
       <c r="B126" s="1"/>
       <c r="C126" s="4" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D126" s="1"/>
       <c r="E126" s="1"/>
@@ -61405,14 +61398,14 @@
       </c>
       <c r="B127" s="1"/>
       <c r="C127" s="4" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D127" s="1"/>
       <c r="E127" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="G127" s="1"/>
       <c r="H127" s="1"/>
@@ -61441,7 +61434,7 @@
       <c r="K128" s="1"/>
       <c r="L128" s="1"/>
       <c r="M128" s="4" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="129" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -61451,10 +61444,10 @@
       </c>
       <c r="B129" s="1"/>
       <c r="C129" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
       <c r="E129" s="1"/>
       <c r="F129" s="1"/>
@@ -61465,7 +61458,7 @@
       <c r="K129" s="1"/>
       <c r="L129" s="1"/>
       <c r="M129" s="4" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="130" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -61475,7 +61468,7 @@
       </c>
       <c r="B130" s="1"/>
       <c r="C130" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D130" s="1"/>
       <c r="E130" s="1"/>
@@ -61495,7 +61488,7 @@
       </c>
       <c r="B131" s="1"/>
       <c r="C131" s="4" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="D131" s="4"/>
       <c r="E131" s="1"/>
@@ -61515,7 +61508,7 @@
       </c>
       <c r="B132" s="1"/>
       <c r="C132" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D132" s="1"/>
       <c r="E132" s="1" t="s">
@@ -61531,7 +61524,7 @@
       <c r="K132" s="5"/>
       <c r="L132" s="5"/>
       <c r="M132" s="4" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.25">
@@ -61561,16 +61554,16 @@
       </c>
       <c r="B134" s="1"/>
       <c r="C134" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="D134" s="4" t="s">
+        <v>597</v>
+      </c>
+      <c r="E134" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="F134" s="5" t="s">
         <v>589</v>
-      </c>
-      <c r="D134" s="4" t="s">
-        <v>598</v>
-      </c>
-      <c r="E134" s="4" t="s">
-        <v>591</v>
-      </c>
-      <c r="F134" s="5" t="s">
-        <v>590</v>
       </c>
       <c r="G134" s="5"/>
       <c r="H134" s="4"/>
@@ -61579,7 +61572,7 @@
       <c r="K134" s="5"/>
       <c r="L134" s="5"/>
       <c r="M134" s="4" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="135" spans="1:13" ht="300" x14ac:dyDescent="0.25">
@@ -61588,28 +61581,28 @@
         <v>Terremoto</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="E135" s="1"/>
       <c r="F135" s="1"/>
       <c r="G135" s="1"/>
       <c r="H135" s="1" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="I135" s="5" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="J135" s="1"/>
       <c r="K135" s="1"/>
       <c r="L135" s="1"/>
       <c r="M135" s="4" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="136" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -61618,10 +61611,10 @@
         <v>Terremoto (Sin Alcohol)</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D136" s="4"/>
       <c r="E136" s="1" t="s">
@@ -61646,16 +61639,16 @@
       <c r="B137" s="13"/>
       <c r="C137" s="1"/>
       <c r="D137" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E137" s="1" t="s">
+        <v>1040</v>
+      </c>
+      <c r="F137" s="5" t="s">
+        <v>1039</v>
+      </c>
+      <c r="G137" s="4" t="s">
         <v>1041</v>
-      </c>
-      <c r="F137" s="5" t="s">
-        <v>1040</v>
-      </c>
-      <c r="G137" s="4" t="s">
-        <v>1042</v>
       </c>
       <c r="H137" s="1"/>
       <c r="I137" s="1"/>
@@ -61671,7 +61664,7 @@
       </c>
       <c r="B138" s="4"/>
       <c r="C138" s="4" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D138" s="1"/>
       <c r="E138" s="1"/>
@@ -61683,7 +61676,7 @@
       <c r="K138" s="1"/>
       <c r="L138" s="1"/>
       <c r="M138" s="4" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="139" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -61693,17 +61686,17 @@
       </c>
       <c r="B139" s="1"/>
       <c r="C139" s="4" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="D139" s="4"/>
       <c r="E139" s="1"/>
       <c r="F139" s="1"/>
       <c r="G139" s="1"/>
       <c r="H139" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I139" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="J139" s="1"/>
       <c r="K139" s="1"/>
@@ -61716,34 +61709,34 @@
         <v>Tropezón</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="D140" s="4" t="s">
         <v>345</v>
       </c>
       <c r="E140" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="F140" s="5" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G140" s="4" t="s">
         <v>1027</v>
-      </c>
-      <c r="F140" s="5" t="s">
-        <v>1026</v>
-      </c>
-      <c r="G140" s="4" t="s">
-        <v>1028</v>
       </c>
       <c r="H140" s="1"/>
       <c r="I140" s="1"/>
       <c r="J140" s="1" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="K140" s="5" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="L140" s="5"/>
       <c r="M140" s="4" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="141" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -61752,19 +61745,19 @@
         <v>Vaina</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="E141" s="4" t="s">
+        <v>613</v>
+      </c>
+      <c r="F141" s="4" t="s">
         <v>614</v>
-      </c>
-      <c r="F141" s="4" t="s">
-        <v>615</v>
       </c>
       <c r="G141" s="4"/>
       <c r="H141" s="1"/>
@@ -61781,7 +61774,7 @@
       </c>
       <c r="B142" s="1"/>
       <c r="C142" s="4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D142" s="4"/>
       <c r="E142" s="4" t="s">
@@ -61804,19 +61797,19 @@
         <v>Vampiro</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E143" s="1" t="s">
+        <v>539</v>
+      </c>
+      <c r="F143" s="1" t="s">
         <v>540</v>
-      </c>
-      <c r="F143" s="1" t="s">
-        <v>541</v>
       </c>
       <c r="G143" s="1"/>
       <c r="H143" s="1"/>
@@ -61825,7 +61818,7 @@
       <c r="K143" s="1"/>
       <c r="L143" s="1"/>
       <c r="M143" s="4" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="144" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -61835,7 +61828,7 @@
       </c>
       <c r="B144" s="1"/>
       <c r="C144" s="1" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="D144" s="4" t="s">
         <v>348</v>
@@ -61848,20 +61841,20 @@
       </c>
       <c r="G144" s="1"/>
       <c r="H144" s="1" t="s">
+        <v>1031</v>
+      </c>
+      <c r="I144" s="5" t="s">
         <v>1032</v>
       </c>
-      <c r="I144" s="5" t="s">
-        <v>1033</v>
-      </c>
       <c r="J144" s="1" t="s">
+        <v>1029</v>
+      </c>
+      <c r="K144" s="5" t="s">
         <v>1030</v>
-      </c>
-      <c r="K144" s="5" t="s">
-        <v>1031</v>
       </c>
       <c r="L144" s="1"/>
       <c r="M144" s="4" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="145" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -61870,19 +61863,19 @@
         <v>Vermouth con Soda</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="G145" s="1"/>
       <c r="H145" s="1"/>
@@ -61891,7 +61884,7 @@
       <c r="K145" s="1"/>
       <c r="L145" s="1"/>
       <c r="M145" s="4" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="146" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -61901,7 +61894,7 @@
       </c>
       <c r="B146" s="1"/>
       <c r="C146" s="4" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D146" s="1"/>
       <c r="E146" s="1"/>
@@ -61921,14 +61914,14 @@
       </c>
       <c r="B147" s="1"/>
       <c r="C147" s="4" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D147" s="4"/>
       <c r="E147" s="1" t="s">
+        <v>714</v>
+      </c>
+      <c r="F147" s="5" t="s">
         <v>715</v>
-      </c>
-      <c r="F147" s="5" t="s">
-        <v>716</v>
       </c>
       <c r="G147" s="5"/>
       <c r="H147" s="1"/>
@@ -61937,7 +61930,7 @@
       <c r="K147" s="5"/>
       <c r="L147" s="5"/>
       <c r="M147" s="4" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="148" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -61947,14 +61940,14 @@
       </c>
       <c r="B148" s="1"/>
       <c r="C148" s="4" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="D148" s="1"/>
       <c r="E148" s="1" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="G148" s="5"/>
       <c r="H148" s="1"/>
@@ -61971,16 +61964,16 @@
       </c>
       <c r="B149" s="1"/>
       <c r="C149" s="4" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="E149" s="1" t="s">
+        <v>708</v>
+      </c>
+      <c r="F149" s="5" t="s">
         <v>709</v>
-      </c>
-      <c r="F149" s="5" t="s">
-        <v>710</v>
       </c>
       <c r="G149" s="5"/>
       <c r="H149" s="1"/>
@@ -61996,19 +61989,19 @@
         <v>Whisky Sour</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="G150" s="1"/>
       <c r="H150" s="1"/>
@@ -62017,7 +62010,7 @@
       <c r="K150" s="1"/>
       <c r="L150" s="1"/>
       <c r="M150" s="4" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="151" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -62026,19 +62019,19 @@
         <v>Bramble</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D151" s="4" t="s">
+        <v>791</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>793</v>
+      </c>
+      <c r="F151" s="1" t="s">
         <v>792</v>
-      </c>
-      <c r="E151" s="1" t="s">
-        <v>794</v>
-      </c>
-      <c r="F151" s="1" t="s">
-        <v>793</v>
       </c>
       <c r="G151" s="1"/>
       <c r="H151" s="1"/>
@@ -62055,14 +62048,14 @@
       </c>
       <c r="B152" s="1"/>
       <c r="C152" s="4" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D152" s="4"/>
       <c r="E152" s="1" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="G152" s="1"/>
       <c r="H152" s="1"/>
@@ -62071,7 +62064,7 @@
       <c r="K152" s="1"/>
       <c r="L152" s="1"/>
       <c r="M152" s="4" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="153" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -62080,19 +62073,19 @@
         <v>Gin Basil Smash</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="E153" s="4" t="s">
+        <v>795</v>
+      </c>
+      <c r="F153" s="1" t="s">
         <v>796</v>
-      </c>
-      <c r="F153" s="1" t="s">
-        <v>797</v>
       </c>
       <c r="G153" s="1"/>
       <c r="H153" s="1"/>
@@ -62109,28 +62102,28 @@
       </c>
       <c r="B154" s="1"/>
       <c r="C154" s="4" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="D154" s="26" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="E154" s="1" t="s">
+        <v>784</v>
+      </c>
+      <c r="F154" s="5" t="s">
         <v>785</v>
-      </c>
-      <c r="F154" s="5" t="s">
-        <v>786</v>
       </c>
       <c r="G154" s="5"/>
       <c r="H154" s="1"/>
       <c r="I154" s="5"/>
       <c r="J154" s="1" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="K154" s="5" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="L154" s="26" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="M154" s="1"/>
     </row>
@@ -62140,10 +62133,10 @@
         <v>Medias de Seda</v>
       </c>
       <c r="B155" s="4" t="s">
+        <v>800</v>
+      </c>
+      <c r="C155" s="4" t="s">
         <v>801</v>
-      </c>
-      <c r="C155" s="4" t="s">
-        <v>802</v>
       </c>
       <c r="D155" s="4"/>
       <c r="E155" s="1"/>
@@ -62162,17 +62155,17 @@
         <v>Brandy Sour</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="D156" s="4"/>
       <c r="E156" s="1" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="G156" s="5"/>
       <c r="H156" s="1"/>
@@ -62188,19 +62181,19 @@
         <v>Juanito Rosado</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="G157" s="1"/>
       <c r="H157" s="1"/>
@@ -62216,17 +62209,17 @@
         <v>Vino Navegado</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="D158" s="10"/>
       <c r="E158" s="1" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="G158" s="1"/>
       <c r="H158" s="1"/>
@@ -62235,7 +62228,7 @@
       <c r="K158" s="1"/>
       <c r="L158" s="1"/>
       <c r="M158" s="10" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
     </row>
     <row r="159" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62244,32 +62237,32 @@
         <v>Cola de Mono</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="G159" s="5"/>
       <c r="H159" s="1" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="I159" s="10" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="J159" s="1"/>
       <c r="K159" s="1"/>
       <c r="L159" s="1"/>
       <c r="M159" s="4" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="160" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62278,22 +62271,22 @@
         <v>Chichón</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="E160" s="1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="F160" s="5" t="s">
         <v>1023</v>
       </c>
-      <c r="F160" s="5" t="s">
-        <v>1024</v>
-      </c>
       <c r="G160" s="4" t="s">
-        <v>1022</v>
+        <v>1021</v>
       </c>
       <c r="H160" s="1"/>
       <c r="I160" s="5"/>
@@ -62301,7 +62294,7 @@
       <c r="K160" s="1"/>
       <c r="L160" s="1"/>
       <c r="M160" s="4" t="s">
-        <v>1029</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="161" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -62310,10 +62303,10 @@
         <v>Ramos Fizz</v>
       </c>
       <c r="B161" s="4" t="s">
+        <v>841</v>
+      </c>
+      <c r="C161" s="4" t="s">
         <v>842</v>
-      </c>
-      <c r="C161" s="4" t="s">
-        <v>843</v>
       </c>
       <c r="D161" s="4"/>
       <c r="E161" s="1"/>
@@ -62332,17 +62325,17 @@
         <v>Gin Fizz</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="D162" s="4"/>
       <c r="E162" s="1" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="G162" s="5"/>
       <c r="H162" s="5"/>
@@ -62359,16 +62352,16 @@
       </c>
       <c r="B163" s="1"/>
       <c r="C163" s="4" t="s">
+        <v>854</v>
+      </c>
+      <c r="D163" s="4" t="s">
+        <v>853</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>856</v>
+      </c>
+      <c r="F163" s="5" t="s">
         <v>855</v>
-      </c>
-      <c r="D163" s="4" t="s">
-        <v>854</v>
-      </c>
-      <c r="E163" s="1" t="s">
-        <v>857</v>
-      </c>
-      <c r="F163" s="5" t="s">
-        <v>856</v>
       </c>
       <c r="G163" s="5"/>
       <c r="H163" s="1"/>
@@ -62377,7 +62370,7 @@
       <c r="K163" s="1"/>
       <c r="L163" s="1"/>
       <c r="M163" s="4" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="164" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62387,29 +62380,29 @@
       </c>
       <c r="B164" s="4"/>
       <c r="C164" s="4" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="G164" s="5"/>
       <c r="H164" s="1"/>
       <c r="I164" s="5"/>
       <c r="J164" s="1" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="K164" s="1" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="L164" s="1"/>
       <c r="M164" s="4" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
     </row>
     <row r="165" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62418,22 +62411,22 @@
         <v>Pihuelo</v>
       </c>
       <c r="B165" s="4" t="s">
+        <v>870</v>
+      </c>
+      <c r="C165" s="4" t="s">
         <v>871</v>
       </c>
-      <c r="C165" s="4" t="s">
-        <v>872</v>
-      </c>
       <c r="D165" s="4" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="E165" s="4" t="s">
+        <v>1033</v>
+      </c>
+      <c r="F165" s="5" t="s">
         <v>1034</v>
       </c>
-      <c r="F165" s="5" t="s">
+      <c r="G165" s="1" t="s">
         <v>1035</v>
-      </c>
-      <c r="G165" s="1" t="s">
-        <v>1036</v>
       </c>
       <c r="H165" s="1"/>
       <c r="I165" s="5"/>
@@ -62441,7 +62434,7 @@
       <c r="K165" s="1"/>
       <c r="L165" s="1"/>
       <c r="M165" s="4" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="166" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62450,19 +62443,19 @@
         <v>Mojito Sandía</v>
       </c>
       <c r="B166" s="4" t="s">
+        <v>882</v>
+      </c>
+      <c r="C166" s="4" t="s">
         <v>883</v>
       </c>
-      <c r="C166" s="4" t="s">
-        <v>884</v>
-      </c>
       <c r="D166" s="4" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="E166" s="1" t="s">
+        <v>880</v>
+      </c>
+      <c r="F166" s="5" t="s">
         <v>881</v>
-      </c>
-      <c r="F166" s="5" t="s">
-        <v>882</v>
       </c>
       <c r="G166" s="5"/>
       <c r="H166" s="1"/>
@@ -62471,7 +62464,7 @@
       <c r="K166" s="1"/>
       <c r="L166" s="1"/>
       <c r="M166" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
     </row>
     <row r="167" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62481,7 +62474,7 @@
       </c>
       <c r="B167" s="1"/>
       <c r="C167" s="4" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="D167" s="4"/>
       <c r="E167" s="1"/>
@@ -62493,7 +62486,7 @@
       <c r="K167" s="1"/>
       <c r="L167" s="1"/>
       <c r="M167" s="4" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="168" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -62503,7 +62496,7 @@
       </c>
       <c r="B168" s="1"/>
       <c r="C168" s="4" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="D168" s="4"/>
       <c r="E168" s="1"/>
@@ -62515,7 +62508,7 @@
       <c r="K168" s="1"/>
       <c r="L168" s="1"/>
       <c r="M168" s="4" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="169" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -62524,10 +62517,10 @@
         <v>Chardonnay Sour</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="D169" s="4"/>
       <c r="E169" s="1"/>
@@ -62546,19 +62539,19 @@
         <v>Carmenere Sour</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="G170" s="1"/>
       <c r="H170" s="1"/>
@@ -62567,7 +62560,7 @@
       <c r="K170" s="1"/>
       <c r="L170" s="1"/>
       <c r="M170" s="4" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
     </row>
     <row r="171" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62576,13 +62569,13 @@
         <v>Jerez Sour</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="E171" s="1"/>
       <c r="F171" s="1"/>
@@ -62593,7 +62586,7 @@
       <c r="K171" s="1"/>
       <c r="L171" s="1"/>
       <c r="M171" s="4" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="172" spans="1:13" x14ac:dyDescent="0.25">
@@ -64050,61 +64043,60 @@
     <hyperlink ref="I63" r:id="rId26" xr:uid="{42834E67-7A35-4EA1-AD87-66249C0E7460}"/>
     <hyperlink ref="F59" r:id="rId27" xr:uid="{4F9542BD-7BD3-436E-8F7D-8129456254A0}"/>
     <hyperlink ref="I17" r:id="rId28" xr:uid="{6B30F263-7BC5-45CD-813B-273E951F9DD5}"/>
-    <hyperlink ref="I28" r:id="rId29" xr:uid="{3C78B1C2-904E-4657-BDF8-8F9F51757BD2}"/>
-    <hyperlink ref="I43" r:id="rId30" xr:uid="{97B90A8F-880F-476C-AE70-F5520CEE28BE}"/>
-    <hyperlink ref="I50" r:id="rId31" xr:uid="{505C68DA-9360-425D-A4C6-00CCBD9804FE}"/>
-    <hyperlink ref="I123" r:id="rId32" xr:uid="{177A866F-431B-4D06-912E-758AA32E2DBB}"/>
-    <hyperlink ref="I119" r:id="rId33" xr:uid="{2CC1FD11-45F7-4E90-8180-4808569A466E}"/>
-    <hyperlink ref="I72" r:id="rId34" xr:uid="{716EB464-A291-40E8-95EF-4C1BEB94A9E9}"/>
-    <hyperlink ref="F117" r:id="rId35" xr:uid="{6A2CA4F1-AB09-430D-9DDC-D0B22E47A043}"/>
-    <hyperlink ref="F71" r:id="rId36" xr:uid="{A0310311-45B1-42AB-B4D5-454C1A2F857A}"/>
-    <hyperlink ref="F104" r:id="rId37" xr:uid="{5F1FE064-20CD-4CD0-BFCD-2A29DCE05378}"/>
-    <hyperlink ref="F50" r:id="rId38" xr:uid="{B9029BDE-2CF2-4C7F-8412-0C40AE11F68F}"/>
-    <hyperlink ref="F112" r:id="rId39" xr:uid="{9D0D4CC8-CC22-44E2-B264-DD6DC0AAB856}"/>
-    <hyperlink ref="F118" r:id="rId40" xr:uid="{D0F5E38C-8D61-4A45-9420-0674EA07BF30}"/>
-    <hyperlink ref="F38" r:id="rId41" xr:uid="{262EA65B-7E4E-40E7-83C0-33F10D141492}"/>
-    <hyperlink ref="I108" r:id="rId42" xr:uid="{D354F0C5-47C3-4AC8-89C3-72A923D81147}"/>
-    <hyperlink ref="F143" r:id="rId43" xr:uid="{F8159653-E06F-48AC-B06F-F96FF8FAC6FB}"/>
-    <hyperlink ref="F22" r:id="rId44" xr:uid="{D5C24302-111F-4DD4-B671-45B434C1F272}"/>
-    <hyperlink ref="F37" r:id="rId45" xr:uid="{BC8299D9-94A5-4297-8A97-2305D757D1DF}"/>
-    <hyperlink ref="F110" r:id="rId46" xr:uid="{D9F12F69-7825-432C-8F17-8179F5ACB838}"/>
-    <hyperlink ref="F90" r:id="rId47" xr:uid="{05CA1CBC-8ECD-4A48-9B49-7B0A090F5B0A}"/>
-    <hyperlink ref="F48" r:id="rId48" xr:uid="{5B202746-9CD3-4DEA-86F6-B02FBFECC9BD}"/>
-    <hyperlink ref="F141" r:id="rId49" xr:uid="{75E0E620-EEE7-456F-8B1D-E144584094F6}"/>
-    <hyperlink ref="F91" r:id="rId50" xr:uid="{FAD199C6-5901-4269-B73C-7936FE7D51A0}"/>
-    <hyperlink ref="F148" r:id="rId51" xr:uid="{A5AAC270-3690-4B95-8FC8-A8FD0A109532}"/>
-    <hyperlink ref="F32" r:id="rId52" xr:uid="{04E04D75-704C-4FE6-A3DA-E28677DD7E74}"/>
-    <hyperlink ref="F147" r:id="rId53" xr:uid="{DEED7687-3797-41E5-8622-295B72CFDA25}"/>
-    <hyperlink ref="I74" r:id="rId54" xr:uid="{92BCF14D-68BF-4577-A968-400B7094B7EC}"/>
-    <hyperlink ref="F49" r:id="rId55" xr:uid="{2147548B-F6F7-4EB8-9101-1DF8578426C8}"/>
-    <hyperlink ref="K154" r:id="rId56" xr:uid="{159A8B66-145C-4FBD-93E9-54444710C298}"/>
-    <hyperlink ref="F78" r:id="rId57" xr:uid="{160BFB4E-F52C-4586-9551-1CC63AFC8DC9}"/>
-    <hyperlink ref="K78" r:id="rId58" xr:uid="{9CF2EC77-5892-4BF7-8320-49B85E7226D1}"/>
-    <hyperlink ref="F156" r:id="rId59" xr:uid="{E88376AE-94E5-45C8-B9C6-C745DAA369F1}"/>
-    <hyperlink ref="M158" r:id="rId60" display="https://blogger.googleusercontent.com/img/b/R29vZ2xl/AVvXsEgo9MT1901v1qHy4lzjVuGMhhUkNsOHrn2_qd_JQYznroS1AvlrM1oWLC4_YQA0e4SXQa-PTptjibmZC7gGZsFz_fzaFzkBvhgvXAzOB4F4L2Cf4pEZ211OR3aIufsSPMQg526vHvJ3Csc/s1600/vino-navegado_pati-aguilera.jpg_x000a_Créditos: Ilustración de Pati Aguilera y Fito Holloway (AJíCOLOR)" xr:uid="{436ED537-67EF-4A46-B4F4-10BD6ADA7FCC}"/>
-    <hyperlink ref="F159" r:id="rId61" xr:uid="{5E921682-2244-4A8F-895D-0E726F507E4B}"/>
-    <hyperlink ref="F162" r:id="rId62" xr:uid="{EF657F86-A49C-4DF5-9318-9BE891FDC415}"/>
-    <hyperlink ref="F163" r:id="rId63" xr:uid="{8B571519-9B2E-4DBD-AB73-A1220F412D75}"/>
-    <hyperlink ref="F125" r:id="rId64" xr:uid="{B8E5BCD6-A355-47CC-A5DA-2F0E1F25AE0F}"/>
-    <hyperlink ref="F61" r:id="rId65" xr:uid="{24079934-3DB4-47C7-A4F6-EB34761E8517}"/>
-    <hyperlink ref="I40" r:id="rId66" xr:uid="{18514F5E-18F5-44D8-BD76-F70D6B1E8FC6}"/>
-    <hyperlink ref="I135" r:id="rId67" xr:uid="{6B3689A7-4101-496D-821F-20A52B38FF72}"/>
-    <hyperlink ref="F16" r:id="rId68" xr:uid="{816C87E7-4A29-4F45-8BD1-D79076FE292E}"/>
-    <hyperlink ref="F97" r:id="rId69" xr:uid="{B4B59D4D-272B-4AEE-820B-4D18D5925638}"/>
-    <hyperlink ref="F31" r:id="rId70" xr:uid="{295A8609-0926-4F9B-85D6-EFECD8ABD350}"/>
-    <hyperlink ref="F160" r:id="rId71" xr:uid="{4AF06AA3-B56D-4EF1-A3DA-0A54500AAB46}"/>
-    <hyperlink ref="K140" r:id="rId72" xr:uid="{2AAF686C-BD90-49C7-BF1A-AD5D0EEB2ADE}"/>
-    <hyperlink ref="F140" r:id="rId73" xr:uid="{40736A97-19E9-43FF-9714-87C9BEC14957}"/>
-    <hyperlink ref="K144" r:id="rId74" xr:uid="{53B80412-D30A-4E61-B7C0-84FAEE3C9B8F}"/>
-    <hyperlink ref="I144" r:id="rId75" xr:uid="{51307B8A-9D3C-440A-95F6-7FAB063FC58B}"/>
-    <hyperlink ref="F165" r:id="rId76" xr:uid="{31D85646-B6D0-4064-847B-6A91577D6D6C}"/>
-    <hyperlink ref="K46" r:id="rId77" xr:uid="{BD04903A-05E0-4F1C-B9C8-226D01E9B9F0}"/>
-    <hyperlink ref="F137" r:id="rId78" xr:uid="{5F4B6BA8-9C2D-4FA6-9E30-3405A5456BC9}"/>
-    <hyperlink ref="F106" r:id="rId79" xr:uid="{ABCFAB17-7667-4D61-879E-A320868B2202}"/>
-    <hyperlink ref="I106" r:id="rId80" xr:uid="{4BF12877-B808-4EA1-A6A9-B6AAB5F55B13}"/>
+    <hyperlink ref="I43" r:id="rId29" xr:uid="{97B90A8F-880F-476C-AE70-F5520CEE28BE}"/>
+    <hyperlink ref="I50" r:id="rId30" xr:uid="{505C68DA-9360-425D-A4C6-00CCBD9804FE}"/>
+    <hyperlink ref="I123" r:id="rId31" xr:uid="{177A866F-431B-4D06-912E-758AA32E2DBB}"/>
+    <hyperlink ref="I119" r:id="rId32" xr:uid="{2CC1FD11-45F7-4E90-8180-4808569A466E}"/>
+    <hyperlink ref="I72" r:id="rId33" xr:uid="{716EB464-A291-40E8-95EF-4C1BEB94A9E9}"/>
+    <hyperlink ref="F117" r:id="rId34" xr:uid="{6A2CA4F1-AB09-430D-9DDC-D0B22E47A043}"/>
+    <hyperlink ref="F71" r:id="rId35" xr:uid="{A0310311-45B1-42AB-B4D5-454C1A2F857A}"/>
+    <hyperlink ref="F104" r:id="rId36" xr:uid="{5F1FE064-20CD-4CD0-BFCD-2A29DCE05378}"/>
+    <hyperlink ref="F50" r:id="rId37" xr:uid="{B9029BDE-2CF2-4C7F-8412-0C40AE11F68F}"/>
+    <hyperlink ref="F112" r:id="rId38" xr:uid="{9D0D4CC8-CC22-44E2-B264-DD6DC0AAB856}"/>
+    <hyperlink ref="F118" r:id="rId39" xr:uid="{D0F5E38C-8D61-4A45-9420-0674EA07BF30}"/>
+    <hyperlink ref="F38" r:id="rId40" xr:uid="{262EA65B-7E4E-40E7-83C0-33F10D141492}"/>
+    <hyperlink ref="I108" r:id="rId41" xr:uid="{D354F0C5-47C3-4AC8-89C3-72A923D81147}"/>
+    <hyperlink ref="F143" r:id="rId42" xr:uid="{F8159653-E06F-48AC-B06F-F96FF8FAC6FB}"/>
+    <hyperlink ref="F22" r:id="rId43" xr:uid="{D5C24302-111F-4DD4-B671-45B434C1F272}"/>
+    <hyperlink ref="F37" r:id="rId44" xr:uid="{BC8299D9-94A5-4297-8A97-2305D757D1DF}"/>
+    <hyperlink ref="F110" r:id="rId45" xr:uid="{D9F12F69-7825-432C-8F17-8179F5ACB838}"/>
+    <hyperlink ref="F90" r:id="rId46" xr:uid="{05CA1CBC-8ECD-4A48-9B49-7B0A090F5B0A}"/>
+    <hyperlink ref="F48" r:id="rId47" xr:uid="{5B202746-9CD3-4DEA-86F6-B02FBFECC9BD}"/>
+    <hyperlink ref="F141" r:id="rId48" xr:uid="{75E0E620-EEE7-456F-8B1D-E144584094F6}"/>
+    <hyperlink ref="F91" r:id="rId49" xr:uid="{FAD199C6-5901-4269-B73C-7936FE7D51A0}"/>
+    <hyperlink ref="F148" r:id="rId50" xr:uid="{A5AAC270-3690-4B95-8FC8-A8FD0A109532}"/>
+    <hyperlink ref="F32" r:id="rId51" xr:uid="{04E04D75-704C-4FE6-A3DA-E28677DD7E74}"/>
+    <hyperlink ref="F147" r:id="rId52" xr:uid="{DEED7687-3797-41E5-8622-295B72CFDA25}"/>
+    <hyperlink ref="I74" r:id="rId53" xr:uid="{92BCF14D-68BF-4577-A968-400B7094B7EC}"/>
+    <hyperlink ref="F49" r:id="rId54" xr:uid="{2147548B-F6F7-4EB8-9101-1DF8578426C8}"/>
+    <hyperlink ref="K154" r:id="rId55" xr:uid="{159A8B66-145C-4FBD-93E9-54444710C298}"/>
+    <hyperlink ref="F78" r:id="rId56" xr:uid="{160BFB4E-F52C-4586-9551-1CC63AFC8DC9}"/>
+    <hyperlink ref="K78" r:id="rId57" xr:uid="{9CF2EC77-5892-4BF7-8320-49B85E7226D1}"/>
+    <hyperlink ref="F156" r:id="rId58" xr:uid="{E88376AE-94E5-45C8-B9C6-C745DAA369F1}"/>
+    <hyperlink ref="M158" r:id="rId59" display="https://blogger.googleusercontent.com/img/b/R29vZ2xl/AVvXsEgo9MT1901v1qHy4lzjVuGMhhUkNsOHrn2_qd_JQYznroS1AvlrM1oWLC4_YQA0e4SXQa-PTptjibmZC7gGZsFz_fzaFzkBvhgvXAzOB4F4L2Cf4pEZ211OR3aIufsSPMQg526vHvJ3Csc/s1600/vino-navegado_pati-aguilera.jpg_x000a_Créditos: Ilustración de Pati Aguilera y Fito Holloway (AJíCOLOR)" xr:uid="{436ED537-67EF-4A46-B4F4-10BD6ADA7FCC}"/>
+    <hyperlink ref="F159" r:id="rId60" xr:uid="{5E921682-2244-4A8F-895D-0E726F507E4B}"/>
+    <hyperlink ref="F162" r:id="rId61" xr:uid="{EF657F86-A49C-4DF5-9318-9BE891FDC415}"/>
+    <hyperlink ref="F163" r:id="rId62" xr:uid="{8B571519-9B2E-4DBD-AB73-A1220F412D75}"/>
+    <hyperlink ref="F125" r:id="rId63" xr:uid="{B8E5BCD6-A355-47CC-A5DA-2F0E1F25AE0F}"/>
+    <hyperlink ref="F61" r:id="rId64" xr:uid="{24079934-3DB4-47C7-A4F6-EB34761E8517}"/>
+    <hyperlink ref="I40" r:id="rId65" xr:uid="{18514F5E-18F5-44D8-BD76-F70D6B1E8FC6}"/>
+    <hyperlink ref="I135" r:id="rId66" xr:uid="{6B3689A7-4101-496D-821F-20A52B38FF72}"/>
+    <hyperlink ref="F16" r:id="rId67" xr:uid="{816C87E7-4A29-4F45-8BD1-D79076FE292E}"/>
+    <hyperlink ref="F97" r:id="rId68" xr:uid="{B4B59D4D-272B-4AEE-820B-4D18D5925638}"/>
+    <hyperlink ref="F31" r:id="rId69" xr:uid="{295A8609-0926-4F9B-85D6-EFECD8ABD350}"/>
+    <hyperlink ref="F160" r:id="rId70" xr:uid="{4AF06AA3-B56D-4EF1-A3DA-0A54500AAB46}"/>
+    <hyperlink ref="K140" r:id="rId71" xr:uid="{2AAF686C-BD90-49C7-BF1A-AD5D0EEB2ADE}"/>
+    <hyperlink ref="F140" r:id="rId72" xr:uid="{40736A97-19E9-43FF-9714-87C9BEC14957}"/>
+    <hyperlink ref="K144" r:id="rId73" xr:uid="{53B80412-D30A-4E61-B7C0-84FAEE3C9B8F}"/>
+    <hyperlink ref="I144" r:id="rId74" xr:uid="{51307B8A-9D3C-440A-95F6-7FAB063FC58B}"/>
+    <hyperlink ref="F165" r:id="rId75" xr:uid="{31D85646-B6D0-4064-847B-6A91577D6D6C}"/>
+    <hyperlink ref="K46" r:id="rId76" xr:uid="{BD04903A-05E0-4F1C-B9C8-226D01E9B9F0}"/>
+    <hyperlink ref="F137" r:id="rId77" xr:uid="{5F4B6BA8-9C2D-4FA6-9E30-3405A5456BC9}"/>
+    <hyperlink ref="F106" r:id="rId78" xr:uid="{ABCFAB17-7667-4D61-879E-A320868B2202}"/>
+    <hyperlink ref="I106" r:id="rId79" xr:uid="{4BF12877-B808-4EA1-A6A9-B6AAB5F55B13}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId81"/>
+  <pageSetup orientation="portrait" r:id="rId80"/>
 </worksheet>
 </file>
 
@@ -64133,10 +64125,10 @@
         <v>62</v>
       </c>
       <c r="B2" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C2" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -64144,7 +64136,7 @@
         <v>67</v>
       </c>
       <c r="B3" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C3" t="s">
         <v>202</v>
@@ -64155,10 +64147,10 @@
         <v>68</v>
       </c>
       <c r="B4" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C4" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -64166,7 +64158,7 @@
         <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C5" t="s">
         <v>203</v>
@@ -64177,10 +64169,10 @@
         <v>69</v>
       </c>
       <c r="B6" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C6" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -64188,7 +64180,7 @@
         <v>70</v>
       </c>
       <c r="B7" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C7" t="s">
         <v>71</v>
@@ -64196,24 +64188,24 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="B8" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="C8" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>809</v>
+      </c>
+      <c r="B9" t="s">
         <v>810</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>811</v>
-      </c>
-      <c r="C9" t="s">
-        <v>812</v>
       </c>
     </row>
   </sheetData>
@@ -64243,7 +64235,7 @@
         <v>115</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -64251,7 +64243,7 @@
         <v>116</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -64259,7 +64251,7 @@
         <v>117</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -64267,7 +64259,7 @@
         <v>118</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -64275,7 +64267,7 @@
         <v>119</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -64283,7 +64275,7 @@
         <v>120</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -64291,31 +64283,31 @@
         <v>215</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="23" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="23" t="s">
+        <v>703</v>
+      </c>
+      <c r="B11" s="23" t="s">
         <v>704</v>
-      </c>
-      <c r="B11" s="23" t="s">
-        <v>705</v>
       </c>
     </row>
   </sheetData>

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6B8AD8B7-9EB4-4F82-A28F-F3C227C8A7DE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8253A68F-948A-4030-BA60-B1E18AF6B348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1601" uniqueCount="1058">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1603" uniqueCount="1060">
   <si>
     <t>Ramazzotti Spritz</t>
   </si>
@@ -4955,6 +4955,12 @@
 ¡Que tenga sed en todos los caminos
 la paloma que olvidó a su amado!
 Extraído de: José María Arguedas, Cantos y cuentos quechuas I. Municipalidad de Lima Metropolitana, Secretaría de Educación y Cultura, 1986.</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=eOs1cfRq1xg</t>
+  </si>
+  <si>
+    <t>Illapu - Volarás</t>
   </si>
 </sst>
 </file>
@@ -58867,8 +58873,12 @@
       <c r="F28" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="G28" s="5"/>
-      <c r="H28" s="1"/>
+      <c r="G28" s="5" t="s">
+        <v>1059</v>
+      </c>
+      <c r="H28" s="5" t="s">
+        <v>1058</v>
+      </c>
       <c r="I28" s="5"/>
       <c r="J28" s="1"/>
       <c r="K28" s="5"/>
@@ -64094,9 +64104,10 @@
     <hyperlink ref="F137" r:id="rId77" xr:uid="{5F4B6BA8-9C2D-4FA6-9E30-3405A5456BC9}"/>
     <hyperlink ref="F106" r:id="rId78" xr:uid="{ABCFAB17-7667-4D61-879E-A320868B2202}"/>
     <hyperlink ref="I106" r:id="rId79" xr:uid="{4BF12877-B808-4EA1-A6A9-B6AAB5F55B13}"/>
+    <hyperlink ref="H28" r:id="rId80" xr:uid="{CF92F393-7C11-4EA1-8FBE-00184A72008E}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId80"/>
+  <pageSetup orientation="portrait" r:id="rId81"/>
 </worksheet>
 </file>
 

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8253A68F-948A-4030-BA60-B1E18AF6B348}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58219253-99C1-4B78-87F3-89B31BCDA824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
@@ -58873,15 +58873,15 @@
       <c r="F28" s="1" t="s">
         <v>528</v>
       </c>
-      <c r="G28" s="5" t="s">
+      <c r="G28" s="5"/>
+      <c r="H28" s="5"/>
+      <c r="I28" s="5"/>
+      <c r="J28" s="1" t="s">
         <v>1059</v>
       </c>
-      <c r="H28" s="5" t="s">
+      <c r="K28" s="5" t="s">
         <v>1058</v>
       </c>
-      <c r="I28" s="5"/>
-      <c r="J28" s="1"/>
-      <c r="K28" s="5"/>
       <c r="L28" s="5"/>
       <c r="M28" s="4" t="s">
         <v>923</v>
@@ -64104,7 +64104,7 @@
     <hyperlink ref="F137" r:id="rId77" xr:uid="{5F4B6BA8-9C2D-4FA6-9E30-3405A5456BC9}"/>
     <hyperlink ref="F106" r:id="rId78" xr:uid="{ABCFAB17-7667-4D61-879E-A320868B2202}"/>
     <hyperlink ref="I106" r:id="rId79" xr:uid="{4BF12877-B808-4EA1-A6A9-B6AAB5F55B13}"/>
-    <hyperlink ref="H28" r:id="rId80" xr:uid="{CF92F393-7C11-4EA1-8FBE-00184A72008E}"/>
+    <hyperlink ref="K28" r:id="rId80" xr:uid="{EABE5019-2D6E-4A59-9FC0-4DBF379C5B0C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId81"/>

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58219253-99C1-4B78-87F3-89B31BCDA824}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2B2E43B-8F41-4D25-8150-360143409D44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1603" uniqueCount="1060">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1607" uniqueCount="1064">
   <si>
     <t>Ramazzotti Spritz</t>
   </si>
@@ -4612,10 +4612,6 @@
     <t>Lo que no te perdono/es haberme besado con tanta alevosía./Tengo testigos: un perro, la madrugada, el frío,/y eso sí que no te lo perdono,/pues si te lo perdono seguro que lo olvido.</t>
   </si>
   <si>
-    <t>aperol.jpg
-Afiche vintage del Aperol Spritz</t>
-  </si>
-  <si>
     <t>camillo-negroni.jpg
 El Conde Camillo Negroni, noble italiano del siglo XIX y principios del XX.</t>
   </si>
@@ -4961,6 +4957,26 @@
   </si>
   <si>
     <t>Illapu - Volarás</t>
+  </si>
+  <si>
+    <t>cynar.jpg
+Afiche publicitario del amaro italiano Cynar, un aperitivo elaborado a base de alcachofa y una mezcla de hierbas y plantas aromáticas.</t>
+  </si>
+  <si>
+    <t>STG.jpg
+Imagen publicitaria del licor St Germain.</t>
+  </si>
+  <si>
+    <t>chambord.jpg
+Imagen publicitaria del licor Chambord.</t>
+  </si>
+  <si>
+    <t>whitelady.jpg
+Ilustración contemporánea inspirada en el cóctel White Lady.</t>
+  </si>
+  <si>
+    <t>aperol.jpg
+Ilustración publicitaria inspirada en el Aperol Spritz.</t>
   </si>
 </sst>
 </file>
@@ -58372,7 +58388,7 @@
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="4" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -58446,7 +58462,7 @@
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="4" t="s">
-        <v>974</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58494,7 +58510,7 @@
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="4" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58546,7 +58562,7 @@
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="4" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -58650,7 +58666,7 @@
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="4" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -58750,7 +58766,7 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="4" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="345" x14ac:dyDescent="0.25">
@@ -58798,7 +58814,7 @@
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="4" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58826,7 +58842,7 @@
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="4" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="375" x14ac:dyDescent="0.25">
@@ -58852,7 +58868,7 @@
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="4" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58865,7 +58881,7 @@
         <v>458</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>529</v>
@@ -58877,10 +58893,10 @@
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
       <c r="J28" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="L28" s="5"/>
       <c r="M28" s="4" t="s">
@@ -58954,13 +58970,13 @@
         <v>425</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="F31" s="5" t="s">
+        <v>1002</v>
+      </c>
+      <c r="G31" s="4" t="s">
         <v>1003</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>1004</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -58968,7 +58984,7 @@
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="4" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -59050,7 +59066,7 @@
       <c r="K34" s="5"/>
       <c r="L34" s="5"/>
       <c r="M34" s="4" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -59148,10 +59164,10 @@
       <c r="K38" s="5"/>
       <c r="L38" s="5"/>
       <c r="M38" s="4" t="s">
-        <v>993</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+        <v>992</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="str">
         <f>IF(receta!A39="","",receta!A39)</f>
         <v>Cynar Spritz</v>
@@ -59169,7 +59185,9 @@
       <c r="J39" s="1"/>
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
-      <c r="M39" s="1"/>
+      <c r="M39" s="4" t="s">
+        <v>1059</v>
+      </c>
     </row>
     <row r="40" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="str">
@@ -59221,7 +59239,9 @@
       <c r="J41" s="1"/>
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
-      <c r="M41" s="1"/>
+      <c r="M41" s="4" t="s">
+        <v>1062</v>
+      </c>
     </row>
     <row r="42" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="str">
@@ -59320,7 +59340,7 @@
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
       <c r="M45" s="4" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="285" x14ac:dyDescent="0.25">
@@ -59333,7 +59353,7 @@
       </c>
       <c r="C46" s="4"/>
       <c r="D46" s="4" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>185</v>
@@ -59345,16 +59365,16 @@
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
       <c r="J46" s="4" t="s">
+        <v>1036</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>1035</v>
+      </c>
+      <c r="L46" s="4" t="s">
         <v>1037</v>
       </c>
-      <c r="K46" s="5" t="s">
-        <v>1036</v>
-      </c>
-      <c r="L46" s="4" t="s">
-        <v>1038</v>
-      </c>
       <c r="M46" s="4" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -59430,7 +59450,7 @@
         <v>771</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -59438,7 +59458,7 @@
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
       <c r="M49" s="4" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="255" x14ac:dyDescent="0.25">
@@ -59458,7 +59478,7 @@
         <v>482</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>326</v>
@@ -59546,7 +59566,7 @@
         <v>404</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>384</v>
@@ -59558,7 +59578,7 @@
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="4" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59630,7 +59650,7 @@
         <v>473</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -59742,7 +59762,7 @@
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
       <c r="M60" s="4" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="165" x14ac:dyDescent="0.25">
@@ -59796,7 +59816,7 @@
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
       <c r="M62" s="4" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59854,7 +59874,7 @@
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
       <c r="M64" s="4" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59901,7 +59921,9 @@
       <c r="J66" s="1"/>
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
-      <c r="M66" s="1"/>
+      <c r="M66" s="4" t="s">
+        <v>1060</v>
+      </c>
     </row>
     <row r="67" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="str">
@@ -60141,7 +60163,9 @@
       <c r="J75" s="1"/>
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
-      <c r="M75" s="1"/>
+      <c r="M75" s="4" t="s">
+        <v>1061</v>
+      </c>
     </row>
     <row r="76" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="str">
@@ -60176,10 +60200,10 @@
       </c>
       <c r="B77" s="1"/>
       <c r="C77" s="4" t="s">
+        <v>1017</v>
+      </c>
+      <c r="D77" s="4" t="s">
         <v>1018</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>1019</v>
       </c>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
@@ -60190,7 +60214,7 @@
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
       <c r="M77" s="4" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="78" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -60360,7 +60384,7 @@
       <c r="K84" s="1"/>
       <c r="L84" s="1"/>
       <c r="M84" s="4" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -60390,7 +60414,7 @@
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
       <c r="M85" s="4" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -60588,7 +60612,7 @@
       <c r="K93" s="1"/>
       <c r="L93" s="1"/>
       <c r="M93" s="4" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="94" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -60632,7 +60656,7 @@
       <c r="K95" s="1"/>
       <c r="L95" s="1"/>
       <c r="M95" s="4" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="96" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -60665,13 +60689,13 @@
         <v>580</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="G97" s="1"/>
       <c r="H97" s="4"/>
@@ -60680,7 +60704,7 @@
       <c r="K97" s="1"/>
       <c r="L97" s="1"/>
       <c r="M97" s="4" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="98" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -60800,7 +60824,7 @@
       <c r="K102" s="1"/>
       <c r="L102" s="1"/>
       <c r="M102" s="4" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="103" spans="1:13" ht="210" x14ac:dyDescent="0.25">
@@ -60822,7 +60846,7 @@
       <c r="K103" s="1"/>
       <c r="L103" s="1"/>
       <c r="M103" s="4" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="104" spans="1:13" ht="345" x14ac:dyDescent="0.25">
@@ -60852,7 +60876,7 @@
       <c r="K104" s="5"/>
       <c r="L104" s="5"/>
       <c r="M104" s="4" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="105" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -60894,25 +60918,25 @@
         <v>565</v>
       </c>
       <c r="E106" s="1" t="s">
+        <v>1042</v>
+      </c>
+      <c r="F106" s="5" t="s">
         <v>1043</v>
       </c>
-      <c r="F106" s="5" t="s">
-        <v>1044</v>
-      </c>
       <c r="G106" s="4" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="I106" s="5" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="J106" s="1"/>
       <c r="K106" s="1"/>
       <c r="L106" s="1"/>
       <c r="M106" s="4" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="107" spans="1:13" ht="192" customHeight="1" x14ac:dyDescent="0.25">
@@ -60960,7 +60984,7 @@
       <c r="K108" s="1"/>
       <c r="L108" s="1"/>
       <c r="M108" s="4" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="109" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -60995,7 +61019,7 @@
         <v>675</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="E110" s="4" t="s">
         <v>585</v>
@@ -61010,7 +61034,7 @@
       <c r="K110" s="5"/>
       <c r="L110" s="5"/>
       <c r="M110" s="4" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.25">
@@ -61178,7 +61202,7 @@
       <c r="K117" s="5"/>
       <c r="L117" s="5"/>
       <c r="M117" s="4" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="118" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -61232,7 +61256,7 @@
       <c r="K119" s="5"/>
       <c r="L119" s="5"/>
       <c r="M119" s="4" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="120" spans="1:13" ht="75" x14ac:dyDescent="0.25">
@@ -61444,7 +61468,7 @@
       <c r="K128" s="1"/>
       <c r="L128" s="1"/>
       <c r="M128" s="4" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="129" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -61534,7 +61558,7 @@
       <c r="K132" s="5"/>
       <c r="L132" s="5"/>
       <c r="M132" s="4" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.25">
@@ -61652,13 +61676,13 @@
         <v>433</v>
       </c>
       <c r="E137" s="1" t="s">
+        <v>1039</v>
+      </c>
+      <c r="F137" s="5" t="s">
+        <v>1038</v>
+      </c>
+      <c r="G137" s="4" t="s">
         <v>1040</v>
-      </c>
-      <c r="F137" s="5" t="s">
-        <v>1039</v>
-      </c>
-      <c r="G137" s="4" t="s">
-        <v>1041</v>
       </c>
       <c r="H137" s="1"/>
       <c r="I137" s="1"/>
@@ -61728,13 +61752,13 @@
         <v>345</v>
       </c>
       <c r="E140" s="1" t="s">
+        <v>1025</v>
+      </c>
+      <c r="F140" s="5" t="s">
+        <v>1024</v>
+      </c>
+      <c r="G140" s="4" t="s">
         <v>1026</v>
-      </c>
-      <c r="F140" s="5" t="s">
-        <v>1025</v>
-      </c>
-      <c r="G140" s="4" t="s">
-        <v>1027</v>
       </c>
       <c r="H140" s="1"/>
       <c r="I140" s="1"/>
@@ -61746,7 +61770,7 @@
       </c>
       <c r="L140" s="5"/>
       <c r="M140" s="4" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="141" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -61851,16 +61875,16 @@
       </c>
       <c r="G144" s="1"/>
       <c r="H144" s="1" t="s">
+        <v>1030</v>
+      </c>
+      <c r="I144" s="5" t="s">
         <v>1031</v>
       </c>
-      <c r="I144" s="5" t="s">
-        <v>1032</v>
-      </c>
       <c r="J144" s="1" t="s">
+        <v>1028</v>
+      </c>
+      <c r="K144" s="5" t="s">
         <v>1029</v>
-      </c>
-      <c r="K144" s="5" t="s">
-        <v>1030</v>
       </c>
       <c r="L144" s="1"/>
       <c r="M144" s="4" t="s">
@@ -61894,7 +61918,7 @@
       <c r="K145" s="1"/>
       <c r="L145" s="1"/>
       <c r="M145" s="4" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="146" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -62074,7 +62098,7 @@
       <c r="K152" s="1"/>
       <c r="L152" s="1"/>
       <c r="M152" s="4" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="153" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -62133,7 +62157,7 @@
         <v>773</v>
       </c>
       <c r="L154" s="26" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="M154" s="1"/>
     </row>
@@ -62287,16 +62311,16 @@
         <v>829</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
       <c r="E160" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="F160" s="5" t="s">
         <v>1022</v>
       </c>
-      <c r="F160" s="5" t="s">
-        <v>1023</v>
-      </c>
       <c r="G160" s="4" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
       <c r="H160" s="1"/>
       <c r="I160" s="5"/>
@@ -62304,7 +62328,7 @@
       <c r="K160" s="1"/>
       <c r="L160" s="1"/>
       <c r="M160" s="4" t="s">
-        <v>1028</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="161" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -62380,7 +62404,7 @@
       <c r="K163" s="1"/>
       <c r="L163" s="1"/>
       <c r="M163" s="4" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="164" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62430,13 +62454,13 @@
         <v>874</v>
       </c>
       <c r="E165" s="4" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F165" s="5" t="s">
         <v>1033</v>
       </c>
-      <c r="F165" s="5" t="s">
+      <c r="G165" s="1" t="s">
         <v>1034</v>
-      </c>
-      <c r="G165" s="1" t="s">
-        <v>1035</v>
       </c>
       <c r="H165" s="1"/>
       <c r="I165" s="5"/>
@@ -62444,7 +62468,7 @@
       <c r="K165" s="1"/>
       <c r="L165" s="1"/>
       <c r="M165" s="4" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="166" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62496,7 +62520,7 @@
       <c r="K167" s="1"/>
       <c r="L167" s="1"/>
       <c r="M167" s="4" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="168" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -62506,7 +62530,7 @@
       </c>
       <c r="B168" s="1"/>
       <c r="C168" s="4" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="D168" s="4"/>
       <c r="E168" s="1"/>
@@ -62518,7 +62542,7 @@
       <c r="K168" s="1"/>
       <c r="L168" s="1"/>
       <c r="M168" s="4" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="169" spans="1:13" ht="120" x14ac:dyDescent="0.25">

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2B2E43B-8F41-4D25-8150-360143409D44}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C08C7AAE-3436-46C5-B90A-A68598CA4C83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
   <sheets>
     <sheet name="receta" sheetId="1" r:id="rId1"/>
@@ -2481,11 +2481,6 @@
 Charly García, en Revista La García, N.º 6, julio de 1999.</t>
   </si>
   <si>
-    <t>El Dama Blanca (en inglés White Lady) es un cóctel clásico, elegante y seco, perteneciente a la familia de los sours y estrechamente emparentado con el Sidecar y el Margarita. Aunque su receta base es simple, se le pueden añadir algunos toques opcionales: clara de huevo, que le aporta una textura sedosa y una ligera espuma en la superficie, y jarabe simple, para suavizar su acidez.
-El White Lady fue creado en la década de 1910 por el legendario bartender Harry MacElhone, inicialmente en el Ciro’s Club de Londres y más tarde en el célebre Harry’s New York Bar de París. La receta original incluía crema de menta blanca, pero fue reformulada poco después, sustituyéndola por gin, dando origen a la versión que conocemos hoy.
-La proporción clásica de sus ingredientes es 2:1:1: dos partes de gin, una parte de licor de naranja (como Cointreau) y una parte de jugo de limón fresco.</t>
-  </si>
-  <si>
     <t>https://www.youtube.com/watch?v=S43YhQ_eGTw</t>
   </si>
   <si>
@@ -4977,6 +4972,11 @@
   <si>
     <t>aperol.jpg
 Ilustración publicitaria inspirada en el Aperol Spritz.</t>
+  </si>
+  <si>
+    <t>El Dama Blanca (en inglés White Lady) es un cóctel clásico, elegante y seco, perteneciente a la familia de los sours y estrechamente emparentado con el Sidecar y el Margarita. Aunque su receta base es simple, se le pueden añadir algunos toques opcionales: clara de huevo, que le aporta una textura sedosa y una ligera espuma en la superficie, y jarabe simple, para suavizar su acidez.
+No existe total certeza sobre su origen, pero suele atribuirse al bartender Harry MacElhone, quien lo habría preparado en el Ciro’s Club de Londres en una versión temprana que incluía crema de menta blanca. Hacia 1929, ya en el Harry’s New York Bar de París, reformuló la receta, sustituyendo este ingrediente por gin, dando origen a la variante que se difundió internacionalmente y que hoy se considera la forma clásica del trago.
+La proporción clásica de sus ingredientes es 2:1:1: dos partes de gin, una parte de licor de naranja (como Cointreau) y una parte de jugo de limón fresco.</t>
   </si>
 </sst>
 </file>
@@ -5654,10 +5654,10 @@
         <v>78</v>
       </c>
       <c r="O1" s="27" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="P1" s="27" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="Q1" s="27" t="s">
         <v>79</v>
@@ -5669,13 +5669,13 @@
         <v>265</v>
       </c>
       <c r="T1" s="27" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="U1" s="27" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="V1" s="27" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="W1" s="27" t="s">
         <v>80</v>
@@ -5690,16 +5690,16 @@
         <v>196</v>
       </c>
       <c r="AA1" s="27" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="AB1" s="27" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="AC1" s="27" t="s">
+        <v>902</v>
+      </c>
+      <c r="AD1" s="27" t="s">
         <v>903</v>
-      </c>
-      <c r="AD1" s="27" t="s">
-        <v>904</v>
       </c>
       <c r="AE1" s="27" t="s">
         <v>82</v>
@@ -5726,7 +5726,7 @@
         <v>87</v>
       </c>
       <c r="AM1" s="27" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AN1" s="27" t="s">
         <v>223</v>
@@ -5753,13 +5753,13 @@
         <v>200</v>
       </c>
       <c r="AV1" s="27" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="AW1" s="27" t="s">
         <v>209</v>
       </c>
       <c r="AX1" s="27" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="AY1" s="27" t="s">
         <v>230</v>
@@ -5849,16 +5849,16 @@
         <v>152</v>
       </c>
       <c r="CB1" s="8" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="CC1" s="8" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="CD1" s="7" t="s">
         <v>280</v>
       </c>
       <c r="CE1" s="7" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="CF1" s="8" t="s">
         <v>198</v>
@@ -5891,10 +5891,10 @@
         <v>215</v>
       </c>
       <c r="CP1" s="8" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="CQ1" s="8" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="CR1" s="7" t="s">
         <v>95</v>
@@ -5906,7 +5906,7 @@
         <v>97</v>
       </c>
       <c r="CU1" s="7" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="CV1" s="7" t="s">
         <v>385</v>
@@ -5915,7 +5915,7 @@
         <v>98</v>
       </c>
       <c r="CX1" s="7" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="CY1" s="7" t="s">
         <v>99</v>
@@ -5930,22 +5930,22 @@
         <v>154</v>
       </c>
       <c r="DC1" s="8" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="DD1" s="18" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="DE1" s="18" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="DF1" s="18" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="DG1" s="18" t="s">
+        <v>845</v>
+      </c>
+      <c r="DH1" s="18" t="s">
         <v>846</v>
-      </c>
-      <c r="DH1" s="18" t="s">
-        <v>847</v>
       </c>
       <c r="DI1" s="15" t="s">
         <v>136</v>
@@ -5954,31 +5954,31 @@
         <v>135</v>
       </c>
       <c r="DK1" s="15" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="DL1" s="15" t="s">
+        <v>568</v>
+      </c>
+      <c r="DM1" s="15" t="s">
         <v>569</v>
       </c>
-      <c r="DM1" s="15" t="s">
-        <v>570</v>
-      </c>
       <c r="DN1" s="15" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="DO1" s="15" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="DP1" s="15" t="s">
+        <v>606</v>
+      </c>
+      <c r="DQ1" s="15" t="s">
+        <v>816</v>
+      </c>
+      <c r="DR1" s="15" t="s">
         <v>607</v>
       </c>
-      <c r="DQ1" s="15" t="s">
-        <v>817</v>
-      </c>
-      <c r="DR1" s="15" t="s">
-        <v>608</v>
-      </c>
       <c r="DS1" s="15" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="DT1" s="15" t="s">
         <v>141</v>
@@ -5987,43 +5987,43 @@
         <v>237</v>
       </c>
       <c r="DV1" s="15" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="DW1" s="15" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="DX1" s="15" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="DY1" s="15" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="DZ1" s="15" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="EA1" s="15" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="EB1" s="21" t="s">
-        <v>560</v>
+        <v>559</v>
       </c>
       <c r="EC1" s="21" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="ED1" s="25" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="EE1" s="12" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="EF1" s="14" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="EG1" s="12" t="s">
         <v>234</v>
       </c>
       <c r="EH1" s="12" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="EI1" s="12" t="s">
         <v>286</v>
@@ -6038,19 +6038,19 @@
         <v>125</v>
       </c>
       <c r="EM1" s="17" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="EN1" s="17" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="EO1" s="17" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="EP1" s="19" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="EQ1" s="19" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="ER1" s="19" t="s">
         <v>126</v>
@@ -6065,7 +6065,7 @@
         <v>231</v>
       </c>
       <c r="EV1" s="20" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="EW1" s="20" t="s">
         <v>232</v>
@@ -7503,13 +7503,13 @@
     </row>
     <row r="10" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>51</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D10" s="2">
         <v>300</v>
@@ -7863,13 +7863,13 @@
     </row>
     <row r="12" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>55</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D12" s="2">
         <v>200</v>
@@ -8571,7 +8571,7 @@
     </row>
     <row r="16" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>278</v>
@@ -9655,7 +9655,7 @@
     </row>
     <row r="22" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>53</v>
@@ -10363,7 +10363,7 @@
     </row>
     <row r="26" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>50</v>
@@ -10541,7 +10541,7 @@
     </row>
     <row r="27" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>51</v>
@@ -11073,7 +11073,7 @@
     </row>
     <row r="30" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>278</v>
@@ -11251,7 +11251,7 @@
     </row>
     <row r="31" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>278</v>
@@ -11429,7 +11429,7 @@
     </row>
     <row r="32" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>278</v>
@@ -11607,7 +11607,7 @@
     </row>
     <row r="33" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>55</v>
@@ -12141,7 +12141,7 @@
     </row>
     <row r="36" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>54</v>
@@ -12317,13 +12317,13 @@
     </row>
     <row r="37" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D37" s="2">
         <v>300</v>
@@ -12499,7 +12499,7 @@
     </row>
     <row r="38" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>50</v>
@@ -14625,7 +14625,7 @@
     </row>
     <row r="50" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>480</v>
+        <v>479</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>53</v>
@@ -14805,7 +14805,7 @@
     </row>
     <row r="51" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>55</v>
@@ -17113,7 +17113,7 @@
     </row>
     <row r="64" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>50</v>
@@ -17469,7 +17469,7 @@
     </row>
     <row r="66" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>49</v>
@@ -18719,10 +18719,10 @@
     </row>
     <row r="73" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>560</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>561</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>562</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>69</v>
@@ -18899,7 +18899,7 @@
     </row>
     <row r="74" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>51</v>
@@ -20151,7 +20151,7 @@
     </row>
     <row r="81" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>51</v>
@@ -20329,7 +20329,7 @@
     </row>
     <row r="82" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>50</v>
@@ -20693,7 +20693,7 @@
     </row>
     <row r="84" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>51</v>
@@ -20869,7 +20869,7 @@
     </row>
     <row r="85" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>51</v>
@@ -21923,10 +21923,10 @@
     </row>
     <row r="91" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>680</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>681</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>682</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>63</v>
@@ -22283,7 +22283,7 @@
     </row>
     <row r="93" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>53</v>
@@ -23173,7 +23173,7 @@
     </row>
     <row r="98" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>49</v>
@@ -24611,7 +24611,7 @@
     </row>
     <row r="106" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>53</v>
@@ -24967,7 +24967,7 @@
     </row>
     <row r="108" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>50</v>
@@ -25335,13 +25335,13 @@
     </row>
     <row r="110" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D110" s="2">
         <v>300</v>
@@ -25515,7 +25515,7 @@
     </row>
     <row r="111" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>50</v>
@@ -26755,7 +26755,7 @@
     </row>
     <row r="118" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>50</v>
@@ -27469,7 +27469,7 @@
     </row>
     <row r="122" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>50</v>
@@ -27999,7 +27999,7 @@
     </row>
     <row r="125" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A125" s="13" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>278</v>
@@ -28183,7 +28183,7 @@
     </row>
     <row r="126" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>278</v>
@@ -28899,7 +28899,7 @@
     </row>
     <row r="130" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>151</v>
@@ -30137,7 +30137,7 @@
     </row>
     <row r="137" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A137" s="13" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>278</v>
@@ -30495,7 +30495,7 @@
     </row>
     <row r="139" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>52</v>
@@ -30857,7 +30857,7 @@
     </row>
     <row r="141" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>55</v>
@@ -31215,7 +31215,7 @@
     </row>
     <row r="143" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>51</v>
@@ -31579,7 +31579,7 @@
     </row>
     <row r="145" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>53</v>
@@ -31931,7 +31931,7 @@
     </row>
     <row r="147" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>51</v>
@@ -32107,7 +32107,7 @@
     </row>
     <row r="148" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>51</v>
@@ -32283,7 +32283,7 @@
     </row>
     <row r="149" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>50</v>
@@ -32637,13 +32637,13 @@
     </row>
     <row r="151" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D151" s="2">
         <v>300</v>
@@ -32817,7 +32817,7 @@
     </row>
     <row r="152" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>53</v>
@@ -32996,13 +32996,13 @@
     </row>
     <row r="153" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D153" s="2">
         <v>300</v>
@@ -33176,7 +33176,7 @@
     </row>
     <row r="154" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>51</v>
@@ -33352,7 +33352,7 @@
     </row>
     <row r="155" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>54</v>
@@ -33528,7 +33528,7 @@
     </row>
     <row r="156" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>53</v>
@@ -33706,7 +33706,7 @@
     </row>
     <row r="157" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>278</v>
@@ -33880,13 +33880,13 @@
     </row>
     <row r="158" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>278</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="D158" s="2">
         <v>1500</v>
@@ -34060,13 +34060,13 @@
     </row>
     <row r="159" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>278</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="D159" s="2">
         <v>1500</v>
@@ -34250,7 +34250,7 @@
     </row>
     <row r="160" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>197</v>
@@ -34422,7 +34422,7 @@
     </row>
     <row r="161" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>51</v>
@@ -34606,7 +34606,7 @@
     </row>
     <row r="162" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>51</v>
@@ -34782,7 +34782,7 @@
     </row>
     <row r="163" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>51</v>
@@ -34962,7 +34962,7 @@
     </row>
     <row r="164" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>53</v>
@@ -35140,7 +35140,7 @@
     </row>
     <row r="165" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>51</v>
@@ -35316,7 +35316,7 @@
     </row>
     <row r="166" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>50</v>
@@ -35498,7 +35498,7 @@
     </row>
     <row r="167" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>53</v>
@@ -35676,7 +35676,7 @@
     </row>
     <row r="168" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>55</v>
@@ -35850,7 +35850,7 @@
     </row>
     <row r="169" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>55</v>
@@ -36028,7 +36028,7 @@
     </row>
     <row r="170" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>53</v>
@@ -36204,7 +36204,7 @@
     </row>
     <row r="171" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>55</v>
@@ -48688,16 +48688,16 @@
         <v>129</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>141</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="J1" s="8" t="s">
         <v>237</v>
@@ -48712,10 +48712,10 @@
         <v>283</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="P1" s="8" t="s">
         <v>132</v>
@@ -48751,7 +48751,7 @@
         <v>131</v>
       </c>
       <c r="AA1" s="7" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="AB1" s="7" t="s">
         <v>199</v>
@@ -58165,7 +58165,7 @@
         <v>72</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>318</v>
@@ -58180,7 +58180,7 @@
         <v>315</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>316</v>
@@ -58189,16 +58189,16 @@
         <v>317</v>
       </c>
       <c r="J1" s="7" t="s">
+        <v>764</v>
+      </c>
+      <c r="K1" s="7" t="s">
         <v>765</v>
       </c>
-      <c r="K1" s="7" t="s">
-        <v>766</v>
-      </c>
       <c r="L1" s="7" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="270" x14ac:dyDescent="0.25">
@@ -58226,7 +58226,7 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="4" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58235,7 +58235,7 @@
         <v>Alejandra</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>366</v>
@@ -58272,7 +58272,7 @@
         <v>239</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="5"/>
@@ -58287,13 +58287,13 @@
         <v>Alexander</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>448</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E5" s="4" t="s">
         <v>365</v>
@@ -58308,7 +58308,7 @@
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
       <c r="M5" s="4" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="270" x14ac:dyDescent="0.25">
@@ -58317,7 +58317,7 @@
         <v>Amaretto Sour</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>352</v>
@@ -58336,7 +58336,7 @@
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="4" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="270" x14ac:dyDescent="0.25">
@@ -58362,7 +58362,7 @@
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="4" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="210" x14ac:dyDescent="0.25">
@@ -58388,7 +58388,7 @@
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="4" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -58416,7 +58416,7 @@
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
       <c r="M9" s="1" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="210" x14ac:dyDescent="0.25">
@@ -58425,10 +58425,10 @@
         <v>Andes Refresh</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="11"/>
@@ -58448,10 +58448,10 @@
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="4" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -58462,7 +58462,7 @@
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="4" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58471,13 +58471,13 @@
         <v>Arándano Sour</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
@@ -58510,7 +58510,7 @@
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="4" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58538,7 +58538,7 @@
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="4" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58548,7 +58548,7 @@
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="4" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D15" s="4" t="s">
         <v>378</v>
@@ -58562,7 +58562,7 @@
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="4" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -58574,13 +58574,13 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -58666,7 +58666,7 @@
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="4" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -58699,10 +58699,10 @@
         <v>Borgoña</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="1"/>
@@ -58718,7 +58718,7 @@
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="4" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="375" x14ac:dyDescent="0.25">
@@ -58727,17 +58727,17 @@
         <v>Caipiriña</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1" t="s">
+        <v>571</v>
+      </c>
+      <c r="F22" s="5" t="s">
         <v>572</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>573</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="1"/>
@@ -58766,7 +58766,7 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="4" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="345" x14ac:dyDescent="0.25">
@@ -58776,7 +58776,7 @@
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="4" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1" t="s">
@@ -58814,7 +58814,7 @@
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="4" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58824,25 +58824,25 @@
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="4" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="4" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="4" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="375" x14ac:dyDescent="0.25">
@@ -58851,13 +58851,13 @@
         <v>Chupilca</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
@@ -58868,7 +58868,7 @@
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="4" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58881,26 +58881,26 @@
         <v>458</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
       <c r="J28" s="1" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="L28" s="5"/>
       <c r="M28" s="4" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="360" x14ac:dyDescent="0.25">
@@ -58910,14 +58910,14 @@
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="4" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
@@ -58926,7 +58926,7 @@
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="4" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58935,13 +58935,13 @@
         <v>Cléry</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
@@ -58952,7 +58952,7 @@
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="4" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58961,22 +58961,22 @@
         <v>Cléry Chirimoya</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>425</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="F31" s="5" t="s">
+        <v>1001</v>
+      </c>
+      <c r="G31" s="4" t="s">
         <v>1002</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>1003</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -58984,7 +58984,7 @@
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="4" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -58993,10 +58993,10 @@
         <v>Cléry Durazno</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1" t="s">
@@ -59019,19 +59019,19 @@
         <v>Clover Club</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="D33" s="4" t="s">
+        <v>548</v>
+      </c>
+      <c r="E33" s="4" t="s">
         <v>549</v>
       </c>
-      <c r="E33" s="4" t="s">
-        <v>550</v>
-      </c>
       <c r="F33" s="1" t="s">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
@@ -59040,7 +59040,7 @@
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="4" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="255" x14ac:dyDescent="0.25">
@@ -59050,7 +59050,7 @@
       </c>
       <c r="B34" s="1"/>
       <c r="C34" s="4" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="1" t="s">
@@ -59066,7 +59066,7 @@
       <c r="K34" s="5"/>
       <c r="L34" s="5"/>
       <c r="M34" s="4" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -59075,10 +59075,10 @@
         <v>Cosmo Patagonia</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="1"/>
@@ -59098,7 +59098,7 @@
       </c>
       <c r="B36" s="1"/>
       <c r="C36" s="4" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
@@ -59110,7 +59110,7 @@
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59119,10 +59119,10 @@
         <v>Crepúsculo</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="4" t="s">
@@ -59138,7 +59138,7 @@
       <c r="K37" s="5"/>
       <c r="L37" s="5"/>
       <c r="M37" s="4" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="255" x14ac:dyDescent="0.25">
@@ -59148,14 +59148,14 @@
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="4" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D38" s="1"/>
       <c r="E38" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="1"/>
@@ -59164,7 +59164,7 @@
       <c r="K38" s="5"/>
       <c r="L38" s="5"/>
       <c r="M38" s="4" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59186,7 +59186,7 @@
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="4" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -59207,28 +59207,28 @@
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="1" t="s">
+        <v>928</v>
+      </c>
+      <c r="I40" s="5" t="s">
         <v>929</v>
-      </c>
-      <c r="I40" s="5" t="s">
-        <v>930</v>
       </c>
       <c r="J40" s="4"/>
       <c r="K40" s="5"/>
       <c r="L40" s="5"/>
       <c r="M40" s="4" t="s">
-        <v>942</v>
-      </c>
-    </row>
-    <row r="41" spans="1:13" ht="210" x14ac:dyDescent="0.25">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="41" spans="1:13" ht="225" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="str">
         <f>IF(receta!A41="","",receta!A41)</f>
         <v>Dama Blanca</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>477</v>
+        <v>1063</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="1"/>
@@ -59240,7 +59240,7 @@
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
       <c r="M41" s="4" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59266,7 +59266,7 @@
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="M42" s="4" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="270" x14ac:dyDescent="0.25">
@@ -59276,10 +59276,10 @@
       </c>
       <c r="B43" s="1"/>
       <c r="C43" s="4" t="s">
+        <v>591</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>592</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>593</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="5"/>
@@ -59294,7 +59294,7 @@
       <c r="K43" s="5"/>
       <c r="L43" s="5"/>
       <c r="M43" s="4" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -59323,10 +59323,10 @@
         <v>Dry Martini</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>392</v>
@@ -59340,7 +59340,7 @@
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
       <c r="M45" s="4" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="285" x14ac:dyDescent="0.25">
@@ -59349,11 +59349,11 @@
         <v>El Amor en los Tiempos del Covid</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C46" s="4"/>
       <c r="D46" s="4" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>185</v>
@@ -59365,16 +59365,16 @@
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
       <c r="J46" s="4" t="s">
+        <v>1035</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>1034</v>
+      </c>
+      <c r="L46" s="4" t="s">
         <v>1036</v>
       </c>
-      <c r="K46" s="5" t="s">
-        <v>1035</v>
-      </c>
-      <c r="L46" s="4" t="s">
-        <v>1037</v>
-      </c>
       <c r="M46" s="4" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -59402,7 +59402,7 @@
       <c r="K47" s="5"/>
       <c r="L47" s="5"/>
       <c r="M47" s="4" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="315" x14ac:dyDescent="0.25">
@@ -59415,13 +59415,13 @@
         <v>380</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E48" s="1" t="s">
+        <v>597</v>
+      </c>
+      <c r="F48" s="5" t="s">
         <v>598</v>
-      </c>
-      <c r="F48" s="5" t="s">
-        <v>599</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="1"/>
@@ -59438,19 +59438,19 @@
       </c>
       <c r="B49" s="1"/>
       <c r="C49" s="4" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>372</v>
       </c>
       <c r="E49" s="1" t="s">
+        <v>769</v>
+      </c>
+      <c r="F49" s="5" t="s">
         <v>770</v>
       </c>
-      <c r="F49" s="5" t="s">
-        <v>771</v>
-      </c>
       <c r="G49" s="4" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -59458,7 +59458,7 @@
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
       <c r="M49" s="4" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="255" x14ac:dyDescent="0.25">
@@ -59468,17 +59468,17 @@
       </c>
       <c r="B50" s="1"/>
       <c r="C50" s="4" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="4" t="s">
+        <v>480</v>
+      </c>
+      <c r="F50" s="5" t="s">
         <v>481</v>
       </c>
-      <c r="F50" s="5" t="s">
-        <v>482</v>
-      </c>
       <c r="G50" s="4" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>326</v>
@@ -59490,7 +59490,7 @@
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
       <c r="M50" s="4" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -59500,7 +59500,7 @@
       </c>
       <c r="B51" s="1"/>
       <c r="C51" s="4" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -59512,7 +59512,7 @@
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
       <c r="M51" s="1" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="150" x14ac:dyDescent="0.25">
@@ -59535,16 +59535,16 @@
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="I52" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="J52" s="1"/>
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
       <c r="M52" s="4" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="390" x14ac:dyDescent="0.25">
@@ -59566,7 +59566,7 @@
         <v>404</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>384</v>
@@ -59578,7 +59578,7 @@
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="4" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59588,7 +59588,7 @@
       </c>
       <c r="B54" s="1"/>
       <c r="C54" s="4" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="1"/>
@@ -59604,7 +59604,7 @@
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
       <c r="M54" s="4" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
@@ -59650,7 +59650,7 @@
         <v>473</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -59658,7 +59658,7 @@
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
       <c r="M56" s="4" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59686,7 +59686,7 @@
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
       <c r="M57" s="4" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="150" x14ac:dyDescent="0.25">
@@ -59695,7 +59695,7 @@
         <v>Frangelico Sour</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>338</v>
@@ -59710,7 +59710,7 @@
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="4" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59719,10 +59719,10 @@
         <v>French 75</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>358</v>
@@ -59740,7 +59740,7 @@
       <c r="K59" s="5"/>
       <c r="L59" s="5"/>
       <c r="M59" s="4" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -59762,7 +59762,7 @@
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
       <c r="M60" s="4" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="165" x14ac:dyDescent="0.25">
@@ -59778,10 +59778,10 @@
         <v>388</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="4"/>
@@ -59790,7 +59790,7 @@
       <c r="K61" s="1"/>
       <c r="L61" s="1"/>
       <c r="M61" s="4" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="345" x14ac:dyDescent="0.25">
@@ -59800,7 +59800,7 @@
       </c>
       <c r="B62" s="1"/>
       <c r="C62" s="4" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D62" s="1"/>
       <c r="E62" s="4" t="s">
@@ -59816,7 +59816,7 @@
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
       <c r="M62" s="4" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59843,16 +59843,16 @@
         <v>337</v>
       </c>
       <c r="J63" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="K63" s="5" t="s">
         <v>767</v>
       </c>
-      <c r="K63" s="5" t="s">
-        <v>768</v>
-      </c>
       <c r="L63" s="4" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="M63" s="4" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -59862,7 +59862,7 @@
       </c>
       <c r="B64" s="1"/>
       <c r="C64" s="4" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
@@ -59874,7 +59874,7 @@
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
       <c r="M64" s="4" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59884,7 +59884,7 @@
       </c>
       <c r="B65" s="1"/>
       <c r="C65" s="4" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>169</v>
@@ -59898,7 +59898,7 @@
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
       <c r="M65" s="1" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="375" x14ac:dyDescent="0.25">
@@ -59908,10 +59908,10 @@
       </c>
       <c r="B66" s="1"/>
       <c r="C66" s="4" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
@@ -59922,7 +59922,7 @@
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
       <c r="M66" s="4" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="67" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59948,7 +59948,7 @@
       <c r="K67" s="5"/>
       <c r="L67" s="5"/>
       <c r="M67" s="4" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="68" spans="1:13" ht="330" x14ac:dyDescent="0.25">
@@ -59958,10 +59958,10 @@
       </c>
       <c r="B68" s="1"/>
       <c r="C68" s="1" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>596</v>
+        <v>595</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>165</v>
@@ -59976,7 +59976,7 @@
       <c r="K68" s="5"/>
       <c r="L68" s="5"/>
       <c r="M68" s="4" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
     </row>
     <row r="69" spans="1:13" ht="300" x14ac:dyDescent="0.25">
@@ -60004,7 +60004,7 @@
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
       <c r="M69" s="4" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -60032,7 +60032,7 @@
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
       <c r="M70" s="4" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -60058,7 +60058,7 @@
       <c r="K71" s="5"/>
       <c r="L71" s="5"/>
       <c r="M71" s="4" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="72" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60067,13 +60067,13 @@
         <v>Jote</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="E72" s="1"/>
       <c r="F72" s="5"/>
@@ -60088,7 +60088,7 @@
       <c r="K72" s="5"/>
       <c r="L72" s="5"/>
       <c r="M72" s="4" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
     </row>
     <row r="73" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -60097,11 +60097,11 @@
         <v>Julepe de Menta</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="C73" s="4"/>
       <c r="D73" s="4" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
@@ -60119,26 +60119,26 @@
         <v>Julieta Flowers</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="E74" s="1" t="s">
+        <v>728</v>
+      </c>
+      <c r="F74" s="5" t="s">
         <v>729</v>
-      </c>
-      <c r="F74" s="5" t="s">
-        <v>730</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="1" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="J74" s="1"/>
       <c r="K74" s="5"/>
@@ -60164,7 +60164,7 @@
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
       <c r="M75" s="4" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="76" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60200,10 +60200,10 @@
       </c>
       <c r="B77" s="1"/>
       <c r="C77" s="4" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D77" s="4" t="s">
         <v>1017</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>1018</v>
       </c>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
@@ -60214,7 +60214,7 @@
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
       <c r="M77" s="4" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="78" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -60228,19 +60228,19 @@
       </c>
       <c r="D78" s="1"/>
       <c r="E78" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="G78" s="5"/>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
       <c r="J78" s="1" t="s">
-        <v>790</v>
+        <v>789</v>
       </c>
       <c r="K78" s="5" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="L78" s="5"/>
       <c r="M78" s="1"/>
@@ -60290,7 +60290,7 @@
       </c>
       <c r="B81" s="1"/>
       <c r="C81" s="4" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D81" s="4"/>
       <c r="E81" s="1"/>
@@ -60309,20 +60309,20 @@
         <v>Mai Tai Piña</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D82" s="4"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
       <c r="G82" s="1"/>
       <c r="H82" s="1" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="I82" s="5" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="J82" s="1"/>
       <c r="K82" s="1"/>
@@ -60336,7 +60336,7 @@
       </c>
       <c r="B83" s="1"/>
       <c r="C83" s="4" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>304</v>
@@ -60354,7 +60354,7 @@
       <c r="K83" s="5"/>
       <c r="L83" s="5"/>
       <c r="M83" s="4" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
     </row>
     <row r="84" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60363,28 +60363,28 @@
         <v>Malta con Huevo</v>
       </c>
       <c r="B84" s="4" t="s">
+        <v>660</v>
+      </c>
+      <c r="C84" s="4" t="s">
         <v>661</v>
       </c>
-      <c r="C84" s="4" t="s">
-        <v>662</v>
-      </c>
       <c r="D84" s="4" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
       <c r="H84" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="J84" s="1"/>
       <c r="K84" s="1"/>
       <c r="L84" s="1"/>
       <c r="M84" s="4" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -60393,28 +60393,28 @@
         <v>Malta con Leche Condensada</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
       <c r="H85" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="J85" s="1"/>
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
       <c r="M85" s="4" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -60423,7 +60423,7 @@
         <v>Mango Sour</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C86" s="4"/>
       <c r="D86" s="1"/>
@@ -60444,18 +60444,18 @@
       </c>
       <c r="B87" s="1"/>
       <c r="C87" s="4" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="D87" s="1"/>
       <c r="E87" s="1" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="G87" s="5"/>
       <c r="H87" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="I87" s="5" t="s">
         <v>373</v>
@@ -60464,7 +60464,7 @@
       <c r="K87" s="5"/>
       <c r="L87" s="5"/>
       <c r="M87" s="4" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="88" spans="1:13" ht="360" x14ac:dyDescent="0.25">
@@ -60473,13 +60473,13 @@
         <v>Maqui Sour</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
@@ -60497,10 +60497,10 @@
         <v>Margarita</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D89" s="1"/>
       <c r="E89" s="1" t="s">
@@ -60526,7 +60526,7 @@
       <c r="C90" s="1"/>
       <c r="D90" s="1"/>
       <c r="E90" s="1" t="s">
-        <v>591</v>
+        <v>590</v>
       </c>
       <c r="F90" s="5" t="s">
         <v>410</v>
@@ -60545,10 +60545,10 @@
         <v>Melón con Vino</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="D91" s="1"/>
       <c r="E91" s="1" t="s">
@@ -60571,10 +60571,10 @@
         <v>Michelada</v>
       </c>
       <c r="B92" s="4" t="s">
+        <v>843</v>
+      </c>
+      <c r="C92" s="4" t="s">
         <v>844</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>845</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>401</v>
@@ -60600,7 +60600,7 @@
       </c>
       <c r="B93" s="1"/>
       <c r="C93" s="4" t="s">
-        <v>538</v>
+        <v>537</v>
       </c>
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
@@ -60612,7 +60612,7 @@
       <c r="K93" s="1"/>
       <c r="L93" s="1"/>
       <c r="M93" s="4" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="94" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -60641,10 +60641,10 @@
         <v>Mojito</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D95" s="4"/>
       <c r="E95" s="1"/>
@@ -60656,7 +60656,7 @@
       <c r="K95" s="1"/>
       <c r="L95" s="1"/>
       <c r="M95" s="4" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="96" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -60666,7 +60666,7 @@
       </c>
       <c r="B96" s="1"/>
       <c r="C96" s="4" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D96" s="4"/>
       <c r="E96" s="1"/>
@@ -60686,16 +60686,16 @@
       </c>
       <c r="B97" s="1"/>
       <c r="C97" s="4" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="G97" s="1"/>
       <c r="H97" s="4"/>
@@ -60704,7 +60704,7 @@
       <c r="K97" s="1"/>
       <c r="L97" s="1"/>
       <c r="M97" s="4" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
     </row>
     <row r="98" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -60714,7 +60714,7 @@
       </c>
       <c r="B98" s="1"/>
       <c r="C98" s="4" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="D98" s="4"/>
       <c r="E98" s="1"/>
@@ -60750,7 +60750,7 @@
       <c r="K99" s="5"/>
       <c r="L99" s="5"/>
       <c r="M99" s="4" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="100" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -60759,7 +60759,7 @@
         <v>Naranja Sour</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>371</v>
@@ -60786,7 +60786,7 @@
       </c>
       <c r="B101" s="1"/>
       <c r="C101" s="4" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="D101" s="4"/>
       <c r="E101" s="4"/>
@@ -60824,7 +60824,7 @@
       <c r="K102" s="1"/>
       <c r="L102" s="1"/>
       <c r="M102" s="4" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="103" spans="1:13" ht="210" x14ac:dyDescent="0.25">
@@ -60834,7 +60834,7 @@
       </c>
       <c r="B103" s="1"/>
       <c r="C103" s="4" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="D103" s="1"/>
       <c r="E103" s="1"/>
@@ -60846,7 +60846,7 @@
       <c r="K103" s="1"/>
       <c r="L103" s="1"/>
       <c r="M103" s="4" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="104" spans="1:13" ht="345" x14ac:dyDescent="0.25">
@@ -60855,19 +60855,19 @@
         <v>New York Sour</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="G104" s="5"/>
       <c r="H104" s="1"/>
@@ -60876,7 +60876,7 @@
       <c r="K104" s="5"/>
       <c r="L104" s="5"/>
       <c r="M104" s="4" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="105" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -60902,7 +60902,7 @@
       <c r="K105" s="1"/>
       <c r="L105" s="1"/>
       <c r="M105" s="4" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="106" spans="1:13" ht="375" x14ac:dyDescent="0.25">
@@ -60911,32 +60911,32 @@
         <v>Old Fashioned</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C106" s="4"/>
       <c r="D106" s="4" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="E106" s="1" t="s">
+        <v>1041</v>
+      </c>
+      <c r="F106" s="5" t="s">
         <v>1042</v>
       </c>
-      <c r="F106" s="5" t="s">
-        <v>1043</v>
-      </c>
       <c r="G106" s="4" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="I106" s="5" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="J106" s="1"/>
       <c r="K106" s="1"/>
       <c r="L106" s="1"/>
       <c r="M106" s="4" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="107" spans="1:13" ht="192" customHeight="1" x14ac:dyDescent="0.25">
@@ -60965,17 +60965,17 @@
         <v>Paloma</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D108" s="1"/>
       <c r="E108" s="1"/>
       <c r="F108" s="1"/>
       <c r="G108" s="1"/>
       <c r="H108" s="1" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="I108" s="5" t="s">
         <v>256</v>
@@ -60984,7 +60984,7 @@
       <c r="K108" s="1"/>
       <c r="L108" s="1"/>
       <c r="M108" s="4" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="109" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -60993,7 +60993,7 @@
         <v>Parrón</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="C109" s="4"/>
       <c r="D109" s="4"/>
@@ -61013,19 +61013,19 @@
         <v>Penicilina</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="G110" s="5"/>
       <c r="H110" s="1"/>
@@ -61034,7 +61034,7 @@
       <c r="K110" s="5"/>
       <c r="L110" s="5"/>
       <c r="M110" s="4" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.25">
@@ -61044,14 +61044,14 @@
       </c>
       <c r="B111" s="1"/>
       <c r="C111" s="4" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="D111" s="1"/>
       <c r="E111" s="1" t="s">
-        <v>500</v>
+        <v>499</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="G111" s="5"/>
       <c r="H111" s="1"/>
@@ -61072,10 +61072,10 @@
       </c>
       <c r="D112" s="1"/>
       <c r="E112" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="G112" s="5"/>
       <c r="H112" s="1"/>
@@ -61108,7 +61108,7 @@
       <c r="K113" s="5"/>
       <c r="L113" s="5"/>
       <c r="M113" s="4" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.25">
@@ -61183,10 +61183,10 @@
         <v>Piscola</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D117" s="5"/>
       <c r="E117" s="1" t="s">
@@ -61202,7 +61202,7 @@
       <c r="K117" s="5"/>
       <c r="L117" s="5"/>
       <c r="M117" s="4" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="118" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -61211,17 +61211,17 @@
         <v>Pistón</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D118" s="1"/>
       <c r="E118" s="1" t="s">
+        <v>500</v>
+      </c>
+      <c r="F118" s="5" t="s">
         <v>501</v>
-      </c>
-      <c r="F118" s="5" t="s">
-        <v>502</v>
       </c>
       <c r="G118" s="5"/>
       <c r="H118" s="1"/>
@@ -61256,7 +61256,7 @@
       <c r="K119" s="5"/>
       <c r="L119" s="5"/>
       <c r="M119" s="4" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="120" spans="1:13" ht="75" x14ac:dyDescent="0.25">
@@ -61290,7 +61290,7 @@
       </c>
       <c r="B121" s="1"/>
       <c r="C121" s="4" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D121" s="1"/>
       <c r="E121" s="1"/>
@@ -61310,14 +61310,14 @@
       </c>
       <c r="B122" s="1"/>
       <c r="C122" s="4" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D122" s="1"/>
       <c r="E122" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G122" s="1"/>
       <c r="H122" s="1"/>
@@ -61334,7 +61334,7 @@
       </c>
       <c r="B123" s="1"/>
       <c r="C123" s="4" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D123" s="4" t="s">
         <v>252</v>
@@ -61352,7 +61352,7 @@
       <c r="K123" s="5"/>
       <c r="L123" s="5"/>
       <c r="M123" s="4" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="124" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -61383,10 +61383,10 @@
         <v>Sangría</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D125" s="4" t="s">
         <v>393</v>
@@ -61412,7 +61412,7 @@
       </c>
       <c r="B126" s="1"/>
       <c r="C126" s="4" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D126" s="1"/>
       <c r="E126" s="1"/>
@@ -61432,14 +61432,14 @@
       </c>
       <c r="B127" s="1"/>
       <c r="C127" s="4" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D127" s="1"/>
       <c r="E127" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="G127" s="1"/>
       <c r="H127" s="1"/>
@@ -61468,7 +61468,7 @@
       <c r="K128" s="1"/>
       <c r="L128" s="1"/>
       <c r="M128" s="4" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="129" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -61481,7 +61481,7 @@
         <v>369</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="E129" s="1"/>
       <c r="F129" s="1"/>
@@ -61492,7 +61492,7 @@
       <c r="K129" s="1"/>
       <c r="L129" s="1"/>
       <c r="M129" s="4" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="130" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -61558,7 +61558,7 @@
       <c r="K132" s="5"/>
       <c r="L132" s="5"/>
       <c r="M132" s="4" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.25">
@@ -61588,16 +61588,16 @@
       </c>
       <c r="B134" s="1"/>
       <c r="C134" s="4" t="s">
+        <v>587</v>
+      </c>
+      <c r="D134" s="4" t="s">
+        <v>596</v>
+      </c>
+      <c r="E134" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="F134" s="5" t="s">
         <v>588</v>
-      </c>
-      <c r="D134" s="4" t="s">
-        <v>597</v>
-      </c>
-      <c r="E134" s="4" t="s">
-        <v>590</v>
-      </c>
-      <c r="F134" s="5" t="s">
-        <v>589</v>
       </c>
       <c r="G134" s="5"/>
       <c r="H134" s="4"/>
@@ -61606,7 +61606,7 @@
       <c r="K134" s="5"/>
       <c r="L134" s="5"/>
       <c r="M134" s="4" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="135" spans="1:13" ht="300" x14ac:dyDescent="0.25">
@@ -61615,28 +61615,28 @@
         <v>Terremoto</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="E135" s="1"/>
       <c r="F135" s="1"/>
       <c r="G135" s="1"/>
       <c r="H135" s="1" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="I135" s="5" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
       <c r="J135" s="1"/>
       <c r="K135" s="1"/>
       <c r="L135" s="1"/>
       <c r="M135" s="4" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="136" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -61645,10 +61645,10 @@
         <v>Terremoto (Sin Alcohol)</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D136" s="4"/>
       <c r="E136" s="1" t="s">
@@ -61676,13 +61676,13 @@
         <v>433</v>
       </c>
       <c r="E137" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="F137" s="5" t="s">
+        <v>1037</v>
+      </c>
+      <c r="G137" s="4" t="s">
         <v>1039</v>
-      </c>
-      <c r="F137" s="5" t="s">
-        <v>1038</v>
-      </c>
-      <c r="G137" s="4" t="s">
-        <v>1040</v>
       </c>
       <c r="H137" s="1"/>
       <c r="I137" s="1"/>
@@ -61698,7 +61698,7 @@
       </c>
       <c r="B138" s="4"/>
       <c r="C138" s="4" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D138" s="1"/>
       <c r="E138" s="1"/>
@@ -61710,7 +61710,7 @@
       <c r="K138" s="1"/>
       <c r="L138" s="1"/>
       <c r="M138" s="4" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="139" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -61720,7 +61720,7 @@
       </c>
       <c r="B139" s="1"/>
       <c r="C139" s="4" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="D139" s="4"/>
       <c r="E139" s="1"/>
@@ -61743,22 +61743,22 @@
         <v>Tropezón</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D140" s="4" t="s">
         <v>345</v>
       </c>
       <c r="E140" s="1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F140" s="5" t="s">
+        <v>1023</v>
+      </c>
+      <c r="G140" s="4" t="s">
         <v>1025</v>
-      </c>
-      <c r="F140" s="5" t="s">
-        <v>1024</v>
-      </c>
-      <c r="G140" s="4" t="s">
-        <v>1026</v>
       </c>
       <c r="H140" s="1"/>
       <c r="I140" s="1"/>
@@ -61770,7 +61770,7 @@
       </c>
       <c r="L140" s="5"/>
       <c r="M140" s="4" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="141" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -61779,19 +61779,19 @@
         <v>Vaina</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="E141" s="4" t="s">
+        <v>612</v>
+      </c>
+      <c r="F141" s="4" t="s">
         <v>613</v>
-      </c>
-      <c r="F141" s="4" t="s">
-        <v>614</v>
       </c>
       <c r="G141" s="4"/>
       <c r="H141" s="1"/>
@@ -61808,7 +61808,7 @@
       </c>
       <c r="B142" s="1"/>
       <c r="C142" s="4" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D142" s="4"/>
       <c r="E142" s="4" t="s">
@@ -61831,19 +61831,19 @@
         <v>Vampiro</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="E143" s="1" t="s">
+        <v>538</v>
+      </c>
+      <c r="F143" s="1" t="s">
         <v>539</v>
-      </c>
-      <c r="F143" s="1" t="s">
-        <v>540</v>
       </c>
       <c r="G143" s="1"/>
       <c r="H143" s="1"/>
@@ -61852,7 +61852,7 @@
       <c r="K143" s="1"/>
       <c r="L143" s="1"/>
       <c r="M143" s="4" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="144" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -61875,20 +61875,20 @@
       </c>
       <c r="G144" s="1"/>
       <c r="H144" s="1" t="s">
+        <v>1029</v>
+      </c>
+      <c r="I144" s="5" t="s">
         <v>1030</v>
       </c>
-      <c r="I144" s="5" t="s">
-        <v>1031</v>
-      </c>
       <c r="J144" s="1" t="s">
+        <v>1027</v>
+      </c>
+      <c r="K144" s="5" t="s">
         <v>1028</v>
-      </c>
-      <c r="K144" s="5" t="s">
-        <v>1029</v>
       </c>
       <c r="L144" s="1"/>
       <c r="M144" s="4" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="145" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -61897,19 +61897,19 @@
         <v>Vermouth con Soda</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="G145" s="1"/>
       <c r="H145" s="1"/>
@@ -61918,7 +61918,7 @@
       <c r="K145" s="1"/>
       <c r="L145" s="1"/>
       <c r="M145" s="4" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="146" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -61928,7 +61928,7 @@
       </c>
       <c r="B146" s="1"/>
       <c r="C146" s="4" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D146" s="1"/>
       <c r="E146" s="1"/>
@@ -61948,14 +61948,14 @@
       </c>
       <c r="B147" s="1"/>
       <c r="C147" s="4" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D147" s="4"/>
       <c r="E147" s="1" t="s">
+        <v>713</v>
+      </c>
+      <c r="F147" s="5" t="s">
         <v>714</v>
-      </c>
-      <c r="F147" s="5" t="s">
-        <v>715</v>
       </c>
       <c r="G147" s="5"/>
       <c r="H147" s="1"/>
@@ -61964,7 +61964,7 @@
       <c r="K147" s="5"/>
       <c r="L147" s="5"/>
       <c r="M147" s="4" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
     </row>
     <row r="148" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -61974,14 +61974,14 @@
       </c>
       <c r="B148" s="1"/>
       <c r="C148" s="4" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D148" s="1"/>
       <c r="E148" s="1" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="G148" s="5"/>
       <c r="H148" s="1"/>
@@ -61998,16 +61998,16 @@
       </c>
       <c r="B149" s="1"/>
       <c r="C149" s="4" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="E149" s="1" t="s">
+        <v>707</v>
+      </c>
+      <c r="F149" s="5" t="s">
         <v>708</v>
-      </c>
-      <c r="F149" s="5" t="s">
-        <v>709</v>
       </c>
       <c r="G149" s="5"/>
       <c r="H149" s="1"/>
@@ -62023,7 +62023,7 @@
         <v>Whisky Sour</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C150" s="4" t="s">
         <v>360</v>
@@ -62044,7 +62044,7 @@
       <c r="K150" s="1"/>
       <c r="L150" s="1"/>
       <c r="M150" s="4" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="151" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -62053,19 +62053,19 @@
         <v>Bramble</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="D151" s="4" t="s">
+        <v>790</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>792</v>
+      </c>
+      <c r="F151" s="1" t="s">
         <v>791</v>
-      </c>
-      <c r="E151" s="1" t="s">
-        <v>793</v>
-      </c>
-      <c r="F151" s="1" t="s">
-        <v>792</v>
       </c>
       <c r="G151" s="1"/>
       <c r="H151" s="1"/>
@@ -62082,14 +62082,14 @@
       </c>
       <c r="B152" s="1"/>
       <c r="C152" s="4" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="D152" s="4"/>
       <c r="E152" s="1" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="G152" s="1"/>
       <c r="H152" s="1"/>
@@ -62098,7 +62098,7 @@
       <c r="K152" s="1"/>
       <c r="L152" s="1"/>
       <c r="M152" s="4" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="153" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -62107,19 +62107,19 @@
         <v>Gin Basil Smash</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="E153" s="4" t="s">
+        <v>794</v>
+      </c>
+      <c r="F153" s="1" t="s">
         <v>795</v>
-      </c>
-      <c r="F153" s="1" t="s">
-        <v>796</v>
       </c>
       <c r="G153" s="1"/>
       <c r="H153" s="1"/>
@@ -62136,28 +62136,28 @@
       </c>
       <c r="B154" s="1"/>
       <c r="C154" s="4" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="D154" s="26" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="E154" s="1" t="s">
+        <v>783</v>
+      </c>
+      <c r="F154" s="5" t="s">
         <v>784</v>
-      </c>
-      <c r="F154" s="5" t="s">
-        <v>785</v>
       </c>
       <c r="G154" s="5"/>
       <c r="H154" s="1"/>
       <c r="I154" s="5"/>
       <c r="J154" s="1" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="K154" s="5" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="L154" s="26" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
       <c r="M154" s="1"/>
     </row>
@@ -62167,10 +62167,10 @@
         <v>Medias de Seda</v>
       </c>
       <c r="B155" s="4" t="s">
+        <v>799</v>
+      </c>
+      <c r="C155" s="4" t="s">
         <v>800</v>
-      </c>
-      <c r="C155" s="4" t="s">
-        <v>801</v>
       </c>
       <c r="D155" s="4"/>
       <c r="E155" s="1"/>
@@ -62189,17 +62189,17 @@
         <v>Brandy Sour</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="D156" s="4"/>
       <c r="E156" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="G156" s="5"/>
       <c r="H156" s="1"/>
@@ -62215,10 +62215,10 @@
         <v>Juanito Rosado</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="D157" s="4" t="s">
         <v>434</v>
@@ -62243,17 +62243,17 @@
         <v>Vino Navegado</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="D158" s="10"/>
       <c r="E158" s="1" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="G158" s="1"/>
       <c r="H158" s="1"/>
@@ -62262,7 +62262,7 @@
       <c r="K158" s="1"/>
       <c r="L158" s="1"/>
       <c r="M158" s="10" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
     </row>
     <row r="159" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62271,32 +62271,32 @@
         <v>Cola de Mono</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="G159" s="5"/>
       <c r="H159" s="1" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="I159" s="10" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="J159" s="1"/>
       <c r="K159" s="1"/>
       <c r="L159" s="1"/>
       <c r="M159" s="4" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="160" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62305,22 +62305,22 @@
         <v>Chichón</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>1023</v>
+        <v>1022</v>
       </c>
       <c r="E160" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="F160" s="5" t="s">
         <v>1021</v>
       </c>
-      <c r="F160" s="5" t="s">
-        <v>1022</v>
-      </c>
       <c r="G160" s="4" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="H160" s="1"/>
       <c r="I160" s="5"/>
@@ -62328,7 +62328,7 @@
       <c r="K160" s="1"/>
       <c r="L160" s="1"/>
       <c r="M160" s="4" t="s">
-        <v>1027</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="161" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -62337,10 +62337,10 @@
         <v>Ramos Fizz</v>
       </c>
       <c r="B161" s="4" t="s">
+        <v>840</v>
+      </c>
+      <c r="C161" s="4" t="s">
         <v>841</v>
-      </c>
-      <c r="C161" s="4" t="s">
-        <v>842</v>
       </c>
       <c r="D161" s="4"/>
       <c r="E161" s="1"/>
@@ -62359,17 +62359,17 @@
         <v>Gin Fizz</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="D162" s="4"/>
       <c r="E162" s="1" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="G162" s="5"/>
       <c r="H162" s="5"/>
@@ -62386,16 +62386,16 @@
       </c>
       <c r="B163" s="1"/>
       <c r="C163" s="4" t="s">
+        <v>853</v>
+      </c>
+      <c r="D163" s="4" t="s">
+        <v>852</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>855</v>
+      </c>
+      <c r="F163" s="5" t="s">
         <v>854</v>
-      </c>
-      <c r="D163" s="4" t="s">
-        <v>853</v>
-      </c>
-      <c r="E163" s="1" t="s">
-        <v>856</v>
-      </c>
-      <c r="F163" s="5" t="s">
-        <v>855</v>
       </c>
       <c r="G163" s="5"/>
       <c r="H163" s="1"/>
@@ -62404,7 +62404,7 @@
       <c r="K163" s="1"/>
       <c r="L163" s="1"/>
       <c r="M163" s="4" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="164" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62414,29 +62414,29 @@
       </c>
       <c r="B164" s="4"/>
       <c r="C164" s="4" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="G164" s="5"/>
       <c r="H164" s="1"/>
       <c r="I164" s="5"/>
       <c r="J164" s="1" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="K164" s="1" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="L164" s="1"/>
       <c r="M164" s="4" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
     </row>
     <row r="165" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62445,22 +62445,22 @@
         <v>Pihuelo</v>
       </c>
       <c r="B165" s="4" t="s">
+        <v>869</v>
+      </c>
+      <c r="C165" s="4" t="s">
         <v>870</v>
       </c>
-      <c r="C165" s="4" t="s">
-        <v>871</v>
-      </c>
       <c r="D165" s="4" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="E165" s="4" t="s">
+        <v>1031</v>
+      </c>
+      <c r="F165" s="5" t="s">
         <v>1032</v>
       </c>
-      <c r="F165" s="5" t="s">
+      <c r="G165" s="1" t="s">
         <v>1033</v>
-      </c>
-      <c r="G165" s="1" t="s">
-        <v>1034</v>
       </c>
       <c r="H165" s="1"/>
       <c r="I165" s="5"/>
@@ -62468,7 +62468,7 @@
       <c r="K165" s="1"/>
       <c r="L165" s="1"/>
       <c r="M165" s="4" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="166" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62477,19 +62477,19 @@
         <v>Mojito Sandía</v>
       </c>
       <c r="B166" s="4" t="s">
+        <v>881</v>
+      </c>
+      <c r="C166" s="4" t="s">
         <v>882</v>
       </c>
-      <c r="C166" s="4" t="s">
-        <v>883</v>
-      </c>
       <c r="D166" s="4" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E166" s="1" t="s">
+        <v>879</v>
+      </c>
+      <c r="F166" s="5" t="s">
         <v>880</v>
-      </c>
-      <c r="F166" s="5" t="s">
-        <v>881</v>
       </c>
       <c r="G166" s="5"/>
       <c r="H166" s="1"/>
@@ -62498,7 +62498,7 @@
       <c r="K166" s="1"/>
       <c r="L166" s="1"/>
       <c r="M166" s="4" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
     </row>
     <row r="167" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62508,7 +62508,7 @@
       </c>
       <c r="B167" s="1"/>
       <c r="C167" s="4" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="D167" s="4"/>
       <c r="E167" s="1"/>
@@ -62520,7 +62520,7 @@
       <c r="K167" s="1"/>
       <c r="L167" s="1"/>
       <c r="M167" s="4" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="168" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -62530,7 +62530,7 @@
       </c>
       <c r="B168" s="1"/>
       <c r="C168" s="4" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="D168" s="4"/>
       <c r="E168" s="1"/>
@@ -62542,7 +62542,7 @@
       <c r="K168" s="1"/>
       <c r="L168" s="1"/>
       <c r="M168" s="4" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="169" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -62551,10 +62551,10 @@
         <v>Chardonnay Sour</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="D169" s="4"/>
       <c r="E169" s="1"/>
@@ -62573,13 +62573,13 @@
         <v>Carmenere Sour</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>470</v>
@@ -62594,7 +62594,7 @@
       <c r="K170" s="1"/>
       <c r="L170" s="1"/>
       <c r="M170" s="4" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="171" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62603,13 +62603,13 @@
         <v>Jerez Sour</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="E171" s="1"/>
       <c r="F171" s="1"/>
@@ -62620,7 +62620,7 @@
       <c r="K171" s="1"/>
       <c r="L171" s="1"/>
       <c r="M171" s="4" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
     </row>
     <row r="172" spans="1:13" x14ac:dyDescent="0.25">
@@ -64160,10 +64160,10 @@
         <v>62</v>
       </c>
       <c r="B2" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C2" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -64171,7 +64171,7 @@
         <v>67</v>
       </c>
       <c r="B3" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C3" t="s">
         <v>202</v>
@@ -64182,10 +64182,10 @@
         <v>68</v>
       </c>
       <c r="B4" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C4" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -64193,7 +64193,7 @@
         <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C5" t="s">
         <v>203</v>
@@ -64204,10 +64204,10 @@
         <v>69</v>
       </c>
       <c r="B6" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C6" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -64215,7 +64215,7 @@
         <v>70</v>
       </c>
       <c r="B7" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C7" t="s">
         <v>71</v>
@@ -64223,24 +64223,24 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="B8" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="C8" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>808</v>
+      </c>
+      <c r="B9" t="s">
         <v>809</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>810</v>
-      </c>
-      <c r="C9" t="s">
-        <v>811</v>
       </c>
     </row>
   </sheetData>
@@ -64270,7 +64270,7 @@
         <v>115</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -64278,7 +64278,7 @@
         <v>116</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -64286,7 +64286,7 @@
         <v>117</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -64294,7 +64294,7 @@
         <v>118</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -64302,7 +64302,7 @@
         <v>119</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -64310,7 +64310,7 @@
         <v>120</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -64318,7 +64318,7 @@
         <v>215</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -64326,23 +64326,23 @@
         <v>428</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="23" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="23" t="s">
+        <v>702</v>
+      </c>
+      <c r="B11" s="23" t="s">
         <v>703</v>
-      </c>
-      <c r="B11" s="23" t="s">
-        <v>704</v>
       </c>
     </row>
   </sheetData>

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C08C7AAE-3436-46C5-B90A-A68598CA4C83}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8BE3724-48E6-4676-B0F3-65925B6AA67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1607" uniqueCount="1064">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1626" uniqueCount="1080">
   <si>
     <t>Ramazzotti Spritz</t>
   </si>
@@ -2827,12 +2827,6 @@
     <t>En una copa de acero inoxidable tipo julep, machaca suavemente la menta junto con el azúcar y el agua. Llena el vaso con hielo picado, añade el bourbon y revuelve bien hasta que la copa se escarche.</t>
   </si>
   <si>
-    <t>Julepe de Menta: Frescura de Kentucky
-El Julepe de Mwenta o Mint Julep es un cóctel clásico del sur de Estados Unidos, con raíces que se remontan al siglo XVIII. Su preparación, a base de bourbon, menta fresca, azúcar y agua sobre hielo picado, lo convirtió en una bebida ideal para los climas cálidos, ganando popularidad especialmente en Kentucky. Tradicionalmente se sirve en una copa de plata o acero inoxidable escarchada por el hielo.
-Al igual que otros cócteles antiguos, el Julepe de Menta se originó como una forma de suavizar destilados de sabor poco agradable, añadiendo menta y azúcar para crear una mezcla más aromática y equilibrada.
-Desde 1938, el Mint Julep es el cóctel oficial del Derby de Kentucky, donde cada año se sirven decenas de miles durante el evento.</t>
-  </si>
-  <si>
     <t>Old Fashioned: Probablemente el Cóctel Original
 El Old Fashioned es uno de los cócteles más antiguos que se conocen, con orígenes que se remontan a principios del siglo XIX en Estados Unidos. Su receta básica, whiskey, azúcar, agua y bitters, refleja la definición más temprana dada a la palabra cocktail, registrada en 1806 como una mezcla de destilado, azúcar, agua y amargos.
 Más allá de su elegancia clásica, el Old Fashioned nació con un propósito muy práctico: mejorar el sabor de destilados de baja calidad que eran comunes en la época. Añadir azúcar, agua y bitters ayudaba a suavizar y equilibrar los sabores del alcohol, haciendo la bebida más placentera.
@@ -4451,10 +4445,6 @@
 Afiche de propaganda soviética contra el alcoholismo, publicado originalmente en 1954. Fue parte de las campañas para mejorar la productividad económica y el orden social en la Unión Soviética, donde el alcoholismo era un problema social reconocido. El texto visible en la imagen es la palabra rusa "НЕТ!", que significa "¡No!". </t>
   </si>
   <si>
-    <t>colada.jpg
-Imagen decorativa estilo cottage, inspirada en una obra original de Lisa Audit.</t>
-  </si>
-  <si>
     <t>tom.jpg
 Cartel publicitario de Old Tom Gin, específicamente de la marca James Mellor &amp; Sons de Liverpool. El cartel original data aproximadamente de 1880.</t>
   </si>
@@ -4977,6 +4967,81 @@
     <t>El Dama Blanca (en inglés White Lady) es un cóctel clásico, elegante y seco, perteneciente a la familia de los sours y estrechamente emparentado con el Sidecar y el Margarita. Aunque su receta base es simple, se le pueden añadir algunos toques opcionales: clara de huevo, que le aporta una textura sedosa y una ligera espuma en la superficie, y jarabe simple, para suavizar su acidez.
 No existe total certeza sobre su origen, pero suele atribuirse al bartender Harry MacElhone, quien lo habría preparado en el Ciro’s Club de Londres en una versión temprana que incluía crema de menta blanca. Hacia 1929, ya en el Harry’s New York Bar de París, reformuló la receta, sustituyendo este ingrediente por gin, dando origen a la variante que se difundió internacionalmente y que hoy se considera la forma clásica del trago.
 La proporción clásica de sus ingredientes es 2:1:1: dos partes de gin, una parte de licor de naranja (como Cointreau) y una parte de jugo de limón fresco.</t>
+  </si>
+  <si>
+    <t>Gold Rush</t>
+  </si>
+  <si>
+    <t>El Gold Rush es una versión del Whiskey Sour que utiliza jarabe de miel en lugar de jarabe simple y prescinde de la clara de huevo.
+En Manhattan existió un bar llamado Milk &amp; Honey, inaugurado en 1999 por Sasha Petraske. Sasha tenía un amigo de infancia, TJ Siegal. Un día de 2001, Sasha le habló de un jarabe de miel que había preparado para probar en otro cóctel, y Siegal le pidió que preparara su Bourbon Sour habitual, sin clara de huevo, pero con ese nuevo jarabe de miel en lugar del jarabe simple.
+Pronto, el Gold Rush comenzó a sugerirse a los amantes del whiskey como una “opción del barman” y, a principios de 2002, ya era un clásico del bar.</t>
+  </si>
+  <si>
+    <t>Bourbon.jpg
+Aviso publicitario de Old Hickory Bourbon, difundido en Estados Unidos a comienzos del siglo XX, en una época en que el whisky bourbon se consolidaba como uno de los destilados emblemáticos del país.</t>
+  </si>
+  <si>
+    <t>mimosa-flowers.jpg
+Flores de mimosa, nombre común de Acacia dealbata, árbol originario de Australia y ampliamente cultivado en el Mediterráneo. El cóctel Mimosa recibió este nombre porque su color dorado y luminoso recuerda el tono de estas flores.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">seda.jpg
+Afiche de la película Silk Stockings (1957), musical estadounidense dirigido por Rouben Mamoulian y protagonizado por Fred Astaire y Cyd Charisse. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medias de Seda 1957
+Existe una película titulada Medias de Seda (Silk Stockings,(1957), musical estadounidense dirigido por Rouben Mamoulian y protagonizado por Fred Astaire y Cyd Charisse, ambientada en el contexto de la Guerra Fría.
+La historia comienza cuando tres torpes agentes soviéticos fracasan en su misión de recuperar en París a un compositor que ha desertado. Para resolver la situación, las autoridades envían a Ninotchka, una estricta y disciplinada emisaria encargada de completar la tarea y poner orden. Sin embargo, el contacto con la vida parisina, el romance y el mundo del espectáculo comienza a transformar su carácter, dando lugar a una comedia que mezcla sátira política, romance y números de baile. La película es recordada como uno de los últimos grandes musicales del período clásico de Hollywood y una de las actuaciones más elegantes de Astaire en su etapa final en el cine.
+El cóctel Medias de Seda, si bien no está documentado que su nombre sea una referencia explícita a esta película, comparte con ella un mismo imaginario: el glamour y la sofisticación asociada a la moda, el cabaret y los bares de mediados del siglo XX, cuando cine, música y coctelería formaban parte de un mismo universo cultural ligado a la vida nocturna y al espectáculo.
+</t>
+  </si>
+  <si>
+    <t>bramble2.jpg
+Ilustración contemporánea inspirada en el cóctel Bramble.</t>
+  </si>
+  <si>
+    <t>Julepe de Menta: Frescura de Kentucky
+El Julepe de Menta o Mint Julep es un cóctel clásico del sur de Estados Unidos, con raíces que se remontan al siglo XVIII. Su preparación, a base de bourbon, menta fresca, azúcar y agua sobre hielo picado, lo convirtió en una bebida ideal para los climas cálidos, ganando popularidad especialmente en Kentucky. Tradicionalmente se sirve en una copa de plata o acero inoxidable escarchada por el hielo.
+Al igual que otros cócteles antiguos, el Julepe de Menta se originó como una forma de suavizar destilados de sabor poco agradable, añadiendo menta y azúcar para crear una mezcla más aromática y equilibrada.
+Desde 1938, el Mint Julep es el cóctel oficial del Derby de Kentucky, donde cada año se sirven decenas de miles durante el evento.</t>
+  </si>
+  <si>
+    <t>mint.jpg
+Aviso publicitario del bourbon Old Forester asociado al cóctel Mint Julep, bebida tradicional del sur de Estados Unidos preparada con bourbon, azúcar, agua y hojas de menta fresca.</t>
+  </si>
+  <si>
+    <t>maqui.jpg
+Ilustración botánica del Aristotelia chilensis, conocido como maqui, arbusto nativo del sur de Chile y Argentina cuyos frutos oscuros han sido utilizados tradicionalmente por el pueblo mapuche como alimento, colorante y bebida.</t>
+  </si>
+  <si>
+    <t>ronrico-maitai-1962.jpg
+Aviso publicitario del cóctel Mai Tai, difundido en Estados Unidos a comienzos de la década de 1960, en el contexto del auge de la coctelería tiki y la fascinación por lo “polinesio” en la cultura popular de posguerra.</t>
+  </si>
+  <si>
+    <t>caipi.jpg
+Classic Caipirinha, obra del artista y diseñador brasileño Felipe Hora, representa uno de los cócteles más emblemáticos de Brasil.</t>
+  </si>
+  <si>
+    <t>Santi.jpg
+Santiago Feliú. Foto de Iván Soca Pascual.</t>
+  </si>
+  <si>
+    <t>pina.jpg
+Ilustración contemporánea de estilo retro que representa una Piña Colada, acompañada de rodaja de piña y flores tropicales..</t>
+  </si>
+  <si>
+    <t>marga.jpg
+Anuncio publicitario de José Cuervo Tequila, probablemente de la década de 1960, que muestra una ilustración pictórica de una mujer junto a una copa Margarita y una botella de tequila.</t>
+  </si>
+  <si>
+    <t>sidecars2.jpg
+Página de la revista Motor Cycle, 9 de septiembre de 1920, en la que se comparan distintos modelos de motocicletas con sidecar y se destacan sus ventajas como medio de transporte familiar. El sidecar, vehículo lateral acoplado a una motocicleta, fue especialmente popular en Europa y América entre las décadas de 1910 y 1930, tanto para uso civil como militar.</t>
+  </si>
+  <si>
+    <t>Salieron en un coche, descansaron en un bar/Con mexicanos, margaritas, dos chicas, una sabe mentir/Eligen una mesa, un par de tragos y a bailar/Thelma y su cowboy, que ahora la saca de allí.</t>
+  </si>
+  <si>
+    <t>Las mismas diez lucas/La caña infernal/El pisco salado no deja pensar/Una vez en la cama/Vergüenza total</t>
   </si>
 </sst>
 </file>
@@ -5654,10 +5719,10 @@
         <v>78</v>
       </c>
       <c r="O1" s="27" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="P1" s="27" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="Q1" s="27" t="s">
         <v>79</v>
@@ -5669,13 +5734,13 @@
         <v>265</v>
       </c>
       <c r="T1" s="27" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="U1" s="27" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="V1" s="27" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="W1" s="27" t="s">
         <v>80</v>
@@ -5690,16 +5755,16 @@
         <v>196</v>
       </c>
       <c r="AA1" s="27" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="AB1" s="27" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="AC1" s="27" t="s">
+        <v>901</v>
+      </c>
+      <c r="AD1" s="27" t="s">
         <v>902</v>
-      </c>
-      <c r="AD1" s="27" t="s">
-        <v>903</v>
       </c>
       <c r="AE1" s="27" t="s">
         <v>82</v>
@@ -5753,13 +5818,13 @@
         <v>200</v>
       </c>
       <c r="AV1" s="27" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="AW1" s="27" t="s">
         <v>209</v>
       </c>
       <c r="AX1" s="27" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="AY1" s="27" t="s">
         <v>230</v>
@@ -5849,16 +5914,16 @@
         <v>152</v>
       </c>
       <c r="CB1" s="8" t="s">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="CC1" s="8" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="CD1" s="7" t="s">
         <v>280</v>
       </c>
       <c r="CE1" s="7" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="CF1" s="8" t="s">
         <v>198</v>
@@ -5891,7 +5956,7 @@
         <v>215</v>
       </c>
       <c r="CP1" s="8" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="CQ1" s="8" t="s">
         <v>515</v>
@@ -5930,22 +5995,22 @@
         <v>154</v>
       </c>
       <c r="DC1" s="8" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="DD1" s="18" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="DE1" s="18" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="DF1" s="18" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="DG1" s="18" t="s">
+        <v>844</v>
+      </c>
+      <c r="DH1" s="18" t="s">
         <v>845</v>
-      </c>
-      <c r="DH1" s="18" t="s">
-        <v>846</v>
       </c>
       <c r="DI1" s="15" t="s">
         <v>136</v>
@@ -5954,28 +6019,28 @@
         <v>135</v>
       </c>
       <c r="DK1" s="15" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="DL1" s="15" t="s">
+        <v>567</v>
+      </c>
+      <c r="DM1" s="15" t="s">
         <v>568</v>
       </c>
-      <c r="DM1" s="15" t="s">
-        <v>569</v>
-      </c>
       <c r="DN1" s="15" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="DO1" s="15" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="DP1" s="15" t="s">
+        <v>605</v>
+      </c>
+      <c r="DQ1" s="15" t="s">
+        <v>815</v>
+      </c>
+      <c r="DR1" s="15" t="s">
         <v>606</v>
-      </c>
-      <c r="DQ1" s="15" t="s">
-        <v>816</v>
-      </c>
-      <c r="DR1" s="15" t="s">
-        <v>607</v>
       </c>
       <c r="DS1" s="15" t="s">
         <v>524</v>
@@ -5987,19 +6052,19 @@
         <v>237</v>
       </c>
       <c r="DV1" s="15" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="DW1" s="15" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="DX1" s="15" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="DY1" s="15" t="s">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="DZ1" s="15" t="s">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="EA1" s="15" t="s">
         <v>556</v>
@@ -6008,22 +6073,22 @@
         <v>559</v>
       </c>
       <c r="EC1" s="21" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="ED1" s="25" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="EE1" s="12" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="EF1" s="14" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="EG1" s="12" t="s">
         <v>234</v>
       </c>
       <c r="EH1" s="12" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="EI1" s="12" t="s">
         <v>286</v>
@@ -6038,19 +6103,19 @@
         <v>125</v>
       </c>
       <c r="EM1" s="17" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="EN1" s="17" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="EO1" s="17" t="s">
         <v>558</v>
       </c>
       <c r="EP1" s="19" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="EQ1" s="19" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="ER1" s="19" t="s">
         <v>126</v>
@@ -6065,7 +6130,7 @@
         <v>231</v>
       </c>
       <c r="EV1" s="20" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="EW1" s="20" t="s">
         <v>232</v>
@@ -7503,13 +7568,13 @@
     </row>
     <row r="10" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>51</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D10" s="2">
         <v>300</v>
@@ -7869,7 +7934,7 @@
         <v>55</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D12" s="2">
         <v>200</v>
@@ -8571,7 +8636,7 @@
     </row>
     <row r="16" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>278</v>
@@ -9655,7 +9720,7 @@
     </row>
     <row r="22" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>53</v>
@@ -10541,7 +10606,7 @@
     </row>
     <row r="27" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>51</v>
@@ -11073,7 +11138,7 @@
     </row>
     <row r="30" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>278</v>
@@ -11251,7 +11316,7 @@
     </row>
     <row r="31" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>278</v>
@@ -11429,7 +11494,7 @@
     </row>
     <row r="32" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>278</v>
@@ -12317,13 +12382,13 @@
     </row>
     <row r="37" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D37" s="2">
         <v>300</v>
@@ -17113,7 +17178,7 @@
     </row>
     <row r="64" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>50</v>
@@ -18899,7 +18964,7 @@
     </row>
     <row r="74" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>51</v>
@@ -20151,7 +20216,7 @@
     </row>
     <row r="81" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>51</v>
@@ -20329,7 +20394,7 @@
     </row>
     <row r="82" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>50</v>
@@ -20693,7 +20758,7 @@
     </row>
     <row r="84" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>51</v>
@@ -20869,7 +20934,7 @@
     </row>
     <row r="85" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>51</v>
@@ -21923,10 +21988,10 @@
     </row>
     <row r="91" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>679</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>680</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>681</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>63</v>
@@ -23173,7 +23238,7 @@
     </row>
     <row r="98" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>49</v>
@@ -25341,7 +25406,7 @@
         <v>53</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D110" s="2">
         <v>300</v>
@@ -27999,7 +28064,7 @@
     </row>
     <row r="125" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A125" s="13" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>278</v>
@@ -28899,7 +28964,7 @@
     </row>
     <row r="130" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>151</v>
@@ -30137,7 +30202,7 @@
     </row>
     <row r="137" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A137" s="13" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>278</v>
@@ -30495,7 +30560,7 @@
     </row>
     <row r="139" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>52</v>
@@ -30857,7 +30922,7 @@
     </row>
     <row r="141" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>55</v>
@@ -31931,7 +31996,7 @@
     </row>
     <row r="147" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>51</v>
@@ -32107,7 +32172,7 @@
     </row>
     <row r="148" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>51</v>
@@ -32283,7 +32348,7 @@
     </row>
     <row r="149" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>50</v>
@@ -32637,13 +32702,13 @@
     </row>
     <row r="151" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D151" s="2">
         <v>300</v>
@@ -32817,7 +32882,7 @@
     </row>
     <row r="152" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>53</v>
@@ -32996,13 +33061,13 @@
     </row>
     <row r="153" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D153" s="2">
         <v>300</v>
@@ -33176,7 +33241,7 @@
     </row>
     <row r="154" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>51</v>
@@ -33352,7 +33417,7 @@
     </row>
     <row r="155" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>54</v>
@@ -33528,7 +33593,7 @@
     </row>
     <row r="156" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>53</v>
@@ -33706,7 +33771,7 @@
     </row>
     <row r="157" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>278</v>
@@ -33880,13 +33945,13 @@
     </row>
     <row r="158" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>278</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="D158" s="2">
         <v>1500</v>
@@ -34060,13 +34125,13 @@
     </row>
     <row r="159" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>278</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="D159" s="2">
         <v>1500</v>
@@ -34250,7 +34315,7 @@
     </row>
     <row r="160" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>197</v>
@@ -34422,7 +34487,7 @@
     </row>
     <row r="161" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>51</v>
@@ -34606,7 +34671,7 @@
     </row>
     <row r="162" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>51</v>
@@ -34782,7 +34847,7 @@
     </row>
     <row r="163" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>51</v>
@@ -34962,7 +35027,7 @@
     </row>
     <row r="164" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>53</v>
@@ -35140,7 +35205,7 @@
     </row>
     <row r="165" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>51</v>
@@ -35316,7 +35381,7 @@
     </row>
     <row r="166" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>50</v>
@@ -35498,7 +35563,7 @@
     </row>
     <row r="167" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>53</v>
@@ -35676,7 +35741,7 @@
     </row>
     <row r="168" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>55</v>
@@ -35850,7 +35915,7 @@
     </row>
     <row r="169" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>55</v>
@@ -36028,7 +36093,7 @@
     </row>
     <row r="170" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>53</v>
@@ -36204,7 +36269,7 @@
     </row>
     <row r="171" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>55</v>
@@ -36221,7 +36286,7 @@
       </c>
       <c r="G171" s="2"/>
       <c r="H171" s="2">
-        <f t="shared" ref="H171" si="7">SUM(I171:DF171)</f>
+        <f t="shared" ref="H171:H172" si="7">SUM(I171:DF171)</f>
         <v>135</v>
       </c>
       <c r="I171" s="2"/>
@@ -36379,19 +36444,38 @@
       <c r="EW171" s="2"/>
     </row>
     <row r="172" spans="1:153" x14ac:dyDescent="0.25">
-      <c r="A172" s="1"/>
-      <c r="B172" s="1"/>
-      <c r="C172" s="2"/>
-      <c r="D172" s="2"/>
-      <c r="E172" s="2"/>
-      <c r="F172" s="2"/>
-      <c r="G172" s="2"/>
-      <c r="H172" s="2"/>
+      <c r="A172" s="1" t="s">
+        <v>1062</v>
+      </c>
+      <c r="B172" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C172" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="D172" s="2">
+        <v>300</v>
+      </c>
+      <c r="E172" s="2">
+        <v>120</v>
+      </c>
+      <c r="F172" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G172" s="2">
+        <v>180</v>
+      </c>
+      <c r="H172" s="2">
+        <f t="shared" si="7"/>
+        <v>120</v>
+      </c>
       <c r="I172" s="2"/>
       <c r="J172" s="2"/>
       <c r="K172" s="2"/>
       <c r="L172" s="2"/>
-      <c r="M172" s="2"/>
+      <c r="M172" s="2">
+        <v>60</v>
+      </c>
       <c r="N172" s="2"/>
       <c r="O172" s="2"/>
       <c r="P172" s="2"/>
@@ -36435,7 +36519,9 @@
       <c r="BB172" s="2"/>
       <c r="BC172" s="2"/>
       <c r="BD172" s="2"/>
-      <c r="BE172" s="2"/>
+      <c r="BE172" s="2">
+        <v>30</v>
+      </c>
       <c r="BF172" s="2"/>
       <c r="BG172" s="2"/>
       <c r="BH172" s="2"/>
@@ -36470,7 +36556,9 @@
       <c r="CK172" s="2"/>
       <c r="CL172" s="2"/>
       <c r="CM172" s="2"/>
-      <c r="CN172" s="2"/>
+      <c r="CN172" s="2">
+        <v>30</v>
+      </c>
       <c r="CO172" s="2"/>
       <c r="CP172" s="2"/>
       <c r="CQ172" s="2"/>
@@ -48691,13 +48779,13 @@
         <v>524</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>141</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>570</v>
+        <v>569</v>
       </c>
       <c r="J1" s="8" t="s">
         <v>237</v>
@@ -48712,10 +48800,10 @@
         <v>283</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
       <c r="P1" s="8" t="s">
         <v>132</v>
@@ -55289,9 +55377,11 @@
     <row r="172" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="str">
         <f>IF(receta!A172="","",receta!A172)</f>
-        <v/>
-      </c>
-      <c r="B172" s="2"/>
+        <v>Gold Rush</v>
+      </c>
+      <c r="B172" s="2">
+        <v>1</v>
+      </c>
       <c r="C172" s="2"/>
       <c r="D172" s="2"/>
       <c r="E172" s="2"/>
@@ -58165,7 +58255,7 @@
         <v>72</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>318</v>
@@ -58180,7 +58270,7 @@
         <v>315</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>316</v>
@@ -58189,16 +58279,16 @@
         <v>317</v>
       </c>
       <c r="J1" s="7" t="s">
+        <v>763</v>
+      </c>
+      <c r="K1" s="7" t="s">
         <v>764</v>
       </c>
-      <c r="K1" s="7" t="s">
-        <v>765</v>
-      </c>
       <c r="L1" s="7" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="270" x14ac:dyDescent="0.25">
@@ -58226,7 +58316,7 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="4" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58235,7 +58325,7 @@
         <v>Alejandra</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>366</v>
@@ -58272,7 +58362,7 @@
         <v>239</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="5"/>
@@ -58287,7 +58377,7 @@
         <v>Alexander</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>448</v>
@@ -58308,7 +58398,7 @@
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
       <c r="M5" s="4" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="270" x14ac:dyDescent="0.25">
@@ -58317,7 +58407,7 @@
         <v>Amaretto Sour</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>352</v>
@@ -58336,7 +58426,7 @@
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="4" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="270" x14ac:dyDescent="0.25">
@@ -58362,7 +58452,7 @@
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="4" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="210" x14ac:dyDescent="0.25">
@@ -58388,7 +58478,7 @@
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="4" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -58416,7 +58506,7 @@
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
       <c r="M9" s="1" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="210" x14ac:dyDescent="0.25">
@@ -58425,10 +58515,10 @@
         <v>Andes Refresh</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="11"/>
@@ -58448,10 +58538,10 @@
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="4" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -58462,7 +58552,7 @@
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="4" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58471,10 +58561,10 @@
         <v>Arándano Sour</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>553</v>
@@ -58510,7 +58600,7 @@
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="4" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58538,7 +58628,7 @@
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="4" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58562,7 +58652,7 @@
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="4" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -58574,13 +58664,13 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -58666,7 +58756,7 @@
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="4" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -58699,10 +58789,10 @@
         <v>Borgoña</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="1"/>
@@ -58718,7 +58808,7 @@
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="4" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="375" x14ac:dyDescent="0.25">
@@ -58727,17 +58817,17 @@
         <v>Caipiriña</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1" t="s">
+        <v>570</v>
+      </c>
+      <c r="F22" s="5" t="s">
         <v>571</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>572</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="1"/>
@@ -58745,7 +58835,9 @@
       <c r="J22" s="1"/>
       <c r="K22" s="5"/>
       <c r="L22" s="5"/>
-      <c r="M22" s="1"/>
+      <c r="M22" s="4" t="s">
+        <v>1073</v>
+      </c>
     </row>
     <row r="23" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A23" s="1" t="str">
@@ -58766,7 +58858,7 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="4" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="345" x14ac:dyDescent="0.25">
@@ -58814,7 +58906,7 @@
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="4" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58842,7 +58934,7 @@
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="4" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="375" x14ac:dyDescent="0.25">
@@ -58851,13 +58943,13 @@
         <v>Chupilca</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
@@ -58868,7 +58960,7 @@
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="4" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58881,7 +58973,7 @@
         <v>458</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>528</v>
@@ -58893,14 +58985,14 @@
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
       <c r="J28" s="1" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
       <c r="L28" s="5"/>
       <c r="M28" s="4" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="360" x14ac:dyDescent="0.25">
@@ -58926,7 +59018,7 @@
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="4" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58935,13 +59027,13 @@
         <v>Cléry</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
@@ -58952,7 +59044,7 @@
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="4" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58961,22 +59053,22 @@
         <v>Cléry Chirimoya</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>425</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -58984,7 +59076,7 @@
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="4" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -58993,10 +59085,10 @@
         <v>Cléry Durazno</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1" t="s">
@@ -59019,10 +59111,10 @@
         <v>Clover Club</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>548</v>
@@ -59040,7 +59132,7 @@
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="4" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="255" x14ac:dyDescent="0.25">
@@ -59050,7 +59142,7 @@
       </c>
       <c r="B34" s="1"/>
       <c r="C34" s="4" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="1" t="s">
@@ -59066,7 +59158,7 @@
       <c r="K34" s="5"/>
       <c r="L34" s="5"/>
       <c r="M34" s="4" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -59075,10 +59167,10 @@
         <v>Cosmo Patagonia</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="1"/>
@@ -59110,7 +59202,7 @@
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59119,10 +59211,10 @@
         <v>Crepúsculo</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="4" t="s">
@@ -59138,7 +59230,7 @@
       <c r="K37" s="5"/>
       <c r="L37" s="5"/>
       <c r="M37" s="4" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="255" x14ac:dyDescent="0.25">
@@ -59164,7 +59256,7 @@
       <c r="K38" s="5"/>
       <c r="L38" s="5"/>
       <c r="M38" s="4" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59186,7 +59278,7 @@
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="4" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -59207,16 +59299,16 @@
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="1" t="s">
+        <v>927</v>
+      </c>
+      <c r="I40" s="5" t="s">
         <v>928</v>
-      </c>
-      <c r="I40" s="5" t="s">
-        <v>929</v>
       </c>
       <c r="J40" s="4"/>
       <c r="K40" s="5"/>
       <c r="L40" s="5"/>
       <c r="M40" s="4" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -59225,10 +59317,10 @@
         <v>Dama Blanca</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="1"/>
@@ -59240,7 +59332,7 @@
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
       <c r="M41" s="4" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59266,7 +59358,7 @@
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="M42" s="4" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="270" x14ac:dyDescent="0.25">
@@ -59276,10 +59368,10 @@
       </c>
       <c r="B43" s="1"/>
       <c r="C43" s="4" t="s">
+        <v>590</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>591</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>592</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="5"/>
@@ -59294,7 +59386,7 @@
       <c r="K43" s="5"/>
       <c r="L43" s="5"/>
       <c r="M43" s="4" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -59323,10 +59415,10 @@
         <v>Dry Martini</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>392</v>
@@ -59340,7 +59432,7 @@
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
       <c r="M45" s="4" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="285" x14ac:dyDescent="0.25">
@@ -59349,11 +59441,11 @@
         <v>El Amor en los Tiempos del Covid</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C46" s="4"/>
       <c r="D46" s="4" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>185</v>
@@ -59365,16 +59457,16 @@
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
       <c r="J46" s="4" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="K46" s="5" t="s">
+        <v>1032</v>
+      </c>
+      <c r="L46" s="4" t="s">
         <v>1034</v>
       </c>
-      <c r="L46" s="4" t="s">
-        <v>1036</v>
-      </c>
       <c r="M46" s="4" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -59402,7 +59494,7 @@
       <c r="K47" s="5"/>
       <c r="L47" s="5"/>
       <c r="M47" s="4" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="315" x14ac:dyDescent="0.25">
@@ -59415,13 +59507,13 @@
         <v>380</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E48" s="1" t="s">
+        <v>596</v>
+      </c>
+      <c r="F48" s="5" t="s">
         <v>597</v>
-      </c>
-      <c r="F48" s="5" t="s">
-        <v>598</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="1"/>
@@ -59438,19 +59530,19 @@
       </c>
       <c r="B49" s="1"/>
       <c r="C49" s="4" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>372</v>
       </c>
       <c r="E49" s="1" t="s">
+        <v>768</v>
+      </c>
+      <c r="F49" s="5" t="s">
         <v>769</v>
       </c>
-      <c r="F49" s="5" t="s">
-        <v>770</v>
-      </c>
       <c r="G49" s="4" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -59458,7 +59550,7 @@
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
       <c r="M49" s="4" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="255" x14ac:dyDescent="0.25">
@@ -59468,7 +59560,7 @@
       </c>
       <c r="B50" s="1"/>
       <c r="C50" s="4" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="4" t="s">
@@ -59478,7 +59570,7 @@
         <v>481</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>326</v>
@@ -59490,7 +59582,7 @@
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
       <c r="M50" s="4" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -59512,7 +59604,7 @@
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
       <c r="M51" s="1" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="150" x14ac:dyDescent="0.25">
@@ -59544,7 +59636,7 @@
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
       <c r="M52" s="4" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="390" x14ac:dyDescent="0.25">
@@ -59566,7 +59658,7 @@
         <v>404</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>384</v>
@@ -59578,7 +59670,7 @@
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="4" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59588,7 +59680,7 @@
       </c>
       <c r="B54" s="1"/>
       <c r="C54" s="4" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="1"/>
@@ -59604,7 +59696,7 @@
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
       <c r="M54" s="4" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
@@ -59650,7 +59742,7 @@
         <v>473</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -59658,7 +59750,7 @@
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
       <c r="M56" s="4" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59686,7 +59778,7 @@
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
       <c r="M57" s="4" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="150" x14ac:dyDescent="0.25">
@@ -59695,7 +59787,7 @@
         <v>Frangelico Sour</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>338</v>
@@ -59710,7 +59802,7 @@
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="4" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59719,10 +59811,10 @@
         <v>French 75</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>358</v>
@@ -59740,7 +59832,7 @@
       <c r="K59" s="5"/>
       <c r="L59" s="5"/>
       <c r="M59" s="4" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -59762,7 +59854,7 @@
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
       <c r="M60" s="4" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="165" x14ac:dyDescent="0.25">
@@ -59778,10 +59870,10 @@
         <v>388</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="4"/>
@@ -59790,7 +59882,7 @@
       <c r="K61" s="1"/>
       <c r="L61" s="1"/>
       <c r="M61" s="4" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="345" x14ac:dyDescent="0.25">
@@ -59800,7 +59892,7 @@
       </c>
       <c r="B62" s="1"/>
       <c r="C62" s="4" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D62" s="1"/>
       <c r="E62" s="4" t="s">
@@ -59816,7 +59908,7 @@
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
       <c r="M62" s="4" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59843,16 +59935,16 @@
         <v>337</v>
       </c>
       <c r="J63" s="1" t="s">
+        <v>765</v>
+      </c>
+      <c r="K63" s="5" t="s">
         <v>766</v>
       </c>
-      <c r="K63" s="5" t="s">
-        <v>767</v>
-      </c>
       <c r="L63" s="4" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="M63" s="4" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -59862,7 +59954,7 @@
       </c>
       <c r="B64" s="1"/>
       <c r="C64" s="4" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
@@ -59874,7 +59966,7 @@
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
       <c r="M64" s="4" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59884,7 +59976,7 @@
       </c>
       <c r="B65" s="1"/>
       <c r="C65" s="4" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>169</v>
@@ -59898,7 +59990,7 @@
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
       <c r="M65" s="1" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="375" x14ac:dyDescent="0.25">
@@ -59908,10 +60000,10 @@
       </c>
       <c r="B66" s="1"/>
       <c r="C66" s="4" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
@@ -59922,7 +60014,7 @@
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
       <c r="M66" s="4" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="67" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59948,7 +60040,7 @@
       <c r="K67" s="5"/>
       <c r="L67" s="5"/>
       <c r="M67" s="4" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="68" spans="1:13" ht="330" x14ac:dyDescent="0.25">
@@ -59958,10 +60050,10 @@
       </c>
       <c r="B68" s="1"/>
       <c r="C68" s="1" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>165</v>
@@ -59976,7 +60068,7 @@
       <c r="K68" s="5"/>
       <c r="L68" s="5"/>
       <c r="M68" s="4" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
     </row>
     <row r="69" spans="1:13" ht="300" x14ac:dyDescent="0.25">
@@ -60004,7 +60096,7 @@
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
       <c r="M69" s="4" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -60032,7 +60124,7 @@
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
       <c r="M70" s="4" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -60058,7 +60150,7 @@
       <c r="K71" s="5"/>
       <c r="L71" s="5"/>
       <c r="M71" s="4" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
     </row>
     <row r="72" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60067,13 +60159,13 @@
         <v>Jote</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="E72" s="1"/>
       <c r="F72" s="5"/>
@@ -60088,7 +60180,7 @@
       <c r="K72" s="5"/>
       <c r="L72" s="5"/>
       <c r="M72" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
     </row>
     <row r="73" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -60101,7 +60193,7 @@
       </c>
       <c r="C73" s="4"/>
       <c r="D73" s="4" t="s">
-        <v>563</v>
+        <v>1069</v>
       </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
@@ -60111,7 +60203,9 @@
       <c r="J73" s="1"/>
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
-      <c r="M73" s="1"/>
+      <c r="M73" s="4" t="s">
+        <v>1070</v>
+      </c>
     </row>
     <row r="74" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="str">
@@ -60119,26 +60213,26 @@
         <v>Julieta Flowers</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>706</v>
+        <v>705</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E74" s="1" t="s">
+        <v>727</v>
+      </c>
+      <c r="F74" s="5" t="s">
         <v>728</v>
-      </c>
-      <c r="F74" s="5" t="s">
-        <v>729</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="1" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="J74" s="1"/>
       <c r="K74" s="5"/>
@@ -60164,7 +60258,7 @@
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
       <c r="M75" s="4" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="76" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60200,10 +60294,10 @@
       </c>
       <c r="B77" s="1"/>
       <c r="C77" s="4" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
@@ -60214,7 +60308,7 @@
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
       <c r="M77" s="4" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="78" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -60228,19 +60322,19 @@
       </c>
       <c r="D78" s="1"/>
       <c r="E78" s="1" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="G78" s="5"/>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
       <c r="J78" s="1" t="s">
-        <v>789</v>
+        <v>788</v>
       </c>
       <c r="K78" s="5" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="L78" s="5"/>
       <c r="M78" s="1"/>
@@ -60290,7 +60384,7 @@
       </c>
       <c r="B81" s="1"/>
       <c r="C81" s="4" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D81" s="4"/>
       <c r="E81" s="1"/>
@@ -60309,25 +60403,27 @@
         <v>Mai Tai Piña</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D82" s="4"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
       <c r="G82" s="1"/>
       <c r="H82" s="1" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="I82" s="5" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="J82" s="1"/>
       <c r="K82" s="1"/>
       <c r="L82" s="1"/>
-      <c r="M82" s="1"/>
+      <c r="M82" s="4" t="s">
+        <v>1072</v>
+      </c>
     </row>
     <row r="83" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="str">
@@ -60336,7 +60432,7 @@
       </c>
       <c r="B83" s="1"/>
       <c r="C83" s="4" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>304</v>
@@ -60354,7 +60450,7 @@
       <c r="K83" s="5"/>
       <c r="L83" s="5"/>
       <c r="M83" s="4" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
     </row>
     <row r="84" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60363,28 +60459,28 @@
         <v>Malta con Huevo</v>
       </c>
       <c r="B84" s="4" t="s">
+        <v>659</v>
+      </c>
+      <c r="C84" s="4" t="s">
         <v>660</v>
       </c>
-      <c r="C84" s="4" t="s">
-        <v>661</v>
-      </c>
       <c r="D84" s="4" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
       <c r="H84" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="J84" s="1"/>
       <c r="K84" s="1"/>
       <c r="L84" s="1"/>
       <c r="M84" s="4" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -60393,28 +60489,28 @@
         <v>Malta con Leche Condensada</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
       <c r="H85" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="J85" s="1"/>
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
       <c r="M85" s="4" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -60423,7 +60519,7 @@
         <v>Mango Sour</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C86" s="4"/>
       <c r="D86" s="1"/>
@@ -60444,18 +60540,18 @@
       </c>
       <c r="B87" s="1"/>
       <c r="C87" s="4" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="D87" s="1"/>
       <c r="E87" s="1" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="G87" s="5"/>
       <c r="H87" s="1" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="I87" s="5" t="s">
         <v>373</v>
@@ -60464,7 +60560,7 @@
       <c r="K87" s="5"/>
       <c r="L87" s="5"/>
       <c r="M87" s="4" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="88" spans="1:13" ht="360" x14ac:dyDescent="0.25">
@@ -60473,13 +60569,13 @@
         <v>Maqui Sour</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
@@ -60489,18 +60585,20 @@
       <c r="J88" s="1"/>
       <c r="K88" s="1"/>
       <c r="L88" s="1"/>
-      <c r="M88" s="1"/>
-    </row>
-    <row r="89" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+      <c r="M88" s="4" t="s">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" ht="180" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="str">
         <f>IF(receta!A89="","",receta!A89)</f>
         <v>Margarita</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D89" s="1"/>
       <c r="E89" s="1" t="s">
@@ -60509,13 +60607,17 @@
       <c r="F89" s="5" t="s">
         <v>180</v>
       </c>
-      <c r="G89" s="5"/>
+      <c r="G89" s="4" t="s">
+        <v>1078</v>
+      </c>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
       <c r="J89" s="1"/>
       <c r="K89" s="5"/>
       <c r="L89" s="5"/>
-      <c r="M89" s="1"/>
+      <c r="M89" s="4" t="s">
+        <v>1076</v>
+      </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="str">
@@ -60526,7 +60628,7 @@
       <c r="C90" s="1"/>
       <c r="D90" s="1"/>
       <c r="E90" s="1" t="s">
-        <v>590</v>
+        <v>589</v>
       </c>
       <c r="F90" s="5" t="s">
         <v>410</v>
@@ -60545,10 +60647,10 @@
         <v>Melón con Vino</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D91" s="1"/>
       <c r="E91" s="1" t="s">
@@ -60571,10 +60673,10 @@
         <v>Michelada</v>
       </c>
       <c r="B92" s="4" t="s">
+        <v>842</v>
+      </c>
+      <c r="C92" s="4" t="s">
         <v>843</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>844</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>401</v>
@@ -60612,10 +60714,10 @@
       <c r="K93" s="1"/>
       <c r="L93" s="1"/>
       <c r="M93" s="4" t="s">
-        <v>1049</v>
-      </c>
-    </row>
-    <row r="94" spans="1:13" ht="180" x14ac:dyDescent="0.25">
+        <v>1047</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" ht="225" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="str">
         <f>IF(receta!A94="","",receta!A94)</f>
         <v>Mimosa</v>
@@ -60633,7 +60735,9 @@
       <c r="J94" s="1"/>
       <c r="K94" s="1"/>
       <c r="L94" s="1"/>
-      <c r="M94" s="1"/>
+      <c r="M94" s="4" t="s">
+        <v>1065</v>
+      </c>
     </row>
     <row r="95" spans="1:13" ht="225" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="str">
@@ -60641,10 +60745,10 @@
         <v>Mojito</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D95" s="4"/>
       <c r="E95" s="1"/>
@@ -60656,7 +60760,7 @@
       <c r="K95" s="1"/>
       <c r="L95" s="1"/>
       <c r="M95" s="4" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
     </row>
     <row r="96" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -60666,7 +60770,7 @@
       </c>
       <c r="B96" s="1"/>
       <c r="C96" s="4" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="D96" s="4"/>
       <c r="E96" s="1"/>
@@ -60686,16 +60790,16 @@
       </c>
       <c r="B97" s="1"/>
       <c r="C97" s="4" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="G97" s="1"/>
       <c r="H97" s="4"/>
@@ -60704,7 +60808,7 @@
       <c r="K97" s="1"/>
       <c r="L97" s="1"/>
       <c r="M97" s="4" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="98" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -60714,7 +60818,7 @@
       </c>
       <c r="B98" s="1"/>
       <c r="C98" s="4" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D98" s="4"/>
       <c r="E98" s="1"/>
@@ -60750,7 +60854,7 @@
       <c r="K99" s="5"/>
       <c r="L99" s="5"/>
       <c r="M99" s="4" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="100" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -60759,7 +60863,7 @@
         <v>Naranja Sour</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>371</v>
@@ -60786,7 +60890,7 @@
       </c>
       <c r="B101" s="1"/>
       <c r="C101" s="4" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D101" s="4"/>
       <c r="E101" s="4"/>
@@ -60824,7 +60928,7 @@
       <c r="K102" s="1"/>
       <c r="L102" s="1"/>
       <c r="M102" s="4" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
     </row>
     <row r="103" spans="1:13" ht="210" x14ac:dyDescent="0.25">
@@ -60834,7 +60938,7 @@
       </c>
       <c r="B103" s="1"/>
       <c r="C103" s="4" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D103" s="1"/>
       <c r="E103" s="1"/>
@@ -60846,7 +60950,7 @@
       <c r="K103" s="1"/>
       <c r="L103" s="1"/>
       <c r="M103" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="104" spans="1:13" ht="345" x14ac:dyDescent="0.25">
@@ -60855,10 +60959,10 @@
         <v>New York Sour</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D104" s="4" t="s">
         <v>482</v>
@@ -60876,7 +60980,7 @@
       <c r="K104" s="5"/>
       <c r="L104" s="5"/>
       <c r="M104" s="4" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="105" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -60902,7 +61006,7 @@
       <c r="K105" s="1"/>
       <c r="L105" s="1"/>
       <c r="M105" s="4" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
     </row>
     <row r="106" spans="1:13" ht="375" x14ac:dyDescent="0.25">
@@ -60911,32 +61015,32 @@
         <v>Old Fashioned</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C106" s="4"/>
       <c r="D106" s="4" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="I106" s="5" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="J106" s="1"/>
       <c r="K106" s="1"/>
       <c r="L106" s="1"/>
       <c r="M106" s="4" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="107" spans="1:13" ht="192" customHeight="1" x14ac:dyDescent="0.25">
@@ -60965,17 +61069,17 @@
         <v>Paloma</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D108" s="1"/>
       <c r="E108" s="1"/>
       <c r="F108" s="1"/>
       <c r="G108" s="1"/>
       <c r="H108" s="1" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="I108" s="5" t="s">
         <v>256</v>
@@ -60984,7 +61088,7 @@
       <c r="K108" s="1"/>
       <c r="L108" s="1"/>
       <c r="M108" s="4" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="109" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -60993,7 +61097,7 @@
         <v>Parrón</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C109" s="4"/>
       <c r="D109" s="4"/>
@@ -61013,16 +61117,16 @@
         <v>Penicilina</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="F110" s="5" t="s">
         <v>544</v>
@@ -61034,7 +61138,7 @@
       <c r="K110" s="5"/>
       <c r="L110" s="5"/>
       <c r="M110" s="4" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.25">
@@ -61077,7 +61181,9 @@
       <c r="F112" s="5" t="s">
         <v>483</v>
       </c>
-      <c r="G112" s="5"/>
+      <c r="G112" s="4" t="s">
+        <v>1079</v>
+      </c>
       <c r="H112" s="1"/>
       <c r="I112" s="5"/>
       <c r="J112" s="1"/>
@@ -61108,7 +61214,7 @@
       <c r="K113" s="5"/>
       <c r="L113" s="5"/>
       <c r="M113" s="4" t="s">
-        <v>934</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.25">
@@ -61183,10 +61289,10 @@
         <v>Piscola</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="D117" s="5"/>
       <c r="E117" s="1" t="s">
@@ -61202,7 +61308,7 @@
       <c r="K117" s="5"/>
       <c r="L117" s="5"/>
       <c r="M117" s="4" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="118" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -61211,10 +61317,10 @@
         <v>Pistón</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D118" s="1"/>
       <c r="E118" s="1" t="s">
@@ -61256,7 +61362,7 @@
       <c r="K119" s="5"/>
       <c r="L119" s="5"/>
       <c r="M119" s="4" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="120" spans="1:13" ht="75" x14ac:dyDescent="0.25">
@@ -61290,7 +61396,7 @@
       </c>
       <c r="B121" s="1"/>
       <c r="C121" s="4" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D121" s="1"/>
       <c r="E121" s="1"/>
@@ -61334,7 +61440,7 @@
       </c>
       <c r="B123" s="1"/>
       <c r="C123" s="4" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D123" s="4" t="s">
         <v>252</v>
@@ -61352,7 +61458,7 @@
       <c r="K123" s="5"/>
       <c r="L123" s="5"/>
       <c r="M123" s="4" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="124" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -61383,10 +61489,10 @@
         <v>Sangría</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D125" s="4" t="s">
         <v>393</v>
@@ -61432,7 +61538,7 @@
       </c>
       <c r="B127" s="1"/>
       <c r="C127" s="4" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D127" s="1"/>
       <c r="E127" s="1" t="s">
@@ -61468,7 +61574,7 @@
       <c r="K128" s="1"/>
       <c r="L128" s="1"/>
       <c r="M128" s="4" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="129" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -61481,7 +61587,7 @@
         <v>369</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
       <c r="E129" s="1"/>
       <c r="F129" s="1"/>
@@ -61492,7 +61598,7 @@
       <c r="K129" s="1"/>
       <c r="L129" s="1"/>
       <c r="M129" s="4" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="130" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -61515,7 +61621,7 @@
       <c r="L130" s="1"/>
       <c r="M130" s="1"/>
     </row>
-    <row r="131" spans="1:13" ht="210" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:13" ht="315" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="str">
         <f>IF(receta!A131="","",receta!A131)</f>
         <v>Sidecar</v>
@@ -61533,7 +61639,9 @@
       <c r="J131" s="1"/>
       <c r="K131" s="1"/>
       <c r="L131" s="1"/>
-      <c r="M131" s="1"/>
+      <c r="M131" s="4" t="s">
+        <v>1077</v>
+      </c>
     </row>
     <row r="132" spans="1:13" ht="165" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="str">
@@ -61558,7 +61666,7 @@
       <c r="K132" s="5"/>
       <c r="L132" s="5"/>
       <c r="M132" s="4" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.25">
@@ -61588,16 +61696,16 @@
       </c>
       <c r="B134" s="1"/>
       <c r="C134" s="4" t="s">
+        <v>586</v>
+      </c>
+      <c r="D134" s="4" t="s">
+        <v>595</v>
+      </c>
+      <c r="E134" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="F134" s="5" t="s">
         <v>587</v>
-      </c>
-      <c r="D134" s="4" t="s">
-        <v>596</v>
-      </c>
-      <c r="E134" s="4" t="s">
-        <v>589</v>
-      </c>
-      <c r="F134" s="5" t="s">
-        <v>588</v>
       </c>
       <c r="G134" s="5"/>
       <c r="H134" s="4"/>
@@ -61606,7 +61714,7 @@
       <c r="K134" s="5"/>
       <c r="L134" s="5"/>
       <c r="M134" s="4" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
     </row>
     <row r="135" spans="1:13" ht="300" x14ac:dyDescent="0.25">
@@ -61615,28 +61723,28 @@
         <v>Terremoto</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="E135" s="1"/>
       <c r="F135" s="1"/>
       <c r="G135" s="1"/>
       <c r="H135" s="1" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="I135" s="5" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="J135" s="1"/>
       <c r="K135" s="1"/>
       <c r="L135" s="1"/>
       <c r="M135" s="4" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
     </row>
     <row r="136" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -61645,10 +61753,10 @@
         <v>Terremoto (Sin Alcohol)</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D136" s="4"/>
       <c r="E136" s="1" t="s">
@@ -61676,13 +61784,13 @@
         <v>433</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="F137" s="5" t="s">
+        <v>1035</v>
+      </c>
+      <c r="G137" s="4" t="s">
         <v>1037</v>
-      </c>
-      <c r="G137" s="4" t="s">
-        <v>1039</v>
       </c>
       <c r="H137" s="1"/>
       <c r="I137" s="1"/>
@@ -61698,7 +61806,7 @@
       </c>
       <c r="B138" s="4"/>
       <c r="C138" s="4" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="D138" s="1"/>
       <c r="E138" s="1"/>
@@ -61710,7 +61818,7 @@
       <c r="K138" s="1"/>
       <c r="L138" s="1"/>
       <c r="M138" s="4" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
     </row>
     <row r="139" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -61720,7 +61828,7 @@
       </c>
       <c r="B139" s="1"/>
       <c r="C139" s="4" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D139" s="4"/>
       <c r="E139" s="1"/>
@@ -61743,22 +61851,22 @@
         <v>Tropezón</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="D140" s="4" t="s">
         <v>345</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="F140" s="5" t="s">
+        <v>1021</v>
+      </c>
+      <c r="G140" s="4" t="s">
         <v>1023</v>
-      </c>
-      <c r="G140" s="4" t="s">
-        <v>1025</v>
       </c>
       <c r="H140" s="1"/>
       <c r="I140" s="1"/>
@@ -61770,7 +61878,7 @@
       </c>
       <c r="L140" s="5"/>
       <c r="M140" s="4" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="141" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -61779,19 +61887,19 @@
         <v>Vaina</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="E141" s="4" t="s">
+        <v>611</v>
+      </c>
+      <c r="F141" s="4" t="s">
         <v>612</v>
-      </c>
-      <c r="F141" s="4" t="s">
-        <v>613</v>
       </c>
       <c r="G141" s="4"/>
       <c r="H141" s="1"/>
@@ -61808,7 +61916,7 @@
       </c>
       <c r="B142" s="1"/>
       <c r="C142" s="4" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D142" s="4"/>
       <c r="E142" s="4" t="s">
@@ -61831,10 +61939,10 @@
         <v>Vampiro</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D143" s="4" t="s">
         <v>540</v>
@@ -61852,7 +61960,7 @@
       <c r="K143" s="1"/>
       <c r="L143" s="1"/>
       <c r="M143" s="4" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
     </row>
     <row r="144" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -61875,20 +61983,20 @@
       </c>
       <c r="G144" s="1"/>
       <c r="H144" s="1" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
       <c r="I144" s="5" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="K144" s="5" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
       <c r="L144" s="1"/>
       <c r="M144" s="4" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="145" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -61897,13 +62005,13 @@
         <v>Vermouth con Soda</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>546</v>
@@ -61918,7 +62026,7 @@
       <c r="K145" s="1"/>
       <c r="L145" s="1"/>
       <c r="M145" s="4" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="146" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -61928,7 +62036,7 @@
       </c>
       <c r="B146" s="1"/>
       <c r="C146" s="4" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D146" s="1"/>
       <c r="E146" s="1"/>
@@ -61948,14 +62056,14 @@
       </c>
       <c r="B147" s="1"/>
       <c r="C147" s="4" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D147" s="4"/>
       <c r="E147" s="1" t="s">
+        <v>712</v>
+      </c>
+      <c r="F147" s="5" t="s">
         <v>713</v>
-      </c>
-      <c r="F147" s="5" t="s">
-        <v>714</v>
       </c>
       <c r="G147" s="5"/>
       <c r="H147" s="1"/>
@@ -61964,7 +62072,7 @@
       <c r="K147" s="5"/>
       <c r="L147" s="5"/>
       <c r="M147" s="4" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="148" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -61974,14 +62082,14 @@
       </c>
       <c r="B148" s="1"/>
       <c r="C148" s="4" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="D148" s="1"/>
       <c r="E148" s="1" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="G148" s="5"/>
       <c r="H148" s="1"/>
@@ -61998,16 +62106,16 @@
       </c>
       <c r="B149" s="1"/>
       <c r="C149" s="4" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="E149" s="1" t="s">
+        <v>706</v>
+      </c>
+      <c r="F149" s="5" t="s">
         <v>707</v>
-      </c>
-      <c r="F149" s="5" t="s">
-        <v>708</v>
       </c>
       <c r="G149" s="5"/>
       <c r="H149" s="1"/>
@@ -62015,7 +62123,9 @@
       <c r="J149" s="1"/>
       <c r="K149" s="5"/>
       <c r="L149" s="5"/>
-      <c r="M149" s="1"/>
+      <c r="M149" s="4" t="s">
+        <v>1074</v>
+      </c>
     </row>
     <row r="150" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="str">
@@ -62023,7 +62133,7 @@
         <v>Whisky Sour</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C150" s="4" t="s">
         <v>360</v>
@@ -62044,7 +62154,7 @@
       <c r="K150" s="1"/>
       <c r="L150" s="1"/>
       <c r="M150" s="4" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="151" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -62053,19 +62163,19 @@
         <v>Bramble</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="D151" s="4" t="s">
+        <v>789</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>791</v>
+      </c>
+      <c r="F151" s="1" t="s">
         <v>790</v>
-      </c>
-      <c r="E151" s="1" t="s">
-        <v>792</v>
-      </c>
-      <c r="F151" s="1" t="s">
-        <v>791</v>
       </c>
       <c r="G151" s="1"/>
       <c r="H151" s="1"/>
@@ -62073,7 +62183,9 @@
       <c r="J151" s="1"/>
       <c r="K151" s="1"/>
       <c r="L151" s="1"/>
-      <c r="M151" s="1"/>
+      <c r="M151" s="4" t="s">
+        <v>1068</v>
+      </c>
     </row>
     <row r="152" spans="1:13" ht="180" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="str">
@@ -62082,14 +62194,14 @@
       </c>
       <c r="B152" s="1"/>
       <c r="C152" s="4" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="D152" s="4"/>
       <c r="E152" s="1" t="s">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="G152" s="1"/>
       <c r="H152" s="1"/>
@@ -62098,7 +62210,7 @@
       <c r="K152" s="1"/>
       <c r="L152" s="1"/>
       <c r="M152" s="4" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="153" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -62107,19 +62219,19 @@
         <v>Gin Basil Smash</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="E153" s="4" t="s">
+        <v>793</v>
+      </c>
+      <c r="F153" s="1" t="s">
         <v>794</v>
-      </c>
-      <c r="F153" s="1" t="s">
-        <v>795</v>
       </c>
       <c r="G153" s="1"/>
       <c r="H153" s="1"/>
@@ -62136,43 +62248,45 @@
       </c>
       <c r="B154" s="1"/>
       <c r="C154" s="4" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="D154" s="26" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="E154" s="1" t="s">
+        <v>782</v>
+      </c>
+      <c r="F154" s="5" t="s">
         <v>783</v>
-      </c>
-      <c r="F154" s="5" t="s">
-        <v>784</v>
       </c>
       <c r="G154" s="5"/>
       <c r="H154" s="1"/>
       <c r="I154" s="5"/>
       <c r="J154" s="1" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="K154" s="5" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="L154" s="26" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
       <c r="M154" s="1"/>
     </row>
-    <row r="155" spans="1:13" ht="240" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:13" ht="330" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="str">
         <f>IF(receta!A155="","",receta!A155)</f>
         <v>Medias de Seda</v>
       </c>
       <c r="B155" s="4" t="s">
+        <v>798</v>
+      </c>
+      <c r="C155" s="4" t="s">
         <v>799</v>
       </c>
-      <c r="C155" s="4" t="s">
-        <v>800</v>
-      </c>
-      <c r="D155" s="4"/>
+      <c r="D155" s="4" t="s">
+        <v>1067</v>
+      </c>
       <c r="E155" s="1"/>
       <c r="F155" s="1"/>
       <c r="G155" s="1"/>
@@ -62181,7 +62295,9 @@
       <c r="J155" s="1"/>
       <c r="K155" s="1"/>
       <c r="L155" s="1"/>
-      <c r="M155" s="1"/>
+      <c r="M155" s="4" t="s">
+        <v>1066</v>
+      </c>
     </row>
     <row r="156" spans="1:13" ht="255" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="str">
@@ -62189,17 +62305,17 @@
         <v>Brandy Sour</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>727</v>
+        <v>726</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="D156" s="4"/>
       <c r="E156" s="1" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="G156" s="5"/>
       <c r="H156" s="1"/>
@@ -62215,10 +62331,10 @@
         <v>Juanito Rosado</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="D157" s="4" t="s">
         <v>434</v>
@@ -62243,17 +62359,17 @@
         <v>Vino Navegado</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="D158" s="10"/>
       <c r="E158" s="1" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="G158" s="1"/>
       <c r="H158" s="1"/>
@@ -62262,7 +62378,7 @@
       <c r="K158" s="1"/>
       <c r="L158" s="1"/>
       <c r="M158" s="10" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
     </row>
     <row r="159" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62271,32 +62387,32 @@
         <v>Cola de Mono</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="G159" s="5"/>
       <c r="H159" s="1" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="I159" s="10" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="J159" s="1"/>
       <c r="K159" s="1"/>
       <c r="L159" s="1"/>
       <c r="M159" s="4" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
     </row>
     <row r="160" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62305,22 +62421,22 @@
         <v>Chichón</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>1022</v>
+        <v>1020</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>1020</v>
+        <v>1018</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="H160" s="1"/>
       <c r="I160" s="5"/>
@@ -62328,7 +62444,7 @@
       <c r="K160" s="1"/>
       <c r="L160" s="1"/>
       <c r="M160" s="4" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="161" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -62337,10 +62453,10 @@
         <v>Ramos Fizz</v>
       </c>
       <c r="B161" s="4" t="s">
+        <v>839</v>
+      </c>
+      <c r="C161" s="4" t="s">
         <v>840</v>
-      </c>
-      <c r="C161" s="4" t="s">
-        <v>841</v>
       </c>
       <c r="D161" s="4"/>
       <c r="E161" s="1"/>
@@ -62359,17 +62475,17 @@
         <v>Gin Fizz</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="D162" s="4"/>
       <c r="E162" s="1" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="G162" s="5"/>
       <c r="H162" s="5"/>
@@ -62386,16 +62502,16 @@
       </c>
       <c r="B163" s="1"/>
       <c r="C163" s="4" t="s">
+        <v>852</v>
+      </c>
+      <c r="D163" s="4" t="s">
+        <v>851</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>854</v>
+      </c>
+      <c r="F163" s="5" t="s">
         <v>853</v>
-      </c>
-      <c r="D163" s="4" t="s">
-        <v>852</v>
-      </c>
-      <c r="E163" s="1" t="s">
-        <v>855</v>
-      </c>
-      <c r="F163" s="5" t="s">
-        <v>854</v>
       </c>
       <c r="G163" s="5"/>
       <c r="H163" s="1"/>
@@ -62404,7 +62520,7 @@
       <c r="K163" s="1"/>
       <c r="L163" s="1"/>
       <c r="M163" s="4" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
     </row>
     <row r="164" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62414,29 +62530,29 @@
       </c>
       <c r="B164" s="4"/>
       <c r="C164" s="4" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="G164" s="5"/>
       <c r="H164" s="1"/>
       <c r="I164" s="5"/>
       <c r="J164" s="1" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="K164" s="1" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="L164" s="1"/>
       <c r="M164" s="4" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
     </row>
     <row r="165" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62445,22 +62561,22 @@
         <v>Pihuelo</v>
       </c>
       <c r="B165" s="4" t="s">
+        <v>868</v>
+      </c>
+      <c r="C165" s="4" t="s">
         <v>869</v>
       </c>
-      <c r="C165" s="4" t="s">
-        <v>870</v>
-      </c>
       <c r="D165" s="4" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="E165" s="4" t="s">
+        <v>1029</v>
+      </c>
+      <c r="F165" s="5" t="s">
+        <v>1030</v>
+      </c>
+      <c r="G165" s="1" t="s">
         <v>1031</v>
-      </c>
-      <c r="F165" s="5" t="s">
-        <v>1032</v>
-      </c>
-      <c r="G165" s="1" t="s">
-        <v>1033</v>
       </c>
       <c r="H165" s="1"/>
       <c r="I165" s="5"/>
@@ -62468,7 +62584,7 @@
       <c r="K165" s="1"/>
       <c r="L165" s="1"/>
       <c r="M165" s="4" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
     </row>
     <row r="166" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62477,19 +62593,19 @@
         <v>Mojito Sandía</v>
       </c>
       <c r="B166" s="4" t="s">
+        <v>880</v>
+      </c>
+      <c r="C166" s="4" t="s">
         <v>881</v>
       </c>
-      <c r="C166" s="4" t="s">
-        <v>882</v>
-      </c>
       <c r="D166" s="4" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="E166" s="1" t="s">
+        <v>878</v>
+      </c>
+      <c r="F166" s="5" t="s">
         <v>879</v>
-      </c>
-      <c r="F166" s="5" t="s">
-        <v>880</v>
       </c>
       <c r="G166" s="5"/>
       <c r="H166" s="1"/>
@@ -62498,7 +62614,7 @@
       <c r="K166" s="1"/>
       <c r="L166" s="1"/>
       <c r="M166" s="4" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
     </row>
     <row r="167" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62508,7 +62624,7 @@
       </c>
       <c r="B167" s="1"/>
       <c r="C167" s="4" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="D167" s="4"/>
       <c r="E167" s="1"/>
@@ -62520,7 +62636,7 @@
       <c r="K167" s="1"/>
       <c r="L167" s="1"/>
       <c r="M167" s="4" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="168" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -62530,7 +62646,7 @@
       </c>
       <c r="B168" s="1"/>
       <c r="C168" s="4" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="D168" s="4"/>
       <c r="E168" s="1"/>
@@ -62542,7 +62658,7 @@
       <c r="K168" s="1"/>
       <c r="L168" s="1"/>
       <c r="M168" s="4" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="169" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -62551,10 +62667,10 @@
         <v>Chardonnay Sour</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="D169" s="4"/>
       <c r="E169" s="1"/>
@@ -62573,13 +62689,13 @@
         <v>Carmenere Sour</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>470</v>
@@ -62594,7 +62710,7 @@
       <c r="K170" s="1"/>
       <c r="L170" s="1"/>
       <c r="M170" s="4" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="171" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62603,13 +62719,13 @@
         <v>Jerez Sour</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="E171" s="1"/>
       <c r="F171" s="1"/>
@@ -62620,16 +62736,18 @@
       <c r="K171" s="1"/>
       <c r="L171" s="1"/>
       <c r="M171" s="4" t="s">
-        <v>904</v>
-      </c>
-    </row>
-    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
+        <v>903</v>
+      </c>
+    </row>
+    <row r="172" spans="1:13" ht="180" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="str">
         <f>IF(receta!A172="","",receta!A172)</f>
-        <v/>
-      </c>
-      <c r="B172" s="1"/>
-      <c r="C172" s="4"/>
+        <v>Gold Rush</v>
+      </c>
+      <c r="B172" s="4"/>
+      <c r="C172" s="4" t="s">
+        <v>1063</v>
+      </c>
       <c r="D172" s="4"/>
       <c r="E172" s="1"/>
       <c r="F172" s="1"/>
@@ -62639,7 +62757,9 @@
       <c r="J172" s="1"/>
       <c r="K172" s="1"/>
       <c r="L172" s="1"/>
-      <c r="M172" s="1"/>
+      <c r="M172" s="4" t="s">
+        <v>1064</v>
+      </c>
     </row>
     <row r="173" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="str">
@@ -64160,10 +64280,10 @@
         <v>62</v>
       </c>
       <c r="B2" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C2" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -64171,7 +64291,7 @@
         <v>67</v>
       </c>
       <c r="B3" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C3" t="s">
         <v>202</v>
@@ -64182,10 +64302,10 @@
         <v>68</v>
       </c>
       <c r="B4" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C4" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -64193,7 +64313,7 @@
         <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C5" t="s">
         <v>203</v>
@@ -64204,10 +64324,10 @@
         <v>69</v>
       </c>
       <c r="B6" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
       <c r="C6" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -64215,7 +64335,7 @@
         <v>70</v>
       </c>
       <c r="B7" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C7" t="s">
         <v>71</v>
@@ -64223,24 +64343,24 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="B8" t="s">
-        <v>782</v>
+        <v>781</v>
       </c>
       <c r="C8" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>807</v>
+      </c>
+      <c r="B9" t="s">
         <v>808</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>809</v>
-      </c>
-      <c r="C9" t="s">
-        <v>810</v>
       </c>
     </row>
   </sheetData>
@@ -64326,7 +64446,7 @@
         <v>428</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>768</v>
+        <v>767</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -64339,10 +64459,10 @@
     </row>
     <row r="11" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="23" t="s">
+        <v>701</v>
+      </c>
+      <c r="B11" s="23" t="s">
         <v>702</v>
-      </c>
-      <c r="B11" s="23" t="s">
-        <v>703</v>
       </c>
     </row>
   </sheetData>

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8BE3724-48E6-4676-B0F3-65925B6AA67B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75B28F7E-A49F-4E22-804E-3559E7BF14DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">complementos!$A$1:$AE$250</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">receta!$A$1:$EW$171</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">receta!$A$1:$EW$174</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">recurso!$A$1:$M$250</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1626" uniqueCount="1080">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1642" uniqueCount="1085">
   <si>
     <t>Ramazzotti Spritz</t>
   </si>
@@ -2939,12 +2939,6 @@
 Fue creado en los años 1970 en el Bar Basso de Milán. Según la leyenda, el bartender Mirko Stocchetto preparaba un Negroni, pero por error utilizó Prosecco en lugar de gin. El resultado fue tan agradable que decidió dejarlo en la carta como una nueva creación.</t>
   </si>
   <si>
-    <t>Maqui
-El maqui (Aristotelia chilensis) es una fruta nativa de Chile y del sur de Argentina, particularmente abundante en la zona centro-sur del territorio chileno. Se trata de una pequeña baya de color morado oscuro, casi negro, que crece en un arbusto silvestre del mismo nombre. Desde tiempos ancestrales, ha sido consumida por diversos pueblos originarios, especialmente por el pueblo mapuche, que le atribuye propiedades medicinales y la ha integrado de manera significativa en su cultura y alimentación.
-El fruto del maqui tiene un sabor dulce, aunque puede presentar un leve dejo astringente. Su forma recuerda a la de un arándano, aunque es más pequeño y de color más intenso. La temporada de cosecha del maqui se concentra durante el verano, entre los meses de diciembre y marzo, y en muchas zonas rurales se recolecta de forma manual directamente desde los arbustos silvestres.
-En la actualidad, el maqui ha sido reconocido como un "superalimento" debido a su excepcional contenido de antioxidantes, en particular antocianinas y polifenoles. Diversos estudios científicos han destacado sus posibles beneficios para la salud, como efectos antiinflamatorios, protectores cardiovasculares, fortalecimiento del sistema inmunológico y propiedades antienvejecimiento. Por ello, su consumo se ha extendido más allá de sus zonas de origen, tanto en su forma natural como en productos procesados como jugos, cápsulas, polvos, mermeladas y vinos artesanales.</t>
-  </si>
-  <si>
     <t>Flor de Jamaica.
 La flor de Jamaica, también conocida como hibisco (nombre científico Hibiscus sabdariffa), es la flor seca de una planta tropical originaria de África, aunque actualmente se cultiva ampliamente en América Latina, Asia y el Caribe. Su sabor es ácido y refrescante, similar al del arándano o el cranberry, y posee un atractivo color rubí que la hace muy apreciada en infusiones, cocina y coctelería. Es especialmente popular en México y otros países latinoamericanos. 
 En Chile, aunque no es una planta tradicional, su uso se ha extendido en los últimos años, principalmente por sus propiedades medicinales. Entre sus beneficios más destacados, la flor de Jamaica es rica en antioxidantes, especialmente flavonoides y antocianinas, y se le atribuyen efectos diuréticos, hipotensores, digestivos y cardioprotectores. 
@@ -4989,13 +4983,6 @@
 Afiche de la película Silk Stockings (1957), musical estadounidense dirigido por Rouben Mamoulian y protagonizado por Fred Astaire y Cyd Charisse. </t>
   </si>
   <si>
-    <t xml:space="preserve">Medias de Seda 1957
-Existe una película titulada Medias de Seda (Silk Stockings,(1957), musical estadounidense dirigido por Rouben Mamoulian y protagonizado por Fred Astaire y Cyd Charisse, ambientada en el contexto de la Guerra Fría.
-La historia comienza cuando tres torpes agentes soviéticos fracasan en su misión de recuperar en París a un compositor que ha desertado. Para resolver la situación, las autoridades envían a Ninotchka, una estricta y disciplinada emisaria encargada de completar la tarea y poner orden. Sin embargo, el contacto con la vida parisina, el romance y el mundo del espectáculo comienza a transformar su carácter, dando lugar a una comedia que mezcla sátira política, romance y números de baile. La película es recordada como uno de los últimos grandes musicales del período clásico de Hollywood y una de las actuaciones más elegantes de Astaire en su etapa final en el cine.
-El cóctel Medias de Seda, si bien no está documentado que su nombre sea una referencia explícita a esta película, comparte con ella un mismo imaginario: el glamour y la sofisticación asociada a la moda, el cabaret y los bares de mediados del siglo XX, cuando cine, música y coctelería formaban parte de un mismo universo cultural ligado a la vida nocturna y al espectáculo.
-</t>
-  </si>
-  <si>
     <t>bramble2.jpg
 Ilustración contemporánea inspirada en el cóctel Bramble.</t>
   </si>
@@ -5042,6 +5029,36 @@
   </si>
   <si>
     <t>Las mismas diez lucas/La caña infernal/El pisco salado no deja pensar/Una vez en la cama/Vergüenza total</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Medias de Seda 1957
+Existe una película titulada Medias de Seda (Silk Stockings, 1957), musical estadounidense dirigido por Rouben Mamoulian y protagonizado por Fred Astaire y Cyd Charisse, ambientada en el contexto de la Guerra Fría.
+La historia comienza cuando tres torpes agentes soviéticos fracasan en su misión de recuperar en París a un compositor que ha desertado. Para resolver la situación, las autoridades envían a Ninotchka, una estricta y disciplinada emisaria encargada de completar la tarea y poner orden. Sin embargo, el contacto con la vida parisina, el romance y el mundo del espectáculo comienza a transformar su carácter, dando lugar a una comedia que mezcla sátira política, romance y números de baile. La película es recordada como uno de los últimos grandes musicales del período clásico de Hollywood y una de las actuaciones más elegantes de Astaire en su etapa final en el cine.
+El cóctel Medias de Seda, si bien no está documentado que su nombre sea una referencia explícita a esta película, comparte con ella un mismo imaginario: el glamour y la sofisticación asociada a la moda, el cabaret y los bares de mediados del siglo XX, cuando cine, música y coctelería formaban parte de un mismo universo cultural ligado a la vida nocturna y al espectáculo.
+</t>
+  </si>
+  <si>
+    <t>Maqui
+El maqui (Aristotelia chilensis) es una fruta nativa de Chile y del sur de Argentina, particularmente abundante en la zona centro-sur del territorio chileno. Se trata de una pequeña baya de color morado oscuro, casi negro, que crece en un arbusto silvestre del mismo nombre. Desde tiempos ancestrales, ha sido consumida por diversos pueblos originarios, especialmente por el pueblo mapuche, que le atribuye propiedades medicinales y la ha integrado de manera significativa en su cultura y alimentación.
+El fruto del maqui tiene un sabor dulce, aunque puede presentar un leve dejo astringente. Su forma recuerda a la de un arándano, aunque es más pequeño y de color más intenso. La temporada de cosecha del maqui se concentra durante el verano, entre los meses de diciembre y marzo, y en muchas zonas rurales se recolecta de forma manual directamente desde los arbustos silvestres.
+En la actualidad, el maqui ha sido reconocido como un "superalimento" debido a su excepcional contenido de antioxidantes, en particular antocianinas y polifenoles. Diversos estudios científicos han destacado sus posibles beneficios para la salud, como efectos antiinflamatorios, protectores cardiovasculares, fortalecimiento del sistema inmunológico y propiedades antienvejecimiento. Por ello, su consumo se ha extendido más allá de sus zonas de origen, tanto en su forma natural como en productos procesados como jugos, cápsulas, polvos y mermeladas artesanales.</t>
+  </si>
+  <si>
+    <t>Campari &amp; Tonic</t>
+  </si>
+  <si>
+    <t>Campari Spritz</t>
+  </si>
+  <si>
+    <t>Campari.jpg
+Afiche publicitario de Bitter Campari, diseñado por el ilustrador italiano Leonetto Cappiello hacia la década de 1920.</t>
+  </si>
+  <si>
+    <t>Para un Spritz, lo ideal es usar un espumante seco y ligero, que aporte frescura sin dominar el aperitivo. La opción clásica es el Prosecco, el espumante tradicional del Spritz en Italia, pero en Chile suele tener un costo más elevado. Por ello, un espumante Brut es una muy buena alternativa local: conserva la acidez y la vivacidad necesarias para equilibrar el trago, sin hacerlo excesivamente dulce.</t>
+  </si>
+  <si>
+    <t>Schweppestonic.jpg
+Anuncio publicitario de Schweppes Tonic Water, publicado en la revista canadiense Maclean’s, 7 de julio de 1986.</t>
   </si>
 </sst>
 </file>
@@ -5719,10 +5736,10 @@
         <v>78</v>
       </c>
       <c r="O1" s="27" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="P1" s="27" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="Q1" s="27" t="s">
         <v>79</v>
@@ -5737,10 +5754,10 @@
         <v>565</v>
       </c>
       <c r="U1" s="27" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="V1" s="27" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="W1" s="27" t="s">
         <v>80</v>
@@ -5755,16 +5772,16 @@
         <v>196</v>
       </c>
       <c r="AA1" s="27" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="AB1" s="27" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="AC1" s="27" t="s">
+        <v>900</v>
+      </c>
+      <c r="AD1" s="27" t="s">
         <v>901</v>
-      </c>
-      <c r="AD1" s="27" t="s">
-        <v>902</v>
       </c>
       <c r="AE1" s="27" t="s">
         <v>82</v>
@@ -5818,13 +5835,13 @@
         <v>200</v>
       </c>
       <c r="AV1" s="27" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="AW1" s="27" t="s">
         <v>209</v>
       </c>
       <c r="AX1" s="27" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="AY1" s="27" t="s">
         <v>230</v>
@@ -5914,10 +5931,10 @@
         <v>152</v>
       </c>
       <c r="CB1" s="8" t="s">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="CC1" s="8" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="CD1" s="7" t="s">
         <v>280</v>
@@ -5956,7 +5973,7 @@
         <v>215</v>
       </c>
       <c r="CP1" s="8" t="s">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="CQ1" s="8" t="s">
         <v>515</v>
@@ -5995,22 +6012,22 @@
         <v>154</v>
       </c>
       <c r="DC1" s="8" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="DD1" s="18" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="DE1" s="18" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="DF1" s="18" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="DG1" s="18" t="s">
+        <v>843</v>
+      </c>
+      <c r="DH1" s="18" t="s">
         <v>844</v>
-      </c>
-      <c r="DH1" s="18" t="s">
-        <v>845</v>
       </c>
       <c r="DI1" s="15" t="s">
         <v>136</v>
@@ -6019,7 +6036,7 @@
         <v>135</v>
       </c>
       <c r="DK1" s="15" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="DL1" s="15" t="s">
         <v>567</v>
@@ -6028,19 +6045,19 @@
         <v>568</v>
       </c>
       <c r="DN1" s="15" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="DO1" s="15" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="DP1" s="15" t="s">
+        <v>604</v>
+      </c>
+      <c r="DQ1" s="15" t="s">
+        <v>814</v>
+      </c>
+      <c r="DR1" s="15" t="s">
         <v>605</v>
-      </c>
-      <c r="DQ1" s="15" t="s">
-        <v>815</v>
-      </c>
-      <c r="DR1" s="15" t="s">
-        <v>606</v>
       </c>
       <c r="DS1" s="15" t="s">
         <v>524</v>
@@ -6052,16 +6069,16 @@
         <v>237</v>
       </c>
       <c r="DV1" s="15" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="DW1" s="15" t="s">
         <v>569</v>
       </c>
       <c r="DX1" s="15" t="s">
-        <v>811</v>
+        <v>810</v>
       </c>
       <c r="DY1" s="15" t="s">
-        <v>604</v>
+        <v>603</v>
       </c>
       <c r="DZ1" s="15" t="s">
         <v>566</v>
@@ -6073,22 +6090,22 @@
         <v>559</v>
       </c>
       <c r="EC1" s="21" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="ED1" s="25" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="EE1" s="12" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="EF1" s="14" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="EG1" s="12" t="s">
         <v>234</v>
       </c>
       <c r="EH1" s="12" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="EI1" s="12" t="s">
         <v>286</v>
@@ -6103,19 +6120,19 @@
         <v>125</v>
       </c>
       <c r="EM1" s="17" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="EN1" s="17" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="EO1" s="17" t="s">
         <v>558</v>
       </c>
       <c r="EP1" s="19" t="s">
-        <v>610</v>
+        <v>609</v>
       </c>
       <c r="EQ1" s="19" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="ER1" s="19" t="s">
         <v>126</v>
@@ -6130,7 +6147,7 @@
         <v>231</v>
       </c>
       <c r="EV1" s="20" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="EW1" s="20" t="s">
         <v>232</v>
@@ -7574,7 +7591,7 @@
         <v>51</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D10" s="2">
         <v>300</v>
@@ -7934,7 +7951,7 @@
         <v>55</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D12" s="2">
         <v>200</v>
@@ -8636,7 +8653,7 @@
     </row>
     <row r="16" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>278</v>
@@ -10606,7 +10623,7 @@
     </row>
     <row r="27" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>51</v>
@@ -11138,7 +11155,7 @@
     </row>
     <row r="30" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>278</v>
@@ -11494,7 +11511,7 @@
     </row>
     <row r="32" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>278</v>
@@ -12388,7 +12405,7 @@
         <v>53</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D37" s="2">
         <v>300</v>
@@ -17178,7 +17195,7 @@
     </row>
     <row r="64" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>50</v>
@@ -18964,7 +18981,7 @@
     </row>
     <row r="74" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>51</v>
@@ -20216,7 +20233,7 @@
     </row>
     <row r="81" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>51</v>
@@ -20394,7 +20411,7 @@
     </row>
     <row r="82" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>50</v>
@@ -20758,7 +20775,7 @@
     </row>
     <row r="84" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>51</v>
@@ -20934,7 +20951,7 @@
     </row>
     <row r="85" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>51</v>
@@ -21988,10 +22005,10 @@
     </row>
     <row r="91" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>678</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>679</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>680</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>63</v>
@@ -23238,7 +23255,7 @@
     </row>
     <row r="98" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>49</v>
@@ -25406,7 +25423,7 @@
         <v>53</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D110" s="2">
         <v>300</v>
@@ -28064,7 +28081,7 @@
     </row>
     <row r="125" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A125" s="13" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>278</v>
@@ -30202,7 +30219,7 @@
     </row>
     <row r="137" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A137" s="13" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>278</v>
@@ -30922,7 +30939,7 @@
     </row>
     <row r="141" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>55</v>
@@ -31996,7 +32013,7 @@
     </row>
     <row r="147" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>711</v>
+        <v>710</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>51</v>
@@ -32172,7 +32189,7 @@
     </row>
     <row r="148" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>51</v>
@@ -32348,7 +32365,7 @@
     </row>
     <row r="149" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>50</v>
@@ -32702,13 +32719,13 @@
     </row>
     <row r="151" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D151" s="2">
         <v>300</v>
@@ -32882,7 +32899,7 @@
     </row>
     <row r="152" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>53</v>
@@ -33061,13 +33078,13 @@
     </row>
     <row r="153" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="D153" s="2">
         <v>300</v>
@@ -33241,7 +33258,7 @@
     </row>
     <row r="154" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>51</v>
@@ -33417,7 +33434,7 @@
     </row>
     <row r="155" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>54</v>
@@ -33593,7 +33610,7 @@
     </row>
     <row r="156" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>53</v>
@@ -33771,7 +33788,7 @@
     </row>
     <row r="157" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>278</v>
@@ -33945,13 +33962,13 @@
     </row>
     <row r="158" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>278</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="D158" s="2">
         <v>1500</v>
@@ -34125,13 +34142,13 @@
     </row>
     <row r="159" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>278</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="D159" s="2">
         <v>1500</v>
@@ -34315,7 +34332,7 @@
     </row>
     <row r="160" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>197</v>
@@ -34487,7 +34504,7 @@
     </row>
     <row r="161" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>51</v>
@@ -34671,7 +34688,7 @@
     </row>
     <row r="162" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>51</v>
@@ -34847,7 +34864,7 @@
     </row>
     <row r="163" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>51</v>
@@ -35027,7 +35044,7 @@
     </row>
     <row r="164" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>53</v>
@@ -35205,7 +35222,7 @@
     </row>
     <row r="165" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>51</v>
@@ -35381,7 +35398,7 @@
     </row>
     <row r="166" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>876</v>
+        <v>875</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>50</v>
@@ -35563,7 +35580,7 @@
     </row>
     <row r="167" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>53</v>
@@ -35741,7 +35758,7 @@
     </row>
     <row r="168" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>55</v>
@@ -35915,7 +35932,7 @@
     </row>
     <row r="169" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>55</v>
@@ -36093,7 +36110,7 @@
     </row>
     <row r="170" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>53</v>
@@ -36269,7 +36286,7 @@
     </row>
     <row r="171" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>55</v>
@@ -36286,7 +36303,7 @@
       </c>
       <c r="G171" s="2"/>
       <c r="H171" s="2">
-        <f t="shared" ref="H171:H172" si="7">SUM(I171:DF171)</f>
+        <f t="shared" ref="H171:H173" si="7">SUM(I171:DF171)</f>
         <v>135</v>
       </c>
       <c r="I171" s="2"/>
@@ -36445,7 +36462,7 @@
     </row>
     <row r="172" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>53</v>
@@ -36622,14 +36639,31 @@
       <c r="EW172" s="2"/>
     </row>
     <row r="173" spans="1:153" x14ac:dyDescent="0.25">
-      <c r="A173" s="1"/>
-      <c r="B173" s="1"/>
-      <c r="C173" s="2"/>
-      <c r="D173" s="2"/>
-      <c r="E173" s="2"/>
-      <c r="F173" s="2"/>
-      <c r="G173" s="2"/>
-      <c r="H173" s="2"/>
+      <c r="A173" s="1" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B173" s="1" t="s">
+        <v>52</v>
+      </c>
+      <c r="C173" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D173" s="2">
+        <v>500</v>
+      </c>
+      <c r="E173" s="2">
+        <v>200</v>
+      </c>
+      <c r="F173" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G173" s="2">
+        <v>300</v>
+      </c>
+      <c r="H173" s="2">
+        <f t="shared" si="7"/>
+        <v>240</v>
+      </c>
       <c r="I173" s="2"/>
       <c r="J173" s="2"/>
       <c r="K173" s="2"/>
@@ -36658,7 +36692,9 @@
       <c r="AH173" s="2"/>
       <c r="AI173" s="2"/>
       <c r="AJ173" s="2"/>
-      <c r="AK173" s="2"/>
+      <c r="AK173" s="2">
+        <v>60</v>
+      </c>
       <c r="AL173" s="2"/>
       <c r="AM173" s="2"/>
       <c r="AN173" s="2"/>
@@ -36717,7 +36753,9 @@
       <c r="CO173" s="2"/>
       <c r="CP173" s="2"/>
       <c r="CQ173" s="2"/>
-      <c r="CR173" s="2"/>
+      <c r="CR173" s="2">
+        <v>180</v>
+      </c>
       <c r="CS173" s="2"/>
       <c r="CT173" s="2"/>
       <c r="CU173" s="2"/>
@@ -36777,14 +36815,31 @@
       <c r="EW173" s="2"/>
     </row>
     <row r="174" spans="1:153" x14ac:dyDescent="0.25">
-      <c r="A174" s="1"/>
-      <c r="B174" s="1"/>
-      <c r="C174" s="2"/>
-      <c r="D174" s="2"/>
-      <c r="E174" s="2"/>
-      <c r="F174" s="2"/>
-      <c r="G174" s="2"/>
-      <c r="H174" s="2"/>
+      <c r="A174" s="1" t="s">
+        <v>1081</v>
+      </c>
+      <c r="B174" s="1" t="s">
+        <v>49</v>
+      </c>
+      <c r="C174" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D174" s="2">
+        <v>500</v>
+      </c>
+      <c r="E174" s="2">
+        <v>200</v>
+      </c>
+      <c r="F174" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G174" s="2">
+        <v>300</v>
+      </c>
+      <c r="H174" s="2">
+        <f t="shared" ref="H174" si="8">SUM(I174:DF174)</f>
+        <v>180</v>
+      </c>
       <c r="I174" s="2"/>
       <c r="J174" s="2"/>
       <c r="K174" s="2"/>
@@ -36802,7 +36857,9 @@
       <c r="W174" s="2"/>
       <c r="X174" s="2"/>
       <c r="Y174" s="2"/>
-      <c r="Z174" s="2"/>
+      <c r="Z174" s="2">
+        <v>90</v>
+      </c>
       <c r="AA174" s="2"/>
       <c r="AB174" s="2"/>
       <c r="AC174" s="2"/>
@@ -36813,7 +36870,9 @@
       <c r="AH174" s="2"/>
       <c r="AI174" s="2"/>
       <c r="AJ174" s="2"/>
-      <c r="AK174" s="2"/>
+      <c r="AK174" s="2">
+        <v>60</v>
+      </c>
       <c r="AL174" s="2"/>
       <c r="AM174" s="2"/>
       <c r="AN174" s="2"/>
@@ -36882,7 +36941,9 @@
       <c r="CY174" s="2"/>
       <c r="CZ174" s="2"/>
       <c r="DA174" s="2"/>
-      <c r="DB174" s="2"/>
+      <c r="DB174" s="2">
+        <v>30</v>
+      </c>
       <c r="DC174" s="2"/>
       <c r="DD174" s="2"/>
       <c r="DE174" s="2"/>
@@ -48712,7 +48773,7 @@
       <c r="EW250" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:EW171" xr:uid="{C7FAA63B-DEDB-48F1-9CCA-3BF0BF1CD86F}">
+  <autoFilter ref="A1:EW174" xr:uid="{C7FAA63B-DEDB-48F1-9CCA-3BF0BF1CD86F}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:EW150">
       <sortCondition ref="A1:A146"/>
     </sortState>
@@ -48779,7 +48840,7 @@
         <v>524</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>141</v>
@@ -48803,7 +48864,7 @@
         <v>580</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>877</v>
+        <v>876</v>
       </c>
       <c r="P1" s="8" t="s">
         <v>132</v>
@@ -55415,9 +55476,11 @@
     <row r="173" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="str">
         <f>IF(receta!A173="","",receta!A173)</f>
-        <v/>
-      </c>
-      <c r="B173" s="2"/>
+        <v>Campari &amp; Tonic</v>
+      </c>
+      <c r="B173" s="2">
+        <v>1</v>
+      </c>
       <c r="C173" s="2"/>
       <c r="D173" s="2"/>
       <c r="E173" s="2"/>
@@ -55451,10 +55514,12 @@
     <row r="174" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="str">
         <f>IF(receta!A174="","",receta!A174)</f>
-        <v/>
+        <v>Campari Spritz</v>
       </c>
       <c r="B174" s="2"/>
-      <c r="C174" s="2"/>
+      <c r="C174" s="2">
+        <v>1</v>
+      </c>
       <c r="D174" s="2"/>
       <c r="E174" s="2"/>
       <c r="F174" s="2"/>
@@ -58255,7 +58320,7 @@
         <v>72</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>318</v>
@@ -58270,7 +58335,7 @@
         <v>315</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>316</v>
@@ -58279,16 +58344,16 @@
         <v>317</v>
       </c>
       <c r="J1" s="7" t="s">
+        <v>762</v>
+      </c>
+      <c r="K1" s="7" t="s">
         <v>763</v>
       </c>
-      <c r="K1" s="7" t="s">
-        <v>764</v>
-      </c>
       <c r="L1" s="7" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="270" x14ac:dyDescent="0.25">
@@ -58316,7 +58381,7 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="4" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58325,7 +58390,7 @@
         <v>Alejandra</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C3" s="4" t="s">
         <v>366</v>
@@ -58362,7 +58427,7 @@
         <v>239</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="5"/>
@@ -58377,7 +58442,7 @@
         <v>Alexander</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C5" s="4" t="s">
         <v>448</v>
@@ -58398,7 +58463,7 @@
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
       <c r="M5" s="4" t="s">
-        <v>916</v>
+        <v>915</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="270" x14ac:dyDescent="0.25">
@@ -58407,7 +58472,7 @@
         <v>Amaretto Sour</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C6" s="4" t="s">
         <v>352</v>
@@ -58426,7 +58491,7 @@
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="4" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="270" x14ac:dyDescent="0.25">
@@ -58434,7 +58499,9 @@
         <f>IF(receta!A7="","",receta!A7)</f>
         <v>Amaretto Spritz</v>
       </c>
-      <c r="B7" s="1"/>
+      <c r="B7" s="4" t="s">
+        <v>1083</v>
+      </c>
       <c r="C7" s="4" t="s">
         <v>352</v>
       </c>
@@ -58452,7 +58519,7 @@
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="4" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="210" x14ac:dyDescent="0.25">
@@ -58478,7 +58545,7 @@
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="4" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -58506,7 +58573,7 @@
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
       <c r="M9" s="1" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="210" x14ac:dyDescent="0.25">
@@ -58515,10 +58582,10 @@
         <v>Andes Refresh</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="11"/>
@@ -58536,12 +58603,14 @@
         <f>IF(receta!A11="","",receta!A11)</f>
         <v>Aperol Spritz</v>
       </c>
-      <c r="B11" s="1"/>
+      <c r="B11" s="4" t="s">
+        <v>1083</v>
+      </c>
       <c r="C11" s="4" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -58552,7 +58621,7 @@
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="4" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58561,10 +58630,10 @@
         <v>Arándano Sour</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="D12" s="4" t="s">
         <v>553</v>
@@ -58600,7 +58669,7 @@
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="4" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58628,7 +58697,7 @@
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="4" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58652,7 +58721,7 @@
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="4" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -58664,13 +58733,13 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -58756,7 +58825,7 @@
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="4" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -58789,10 +58858,10 @@
         <v>Borgoña</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="1"/>
@@ -58808,7 +58877,7 @@
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="4" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="375" x14ac:dyDescent="0.25">
@@ -58817,10 +58886,10 @@
         <v>Caipiriña</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1" t="s">
@@ -58836,7 +58905,7 @@
       <c r="K22" s="5"/>
       <c r="L22" s="5"/>
       <c r="M22" s="4" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -58858,7 +58927,7 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="4" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="345" x14ac:dyDescent="0.25">
@@ -58906,7 +58975,7 @@
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="4" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58934,7 +59003,7 @@
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="4" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="375" x14ac:dyDescent="0.25">
@@ -58943,13 +59012,13 @@
         <v>Chupilca</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="E27" s="1"/>
       <c r="F27" s="1"/>
@@ -58960,7 +59029,7 @@
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="4" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58973,7 +59042,7 @@
         <v>458</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>528</v>
@@ -58985,14 +59054,14 @@
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
       <c r="J28" s="1" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
       <c r="L28" s="5"/>
       <c r="M28" s="4" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="360" x14ac:dyDescent="0.25">
@@ -59018,7 +59087,7 @@
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="4" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59027,13 +59096,13 @@
         <v>Cléry</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
@@ -59044,7 +59113,7 @@
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="4" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59053,22 +59122,22 @@
         <v>Cléry Chirimoya</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>425</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="F31" s="5" t="s">
+        <v>998</v>
+      </c>
+      <c r="G31" s="4" t="s">
         <v>999</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>1000</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -59076,7 +59145,7 @@
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="4" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -59085,10 +59154,10 @@
         <v>Cléry Durazno</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1" t="s">
@@ -59111,10 +59180,10 @@
         <v>Clover Club</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>841</v>
+        <v>840</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>548</v>
@@ -59132,7 +59201,7 @@
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="4" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="255" x14ac:dyDescent="0.25">
@@ -59142,7 +59211,7 @@
       </c>
       <c r="B34" s="1"/>
       <c r="C34" s="4" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="1" t="s">
@@ -59158,7 +59227,7 @@
       <c r="K34" s="5"/>
       <c r="L34" s="5"/>
       <c r="M34" s="4" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -59167,10 +59236,10 @@
         <v>Cosmo Patagonia</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="1"/>
@@ -59202,7 +59271,7 @@
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59211,10 +59280,10 @@
         <v>Crepúsculo</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="4" t="s">
@@ -59230,7 +59299,7 @@
       <c r="K37" s="5"/>
       <c r="L37" s="5"/>
       <c r="M37" s="4" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="255" x14ac:dyDescent="0.25">
@@ -59256,15 +59325,17 @@
       <c r="K38" s="5"/>
       <c r="L38" s="5"/>
       <c r="M38" s="4" t="s">
-        <v>989</v>
-      </c>
-    </row>
-    <row r="39" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+        <v>988</v>
+      </c>
+    </row>
+    <row r="39" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="str">
         <f>IF(receta!A39="","",receta!A39)</f>
         <v>Cynar Spritz</v>
       </c>
-      <c r="B39" s="1"/>
+      <c r="B39" s="4" t="s">
+        <v>1083</v>
+      </c>
       <c r="C39" s="4" t="s">
         <v>333</v>
       </c>
@@ -59278,7 +59349,7 @@
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="4" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -59299,16 +59370,16 @@
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="1" t="s">
+        <v>926</v>
+      </c>
+      <c r="I40" s="5" t="s">
         <v>927</v>
-      </c>
-      <c r="I40" s="5" t="s">
-        <v>928</v>
       </c>
       <c r="J40" s="4"/>
       <c r="K40" s="5"/>
       <c r="L40" s="5"/>
       <c r="M40" s="4" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -59317,10 +59388,10 @@
         <v>Dama Blanca</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="1"/>
@@ -59332,7 +59403,7 @@
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
       <c r="M41" s="4" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59358,7 +59429,7 @@
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="M42" s="4" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="270" x14ac:dyDescent="0.25">
@@ -59386,7 +59457,7 @@
       <c r="K43" s="5"/>
       <c r="L43" s="5"/>
       <c r="M43" s="4" t="s">
-        <v>924</v>
+        <v>923</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -59415,10 +59486,10 @@
         <v>Dry Martini</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D45" s="4" t="s">
         <v>392</v>
@@ -59432,7 +59503,7 @@
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
       <c r="M45" s="4" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="285" x14ac:dyDescent="0.25">
@@ -59441,11 +59512,11 @@
         <v>El Amor en los Tiempos del Covid</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C46" s="4"/>
       <c r="D46" s="4" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>185</v>
@@ -59457,16 +59528,16 @@
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
       <c r="J46" s="4" t="s">
+        <v>1032</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>1031</v>
+      </c>
+      <c r="L46" s="4" t="s">
         <v>1033</v>
       </c>
-      <c r="K46" s="5" t="s">
-        <v>1032</v>
-      </c>
-      <c r="L46" s="4" t="s">
-        <v>1034</v>
-      </c>
       <c r="M46" s="4" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -59494,7 +59565,7 @@
       <c r="K47" s="5"/>
       <c r="L47" s="5"/>
       <c r="M47" s="4" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="315" x14ac:dyDescent="0.25">
@@ -59507,13 +59578,13 @@
         <v>380</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E48" s="1" t="s">
+        <v>595</v>
+      </c>
+      <c r="F48" s="5" t="s">
         <v>596</v>
-      </c>
-      <c r="F48" s="5" t="s">
-        <v>597</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="1"/>
@@ -59530,19 +59601,19 @@
       </c>
       <c r="B49" s="1"/>
       <c r="C49" s="4" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D49" s="4" t="s">
         <v>372</v>
       </c>
       <c r="E49" s="1" t="s">
+        <v>767</v>
+      </c>
+      <c r="F49" s="5" t="s">
         <v>768</v>
       </c>
-      <c r="F49" s="5" t="s">
-        <v>769</v>
-      </c>
       <c r="G49" s="4" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -59550,7 +59621,7 @@
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
       <c r="M49" s="4" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="255" x14ac:dyDescent="0.25">
@@ -59560,7 +59631,7 @@
       </c>
       <c r="B50" s="1"/>
       <c r="C50" s="4" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="4" t="s">
@@ -59570,7 +59641,7 @@
         <v>481</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>326</v>
@@ -59582,7 +59653,7 @@
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
       <c r="M50" s="4" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -59604,7 +59675,7 @@
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
       <c r="M51" s="1" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="150" x14ac:dyDescent="0.25">
@@ -59636,7 +59707,7 @@
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
       <c r="M52" s="4" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="390" x14ac:dyDescent="0.25">
@@ -59658,7 +59729,7 @@
         <v>404</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>384</v>
@@ -59670,7 +59741,7 @@
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="4" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59680,7 +59751,7 @@
       </c>
       <c r="B54" s="1"/>
       <c r="C54" s="4" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="1"/>
@@ -59696,7 +59767,7 @@
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
       <c r="M54" s="4" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
@@ -59742,7 +59813,7 @@
         <v>473</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -59750,7 +59821,7 @@
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
       <c r="M56" s="4" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59778,7 +59849,7 @@
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
       <c r="M57" s="4" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="150" x14ac:dyDescent="0.25">
@@ -59787,7 +59858,7 @@
         <v>Frangelico Sour</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C58" s="4" t="s">
         <v>338</v>
@@ -59802,7 +59873,7 @@
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="4" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59811,10 +59882,10 @@
         <v>French 75</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="D59" s="4" t="s">
         <v>358</v>
@@ -59832,7 +59903,7 @@
       <c r="K59" s="5"/>
       <c r="L59" s="5"/>
       <c r="M59" s="4" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -59854,7 +59925,7 @@
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
       <c r="M60" s="4" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="165" x14ac:dyDescent="0.25">
@@ -59870,10 +59941,10 @@
         <v>388</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="4"/>
@@ -59882,7 +59953,7 @@
       <c r="K61" s="1"/>
       <c r="L61" s="1"/>
       <c r="M61" s="4" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="345" x14ac:dyDescent="0.25">
@@ -59892,7 +59963,7 @@
       </c>
       <c r="B62" s="1"/>
       <c r="C62" s="4" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D62" s="1"/>
       <c r="E62" s="4" t="s">
@@ -59908,7 +59979,7 @@
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
       <c r="M62" s="4" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59935,16 +60006,16 @@
         <v>337</v>
       </c>
       <c r="J63" s="1" t="s">
+        <v>764</v>
+      </c>
+      <c r="K63" s="5" t="s">
         <v>765</v>
       </c>
-      <c r="K63" s="5" t="s">
-        <v>766</v>
-      </c>
       <c r="L63" s="4" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="M63" s="4" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -59954,7 +60025,7 @@
       </c>
       <c r="B64" s="1"/>
       <c r="C64" s="4" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="D64" s="1"/>
       <c r="E64" s="1"/>
@@ -59966,7 +60037,7 @@
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
       <c r="M64" s="4" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59976,7 +60047,7 @@
       </c>
       <c r="B65" s="1"/>
       <c r="C65" s="4" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>169</v>
@@ -59990,7 +60061,7 @@
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
       <c r="M65" s="1" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="375" x14ac:dyDescent="0.25">
@@ -60000,10 +60071,10 @@
       </c>
       <c r="B66" s="1"/>
       <c r="C66" s="4" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
@@ -60014,7 +60085,7 @@
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
       <c r="M66" s="4" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="67" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60040,7 +60111,7 @@
       <c r="K67" s="5"/>
       <c r="L67" s="5"/>
       <c r="M67" s="4" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="68" spans="1:13" ht="330" x14ac:dyDescent="0.25">
@@ -60050,10 +60121,10 @@
       </c>
       <c r="B68" s="1"/>
       <c r="C68" s="1" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>165</v>
@@ -60068,7 +60139,7 @@
       <c r="K68" s="5"/>
       <c r="L68" s="5"/>
       <c r="M68" s="4" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
     </row>
     <row r="69" spans="1:13" ht="300" x14ac:dyDescent="0.25">
@@ -60096,7 +60167,7 @@
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
       <c r="M69" s="4" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -60124,7 +60195,7 @@
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
       <c r="M70" s="4" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -60150,7 +60221,7 @@
       <c r="K71" s="5"/>
       <c r="L71" s="5"/>
       <c r="M71" s="4" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="72" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60159,13 +60230,13 @@
         <v>Jote</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="E72" s="1"/>
       <c r="F72" s="5"/>
@@ -60180,7 +60251,7 @@
       <c r="K72" s="5"/>
       <c r="L72" s="5"/>
       <c r="M72" s="4" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
     </row>
     <row r="73" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -60193,7 +60264,7 @@
       </c>
       <c r="C73" s="4"/>
       <c r="D73" s="4" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
@@ -60204,7 +60275,7 @@
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
       <c r="M73" s="4" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="74" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60213,26 +60284,26 @@
         <v>Julieta Flowers</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="E74" s="1" t="s">
+        <v>726</v>
+      </c>
+      <c r="F74" s="5" t="s">
         <v>727</v>
-      </c>
-      <c r="F74" s="5" t="s">
-        <v>728</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="1" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="J74" s="1"/>
       <c r="K74" s="5"/>
@@ -60258,7 +60329,7 @@
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
       <c r="M75" s="4" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="76" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60294,10 +60365,10 @@
       </c>
       <c r="B77" s="1"/>
       <c r="C77" s="4" t="s">
+        <v>1013</v>
+      </c>
+      <c r="D77" s="4" t="s">
         <v>1014</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>1015</v>
       </c>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
@@ -60308,7 +60379,7 @@
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
       <c r="M77" s="4" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="78" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -60322,19 +60393,19 @@
       </c>
       <c r="D78" s="1"/>
       <c r="E78" s="1" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="G78" s="5"/>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
       <c r="J78" s="1" t="s">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="K78" s="5" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="L78" s="5"/>
       <c r="M78" s="1"/>
@@ -60384,7 +60455,7 @@
       </c>
       <c r="B81" s="1"/>
       <c r="C81" s="4" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D81" s="4"/>
       <c r="E81" s="1"/>
@@ -60403,26 +60474,26 @@
         <v>Mai Tai Piña</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D82" s="4"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
       <c r="G82" s="1"/>
       <c r="H82" s="1" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="I82" s="5" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="J82" s="1"/>
       <c r="K82" s="1"/>
       <c r="L82" s="1"/>
       <c r="M82" s="4" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60432,7 +60503,7 @@
       </c>
       <c r="B83" s="1"/>
       <c r="C83" s="4" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>304</v>
@@ -60450,7 +60521,7 @@
       <c r="K83" s="5"/>
       <c r="L83" s="5"/>
       <c r="M83" s="4" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="84" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60459,28 +60530,28 @@
         <v>Malta con Huevo</v>
       </c>
       <c r="B84" s="4" t="s">
+        <v>658</v>
+      </c>
+      <c r="C84" s="4" t="s">
         <v>659</v>
       </c>
-      <c r="C84" s="4" t="s">
-        <v>660</v>
-      </c>
       <c r="D84" s="4" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
       <c r="H84" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="J84" s="1"/>
       <c r="K84" s="1"/>
       <c r="L84" s="1"/>
       <c r="M84" s="4" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -60489,28 +60560,28 @@
         <v>Malta con Leche Condensada</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
       <c r="H85" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="J85" s="1"/>
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
       <c r="M85" s="4" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -60519,7 +60590,7 @@
         <v>Mango Sour</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="C86" s="4"/>
       <c r="D86" s="1"/>
@@ -60540,18 +60611,18 @@
       </c>
       <c r="B87" s="1"/>
       <c r="C87" s="4" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="D87" s="1"/>
       <c r="E87" s="1" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="G87" s="5"/>
       <c r="H87" s="1" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="I87" s="5" t="s">
         <v>373</v>
@@ -60560,7 +60631,7 @@
       <c r="K87" s="5"/>
       <c r="L87" s="5"/>
       <c r="M87" s="4" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="88" spans="1:13" ht="360" x14ac:dyDescent="0.25">
@@ -60569,13 +60640,13 @@
         <v>Maqui Sour</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>593</v>
+        <v>1079</v>
       </c>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
@@ -60586,7 +60657,7 @@
       <c r="K88" s="1"/>
       <c r="L88" s="1"/>
       <c r="M88" s="4" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="89" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -60595,10 +60666,10 @@
         <v>Margarita</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="D89" s="1"/>
       <c r="E89" s="1" t="s">
@@ -60608,7 +60679,7 @@
         <v>180</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
@@ -60616,7 +60687,7 @@
       <c r="K89" s="5"/>
       <c r="L89" s="5"/>
       <c r="M89" s="4" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
@@ -60647,10 +60718,10 @@
         <v>Melón con Vino</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D91" s="1"/>
       <c r="E91" s="1" t="s">
@@ -60673,10 +60744,10 @@
         <v>Michelada</v>
       </c>
       <c r="B92" s="4" t="s">
+        <v>841</v>
+      </c>
+      <c r="C92" s="4" t="s">
         <v>842</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>843</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>401</v>
@@ -60714,7 +60785,7 @@
       <c r="K93" s="1"/>
       <c r="L93" s="1"/>
       <c r="M93" s="4" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="94" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -60736,7 +60807,7 @@
       <c r="K94" s="1"/>
       <c r="L94" s="1"/>
       <c r="M94" s="4" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="95" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -60745,10 +60816,10 @@
         <v>Mojito</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="D95" s="4"/>
       <c r="E95" s="1"/>
@@ -60760,7 +60831,7 @@
       <c r="K95" s="1"/>
       <c r="L95" s="1"/>
       <c r="M95" s="4" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
     </row>
     <row r="96" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -60793,13 +60864,13 @@
         <v>578</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="G97" s="1"/>
       <c r="H97" s="4"/>
@@ -60808,17 +60879,19 @@
       <c r="K97" s="1"/>
       <c r="L97" s="1"/>
       <c r="M97" s="4" t="s">
-        <v>995</v>
-      </c>
-    </row>
-    <row r="98" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="str">
         <f>IF(receta!A98="","",receta!A98)</f>
         <v>Mojito Spritz</v>
       </c>
-      <c r="B98" s="1"/>
+      <c r="B98" s="4" t="s">
+        <v>1083</v>
+      </c>
       <c r="C98" s="4" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D98" s="4"/>
       <c r="E98" s="1"/>
@@ -60854,7 +60927,7 @@
       <c r="K99" s="5"/>
       <c r="L99" s="5"/>
       <c r="M99" s="4" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="100" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -60863,7 +60936,7 @@
         <v>Naranja Sour</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C100" s="4" t="s">
         <v>371</v>
@@ -60890,7 +60963,7 @@
       </c>
       <c r="B101" s="1"/>
       <c r="C101" s="4" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="D101" s="4"/>
       <c r="E101" s="4"/>
@@ -60928,7 +61001,7 @@
       <c r="K102" s="1"/>
       <c r="L102" s="1"/>
       <c r="M102" s="4" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="103" spans="1:13" ht="210" x14ac:dyDescent="0.25">
@@ -60950,7 +61023,7 @@
       <c r="K103" s="1"/>
       <c r="L103" s="1"/>
       <c r="M103" s="4" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="104" spans="1:13" ht="345" x14ac:dyDescent="0.25">
@@ -60959,10 +61032,10 @@
         <v>New York Sour</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="D104" s="4" t="s">
         <v>482</v>
@@ -60980,7 +61053,7 @@
       <c r="K104" s="5"/>
       <c r="L104" s="5"/>
       <c r="M104" s="4" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="105" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -61006,7 +61079,7 @@
       <c r="K105" s="1"/>
       <c r="L105" s="1"/>
       <c r="M105" s="4" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
     </row>
     <row r="106" spans="1:13" ht="375" x14ac:dyDescent="0.25">
@@ -61015,32 +61088,32 @@
         <v>Old Fashioned</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="C106" s="4"/>
       <c r="D106" s="4" t="s">
         <v>563</v>
       </c>
       <c r="E106" s="1" t="s">
+        <v>1038</v>
+      </c>
+      <c r="F106" s="5" t="s">
         <v>1039</v>
       </c>
-      <c r="F106" s="5" t="s">
-        <v>1040</v>
-      </c>
       <c r="G106" s="4" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="I106" s="5" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="J106" s="1"/>
       <c r="K106" s="1"/>
       <c r="L106" s="1"/>
       <c r="M106" s="4" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="107" spans="1:13" ht="192" customHeight="1" x14ac:dyDescent="0.25">
@@ -61069,17 +61142,17 @@
         <v>Paloma</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="D108" s="1"/>
       <c r="E108" s="1"/>
       <c r="F108" s="1"/>
       <c r="G108" s="1"/>
       <c r="H108" s="1" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="I108" s="5" t="s">
         <v>256</v>
@@ -61088,7 +61161,7 @@
       <c r="K108" s="1"/>
       <c r="L108" s="1"/>
       <c r="M108" s="4" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="109" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -61117,13 +61190,13 @@
         <v>Penicilina</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="E110" s="4" t="s">
         <v>583</v>
@@ -61138,7 +61211,7 @@
       <c r="K110" s="5"/>
       <c r="L110" s="5"/>
       <c r="M110" s="4" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.25">
@@ -61182,7 +61255,7 @@
         <v>483</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="H112" s="1"/>
       <c r="I112" s="5"/>
@@ -61214,7 +61287,7 @@
       <c r="K113" s="5"/>
       <c r="L113" s="5"/>
       <c r="M113" s="4" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.25">
@@ -61289,10 +61362,10 @@
         <v>Piscola</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="D117" s="5"/>
       <c r="E117" s="1" t="s">
@@ -61308,7 +61381,7 @@
       <c r="K117" s="5"/>
       <c r="L117" s="5"/>
       <c r="M117" s="4" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
     </row>
     <row r="118" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -61317,10 +61390,10 @@
         <v>Pistón</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="D118" s="1"/>
       <c r="E118" s="1" t="s">
@@ -61362,15 +61435,17 @@
       <c r="K119" s="5"/>
       <c r="L119" s="5"/>
       <c r="M119" s="4" t="s">
-        <v>1010</v>
-      </c>
-    </row>
-    <row r="120" spans="1:13" ht="75" x14ac:dyDescent="0.25">
+        <v>1009</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="str">
         <f>IF(receta!A120="","",receta!A120)</f>
         <v>Ramazzotti Spritz</v>
       </c>
-      <c r="B120" s="1"/>
+      <c r="B120" s="4" t="s">
+        <v>1083</v>
+      </c>
       <c r="C120" s="4" t="s">
         <v>353</v>
       </c>
@@ -61396,7 +61471,7 @@
       </c>
       <c r="B121" s="1"/>
       <c r="C121" s="4" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D121" s="1"/>
       <c r="E121" s="1"/>
@@ -61440,7 +61515,7 @@
       </c>
       <c r="B123" s="1"/>
       <c r="C123" s="4" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D123" s="4" t="s">
         <v>252</v>
@@ -61458,7 +61533,7 @@
       <c r="K123" s="5"/>
       <c r="L123" s="5"/>
       <c r="M123" s="4" t="s">
-        <v>925</v>
+        <v>924</v>
       </c>
     </row>
     <row r="124" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -61489,10 +61564,10 @@
         <v>Sangría</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="D125" s="4" t="s">
         <v>393</v>
@@ -61538,7 +61613,7 @@
       </c>
       <c r="B127" s="1"/>
       <c r="C127" s="4" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="D127" s="1"/>
       <c r="E127" s="1" t="s">
@@ -61574,7 +61649,7 @@
       <c r="K128" s="1"/>
       <c r="L128" s="1"/>
       <c r="M128" s="4" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="129" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -61587,7 +61662,7 @@
         <v>369</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="E129" s="1"/>
       <c r="F129" s="1"/>
@@ -61598,7 +61673,7 @@
       <c r="K129" s="1"/>
       <c r="L129" s="1"/>
       <c r="M129" s="4" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
     </row>
     <row r="130" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -61640,7 +61715,7 @@
       <c r="K131" s="1"/>
       <c r="L131" s="1"/>
       <c r="M131" s="4" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="132" spans="1:13" ht="165" x14ac:dyDescent="0.25">
@@ -61666,7 +61741,7 @@
       <c r="K132" s="5"/>
       <c r="L132" s="5"/>
       <c r="M132" s="4" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.25">
@@ -61699,7 +61774,7 @@
         <v>586</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>595</v>
+        <v>594</v>
       </c>
       <c r="E134" s="4" t="s">
         <v>588</v>
@@ -61714,7 +61789,7 @@
       <c r="K134" s="5"/>
       <c r="L134" s="5"/>
       <c r="M134" s="4" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="135" spans="1:13" ht="300" x14ac:dyDescent="0.25">
@@ -61723,28 +61798,28 @@
         <v>Terremoto</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="E135" s="1"/>
       <c r="F135" s="1"/>
       <c r="G135" s="1"/>
       <c r="H135" s="1" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="I135" s="5" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="J135" s="1"/>
       <c r="K135" s="1"/>
       <c r="L135" s="1"/>
       <c r="M135" s="4" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="136" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -61753,10 +61828,10 @@
         <v>Terremoto (Sin Alcohol)</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="D136" s="4"/>
       <c r="E136" s="1" t="s">
@@ -61784,13 +61859,13 @@
         <v>433</v>
       </c>
       <c r="E137" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="F137" s="5" t="s">
+        <v>1034</v>
+      </c>
+      <c r="G137" s="4" t="s">
         <v>1036</v>
-      </c>
-      <c r="F137" s="5" t="s">
-        <v>1035</v>
-      </c>
-      <c r="G137" s="4" t="s">
-        <v>1037</v>
       </c>
       <c r="H137" s="1"/>
       <c r="I137" s="1"/>
@@ -61806,7 +61881,7 @@
       </c>
       <c r="B138" s="4"/>
       <c r="C138" s="4" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="D138" s="1"/>
       <c r="E138" s="1"/>
@@ -61818,7 +61893,7 @@
       <c r="K138" s="1"/>
       <c r="L138" s="1"/>
       <c r="M138" s="4" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="139" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -61851,22 +61926,22 @@
         <v>Tropezón</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="D140" s="4" t="s">
         <v>345</v>
       </c>
       <c r="E140" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="F140" s="5" t="s">
+        <v>1020</v>
+      </c>
+      <c r="G140" s="4" t="s">
         <v>1022</v>
-      </c>
-      <c r="F140" s="5" t="s">
-        <v>1021</v>
-      </c>
-      <c r="G140" s="4" t="s">
-        <v>1023</v>
       </c>
       <c r="H140" s="1"/>
       <c r="I140" s="1"/>
@@ -61878,7 +61953,7 @@
       </c>
       <c r="L140" s="5"/>
       <c r="M140" s="4" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="141" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -61887,19 +61962,19 @@
         <v>Vaina</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="E141" s="4" t="s">
+        <v>610</v>
+      </c>
+      <c r="F141" s="4" t="s">
         <v>611</v>
-      </c>
-      <c r="F141" s="4" t="s">
-        <v>612</v>
       </c>
       <c r="G141" s="4"/>
       <c r="H141" s="1"/>
@@ -61916,7 +61991,7 @@
       </c>
       <c r="B142" s="1"/>
       <c r="C142" s="4" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D142" s="4"/>
       <c r="E142" s="4" t="s">
@@ -61939,10 +62014,10 @@
         <v>Vampiro</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D143" s="4" t="s">
         <v>540</v>
@@ -61960,7 +62035,7 @@
       <c r="K143" s="1"/>
       <c r="L143" s="1"/>
       <c r="M143" s="4" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="144" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -61983,20 +62058,20 @@
       </c>
       <c r="G144" s="1"/>
       <c r="H144" s="1" t="s">
+        <v>1026</v>
+      </c>
+      <c r="I144" s="5" t="s">
         <v>1027</v>
       </c>
-      <c r="I144" s="5" t="s">
-        <v>1028</v>
-      </c>
       <c r="J144" s="1" t="s">
+        <v>1024</v>
+      </c>
+      <c r="K144" s="5" t="s">
         <v>1025</v>
-      </c>
-      <c r="K144" s="5" t="s">
-        <v>1026</v>
       </c>
       <c r="L144" s="1"/>
       <c r="M144" s="4" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="145" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62005,10 +62080,10 @@
         <v>Vermouth con Soda</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="D145" s="4" t="s">
         <v>585</v>
@@ -62026,7 +62101,7 @@
       <c r="K145" s="1"/>
       <c r="L145" s="1"/>
       <c r="M145" s="4" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="146" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -62036,7 +62111,7 @@
       </c>
       <c r="B146" s="1"/>
       <c r="C146" s="4" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D146" s="1"/>
       <c r="E146" s="1"/>
@@ -62056,14 +62131,14 @@
       </c>
       <c r="B147" s="1"/>
       <c r="C147" s="4" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="D147" s="4"/>
       <c r="E147" s="1" t="s">
+        <v>711</v>
+      </c>
+      <c r="F147" s="5" t="s">
         <v>712</v>
-      </c>
-      <c r="F147" s="5" t="s">
-        <v>713</v>
       </c>
       <c r="G147" s="5"/>
       <c r="H147" s="1"/>
@@ -62072,7 +62147,7 @@
       <c r="K147" s="5"/>
       <c r="L147" s="5"/>
       <c r="M147" s="4" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
     </row>
     <row r="148" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -62082,14 +62157,14 @@
       </c>
       <c r="B148" s="1"/>
       <c r="C148" s="4" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="D148" s="1"/>
       <c r="E148" s="1" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="G148" s="5"/>
       <c r="H148" s="1"/>
@@ -62106,16 +62181,16 @@
       </c>
       <c r="B149" s="1"/>
       <c r="C149" s="4" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="E149" s="1" t="s">
+        <v>705</v>
+      </c>
+      <c r="F149" s="5" t="s">
         <v>706</v>
-      </c>
-      <c r="F149" s="5" t="s">
-        <v>707</v>
       </c>
       <c r="G149" s="5"/>
       <c r="H149" s="1"/>
@@ -62124,7 +62199,7 @@
       <c r="K149" s="5"/>
       <c r="L149" s="5"/>
       <c r="M149" s="4" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="150" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62133,7 +62208,7 @@
         <v>Whisky Sour</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C150" s="4" t="s">
         <v>360</v>
@@ -62154,7 +62229,7 @@
       <c r="K150" s="1"/>
       <c r="L150" s="1"/>
       <c r="M150" s="4" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
     </row>
     <row r="151" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -62163,19 +62238,19 @@
         <v>Bramble</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="D151" s="4" t="s">
+        <v>788</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>790</v>
+      </c>
+      <c r="F151" s="1" t="s">
         <v>789</v>
-      </c>
-      <c r="E151" s="1" t="s">
-        <v>791</v>
-      </c>
-      <c r="F151" s="1" t="s">
-        <v>790</v>
       </c>
       <c r="G151" s="1"/>
       <c r="H151" s="1"/>
@@ -62184,7 +62259,7 @@
       <c r="K151" s="1"/>
       <c r="L151" s="1"/>
       <c r="M151" s="4" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="152" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -62194,14 +62269,14 @@
       </c>
       <c r="B152" s="1"/>
       <c r="C152" s="4" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="D152" s="4"/>
       <c r="E152" s="1" t="s">
-        <v>792</v>
+        <v>791</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="G152" s="1"/>
       <c r="H152" s="1"/>
@@ -62210,7 +62285,7 @@
       <c r="K152" s="1"/>
       <c r="L152" s="1"/>
       <c r="M152" s="4" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="153" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -62219,19 +62294,19 @@
         <v>Gin Basil Smash</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="E153" s="4" t="s">
+        <v>792</v>
+      </c>
+      <c r="F153" s="1" t="s">
         <v>793</v>
-      </c>
-      <c r="F153" s="1" t="s">
-        <v>794</v>
       </c>
       <c r="G153" s="1"/>
       <c r="H153" s="1"/>
@@ -62248,28 +62323,28 @@
       </c>
       <c r="B154" s="1"/>
       <c r="C154" s="4" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="D154" s="26" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="E154" s="1" t="s">
+        <v>781</v>
+      </c>
+      <c r="F154" s="5" t="s">
         <v>782</v>
-      </c>
-      <c r="F154" s="5" t="s">
-        <v>783</v>
       </c>
       <c r="G154" s="5"/>
       <c r="H154" s="1"/>
       <c r="I154" s="5"/>
       <c r="J154" s="1" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="K154" s="5" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="L154" s="26" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="M154" s="1"/>
     </row>
@@ -62279,13 +62354,13 @@
         <v>Medias de Seda</v>
       </c>
       <c r="B155" s="4" t="s">
+        <v>797</v>
+      </c>
+      <c r="C155" s="4" t="s">
         <v>798</v>
       </c>
-      <c r="C155" s="4" t="s">
-        <v>799</v>
-      </c>
       <c r="D155" s="4" t="s">
-        <v>1067</v>
+        <v>1078</v>
       </c>
       <c r="E155" s="1"/>
       <c r="F155" s="1"/>
@@ -62296,7 +62371,7 @@
       <c r="K155" s="1"/>
       <c r="L155" s="1"/>
       <c r="M155" s="4" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="156" spans="1:13" ht="255" x14ac:dyDescent="0.25">
@@ -62305,17 +62380,17 @@
         <v>Brandy Sour</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D156" s="4"/>
       <c r="E156" s="1" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="G156" s="5"/>
       <c r="H156" s="1"/>
@@ -62331,10 +62406,10 @@
         <v>Juanito Rosado</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="D157" s="4" t="s">
         <v>434</v>
@@ -62359,17 +62434,17 @@
         <v>Vino Navegado</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="D158" s="10"/>
       <c r="E158" s="1" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="G158" s="1"/>
       <c r="H158" s="1"/>
@@ -62378,7 +62453,7 @@
       <c r="K158" s="1"/>
       <c r="L158" s="1"/>
       <c r="M158" s="10" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
     </row>
     <row r="159" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62387,32 +62462,32 @@
         <v>Cola de Mono</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="G159" s="5"/>
       <c r="H159" s="1" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="I159" s="10" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="J159" s="1"/>
       <c r="K159" s="1"/>
       <c r="L159" s="1"/>
       <c r="M159" s="4" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="160" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62421,22 +62496,22 @@
         <v>Chichón</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="E160" s="1" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F160" s="5" t="s">
         <v>1018</v>
       </c>
-      <c r="F160" s="5" t="s">
-        <v>1019</v>
-      </c>
       <c r="G160" s="4" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="H160" s="1"/>
       <c r="I160" s="5"/>
@@ -62444,7 +62519,7 @@
       <c r="K160" s="1"/>
       <c r="L160" s="1"/>
       <c r="M160" s="4" t="s">
-        <v>1024</v>
+        <v>1023</v>
       </c>
     </row>
     <row r="161" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -62453,10 +62528,10 @@
         <v>Ramos Fizz</v>
       </c>
       <c r="B161" s="4" t="s">
+        <v>838</v>
+      </c>
+      <c r="C161" s="4" t="s">
         <v>839</v>
-      </c>
-      <c r="C161" s="4" t="s">
-        <v>840</v>
       </c>
       <c r="D161" s="4"/>
       <c r="E161" s="1"/>
@@ -62475,17 +62550,17 @@
         <v>Gin Fizz</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="D162" s="4"/>
       <c r="E162" s="1" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="G162" s="5"/>
       <c r="H162" s="5"/>
@@ -62502,16 +62577,16 @@
       </c>
       <c r="B163" s="1"/>
       <c r="C163" s="4" t="s">
+        <v>851</v>
+      </c>
+      <c r="D163" s="4" t="s">
+        <v>850</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>853</v>
+      </c>
+      <c r="F163" s="5" t="s">
         <v>852</v>
-      </c>
-      <c r="D163" s="4" t="s">
-        <v>851</v>
-      </c>
-      <c r="E163" s="1" t="s">
-        <v>854</v>
-      </c>
-      <c r="F163" s="5" t="s">
-        <v>853</v>
       </c>
       <c r="G163" s="5"/>
       <c r="H163" s="1"/>
@@ -62520,7 +62595,7 @@
       <c r="K163" s="1"/>
       <c r="L163" s="1"/>
       <c r="M163" s="4" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
     </row>
     <row r="164" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62530,29 +62605,29 @@
       </c>
       <c r="B164" s="4"/>
       <c r="C164" s="4" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="G164" s="5"/>
       <c r="H164" s="1"/>
       <c r="I164" s="5"/>
       <c r="J164" s="1" t="s">
-        <v>865</v>
+        <v>864</v>
       </c>
       <c r="K164" s="1" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="L164" s="1"/>
       <c r="M164" s="4" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
     </row>
     <row r="165" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62561,22 +62636,22 @@
         <v>Pihuelo</v>
       </c>
       <c r="B165" s="4" t="s">
+        <v>867</v>
+      </c>
+      <c r="C165" s="4" t="s">
         <v>868</v>
       </c>
-      <c r="C165" s="4" t="s">
-        <v>869</v>
-      </c>
       <c r="D165" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="E165" s="4" t="s">
+        <v>1028</v>
+      </c>
+      <c r="F165" s="5" t="s">
         <v>1029</v>
       </c>
-      <c r="F165" s="5" t="s">
+      <c r="G165" s="1" t="s">
         <v>1030</v>
-      </c>
-      <c r="G165" s="1" t="s">
-        <v>1031</v>
       </c>
       <c r="H165" s="1"/>
       <c r="I165" s="5"/>
@@ -62584,7 +62659,7 @@
       <c r="K165" s="1"/>
       <c r="L165" s="1"/>
       <c r="M165" s="4" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="166" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62593,19 +62668,19 @@
         <v>Mojito Sandía</v>
       </c>
       <c r="B166" s="4" t="s">
+        <v>879</v>
+      </c>
+      <c r="C166" s="4" t="s">
         <v>880</v>
       </c>
-      <c r="C166" s="4" t="s">
-        <v>881</v>
-      </c>
       <c r="D166" s="4" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="E166" s="1" t="s">
+        <v>877</v>
+      </c>
+      <c r="F166" s="5" t="s">
         <v>878</v>
-      </c>
-      <c r="F166" s="5" t="s">
-        <v>879</v>
       </c>
       <c r="G166" s="5"/>
       <c r="H166" s="1"/>
@@ -62614,7 +62689,7 @@
       <c r="K166" s="1"/>
       <c r="L166" s="1"/>
       <c r="M166" s="4" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
     </row>
     <row r="167" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62624,7 +62699,7 @@
       </c>
       <c r="B167" s="1"/>
       <c r="C167" s="4" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="D167" s="4"/>
       <c r="E167" s="1"/>
@@ -62636,7 +62711,7 @@
       <c r="K167" s="1"/>
       <c r="L167" s="1"/>
       <c r="M167" s="4" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="168" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -62646,7 +62721,7 @@
       </c>
       <c r="B168" s="1"/>
       <c r="C168" s="4" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="D168" s="4"/>
       <c r="E168" s="1"/>
@@ -62658,7 +62733,7 @@
       <c r="K168" s="1"/>
       <c r="L168" s="1"/>
       <c r="M168" s="4" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="169" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -62667,10 +62742,10 @@
         <v>Chardonnay Sour</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="D169" s="4"/>
       <c r="E169" s="1"/>
@@ -62689,13 +62764,13 @@
         <v>Carmenere Sour</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>470</v>
@@ -62710,7 +62785,7 @@
       <c r="K170" s="1"/>
       <c r="L170" s="1"/>
       <c r="M170" s="4" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
     </row>
     <row r="171" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62719,13 +62794,13 @@
         <v>Jerez Sour</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="E171" s="1"/>
       <c r="F171" s="1"/>
@@ -62736,7 +62811,7 @@
       <c r="K171" s="1"/>
       <c r="L171" s="1"/>
       <c r="M171" s="4" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="172" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -62746,7 +62821,7 @@
       </c>
       <c r="B172" s="4"/>
       <c r="C172" s="4" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="D172" s="4"/>
       <c r="E172" s="1"/>
@@ -62758,13 +62833,13 @@
       <c r="K172" s="1"/>
       <c r="L172" s="1"/>
       <c r="M172" s="4" t="s">
-        <v>1064</v>
-      </c>
-    </row>
-    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1063</v>
+      </c>
+    </row>
+    <row r="173" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="str">
         <f>IF(receta!A173="","",receta!A173)</f>
-        <v/>
+        <v>Campari &amp; Tonic</v>
       </c>
       <c r="B173" s="1"/>
       <c r="C173" s="4"/>
@@ -62777,14 +62852,18 @@
       <c r="J173" s="1"/>
       <c r="K173" s="1"/>
       <c r="L173" s="1"/>
-      <c r="M173" s="1"/>
-    </row>
-    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="M173" s="4" t="s">
+        <v>1084</v>
+      </c>
+    </row>
+    <row r="174" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="str">
         <f>IF(receta!A174="","",receta!A174)</f>
-        <v/>
-      </c>
-      <c r="B174" s="1"/>
+        <v>Campari Spritz</v>
+      </c>
+      <c r="B174" s="4" t="s">
+        <v>1083</v>
+      </c>
       <c r="C174" s="4"/>
       <c r="D174" s="4"/>
       <c r="E174" s="1"/>
@@ -62795,7 +62874,9 @@
       <c r="J174" s="1"/>
       <c r="K174" s="1"/>
       <c r="L174" s="1"/>
-      <c r="M174" s="1"/>
+      <c r="M174" s="4" t="s">
+        <v>1082</v>
+      </c>
     </row>
     <row r="175" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="str">
@@ -64280,7 +64361,7 @@
         <v>62</v>
       </c>
       <c r="B2" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C2" t="s">
         <v>575</v>
@@ -64291,7 +64372,7 @@
         <v>67</v>
       </c>
       <c r="B3" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C3" t="s">
         <v>202</v>
@@ -64302,10 +64383,10 @@
         <v>68</v>
       </c>
       <c r="B4" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C4" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -64313,7 +64394,7 @@
         <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C5" t="s">
         <v>203</v>
@@ -64324,10 +64405,10 @@
         <v>69</v>
       </c>
       <c r="B6" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C6" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -64335,7 +64416,7 @@
         <v>70</v>
       </c>
       <c r="B7" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C7" t="s">
         <v>71</v>
@@ -64343,24 +64424,24 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="B8" t="s">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C8" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>806</v>
+      </c>
+      <c r="B9" t="s">
         <v>807</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>808</v>
-      </c>
-      <c r="C9" t="s">
-        <v>809</v>
       </c>
     </row>
   </sheetData>
@@ -64446,7 +64527,7 @@
         <v>428</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>767</v>
+        <v>766</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -64459,10 +64540,10 @@
     </row>
     <row r="11" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="23" t="s">
+        <v>700</v>
+      </c>
+      <c r="B11" s="23" t="s">
         <v>701</v>
-      </c>
-      <c r="B11" s="23" t="s">
-        <v>702</v>
       </c>
     </row>
   </sheetData>

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75B28F7E-A49F-4E22-804E-3559E7BF14DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4423834-1C6E-4459-ABD1-E339E6B66F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
+    <workbookView xWindow="0" yWindow="1440" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
   <sheets>
     <sheet name="receta" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1642" uniqueCount="1085">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1643" uniqueCount="1085">
   <si>
     <t>Ramazzotti Spritz</t>
   </si>
@@ -5054,11 +5054,11 @@
 Afiche publicitario de Bitter Campari, diseñado por el ilustrador italiano Leonetto Cappiello hacia la década de 1920.</t>
   </si>
   <si>
-    <t>Para un Spritz, lo ideal es usar un espumante seco y ligero, que aporte frescura sin dominar el aperitivo. La opción clásica es el Prosecco, el espumante tradicional del Spritz en Italia, pero en Chile suele tener un costo más elevado. Por ello, un espumante Brut es una muy buena alternativa local: conserva la acidez y la vivacidad necesarias para equilibrar el trago, sin hacerlo excesivamente dulce.</t>
-  </si>
-  <si>
     <t>Schweppestonic.jpg
 Anuncio publicitario de Schweppes Tonic Water, publicado en la revista canadiense Maclean’s, 7 de julio de 1986.</t>
+  </si>
+  <si>
+    <t>Para un Spritz, lo ideal es usar un espumante seco y ligero, que aporte frescura sin dominar el aperitivo. La opción clásica es el Prosecco, el espumante tradicional del Spritz en Italia, aunque en Chile suele tener un costo más elevado. Por ello, un espumante Brut es una muy buena alternativa local, ya que conserva la acidez y la vivacidad necesarias para equilibrar el trago, sin volverlo excesivamente dulce.</t>
   </si>
 </sst>
 </file>
@@ -58500,7 +58500,7 @@
         <v>Amaretto Spritz</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>352</v>
@@ -58604,7 +58604,7 @@
         <v>Aperol Spritz</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>599</v>
@@ -58648,7 +58648,7 @@
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
-    <row r="13" spans="1:13" ht="195" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="210" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="str">
         <f>IF(receta!A13="","",receta!A13)</f>
         <v>Bellini</v>
@@ -59148,7 +59148,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="240" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" ht="255" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="str">
         <f>IF(receta!A32="","",receta!A32)</f>
         <v>Cléry Durazno</v>
@@ -59334,7 +59334,7 @@
         <v>Cynar Spritz</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>333</v>
@@ -59656,7 +59656,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="str">
         <f>IF(receta!A51="","",receta!A51)</f>
         <v>Espresso Martini</v>
@@ -60888,7 +60888,7 @@
         <v>Mojito Spritz</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>724</v>
@@ -61444,7 +61444,7 @@
         <v>Ramazzotti Spritz</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>353</v>
@@ -61464,12 +61464,14 @@
       <c r="L120" s="5"/>
       <c r="M120" s="1"/>
     </row>
-    <row r="121" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="str">
         <f>IF(receta!A121="","",receta!A121)</f>
         <v>Ramazzotti Violetto Spritz</v>
       </c>
-      <c r="B121" s="1"/>
+      <c r="B121" s="4" t="s">
+        <v>1084</v>
+      </c>
       <c r="C121" s="4" t="s">
         <v>746</v>
       </c>
@@ -62853,7 +62855,7 @@
       <c r="K173" s="1"/>
       <c r="L173" s="1"/>
       <c r="M173" s="4" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="174" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -62862,7 +62864,7 @@
         <v>Campari Spritz</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="C174" s="4"/>
       <c r="D174" s="4"/>

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4423834-1C6E-4459-ABD1-E339E6B66F1F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E98422E-BA08-4B4E-9401-DD49F880E997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="1440" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1643" uniqueCount="1085">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1644" uniqueCount="1086">
   <si>
     <t>Ramazzotti Spritz</t>
   </si>
@@ -5059,6 +5059,9 @@
   </si>
   <si>
     <t>Para un Spritz, lo ideal es usar un espumante seco y ligero, que aporte frescura sin dominar el aperitivo. La opción clásica es el Prosecco, el espumante tradicional del Spritz en Italia, aunque en Chile suele tener un costo más elevado. Por ello, un espumante Brut es una muy buena alternativa local, ya que conserva la acidez y la vivacidad necesarias para equilibrar el trago, sin volverlo excesivamente dulce.</t>
+  </si>
+  <si>
+    <t>Lo ideal es usar un espumante seco y ligero, que aporte frescura sin dominar el aperitivo. La opción clásica es el Prosecco, el espumante tradicional del Spritz en Italia, aunque en Chile suele tener un costo más elevado. Por ello, un espumante Brut es una muy buena alternativa local, ya que conserva la acidez y la vivacidad necesarias para equilibrar el trago, sin volverlo excesivamente dulce.</t>
   </si>
 </sst>
 </file>
@@ -58648,7 +58651,7 @@
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
-    <row r="13" spans="1:13" ht="210" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="195" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="str">
         <f>IF(receta!A13="","",receta!A13)</f>
         <v>Bellini</v>
@@ -59148,7 +59151,7 @@
         <v>976</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="255" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" ht="240" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="str">
         <f>IF(receta!A32="","",receta!A32)</f>
         <v>Cléry Durazno</v>
@@ -59656,7 +59659,7 @@
         <v>960</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="str">
         <f>IF(receta!A51="","",receta!A51)</f>
         <v>Espresso Martini</v>
@@ -60069,7 +60072,9 @@
         <f>IF(receta!A66="","",receta!A66)</f>
         <v>Hugo</v>
       </c>
-      <c r="B66" s="1"/>
+      <c r="B66" s="1" t="s">
+        <v>1085</v>
+      </c>
       <c r="C66" s="4" t="s">
         <v>732</v>
       </c>

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7E98422E-BA08-4B4E-9401-DD49F880E997}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7BA5AD7-8844-4066-9DAB-3E933559D5B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="1440" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
   <sheets>
     <sheet name="receta" sheetId="1" r:id="rId1"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1644" uniqueCount="1086">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1645" uniqueCount="1087">
   <si>
     <t>Ramazzotti Spritz</t>
   </si>
@@ -5062,6 +5062,10 @@
   </si>
   <si>
     <t>Lo ideal es usar un espumante seco y ligero, que aporte frescura sin dominar el aperitivo. La opción clásica es el Prosecco, el espumante tradicional del Spritz en Italia, aunque en Chile suele tener un costo más elevado. Por ello, un espumante Brut es una muy buena alternativa local, ya que conserva la acidez y la vivacidad necesarias para equilibrar el trago, sin volverlo excesivamente dulce.</t>
+  </si>
+  <si>
+    <t>Lemmy2.jpg
+Lemmy Kilmister, líder y bajista de Motörhead, fotografiado en el Hammersmith Odeon de Londres el 26 de marzo de 1982. Fotografía de Steve Rapport.</t>
   </si>
 </sst>
 </file>
@@ -62179,7 +62183,9 @@
       <c r="J148" s="1"/>
       <c r="K148" s="5"/>
       <c r="L148" s="5"/>
-      <c r="M148" s="1"/>
+      <c r="M148" s="4" t="s">
+        <v>1086</v>
+      </c>
     </row>
     <row r="149" spans="1:13" ht="324" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="str">

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7BA5AD7-8844-4066-9DAB-3E933559D5B2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D3587C-2CC6-4C3C-857E-2DE7161A1DE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1645" uniqueCount="1087">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1646" uniqueCount="1088">
   <si>
     <t>Ramazzotti Spritz</t>
   </si>
@@ -3918,10 +3918,6 @@
 Para lograr una espuma más cremosa y uniforme, se recomienda aplicar la técnica dry shake, que consiste en agitar los ingredientes sin hielo durante unos segundos antes de volver a agitarlos con hielo. Este primer batido en seco permite emulsionar correctamente la clara de huevo, generando una textura sedosa y una corona espumosa más estable al servir.</t>
   </si>
   <si>
-    <t>La bebida fue inventada por Henry Ramos en 1888, en su bar Meyer’s Table d’Hôtel Internationale, en Nueva Orleans. La combinación de crema y clara de huevo requiere una agitación prolongada para emulsionar adecuadamente y conseguir una espuma densa y sedosa. Originalmente, el Ramos Fizz se agitaba durante cerca de doce minutos, tarea que realizaba un equipo de bármanes que se iban pasando la coctelera cuando sus brazos se cansaban, con el fin de mantener un batido constante y lograr su característica textura.
-El cóctel se hizo tan famoso que, según relatos de la época, para ciertas festividades era necesario contratar a más de una docena de “shaker boys” dedicados exclusivamente a agitar Ramos Fizz. Esta dedicación contribuyó a consolidar la bebida como uno de los grandes íconos de la coctelería clásica de Nueva Orleans.</t>
-  </si>
-  <si>
     <t>El Clover Club es un cóctel clásico estadounidense que antecede a la Ley Seca y debe su nombre a un club de caballeros de Filadelfia que se reunía en el Hotel Bellevue-Stratford. La receta aparece en publicaciones desde 1908, bajo el nombre “Hoja de Trébol”, y fue recogida oficialmente como The Clover Club Cocktail en The Barkeeper’s Manual de Raymond E. Sullivan en 1910, donde se incluía una ramita de menta como decoración. Con el tiempo, la menta fue eliminada de la receta, y su presencia hoy en día suele asociarse a una variante llamada precisamente “Hoja de Trébol”.
 Aunque la receta aquí compartida corresponde al Clover Club clásico, incluido en la lista oficial de la IBA, existen diversas adaptaciones del cóctel. Una de las más conocidas sustituye el jarabe de frambuesa por granadina, mientras que otra variante contemporánea muy apreciada reemplaza ½ oz de gin por ½ oz de vermouth dry. Esta última aporta un perfil más seco y herbal, dando como resultado un cóctel de mayor complejidad aromática.</t>
   </si>
@@ -3975,9 +3971,6 @@
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=iCifleyKJMg</t>
-  </si>
-  <si>
-    <t>Santiago del Nuevo Extremo · Inti illimani - La Mitad Lejana</t>
   </si>
   <si>
     <t>Orgasmo</t>
@@ -5066,6 +5059,17 @@
   <si>
     <t>Lemmy2.jpg
 Lemmy Kilmister, líder y bajista de Motörhead, fotografiado en el Hammersmith Odeon de Londres el 26 de marzo de 1982. Fotografía de Steve Rapport.</t>
+  </si>
+  <si>
+    <t>Santiago del Nuevo Extremo e Inti illimani - La Mitad Lejana</t>
+  </si>
+  <si>
+    <t>La bebida fue inventada por Henry C. Ramos en el bar Imperial Cabinet Saloon de Nueva Orleans. La combinación de crema y clara de huevo requiere una agitación prolongada para emulsionar adecuadamente y conseguir una espuma densa y sedosa. Originalmente, el Ramos Fizz se agitaba durante cerca de doce minutos, tarea que realizaba un equipo de bármanes que se iban pasando la coctelera cuando sus brazos se cansaban, con el fin de mantener un batido constante y lograr su característica textura.
+El cóctel se hizo tan famoso que, según relatos de la época, para ciertas festividades era necesario contratar a más de una docena de “shaker boys” dedicados exclusivamente a agitar Ramos Fizz. Esta dedicación contribuyó a consolidar la bebida como uno de los grandes íconos de la coctelería clásica de Nueva Orleans.</t>
+  </si>
+  <si>
+    <t>ramos.jpg
+Henry C. Ramos (1846–1928), barman de Nueva Orleans y creador del Ramos Gin Fizz en 1888.</t>
   </si>
 </sst>
 </file>
@@ -5743,7 +5747,7 @@
         <v>78</v>
       </c>
       <c r="O1" s="27" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="P1" s="27" t="s">
         <v>691</v>
@@ -5761,7 +5765,7 @@
         <v>565</v>
       </c>
       <c r="U1" s="27" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
       <c r="V1" s="27" t="s">
         <v>617</v>
@@ -5785,10 +5789,10 @@
         <v>824</v>
       </c>
       <c r="AC1" s="27" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="AD1" s="27" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="AE1" s="27" t="s">
         <v>82</v>
@@ -5842,7 +5846,7 @@
         <v>200</v>
       </c>
       <c r="AV1" s="27" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="AW1" s="27" t="s">
         <v>209</v>
@@ -6031,10 +6035,10 @@
         <v>665</v>
       </c>
       <c r="DG1" s="18" t="s">
+        <v>842</v>
+      </c>
+      <c r="DH1" s="18" t="s">
         <v>843</v>
-      </c>
-      <c r="DH1" s="18" t="s">
-        <v>844</v>
       </c>
       <c r="DI1" s="15" t="s">
         <v>136</v>
@@ -6097,13 +6101,13 @@
         <v>559</v>
       </c>
       <c r="EC1" s="21" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="ED1" s="25" t="s">
         <v>812</v>
       </c>
       <c r="EE1" s="12" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="EF1" s="14" t="s">
         <v>608</v>
@@ -6154,7 +6158,7 @@
         <v>231</v>
       </c>
       <c r="EV1" s="20" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="EW1" s="20" t="s">
         <v>232</v>
@@ -34871,7 +34875,7 @@
     </row>
     <row r="163" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>849</v>
+        <v>848</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>51</v>
@@ -35051,7 +35055,7 @@
     </row>
     <row r="164" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>53</v>
@@ -35229,7 +35233,7 @@
     </row>
     <row r="165" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>51</v>
@@ -35405,7 +35409,7 @@
     </row>
     <row r="166" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>50</v>
@@ -35587,7 +35591,7 @@
     </row>
     <row r="167" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>53</v>
@@ -35765,7 +35769,7 @@
     </row>
     <row r="168" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>55</v>
@@ -35939,7 +35943,7 @@
     </row>
     <row r="169" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>892</v>
+        <v>890</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>55</v>
@@ -36117,7 +36121,7 @@
     </row>
     <row r="170" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>53</v>
@@ -36293,7 +36297,7 @@
     </row>
     <row r="171" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>55</v>
@@ -36469,7 +36473,7 @@
     </row>
     <row r="172" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>53</v>
@@ -36647,7 +36651,7 @@
     </row>
     <row r="173" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>52</v>
@@ -36823,7 +36827,7 @@
     </row>
     <row r="174" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>1081</v>
+        <v>1079</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>49</v>
@@ -48871,7 +48875,7 @@
         <v>580</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="P1" s="8" t="s">
         <v>132</v>
@@ -58342,7 +58346,7 @@
         <v>315</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>316</v>
@@ -58357,7 +58361,7 @@
         <v>763</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
       <c r="M1" s="7" t="s">
         <v>811</v>
@@ -58388,7 +58392,7 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="4" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58434,7 +58438,7 @@
         <v>239</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="5"/>
@@ -58470,7 +58474,7 @@
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
       <c r="M5" s="4" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="270" x14ac:dyDescent="0.25">
@@ -58498,7 +58502,7 @@
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="4" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="270" x14ac:dyDescent="0.25">
@@ -58507,7 +58511,7 @@
         <v>Amaretto Spritz</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>352</v>
@@ -58526,7 +58530,7 @@
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="4" t="s">
-        <v>954</v>
+        <v>952</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="210" x14ac:dyDescent="0.25">
@@ -58552,7 +58556,7 @@
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="4" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -58580,7 +58584,7 @@
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
       <c r="M9" s="1" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="210" x14ac:dyDescent="0.25">
@@ -58611,7 +58615,7 @@
         <v>Aperol Spritz</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>599</v>
@@ -58628,7 +58632,7 @@
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="4" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58676,7 +58680,7 @@
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="4" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58704,7 +58708,7 @@
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="4" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58728,7 +58732,7 @@
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="4" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -58740,13 +58744,13 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -58832,7 +58836,7 @@
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="4" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -58884,7 +58888,7 @@
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="4" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="375" x14ac:dyDescent="0.25">
@@ -58912,7 +58916,7 @@
       <c r="K22" s="5"/>
       <c r="L22" s="5"/>
       <c r="M22" s="4" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -58934,7 +58938,7 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="4" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="345" x14ac:dyDescent="0.25">
@@ -58982,7 +58986,7 @@
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="4" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59010,7 +59014,7 @@
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="4" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="375" x14ac:dyDescent="0.25">
@@ -59036,7 +59040,7 @@
       <c r="K27" s="1"/>
       <c r="L27" s="1"/>
       <c r="M27" s="4" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59049,7 +59053,7 @@
         <v>458</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>528</v>
@@ -59061,14 +59065,14 @@
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
       <c r="J28" s="1" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="L28" s="5"/>
       <c r="M28" s="4" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="360" x14ac:dyDescent="0.25">
@@ -59094,7 +59098,7 @@
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="4" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59109,7 +59113,7 @@
         <v>667</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
       <c r="E30" s="1"/>
       <c r="F30" s="1"/>
@@ -59120,7 +59124,7 @@
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="4" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59138,13 +59142,13 @@
         <v>425</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -59152,7 +59156,7 @@
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="4" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -59190,7 +59194,7 @@
         <v>725</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>840</v>
+        <v>839</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>548</v>
@@ -59208,7 +59212,7 @@
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="255" x14ac:dyDescent="0.25">
@@ -59234,7 +59238,7 @@
       <c r="K34" s="5"/>
       <c r="L34" s="5"/>
       <c r="M34" s="4" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -59278,7 +59282,7 @@
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59306,7 +59310,7 @@
       <c r="K37" s="5"/>
       <c r="L37" s="5"/>
       <c r="M37" s="4" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="255" x14ac:dyDescent="0.25">
@@ -59332,7 +59336,7 @@
       <c r="K38" s="5"/>
       <c r="L38" s="5"/>
       <c r="M38" s="4" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -59341,7 +59345,7 @@
         <v>Cynar Spritz</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>333</v>
@@ -59356,7 +59360,7 @@
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="4" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -59377,16 +59381,16 @@
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="1" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
       <c r="J40" s="4"/>
       <c r="K40" s="5"/>
       <c r="L40" s="5"/>
       <c r="M40" s="4" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -59398,7 +59402,7 @@
         <v>725</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="1"/>
@@ -59410,7 +59414,7 @@
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
       <c r="M41" s="4" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59436,7 +59440,7 @@
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="M42" s="4" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="270" x14ac:dyDescent="0.25">
@@ -59464,7 +59468,7 @@
       <c r="K43" s="5"/>
       <c r="L43" s="5"/>
       <c r="M43" s="4" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -59510,7 +59514,7 @@
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
       <c r="M45" s="4" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="285" x14ac:dyDescent="0.25">
@@ -59523,7 +59527,7 @@
       </c>
       <c r="C46" s="4"/>
       <c r="D46" s="4" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>185</v>
@@ -59535,16 +59539,16 @@
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
       <c r="J46" s="4" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
       <c r="K46" s="5" t="s">
+        <v>1029</v>
+      </c>
+      <c r="L46" s="4" t="s">
         <v>1031</v>
       </c>
-      <c r="L46" s="4" t="s">
-        <v>1033</v>
-      </c>
       <c r="M46" s="4" t="s">
-        <v>985</v>
+        <v>983</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -59572,7 +59576,7 @@
       <c r="K47" s="5"/>
       <c r="L47" s="5"/>
       <c r="M47" s="4" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="315" x14ac:dyDescent="0.25">
@@ -59620,7 +59624,7 @@
         <v>768</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -59628,7 +59632,7 @@
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
       <c r="M49" s="4" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="255" x14ac:dyDescent="0.25">
@@ -59648,7 +59652,7 @@
         <v>481</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>326</v>
@@ -59660,7 +59664,7 @@
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
       <c r="M50" s="4" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -59682,7 +59686,7 @@
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
       <c r="M51" s="1" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="150" x14ac:dyDescent="0.25">
@@ -59714,7 +59718,7 @@
       <c r="K52" s="1"/>
       <c r="L52" s="1"/>
       <c r="M52" s="4" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="390" x14ac:dyDescent="0.25">
@@ -59736,7 +59740,7 @@
         <v>404</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>384</v>
@@ -59748,7 +59752,7 @@
       <c r="K53" s="1"/>
       <c r="L53" s="1"/>
       <c r="M53" s="4" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59774,7 +59778,7 @@
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
       <c r="M54" s="4" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
@@ -59820,7 +59824,7 @@
         <v>473</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -59828,7 +59832,7 @@
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
       <c r="M56" s="4" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59856,7 +59860,7 @@
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
       <c r="M57" s="4" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="150" x14ac:dyDescent="0.25">
@@ -59880,7 +59884,7 @@
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="4" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59910,7 +59914,7 @@
       <c r="K59" s="5"/>
       <c r="L59" s="5"/>
       <c r="M59" s="4" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -59932,7 +59936,7 @@
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
       <c r="M60" s="4" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="165" x14ac:dyDescent="0.25">
@@ -59948,10 +59952,10 @@
         <v>388</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="4"/>
@@ -59960,7 +59964,7 @@
       <c r="K61" s="1"/>
       <c r="L61" s="1"/>
       <c r="M61" s="4" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="345" x14ac:dyDescent="0.25">
@@ -59986,7 +59990,7 @@
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
       <c r="M62" s="4" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60019,10 +60023,10 @@
         <v>765</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="M63" s="4" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -60044,7 +60048,7 @@
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
       <c r="M64" s="4" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60068,7 +60072,7 @@
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
       <c r="M65" s="1" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="375" x14ac:dyDescent="0.25">
@@ -60077,7 +60081,7 @@
         <v>Hugo</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>1085</v>
+        <v>1083</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>732</v>
@@ -60094,7 +60098,7 @@
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
       <c r="M66" s="4" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="67" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60120,7 +60124,7 @@
       <c r="K67" s="5"/>
       <c r="L67" s="5"/>
       <c r="M67" s="4" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
     </row>
     <row r="68" spans="1:13" ht="330" x14ac:dyDescent="0.25">
@@ -60130,7 +60134,7 @@
       </c>
       <c r="B68" s="1"/>
       <c r="C68" s="1" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>593</v>
@@ -60148,7 +60152,7 @@
       <c r="K68" s="5"/>
       <c r="L68" s="5"/>
       <c r="M68" s="4" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
     </row>
     <row r="69" spans="1:13" ht="300" x14ac:dyDescent="0.25">
@@ -60176,7 +60180,7 @@
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
       <c r="M69" s="4" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -60204,7 +60208,7 @@
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
       <c r="M70" s="4" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -60230,7 +60234,7 @@
       <c r="K71" s="5"/>
       <c r="L71" s="5"/>
       <c r="M71" s="4" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
     <row r="72" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60245,7 +60249,7 @@
         <v>633</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="E72" s="1"/>
       <c r="F72" s="5"/>
@@ -60260,7 +60264,7 @@
       <c r="K72" s="5"/>
       <c r="L72" s="5"/>
       <c r="M72" s="4" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
     </row>
     <row r="73" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -60273,7 +60277,7 @@
       </c>
       <c r="C73" s="4"/>
       <c r="D73" s="4" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
@@ -60284,7 +60288,7 @@
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
       <c r="M73" s="4" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="74" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60338,7 +60342,7 @@
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
       <c r="M75" s="4" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="76" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60374,10 +60378,10 @@
       </c>
       <c r="B77" s="1"/>
       <c r="C77" s="4" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>1014</v>
+        <v>1012</v>
       </c>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
@@ -60388,7 +60392,7 @@
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
       <c r="M77" s="4" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="78" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -60502,7 +60506,7 @@
       <c r="K82" s="1"/>
       <c r="L82" s="1"/>
       <c r="M82" s="4" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60512,7 +60516,7 @@
       </c>
       <c r="B83" s="1"/>
       <c r="C83" s="4" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>304</v>
@@ -60530,7 +60534,7 @@
       <c r="K83" s="5"/>
       <c r="L83" s="5"/>
       <c r="M83" s="4" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
     </row>
     <row r="84" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60545,7 +60549,7 @@
         <v>659</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
@@ -60560,7 +60564,7 @@
       <c r="K84" s="1"/>
       <c r="L84" s="1"/>
       <c r="M84" s="4" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -60575,7 +60579,7 @@
         <v>660</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
@@ -60590,7 +60594,7 @@
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
       <c r="M85" s="4" t="s">
-        <v>984</v>
+        <v>982</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -60640,7 +60644,7 @@
       <c r="K87" s="5"/>
       <c r="L87" s="5"/>
       <c r="M87" s="4" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
     </row>
     <row r="88" spans="1:13" ht="360" x14ac:dyDescent="0.25">
@@ -60655,7 +60659,7 @@
         <v>635</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
@@ -60666,7 +60670,7 @@
       <c r="K88" s="1"/>
       <c r="L88" s="1"/>
       <c r="M88" s="4" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="89" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -60688,7 +60692,7 @@
         <v>180</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
@@ -60696,7 +60700,7 @@
       <c r="K89" s="5"/>
       <c r="L89" s="5"/>
       <c r="M89" s="4" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
@@ -60753,10 +60757,10 @@
         <v>Michelada</v>
       </c>
       <c r="B92" s="4" t="s">
+        <v>840</v>
+      </c>
+      <c r="C92" s="4" t="s">
         <v>841</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>842</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>401</v>
@@ -60794,7 +60798,7 @@
       <c r="K93" s="1"/>
       <c r="L93" s="1"/>
       <c r="M93" s="4" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="94" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -60816,7 +60820,7 @@
       <c r="K94" s="1"/>
       <c r="L94" s="1"/>
       <c r="M94" s="4" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="95" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -60840,7 +60844,7 @@
       <c r="K95" s="1"/>
       <c r="L95" s="1"/>
       <c r="M95" s="4" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="96" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -60873,13 +60877,13 @@
         <v>578</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
       <c r="G97" s="1"/>
       <c r="H97" s="4"/>
@@ -60888,7 +60892,7 @@
       <c r="K97" s="1"/>
       <c r="L97" s="1"/>
       <c r="M97" s="4" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="98" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -60897,7 +60901,7 @@
         <v>Mojito Spritz</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>724</v>
@@ -60936,7 +60940,7 @@
       <c r="K99" s="5"/>
       <c r="L99" s="5"/>
       <c r="M99" s="4" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="100" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -61010,7 +61014,7 @@
       <c r="K102" s="1"/>
       <c r="L102" s="1"/>
       <c r="M102" s="4" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
     </row>
     <row r="103" spans="1:13" ht="210" x14ac:dyDescent="0.25">
@@ -61032,7 +61036,7 @@
       <c r="K103" s="1"/>
       <c r="L103" s="1"/>
       <c r="M103" s="4" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="104" spans="1:13" ht="345" x14ac:dyDescent="0.25">
@@ -61062,7 +61066,7 @@
       <c r="K104" s="5"/>
       <c r="L104" s="5"/>
       <c r="M104" s="4" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="105" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -61088,7 +61092,7 @@
       <c r="K105" s="1"/>
       <c r="L105" s="1"/>
       <c r="M105" s="4" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
     </row>
     <row r="106" spans="1:13" ht="375" x14ac:dyDescent="0.25">
@@ -61104,25 +61108,25 @@
         <v>563</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
       <c r="I106" s="5" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="J106" s="1"/>
       <c r="K106" s="1"/>
       <c r="L106" s="1"/>
       <c r="M106" s="4" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="107" spans="1:13" ht="192" customHeight="1" x14ac:dyDescent="0.25">
@@ -61161,7 +61165,7 @@
       <c r="F108" s="1"/>
       <c r="G108" s="1"/>
       <c r="H108" s="1" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
       <c r="I108" s="5" t="s">
         <v>256</v>
@@ -61170,7 +61174,7 @@
       <c r="K108" s="1"/>
       <c r="L108" s="1"/>
       <c r="M108" s="4" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="109" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -61205,7 +61209,7 @@
         <v>672</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="E110" s="4" t="s">
         <v>583</v>
@@ -61220,7 +61224,7 @@
       <c r="K110" s="5"/>
       <c r="L110" s="5"/>
       <c r="M110" s="4" t="s">
-        <v>1006</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.25">
@@ -61264,7 +61268,7 @@
         <v>483</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="H112" s="1"/>
       <c r="I112" s="5"/>
@@ -61283,7 +61287,7 @@
         <v>464</v>
       </c>
       <c r="D113" s="5"/>
-      <c r="E113" s="6" t="s">
+      <c r="E113" s="1" t="s">
         <v>416</v>
       </c>
       <c r="F113" s="5" t="s">
@@ -61296,7 +61300,7 @@
       <c r="K113" s="5"/>
       <c r="L113" s="5"/>
       <c r="M113" s="4" t="s">
-        <v>1073</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.25">
@@ -61390,7 +61394,7 @@
       <c r="K117" s="5"/>
       <c r="L117" s="5"/>
       <c r="M117" s="4" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="118" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -61444,7 +61448,7 @@
       <c r="K119" s="5"/>
       <c r="L119" s="5"/>
       <c r="M119" s="4" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="120" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -61453,7 +61457,7 @@
         <v>Ramazzotti Spritz</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>353</v>
@@ -61479,7 +61483,7 @@
         <v>Ramazzotti Violetto Spritz</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>746</v>
@@ -61544,7 +61548,7 @@
       <c r="K123" s="5"/>
       <c r="L123" s="5"/>
       <c r="M123" s="4" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
     </row>
     <row r="124" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -61660,7 +61664,7 @@
       <c r="K128" s="1"/>
       <c r="L128" s="1"/>
       <c r="M128" s="4" t="s">
-        <v>1008</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="129" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -61673,7 +61677,7 @@
         <v>369</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
       <c r="E129" s="1"/>
       <c r="F129" s="1"/>
@@ -61684,7 +61688,7 @@
       <c r="K129" s="1"/>
       <c r="L129" s="1"/>
       <c r="M129" s="4" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="130" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -61726,7 +61730,7 @@
       <c r="K131" s="1"/>
       <c r="L131" s="1"/>
       <c r="M131" s="4" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="132" spans="1:13" ht="165" x14ac:dyDescent="0.25">
@@ -61752,7 +61756,7 @@
       <c r="K132" s="5"/>
       <c r="L132" s="5"/>
       <c r="M132" s="4" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.25">
@@ -61800,7 +61804,7 @@
       <c r="K134" s="5"/>
       <c r="L134" s="5"/>
       <c r="M134" s="4" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
     </row>
     <row r="135" spans="1:13" ht="300" x14ac:dyDescent="0.25">
@@ -61812,25 +61816,25 @@
         <v>651</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
       <c r="E135" s="1"/>
       <c r="F135" s="1"/>
       <c r="G135" s="1"/>
       <c r="H135" s="1" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
       <c r="I135" s="5" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
       <c r="J135" s="1"/>
       <c r="K135" s="1"/>
       <c r="L135" s="1"/>
       <c r="M135" s="4" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
     </row>
     <row r="136" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -61870,13 +61874,13 @@
         <v>433</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
       <c r="F137" s="5" t="s">
+        <v>1032</v>
+      </c>
+      <c r="G137" s="4" t="s">
         <v>1034</v>
-      </c>
-      <c r="G137" s="4" t="s">
-        <v>1036</v>
       </c>
       <c r="H137" s="1"/>
       <c r="I137" s="1"/>
@@ -61904,7 +61908,7 @@
       <c r="K138" s="1"/>
       <c r="L138" s="1"/>
       <c r="M138" s="4" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
     </row>
     <row r="139" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -61946,13 +61950,13 @@
         <v>345</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="F140" s="5" t="s">
+        <v>1018</v>
+      </c>
+      <c r="G140" s="4" t="s">
         <v>1020</v>
-      </c>
-      <c r="G140" s="4" t="s">
-        <v>1022</v>
       </c>
       <c r="H140" s="1"/>
       <c r="I140" s="1"/>
@@ -61964,7 +61968,7 @@
       </c>
       <c r="L140" s="5"/>
       <c r="M140" s="4" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="141" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -61979,7 +61983,7 @@
         <v>683</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="E141" s="4" t="s">
         <v>610</v>
@@ -62046,7 +62050,7 @@
       <c r="K143" s="1"/>
       <c r="L143" s="1"/>
       <c r="M143" s="4" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
     </row>
     <row r="144" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62069,20 +62073,20 @@
       </c>
       <c r="G144" s="1"/>
       <c r="H144" s="1" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
       <c r="I144" s="5" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="K144" s="5" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="L144" s="1"/>
       <c r="M144" s="4" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
     </row>
     <row r="145" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62112,7 +62116,7 @@
       <c r="K145" s="1"/>
       <c r="L145" s="1"/>
       <c r="M145" s="4" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="146" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -62158,7 +62162,7 @@
       <c r="K147" s="5"/>
       <c r="L147" s="5"/>
       <c r="M147" s="4" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="148" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -62184,7 +62188,7 @@
       <c r="K148" s="5"/>
       <c r="L148" s="5"/>
       <c r="M148" s="4" t="s">
-        <v>1086</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="149" spans="1:13" ht="324" customHeight="1" x14ac:dyDescent="0.25">
@@ -62212,7 +62216,7 @@
       <c r="K149" s="5"/>
       <c r="L149" s="5"/>
       <c r="M149" s="4" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="150" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62242,7 +62246,7 @@
       <c r="K150" s="1"/>
       <c r="L150" s="1"/>
       <c r="M150" s="4" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
     </row>
     <row r="151" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -62272,7 +62276,7 @@
       <c r="K151" s="1"/>
       <c r="L151" s="1"/>
       <c r="M151" s="4" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="152" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -62298,7 +62302,7 @@
       <c r="K152" s="1"/>
       <c r="L152" s="1"/>
       <c r="M152" s="4" t="s">
-        <v>1015</v>
+        <v>1013</v>
       </c>
     </row>
     <row r="153" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -62339,7 +62343,7 @@
         <v>783</v>
       </c>
       <c r="D154" s="26" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>781</v>
@@ -62357,7 +62361,7 @@
         <v>770</v>
       </c>
       <c r="L154" s="26" t="s">
-        <v>982</v>
+        <v>980</v>
       </c>
       <c r="M154" s="1"/>
     </row>
@@ -62373,7 +62377,7 @@
         <v>798</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="E155" s="1"/>
       <c r="F155" s="1"/>
@@ -62384,7 +62388,7 @@
       <c r="K155" s="1"/>
       <c r="L155" s="1"/>
       <c r="M155" s="4" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="156" spans="1:13" ht="255" x14ac:dyDescent="0.25">
@@ -62447,17 +62451,17 @@
         <v>Vino Navegado</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="C158" s="4" t="s">
         <v>830</v>
       </c>
       <c r="D158" s="10"/>
       <c r="E158" s="1" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="G158" s="1"/>
       <c r="H158" s="1"/>
@@ -62475,7 +62479,7 @@
         <v>Cola de Mono</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="C159" s="4" t="s">
         <v>818</v>
@@ -62500,7 +62504,7 @@
       <c r="K159" s="1"/>
       <c r="L159" s="1"/>
       <c r="M159" s="4" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
     </row>
     <row r="160" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62515,16 +62519,16 @@
         <v>826</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>1019</v>
+        <v>1017</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>1017</v>
+        <v>1015</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>1016</v>
+        <v>1014</v>
       </c>
       <c r="H160" s="1"/>
       <c r="I160" s="5"/>
@@ -62532,7 +62536,7 @@
       <c r="K160" s="1"/>
       <c r="L160" s="1"/>
       <c r="M160" s="4" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
     </row>
     <row r="161" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -62544,7 +62548,7 @@
         <v>838</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>839</v>
+        <v>1086</v>
       </c>
       <c r="D161" s="4"/>
       <c r="E161" s="1"/>
@@ -62555,7 +62559,9 @@
       <c r="J161" s="1"/>
       <c r="K161" s="1"/>
       <c r="L161" s="1"/>
-      <c r="M161" s="1"/>
+      <c r="M161" s="4" t="s">
+        <v>1087</v>
+      </c>
     </row>
     <row r="162" spans="1:13" ht="195" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="str">
@@ -62590,16 +62596,16 @@
       </c>
       <c r="B163" s="1"/>
       <c r="C163" s="4" t="s">
+        <v>850</v>
+      </c>
+      <c r="D163" s="4" t="s">
+        <v>849</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>1085</v>
+      </c>
+      <c r="F163" s="5" t="s">
         <v>851</v>
-      </c>
-      <c r="D163" s="4" t="s">
-        <v>850</v>
-      </c>
-      <c r="E163" s="1" t="s">
-        <v>853</v>
-      </c>
-      <c r="F163" s="5" t="s">
-        <v>852</v>
       </c>
       <c r="G163" s="5"/>
       <c r="H163" s="1"/>
@@ -62608,7 +62614,7 @@
       <c r="K163" s="1"/>
       <c r="L163" s="1"/>
       <c r="M163" s="4" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
     </row>
     <row r="164" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62618,29 +62624,29 @@
       </c>
       <c r="B164" s="4"/>
       <c r="C164" s="4" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="G164" s="5"/>
       <c r="H164" s="1"/>
       <c r="I164" s="5"/>
       <c r="J164" s="1" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="K164" s="1" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="L164" s="1"/>
       <c r="M164" s="4" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
     </row>
     <row r="165" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62649,22 +62655,22 @@
         <v>Pihuelo</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="E165" s="4" t="s">
+        <v>1026</v>
+      </c>
+      <c r="F165" s="5" t="s">
+        <v>1027</v>
+      </c>
+      <c r="G165" s="1" t="s">
         <v>1028</v>
-      </c>
-      <c r="F165" s="5" t="s">
-        <v>1029</v>
-      </c>
-      <c r="G165" s="1" t="s">
-        <v>1030</v>
       </c>
       <c r="H165" s="1"/>
       <c r="I165" s="5"/>
@@ -62672,7 +62678,7 @@
       <c r="K165" s="1"/>
       <c r="L165" s="1"/>
       <c r="M165" s="4" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
     </row>
     <row r="166" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62681,19 +62687,19 @@
         <v>Mojito Sandía</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
       <c r="G166" s="5"/>
       <c r="H166" s="1"/>
@@ -62702,7 +62708,7 @@
       <c r="K166" s="1"/>
       <c r="L166" s="1"/>
       <c r="M166" s="4" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
     </row>
     <row r="167" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62712,7 +62718,7 @@
       </c>
       <c r="B167" s="1"/>
       <c r="C167" s="4" t="s">
-        <v>890</v>
+        <v>888</v>
       </c>
       <c r="D167" s="4"/>
       <c r="E167" s="1"/>
@@ -62724,7 +62730,7 @@
       <c r="K167" s="1"/>
       <c r="L167" s="1"/>
       <c r="M167" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="168" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -62734,7 +62740,7 @@
       </c>
       <c r="B168" s="1"/>
       <c r="C168" s="4" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="D168" s="4"/>
       <c r="E168" s="1"/>
@@ -62746,7 +62752,7 @@
       <c r="K168" s="1"/>
       <c r="L168" s="1"/>
       <c r="M168" s="4" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="169" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -62755,10 +62761,10 @@
         <v>Chardonnay Sour</v>
       </c>
       <c r="B169" s="4" t="s">
+        <v>892</v>
+      </c>
+      <c r="C169" s="4" t="s">
         <v>894</v>
-      </c>
-      <c r="C169" s="4" t="s">
-        <v>896</v>
       </c>
       <c r="D169" s="4"/>
       <c r="E169" s="1"/>
@@ -62777,13 +62783,13 @@
         <v>Carmenere Sour</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>470</v>
@@ -62798,7 +62804,7 @@
       <c r="K170" s="1"/>
       <c r="L170" s="1"/>
       <c r="M170" s="4" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
     </row>
     <row r="171" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62807,13 +62813,13 @@
         <v>Jerez Sour</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="E171" s="1"/>
       <c r="F171" s="1"/>
@@ -62824,7 +62830,7 @@
       <c r="K171" s="1"/>
       <c r="L171" s="1"/>
       <c r="M171" s="4" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
     </row>
     <row r="172" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -62834,7 +62840,7 @@
       </c>
       <c r="B172" s="4"/>
       <c r="C172" s="4" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="D172" s="4"/>
       <c r="E172" s="1"/>
@@ -62846,7 +62852,7 @@
       <c r="K172" s="1"/>
       <c r="L172" s="1"/>
       <c r="M172" s="4" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="173" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -62866,7 +62872,7 @@
       <c r="K173" s="1"/>
       <c r="L173" s="1"/>
       <c r="M173" s="4" t="s">
-        <v>1083</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="174" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -62875,7 +62881,7 @@
         <v>Campari Spritz</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>1084</v>
+        <v>1082</v>
       </c>
       <c r="C174" s="4"/>
       <c r="D174" s="4"/>
@@ -62888,7 +62894,7 @@
       <c r="K174" s="1"/>
       <c r="L174" s="1"/>
       <c r="M174" s="4" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="175" spans="1:13" x14ac:dyDescent="0.25">

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1D3587C-2CC6-4C3C-857E-2DE7161A1DE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB6027FF-B2D2-45D9-8DC0-C79BBFDF855F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1646" uniqueCount="1088">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1649" uniqueCount="1091">
   <si>
     <t>Ramazzotti Spritz</t>
   </si>
@@ -5070,6 +5070,19 @@
   <si>
     <t>ramos.jpg
 Henry C. Ramos (1846–1928), barman de Nueva Orleans y creador del Ramos Gin Fizz en 1888.</t>
+  </si>
+  <si>
+    <t>Bodegón_de_naranjas_by_Rafael_Romero_Barros.jpg
+Título: “Bodegón de naranjas”
+Autor: Rafael Romero Barros
+Técnica:  Óleo sobre lienzo 
+Año: 1863</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=2Nkb3p9bquY</t>
+  </si>
+  <si>
+    <t>José Larralde - Patagonia</t>
   </si>
 </sst>
 </file>
@@ -59253,8 +59266,12 @@
         <v>625</v>
       </c>
       <c r="D35" s="4"/>
-      <c r="E35" s="1"/>
-      <c r="F35" s="1"/>
+      <c r="E35" s="1" t="s">
+        <v>1090</v>
+      </c>
+      <c r="F35" s="5" t="s">
+        <v>1089</v>
+      </c>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
       <c r="I35" s="5"/>
@@ -59708,14 +59725,14 @@
         <v>192</v>
       </c>
       <c r="G52" s="1"/>
-      <c r="H52" s="1" t="s">
+      <c r="H52" s="1"/>
+      <c r="I52" s="1"/>
+      <c r="J52" s="1" t="s">
         <v>505</v>
       </c>
-      <c r="I52" s="1" t="s">
+      <c r="K52" s="1" t="s">
         <v>504</v>
       </c>
-      <c r="J52" s="1"/>
-      <c r="K52" s="1"/>
       <c r="L52" s="1"/>
       <c r="M52" s="4" t="s">
         <v>933</v>
@@ -60943,7 +60960,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="100" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" ht="150" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="str">
         <f>IF(receta!A100="","",receta!A100)</f>
         <v>Naranja Sour</v>
@@ -60967,7 +60984,9 @@
       <c r="J100" s="1"/>
       <c r="K100" s="5"/>
       <c r="L100" s="5"/>
-      <c r="M100" s="1"/>
+      <c r="M100" s="4" t="s">
+        <v>1088</v>
+      </c>
     </row>
     <row r="101" spans="1:13" ht="195" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="str">
@@ -64349,9 +64368,10 @@
     <hyperlink ref="F106" r:id="rId78" xr:uid="{ABCFAB17-7667-4D61-879E-A320868B2202}"/>
     <hyperlink ref="I106" r:id="rId79" xr:uid="{4BF12877-B808-4EA1-A6A9-B6AAB5F55B13}"/>
     <hyperlink ref="K28" r:id="rId80" xr:uid="{EABE5019-2D6E-4A59-9FC0-4DBF379C5B0C}"/>
+    <hyperlink ref="F35" r:id="rId81" xr:uid="{B54BA2B3-1270-4890-885E-4EB30592F48D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId81"/>
+  <pageSetup orientation="portrait" r:id="rId82"/>
 </worksheet>
 </file>
 

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB6027FF-B2D2-45D9-8DC0-C79BBFDF855F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1D92F93-35AC-4A8B-A9C7-6513D444D9F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1649" uniqueCount="1091">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1683" uniqueCount="1125">
   <si>
     <t>Ramazzotti Spritz</t>
   </si>
@@ -4364,15 +4364,6 @@
 Mauricio Redolés, 1990.</t>
   </si>
   <si>
-    <t>Beber menos y mejor
-Jorge Teillier
-Me gusta un rincón central de Santiago en donde sinuosamente se pierde la uniformidad ajedrezada que heredamos de los alarifes españoles, y con un poco de imaginación nos podemos batir, bajo un vuelo de palomas y entre maullidos de gatos vagabundos que nunca faltan, en una ciudad del centro de Europa. Entre otras, las calles tienen nombres como París y Londres, y una sombra china e ignorada, gemela a la de Jack el Destripador, degollador de prostitutas en el Londres de fines de siglo, planea sobre los hoteles de paso que en los años 30 fueran casas de las entonces grandes familias santiaguinas.
-En este sector -además de las peñas folklóricas- está situado un Club de Abstemios que el otro día pasé a visitar "no por simple capricho de poeta", como diría Nicanor Parra, sino porque me interesaba íntimamente todo lo relacionado con el alcoholismo, más aún después de que en una librería de viejo logré encontrar Días sin huellas, el estremecedor libro del recientemente fallecido Charles Jackson que dio origen a la película en que Ray Milland llegó a lo que damos en llamar la fama. No soy ningún moralista, y mi tejado en el aspecto alcohol es de vidrio puro. Si le hago caso al SNS estaría por lo menos dentro del millón de chilenos bebedores excesivos. Como tal se considera al que ingiere por término medio más de una botella de vino diaria o su equivalente en alcohol. (Los franceses son más piadosos: es alcohólico el que bebe más de tres litros cotidianos.) Para retomar el relato, diré que entré de visita al Club de Abstemios (uno de los 93 que funciona en el país) y estuve conversando con varios de los socios, que no tienen ninguna reticencia en contar sus historias. En total son más o menos semejantes: perdieron hogar, trabajo, amistades por el beber excesivo, hasta terminar en las "Embajadas" (como se llama entre el gremio a las hospederías), o aun en la calle pidiendo limosna, con el clásico tarrito en la mano. A veces por sola voluntad, otras veces tras un tratamiento antialcohólico, abandonaron el vicio. Agrupados en su Club, reproducen el mismo ambiente del bar, con la diferencia de que sólo se bebe refrescos o café. Porque el "curado" chileno encuentra en el bar su lugar metafísico, en donde está libre de la rutina cotidiana, y por algo un amigo mío decía: "Quiero mucho mi hogar porque es mi segundo bar" (contaba, eso sí, con una esposa complaciente que lo proveía con la generosidad de una cantinera de la Guerra del Pacífico). Así, los ex alcohólicos pueden hacerse una terapia solidaria con la ayuda de algunos médicos, aunque en el fondo el alcohólico tiene más confianza en sus congéneres que en el doctor. "El alcohol es la más terrible de las enfermedades", escribió Edgar A. Poe (por algo muerto a los 39 años de delirium tremens) y el enfermo confía más en quien se ha mejorado por su voluntad, ganando en carne propia la batalla contra sí mismo.
-Por eso, creo que los clubes de abstemios son bastante positivos y debieran recibir una más efectiva ayuda estatal.
-Naturalmente, no soy ningún hipócrita para preconizar que haya una campaña de "ley seca" (en estos momentos estoy pensando que he sido invitado a la botillería de un amigo a probar cierto tinto de buena cepa), y por eso pienso que el programa de la Unidad Popular (en una de las 40 primeras medidas) tiene razón cuando dice que el alcoholismo debe combatirse creando mejores medios de vida y erradicando el clandestinaje. El "borracho dionisíaco", como lo definió Pablo de Rokha, es el chileno típico, y ningún decreto hará cambiar una conducta etílica heredada por generaciones. Por algo nuestro primer cronista Góngora y Marmolejo describe a Pedro de Valdivia como excesivamente aficionado a la chicha y los araucanos perdieron muchas batallas por dedicarse a celebrar el triunfo tras ganar una, como le suele pasar ahora a nuestros deportistas. Pero el beber vinos baratos y falsificados, por comerciantes inescrupulosos, el beber sin comer, ha hecho que Santiago -como lo dice una autoridad, el Dr. Hernán Romero- sea la ciudad con mayor índice de mortalidad por cirrosis hepática en el mundo, y que la tasa de enfermos alcohólicos sea más grande que la ya elevadísima de tuberculosos que tuvo el país en la fase epidémica por la que atravesamos años atrás. Parece entonces que llega la hora de que "los más y los mejores" empecemos a tomar la sabia medida de "beber menos y mejor".
-Teillier, Jorge. Puro Chile, Santiago, 28 de Octubre de 1970.</t>
-  </si>
-  <si>
     <t>La-vendimia.jpg
 Título: "Vendimia en la Ribera del Duero”
 Autor: José Vela Zanetti
@@ -5083,6 +5074,117 @@
   </si>
   <si>
     <t>José Larralde - Patagonia</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=s6wYk7G3qx8</t>
+  </si>
+  <si>
+    <t>Lucho Barrios - Copa De Licor</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=IBmhBH4gVjc</t>
+  </si>
+  <si>
+    <t>Jose Feliciano - La Copa Rota</t>
+  </si>
+  <si>
+    <t>Una noche, como un loco/Mordió la copa de vino/Y le hizo un cortante filo/Que su boca destrozó/Y la sangre que brotaba/Confundióse con el vino/Y en la cantina, este grito/A todos estremeció</t>
+  </si>
+  <si>
+    <t>Carlos Gardel - La Última Copa</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=1tyjd6Oz4Ck</t>
+  </si>
+  <si>
+    <t>Eche mozo más champán/Que todo mi dolor bebiendo lo he de ahogar/Y si la ven amigos, díganle/Que ha sido por su amor que mi vida ya se fue</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=0TphuR-oUNo</t>
+  </si>
+  <si>
+    <t>Amar Azul - Yo Tomo Licor</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=C4sXQmkuhRo</t>
+  </si>
+  <si>
+    <t>2 Minutos - Canción De Amor</t>
+  </si>
+  <si>
+    <t>¡Cerveza, yo te quiero!</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=X-6mcGFfqVo</t>
+  </si>
+  <si>
+    <t>Chavela Vargas - El Último Trago</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=zIXy43-h8i8</t>
+  </si>
+  <si>
+    <t>Fother Muckers - 2022</t>
+  </si>
+  <si>
+    <t>El mundo no está/Como para andar/Sobreviviéndolo solo/Acompáñame a caminar/Por el Parque Bustamante/Compramos después una caja de vino/Por esta vez la pagas tú</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=bHvizieGt9s</t>
+  </si>
+  <si>
+    <t>No ves que vengo de un país que está de olvido/Siempre gris tras el alcohol/Contame tu condena decime tu fracaso/No ves la pena que me ha herido/Y hablame simplemente de aquel amor ausente/Tras un retazo del olvido/Ya sé que te lastima, yo sé que me hace daño/Llorarte mi sermón de vino/Pero es el viejo amor que tiembla bandoneón/Buscando en un licor que aturda/La curda que al final termine la función/Corriéndole un telón al corazón</t>
+  </si>
+  <si>
+    <t>Aníbal Troilo y  Roberto Goyeneche - La Última Curda</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=tWcdfcuWl3M</t>
+  </si>
+  <si>
+    <t>Divididos - Sobrio A Las Piñas/ Quien Se Tomo Todo El Vino</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=whZ5YPUZ87w</t>
+  </si>
+  <si>
+    <t>Horacio Guarany - Volver En Vino</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=eftRt_64JGU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alfredo Zitarrosa - Gotita de Licor </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=8fDOxkrImGU</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Piero - Juan Tequila </t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=SGyOaCXr8Lw</t>
+  </si>
+  <si>
+    <t>The Rolling Stones - Start Me Up</t>
+  </si>
+  <si>
+    <t>Beber menos y mejor
+Jorge Teillier
+Me gusta un rincón central de Santiago en donde sinuosamente se pierde la uniformidad ajedrezada que heredamos de los alarifes españoles, y con un poco de imaginación nos podemos batir, bajo un vuelo de palomas y entre maullidos de gatos vagabundos que nunca faltan, en una ciudad del centro de Europa. Entre otras, las calles tienen nombres como París y Londres, y una sombra china e ignorada, gemela a la de Jack el Destripador, degollador de prostitutas en el Londres de fines de siglo, planea sobre los hoteles de paso que en los años 30 fueran casas de las entonces grandes familias santiaguinas.
+En este sector -además de las peñas folklóricas- está situado un Club de Abstemios que el otro día pasé a visitar "no por simple capricho de poeta", como diría Nicanor Parra, sino porque me interesaba íntimamente todo lo relacionado con el alcoholismo, más aún después de que en una librería de viejo logré encontrar Días sin huellas, el estremecedor libro del recientemente fallecido Charles Jackson que dio origen a la película en que Ray Milland llegó a lo que damos en llamar la fama. No soy ningún moralista, y mi tejado en el aspecto alcohol es de vidrio puro. Si le hago caso al SNS estaría por lo menos dentro del millón de chilenos bebedores excesivos. Como tal se considera al que ingiere por término medio más de una botella de vino diaria o su equivalente en alcohol. (Los franceses son más piadosos: es alcohólico el que bebe más de tres litros cotidianos.) Para retomar el relato, diré que entré de visita al Club de Abstemios (uno de los 93 que funciona en el país) y estuve conversando con varios de los socios, que no tienen ninguna reticencia en contar sus historias. En total son más o menos semejantes: perdieron hogar, trabajo, amistades por el beber excesivo, hasta terminar en las "Embajadas" (como se llama entre el gremio a las hospederías), o aun en la calle pidiendo limosna, con el clásico tarrito en la mano. A veces por sola voluntad, otras veces tras un tratamiento antialcohólico, abandonaron el vicio. Agrupados en su Club, reproducen el mismo ambiente del bar, con la diferencia de que sólo se bebe refrescos o café. Porque el "curado" chileno encuentra en el bar su lugar metafísico, en donde está libre de la rutina cotidiana, y por algo un amigo mío decía: "Quiero mucho mi hogar porque es mi segundo bar" (contaba, eso sí, con una esposa complaciente que lo proveía con la generosidad de una cantinera de la Guerra del Pacífico). Así, los ex alcohólicos pueden hacerse una terapia solidaria con la ayuda de algunos médicos, aunque en el fondo el alcohólico tiene más confianza en sus congéneres que en el doctor. "El alcohol es la más terrible de las enfermedades", escribió Edgar A. Poe (por algo muerto a los 39 años de delirium tremens) y el enfermo confía más en quien se ha mejorado por su voluntad, ganando en carne propia la batalla contra sí mismo.
+Por eso, creo que los clubes de abstemios son bastante positivos y debieran recibir una más efectiva ayuda estatal.
+Naturalmente, no soy ningún hipócrita para preconizar que haya una campaña de "ley seca" (en estos momentos estoy pensando que he sido invitado a la botillería de un amigo a probar cierto tinto de buena cepa), y por eso pienso que el programa de la Unidad Popular (en una de las 40 primeras medidas) tiene razón cuando dice que el alcoholismo debe combatirse creando mejores medios de vida y erradicando el clandestinaje. El "borracho dionisíaco", como lo definió Pablo de Rokha, es el chileno típico, y ningún decreto hará cambiar una conducta etílica heredada por generaciones. Por algo nuestro primer cronista Góngora y Marmolejo describe a Pedro de Valdivia como excesivamente aficionado a la chicha y los araucanos perdieron muchas batallas por dedicarse a celebrar el triunfo tras ganar una, como le suele pasar ahora a nuestros deportistas. Pero el beber vinos baratos y falsificados, por comerciantes inescrupulosos, el beber sin comer, ha hecho que Santiago -como lo dice una autoridad, el Dr. Hernán Romero- sea la ciudad con mayor índice de mortalidad por cirrosis hepática en el mundo, y que la tasa de enfermos alcohólicos sea más grande que la ya elevadísima de tuberculosos que tuvo el país en la fase epidémica por la que atravesamos años atrás. Parece entonces que llega la hora de que "los más y los mejores" empecemos a tomar la sabia medida de "beber menos y mejor".
+Teillier, Jorge. Puro Chile, Santiago, 28 de octubre de 1970.</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=f9FEsL7K1mw</t>
+  </si>
+  <si>
+    <t>Café Tacvba - Bar Tacuba</t>
+  </si>
+  <si>
+    <t>El tequila rápido es muy malo para mí/Y me he preguntado: "¿por qué otra vez estoy pensando en ti?"/Estoy en una cantina/Estoy escuchando una canción que yo pedí</t>
   </si>
 </sst>
 </file>
@@ -36486,7 +36588,7 @@
     </row>
     <row r="172" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>53</v>
@@ -36664,7 +36766,7 @@
     </row>
     <row r="173" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>52</v>
@@ -36840,7 +36942,7 @@
     </row>
     <row r="174" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>49</v>
@@ -58359,7 +58461,7 @@
         <v>315</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>316</v>
@@ -58374,7 +58476,7 @@
         <v>763</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="M1" s="7" t="s">
         <v>811</v>
@@ -58451,7 +58553,7 @@
         <v>239</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="5"/>
@@ -58515,7 +58617,7 @@
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="4" t="s">
-        <v>951</v>
+        <v>950</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="270" x14ac:dyDescent="0.25">
@@ -58524,7 +58626,7 @@
         <v>Amaretto Spritz</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>352</v>
@@ -58543,7 +58645,7 @@
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="4" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="210" x14ac:dyDescent="0.25">
@@ -58569,7 +58671,7 @@
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="4" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -58628,7 +58730,7 @@
         <v>Aperol Spritz</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>599</v>
@@ -58645,7 +58747,7 @@
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="4" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58672,7 +58774,7 @@
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
-    <row r="13" spans="1:13" ht="195" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="210" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="str">
         <f>IF(receta!A13="","",receta!A13)</f>
         <v>Bellini</v>
@@ -58693,7 +58795,7 @@
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="4" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58745,7 +58847,7 @@
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="4" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -58757,13 +58859,13 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -58849,7 +58951,7 @@
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="4" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -58901,7 +59003,7 @@
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="4" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="375" x14ac:dyDescent="0.25">
@@ -58929,7 +59031,7 @@
       <c r="K22" s="5"/>
       <c r="L22" s="5"/>
       <c r="M22" s="4" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -58951,7 +59053,7 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="4" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="345" x14ac:dyDescent="0.25">
@@ -58999,7 +59101,7 @@
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="4" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59027,7 +59129,7 @@
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="4" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="375" x14ac:dyDescent="0.25">
@@ -59044,16 +59146,24 @@
       <c r="D27" s="4" t="s">
         <v>675</v>
       </c>
-      <c r="E27" s="1"/>
-      <c r="F27" s="1"/>
+      <c r="E27" s="1" t="s">
+        <v>1114</v>
+      </c>
+      <c r="F27" s="5" t="s">
+        <v>1113</v>
+      </c>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
-      <c r="J27" s="1"/>
-      <c r="K27" s="1"/>
+      <c r="J27" s="1" t="s">
+        <v>1116</v>
+      </c>
+      <c r="K27" s="5" t="s">
+        <v>1115</v>
+      </c>
       <c r="L27" s="1"/>
       <c r="M27" s="4" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59066,7 +59176,7 @@
         <v>458</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>528</v>
@@ -59078,14 +59188,14 @@
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
       <c r="J28" s="1" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="L28" s="5"/>
       <c r="M28" s="4" t="s">
-        <v>918</v>
+        <v>917</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="360" x14ac:dyDescent="0.25">
@@ -59111,7 +59221,7 @@
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="4" t="s">
-        <v>928</v>
+        <v>927</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59126,18 +59236,24 @@
         <v>667</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>916</v>
-      </c>
-      <c r="E30" s="1"/>
-      <c r="F30" s="1"/>
-      <c r="G30" s="1"/>
+        <v>1121</v>
+      </c>
+      <c r="E30" s="1" t="s">
+        <v>1110</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>1108</v>
+      </c>
+      <c r="G30" s="4" t="s">
+        <v>1109</v>
+      </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
       <c r="J30" s="1"/>
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="4" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59155,13 +59271,13 @@
         <v>425</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="F31" s="5" t="s">
+        <v>995</v>
+      </c>
+      <c r="G31" s="4" t="s">
         <v>996</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>997</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -59169,10 +59285,10 @@
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="4" t="s">
-        <v>974</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="240" x14ac:dyDescent="0.25">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="255" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="str">
         <f>IF(receta!A32="","",receta!A32)</f>
         <v>Cléry Durazno</v>
@@ -59251,7 +59367,7 @@
       <c r="K34" s="5"/>
       <c r="L34" s="5"/>
       <c r="M34" s="4" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -59267,10 +59383,10 @@
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="1" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
@@ -59299,7 +59415,7 @@
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1" t="s">
-        <v>956</v>
+        <v>955</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59327,7 +59443,7 @@
       <c r="K37" s="5"/>
       <c r="L37" s="5"/>
       <c r="M37" s="4" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="255" x14ac:dyDescent="0.25">
@@ -59353,7 +59469,7 @@
       <c r="K38" s="5"/>
       <c r="L38" s="5"/>
       <c r="M38" s="4" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -59362,7 +59478,7 @@
         <v>Cynar Spritz</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>333</v>
@@ -59377,7 +59493,7 @@
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="4" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -59398,16 +59514,16 @@
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="1" t="s">
+        <v>923</v>
+      </c>
+      <c r="I40" s="5" t="s">
         <v>924</v>
-      </c>
-      <c r="I40" s="5" t="s">
-        <v>925</v>
       </c>
       <c r="J40" s="4"/>
       <c r="K40" s="5"/>
       <c r="L40" s="5"/>
       <c r="M40" s="4" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -59419,7 +59535,7 @@
         <v>725</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="1"/>
@@ -59431,7 +59547,7 @@
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
       <c r="M41" s="4" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59457,7 +59573,7 @@
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="M42" s="4" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="270" x14ac:dyDescent="0.25">
@@ -59485,7 +59601,7 @@
       <c r="K43" s="5"/>
       <c r="L43" s="5"/>
       <c r="M43" s="4" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -59531,7 +59647,7 @@
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
       <c r="M45" s="4" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="285" x14ac:dyDescent="0.25">
@@ -59544,7 +59660,7 @@
       </c>
       <c r="C46" s="4"/>
       <c r="D46" s="4" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>185</v>
@@ -59556,16 +59672,16 @@
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
       <c r="J46" s="4" t="s">
+        <v>1029</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>1028</v>
+      </c>
+      <c r="L46" s="4" t="s">
         <v>1030</v>
       </c>
-      <c r="K46" s="5" t="s">
-        <v>1029</v>
-      </c>
-      <c r="L46" s="4" t="s">
-        <v>1031</v>
-      </c>
       <c r="M46" s="4" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -59593,7 +59709,7 @@
       <c r="K47" s="5"/>
       <c r="L47" s="5"/>
       <c r="M47" s="4" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="315" x14ac:dyDescent="0.25">
@@ -59641,7 +59757,7 @@
         <v>768</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -59649,7 +59765,7 @@
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
       <c r="M49" s="4" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="255" x14ac:dyDescent="0.25">
@@ -59669,7 +59785,7 @@
         <v>481</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>326</v>
@@ -59681,10 +59797,10 @@
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
       <c r="M50" s="4" t="s">
-        <v>958</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+        <v>957</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="str">
         <f>IF(receta!A51="","",receta!A51)</f>
         <v>Espresso Martini</v>
@@ -59703,7 +59819,7 @@
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
       <c r="M51" s="1" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="150" x14ac:dyDescent="0.25">
@@ -59735,7 +59851,7 @@
       </c>
       <c r="L52" s="1"/>
       <c r="M52" s="4" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="390" x14ac:dyDescent="0.25">
@@ -59757,7 +59873,7 @@
         <v>404</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>384</v>
@@ -59765,11 +59881,17 @@
       <c r="I53" s="1" t="s">
         <v>383</v>
       </c>
-      <c r="J53" s="1"/>
-      <c r="K53" s="1"/>
-      <c r="L53" s="1"/>
+      <c r="J53" s="1" t="s">
+        <v>1101</v>
+      </c>
+      <c r="K53" s="5" t="s">
+        <v>1100</v>
+      </c>
+      <c r="L53" s="1" t="s">
+        <v>1102</v>
+      </c>
       <c r="M53" s="4" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59841,7 +59963,7 @@
         <v>473</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -59849,7 +59971,7 @@
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
       <c r="M56" s="4" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59877,7 +59999,7 @@
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
       <c r="M57" s="4" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="150" x14ac:dyDescent="0.25">
@@ -59901,7 +60023,7 @@
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="4" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59918,20 +60040,26 @@
       <c r="D59" s="4" t="s">
         <v>358</v>
       </c>
-      <c r="E59" s="1" t="s">
-        <v>412</v>
+      <c r="E59" s="4" t="s">
+        <v>1095</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>411</v>
-      </c>
-      <c r="G59" s="5"/>
+        <v>1096</v>
+      </c>
+      <c r="G59" s="4" t="s">
+        <v>1097</v>
+      </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
-      <c r="J59" s="1"/>
-      <c r="K59" s="5"/>
+      <c r="J59" s="1" t="s">
+        <v>412</v>
+      </c>
+      <c r="K59" s="5" t="s">
+        <v>411</v>
+      </c>
       <c r="L59" s="5"/>
       <c r="M59" s="4" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -59953,7 +60081,7 @@
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
       <c r="M60" s="4" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="165" x14ac:dyDescent="0.25">
@@ -60007,7 +60135,7 @@
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
       <c r="M62" s="4" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60040,10 +60168,10 @@
         <v>765</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="M63" s="4" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -60056,8 +60184,12 @@
         <v>692</v>
       </c>
       <c r="D64" s="1"/>
-      <c r="E64" s="1"/>
-      <c r="F64" s="1"/>
+      <c r="E64" s="1" t="s">
+        <v>1104</v>
+      </c>
+      <c r="F64" s="5" t="s">
+        <v>1103</v>
+      </c>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
       <c r="I64" s="1"/>
@@ -60065,7 +60197,7 @@
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
       <c r="M64" s="4" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60089,7 +60221,7 @@
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
       <c r="M65" s="1" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="375" x14ac:dyDescent="0.25">
@@ -60098,7 +60230,7 @@
         <v>Hugo</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>732</v>
@@ -60115,7 +60247,7 @@
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
       <c r="M66" s="4" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="67" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60141,7 +60273,7 @@
       <c r="K67" s="5"/>
       <c r="L67" s="5"/>
       <c r="M67" s="4" t="s">
-        <v>950</v>
+        <v>949</v>
       </c>
     </row>
     <row r="68" spans="1:13" ht="330" x14ac:dyDescent="0.25">
@@ -60150,8 +60282,8 @@
         <v>Ingrata</v>
       </c>
       <c r="B68" s="1"/>
-      <c r="C68" s="1" t="s">
-        <v>944</v>
+      <c r="C68" s="4" t="s">
+        <v>943</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>593</v>
@@ -60165,11 +60297,17 @@
       <c r="G68" s="5"/>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
-      <c r="J68" s="1"/>
-      <c r="K68" s="5"/>
-      <c r="L68" s="5"/>
+      <c r="J68" s="1" t="s">
+        <v>1123</v>
+      </c>
+      <c r="K68" s="5" t="s">
+        <v>1122</v>
+      </c>
+      <c r="L68" s="4" t="s">
+        <v>1124</v>
+      </c>
       <c r="M68" s="4" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
     </row>
     <row r="69" spans="1:13" ht="300" x14ac:dyDescent="0.25">
@@ -60225,7 +60363,7 @@
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
       <c r="M70" s="4" t="s">
-        <v>940</v>
+        <v>939</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -60251,7 +60389,7 @@
       <c r="K71" s="5"/>
       <c r="L71" s="5"/>
       <c r="M71" s="4" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
     </row>
     <row r="72" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60268,9 +60406,15 @@
       <c r="D72" s="4" t="s">
         <v>867</v>
       </c>
-      <c r="E72" s="1"/>
-      <c r="F72" s="5"/>
-      <c r="G72" s="5"/>
+      <c r="E72" s="1" t="s">
+        <v>1093</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>1092</v>
+      </c>
+      <c r="G72" s="4" t="s">
+        <v>1094</v>
+      </c>
       <c r="H72" s="1" t="s">
         <v>415</v>
       </c>
@@ -60294,7 +60438,7 @@
       </c>
       <c r="C73" s="4"/>
       <c r="D73" s="4" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
@@ -60305,7 +60449,7 @@
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
       <c r="M73" s="4" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="74" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60359,7 +60503,7 @@
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
       <c r="M75" s="4" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="76" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60395,10 +60539,10 @@
       </c>
       <c r="B77" s="1"/>
       <c r="C77" s="4" t="s">
+        <v>1010</v>
+      </c>
+      <c r="D77" s="4" t="s">
         <v>1011</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>1012</v>
       </c>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
@@ -60409,7 +60553,7 @@
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
       <c r="M77" s="4" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="78" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -60523,7 +60667,7 @@
       <c r="K82" s="1"/>
       <c r="L82" s="1"/>
       <c r="M82" s="4" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60581,7 +60725,7 @@
       <c r="K84" s="1"/>
       <c r="L84" s="1"/>
       <c r="M84" s="4" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -60611,7 +60755,7 @@
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
       <c r="M85" s="4" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -60661,7 +60805,7 @@
       <c r="K87" s="5"/>
       <c r="L87" s="5"/>
       <c r="M87" s="4" t="s">
-        <v>938</v>
+        <v>937</v>
       </c>
     </row>
     <row r="88" spans="1:13" ht="360" x14ac:dyDescent="0.25">
@@ -60676,7 +60820,7 @@
         <v>635</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
@@ -60687,7 +60831,7 @@
       <c r="K88" s="1"/>
       <c r="L88" s="1"/>
       <c r="M88" s="4" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="89" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -60709,7 +60853,7 @@
         <v>180</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
@@ -60717,7 +60861,7 @@
       <c r="K89" s="5"/>
       <c r="L89" s="5"/>
       <c r="M89" s="4" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
@@ -60737,8 +60881,12 @@
       <c r="G90" s="5"/>
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
-      <c r="J90" s="1"/>
-      <c r="K90" s="5"/>
+      <c r="J90" s="1" t="s">
+        <v>1118</v>
+      </c>
+      <c r="K90" s="5" t="s">
+        <v>1117</v>
+      </c>
       <c r="L90" s="5"/>
       <c r="M90" s="1"/>
     </row>
@@ -60791,8 +60939,12 @@
       <c r="G92" s="5"/>
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
-      <c r="J92" s="1"/>
-      <c r="K92" s="5"/>
+      <c r="J92" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K92" s="5" t="s">
+        <v>1098</v>
+      </c>
       <c r="L92" s="5"/>
       <c r="M92" s="1"/>
     </row>
@@ -60815,7 +60967,7 @@
       <c r="K93" s="1"/>
       <c r="L93" s="1"/>
       <c r="M93" s="4" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="94" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -60837,7 +60989,7 @@
       <c r="K94" s="1"/>
       <c r="L94" s="1"/>
       <c r="M94" s="4" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="95" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -60861,7 +61013,7 @@
       <c r="K95" s="1"/>
       <c r="L95" s="1"/>
       <c r="M95" s="4" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
     </row>
     <row r="96" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -60894,13 +61046,13 @@
         <v>578</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>995</v>
+        <v>994</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="G97" s="1"/>
       <c r="H97" s="4"/>
@@ -60909,7 +61061,7 @@
       <c r="K97" s="1"/>
       <c r="L97" s="1"/>
       <c r="M97" s="4" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="98" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -60918,7 +61070,7 @@
         <v>Mojito Spritz</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>724</v>
@@ -60957,7 +61109,7 @@
       <c r="K99" s="5"/>
       <c r="L99" s="5"/>
       <c r="M99" s="4" t="s">
-        <v>926</v>
+        <v>925</v>
       </c>
     </row>
     <row r="100" spans="1:13" ht="150" x14ac:dyDescent="0.25">
@@ -60985,7 +61137,7 @@
       <c r="K100" s="5"/>
       <c r="L100" s="5"/>
       <c r="M100" s="4" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="101" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -61033,7 +61185,7 @@
       <c r="K102" s="1"/>
       <c r="L102" s="1"/>
       <c r="M102" s="4" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="103" spans="1:13" ht="210" x14ac:dyDescent="0.25">
@@ -61055,7 +61207,7 @@
       <c r="K103" s="1"/>
       <c r="L103" s="1"/>
       <c r="M103" s="4" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="104" spans="1:13" ht="345" x14ac:dyDescent="0.25">
@@ -61085,7 +61237,7 @@
       <c r="K104" s="5"/>
       <c r="L104" s="5"/>
       <c r="M104" s="4" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="105" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -61111,7 +61263,7 @@
       <c r="K105" s="1"/>
       <c r="L105" s="1"/>
       <c r="M105" s="4" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
     </row>
     <row r="106" spans="1:13" ht="375" x14ac:dyDescent="0.25">
@@ -61127,25 +61279,25 @@
         <v>563</v>
       </c>
       <c r="E106" s="1" t="s">
+        <v>1035</v>
+      </c>
+      <c r="F106" s="5" t="s">
         <v>1036</v>
       </c>
-      <c r="F106" s="5" t="s">
-        <v>1037</v>
-      </c>
       <c r="G106" s="4" t="s">
-        <v>1035</v>
+        <v>1034</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="I106" s="5" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="J106" s="1"/>
       <c r="K106" s="1"/>
       <c r="L106" s="1"/>
       <c r="M106" s="4" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="107" spans="1:13" ht="192" customHeight="1" x14ac:dyDescent="0.25">
@@ -61184,7 +61336,7 @@
       <c r="F108" s="1"/>
       <c r="G108" s="1"/>
       <c r="H108" s="1" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="I108" s="5" t="s">
         <v>256</v>
@@ -61193,7 +61345,7 @@
       <c r="K108" s="1"/>
       <c r="L108" s="1"/>
       <c r="M108" s="4" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="109" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -61228,7 +61380,7 @@
         <v>672</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="E110" s="4" t="s">
         <v>583</v>
@@ -61243,7 +61395,7 @@
       <c r="K110" s="5"/>
       <c r="L110" s="5"/>
       <c r="M110" s="4" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.25">
@@ -61287,7 +61439,7 @@
         <v>483</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="H112" s="1"/>
       <c r="I112" s="5"/>
@@ -61319,7 +61471,7 @@
       <c r="K113" s="5"/>
       <c r="L113" s="5"/>
       <c r="M113" s="4" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.25">
@@ -61413,7 +61565,7 @@
       <c r="K117" s="5"/>
       <c r="L117" s="5"/>
       <c r="M117" s="4" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="118" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -61467,7 +61619,7 @@
       <c r="K119" s="5"/>
       <c r="L119" s="5"/>
       <c r="M119" s="4" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="120" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -61476,7 +61628,7 @@
         <v>Ramazzotti Spritz</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>353</v>
@@ -61502,14 +61654,18 @@
         <v>Ramazzotti Violetto Spritz</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>746</v>
       </c>
       <c r="D121" s="1"/>
-      <c r="E121" s="1"/>
-      <c r="F121" s="1"/>
+      <c r="E121" s="1" t="s">
+        <v>1091</v>
+      </c>
+      <c r="F121" s="5" t="s">
+        <v>1090</v>
+      </c>
       <c r="G121" s="1"/>
       <c r="H121" s="1"/>
       <c r="I121" s="1"/>
@@ -61567,7 +61723,7 @@
       <c r="K123" s="5"/>
       <c r="L123" s="5"/>
       <c r="M123" s="4" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="124" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -61683,7 +61839,7 @@
       <c r="K128" s="1"/>
       <c r="L128" s="1"/>
       <c r="M128" s="4" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="129" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -61749,7 +61905,7 @@
       <c r="K131" s="1"/>
       <c r="L131" s="1"/>
       <c r="M131" s="4" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="132" spans="1:13" ht="165" x14ac:dyDescent="0.25">
@@ -61775,7 +61931,7 @@
       <c r="K132" s="5"/>
       <c r="L132" s="5"/>
       <c r="M132" s="4" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.25">
@@ -61811,19 +61967,23 @@
         <v>594</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>588</v>
+        <v>1120</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>587</v>
+        <v>1119</v>
       </c>
       <c r="G134" s="5"/>
       <c r="H134" s="4"/>
       <c r="I134" s="5"/>
-      <c r="J134" s="4"/>
-      <c r="K134" s="5"/>
+      <c r="J134" s="4" t="s">
+        <v>588</v>
+      </c>
+      <c r="K134" s="5" t="s">
+        <v>587</v>
+      </c>
       <c r="L134" s="5"/>
       <c r="M134" s="4" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="135" spans="1:13" ht="300" x14ac:dyDescent="0.25">
@@ -61835,25 +61995,25 @@
         <v>651</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="E135" s="1"/>
       <c r="F135" s="1"/>
       <c r="G135" s="1"/>
       <c r="H135" s="1" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="I135" s="5" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="J135" s="1"/>
       <c r="K135" s="1"/>
       <c r="L135" s="1"/>
       <c r="M135" s="4" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
     </row>
     <row r="136" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -61893,13 +62053,13 @@
         <v>433</v>
       </c>
       <c r="E137" s="1" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F137" s="5" t="s">
+        <v>1031</v>
+      </c>
+      <c r="G137" s="4" t="s">
         <v>1033</v>
-      </c>
-      <c r="F137" s="5" t="s">
-        <v>1032</v>
-      </c>
-      <c r="G137" s="4" t="s">
-        <v>1034</v>
       </c>
       <c r="H137" s="1"/>
       <c r="I137" s="1"/>
@@ -61927,7 +62087,7 @@
       <c r="K138" s="1"/>
       <c r="L138" s="1"/>
       <c r="M138" s="4" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
     </row>
     <row r="139" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -61969,13 +62129,13 @@
         <v>345</v>
       </c>
       <c r="E140" s="1" t="s">
+        <v>1018</v>
+      </c>
+      <c r="F140" s="5" t="s">
+        <v>1017</v>
+      </c>
+      <c r="G140" s="4" t="s">
         <v>1019</v>
-      </c>
-      <c r="F140" s="5" t="s">
-        <v>1018</v>
-      </c>
-      <c r="G140" s="4" t="s">
-        <v>1020</v>
       </c>
       <c r="H140" s="1"/>
       <c r="I140" s="1"/>
@@ -61987,7 +62147,7 @@
       </c>
       <c r="L140" s="5"/>
       <c r="M140" s="4" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="141" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62069,7 +62229,7 @@
       <c r="K143" s="1"/>
       <c r="L143" s="1"/>
       <c r="M143" s="4" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
     </row>
     <row r="144" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62092,20 +62252,20 @@
       </c>
       <c r="G144" s="1"/>
       <c r="H144" s="1" t="s">
+        <v>1023</v>
+      </c>
+      <c r="I144" s="5" t="s">
         <v>1024</v>
       </c>
-      <c r="I144" s="5" t="s">
-        <v>1025</v>
-      </c>
       <c r="J144" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="K144" s="5" t="s">
         <v>1022</v>
-      </c>
-      <c r="K144" s="5" t="s">
-        <v>1023</v>
       </c>
       <c r="L144" s="1"/>
       <c r="M144" s="4" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="145" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62135,7 +62295,7 @@
       <c r="K145" s="1"/>
       <c r="L145" s="1"/>
       <c r="M145" s="4" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="146" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -62181,7 +62341,7 @@
       <c r="K147" s="5"/>
       <c r="L147" s="5"/>
       <c r="M147" s="4" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
     </row>
     <row r="148" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -62207,7 +62367,7 @@
       <c r="K148" s="5"/>
       <c r="L148" s="5"/>
       <c r="M148" s="4" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="149" spans="1:13" ht="324" customHeight="1" x14ac:dyDescent="0.25">
@@ -62235,7 +62395,7 @@
       <c r="K149" s="5"/>
       <c r="L149" s="5"/>
       <c r="M149" s="4" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="150" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62295,7 +62455,7 @@
       <c r="K151" s="1"/>
       <c r="L151" s="1"/>
       <c r="M151" s="4" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="152" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -62321,7 +62481,7 @@
       <c r="K152" s="1"/>
       <c r="L152" s="1"/>
       <c r="M152" s="4" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
     </row>
     <row r="153" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -62380,7 +62540,7 @@
         <v>770</v>
       </c>
       <c r="L154" s="26" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
       <c r="M154" s="1"/>
     </row>
@@ -62396,7 +62556,7 @@
         <v>798</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="E155" s="1"/>
       <c r="F155" s="1"/>
@@ -62407,7 +62567,7 @@
       <c r="K155" s="1"/>
       <c r="L155" s="1"/>
       <c r="M155" s="4" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
     </row>
     <row r="156" spans="1:13" ht="255" x14ac:dyDescent="0.25">
@@ -62523,7 +62683,7 @@
       <c r="K159" s="1"/>
       <c r="L159" s="1"/>
       <c r="M159" s="4" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
     </row>
     <row r="160" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62538,16 +62698,16 @@
         <v>826</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="E160" s="1" t="s">
+        <v>1014</v>
+      </c>
+      <c r="F160" s="5" t="s">
         <v>1015</v>
       </c>
-      <c r="F160" s="5" t="s">
-        <v>1016</v>
-      </c>
       <c r="G160" s="4" t="s">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="H160" s="1"/>
       <c r="I160" s="5"/>
@@ -62555,7 +62715,7 @@
       <c r="K160" s="1"/>
       <c r="L160" s="1"/>
       <c r="M160" s="4" t="s">
-        <v>1021</v>
+        <v>1020</v>
       </c>
     </row>
     <row r="161" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -62567,7 +62727,7 @@
         <v>838</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="D161" s="4"/>
       <c r="E161" s="1"/>
@@ -62579,7 +62739,7 @@
       <c r="K161" s="1"/>
       <c r="L161" s="1"/>
       <c r="M161" s="4" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="162" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -62621,7 +62781,7 @@
         <v>849</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="F163" s="5" t="s">
         <v>851</v>
@@ -62633,7 +62793,7 @@
       <c r="K163" s="1"/>
       <c r="L163" s="1"/>
       <c r="M163" s="4" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="164" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62683,13 +62843,13 @@
         <v>869</v>
       </c>
       <c r="E165" s="4" t="s">
+        <v>1025</v>
+      </c>
+      <c r="F165" s="5" t="s">
         <v>1026</v>
       </c>
-      <c r="F165" s="5" t="s">
+      <c r="G165" s="1" t="s">
         <v>1027</v>
-      </c>
-      <c r="G165" s="1" t="s">
-        <v>1028</v>
       </c>
       <c r="H165" s="1"/>
       <c r="I165" s="5"/>
@@ -62697,7 +62857,7 @@
       <c r="K165" s="1"/>
       <c r="L165" s="1"/>
       <c r="M165" s="4" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="166" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62749,7 +62909,7 @@
       <c r="K167" s="1"/>
       <c r="L167" s="1"/>
       <c r="M167" s="4" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="168" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -62759,7 +62919,7 @@
       </c>
       <c r="B168" s="1"/>
       <c r="C168" s="4" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="D168" s="4"/>
       <c r="E168" s="1"/>
@@ -62771,7 +62931,7 @@
       <c r="K168" s="1"/>
       <c r="L168" s="1"/>
       <c r="M168" s="4" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="169" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -62786,13 +62946,23 @@
         <v>894</v>
       </c>
       <c r="D169" s="4"/>
-      <c r="E169" s="1"/>
-      <c r="F169" s="1"/>
-      <c r="G169" s="1"/>
+      <c r="E169" s="1" t="s">
+        <v>1106</v>
+      </c>
+      <c r="F169" s="5" t="s">
+        <v>1105</v>
+      </c>
+      <c r="G169" s="4" t="s">
+        <v>1107</v>
+      </c>
       <c r="H169" s="1"/>
       <c r="I169" s="5"/>
-      <c r="J169" s="1"/>
-      <c r="K169" s="1"/>
+      <c r="J169" s="1" t="s">
+        <v>1112</v>
+      </c>
+      <c r="K169" s="5" t="s">
+        <v>1111</v>
+      </c>
       <c r="L169" s="1"/>
       <c r="M169" s="1"/>
     </row>
@@ -62859,7 +63029,7 @@
       </c>
       <c r="B172" s="4"/>
       <c r="C172" s="4" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
       <c r="D172" s="4"/>
       <c r="E172" s="1"/>
@@ -62871,7 +63041,7 @@
       <c r="K172" s="1"/>
       <c r="L172" s="1"/>
       <c r="M172" s="4" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="173" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -62891,7 +63061,7 @@
       <c r="K173" s="1"/>
       <c r="L173" s="1"/>
       <c r="M173" s="4" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
     </row>
     <row r="174" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -62900,7 +63070,7 @@
         <v>Campari Spritz</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="C174" s="4"/>
       <c r="D174" s="4"/>
@@ -62913,7 +63083,7 @@
       <c r="K174" s="1"/>
       <c r="L174" s="1"/>
       <c r="M174" s="4" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="175" spans="1:13" x14ac:dyDescent="0.25">
@@ -64369,9 +64539,22 @@
     <hyperlink ref="I106" r:id="rId79" xr:uid="{4BF12877-B808-4EA1-A6A9-B6AAB5F55B13}"/>
     <hyperlink ref="K28" r:id="rId80" xr:uid="{EABE5019-2D6E-4A59-9FC0-4DBF379C5B0C}"/>
     <hyperlink ref="F35" r:id="rId81" xr:uid="{B54BA2B3-1270-4890-885E-4EB30592F48D}"/>
+    <hyperlink ref="F121" r:id="rId82" xr:uid="{7DFE895E-D795-42A6-8E4A-F0B1B8754CA7}"/>
+    <hyperlink ref="K59" r:id="rId83" xr:uid="{A51404B4-BE26-4DCE-A3D8-E22560C4320B}"/>
+    <hyperlink ref="K92" r:id="rId84" xr:uid="{5FFB8816-5477-4530-98E6-6384D7000156}"/>
+    <hyperlink ref="K53" r:id="rId85" xr:uid="{EFE11CB5-E5C1-4DD4-958C-FBA5FAE79E08}"/>
+    <hyperlink ref="F64" r:id="rId86" xr:uid="{1DF66D0B-D856-4BBB-8B77-1EE79AB1F1E6}"/>
+    <hyperlink ref="F169" r:id="rId87" xr:uid="{F819A654-761E-47E2-92E4-2EB6511D70F5}"/>
+    <hyperlink ref="F30" r:id="rId88" xr:uid="{8A955A94-32F6-412E-9D1F-FD9FBB3838DE}"/>
+    <hyperlink ref="K169" r:id="rId89" xr:uid="{0E854B66-4BC1-4272-BF5F-DE39E711113C}"/>
+    <hyperlink ref="F27" r:id="rId90" xr:uid="{1458DC33-7898-4869-940E-F70E2A9260BF}"/>
+    <hyperlink ref="K27" r:id="rId91" xr:uid="{7970C379-C4E0-41FC-AF32-3346E87C390B}"/>
+    <hyperlink ref="K90" r:id="rId92" xr:uid="{D8D0F5DC-7359-4E9F-950F-B003241F9665}"/>
+    <hyperlink ref="F134" r:id="rId93" xr:uid="{D7523DD3-FE84-4AED-B41A-68B668DAABE6}"/>
+    <hyperlink ref="K68" r:id="rId94" xr:uid="{3E73A1DB-0A1B-4D6D-9C5D-9C6C53A649F7}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId82"/>
+  <pageSetup orientation="portrait" r:id="rId95"/>
 </worksheet>
 </file>
 

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B1D92F93-35AC-4A8B-A9C7-6513D444D9F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24E1957C-FE50-47A3-BDE0-B1CE24B7F684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1683" uniqueCount="1125">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1687" uniqueCount="1129">
   <si>
     <t>Ramazzotti Spritz</t>
   </si>
@@ -1270,9 +1270,6 @@
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=22OZdZYeFe0</t>
-  </si>
-  <si>
-    <t>Chancho En Piedra - El Durazno Y El Melón (Programa de TV  2001)</t>
   </si>
   <si>
     <t>Este cóctel se creó para salvar vidas. Su origen se remonta al siglo XIX, en alta mar, cuando los marineros británicos enfrentaban un enemigo silencioso y devastador: el escorbuto, una enfermedad provocada por la falta de vitamina C. Para combatirla, la Royal Navy comenzó a distribuir jugo de lima a sus tripulaciones, pero su sabor ácido no era del agrado de todos. Entonces, según cuenta la historia, un médico naval llamado Sir Thomas Gimlette sugirió combinar el jugo de lima recetado con una ración de ginebra para mejorar el sabor y facilitar la absorción del medicamento.</t>
@@ -5185,6 +5182,21 @@
   </si>
   <si>
     <t>El tequila rápido es muy malo para mí/Y me he preguntado: "¿por qué otra vez estoy pensando en ti?"/Estoy en una cantina/Estoy escuchando una canción que yo pedí</t>
+  </si>
+  <si>
+    <t>Pancho Molina y los titulares - Piscolón</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=IC6oJ99-YGQ</t>
+  </si>
+  <si>
+    <t>Chancho en Piedra - El Durazno y el Melón (Programa de TV  2001)</t>
+  </si>
+  <si>
+    <t>Bersuit Vergarabat - Yo Tomo</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=eJk8N4mSlQw</t>
   </si>
 </sst>
 </file>
@@ -5862,10 +5874,10 @@
         <v>78</v>
       </c>
       <c r="O1" s="27" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="P1" s="27" t="s">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="Q1" s="27" t="s">
         <v>79</v>
@@ -5877,13 +5889,13 @@
         <v>265</v>
       </c>
       <c r="T1" s="27" t="s">
-        <v>565</v>
+        <v>564</v>
       </c>
       <c r="U1" s="27" t="s">
-        <v>864</v>
+        <v>863</v>
       </c>
       <c r="V1" s="27" t="s">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="W1" s="27" t="s">
         <v>80</v>
@@ -5898,16 +5910,16 @@
         <v>196</v>
       </c>
       <c r="AA1" s="27" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="AB1" s="27" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="AC1" s="27" t="s">
+        <v>897</v>
+      </c>
+      <c r="AD1" s="27" t="s">
         <v>898</v>
-      </c>
-      <c r="AD1" s="27" t="s">
-        <v>899</v>
       </c>
       <c r="AE1" s="27" t="s">
         <v>82</v>
@@ -5934,7 +5946,7 @@
         <v>87</v>
       </c>
       <c r="AM1" s="27" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="AN1" s="27" t="s">
         <v>223</v>
@@ -5961,13 +5973,13 @@
         <v>200</v>
       </c>
       <c r="AV1" s="27" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="AW1" s="27" t="s">
         <v>209</v>
       </c>
       <c r="AX1" s="27" t="s">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="AY1" s="27" t="s">
         <v>230</v>
@@ -6057,16 +6069,16 @@
         <v>152</v>
       </c>
       <c r="CB1" s="8" t="s">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="CC1" s="8" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="CD1" s="7" t="s">
         <v>280</v>
       </c>
       <c r="CE1" s="7" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
       <c r="CF1" s="8" t="s">
         <v>198</v>
@@ -6093,16 +6105,16 @@
         <v>120</v>
       </c>
       <c r="CN1" s="8" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="CO1" s="8" t="s">
         <v>215</v>
       </c>
       <c r="CP1" s="8" t="s">
-        <v>700</v>
+        <v>699</v>
       </c>
       <c r="CQ1" s="8" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="CR1" s="7" t="s">
         <v>95</v>
@@ -6114,16 +6126,16 @@
         <v>97</v>
       </c>
       <c r="CU1" s="7" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="CV1" s="7" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="CW1" s="7" t="s">
         <v>98</v>
       </c>
       <c r="CX1" s="7" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="CY1" s="7" t="s">
         <v>99</v>
@@ -6138,22 +6150,22 @@
         <v>154</v>
       </c>
       <c r="DC1" s="8" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="DD1" s="18" t="s">
-        <v>666</v>
+        <v>665</v>
       </c>
       <c r="DE1" s="18" t="s">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="DF1" s="18" t="s">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="DG1" s="18" t="s">
+        <v>841</v>
+      </c>
+      <c r="DH1" s="18" t="s">
         <v>842</v>
-      </c>
-      <c r="DH1" s="18" t="s">
-        <v>843</v>
       </c>
       <c r="DI1" s="15" t="s">
         <v>136</v>
@@ -6162,31 +6174,31 @@
         <v>135</v>
       </c>
       <c r="DK1" s="15" t="s">
-        <v>671</v>
+        <v>670</v>
       </c>
       <c r="DL1" s="15" t="s">
+        <v>566</v>
+      </c>
+      <c r="DM1" s="15" t="s">
         <v>567</v>
       </c>
-      <c r="DM1" s="15" t="s">
-        <v>568</v>
-      </c>
       <c r="DN1" s="15" t="s">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="DO1" s="15" t="s">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="DP1" s="15" t="s">
+        <v>603</v>
+      </c>
+      <c r="DQ1" s="15" t="s">
+        <v>813</v>
+      </c>
+      <c r="DR1" s="15" t="s">
         <v>604</v>
       </c>
-      <c r="DQ1" s="15" t="s">
-        <v>814</v>
-      </c>
-      <c r="DR1" s="15" t="s">
-        <v>605</v>
-      </c>
       <c r="DS1" s="15" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="DT1" s="15" t="s">
         <v>141</v>
@@ -6195,43 +6207,43 @@
         <v>237</v>
       </c>
       <c r="DV1" s="15" t="s">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="DW1" s="15" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="DX1" s="15" t="s">
-        <v>810</v>
+        <v>809</v>
       </c>
       <c r="DY1" s="15" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="DZ1" s="15" t="s">
-        <v>566</v>
+        <v>565</v>
       </c>
       <c r="EA1" s="15" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="EB1" s="21" t="s">
-        <v>559</v>
+        <v>558</v>
       </c>
       <c r="EC1" s="21" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="ED1" s="25" t="s">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="EE1" s="12" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="EF1" s="14" t="s">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="EG1" s="12" t="s">
         <v>234</v>
       </c>
       <c r="EH1" s="12" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="EI1" s="12" t="s">
         <v>286</v>
@@ -6246,19 +6258,19 @@
         <v>125</v>
       </c>
       <c r="EM1" s="17" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="EN1" s="17" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="EO1" s="17" t="s">
-        <v>558</v>
+        <v>557</v>
       </c>
       <c r="EP1" s="19" t="s">
-        <v>609</v>
+        <v>608</v>
       </c>
       <c r="EQ1" s="19" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="ER1" s="19" t="s">
         <v>126</v>
@@ -6273,7 +6285,7 @@
         <v>231</v>
       </c>
       <c r="EV1" s="20" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="EW1" s="20" t="s">
         <v>232</v>
@@ -7711,13 +7723,13 @@
     </row>
     <row r="10" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>51</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D10" s="2">
         <v>300</v>
@@ -8071,13 +8083,13 @@
     </row>
     <row r="12" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>55</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D12" s="2">
         <v>200</v>
@@ -8779,7 +8791,7 @@
     </row>
     <row r="16" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>278</v>
@@ -9507,7 +9519,7 @@
     </row>
     <row r="20" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>151</v>
@@ -9863,7 +9875,7 @@
     </row>
     <row r="22" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>53</v>
@@ -10571,7 +10583,7 @@
     </row>
     <row r="26" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>50</v>
@@ -10749,7 +10761,7 @@
     </row>
     <row r="27" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>674</v>
+        <v>673</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>51</v>
@@ -11281,7 +11293,7 @@
     </row>
     <row r="30" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="B30" s="1" t="s">
         <v>278</v>
@@ -11459,7 +11471,7 @@
     </row>
     <row r="31" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="B31" s="1" t="s">
         <v>278</v>
@@ -11637,7 +11649,7 @@
     </row>
     <row r="32" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="B32" s="1" t="s">
         <v>278</v>
@@ -11815,7 +11827,7 @@
     </row>
     <row r="33" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>55</v>
@@ -12349,7 +12361,7 @@
     </row>
     <row r="36" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>54</v>
@@ -12525,13 +12537,13 @@
     </row>
     <row r="37" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D37" s="2">
         <v>300</v>
@@ -12707,7 +12719,7 @@
     </row>
     <row r="38" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>50</v>
@@ -14833,7 +14845,7 @@
     </row>
     <row r="50" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>479</v>
+        <v>478</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>53</v>
@@ -15013,7 +15025,7 @@
     </row>
     <row r="51" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>55</v>
@@ -15373,7 +15385,7 @@
     </row>
     <row r="53" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>56</v>
@@ -15907,7 +15919,7 @@
     </row>
     <row r="56" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>51</v>
@@ -16441,7 +16453,7 @@
     </row>
     <row r="59" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>55</v>
@@ -17321,7 +17333,7 @@
     </row>
     <row r="64" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>50</v>
@@ -17677,7 +17689,7 @@
     </row>
     <row r="66" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>49</v>
@@ -18213,7 +18225,7 @@
     </row>
     <row r="69" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>55</v>
@@ -18389,7 +18401,7 @@
     </row>
     <row r="70" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>51</v>
@@ -18751,7 +18763,7 @@
     </row>
     <row r="72" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>50</v>
@@ -18927,10 +18939,10 @@
     </row>
     <row r="73" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>559</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>560</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>561</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>69</v>
@@ -19107,7 +19119,7 @@
     </row>
     <row r="74" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>699</v>
+        <v>698</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>51</v>
@@ -20359,7 +20371,7 @@
     </row>
     <row r="81" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>715</v>
+        <v>714</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>51</v>
@@ -20537,7 +20549,7 @@
     </row>
     <row r="82" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>50</v>
@@ -20901,7 +20913,7 @@
     </row>
     <row r="84" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>51</v>
@@ -21077,7 +21089,7 @@
     </row>
     <row r="85" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>51</v>
@@ -22131,10 +22143,10 @@
     </row>
     <row r="91" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
+        <v>677</v>
+      </c>
+      <c r="B91" s="1" t="s">
         <v>678</v>
-      </c>
-      <c r="B91" s="1" t="s">
-        <v>679</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>63</v>
@@ -22491,7 +22503,7 @@
     </row>
     <row r="93" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>53</v>
@@ -23381,7 +23393,7 @@
     </row>
     <row r="98" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>49</v>
@@ -24819,7 +24831,7 @@
     </row>
     <row r="106" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>53</v>
@@ -25175,7 +25187,7 @@
     </row>
     <row r="108" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>50</v>
@@ -25543,13 +25555,13 @@
     </row>
     <row r="110" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D110" s="2">
         <v>300</v>
@@ -25723,7 +25735,7 @@
     </row>
     <row r="111" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>50</v>
@@ -26963,7 +26975,7 @@
     </row>
     <row r="118" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>50</v>
@@ -27677,7 +27689,7 @@
     </row>
     <row r="122" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>50</v>
@@ -28207,7 +28219,7 @@
     </row>
     <row r="125" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A125" s="13" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>278</v>
@@ -28391,7 +28403,7 @@
     </row>
     <row r="126" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>278</v>
@@ -29107,7 +29119,7 @@
     </row>
     <row r="130" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>151</v>
@@ -30345,7 +30357,7 @@
     </row>
     <row r="137" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A137" s="13" t="s">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>278</v>
@@ -30703,7 +30715,7 @@
     </row>
     <row r="139" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>52</v>
@@ -30883,7 +30895,7 @@
     </row>
     <row r="140" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>50</v>
@@ -31065,7 +31077,7 @@
     </row>
     <row r="141" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>55</v>
@@ -31423,7 +31435,7 @@
     </row>
     <row r="143" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>51</v>
@@ -31787,7 +31799,7 @@
     </row>
     <row r="145" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>53</v>
@@ -32139,7 +32151,7 @@
     </row>
     <row r="147" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>710</v>
+        <v>709</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>51</v>
@@ -32315,7 +32327,7 @@
     </row>
     <row r="148" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>51</v>
@@ -32491,7 +32503,7 @@
     </row>
     <row r="149" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>50</v>
@@ -32845,13 +32857,13 @@
     </row>
     <row r="151" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>752</v>
+        <v>751</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D151" s="2">
         <v>300</v>
@@ -33025,7 +33037,7 @@
     </row>
     <row r="152" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>755</v>
+        <v>754</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>53</v>
@@ -33204,13 +33216,13 @@
     </row>
     <row r="153" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="D153" s="2">
         <v>300</v>
@@ -33384,7 +33396,7 @@
     </row>
     <row r="154" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>51</v>
@@ -33560,7 +33572,7 @@
     </row>
     <row r="155" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>795</v>
+        <v>794</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>54</v>
@@ -33736,7 +33748,7 @@
     </row>
     <row r="156" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>53</v>
@@ -33914,7 +33926,7 @@
     </row>
     <row r="157" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>803</v>
+        <v>802</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>278</v>
@@ -34088,13 +34100,13 @@
     </row>
     <row r="158" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>809</v>
+        <v>808</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>278</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="D158" s="2">
         <v>1500</v>
@@ -34268,13 +34280,13 @@
     </row>
     <row r="159" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>278</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="D159" s="2">
         <v>1500</v>
@@ -34458,7 +34470,7 @@
     </row>
     <row r="160" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>197</v>
@@ -34630,7 +34642,7 @@
     </row>
     <row r="161" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>51</v>
@@ -34814,7 +34826,7 @@
     </row>
     <row r="162" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>51</v>
@@ -34990,7 +35002,7 @@
     </row>
     <row r="163" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>51</v>
@@ -35170,7 +35182,7 @@
     </row>
     <row r="164" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>53</v>
@@ -35348,7 +35360,7 @@
     </row>
     <row r="165" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>51</v>
@@ -35524,7 +35536,7 @@
     </row>
     <row r="166" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>50</v>
@@ -35706,7 +35718,7 @@
     </row>
     <row r="167" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>53</v>
@@ -35884,7 +35896,7 @@
     </row>
     <row r="168" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>55</v>
@@ -36058,7 +36070,7 @@
     </row>
     <row r="169" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>55</v>
@@ -36236,7 +36248,7 @@
     </row>
     <row r="170" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>53</v>
@@ -36412,7 +36424,7 @@
     </row>
     <row r="171" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>55</v>
@@ -36588,7 +36600,7 @@
     </row>
     <row r="172" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>53</v>
@@ -36766,7 +36778,7 @@
     </row>
     <row r="173" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>52</v>
@@ -36942,7 +36954,7 @@
     </row>
     <row r="174" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>49</v>
@@ -48963,16 +48975,16 @@
         <v>129</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>713</v>
+        <v>712</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>141</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="J1" s="8" t="s">
         <v>237</v>
@@ -48987,10 +48999,10 @@
         <v>283</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="P1" s="8" t="s">
         <v>132</v>
@@ -49011,7 +49023,7 @@
         <v>137</v>
       </c>
       <c r="V1" s="7" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
       <c r="W1" s="7" t="s">
         <v>138</v>
@@ -49026,7 +49038,7 @@
         <v>131</v>
       </c>
       <c r="AA1" s="7" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="AB1" s="7" t="s">
         <v>199</v>
@@ -49038,7 +49050,7 @@
         <v>286</v>
       </c>
       <c r="AE1" s="7" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
@@ -58423,6 +58435,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43DB3A21-6E97-43C0-9768-D0796C62C1D9}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:M250"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -58446,7 +58459,7 @@
         <v>72</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="C1" s="7" t="s">
         <v>318</v>
@@ -58461,7 +58474,7 @@
         <v>315</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>316</v>
@@ -58470,26 +58483,26 @@
         <v>317</v>
       </c>
       <c r="J1" s="7" t="s">
+        <v>761</v>
+      </c>
+      <c r="K1" s="7" t="s">
         <v>762</v>
       </c>
-      <c r="K1" s="7" t="s">
-        <v>763</v>
-      </c>
       <c r="L1" s="7" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>811</v>
-      </c>
-    </row>
-    <row r="2" spans="1:13" ht="270" x14ac:dyDescent="0.25">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="2" spans="1:13" ht="270" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="str">
         <f>IF(receta!A2="","",receta!A2)</f>
         <v>Agua de Valencia</v>
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>309</v>
@@ -58507,7 +58520,7 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="4" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58516,10 +58529,10 @@
         <v>Alejandra</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D3" s="4" t="s">
         <v>235</v>
@@ -58534,17 +58547,17 @@
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:13" ht="180" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="180" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="str">
         <f>IF(receta!A4="","",receta!A4)</f>
         <v>Alevosía</v>
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="E4" s="1" t="s">
         <v>238</v>
@@ -58553,7 +58566,7 @@
         <v>239</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="5"/>
@@ -58562,25 +58575,25 @@
       <c r="L4" s="5"/>
       <c r="M4" s="1"/>
     </row>
-    <row r="5" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="str">
         <f>IF(receta!A5="","",receta!A5)</f>
         <v>Alexander</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="1"/>
@@ -58589,26 +58602,26 @@
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
       <c r="M5" s="4" t="s">
-        <v>913</v>
-      </c>
-    </row>
-    <row r="6" spans="1:13" ht="270" x14ac:dyDescent="0.25">
+        <v>912</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="270" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="str">
         <f>IF(receta!A6="","",receta!A6)</f>
         <v>Amaretto Sour</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
@@ -58617,26 +58630,26 @@
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="4" t="s">
-        <v>950</v>
-      </c>
-    </row>
-    <row r="7" spans="1:13" ht="270" x14ac:dyDescent="0.25">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="270" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="str">
         <f>IF(receta!A7="","",receta!A7)</f>
         <v>Amaretto Spritz</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
@@ -58645,17 +58658,17 @@
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="4" t="s">
-        <v>951</v>
-      </c>
-    </row>
-    <row r="8" spans="1:13" ht="210" x14ac:dyDescent="0.25">
+        <v>950</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="210" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="str">
         <f>IF(receta!A8="","",receta!A8)</f>
         <v>Americano</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
@@ -58671,20 +58684,20 @@
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="4" t="s">
-        <v>1039</v>
-      </c>
-    </row>
-    <row r="9" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+        <v>1038</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="105" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="str">
         <f>IF(receta!A9="","",receta!A9)</f>
         <v>Amiga Mía</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E9" s="1" t="s">
         <v>188</v>
@@ -58699,7 +58712,7 @@
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
       <c r="M9" s="1" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="210" x14ac:dyDescent="0.25">
@@ -58708,10 +58721,10 @@
         <v>Andes Refresh</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>622</v>
+        <v>621</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="11"/>
@@ -58730,13 +58743,13 @@
         <v>Aperol Spritz</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>599</v>
+        <v>598</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>598</v>
+        <v>597</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -58747,7 +58760,7 @@
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="4" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58756,13 +58769,13 @@
         <v>Arándano Sour</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
@@ -58781,10 +58794,10 @@
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="4" t="s">
-        <v>449</v>
+        <v>448</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
@@ -58795,7 +58808,7 @@
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="4" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58805,10 +58818,10 @@
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
@@ -58823,7 +58836,7 @@
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="4" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58833,10 +58846,10 @@
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="4" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
@@ -58847,10 +58860,10 @@
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="4" t="s">
-        <v>1038</v>
-      </c>
-    </row>
-    <row r="16" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+        <v>1037</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="str">
         <f>IF(receta!A16="","",receta!A16)</f>
         <v>Blanco de Verano</v>
@@ -58859,13 +58872,13 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -58874,23 +58887,23 @@
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
     </row>
-    <row r="17" spans="1:13" ht="390" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="390" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="str">
         <f>IF(receta!A17="","",receta!A17)</f>
         <v>Bloody Mary</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="4" t="s">
-        <v>450</v>
+        <v>449</v>
       </c>
       <c r="D17" s="4" t="s">
         <v>157</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="F17" s="10" t="s">
-        <v>451</v>
+        <v>450</v>
       </c>
       <c r="G17" s="10"/>
       <c r="H17" s="4" t="s">
@@ -58904,7 +58917,7 @@
       <c r="L17" s="10"/>
       <c r="M17" s="1"/>
     </row>
-    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="str">
         <f>IF(receta!A18="","",receta!A18)</f>
         <v>Bloody Mary (Sin Alcohol)</v>
@@ -58928,21 +58941,21 @@
       <c r="L18" s="5"/>
       <c r="M18" s="1"/>
     </row>
-    <row r="19" spans="1:13" ht="180" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="180" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="str">
         <f>IF(receta!A19="","",receta!A19)</f>
         <v>Blue Hawaii</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="1" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
@@ -58951,17 +58964,17 @@
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="4" t="s">
-        <v>969</v>
-      </c>
-    </row>
-    <row r="20" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+        <v>968</v>
+      </c>
+    </row>
+    <row r="20" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="str">
         <f>IF(receta!A20="","",receta!A20)</f>
         <v>Blue Hawaiian</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="1" t="s">
@@ -58984,45 +58997,45 @@
         <v>Borgoña</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>736</v>
+        <v>735</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="4" t="s">
-        <v>916</v>
-      </c>
-    </row>
-    <row r="22" spans="1:13" ht="375" x14ac:dyDescent="0.25">
+        <v>915</v>
+      </c>
+    </row>
+    <row r="22" spans="1:13" ht="375" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="str">
         <f>IF(receta!A22="","",receta!A22)</f>
         <v>Caipiriña</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1" t="s">
+        <v>569</v>
+      </c>
+      <c r="F22" s="5" t="s">
         <v>570</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>571</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="1"/>
@@ -59031,7 +59044,7 @@
       <c r="K22" s="5"/>
       <c r="L22" s="5"/>
       <c r="M22" s="4" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -59042,7 +59055,7 @@
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
@@ -59053,17 +59066,17 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="4" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="24" spans="1:13" ht="345" x14ac:dyDescent="0.25">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="24" spans="1:13" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="str">
         <f>IF(receta!A24="","",receta!A24)</f>
         <v>Carajillo</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="4" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1" t="s">
@@ -59087,10 +59100,10 @@
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
@@ -59101,7 +59114,7 @@
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="4" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59111,108 +59124,108 @@
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="4" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="4" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="4" t="s">
-        <v>988</v>
-      </c>
-    </row>
-    <row r="27" spans="1:13" ht="375" x14ac:dyDescent="0.25">
+        <v>987</v>
+      </c>
+    </row>
+    <row r="27" spans="1:13" ht="375" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="str">
         <f>IF(receta!A27="","",receta!A27)</f>
         <v>Chupilca</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>693</v>
+        <v>692</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="L27" s="1"/>
       <c r="M27" s="4" t="s">
-        <v>972</v>
-      </c>
-    </row>
-    <row r="28" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>971</v>
+      </c>
+    </row>
+    <row r="28" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="str">
         <f>IF(receta!A28="","",receta!A28)</f>
         <v>Cimarrón</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
       <c r="J28" s="1" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="L28" s="5"/>
       <c r="M28" s="4" t="s">
-        <v>917</v>
-      </c>
-    </row>
-    <row r="29" spans="1:13" ht="360" x14ac:dyDescent="0.25">
+        <v>916</v>
+      </c>
+    </row>
+    <row r="29" spans="1:13" ht="360" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="str">
         <f>IF(receta!A29="","",receta!A29)</f>
         <v>Clavo Oxidado</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="4" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
@@ -59221,31 +59234,31 @@
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="4" t="s">
-        <v>927</v>
-      </c>
-    </row>
-    <row r="30" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>926</v>
+      </c>
+    </row>
+    <row r="30" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="str">
         <f>IF(receta!A30="","",receta!A30)</f>
         <v>Cléry</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>1121</v>
+        <v>1120</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="F30" s="5" t="s">
+        <v>1107</v>
+      </c>
+      <c r="G30" s="4" t="s">
         <v>1108</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>1109</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -59253,31 +59266,31 @@
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="4" t="s">
-        <v>928</v>
-      </c>
-    </row>
-    <row r="31" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="31" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="str">
         <f>IF(receta!A31="","",receta!A31)</f>
         <v>Cléry Chirimoya</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>738</v>
+        <v>737</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="F31" s="5" t="s">
+        <v>994</v>
+      </c>
+      <c r="G31" s="4" t="s">
         <v>995</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>996</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -59285,23 +59298,23 @@
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="4" t="s">
-        <v>973</v>
-      </c>
-    </row>
-    <row r="32" spans="1:13" ht="255" x14ac:dyDescent="0.25">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="32" spans="1:13" ht="255" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="str">
         <f>IF(receta!A32="","",receta!A32)</f>
         <v>Cléry Durazno</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>739</v>
+        <v>738</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1" t="s">
-        <v>335</v>
+        <v>1126</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>334</v>
@@ -59314,25 +59327,25 @@
       <c r="L32" s="5"/>
       <c r="M32" s="1"/>
     </row>
-    <row r="33" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="str">
         <f>IF(receta!A33="","",receta!A33)</f>
         <v>Clover Club</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>839</v>
+        <v>838</v>
       </c>
       <c r="D33" s="4" t="s">
+        <v>547</v>
+      </c>
+      <c r="E33" s="4" t="s">
         <v>548</v>
       </c>
-      <c r="E33" s="4" t="s">
-        <v>549</v>
-      </c>
       <c r="F33" s="1" t="s">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
@@ -59341,17 +59354,17 @@
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="4" t="s">
-        <v>879</v>
-      </c>
-    </row>
-    <row r="34" spans="1:13" ht="255" x14ac:dyDescent="0.25">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="34" spans="1:13" ht="255" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="str">
         <f>IF(receta!A34="","",receta!A34)</f>
         <v>Cordillera</v>
       </c>
       <c r="B34" s="1"/>
       <c r="C34" s="4" t="s">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="1" t="s">
@@ -59367,26 +59380,26 @@
       <c r="K34" s="5"/>
       <c r="L34" s="5"/>
       <c r="M34" s="4" t="s">
-        <v>974</v>
-      </c>
-    </row>
-    <row r="35" spans="1:13" ht="45" x14ac:dyDescent="0.25">
+        <v>973</v>
+      </c>
+    </row>
+    <row r="35" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="str">
         <f>IF(receta!A35="","",receta!A35)</f>
         <v>Cosmo Patagonia</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>731</v>
+        <v>730</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="1" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
@@ -59403,7 +59416,7 @@
       </c>
       <c r="B36" s="1"/>
       <c r="C36" s="4" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
@@ -59415,19 +59428,19 @@
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1" t="s">
-        <v>955</v>
-      </c>
-    </row>
-    <row r="37" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+        <v>954</v>
+      </c>
+    </row>
+    <row r="37" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="str">
         <f>IF(receta!A37="","",receta!A37)</f>
         <v>Crepúsculo</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>627</v>
+        <v>626</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>626</v>
+        <v>625</v>
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="4" t="s">
@@ -59443,24 +59456,24 @@
       <c r="K37" s="5"/>
       <c r="L37" s="5"/>
       <c r="M37" s="4" t="s">
-        <v>938</v>
-      </c>
-    </row>
-    <row r="38" spans="1:13" ht="255" x14ac:dyDescent="0.25">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="38" spans="1:13" ht="255" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="str">
         <f>IF(receta!A38="","",receta!A38)</f>
         <v>Cuba Libre</v>
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="4" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D38" s="1"/>
       <c r="E38" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="1"/>
@@ -59469,7 +59482,7 @@
       <c r="K38" s="5"/>
       <c r="L38" s="5"/>
       <c r="M38" s="4" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -59478,7 +59491,7 @@
         <v>Cynar Spritz</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>333</v>
@@ -59493,37 +59506,37 @@
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="4" t="s">
-        <v>1052</v>
-      </c>
-    </row>
-    <row r="40" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+        <v>1051</v>
+      </c>
+    </row>
+    <row r="40" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="str">
         <f>IF(receta!A40="","",receta!A40)</f>
         <v>Daiquiri</v>
       </c>
       <c r="B40" s="1"/>
       <c r="C40" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D40" s="1"/>
       <c r="E40" s="4" t="s">
-        <v>406</v>
+        <v>405</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="1" t="s">
+        <v>922</v>
+      </c>
+      <c r="I40" s="5" t="s">
         <v>923</v>
-      </c>
-      <c r="I40" s="5" t="s">
-        <v>924</v>
       </c>
       <c r="J40" s="4"/>
       <c r="K40" s="5"/>
       <c r="L40" s="5"/>
       <c r="M40" s="4" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -59532,10 +59545,10 @@
         <v>Dama Blanca</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="1"/>
@@ -59547,24 +59560,24 @@
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
       <c r="M41" s="4" t="s">
-        <v>1055</v>
-      </c>
-    </row>
-    <row r="42" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+        <v>1054</v>
+      </c>
+    </row>
+    <row r="42" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="str">
         <f>IF(receta!A42="","",receta!A42)</f>
         <v>Dark &amp; Stormy</v>
       </c>
       <c r="B42" s="1"/>
       <c r="C42" s="4" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
@@ -59573,7 +59586,7 @@
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="M42" s="4" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="270" x14ac:dyDescent="0.25">
@@ -59583,10 +59596,10 @@
       </c>
       <c r="B43" s="1"/>
       <c r="C43" s="4" t="s">
+        <v>589</v>
+      </c>
+      <c r="D43" s="4" t="s">
         <v>590</v>
-      </c>
-      <c r="D43" s="4" t="s">
-        <v>591</v>
       </c>
       <c r="E43" s="1"/>
       <c r="F43" s="5"/>
@@ -59601,7 +59614,7 @@
       <c r="K43" s="5"/>
       <c r="L43" s="5"/>
       <c r="M43" s="4" t="s">
-        <v>920</v>
+        <v>919</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -59611,7 +59624,7 @@
       </c>
       <c r="B44" s="1"/>
       <c r="C44" s="4" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
@@ -59630,13 +59643,13 @@
         <v>Dry Martini</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>694</v>
+        <v>693</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
@@ -59647,20 +59660,20 @@
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
       <c r="M45" s="4" t="s">
-        <v>1041</v>
-      </c>
-    </row>
-    <row r="46" spans="1:13" ht="285" x14ac:dyDescent="0.25">
+        <v>1040</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" ht="285" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="str">
         <f>IF(receta!A46="","",receta!A46)</f>
         <v>El Amor en los Tiempos del Covid</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C46" s="4"/>
       <c r="D46" s="4" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>185</v>
@@ -59672,26 +59685,26 @@
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
       <c r="J46" s="4" t="s">
+        <v>1028</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>1027</v>
+      </c>
+      <c r="L46" s="4" t="s">
         <v>1029</v>
       </c>
-      <c r="K46" s="5" t="s">
-        <v>1028</v>
-      </c>
-      <c r="L46" s="4" t="s">
-        <v>1030</v>
-      </c>
       <c r="M46" s="4" t="s">
-        <v>982</v>
-      </c>
-    </row>
-    <row r="47" spans="1:13" ht="240" x14ac:dyDescent="0.25">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" ht="240" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="str">
         <f>IF(receta!A47="","",receta!A47)</f>
         <v>Enemigo Íntimo</v>
       </c>
       <c r="B47" s="1"/>
       <c r="C47" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D47" s="4" t="s">
         <v>306</v>
@@ -59709,26 +59722,26 @@
       <c r="K47" s="5"/>
       <c r="L47" s="5"/>
       <c r="M47" s="4" t="s">
-        <v>934</v>
-      </c>
-    </row>
-    <row r="48" spans="1:13" ht="315" x14ac:dyDescent="0.25">
+        <v>933</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" ht="315" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="str">
         <f>IF(receta!A48="","",receta!A48)</f>
         <v>Escarabajo</v>
       </c>
       <c r="B48" s="1"/>
       <c r="C48" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>597</v>
+        <v>596</v>
       </c>
       <c r="E48" s="1" t="s">
+        <v>594</v>
+      </c>
+      <c r="F48" s="5" t="s">
         <v>595</v>
-      </c>
-      <c r="F48" s="5" t="s">
-        <v>596</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="1"/>
@@ -59738,26 +59751,26 @@
       <c r="L48" s="5"/>
       <c r="M48" s="1"/>
     </row>
-    <row r="49" spans="1:13" ht="270" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" ht="270" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="str">
         <f>IF(receta!A49="","",receta!A49)</f>
         <v>Española</v>
       </c>
       <c r="B49" s="1"/>
       <c r="C49" s="4" t="s">
-        <v>629</v>
+        <v>628</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="E49" s="1" t="s">
+        <v>766</v>
+      </c>
+      <c r="F49" s="5" t="s">
         <v>767</v>
       </c>
-      <c r="F49" s="5" t="s">
-        <v>768</v>
-      </c>
       <c r="G49" s="4" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -59765,27 +59778,27 @@
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
       <c r="M49" s="4" t="s">
-        <v>1000</v>
-      </c>
-    </row>
-    <row r="50" spans="1:13" ht="255" x14ac:dyDescent="0.25">
+        <v>999</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" ht="255" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="str">
         <f>IF(receta!A50="","",receta!A50)</f>
         <v>Espiral</v>
       </c>
       <c r="B50" s="1"/>
       <c r="C50" s="4" t="s">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="4" t="s">
+        <v>479</v>
+      </c>
+      <c r="F50" s="5" t="s">
         <v>480</v>
       </c>
-      <c r="F50" s="5" t="s">
-        <v>481</v>
-      </c>
       <c r="G50" s="4" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>326</v>
@@ -59797,7 +59810,7 @@
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
       <c r="M50" s="4" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -59807,7 +59820,7 @@
       </c>
       <c r="B51" s="1"/>
       <c r="C51" s="4" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -59819,20 +59832,20 @@
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
       <c r="M51" s="1" t="s">
-        <v>952</v>
-      </c>
-    </row>
-    <row r="52" spans="1:13" ht="150" x14ac:dyDescent="0.25">
+        <v>951</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="str">
         <f>IF(receta!A52="","",receta!A52)</f>
         <v>Estoy Verde</v>
       </c>
       <c r="B52" s="1"/>
       <c r="C52" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>193</v>
@@ -59844,54 +59857,54 @@
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="L52" s="1"/>
       <c r="M52" s="4" t="s">
-        <v>932</v>
-      </c>
-    </row>
-    <row r="53" spans="1:13" ht="390" x14ac:dyDescent="0.25">
+        <v>931</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" ht="390" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="str">
         <f>IF(receta!A53="","",receta!A53)</f>
         <v>Fanshop</v>
       </c>
       <c r="B53" s="1"/>
       <c r="C53" s="4" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="D53" s="4" t="s">
+        <v>401</v>
+      </c>
+      <c r="E53" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="F53" s="1" t="s">
         <v>403</v>
       </c>
-      <c r="F53" s="1" t="s">
-        <v>404</v>
-      </c>
       <c r="G53" s="4" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="J53" s="1" t="s">
+        <v>1100</v>
+      </c>
+      <c r="K53" s="5" t="s">
+        <v>1099</v>
+      </c>
+      <c r="L53" s="1" t="s">
         <v>1101</v>
       </c>
-      <c r="K53" s="5" t="s">
-        <v>1100</v>
-      </c>
-      <c r="L53" s="1" t="s">
-        <v>1102</v>
-      </c>
       <c r="M53" s="4" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59901,14 +59914,14 @@
       </c>
       <c r="B54" s="1"/>
       <c r="C54" s="4" t="s">
-        <v>680</v>
+        <v>679</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="1"/>
       <c r="F54" s="5"/>
       <c r="G54" s="4"/>
       <c r="H54" s="1" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="I54" s="5" t="s">
         <v>290</v>
@@ -59917,17 +59930,17 @@
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
       <c r="M54" s="4" t="s">
-        <v>911</v>
-      </c>
-    </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+        <v>910</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="str">
         <f>IF(receta!A55="","",receta!A55)</f>
         <v>Feria Libre</v>
       </c>
       <c r="B55" s="1"/>
       <c r="C55" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D55" s="1"/>
       <c r="E55" s="1" t="s">
@@ -59944,26 +59957,26 @@
       <c r="L55" s="5"/>
       <c r="M55" s="1"/>
     </row>
-    <row r="56" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="str">
         <f>IF(receta!A56="","",receta!A56)</f>
         <v>Fernet con Coca</v>
       </c>
       <c r="B56" s="1"/>
       <c r="C56" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -59971,20 +59984,20 @@
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
       <c r="M56" s="4" t="s">
-        <v>953</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+        <v>952</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="str">
         <f>IF(receta!A57="","",receta!A57)</f>
         <v>Ferroviario</v>
       </c>
       <c r="B57" s="1"/>
       <c r="C57" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="E57" s="11" t="s">
         <v>172</v>
@@ -59999,7 +60012,7 @@
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
       <c r="M57" s="4" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="150" x14ac:dyDescent="0.25">
@@ -60008,10 +60021,10 @@
         <v>Frangelico Sour</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
@@ -60023,43 +60036,43 @@
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="4" t="s">
-        <v>956</v>
-      </c>
-    </row>
-    <row r="59" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="str">
         <f>IF(receta!A59="","",receta!A59)</f>
         <v>French 75</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>631</v>
+        <v>630</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>630</v>
+        <v>629</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E59" s="4" t="s">
+        <v>1094</v>
+      </c>
+      <c r="F59" s="5" t="s">
         <v>1095</v>
       </c>
-      <c r="F59" s="5" t="s">
+      <c r="G59" s="4" t="s">
         <v>1096</v>
-      </c>
-      <c r="G59" s="4" t="s">
-        <v>1097</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
       <c r="J59" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="K59" s="5" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="L59" s="5"/>
       <c r="M59" s="4" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -60069,7 +60082,7 @@
       </c>
       <c r="B60" s="1"/>
       <c r="C60" s="4" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
@@ -60081,26 +60094,26 @@
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
       <c r="M60" s="4" t="s">
-        <v>978</v>
-      </c>
-    </row>
-    <row r="61" spans="1:13" ht="165" x14ac:dyDescent="0.25">
+        <v>977</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" ht="165" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="str">
         <f>IF(receta!A61="","",receta!A61)</f>
         <v>Gimlet</v>
       </c>
       <c r="B61" s="1"/>
       <c r="C61" s="4" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="4"/>
@@ -60109,24 +60122,24 @@
       <c r="K61" s="1"/>
       <c r="L61" s="1"/>
       <c r="M61" s="4" t="s">
-        <v>907</v>
-      </c>
-    </row>
-    <row r="62" spans="1:13" ht="345" x14ac:dyDescent="0.25">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="str">
         <f>IF(receta!A62="","",receta!A62)</f>
         <v>Gin con Gin</v>
       </c>
       <c r="B62" s="1"/>
       <c r="C62" s="4" t="s">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D62" s="1"/>
       <c r="E62" s="4" t="s">
+        <v>406</v>
+      </c>
+      <c r="F62" s="5" t="s">
         <v>407</v>
-      </c>
-      <c r="F62" s="5" t="s">
-        <v>408</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="4"/>
@@ -60135,10 +60148,10 @@
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
       <c r="M62" s="4" t="s">
-        <v>987</v>
-      </c>
-    </row>
-    <row r="63" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>986</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="str">
         <f>IF(receta!A63="","",receta!A63)</f>
         <v>Gin Tonic</v>
@@ -60146,7 +60159,7 @@
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>159</v>
@@ -60156,39 +60169,39 @@
       </c>
       <c r="G63" s="4"/>
       <c r="H63" s="4" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="I63" s="5" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="J63" s="1" t="s">
+        <v>763</v>
+      </c>
+      <c r="K63" s="5" t="s">
         <v>764</v>
       </c>
-      <c r="K63" s="5" t="s">
-        <v>765</v>
-      </c>
       <c r="L63" s="4" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="M63" s="4" t="s">
-        <v>926</v>
-      </c>
-    </row>
-    <row r="64" spans="1:13" ht="135" x14ac:dyDescent="0.25">
+        <v>925</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="str">
         <f>IF(receta!A64="","",receta!A64)</f>
         <v>Ginger Fire</v>
       </c>
       <c r="B64" s="1"/>
       <c r="C64" s="4" t="s">
-        <v>692</v>
+        <v>691</v>
       </c>
       <c r="D64" s="1"/>
       <c r="E64" s="1" t="s">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
@@ -60197,7 +60210,7 @@
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
       <c r="M64" s="4" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60207,7 +60220,7 @@
       </c>
       <c r="B65" s="1"/>
       <c r="C65" s="4" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D65" s="4" t="s">
         <v>169</v>
@@ -60221,7 +60234,7 @@
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
       <c r="M65" s="1" t="s">
-        <v>922</v>
+        <v>921</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="375" x14ac:dyDescent="0.25">
@@ -60230,13 +60243,13 @@
         <v>Hugo</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>745</v>
+        <v>744</v>
       </c>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
@@ -60247,17 +60260,17 @@
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
       <c r="M66" s="4" t="s">
-        <v>1053</v>
-      </c>
-    </row>
-    <row r="67" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>1052</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="str">
         <f>IF(receta!A67="","",receta!A67)</f>
         <v>Incendio</v>
       </c>
       <c r="B67" s="1"/>
       <c r="C67" s="4" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D67" s="4"/>
       <c r="E67" s="1" t="s">
@@ -60273,20 +60286,20 @@
       <c r="K67" s="5"/>
       <c r="L67" s="5"/>
       <c r="M67" s="4" t="s">
-        <v>949</v>
-      </c>
-    </row>
-    <row r="68" spans="1:13" ht="330" x14ac:dyDescent="0.25">
+        <v>948</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" ht="330" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="str">
         <f>IF(receta!A68="","",receta!A68)</f>
         <v>Ingrata</v>
       </c>
       <c r="B68" s="1"/>
       <c r="C68" s="4" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="E68" s="1" t="s">
         <v>165</v>
@@ -60298,35 +60311,35 @@
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
       <c r="J68" s="1" t="s">
+        <v>1122</v>
+      </c>
+      <c r="K68" s="5" t="s">
+        <v>1121</v>
+      </c>
+      <c r="L68" s="4" t="s">
         <v>1123</v>
       </c>
-      <c r="K68" s="5" t="s">
-        <v>1122</v>
-      </c>
-      <c r="L68" s="4" t="s">
-        <v>1124</v>
-      </c>
       <c r="M68" s="4" t="s">
-        <v>942</v>
-      </c>
-    </row>
-    <row r="69" spans="1:13" ht="300" x14ac:dyDescent="0.25">
+        <v>941</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" ht="300" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="str">
         <f>IF(receta!A69="","",receta!A69)</f>
         <v>Isla Negra</v>
       </c>
       <c r="B69" s="1"/>
       <c r="C69" s="4" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="D69" s="4" t="s">
+        <v>429</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>431</v>
+      </c>
+      <c r="F69" s="1" t="s">
         <v>430</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>432</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>431</v>
       </c>
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
@@ -60335,26 +60348,26 @@
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
       <c r="M69" s="4" t="s">
-        <v>910</v>
-      </c>
-    </row>
-    <row r="70" spans="1:13" ht="195" x14ac:dyDescent="0.25">
+        <v>909</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" ht="195" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="str">
         <f>IF(receta!A70="","",receta!A70)</f>
         <v>Jardín</v>
       </c>
       <c r="B70" s="1"/>
       <c r="C70" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E70" s="1" t="s">
+        <v>397</v>
+      </c>
+      <c r="F70" s="1" t="s">
         <v>398</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>399</v>
       </c>
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
@@ -60363,24 +60376,24 @@
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
       <c r="M70" s="4" t="s">
-        <v>939</v>
-      </c>
-    </row>
-    <row r="71" spans="1:13" ht="225" x14ac:dyDescent="0.25">
+        <v>938</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" ht="225" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="str">
         <f>IF(receta!A71="","",receta!A71)</f>
         <v>John Collins</v>
       </c>
       <c r="B71" s="1"/>
       <c r="C71" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D71" s="1"/>
       <c r="E71" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="1"/>
@@ -60389,43 +60402,43 @@
       <c r="K71" s="5"/>
       <c r="L71" s="5"/>
       <c r="M71" s="4" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="72" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>929</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="str">
         <f>IF(receta!A72="","",receta!A72)</f>
         <v>Jote</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>634</v>
+        <v>633</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>633</v>
+        <v>632</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="E72" s="1" t="s">
+        <v>1092</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>1091</v>
+      </c>
+      <c r="G72" s="4" t="s">
         <v>1093</v>
       </c>
-      <c r="F72" s="5" t="s">
-        <v>1092</v>
-      </c>
-      <c r="G72" s="4" t="s">
-        <v>1094</v>
-      </c>
       <c r="H72" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="J72" s="1"/>
       <c r="K72" s="5"/>
       <c r="L72" s="5"/>
       <c r="M72" s="4" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
     </row>
     <row r="73" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -60434,11 +60447,11 @@
         <v>Julepe de Menta</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="C73" s="4"/>
       <c r="D73" s="4" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
@@ -60449,35 +60462,35 @@
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
       <c r="M73" s="4" t="s">
-        <v>1065</v>
-      </c>
-    </row>
-    <row r="74" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>1064</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="str">
         <f>IF(receta!A74="","",receta!A74)</f>
         <v>Julieta Flowers</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>709</v>
+        <v>708</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>707</v>
+        <v>706</v>
       </c>
       <c r="E74" s="1" t="s">
+        <v>725</v>
+      </c>
+      <c r="F74" s="5" t="s">
         <v>726</v>
-      </c>
-      <c r="F74" s="5" t="s">
-        <v>727</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="1" t="s">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>728</v>
+        <v>727</v>
       </c>
       <c r="J74" s="1"/>
       <c r="K74" s="5"/>
@@ -60503,17 +60516,17 @@
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
       <c r="M75" s="4" t="s">
-        <v>1054</v>
-      </c>
-    </row>
-    <row r="76" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>1053</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="str">
         <f>IF(receta!A76="","",receta!A76)</f>
         <v>Kokomo</v>
       </c>
       <c r="B76" s="1"/>
       <c r="C76" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D76" s="4" t="s">
         <v>270</v>
@@ -60539,10 +60552,10 @@
       </c>
       <c r="B77" s="1"/>
       <c r="C77" s="4" t="s">
+        <v>1009</v>
+      </c>
+      <c r="D77" s="4" t="s">
         <v>1010</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>1011</v>
       </c>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
@@ -60553,33 +60566,33 @@
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
       <c r="M77" s="4" t="s">
-        <v>1009</v>
-      </c>
-    </row>
-    <row r="78" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+        <v>1008</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="str">
         <f>IF(receta!A78="","",receta!A78)</f>
         <v>London Mule</v>
       </c>
       <c r="B78" s="1"/>
       <c r="C78" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D78" s="1"/>
       <c r="E78" s="1" t="s">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="G78" s="5"/>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
       <c r="J78" s="1" t="s">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="K78" s="5" t="s">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="L78" s="5"/>
       <c r="M78" s="1"/>
@@ -60592,8 +60605,12 @@
       <c r="B79" s="1"/>
       <c r="C79" s="4"/>
       <c r="D79" s="1"/>
-      <c r="E79" s="1"/>
-      <c r="F79" s="1"/>
+      <c r="E79" s="1" t="s">
+        <v>1127</v>
+      </c>
+      <c r="F79" s="5" t="s">
+        <v>1128</v>
+      </c>
       <c r="G79" s="1"/>
       <c r="H79" s="1"/>
       <c r="I79" s="1"/>
@@ -60629,7 +60646,7 @@
       </c>
       <c r="B81" s="1"/>
       <c r="C81" s="4" t="s">
-        <v>723</v>
+        <v>722</v>
       </c>
       <c r="D81" s="4"/>
       <c r="E81" s="1"/>
@@ -60648,45 +60665,45 @@
         <v>Mai Tai Piña</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>718</v>
+        <v>717</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>721</v>
+        <v>720</v>
       </c>
       <c r="D82" s="4"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
       <c r="G82" s="1"/>
       <c r="H82" s="1" t="s">
-        <v>720</v>
+        <v>719</v>
       </c>
       <c r="I82" s="5" t="s">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="J82" s="1"/>
       <c r="K82" s="1"/>
       <c r="L82" s="1"/>
       <c r="M82" s="4" t="s">
-        <v>1067</v>
-      </c>
-    </row>
-    <row r="83" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>1066</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="str">
         <f>IF(receta!A83="","",receta!A83)</f>
         <v>Mala Reputación</v>
       </c>
       <c r="B83" s="1"/>
       <c r="C83" s="4" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>304</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="G83" s="5"/>
       <c r="H83" s="1"/>
@@ -60695,7 +60712,7 @@
       <c r="K83" s="5"/>
       <c r="L83" s="5"/>
       <c r="M83" s="4" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
     </row>
     <row r="84" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60704,28 +60721,28 @@
         <v>Malta con Huevo</v>
       </c>
       <c r="B84" s="4" t="s">
+        <v>657</v>
+      </c>
+      <c r="C84" s="4" t="s">
         <v>658</v>
       </c>
-      <c r="C84" s="4" t="s">
-        <v>659</v>
-      </c>
       <c r="D84" s="4" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
       <c r="H84" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="J84" s="1"/>
       <c r="K84" s="1"/>
       <c r="L84" s="1"/>
       <c r="M84" s="4" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -60734,28 +60751,28 @@
         <v>Malta con Leche Condensada</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
       <c r="H85" s="1" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="J85" s="1"/>
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
       <c r="M85" s="4" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -60764,7 +60781,7 @@
         <v>Mango Sour</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>670</v>
+        <v>669</v>
       </c>
       <c r="C86" s="4"/>
       <c r="D86" s="1"/>
@@ -60778,34 +60795,34 @@
       <c r="L86" s="1"/>
       <c r="M86" s="1"/>
     </row>
-    <row r="87" spans="1:13" ht="165" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" ht="165" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="str">
         <f>IF(receta!A87="","",receta!A87)</f>
         <v>Manhattan</v>
       </c>
       <c r="B87" s="1"/>
       <c r="C87" s="4" t="s">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D87" s="1"/>
       <c r="E87" s="1" t="s">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>748</v>
+        <v>747</v>
       </c>
       <c r="G87" s="5"/>
       <c r="H87" s="1" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="I87" s="5" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="J87" s="1"/>
       <c r="K87" s="5"/>
       <c r="L87" s="5"/>
       <c r="M87" s="4" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
     </row>
     <row r="88" spans="1:13" ht="360" x14ac:dyDescent="0.25">
@@ -60814,13 +60831,13 @@
         <v>Maqui Sour</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
@@ -60831,19 +60848,19 @@
       <c r="K88" s="1"/>
       <c r="L88" s="1"/>
       <c r="M88" s="4" t="s">
-        <v>1066</v>
-      </c>
-    </row>
-    <row r="89" spans="1:13" ht="180" x14ac:dyDescent="0.25">
+        <v>1065</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" ht="180" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="str">
         <f>IF(receta!A89="","",receta!A89)</f>
         <v>Margarita</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D89" s="1"/>
       <c r="E89" s="1" t="s">
@@ -60853,7 +60870,7 @@
         <v>180</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
@@ -60861,10 +60878,10 @@
       <c r="K89" s="5"/>
       <c r="L89" s="5"/>
       <c r="M89" s="4" t="s">
-        <v>1071</v>
-      </c>
-    </row>
-    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1070</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="str">
         <f>IF(receta!A90="","",receta!A90)</f>
         <v>Margarita Maracuyá</v>
@@ -60873,37 +60890,37 @@
       <c r="C90" s="1"/>
       <c r="D90" s="1"/>
       <c r="E90" s="1" t="s">
-        <v>589</v>
+        <v>588</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="G90" s="5"/>
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
       <c r="J90" s="1" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="K90" s="5" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="L90" s="5"/>
       <c r="M90" s="1"/>
     </row>
-    <row r="91" spans="1:13" ht="225" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" ht="225" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="str">
         <f>IF(receta!A91="","",receta!A91)</f>
         <v>Melón con Vino</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>681</v>
+        <v>680</v>
       </c>
       <c r="D91" s="1"/>
       <c r="E91" s="1" t="s">
-        <v>335</v>
+        <v>1126</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>334</v>
@@ -60916,19 +60933,19 @@
       <c r="L91" s="5"/>
       <c r="M91" s="1"/>
     </row>
-    <row r="92" spans="1:13" ht="375" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" ht="375" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="str">
         <f>IF(receta!A92="","",receta!A92)</f>
         <v>Michelada</v>
       </c>
       <c r="B92" s="4" t="s">
+        <v>839</v>
+      </c>
+      <c r="C92" s="4" t="s">
         <v>840</v>
       </c>
-      <c r="C92" s="4" t="s">
-        <v>841</v>
-      </c>
       <c r="D92" s="4" t="s">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>178</v>
@@ -60940,10 +60957,10 @@
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
       <c r="J92" s="1" t="s">
-        <v>1099</v>
+        <v>1098</v>
       </c>
       <c r="K92" s="5" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="L92" s="5"/>
       <c r="M92" s="1"/>
@@ -60955,7 +60972,7 @@
       </c>
       <c r="B93" s="1"/>
       <c r="C93" s="4" t="s">
-        <v>537</v>
+        <v>536</v>
       </c>
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
@@ -60967,7 +60984,7 @@
       <c r="K93" s="1"/>
       <c r="L93" s="1"/>
       <c r="M93" s="4" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="94" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -60977,7 +60994,7 @@
       </c>
       <c r="B94" s="1"/>
       <c r="C94" s="4" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="D94" s="1"/>
       <c r="E94" s="1"/>
@@ -60989,7 +61006,7 @@
       <c r="K94" s="1"/>
       <c r="L94" s="1"/>
       <c r="M94" s="4" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="95" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -60998,10 +61015,10 @@
         <v>Mojito</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>639</v>
+        <v>638</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="D95" s="4"/>
       <c r="E95" s="1"/>
@@ -61013,7 +61030,7 @@
       <c r="K95" s="1"/>
       <c r="L95" s="1"/>
       <c r="M95" s="4" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
     </row>
     <row r="96" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -61023,7 +61040,7 @@
       </c>
       <c r="B96" s="1"/>
       <c r="C96" s="4" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="D96" s="4"/>
       <c r="E96" s="1"/>
@@ -61036,23 +61053,23 @@
       <c r="L96" s="1"/>
       <c r="M96" s="1"/>
     </row>
-    <row r="97" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="str">
         <f>IF(receta!A97="","",receta!A97)</f>
         <v>Mojito Maracuyá</v>
       </c>
       <c r="B97" s="1"/>
       <c r="C97" s="4" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="G97" s="1"/>
       <c r="H97" s="4"/>
@@ -61061,7 +61078,7 @@
       <c r="K97" s="1"/>
       <c r="L97" s="1"/>
       <c r="M97" s="4" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="98" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -61070,10 +61087,10 @@
         <v>Mojito Spritz</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="D98" s="4"/>
       <c r="E98" s="1"/>
@@ -61086,7 +61103,7 @@
       <c r="L98" s="1"/>
       <c r="M98" s="1"/>
     </row>
-    <row r="99" spans="1:13" ht="375" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" ht="375" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="str">
         <f>IF(receta!A99="","",receta!A99)</f>
         <v>Moscow Mule</v>
@@ -61109,26 +61126,26 @@
       <c r="K99" s="5"/>
       <c r="L99" s="5"/>
       <c r="M99" s="4" t="s">
-        <v>925</v>
-      </c>
-    </row>
-    <row r="100" spans="1:13" ht="150" x14ac:dyDescent="0.25">
+        <v>924</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" ht="150" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="str">
         <f>IF(receta!A100="","",receta!A100)</f>
         <v>Naranja Sour</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D100" s="4"/>
       <c r="E100" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="G100" s="5"/>
       <c r="H100" s="1"/>
@@ -61137,7 +61154,7 @@
       <c r="K100" s="5"/>
       <c r="L100" s="5"/>
       <c r="M100" s="4" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
     </row>
     <row r="101" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -61147,7 +61164,7 @@
       </c>
       <c r="B101" s="1"/>
       <c r="C101" s="4" t="s">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D101" s="4"/>
       <c r="E101" s="4"/>
@@ -61171,7 +61188,7 @@
       </c>
       <c r="B102" s="1"/>
       <c r="C102" s="4" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="D102" s="4" t="s">
         <v>224</v>
@@ -61185,7 +61202,7 @@
       <c r="K102" s="1"/>
       <c r="L102" s="1"/>
       <c r="M102" s="4" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="103" spans="1:13" ht="210" x14ac:dyDescent="0.25">
@@ -61195,7 +61212,7 @@
       </c>
       <c r="B103" s="1"/>
       <c r="C103" s="4" t="s">
-        <v>592</v>
+        <v>591</v>
       </c>
       <c r="D103" s="1"/>
       <c r="E103" s="1"/>
@@ -61207,28 +61224,28 @@
       <c r="K103" s="1"/>
       <c r="L103" s="1"/>
       <c r="M103" s="4" t="s">
-        <v>1037</v>
-      </c>
-    </row>
-    <row r="104" spans="1:13" ht="345" x14ac:dyDescent="0.25">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" ht="345" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="str">
         <f>IF(receta!A104="","",receta!A104)</f>
         <v>New York Sour</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="G104" s="5"/>
       <c r="H104" s="1"/>
@@ -61237,17 +61254,17 @@
       <c r="K104" s="5"/>
       <c r="L104" s="5"/>
       <c r="M104" s="4" t="s">
-        <v>1004</v>
-      </c>
-    </row>
-    <row r="105" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+        <v>1003</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="str">
         <f>IF(receta!A105="","",receta!A105)</f>
         <v>No Me Falles</v>
       </c>
       <c r="B105" s="1"/>
       <c r="C105" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D105" s="1"/>
       <c r="E105" s="1" t="s">
@@ -61263,41 +61280,41 @@
       <c r="K105" s="1"/>
       <c r="L105" s="1"/>
       <c r="M105" s="4" t="s">
-        <v>941</v>
-      </c>
-    </row>
-    <row r="106" spans="1:13" ht="375" x14ac:dyDescent="0.25">
+        <v>940</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" ht="375" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="str">
         <f>IF(receta!A106="","",receta!A106)</f>
         <v>Old Fashioned</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>641</v>
+        <v>640</v>
       </c>
       <c r="C106" s="4"/>
       <c r="D106" s="4" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="E106" s="1" t="s">
+        <v>1034</v>
+      </c>
+      <c r="F106" s="5" t="s">
         <v>1035</v>
       </c>
-      <c r="F106" s="5" t="s">
-        <v>1036</v>
-      </c>
       <c r="G106" s="4" t="s">
-        <v>1034</v>
+        <v>1033</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="I106" s="5" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="J106" s="1"/>
       <c r="K106" s="1"/>
       <c r="L106" s="1"/>
       <c r="M106" s="4" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="107" spans="1:13" ht="192" customHeight="1" x14ac:dyDescent="0.25">
@@ -61307,7 +61324,7 @@
       </c>
       <c r="B107" s="1"/>
       <c r="C107" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="D107" s="1"/>
       <c r="E107" s="1"/>
@@ -61326,17 +61343,17 @@
         <v>Paloma</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>643</v>
+        <v>642</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>642</v>
+        <v>641</v>
       </c>
       <c r="D108" s="1"/>
       <c r="E108" s="1"/>
       <c r="F108" s="1"/>
       <c r="G108" s="1"/>
       <c r="H108" s="1" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="I108" s="5" t="s">
         <v>256</v>
@@ -61345,7 +61362,7 @@
       <c r="K108" s="1"/>
       <c r="L108" s="1"/>
       <c r="M108" s="4" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="109" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -61354,7 +61371,7 @@
         <v>Parrón</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="C109" s="4"/>
       <c r="D109" s="4"/>
@@ -61368,25 +61385,25 @@
       <c r="L109" s="1"/>
       <c r="M109" s="1"/>
     </row>
-    <row r="110" spans="1:13" ht="330" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" ht="330" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="str">
         <f>IF(receta!A110="","",receta!A110)</f>
         <v>Penicilina</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>673</v>
+        <v>672</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="G110" s="5"/>
       <c r="H110" s="1"/>
@@ -61395,24 +61412,24 @@
       <c r="K110" s="5"/>
       <c r="L110" s="5"/>
       <c r="M110" s="4" t="s">
-        <v>1003</v>
-      </c>
-    </row>
-    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+        <v>1002</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="str">
         <f>IF(receta!A111="","",receta!A111)</f>
         <v>Phil Collins</v>
       </c>
       <c r="B111" s="1"/>
       <c r="C111" s="4" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="D111" s="1"/>
       <c r="E111" s="1" t="s">
-        <v>499</v>
+        <v>498</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="G111" s="5"/>
       <c r="H111" s="1"/>
@@ -61422,24 +61439,24 @@
       <c r="L111" s="5"/>
       <c r="M111" s="1"/>
     </row>
-    <row r="112" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="str">
         <f>IF(receta!A112="","",receta!A112)</f>
         <v>Pichuncho</v>
       </c>
       <c r="B112" s="1"/>
       <c r="C112" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="D112" s="1"/>
       <c r="E112" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="H112" s="1"/>
       <c r="I112" s="5"/>
@@ -61448,18 +61465,18 @@
       <c r="L112" s="5"/>
       <c r="M112" s="1"/>
     </row>
-    <row r="113" spans="1:13" ht="195" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" ht="195" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="str">
         <f>IF(receta!A113="","",receta!A113)</f>
         <v>Piña Colada</v>
       </c>
       <c r="B113" s="1"/>
       <c r="C113" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D113" s="5"/>
       <c r="E113" s="1" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="F113" s="5" t="s">
         <v>158</v>
@@ -61471,7 +61488,7 @@
       <c r="K113" s="5"/>
       <c r="L113" s="5"/>
       <c r="M113" s="4" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.25">
@@ -61514,17 +61531,17 @@
       <c r="L115" s="1"/>
       <c r="M115" s="1"/>
     </row>
-    <row r="116" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="str">
         <f>IF(receta!A116="","",receta!A116)</f>
         <v>Pisco Sour</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="C116" s="4"/>
       <c r="D116" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>161</v>
@@ -61540,51 +61557,55 @@
       <c r="L116" s="5"/>
       <c r="M116" s="1"/>
     </row>
-    <row r="117" spans="1:13" ht="210" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" ht="210" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="str">
         <f>IF(receta!A117="","",receta!A117)</f>
         <v>Piscola</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>644</v>
+        <v>643</v>
       </c>
       <c r="D117" s="5"/>
       <c r="E117" s="1" t="s">
         <v>156</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="G117" s="5"/>
       <c r="H117" s="1"/>
       <c r="I117" s="1"/>
-      <c r="J117" s="1"/>
-      <c r="K117" s="5"/>
+      <c r="J117" s="4" t="s">
+        <v>1124</v>
+      </c>
+      <c r="K117" s="5" t="s">
+        <v>1125</v>
+      </c>
       <c r="L117" s="5"/>
       <c r="M117" s="4" t="s">
-        <v>1008</v>
-      </c>
-    </row>
-    <row r="118" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+        <v>1007</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="str">
         <f>IF(receta!A118="","",receta!A118)</f>
         <v>Pistón</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>647</v>
+        <v>646</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="D118" s="1"/>
       <c r="E118" s="1" t="s">
+        <v>499</v>
+      </c>
+      <c r="F118" s="5" t="s">
         <v>500</v>
-      </c>
-      <c r="F118" s="5" t="s">
-        <v>501</v>
       </c>
       <c r="G118" s="5"/>
       <c r="H118" s="1"/>
@@ -61601,10 +61622,10 @@
       </c>
       <c r="B119" s="1"/>
       <c r="C119" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E119" s="1"/>
       <c r="F119" s="5"/>
@@ -61619,26 +61640,26 @@
       <c r="K119" s="5"/>
       <c r="L119" s="5"/>
       <c r="M119" s="4" t="s">
-        <v>1006</v>
-      </c>
-    </row>
-    <row r="120" spans="1:13" ht="135" x14ac:dyDescent="0.25">
+        <v>1005</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="str">
         <f>IF(receta!A120="","",receta!A120)</f>
         <v>Ramazzotti Spritz</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="D120" s="1"/>
       <c r="E120" s="1" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="G120" s="5"/>
       <c r="H120" s="1"/>
@@ -61648,23 +61669,23 @@
       <c r="L120" s="5"/>
       <c r="M120" s="1"/>
     </row>
-    <row r="121" spans="1:13" ht="135" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" ht="135" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="str">
         <f>IF(receta!A121="","",receta!A121)</f>
         <v>Ramazzotti Violetto Spritz</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D121" s="1"/>
       <c r="E121" s="1" t="s">
-        <v>1091</v>
+        <v>1090</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="G121" s="1"/>
       <c r="H121" s="1"/>
@@ -61674,21 +61695,21 @@
       <c r="L121" s="1"/>
       <c r="M121" s="1"/>
     </row>
-    <row r="122" spans="1:13" ht="30" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="str">
         <f>IF(receta!A122="","",receta!A122)</f>
         <v>Ron Cola</v>
       </c>
       <c r="B122" s="1"/>
       <c r="C122" s="4" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D122" s="1"/>
       <c r="E122" s="1" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="G122" s="1"/>
       <c r="H122" s="1"/>
@@ -61705,7 +61726,7 @@
       </c>
       <c r="B123" s="1"/>
       <c r="C123" s="4" t="s">
-        <v>648</v>
+        <v>647</v>
       </c>
       <c r="D123" s="4" t="s">
         <v>252</v>
@@ -61714,7 +61735,7 @@
       <c r="F123" s="5"/>
       <c r="G123" s="5"/>
       <c r="H123" s="1" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="I123" s="5" t="s">
         <v>176</v>
@@ -61723,7 +61744,7 @@
       <c r="K123" s="5"/>
       <c r="L123" s="5"/>
       <c r="M123" s="4" t="s">
-        <v>921</v>
+        <v>920</v>
       </c>
     </row>
     <row r="124" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -61733,10 +61754,10 @@
       </c>
       <c r="B124" s="1"/>
       <c r="C124" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="E124" s="1"/>
       <c r="F124" s="1"/>
@@ -61748,25 +61769,25 @@
       <c r="L124" s="1"/>
       <c r="M124" s="1"/>
     </row>
-    <row r="125" spans="1:13" ht="330" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" ht="330" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="str">
         <f>IF(receta!A125="","",receta!A125)</f>
         <v>Sangría</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>650</v>
+        <v>649</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>649</v>
+        <v>648</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="G125" s="5"/>
       <c r="H125" s="1"/>
@@ -61783,7 +61804,7 @@
       </c>
       <c r="B126" s="1"/>
       <c r="C126" s="4" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D126" s="1"/>
       <c r="E126" s="1"/>
@@ -61796,21 +61817,21 @@
       <c r="L126" s="1"/>
       <c r="M126" s="1"/>
     </row>
-    <row r="127" spans="1:13" ht="165" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" ht="165" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="str">
         <f>IF(receta!A127="","",receta!A127)</f>
         <v>Sea Breeze</v>
       </c>
       <c r="B127" s="1"/>
       <c r="C127" s="4" t="s">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D127" s="1"/>
       <c r="E127" s="1" t="s">
-        <v>555</v>
+        <v>554</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="G127" s="1"/>
       <c r="H127" s="1"/>
@@ -61839,7 +61860,7 @@
       <c r="K128" s="1"/>
       <c r="L128" s="1"/>
       <c r="M128" s="4" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="129" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -61849,10 +61870,10 @@
       </c>
       <c r="B129" s="1"/>
       <c r="C129" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="E129" s="1"/>
       <c r="F129" s="1"/>
@@ -61863,7 +61884,7 @@
       <c r="K129" s="1"/>
       <c r="L129" s="1"/>
       <c r="M129" s="4" t="s">
-        <v>908</v>
+        <v>907</v>
       </c>
     </row>
     <row r="130" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -61873,7 +61894,7 @@
       </c>
       <c r="B130" s="1"/>
       <c r="C130" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D130" s="1"/>
       <c r="E130" s="1"/>
@@ -61893,7 +61914,7 @@
       </c>
       <c r="B131" s="1"/>
       <c r="C131" s="4" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="D131" s="4"/>
       <c r="E131" s="1"/>
@@ -61905,17 +61926,17 @@
       <c r="K131" s="1"/>
       <c r="L131" s="1"/>
       <c r="M131" s="4" t="s">
-        <v>1072</v>
-      </c>
-    </row>
-    <row r="132" spans="1:13" ht="165" x14ac:dyDescent="0.25">
+        <v>1071</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" ht="165" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="str">
         <f>IF(receta!A132="","",receta!A132)</f>
         <v>Síndrome Impostor</v>
       </c>
       <c r="B132" s="1"/>
       <c r="C132" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D132" s="1"/>
       <c r="E132" s="1" t="s">
@@ -61931,7 +61952,7 @@
       <c r="K132" s="5"/>
       <c r="L132" s="5"/>
       <c r="M132" s="4" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.25">
@@ -61954,36 +61975,36 @@
       <c r="L133" s="1"/>
       <c r="M133" s="1"/>
     </row>
-    <row r="134" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="str">
         <f>IF(receta!A134="","",receta!A134)</f>
         <v>Tequila Sunrise</v>
       </c>
       <c r="B134" s="1"/>
       <c r="C134" s="4" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="G134" s="5"/>
       <c r="H134" s="4"/>
       <c r="I134" s="5"/>
       <c r="J134" s="4" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="K134" s="5" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="L134" s="5"/>
       <c r="M134" s="4" t="s">
-        <v>936</v>
+        <v>935</v>
       </c>
     </row>
     <row r="135" spans="1:13" ht="300" x14ac:dyDescent="0.25">
@@ -61992,40 +62013,40 @@
         <v>Terremoto</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>948</v>
+        <v>947</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="E135" s="1"/>
       <c r="F135" s="1"/>
       <c r="G135" s="1"/>
       <c r="H135" s="1" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="I135" s="5" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="J135" s="1"/>
       <c r="K135" s="1"/>
       <c r="L135" s="1"/>
       <c r="M135" s="4" t="s">
-        <v>947</v>
-      </c>
-    </row>
-    <row r="136" spans="1:13" ht="180" x14ac:dyDescent="0.25">
+        <v>946</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" ht="180" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="str">
         <f>IF(receta!A136="","",receta!A136)</f>
         <v>Terremoto (Sin Alcohol)</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>653</v>
+        <v>652</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>652</v>
+        <v>651</v>
       </c>
       <c r="D136" s="4"/>
       <c r="E136" s="1" t="s">
@@ -62042,7 +62063,7 @@
       <c r="L136" s="5"/>
       <c r="M136" s="1"/>
     </row>
-    <row r="137" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="str">
         <f>IF(receta!A137="","",receta!A137)</f>
         <v>Tinto de Verano</v>
@@ -62050,16 +62071,16 @@
       <c r="B137" s="13"/>
       <c r="C137" s="1"/>
       <c r="D137" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E137" s="1" t="s">
+        <v>1031</v>
+      </c>
+      <c r="F137" s="5" t="s">
+        <v>1030</v>
+      </c>
+      <c r="G137" s="4" t="s">
         <v>1032</v>
-      </c>
-      <c r="F137" s="5" t="s">
-        <v>1031</v>
-      </c>
-      <c r="G137" s="4" t="s">
-        <v>1033</v>
       </c>
       <c r="H137" s="1"/>
       <c r="I137" s="1"/>
@@ -62075,7 +62096,7 @@
       </c>
       <c r="B138" s="4"/>
       <c r="C138" s="4" t="s">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="D138" s="1"/>
       <c r="E138" s="1"/>
@@ -62087,7 +62108,7 @@
       <c r="K138" s="1"/>
       <c r="L138" s="1"/>
       <c r="M138" s="4" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
     </row>
     <row r="139" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -62097,78 +62118,78 @@
       </c>
       <c r="B139" s="1"/>
       <c r="C139" s="4" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="D139" s="4"/>
       <c r="E139" s="1"/>
       <c r="F139" s="1"/>
       <c r="G139" s="1"/>
       <c r="H139" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="I139" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="J139" s="1"/>
       <c r="K139" s="1"/>
       <c r="L139" s="1"/>
       <c r="M139" s="1"/>
     </row>
-    <row r="140" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="str">
         <f>IF(receta!A140="","",receta!A140)</f>
         <v>Tropezón</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>703</v>
+        <v>702</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="E140" s="1" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F140" s="5" t="s">
+        <v>1016</v>
+      </c>
+      <c r="G140" s="4" t="s">
         <v>1018</v>
-      </c>
-      <c r="F140" s="5" t="s">
-        <v>1017</v>
-      </c>
-      <c r="G140" s="4" t="s">
-        <v>1019</v>
       </c>
       <c r="H140" s="1"/>
       <c r="I140" s="1"/>
       <c r="J140" s="1" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="K140" s="5" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="L140" s="5"/>
       <c r="M140" s="4" t="s">
-        <v>1007</v>
-      </c>
-    </row>
-    <row r="141" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="str">
         <f>IF(receta!A141="","",receta!A141)</f>
         <v>Vaina</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="E141" s="4" t="s">
+        <v>609</v>
+      </c>
+      <c r="F141" s="4" t="s">
         <v>610</v>
-      </c>
-      <c r="F141" s="4" t="s">
-        <v>611</v>
       </c>
       <c r="G141" s="4"/>
       <c r="H141" s="1"/>
@@ -62178,14 +62199,14 @@
       <c r="L141" s="4"/>
       <c r="M141" s="1"/>
     </row>
-    <row r="142" spans="1:13" ht="60" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="str">
         <f>IF(receta!A142="","",receta!A142)</f>
         <v>Valentín</v>
       </c>
       <c r="B142" s="1"/>
       <c r="C142" s="4" t="s">
-        <v>654</v>
+        <v>653</v>
       </c>
       <c r="D142" s="4"/>
       <c r="E142" s="4" t="s">
@@ -62202,25 +62223,25 @@
       <c r="L142" s="5"/>
       <c r="M142" s="1"/>
     </row>
-    <row r="143" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="str">
         <f>IF(receta!A143="","",receta!A143)</f>
         <v>Vampiro</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>655</v>
+        <v>654</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="E143" s="1" t="s">
+        <v>537</v>
+      </c>
+      <c r="F143" s="1" t="s">
         <v>538</v>
-      </c>
-      <c r="F143" s="1" t="s">
-        <v>539</v>
       </c>
       <c r="G143" s="1"/>
       <c r="H143" s="1"/>
@@ -62229,20 +62250,20 @@
       <c r="K143" s="1"/>
       <c r="L143" s="1"/>
       <c r="M143" s="4" t="s">
-        <v>933</v>
-      </c>
-    </row>
-    <row r="144" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="str">
         <f>IF(receta!A144="","",receta!A144)</f>
         <v>Venganza</v>
       </c>
       <c r="B144" s="1"/>
       <c r="C144" s="1" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>311</v>
@@ -62252,41 +62273,41 @@
       </c>
       <c r="G144" s="1"/>
       <c r="H144" s="1" t="s">
+        <v>1022</v>
+      </c>
+      <c r="I144" s="5" t="s">
         <v>1023</v>
       </c>
-      <c r="I144" s="5" t="s">
-        <v>1024</v>
-      </c>
       <c r="J144" s="1" t="s">
+        <v>1020</v>
+      </c>
+      <c r="K144" s="5" t="s">
         <v>1021</v>
-      </c>
-      <c r="K144" s="5" t="s">
-        <v>1022</v>
       </c>
       <c r="L144" s="1"/>
       <c r="M144" s="4" t="s">
-        <v>918</v>
-      </c>
-    </row>
-    <row r="145" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="str">
         <f>IF(receta!A145="","",receta!A145)</f>
         <v>Vermouth con Soda</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="G145" s="1"/>
       <c r="H145" s="1"/>
@@ -62295,7 +62316,7 @@
       <c r="K145" s="1"/>
       <c r="L145" s="1"/>
       <c r="M145" s="4" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="146" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -62305,7 +62326,7 @@
       </c>
       <c r="B146" s="1"/>
       <c r="C146" s="4" t="s">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="D146" s="1"/>
       <c r="E146" s="1"/>
@@ -62318,21 +62339,21 @@
       <c r="L146" s="1"/>
       <c r="M146" s="1"/>
     </row>
-    <row r="147" spans="1:13" ht="240" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:13" ht="240" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="str">
         <f>IF(receta!A147="","",receta!A147)</f>
         <v>Vodka Cranberry</v>
       </c>
       <c r="B147" s="1"/>
       <c r="C147" s="4" t="s">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="D147" s="4"/>
       <c r="E147" s="1" t="s">
+        <v>710</v>
+      </c>
+      <c r="F147" s="5" t="s">
         <v>711</v>
-      </c>
-      <c r="F147" s="5" t="s">
-        <v>712</v>
       </c>
       <c r="G147" s="5"/>
       <c r="H147" s="1"/>
@@ -62341,24 +62362,24 @@
       <c r="K147" s="5"/>
       <c r="L147" s="5"/>
       <c r="M147" s="4" t="s">
-        <v>940</v>
-      </c>
-    </row>
-    <row r="148" spans="1:13" ht="225" x14ac:dyDescent="0.25">
+        <v>939</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13" ht="225" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="str">
         <f>IF(receta!A148="","",receta!A148)</f>
         <v>Whiscola</v>
       </c>
       <c r="B148" s="1"/>
       <c r="C148" s="4" t="s">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D148" s="1"/>
       <c r="E148" s="1" t="s">
-        <v>687</v>
+        <v>686</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>686</v>
+        <v>685</v>
       </c>
       <c r="G148" s="5"/>
       <c r="H148" s="1"/>
@@ -62367,26 +62388,26 @@
       <c r="K148" s="5"/>
       <c r="L148" s="5"/>
       <c r="M148" s="4" t="s">
-        <v>1083</v>
-      </c>
-    </row>
-    <row r="149" spans="1:13" ht="324" customHeight="1" x14ac:dyDescent="0.25">
+        <v>1082</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" ht="324" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="str">
         <f>IF(receta!A149="","",receta!A149)</f>
         <v>Whiskey Highball</v>
       </c>
       <c r="B149" s="1"/>
       <c r="C149" s="4" t="s">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="E149" s="1" t="s">
+        <v>704</v>
+      </c>
+      <c r="F149" s="5" t="s">
         <v>705</v>
-      </c>
-      <c r="F149" s="5" t="s">
-        <v>706</v>
       </c>
       <c r="G149" s="5"/>
       <c r="H149" s="1"/>
@@ -62395,28 +62416,28 @@
       <c r="K149" s="5"/>
       <c r="L149" s="5"/>
       <c r="M149" s="4" t="s">
-        <v>1069</v>
-      </c>
-    </row>
-    <row r="150" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>1068</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="str">
         <f>IF(receta!A150="","",receta!A150)</f>
         <v>Whisky Sour</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="G150" s="1"/>
       <c r="H150" s="1"/>
@@ -62425,28 +62446,28 @@
       <c r="K150" s="1"/>
       <c r="L150" s="1"/>
       <c r="M150" s="4" t="s">
-        <v>909</v>
-      </c>
-    </row>
-    <row r="151" spans="1:13" ht="180" x14ac:dyDescent="0.25">
+        <v>908</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" ht="180" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="str">
         <f>IF(receta!A151="","",receta!A151)</f>
         <v>Bramble</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="D151" s="4" t="s">
+        <v>787</v>
+      </c>
+      <c r="E151" s="1" t="s">
+        <v>789</v>
+      </c>
+      <c r="F151" s="1" t="s">
         <v>788</v>
-      </c>
-      <c r="E151" s="1" t="s">
-        <v>790</v>
-      </c>
-      <c r="F151" s="1" t="s">
-        <v>789</v>
       </c>
       <c r="G151" s="1"/>
       <c r="H151" s="1"/>
@@ -62455,24 +62476,24 @@
       <c r="K151" s="1"/>
       <c r="L151" s="1"/>
       <c r="M151" s="4" t="s">
-        <v>1063</v>
-      </c>
-    </row>
-    <row r="152" spans="1:13" ht="180" x14ac:dyDescent="0.25">
+        <v>1062</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13" ht="180" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="str">
         <f>IF(receta!A152="","",receta!A152)</f>
         <v>Pantera Rosa</v>
       </c>
       <c r="B152" s="1"/>
       <c r="C152" s="4" t="s">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D152" s="4"/>
       <c r="E152" s="1" t="s">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>756</v>
+        <v>755</v>
       </c>
       <c r="G152" s="1"/>
       <c r="H152" s="1"/>
@@ -62481,28 +62502,28 @@
       <c r="K152" s="1"/>
       <c r="L152" s="1"/>
       <c r="M152" s="4" t="s">
-        <v>1012</v>
-      </c>
-    </row>
-    <row r="153" spans="1:13" ht="240" x14ac:dyDescent="0.25">
+        <v>1011</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" ht="240" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="str">
         <f>IF(receta!A153="","",receta!A153)</f>
         <v>Gin Basil Smash</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>794</v>
+        <v>793</v>
       </c>
       <c r="E153" s="4" t="s">
+        <v>791</v>
+      </c>
+      <c r="F153" s="1" t="s">
         <v>792</v>
-      </c>
-      <c r="F153" s="1" t="s">
-        <v>793</v>
       </c>
       <c r="G153" s="1"/>
       <c r="H153" s="1"/>
@@ -62512,35 +62533,35 @@
       <c r="L153" s="1"/>
       <c r="M153" s="1"/>
     </row>
-    <row r="154" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="str">
         <f>IF(receta!A154="","",receta!A154)</f>
         <v>Vodka Tonic</v>
       </c>
       <c r="B154" s="1"/>
       <c r="C154" s="4" t="s">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="D154" s="26" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="E154" s="1" t="s">
+        <v>780</v>
+      </c>
+      <c r="F154" s="5" t="s">
         <v>781</v>
-      </c>
-      <c r="F154" s="5" t="s">
-        <v>782</v>
       </c>
       <c r="G154" s="5"/>
       <c r="H154" s="1"/>
       <c r="I154" s="5"/>
       <c r="J154" s="1" t="s">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="K154" s="5" t="s">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="L154" s="26" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="M154" s="1"/>
     </row>
@@ -62550,13 +62571,13 @@
         <v>Medias de Seda</v>
       </c>
       <c r="B155" s="4" t="s">
+        <v>796</v>
+      </c>
+      <c r="C155" s="4" t="s">
         <v>797</v>
       </c>
-      <c r="C155" s="4" t="s">
-        <v>798</v>
-      </c>
       <c r="D155" s="4" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="E155" s="1"/>
       <c r="F155" s="1"/>
@@ -62567,26 +62588,26 @@
       <c r="K155" s="1"/>
       <c r="L155" s="1"/>
       <c r="M155" s="4" t="s">
-        <v>1062</v>
-      </c>
-    </row>
-    <row r="156" spans="1:13" ht="255" x14ac:dyDescent="0.25">
+        <v>1061</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" ht="255" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="str">
         <f>IF(receta!A156="","",receta!A156)</f>
         <v>Brandy Sour</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>800</v>
+        <v>799</v>
       </c>
       <c r="D156" s="4"/>
       <c r="E156" s="1" t="s">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="G156" s="5"/>
       <c r="H156" s="1"/>
@@ -62596,25 +62617,25 @@
       <c r="L156" s="1"/>
       <c r="M156" s="1"/>
     </row>
-    <row r="157" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="str">
         <f>IF(receta!A157="","",receta!A157)</f>
         <v>Juanito Rosado</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>805</v>
+        <v>804</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>804</v>
+        <v>803</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="G157" s="1"/>
       <c r="H157" s="1"/>
@@ -62624,23 +62645,23 @@
       <c r="L157" s="1"/>
       <c r="M157" s="4"/>
     </row>
-    <row r="158" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="str">
         <f>IF(receta!A158="","",receta!A158)</f>
         <v>Vino Navegado</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="D158" s="10"/>
       <c r="E158" s="1" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="G158" s="1"/>
       <c r="H158" s="1"/>
@@ -62649,65 +62670,65 @@
       <c r="K158" s="1"/>
       <c r="L158" s="1"/>
       <c r="M158" s="10" t="s">
-        <v>813</v>
-      </c>
-    </row>
-    <row r="159" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>812</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="str">
         <f>IF(receta!A159="","",receta!A159)</f>
         <v>Cola de Mono</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="G159" s="5"/>
       <c r="H159" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="I159" s="10" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="J159" s="1"/>
       <c r="K159" s="1"/>
       <c r="L159" s="1"/>
       <c r="M159" s="4" t="s">
-        <v>931</v>
-      </c>
-    </row>
-    <row r="160" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="str">
         <f>IF(receta!A160="","",receta!A160)</f>
         <v>Chichón</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="E160" s="1" t="s">
+        <v>1013</v>
+      </c>
+      <c r="F160" s="5" t="s">
         <v>1014</v>
       </c>
-      <c r="F160" s="5" t="s">
-        <v>1015</v>
-      </c>
       <c r="G160" s="4" t="s">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="H160" s="1"/>
       <c r="I160" s="5"/>
@@ -62715,7 +62736,7 @@
       <c r="K160" s="1"/>
       <c r="L160" s="1"/>
       <c r="M160" s="4" t="s">
-        <v>1020</v>
+        <v>1019</v>
       </c>
     </row>
     <row r="161" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -62724,10 +62745,10 @@
         <v>Ramos Fizz</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
       <c r="D161" s="4"/>
       <c r="E161" s="1"/>
@@ -62739,26 +62760,26 @@
       <c r="K161" s="1"/>
       <c r="L161" s="1"/>
       <c r="M161" s="4" t="s">
-        <v>1086</v>
-      </c>
-    </row>
-    <row r="162" spans="1:13" ht="195" x14ac:dyDescent="0.25">
+        <v>1085</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" ht="195" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="str">
         <f>IF(receta!A162="","",receta!A162)</f>
         <v>Gin Fizz</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="D162" s="4"/>
       <c r="E162" s="1" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="G162" s="5"/>
       <c r="H162" s="5"/>
@@ -62768,23 +62789,23 @@
       <c r="L162" s="1"/>
       <c r="M162" s="1"/>
     </row>
-    <row r="163" spans="1:13" ht="255" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:13" ht="255" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="str">
         <f>IF(receta!A163="","",receta!A163)</f>
         <v>Carta Breve</v>
       </c>
       <c r="B163" s="1"/>
       <c r="C163" s="4" t="s">
+        <v>849</v>
+      </c>
+      <c r="D163" s="4" t="s">
+        <v>848</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>1083</v>
+      </c>
+      <c r="F163" s="5" t="s">
         <v>850</v>
-      </c>
-      <c r="D163" s="4" t="s">
-        <v>849</v>
-      </c>
-      <c r="E163" s="1" t="s">
-        <v>1084</v>
-      </c>
-      <c r="F163" s="5" t="s">
-        <v>851</v>
       </c>
       <c r="G163" s="5"/>
       <c r="H163" s="1"/>
@@ -62793,63 +62814,63 @@
       <c r="K163" s="1"/>
       <c r="L163" s="1"/>
       <c r="M163" s="4" t="s">
-        <v>970</v>
-      </c>
-    </row>
-    <row r="164" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="str">
         <f>IF(receta!A164="","",receta!A164)</f>
         <v>Orgasmo</v>
       </c>
       <c r="B164" s="4"/>
       <c r="C164" s="4" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="G164" s="5"/>
       <c r="H164" s="1"/>
       <c r="I164" s="5"/>
       <c r="J164" s="1" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="K164" s="1" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="L164" s="1"/>
       <c r="M164" s="4" t="s">
-        <v>856</v>
-      </c>
-    </row>
-    <row r="165" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>855</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="str">
         <f>IF(receta!A165="","",receta!A165)</f>
         <v>Pihuelo</v>
       </c>
       <c r="B165" s="4" t="s">
+        <v>864</v>
+      </c>
+      <c r="C165" s="4" t="s">
         <v>865</v>
       </c>
-      <c r="C165" s="4" t="s">
-        <v>866</v>
-      </c>
       <c r="D165" s="4" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="E165" s="4" t="s">
+        <v>1024</v>
+      </c>
+      <c r="F165" s="5" t="s">
         <v>1025</v>
       </c>
-      <c r="F165" s="5" t="s">
+      <c r="G165" s="1" t="s">
         <v>1026</v>
-      </c>
-      <c r="G165" s="1" t="s">
-        <v>1027</v>
       </c>
       <c r="H165" s="1"/>
       <c r="I165" s="5"/>
@@ -62857,28 +62878,28 @@
       <c r="K165" s="1"/>
       <c r="L165" s="1"/>
       <c r="M165" s="4" t="s">
-        <v>984</v>
-      </c>
-    </row>
-    <row r="166" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+        <v>983</v>
+      </c>
+    </row>
+    <row r="166" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="str">
         <f>IF(receta!A166="","",receta!A166)</f>
         <v>Mojito Sandía</v>
       </c>
       <c r="B166" s="4" t="s">
+        <v>876</v>
+      </c>
+      <c r="C166" s="4" t="s">
         <v>877</v>
       </c>
-      <c r="C166" s="4" t="s">
-        <v>878</v>
-      </c>
       <c r="D166" s="4" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="E166" s="1" t="s">
+        <v>874</v>
+      </c>
+      <c r="F166" s="5" t="s">
         <v>875</v>
-      </c>
-      <c r="F166" s="5" t="s">
-        <v>876</v>
       </c>
       <c r="G166" s="5"/>
       <c r="H166" s="1"/>
@@ -62887,7 +62908,7 @@
       <c r="K166" s="1"/>
       <c r="L166" s="1"/>
       <c r="M166" s="4" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
     </row>
     <row r="167" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62897,7 +62918,7 @@
       </c>
       <c r="B167" s="1"/>
       <c r="C167" s="4" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="D167" s="4"/>
       <c r="E167" s="1"/>
@@ -62909,7 +62930,7 @@
       <c r="K167" s="1"/>
       <c r="L167" s="1"/>
       <c r="M167" s="4" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="168" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -62919,7 +62940,7 @@
       </c>
       <c r="B168" s="1"/>
       <c r="C168" s="4" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="D168" s="4"/>
       <c r="E168" s="1"/>
@@ -62931,60 +62952,60 @@
       <c r="K168" s="1"/>
       <c r="L168" s="1"/>
       <c r="M168" s="4" t="s">
-        <v>1001</v>
-      </c>
-    </row>
-    <row r="169" spans="1:13" ht="120" x14ac:dyDescent="0.25">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="169" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="str">
         <f>IF(receta!A169="","",receta!A169)</f>
         <v>Chardonnay Sour</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="D169" s="4"/>
       <c r="E169" s="1" t="s">
+        <v>1105</v>
+      </c>
+      <c r="F169" s="5" t="s">
+        <v>1104</v>
+      </c>
+      <c r="G169" s="4" t="s">
         <v>1106</v>
-      </c>
-      <c r="F169" s="5" t="s">
-        <v>1105</v>
-      </c>
-      <c r="G169" s="4" t="s">
-        <v>1107</v>
       </c>
       <c r="H169" s="1"/>
       <c r="I169" s="5"/>
       <c r="J169" s="1" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="K169" s="5" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="L169" s="1"/>
       <c r="M169" s="1"/>
     </row>
-    <row r="170" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="str">
         <f>IF(receta!A170="","",receta!A170)</f>
         <v>Carmenere Sour</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>904</v>
+        <v>903</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="G170" s="1"/>
       <c r="H170" s="1"/>
@@ -62993,7 +63014,7 @@
       <c r="K170" s="1"/>
       <c r="L170" s="1"/>
       <c r="M170" s="4" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
     </row>
     <row r="171" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -63002,13 +63023,13 @@
         <v>Jerez Sour</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="E171" s="1"/>
       <c r="F171" s="1"/>
@@ -63019,7 +63040,7 @@
       <c r="K171" s="1"/>
       <c r="L171" s="1"/>
       <c r="M171" s="4" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
     </row>
     <row r="172" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -63029,7 +63050,7 @@
       </c>
       <c r="B172" s="4"/>
       <c r="C172" s="4" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="D172" s="4"/>
       <c r="E172" s="1"/>
@@ -63041,7 +63062,7 @@
       <c r="K172" s="1"/>
       <c r="L172" s="1"/>
       <c r="M172" s="4" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="173" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -63061,7 +63082,7 @@
       <c r="K173" s="1"/>
       <c r="L173" s="1"/>
       <c r="M173" s="4" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="174" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -63070,7 +63091,7 @@
         <v>Campari Spritz</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="C174" s="4"/>
       <c r="D174" s="4"/>
@@ -63083,7 +63104,7 @@
       <c r="K174" s="1"/>
       <c r="L174" s="1"/>
       <c r="M174" s="4" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="175" spans="1:13" x14ac:dyDescent="0.25">
@@ -64455,7 +64476,11 @@
       <c r="M250" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M250" xr:uid="{43DB3A21-6E97-43C0-9768-D0796C62C1D9}"/>
+  <autoFilter ref="A1:M250" xr:uid="{43DB3A21-6E97-43C0-9768-D0796C62C1D9}">
+    <filterColumn colId="5">
+      <filters blank="1"/>
+    </filterColumn>
+  </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="F63" r:id="rId1" xr:uid="{F4C5002B-4D4E-44DF-92F8-067F77645455}"/>
@@ -64552,9 +64577,11 @@
     <hyperlink ref="K90" r:id="rId92" xr:uid="{D8D0F5DC-7359-4E9F-950F-B003241F9665}"/>
     <hyperlink ref="F134" r:id="rId93" xr:uid="{D7523DD3-FE84-4AED-B41A-68B668DAABE6}"/>
     <hyperlink ref="K68" r:id="rId94" xr:uid="{3E73A1DB-0A1B-4D6D-9C5D-9C6C53A649F7}"/>
+    <hyperlink ref="K117" r:id="rId95" xr:uid="{16A48F14-FDEF-49B0-965F-21300919D816}"/>
+    <hyperlink ref="F79" r:id="rId96" xr:uid="{FE069020-1D93-4689-B554-F77D35BE7D23}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId95"/>
+  <pageSetup orientation="portrait" r:id="rId97"/>
 </worksheet>
 </file>
 
@@ -64583,10 +64610,10 @@
         <v>62</v>
       </c>
       <c r="B2" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C2" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -64594,7 +64621,7 @@
         <v>67</v>
       </c>
       <c r="B3" t="s">
-        <v>773</v>
+        <v>772</v>
       </c>
       <c r="C3" t="s">
         <v>202</v>
@@ -64605,10 +64632,10 @@
         <v>68</v>
       </c>
       <c r="B4" t="s">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="C4" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -64616,7 +64643,7 @@
         <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C5" t="s">
         <v>203</v>
@@ -64627,10 +64654,10 @@
         <v>69</v>
       </c>
       <c r="B6" t="s">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="C6" t="s">
-        <v>779</v>
+        <v>778</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -64638,7 +64665,7 @@
         <v>70</v>
       </c>
       <c r="B7" t="s">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="C7" t="s">
         <v>71</v>
@@ -64646,24 +64673,24 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>730</v>
+        <v>729</v>
       </c>
       <c r="B8" t="s">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="C8" t="s">
-        <v>778</v>
+        <v>777</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>805</v>
+      </c>
+      <c r="B9" t="s">
         <v>806</v>
       </c>
-      <c r="B9" t="s">
+      <c r="C9" t="s">
         <v>807</v>
-      </c>
-      <c r="C9" t="s">
-        <v>808</v>
       </c>
     </row>
   </sheetData>
@@ -64693,7 +64720,7 @@
         <v>115</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -64701,7 +64728,7 @@
         <v>116</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -64709,7 +64736,7 @@
         <v>117</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -64717,7 +64744,7 @@
         <v>118</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -64725,7 +64752,7 @@
         <v>119</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -64733,7 +64760,7 @@
         <v>120</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -64741,31 +64768,31 @@
         <v>215</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>766</v>
+        <v>765</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="23" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="23" t="s">
+        <v>699</v>
+      </c>
+      <c r="B11" s="23" t="s">
         <v>700</v>
-      </c>
-      <c r="B11" s="23" t="s">
-        <v>701</v>
       </c>
     </row>
   </sheetData>

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24E1957C-FE50-47A3-BDE0-B1CE24B7F684}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A5F085D-0B55-46E9-9736-88FCE2E79D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
@@ -22,7 +22,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">complementos!$A$1:$AE$250</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">receta!$A$1:$EW$174</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">recurso!$A$1:$M$250</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">recurso!$A$1:$M$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1687" uniqueCount="1129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1689" uniqueCount="1131">
   <si>
     <t>Ramazzotti Spritz</t>
   </si>
@@ -5197,6 +5197,12 @@
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=eJk8N4mSlQw</t>
+  </si>
+  <si>
+    <t>Víctor Jara - Ni chicha ni limoná</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=Iaore8_sjJY</t>
   </si>
 </sst>
 </file>
@@ -58435,7 +58441,6 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{43DB3A21-6E97-43C0-9768-D0796C62C1D9}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:M250"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -58495,7 +58500,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="2" spans="1:13" ht="270" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" ht="270" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="str">
         <f>IF(receta!A2="","",receta!A2)</f>
         <v>Agua de Valencia</v>
@@ -58547,7 +58552,7 @@
       <c r="L3" s="1"/>
       <c r="M3" s="1"/>
     </row>
-    <row r="4" spans="1:13" ht="180" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:13" ht="180" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="str">
         <f>IF(receta!A4="","",receta!A4)</f>
         <v>Alevosía</v>
@@ -58575,7 +58580,7 @@
       <c r="L4" s="5"/>
       <c r="M4" s="1"/>
     </row>
-    <row r="5" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="str">
         <f>IF(receta!A5="","",receta!A5)</f>
         <v>Alexander</v>
@@ -58605,7 +58610,7 @@
         <v>912</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="270" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:13" ht="270" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="str">
         <f>IF(receta!A6="","",receta!A6)</f>
         <v>Amaretto Sour</v>
@@ -58633,7 +58638,7 @@
         <v>949</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="270" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:13" ht="270" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="str">
         <f>IF(receta!A7="","",receta!A7)</f>
         <v>Amaretto Spritz</v>
@@ -58661,7 +58666,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="210" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:13" ht="210" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="str">
         <f>IF(receta!A8="","",receta!A8)</f>
         <v>Americano</v>
@@ -58687,7 +58692,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="9" spans="1:13" ht="105" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:13" ht="105" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="str">
         <f>IF(receta!A9="","",receta!A9)</f>
         <v>Amiga Mía</v>
@@ -58787,7 +58792,7 @@
       <c r="L12" s="1"/>
       <c r="M12" s="1"/>
     </row>
-    <row r="13" spans="1:13" ht="210" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:13" ht="195" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="str">
         <f>IF(receta!A13="","",receta!A13)</f>
         <v>Bellini</v>
@@ -58863,7 +58868,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="str">
         <f>IF(receta!A16="","",receta!A16)</f>
         <v>Blanco de Verano</v>
@@ -58887,7 +58892,7 @@
       <c r="L16" s="1"/>
       <c r="M16" s="1"/>
     </row>
-    <row r="17" spans="1:13" ht="390" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:13" ht="390" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="str">
         <f>IF(receta!A17="","",receta!A17)</f>
         <v>Bloody Mary</v>
@@ -58917,7 +58922,7 @@
       <c r="L17" s="10"/>
       <c r="M17" s="1"/>
     </row>
-    <row r="18" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="str">
         <f>IF(receta!A18="","",receta!A18)</f>
         <v>Bloody Mary (Sin Alcohol)</v>
@@ -58941,7 +58946,7 @@
       <c r="L18" s="5"/>
       <c r="M18" s="1"/>
     </row>
-    <row r="19" spans="1:13" ht="180" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:13" ht="180" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="str">
         <f>IF(receta!A19="","",receta!A19)</f>
         <v>Blue Hawaii</v>
@@ -58967,7 +58972,7 @@
         <v>968</v>
       </c>
     </row>
-    <row r="20" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="str">
         <f>IF(receta!A20="","",receta!A20)</f>
         <v>Blue Hawaiian</v>
@@ -59019,7 +59024,7 @@
         <v>915</v>
       </c>
     </row>
-    <row r="22" spans="1:13" ht="375" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:13" ht="375" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="str">
         <f>IF(receta!A22="","",receta!A22)</f>
         <v>Caipiriña</v>
@@ -59069,7 +59074,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:13" ht="345" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="str">
         <f>IF(receta!A24="","",receta!A24)</f>
         <v>Carajillo</v>
@@ -59145,7 +59150,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="375" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:13" ht="375" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="str">
         <f>IF(receta!A27="","",receta!A27)</f>
         <v>Chupilca</v>
@@ -59179,7 +59184,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="str">
         <f>IF(receta!A28="","",receta!A28)</f>
         <v>Cimarrón</v>
@@ -59211,7 +59216,7 @@
         <v>916</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="360" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:13" ht="360" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="str">
         <f>IF(receta!A29="","",receta!A29)</f>
         <v>Clavo Oxidado</v>
@@ -59237,7 +59242,7 @@
         <v>926</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="str">
         <f>IF(receta!A30="","",receta!A30)</f>
         <v>Cléry</v>
@@ -59269,7 +59274,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="str">
         <f>IF(receta!A31="","",receta!A31)</f>
         <v>Cléry Chirimoya</v>
@@ -59301,7 +59306,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="255" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" ht="255" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="str">
         <f>IF(receta!A32="","",receta!A32)</f>
         <v>Cléry Durazno</v>
@@ -59327,7 +59332,7 @@
       <c r="L32" s="5"/>
       <c r="M32" s="1"/>
     </row>
-    <row r="33" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="str">
         <f>IF(receta!A33="","",receta!A33)</f>
         <v>Clover Club</v>
@@ -59357,7 +59362,7 @@
         <v>878</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="255" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:13" ht="255" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="str">
         <f>IF(receta!A34="","",receta!A34)</f>
         <v>Cordillera</v>
@@ -59383,7 +59388,7 @@
         <v>973</v>
       </c>
     </row>
-    <row r="35" spans="1:13" ht="45" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:13" ht="45" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="str">
         <f>IF(receta!A35="","",receta!A35)</f>
         <v>Cosmo Patagonia</v>
@@ -59431,7 +59436,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="37" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="str">
         <f>IF(receta!A37="","",receta!A37)</f>
         <v>Crepúsculo</v>
@@ -59459,7 +59464,7 @@
         <v>937</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="255" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:13" ht="255" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="str">
         <f>IF(receta!A38="","",receta!A38)</f>
         <v>Cuba Libre</v>
@@ -59509,7 +59514,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="40" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="str">
         <f>IF(receta!A40="","",receta!A40)</f>
         <v>Daiquiri</v>
@@ -59563,7 +59568,7 @@
         <v>1054</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="str">
         <f>IF(receta!A42="","",receta!A42)</f>
         <v>Dark &amp; Stormy</v>
@@ -59663,7 +59668,7 @@
         <v>1040</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="285" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:13" ht="285" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="str">
         <f>IF(receta!A46="","",receta!A46)</f>
         <v>El Amor en los Tiempos del Covid</v>
@@ -59697,7 +59702,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="240" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:13" ht="240" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="str">
         <f>IF(receta!A47="","",receta!A47)</f>
         <v>Enemigo Íntimo</v>
@@ -59725,7 +59730,7 @@
         <v>933</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="315" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:13" ht="315" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="str">
         <f>IF(receta!A48="","",receta!A48)</f>
         <v>Escarabajo</v>
@@ -59751,7 +59756,7 @@
       <c r="L48" s="5"/>
       <c r="M48" s="1"/>
     </row>
-    <row r="49" spans="1:13" ht="270" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:13" ht="270" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="str">
         <f>IF(receta!A49="","",receta!A49)</f>
         <v>Española</v>
@@ -59781,7 +59786,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="50" spans="1:13" ht="255" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:13" ht="255" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="str">
         <f>IF(receta!A50="","",receta!A50)</f>
         <v>Espiral</v>
@@ -59813,7 +59818,7 @@
         <v>956</v>
       </c>
     </row>
-    <row r="51" spans="1:13" ht="105" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="str">
         <f>IF(receta!A51="","",receta!A51)</f>
         <v>Espresso Martini</v>
@@ -59835,7 +59840,7 @@
         <v>951</v>
       </c>
     </row>
-    <row r="52" spans="1:13" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:13" ht="150" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="str">
         <f>IF(receta!A52="","",receta!A52)</f>
         <v>Estoy Verde</v>
@@ -59867,7 +59872,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="53" spans="1:13" ht="390" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:13" ht="390" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="str">
         <f>IF(receta!A53="","",receta!A53)</f>
         <v>Fanshop</v>
@@ -59933,7 +59938,7 @@
         <v>910</v>
       </c>
     </row>
-    <row r="55" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="str">
         <f>IF(receta!A55="","",receta!A55)</f>
         <v>Feria Libre</v>
@@ -59957,7 +59962,7 @@
       <c r="L55" s="5"/>
       <c r="M55" s="1"/>
     </row>
-    <row r="56" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="str">
         <f>IF(receta!A56="","",receta!A56)</f>
         <v>Fernet con Coca</v>
@@ -59987,7 +59992,7 @@
         <v>952</v>
       </c>
     </row>
-    <row r="57" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="str">
         <f>IF(receta!A57="","",receta!A57)</f>
         <v>Ferroviario</v>
@@ -60015,7 +60020,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="58" spans="1:13" ht="150" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" ht="165" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="str">
         <f>IF(receta!A58="","",receta!A58)</f>
         <v>Frangelico Sour</v>
@@ -60039,7 +60044,7 @@
         <v>955</v>
       </c>
     </row>
-    <row r="59" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="str">
         <f>IF(receta!A59="","",receta!A59)</f>
         <v>French 75</v>
@@ -60097,7 +60102,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="61" spans="1:13" ht="165" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:13" ht="165" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="str">
         <f>IF(receta!A61="","",receta!A61)</f>
         <v>Gimlet</v>
@@ -60125,7 +60130,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="62" spans="1:13" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:13" ht="345" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="str">
         <f>IF(receta!A62="","",receta!A62)</f>
         <v>Gin con Gin</v>
@@ -60151,7 +60156,7 @@
         <v>986</v>
       </c>
     </row>
-    <row r="63" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="str">
         <f>IF(receta!A63="","",receta!A63)</f>
         <v>Gin Tonic</v>
@@ -60187,7 +60192,7 @@
         <v>925</v>
       </c>
     </row>
-    <row r="64" spans="1:13" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="str">
         <f>IF(receta!A64="","",receta!A64)</f>
         <v>Ginger Fire</v>
@@ -60263,7 +60268,7 @@
         <v>1052</v>
       </c>
     </row>
-    <row r="67" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="str">
         <f>IF(receta!A67="","",receta!A67)</f>
         <v>Incendio</v>
@@ -60289,7 +60294,7 @@
         <v>948</v>
       </c>
     </row>
-    <row r="68" spans="1:13" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:13" ht="330" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="str">
         <f>IF(receta!A68="","",receta!A68)</f>
         <v>Ingrata</v>
@@ -60323,7 +60328,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="69" spans="1:13" ht="300" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:13" ht="300" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="str">
         <f>IF(receta!A69="","",receta!A69)</f>
         <v>Isla Negra</v>
@@ -60351,7 +60356,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="70" spans="1:13" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:13" ht="195" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="str">
         <f>IF(receta!A70="","",receta!A70)</f>
         <v>Jardín</v>
@@ -60379,7 +60384,7 @@
         <v>938</v>
       </c>
     </row>
-    <row r="71" spans="1:13" ht="225" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:13" ht="225" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="str">
         <f>IF(receta!A71="","",receta!A71)</f>
         <v>John Collins</v>
@@ -60405,7 +60410,7 @@
         <v>929</v>
       </c>
     </row>
-    <row r="72" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="str">
         <f>IF(receta!A72="","",receta!A72)</f>
         <v>Jote</v>
@@ -60465,7 +60470,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="74" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="str">
         <f>IF(receta!A74="","",receta!A74)</f>
         <v>Julieta Flowers</v>
@@ -60519,7 +60524,7 @@
         <v>1053</v>
       </c>
     </row>
-    <row r="76" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="str">
         <f>IF(receta!A76="","",receta!A76)</f>
         <v>Kokomo</v>
@@ -60569,7 +60574,7 @@
         <v>1008</v>
       </c>
     </row>
-    <row r="78" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="str">
         <f>IF(receta!A78="","",receta!A78)</f>
         <v>London Mule</v>
@@ -60687,7 +60692,7 @@
         <v>1066</v>
       </c>
     </row>
-    <row r="83" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="str">
         <f>IF(receta!A83="","",receta!A83)</f>
         <v>Mala Reputación</v>
@@ -60795,7 +60800,7 @@
       <c r="L86" s="1"/>
       <c r="M86" s="1"/>
     </row>
-    <row r="87" spans="1:13" ht="165" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:13" ht="165" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="str">
         <f>IF(receta!A87="","",receta!A87)</f>
         <v>Manhattan</v>
@@ -60851,7 +60856,7 @@
         <v>1065</v>
       </c>
     </row>
-    <row r="89" spans="1:13" ht="180" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:13" ht="180" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="str">
         <f>IF(receta!A89="","",receta!A89)</f>
         <v>Margarita</v>
@@ -60881,7 +60886,7 @@
         <v>1070</v>
       </c>
     </row>
-    <row r="90" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="str">
         <f>IF(receta!A90="","",receta!A90)</f>
         <v>Margarita Maracuyá</v>
@@ -60907,7 +60912,7 @@
       <c r="L90" s="5"/>
       <c r="M90" s="1"/>
     </row>
-    <row r="91" spans="1:13" ht="225" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:13" ht="225" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="str">
         <f>IF(receta!A91="","",receta!A91)</f>
         <v>Melón con Vino</v>
@@ -60933,7 +60938,7 @@
       <c r="L91" s="5"/>
       <c r="M91" s="1"/>
     </row>
-    <row r="92" spans="1:13" ht="375" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:13" ht="375" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="str">
         <f>IF(receta!A92="","",receta!A92)</f>
         <v>Michelada</v>
@@ -60965,7 +60970,7 @@
       <c r="L92" s="5"/>
       <c r="M92" s="1"/>
     </row>
-    <row r="93" spans="1:13" ht="180" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" ht="165" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="str">
         <f>IF(receta!A93="","",receta!A93)</f>
         <v>Milano Torino</v>
@@ -60987,7 +60992,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="94" spans="1:13" ht="225" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" ht="210" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="str">
         <f>IF(receta!A94="","",receta!A94)</f>
         <v>Mimosa</v>
@@ -61053,7 +61058,7 @@
       <c r="L96" s="1"/>
       <c r="M96" s="1"/>
     </row>
-    <row r="97" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="str">
         <f>IF(receta!A97="","",receta!A97)</f>
         <v>Mojito Maracuyá</v>
@@ -61103,7 +61108,7 @@
       <c r="L98" s="1"/>
       <c r="M98" s="1"/>
     </row>
-    <row r="99" spans="1:13" ht="375" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:13" ht="375" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="str">
         <f>IF(receta!A99="","",receta!A99)</f>
         <v>Moscow Mule</v>
@@ -61129,7 +61134,7 @@
         <v>924</v>
       </c>
     </row>
-    <row r="100" spans="1:13" ht="150" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:13" ht="150" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="str">
         <f>IF(receta!A100="","",receta!A100)</f>
         <v>Naranja Sour</v>
@@ -61227,7 +61232,7 @@
         <v>1036</v>
       </c>
     </row>
-    <row r="104" spans="1:13" ht="345" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:13" ht="345" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="str">
         <f>IF(receta!A104="","",receta!A104)</f>
         <v>New York Sour</v>
@@ -61257,7 +61262,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="105" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="str">
         <f>IF(receta!A105="","",receta!A105)</f>
         <v>No Me Falles</v>
@@ -61283,7 +61288,7 @@
         <v>940</v>
       </c>
     </row>
-    <row r="106" spans="1:13" ht="375" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:13" ht="375" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="str">
         <f>IF(receta!A106="","",receta!A106)</f>
         <v>Old Fashioned</v>
@@ -61385,7 +61390,7 @@
       <c r="L109" s="1"/>
       <c r="M109" s="1"/>
     </row>
-    <row r="110" spans="1:13" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:13" ht="330" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="str">
         <f>IF(receta!A110="","",receta!A110)</f>
         <v>Penicilina</v>
@@ -61415,7 +61420,7 @@
         <v>1002</v>
       </c>
     </row>
-    <row r="111" spans="1:13" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="str">
         <f>IF(receta!A111="","",receta!A111)</f>
         <v>Phil Collins</v>
@@ -61439,7 +61444,7 @@
       <c r="L111" s="5"/>
       <c r="M111" s="1"/>
     </row>
-    <row r="112" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="str">
         <f>IF(receta!A112="","",receta!A112)</f>
         <v>Pichuncho</v>
@@ -61465,7 +61470,7 @@
       <c r="L112" s="5"/>
       <c r="M112" s="1"/>
     </row>
-    <row r="113" spans="1:13" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:13" ht="195" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="str">
         <f>IF(receta!A113="","",receta!A113)</f>
         <v>Piña Colada</v>
@@ -61531,7 +61536,7 @@
       <c r="L115" s="1"/>
       <c r="M115" s="1"/>
     </row>
-    <row r="116" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="str">
         <f>IF(receta!A116="","",receta!A116)</f>
         <v>Pisco Sour</v>
@@ -61557,7 +61562,7 @@
       <c r="L116" s="5"/>
       <c r="M116" s="1"/>
     </row>
-    <row r="117" spans="1:13" ht="210" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:13" ht="210" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="str">
         <f>IF(receta!A117="","",receta!A117)</f>
         <v>Piscola</v>
@@ -61589,7 +61594,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="118" spans="1:13" ht="90" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="str">
         <f>IF(receta!A118="","",receta!A118)</f>
         <v>Pistón</v>
@@ -61643,7 +61648,7 @@
         <v>1005</v>
       </c>
     </row>
-    <row r="120" spans="1:13" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="str">
         <f>IF(receta!A120="","",receta!A120)</f>
         <v>Ramazzotti Spritz</v>
@@ -61669,7 +61674,7 @@
       <c r="L120" s="5"/>
       <c r="M120" s="1"/>
     </row>
-    <row r="121" spans="1:13" ht="135" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:13" ht="135" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="str">
         <f>IF(receta!A121="","",receta!A121)</f>
         <v>Ramazzotti Violetto Spritz</v>
@@ -61695,7 +61700,7 @@
       <c r="L121" s="1"/>
       <c r="M121" s="1"/>
     </row>
-    <row r="122" spans="1:13" ht="30" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:13" ht="30" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="str">
         <f>IF(receta!A122="","",receta!A122)</f>
         <v>Ron Cola</v>
@@ -61769,7 +61774,7 @@
       <c r="L124" s="1"/>
       <c r="M124" s="1"/>
     </row>
-    <row r="125" spans="1:13" ht="330" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:13" ht="330" x14ac:dyDescent="0.25">
       <c r="A125" s="1" t="str">
         <f>IF(receta!A125="","",receta!A125)</f>
         <v>Sangría</v>
@@ -61817,7 +61822,7 @@
       <c r="L126" s="1"/>
       <c r="M126" s="1"/>
     </row>
-    <row r="127" spans="1:13" ht="165" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:13" ht="165" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="str">
         <f>IF(receta!A127="","",receta!A127)</f>
         <v>Sea Breeze</v>
@@ -61929,7 +61934,7 @@
         <v>1071</v>
       </c>
     </row>
-    <row r="132" spans="1:13" ht="165" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:13" ht="165" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="str">
         <f>IF(receta!A132="","",receta!A132)</f>
         <v>Síndrome Impostor</v>
@@ -61975,7 +61980,7 @@
       <c r="L133" s="1"/>
       <c r="M133" s="1"/>
     </row>
-    <row r="134" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="str">
         <f>IF(receta!A134="","",receta!A134)</f>
         <v>Tequila Sunrise</v>
@@ -62037,7 +62042,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="136" spans="1:13" ht="180" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:13" ht="180" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="str">
         <f>IF(receta!A136="","",receta!A136)</f>
         <v>Terremoto (Sin Alcohol)</v>
@@ -62063,7 +62068,7 @@
       <c r="L136" s="5"/>
       <c r="M136" s="1"/>
     </row>
-    <row r="137" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A137" s="1" t="str">
         <f>IF(receta!A137="","",receta!A137)</f>
         <v>Tinto de Verano</v>
@@ -62135,7 +62140,7 @@
       <c r="L139" s="1"/>
       <c r="M139" s="1"/>
     </row>
-    <row r="140" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="str">
         <f>IF(receta!A140="","",receta!A140)</f>
         <v>Tropezón</v>
@@ -62171,7 +62176,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="141" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="str">
         <f>IF(receta!A141="","",receta!A141)</f>
         <v>Vaina</v>
@@ -62199,7 +62204,7 @@
       <c r="L141" s="4"/>
       <c r="M141" s="1"/>
     </row>
-    <row r="142" spans="1:13" ht="60" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:13" ht="60" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="str">
         <f>IF(receta!A142="","",receta!A142)</f>
         <v>Valentín</v>
@@ -62223,7 +62228,7 @@
       <c r="L142" s="5"/>
       <c r="M142" s="1"/>
     </row>
-    <row r="143" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="str">
         <f>IF(receta!A143="","",receta!A143)</f>
         <v>Vampiro</v>
@@ -62253,7 +62258,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="144" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="str">
         <f>IF(receta!A144="","",receta!A144)</f>
         <v>Venganza</v>
@@ -62289,7 +62294,7 @@
         <v>917</v>
       </c>
     </row>
-    <row r="145" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="str">
         <f>IF(receta!A145="","",receta!A145)</f>
         <v>Vermouth con Soda</v>
@@ -62339,7 +62344,7 @@
       <c r="L146" s="1"/>
       <c r="M146" s="1"/>
     </row>
-    <row r="147" spans="1:13" ht="240" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:13" ht="240" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="str">
         <f>IF(receta!A147="","",receta!A147)</f>
         <v>Vodka Cranberry</v>
@@ -62365,7 +62370,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="148" spans="1:13" ht="225" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:13" ht="225" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="str">
         <f>IF(receta!A148="","",receta!A148)</f>
         <v>Whiscola</v>
@@ -62391,7 +62396,7 @@
         <v>1082</v>
       </c>
     </row>
-    <row r="149" spans="1:13" ht="324" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:13" ht="324" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="str">
         <f>IF(receta!A149="","",receta!A149)</f>
         <v>Whiskey Highball</v>
@@ -62419,7 +62424,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="150" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="str">
         <f>IF(receta!A150="","",receta!A150)</f>
         <v>Whisky Sour</v>
@@ -62449,7 +62454,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="151" spans="1:13" ht="180" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:13" ht="180" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="str">
         <f>IF(receta!A151="","",receta!A151)</f>
         <v>Bramble</v>
@@ -62479,7 +62484,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="152" spans="1:13" ht="180" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:13" ht="180" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="str">
         <f>IF(receta!A152="","",receta!A152)</f>
         <v>Pantera Rosa</v>
@@ -62505,7 +62510,7 @@
         <v>1011</v>
       </c>
     </row>
-    <row r="153" spans="1:13" ht="240" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:13" ht="240" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="str">
         <f>IF(receta!A153="","",receta!A153)</f>
         <v>Gin Basil Smash</v>
@@ -62533,7 +62538,7 @@
       <c r="L153" s="1"/>
       <c r="M153" s="1"/>
     </row>
-    <row r="154" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="str">
         <f>IF(receta!A154="","",receta!A154)</f>
         <v>Vodka Tonic</v>
@@ -62591,7 +62596,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="156" spans="1:13" ht="255" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:13" ht="255" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="str">
         <f>IF(receta!A156="","",receta!A156)</f>
         <v>Brandy Sour</v>
@@ -62617,7 +62622,7 @@
       <c r="L156" s="1"/>
       <c r="M156" s="1"/>
     </row>
-    <row r="157" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="str">
         <f>IF(receta!A157="","",receta!A157)</f>
         <v>Juanito Rosado</v>
@@ -62645,7 +62650,7 @@
       <c r="L157" s="1"/>
       <c r="M157" s="4"/>
     </row>
-    <row r="158" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="str">
         <f>IF(receta!A158="","",receta!A158)</f>
         <v>Vino Navegado</v>
@@ -62673,7 +62678,7 @@
         <v>812</v>
       </c>
     </row>
-    <row r="159" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="str">
         <f>IF(receta!A159="","",receta!A159)</f>
         <v>Cola de Mono</v>
@@ -62707,7 +62712,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="160" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="str">
         <f>IF(receta!A160="","",receta!A160)</f>
         <v>Chichón</v>
@@ -62732,8 +62737,12 @@
       </c>
       <c r="H160" s="1"/>
       <c r="I160" s="5"/>
-      <c r="J160" s="1"/>
-      <c r="K160" s="1"/>
+      <c r="J160" s="1" t="s">
+        <v>1129</v>
+      </c>
+      <c r="K160" s="5" t="s">
+        <v>1130</v>
+      </c>
       <c r="L160" s="1"/>
       <c r="M160" s="4" t="s">
         <v>1019</v>
@@ -62763,7 +62772,7 @@
         <v>1085</v>
       </c>
     </row>
-    <row r="162" spans="1:13" ht="195" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:13" ht="195" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="str">
         <f>IF(receta!A162="","",receta!A162)</f>
         <v>Gin Fizz</v>
@@ -62789,7 +62798,7 @@
       <c r="L162" s="1"/>
       <c r="M162" s="1"/>
     </row>
-    <row r="163" spans="1:13" ht="255" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:13" ht="255" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="str">
         <f>IF(receta!A163="","",receta!A163)</f>
         <v>Carta Breve</v>
@@ -62817,7 +62826,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="164" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="str">
         <f>IF(receta!A164="","",receta!A164)</f>
         <v>Orgasmo</v>
@@ -62849,7 +62858,7 @@
         <v>855</v>
       </c>
     </row>
-    <row r="165" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="str">
         <f>IF(receta!A165="","",receta!A165)</f>
         <v>Pihuelo</v>
@@ -62881,7 +62890,7 @@
         <v>983</v>
       </c>
     </row>
-    <row r="166" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="str">
         <f>IF(receta!A166="","",receta!A166)</f>
         <v>Mojito Sandía</v>
@@ -62955,7 +62964,7 @@
         <v>1000</v>
       </c>
     </row>
-    <row r="169" spans="1:13" ht="120" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="str">
         <f>IF(receta!A169="","",receta!A169)</f>
         <v>Chardonnay Sour</v>
@@ -62987,7 +62996,7 @@
       <c r="L169" s="1"/>
       <c r="M169" s="1"/>
     </row>
-    <row r="170" spans="1:13" ht="409.5" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="str">
         <f>IF(receta!A170="","",receta!A170)</f>
         <v>Carmenere Sour</v>
@@ -64476,11 +64485,7 @@
       <c r="M250" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M250" xr:uid="{43DB3A21-6E97-43C0-9768-D0796C62C1D9}">
-    <filterColumn colId="5">
-      <filters blank="1"/>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:M1" xr:uid="{43DB3A21-6E97-43C0-9768-D0796C62C1D9}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="F63" r:id="rId1" xr:uid="{F4C5002B-4D4E-44DF-92F8-067F77645455}"/>
@@ -64579,9 +64584,10 @@
     <hyperlink ref="K68" r:id="rId94" xr:uid="{3E73A1DB-0A1B-4D6D-9C5D-9C6C53A649F7}"/>
     <hyperlink ref="K117" r:id="rId95" xr:uid="{16A48F14-FDEF-49B0-965F-21300919D816}"/>
     <hyperlink ref="F79" r:id="rId96" xr:uid="{FE069020-1D93-4689-B554-F77D35BE7D23}"/>
+    <hyperlink ref="K160" r:id="rId97" xr:uid="{94CE9F4F-36BE-4CCF-979C-57660D3F048C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId97"/>
+  <pageSetup orientation="portrait" r:id="rId98"/>
 </worksheet>
 </file>
 

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2A5F085D-0B55-46E9-9736-88FCE2E79D2E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B70BA4B5-784B-4DE0-AE76-17EEC252B155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
@@ -22,7 +22,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">complementos!$A$1:$AE$250</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">receta!$A$1:$EW$174</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">recurso!$A$1:$M$1</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">recurso!$A$1:$M$250</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1689" uniqueCount="1131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1701" uniqueCount="1140">
   <si>
     <t>Ramazzotti Spritz</t>
   </si>
@@ -5203,6 +5203,36 @@
   </si>
   <si>
     <t>https://www.youtube.com/watch?v=Iaore8_sjJY</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=hldVpswGtts</t>
+  </si>
+  <si>
+    <t>Kumbia Queers - Puesta</t>
+  </si>
+  <si>
+    <t>Yo quería hacer una canción de protesta/Pero la verdad es que estoy puesta/Perdoname amiga si me pongo molesta/Pero la verdad hoy estoy puesta/La cosa no es con vos es que la realidad me cuesta/Me siento mejor cuando estoy puesta/Yo queria hacer una cancion de protesta/Ya fue, me escabio y que explote la fiesta.</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=NOjgze5Nmzc</t>
+  </si>
+  <si>
+    <t>Estopa - Vino Tinto</t>
+  </si>
+  <si>
+    <t>Hanky Panky</t>
+  </si>
+  <si>
+    <t>El Hanky Panky fue creado a comienzos del siglo XX por Ada “Coley” Coleman, legendaria jefa de barra del American Bar del Hotel Savoy de Londres, para el actor Sir Charles Hawtrey (1858-1923). El cóctel aparece posteriormente en The Savoy Cocktail Book de Harry Craddock (1930), lo que contribuyó a consolidar su fama.
+La historia cuenta que fue el propio Hawtrey quien dio nombre al trago. Un día, al entrar al bar, le dijo a Coleman: "Coley, estoy medio muerto; ¿qué puedes hacer para revivirme?". Coleman improvisó una nueva mezcla y, al probarla, el actor exclamó que era “un verdadero hanky-panky”, expresión coloquial inglesa que puede significar algo sorprendente, ingenioso o casi mágico.
+Se cree que Coleman creó el cóctel hacia 1921, cuando Hawtrey producía y protagonizaba The Adventure of Ambrose Applejohn en el Teatro Savoy, situado junto al hotel. Ese mismo año también había producido Hanky Panky John, obra de Basil Macdonald Hastings, lo que probablemente influyó en la selección del nombre.</t>
+  </si>
+  <si>
+    <t>Despúes de servir, se recomienda exprimir una piel de naranja sobre la superficie del cóctel para liberar sus aceites y usarla como decoración.</t>
+  </si>
+  <si>
+    <t>world-charles-hawtrey.jpg
+Caricatura, firmada por el ilustrador Bert Thomas, de Sir Charles Hawtrey (1858-1923), actor y productor teatral británico, publicada como suplemento de la revista The World (magazine, UK) a comienzos del siglo XX.</t>
   </si>
 </sst>
 </file>
@@ -36981,7 +37011,7 @@
         <v>300</v>
       </c>
       <c r="H174" s="2">
-        <f t="shared" ref="H174" si="8">SUM(I174:DF174)</f>
+        <f t="shared" ref="H174:H175" si="8">SUM(I174:DF174)</f>
         <v>180</v>
       </c>
       <c r="I174" s="2"/>
@@ -37137,16 +37167,31 @@
       <c r="EW174" s="2"/>
     </row>
     <row r="175" spans="1:153" x14ac:dyDescent="0.25">
-      <c r="A175" s="1"/>
-      <c r="B175" s="1"/>
-      <c r="C175" s="2"/>
-      <c r="D175" s="2"/>
+      <c r="A175" s="1" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B175" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="C175" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D175" s="2">
+        <v>300</v>
+      </c>
       <c r="E175" s="2"/>
-      <c r="F175" s="2"/>
+      <c r="F175" s="2" t="s">
+        <v>60</v>
+      </c>
       <c r="G175" s="2"/>
-      <c r="H175" s="2"/>
+      <c r="H175" s="2">
+        <f t="shared" si="8"/>
+        <v>97.5</v>
+      </c>
       <c r="I175" s="2"/>
-      <c r="J175" s="2"/>
+      <c r="J175" s="2">
+        <v>45</v>
+      </c>
       <c r="K175" s="2"/>
       <c r="L175" s="2"/>
       <c r="M175" s="2"/>
@@ -37168,7 +37213,9 @@
       <c r="AC175" s="2"/>
       <c r="AD175" s="2"/>
       <c r="AE175" s="2"/>
-      <c r="AF175" s="2"/>
+      <c r="AF175" s="2">
+        <v>45</v>
+      </c>
       <c r="AG175" s="2"/>
       <c r="AH175" s="2"/>
       <c r="AI175" s="2"/>
@@ -37182,7 +37229,9 @@
       <c r="AQ175" s="2"/>
       <c r="AR175" s="2"/>
       <c r="AS175" s="2"/>
-      <c r="AT175" s="2"/>
+      <c r="AT175" s="2">
+        <v>7.5</v>
+      </c>
       <c r="AU175" s="2"/>
       <c r="AV175" s="2"/>
       <c r="AW175" s="2"/>
@@ -55696,10 +55745,12 @@
     <row r="175" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="str">
         <f>IF(receta!A175="","",receta!A175)</f>
-        <v/>
+        <v>Hanky Panky</v>
       </c>
       <c r="B175" s="2"/>
-      <c r="C175" s="2"/>
+      <c r="C175" s="2">
+        <v>1</v>
+      </c>
       <c r="D175" s="2"/>
       <c r="E175" s="2"/>
       <c r="F175" s="2"/>
@@ -59306,7 +59357,7 @@
         <v>972</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="255" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:13" ht="240" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="str">
         <f>IF(receta!A32="","",receta!A32)</f>
         <v>Cléry Durazno</v>
@@ -59606,9 +59657,15 @@
       <c r="D43" s="4" t="s">
         <v>590</v>
       </c>
-      <c r="E43" s="1"/>
-      <c r="F43" s="5"/>
-      <c r="G43" s="5"/>
+      <c r="E43" s="1" t="s">
+        <v>1132</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>1131</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>1133</v>
+      </c>
       <c r="H43" s="1" t="s">
         <v>257</v>
       </c>
@@ -60020,7 +60077,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="58" spans="1:13" ht="165" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:13" ht="150" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="str">
         <f>IF(receta!A58="","",receta!A58)</f>
         <v>Frangelico Sour</v>
@@ -60970,7 +61027,7 @@
       <c r="L92" s="5"/>
       <c r="M92" s="1"/>
     </row>
-    <row r="93" spans="1:13" ht="165" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:13" ht="180" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="str">
         <f>IF(receta!A93="","",receta!A93)</f>
         <v>Milano Torino</v>
@@ -60992,7 +61049,7 @@
         <v>1042</v>
       </c>
     </row>
-    <row r="94" spans="1:13" ht="210" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:13" ht="225" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="str">
         <f>IF(receta!A94="","",receta!A94)</f>
         <v>Mimosa</v>
@@ -61795,10 +61852,14 @@
         <v>388</v>
       </c>
       <c r="G125" s="5"/>
-      <c r="H125" s="1"/>
+      <c r="H125" s="5"/>
       <c r="I125" s="1"/>
-      <c r="J125" s="1"/>
-      <c r="K125" s="1"/>
+      <c r="J125" s="1" t="s">
+        <v>1135</v>
+      </c>
+      <c r="K125" s="5" t="s">
+        <v>1134</v>
+      </c>
       <c r="L125" s="1"/>
       <c r="M125" s="1"/>
     </row>
@@ -63116,13 +63177,17 @@
         <v>1078</v>
       </c>
     </row>
-    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:13" ht="255" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="str">
         <f>IF(receta!A175="","",receta!A175)</f>
-        <v/>
-      </c>
-      <c r="B175" s="1"/>
-      <c r="C175" s="4"/>
+        <v>Hanky Panky</v>
+      </c>
+      <c r="B175" s="4" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C175" s="4" t="s">
+        <v>1137</v>
+      </c>
       <c r="D175" s="4"/>
       <c r="E175" s="1"/>
       <c r="F175" s="1"/>
@@ -63132,7 +63197,9 @@
       <c r="J175" s="1"/>
       <c r="K175" s="1"/>
       <c r="L175" s="1"/>
-      <c r="M175" s="1"/>
+      <c r="M175" s="4" t="s">
+        <v>1139</v>
+      </c>
     </row>
     <row r="176" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="str">
@@ -64485,7 +64552,7 @@
       <c r="M250" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:M1" xr:uid="{43DB3A21-6E97-43C0-9768-D0796C62C1D9}"/>
+  <autoFilter ref="A1:M250" xr:uid="{43DB3A21-6E97-43C0-9768-D0796C62C1D9}"/>
   <phoneticPr fontId="1" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="F63" r:id="rId1" xr:uid="{F4C5002B-4D4E-44DF-92F8-067F77645455}"/>
@@ -64585,9 +64652,11 @@
     <hyperlink ref="K117" r:id="rId95" xr:uid="{16A48F14-FDEF-49B0-965F-21300919D816}"/>
     <hyperlink ref="F79" r:id="rId96" xr:uid="{FE069020-1D93-4689-B554-F77D35BE7D23}"/>
     <hyperlink ref="K160" r:id="rId97" xr:uid="{94CE9F4F-36BE-4CCF-979C-57660D3F048C}"/>
+    <hyperlink ref="F43" r:id="rId98" xr:uid="{8CF791BE-869A-4F43-9C91-AF8E24DC71C9}"/>
+    <hyperlink ref="K125" r:id="rId99" xr:uid="{F4AC4FB8-FB91-4049-878D-BBEAAE2B5094}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId98"/>
+  <pageSetup orientation="portrait" r:id="rId100"/>
 </worksheet>
 </file>
 

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B70BA4B5-784B-4DE0-AE76-17EEC252B155}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8918B05-9EE5-4E6F-9CDD-B48765B0F414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1701" uniqueCount="1140">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1703" uniqueCount="1142">
   <si>
     <t>Ramazzotti Spritz</t>
   </si>
@@ -4516,9 +4516,6 @@
 Publicidad de época de Amaretto Disaronno</t>
   </si>
   <si>
-    <t>espresso.jpg</t>
-  </si>
-  <si>
     <t>fernet.jpg
 Título: "El pueblo quiere fernet”
 Autor: Gustavo Ferrari 
@@ -5233,6 +5230,16 @@
   <si>
     <t>world-charles-hawtrey.jpg
 Caricatura, firmada por el ilustrador Bert Thomas, de Sir Charles Hawtrey (1858-1923), actor y productor teatral británico, publicada como suplemento de la revista The World (magazine, UK) a comienzos del siglo XX.</t>
+  </si>
+  <si>
+    <t>La Máquina de Hacer Pájaros - Por Probar el Vino y el Agua Salada</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=BpMyfQIgz6M</t>
+  </si>
+  <si>
+    <t>espresso.jpg
+Ilustración contemporánea del cóctel Espresso Martini, inspirada en el estilo gráfico de los antiguos carteles y publicidades de bar.</t>
   </si>
 </sst>
 </file>
@@ -36636,7 +36643,7 @@
     </row>
     <row r="172" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>1057</v>
+        <v>1056</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>53</v>
@@ -36814,7 +36821,7 @@
     </row>
     <row r="173" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>1076</v>
+        <v>1075</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>52</v>
@@ -36990,7 +36997,7 @@
     </row>
     <row r="174" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>1077</v>
+        <v>1076</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>49</v>
@@ -37168,7 +37175,7 @@
     </row>
     <row r="175" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>1136</v>
+        <v>1135</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>55</v>
@@ -58530,7 +58537,7 @@
         <v>315</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>316</v>
@@ -58545,7 +58552,7 @@
         <v>762</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>962</v>
+        <v>961</v>
       </c>
       <c r="M1" s="7" t="s">
         <v>810</v>
@@ -58622,7 +58629,7 @@
         <v>239</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>965</v>
+        <v>964</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="5"/>
@@ -58695,7 +58702,7 @@
         <v>Amaretto Spritz</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>351</v>
@@ -58740,7 +58747,7 @@
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="4" t="s">
-        <v>1038</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -58799,7 +58806,7 @@
         <v>Aperol Spritz</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>598</v>
@@ -58816,7 +58823,7 @@
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="4" t="s">
-        <v>1055</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58864,7 +58871,7 @@
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="4" t="s">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58916,7 +58923,7 @@
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="4" t="s">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -58928,13 +58935,13 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>963</v>
+        <v>962</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -59020,7 +59027,7 @@
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="4" t="s">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59100,7 +59107,7 @@
       <c r="K22" s="5"/>
       <c r="L22" s="5"/>
       <c r="M22" s="4" t="s">
-        <v>1067</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -59122,7 +59129,7 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="4" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="345" x14ac:dyDescent="0.25">
@@ -59170,7 +59177,7 @@
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="4" t="s">
-        <v>970</v>
+        <v>969</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59198,7 +59205,7 @@
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="4" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="375" x14ac:dyDescent="0.25">
@@ -59216,23 +59223,23 @@
         <v>674</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>1112</v>
+        <v>1111</v>
       </c>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1" t="s">
-        <v>1115</v>
+        <v>1114</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>1114</v>
+        <v>1113</v>
       </c>
       <c r="L27" s="1"/>
       <c r="M27" s="4" t="s">
-        <v>971</v>
+        <v>970</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59245,7 +59252,7 @@
         <v>457</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>527</v>
@@ -59257,10 +59264,10 @@
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
       <c r="J28" s="1" t="s">
-        <v>1050</v>
+        <v>1049</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>1049</v>
+        <v>1048</v>
       </c>
       <c r="L28" s="5"/>
       <c r="M28" s="4" t="s">
@@ -59305,16 +59312,16 @@
         <v>666</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>1109</v>
+        <v>1108</v>
       </c>
       <c r="F30" s="5" t="s">
+        <v>1106</v>
+      </c>
+      <c r="G30" s="4" t="s">
         <v>1107</v>
-      </c>
-      <c r="G30" s="4" t="s">
-        <v>1108</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -59340,13 +59347,13 @@
         <v>424</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="F31" s="5" t="s">
+        <v>993</v>
+      </c>
+      <c r="G31" s="4" t="s">
         <v>994</v>
-      </c>
-      <c r="G31" s="4" t="s">
-        <v>995</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -59354,7 +59361,7 @@
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="4" t="s">
-        <v>972</v>
+        <v>971</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -59370,7 +59377,7 @@
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>334</v>
@@ -59436,7 +59443,7 @@
       <c r="K34" s="5"/>
       <c r="L34" s="5"/>
       <c r="M34" s="4" t="s">
-        <v>973</v>
+        <v>972</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -59452,10 +59459,10 @@
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="1" t="s">
-        <v>1088</v>
+        <v>1087</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>1087</v>
+        <v>1086</v>
       </c>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
@@ -59484,7 +59491,7 @@
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="1" t="s">
-        <v>954</v>
+        <v>953</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59538,7 +59545,7 @@
       <c r="K38" s="5"/>
       <c r="L38" s="5"/>
       <c r="M38" s="4" t="s">
-        <v>984</v>
+        <v>983</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -59547,7 +59554,7 @@
         <v>Cynar Spritz</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>333</v>
@@ -59562,7 +59569,7 @@
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="4" t="s">
-        <v>1051</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -59604,7 +59611,7 @@
         <v>724</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="1"/>
@@ -59616,7 +59623,7 @@
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
       <c r="M41" s="4" t="s">
-        <v>1054</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59658,13 +59665,13 @@
         <v>590</v>
       </c>
       <c r="E43" s="1" t="s">
+        <v>1131</v>
+      </c>
+      <c r="F43" s="5" t="s">
+        <v>1130</v>
+      </c>
+      <c r="G43" s="4" t="s">
         <v>1132</v>
-      </c>
-      <c r="F43" s="5" t="s">
-        <v>1131</v>
-      </c>
-      <c r="G43" s="4" t="s">
-        <v>1133</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>257</v>
@@ -59722,7 +59729,7 @@
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
       <c r="M45" s="4" t="s">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="285" x14ac:dyDescent="0.25">
@@ -59735,7 +59742,7 @@
       </c>
       <c r="C46" s="4"/>
       <c r="D46" s="4" t="s">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>185</v>
@@ -59747,16 +59754,16 @@
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
       <c r="J46" s="4" t="s">
+        <v>1027</v>
+      </c>
+      <c r="K46" s="5" t="s">
+        <v>1026</v>
+      </c>
+      <c r="L46" s="4" t="s">
         <v>1028</v>
       </c>
-      <c r="K46" s="5" t="s">
-        <v>1027</v>
-      </c>
-      <c r="L46" s="4" t="s">
-        <v>1029</v>
-      </c>
       <c r="M46" s="4" t="s">
-        <v>981</v>
+        <v>980</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -59832,7 +59839,7 @@
         <v>767</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -59840,7 +59847,7 @@
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
       <c r="M49" s="4" t="s">
-        <v>999</v>
+        <v>998</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="255" x14ac:dyDescent="0.25">
@@ -59860,7 +59867,7 @@
         <v>480</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>326</v>
@@ -59872,10 +59879,10 @@
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
       <c r="M50" s="4" t="s">
-        <v>956</v>
-      </c>
-    </row>
-    <row r="51" spans="1:13" ht="90" x14ac:dyDescent="0.25">
+        <v>955</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" ht="120" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="str">
         <f>IF(receta!A51="","",receta!A51)</f>
         <v>Espresso Martini</v>
@@ -59893,8 +59900,8 @@
       <c r="J51" s="1"/>
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
-      <c r="M51" s="1" t="s">
-        <v>951</v>
+      <c r="M51" s="4" t="s">
+        <v>1141</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="150" x14ac:dyDescent="0.25">
@@ -59948,7 +59955,7 @@
         <v>403</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>383</v>
@@ -59957,16 +59964,16 @@
         <v>382</v>
       </c>
       <c r="J53" s="1" t="s">
+        <v>1099</v>
+      </c>
+      <c r="K53" s="5" t="s">
+        <v>1098</v>
+      </c>
+      <c r="L53" s="1" t="s">
         <v>1100</v>
       </c>
-      <c r="K53" s="5" t="s">
-        <v>1099</v>
-      </c>
-      <c r="L53" s="1" t="s">
-        <v>1101</v>
-      </c>
       <c r="M53" s="4" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -60038,7 +60045,7 @@
         <v>472</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>976</v>
+        <v>975</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -60046,7 +60053,7 @@
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
       <c r="M56" s="4" t="s">
-        <v>952</v>
+        <v>951</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -60074,7 +60081,7 @@
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
       <c r="M57" s="4" t="s">
-        <v>958</v>
+        <v>957</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="150" x14ac:dyDescent="0.25">
@@ -60098,7 +60105,7 @@
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="4" t="s">
-        <v>955</v>
+        <v>954</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60116,13 +60123,13 @@
         <v>357</v>
       </c>
       <c r="E59" s="4" t="s">
+        <v>1093</v>
+      </c>
+      <c r="F59" s="5" t="s">
         <v>1094</v>
       </c>
-      <c r="F59" s="5" t="s">
+      <c r="G59" s="4" t="s">
         <v>1095</v>
-      </c>
-      <c r="G59" s="4" t="s">
-        <v>1096</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
@@ -60134,7 +60141,7 @@
       </c>
       <c r="L59" s="5"/>
       <c r="M59" s="4" t="s">
-        <v>953</v>
+        <v>952</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -60156,7 +60163,7 @@
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
       <c r="M60" s="4" t="s">
-        <v>977</v>
+        <v>976</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="165" x14ac:dyDescent="0.25">
@@ -60210,7 +60217,7 @@
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
       <c r="M62" s="4" t="s">
-        <v>986</v>
+        <v>985</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60243,7 +60250,7 @@
         <v>764</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="M63" s="4" t="s">
         <v>925</v>
@@ -60260,10 +60267,10 @@
       </c>
       <c r="D64" s="1"/>
       <c r="E64" s="1" t="s">
-        <v>1103</v>
+        <v>1102</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>1102</v>
+        <v>1101</v>
       </c>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
@@ -60272,7 +60279,7 @@
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
       <c r="M64" s="4" t="s">
-        <v>985</v>
+        <v>984</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60305,7 +60312,7 @@
         <v>Hugo</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>1081</v>
+        <v>1080</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>731</v>
@@ -60322,7 +60329,7 @@
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
       <c r="M66" s="4" t="s">
-        <v>1052</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="67" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60373,13 +60380,13 @@
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
       <c r="J68" s="1" t="s">
+        <v>1121</v>
+      </c>
+      <c r="K68" s="5" t="s">
+        <v>1120</v>
+      </c>
+      <c r="L68" s="4" t="s">
         <v>1122</v>
-      </c>
-      <c r="K68" s="5" t="s">
-        <v>1121</v>
-      </c>
-      <c r="L68" s="4" t="s">
-        <v>1123</v>
       </c>
       <c r="M68" s="4" t="s">
         <v>941</v>
@@ -60482,13 +60489,13 @@
         <v>866</v>
       </c>
       <c r="E72" s="1" t="s">
+        <v>1091</v>
+      </c>
+      <c r="F72" s="5" t="s">
+        <v>1090</v>
+      </c>
+      <c r="G72" s="4" t="s">
         <v>1092</v>
-      </c>
-      <c r="F72" s="5" t="s">
-        <v>1091</v>
-      </c>
-      <c r="G72" s="4" t="s">
-        <v>1093</v>
       </c>
       <c r="H72" s="1" t="s">
         <v>414</v>
@@ -60513,7 +60520,7 @@
       </c>
       <c r="C73" s="4"/>
       <c r="D73" s="4" t="s">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
@@ -60524,7 +60531,7 @@
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
       <c r="M73" s="4" t="s">
-        <v>1064</v>
+        <v>1063</v>
       </c>
     </row>
     <row r="74" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60578,7 +60585,7 @@
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
       <c r="M75" s="4" t="s">
-        <v>1053</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="76" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60614,10 +60621,10 @@
       </c>
       <c r="B77" s="1"/>
       <c r="C77" s="4" t="s">
+        <v>1008</v>
+      </c>
+      <c r="D77" s="4" t="s">
         <v>1009</v>
-      </c>
-      <c r="D77" s="4" t="s">
-        <v>1010</v>
       </c>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
@@ -60628,7 +60635,7 @@
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
       <c r="M77" s="4" t="s">
-        <v>1008</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="78" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -60668,10 +60675,10 @@
       <c r="C79" s="4"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1" t="s">
+        <v>1126</v>
+      </c>
+      <c r="F79" s="5" t="s">
         <v>1127</v>
-      </c>
-      <c r="F79" s="5" t="s">
-        <v>1128</v>
       </c>
       <c r="G79" s="1"/>
       <c r="H79" s="1"/>
@@ -60746,7 +60753,7 @@
       <c r="K82" s="1"/>
       <c r="L82" s="1"/>
       <c r="M82" s="4" t="s">
-        <v>1066</v>
+        <v>1065</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60804,7 +60811,7 @@
       <c r="K84" s="1"/>
       <c r="L84" s="1"/>
       <c r="M84" s="4" t="s">
-        <v>979</v>
+        <v>978</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -60834,7 +60841,7 @@
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
       <c r="M85" s="4" t="s">
-        <v>980</v>
+        <v>979</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -60899,7 +60906,7 @@
         <v>634</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
@@ -60910,7 +60917,7 @@
       <c r="K88" s="1"/>
       <c r="L88" s="1"/>
       <c r="M88" s="4" t="s">
-        <v>1065</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="89" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -60932,7 +60939,7 @@
         <v>180</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>1072</v>
+        <v>1071</v>
       </c>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
@@ -60940,7 +60947,7 @@
       <c r="K89" s="5"/>
       <c r="L89" s="5"/>
       <c r="M89" s="4" t="s">
-        <v>1070</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
@@ -60961,10 +60968,10 @@
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
       <c r="J90" s="1" t="s">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="K90" s="5" t="s">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="L90" s="5"/>
       <c r="M90" s="1"/>
@@ -60982,7 +60989,7 @@
       </c>
       <c r="D91" s="1"/>
       <c r="E91" s="1" t="s">
-        <v>1126</v>
+        <v>1125</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>334</v>
@@ -61019,10 +61026,10 @@
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
       <c r="J92" s="1" t="s">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="K92" s="5" t="s">
-        <v>1097</v>
+        <v>1096</v>
       </c>
       <c r="L92" s="5"/>
       <c r="M92" s="1"/>
@@ -61046,7 +61053,7 @@
       <c r="K93" s="1"/>
       <c r="L93" s="1"/>
       <c r="M93" s="4" t="s">
-        <v>1042</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="94" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -61068,7 +61075,7 @@
       <c r="K94" s="1"/>
       <c r="L94" s="1"/>
       <c r="M94" s="4" t="s">
-        <v>1060</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="95" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -61092,7 +61099,7 @@
       <c r="K95" s="1"/>
       <c r="L95" s="1"/>
       <c r="M95" s="4" t="s">
-        <v>991</v>
+        <v>990</v>
       </c>
     </row>
     <row r="96" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -61125,13 +61132,13 @@
         <v>577</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="G97" s="1"/>
       <c r="H97" s="4"/>
@@ -61140,7 +61147,7 @@
       <c r="K97" s="1"/>
       <c r="L97" s="1"/>
       <c r="M97" s="4" t="s">
-        <v>990</v>
+        <v>989</v>
       </c>
     </row>
     <row r="98" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -61149,7 +61156,7 @@
         <v>Mojito Spritz</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>723</v>
@@ -61216,7 +61223,7 @@
       <c r="K100" s="5"/>
       <c r="L100" s="5"/>
       <c r="M100" s="4" t="s">
-        <v>1086</v>
+        <v>1085</v>
       </c>
     </row>
     <row r="101" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -61264,7 +61271,7 @@
       <c r="K102" s="1"/>
       <c r="L102" s="1"/>
       <c r="M102" s="4" t="s">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="103" spans="1:13" ht="210" x14ac:dyDescent="0.25">
@@ -61286,7 +61293,7 @@
       <c r="K103" s="1"/>
       <c r="L103" s="1"/>
       <c r="M103" s="4" t="s">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="104" spans="1:13" ht="345" x14ac:dyDescent="0.25">
@@ -61316,7 +61323,7 @@
       <c r="K104" s="5"/>
       <c r="L104" s="5"/>
       <c r="M104" s="4" t="s">
-        <v>1003</v>
+        <v>1002</v>
       </c>
     </row>
     <row r="105" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -61358,25 +61365,25 @@
         <v>562</v>
       </c>
       <c r="E106" s="1" t="s">
+        <v>1033</v>
+      </c>
+      <c r="F106" s="5" t="s">
         <v>1034</v>
       </c>
-      <c r="F106" s="5" t="s">
-        <v>1035</v>
-      </c>
       <c r="G106" s="4" t="s">
-        <v>1033</v>
+        <v>1032</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="I106" s="5" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="J106" s="1"/>
       <c r="K106" s="1"/>
       <c r="L106" s="1"/>
       <c r="M106" s="4" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="107" spans="1:13" ht="192" customHeight="1" x14ac:dyDescent="0.25">
@@ -61415,7 +61422,7 @@
       <c r="F108" s="1"/>
       <c r="G108" s="1"/>
       <c r="H108" s="1" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="I108" s="5" t="s">
         <v>256</v>
@@ -61424,7 +61431,7 @@
       <c r="K108" s="1"/>
       <c r="L108" s="1"/>
       <c r="M108" s="4" t="s">
-        <v>1046</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="109" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -61459,7 +61466,7 @@
         <v>671</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="E110" s="4" t="s">
         <v>582</v>
@@ -61474,7 +61481,7 @@
       <c r="K110" s="5"/>
       <c r="L110" s="5"/>
       <c r="M110" s="4" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.25">
@@ -61518,7 +61525,7 @@
         <v>482</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>1073</v>
+        <v>1072</v>
       </c>
       <c r="H112" s="1"/>
       <c r="I112" s="5"/>
@@ -61550,7 +61557,7 @@
       <c r="K113" s="5"/>
       <c r="L113" s="5"/>
       <c r="M113" s="4" t="s">
-        <v>1069</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.25">
@@ -61641,14 +61648,14 @@
       <c r="H117" s="1"/>
       <c r="I117" s="1"/>
       <c r="J117" s="4" t="s">
+        <v>1123</v>
+      </c>
+      <c r="K117" s="5" t="s">
         <v>1124</v>
-      </c>
-      <c r="K117" s="5" t="s">
-        <v>1125</v>
       </c>
       <c r="L117" s="5"/>
       <c r="M117" s="4" t="s">
-        <v>1007</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="118" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -61702,7 +61709,7 @@
       <c r="K119" s="5"/>
       <c r="L119" s="5"/>
       <c r="M119" s="4" t="s">
-        <v>1005</v>
+        <v>1004</v>
       </c>
     </row>
     <row r="120" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -61711,7 +61718,7 @@
         <v>Ramazzotti Spritz</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>352</v>
@@ -61737,17 +61744,17 @@
         <v>Ramazzotti Violetto Spritz</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>745</v>
       </c>
       <c r="D121" s="1"/>
       <c r="E121" s="1" t="s">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>1089</v>
+        <v>1088</v>
       </c>
       <c r="G121" s="1"/>
       <c r="H121" s="1"/>
@@ -61855,10 +61862,10 @@
       <c r="H125" s="5"/>
       <c r="I125" s="1"/>
       <c r="J125" s="1" t="s">
-        <v>1135</v>
+        <v>1134</v>
       </c>
       <c r="K125" s="5" t="s">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="L125" s="1"/>
       <c r="M125" s="1"/>
@@ -61926,7 +61933,7 @@
       <c r="K128" s="1"/>
       <c r="L128" s="1"/>
       <c r="M128" s="4" t="s">
-        <v>1004</v>
+        <v>1003</v>
       </c>
     </row>
     <row r="129" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -61992,7 +61999,7 @@
       <c r="K131" s="1"/>
       <c r="L131" s="1"/>
       <c r="M131" s="4" t="s">
-        <v>1071</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="132" spans="1:13" ht="165" x14ac:dyDescent="0.25">
@@ -62018,7 +62025,7 @@
       <c r="K132" s="5"/>
       <c r="L132" s="5"/>
       <c r="M132" s="4" t="s">
-        <v>1041</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.25">
@@ -62054,10 +62061,10 @@
         <v>593</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>1119</v>
+        <v>1118</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>1118</v>
+        <v>1117</v>
       </c>
       <c r="G134" s="5"/>
       <c r="H134" s="4"/>
@@ -62140,13 +62147,13 @@
         <v>432</v>
       </c>
       <c r="E137" s="1" t="s">
+        <v>1030</v>
+      </c>
+      <c r="F137" s="5" t="s">
+        <v>1029</v>
+      </c>
+      <c r="G137" s="4" t="s">
         <v>1031</v>
-      </c>
-      <c r="F137" s="5" t="s">
-        <v>1030</v>
-      </c>
-      <c r="G137" s="4" t="s">
-        <v>1032</v>
       </c>
       <c r="H137" s="1"/>
       <c r="I137" s="1"/>
@@ -62216,13 +62223,13 @@
         <v>344</v>
       </c>
       <c r="E140" s="1" t="s">
+        <v>1016</v>
+      </c>
+      <c r="F140" s="5" t="s">
+        <v>1015</v>
+      </c>
+      <c r="G140" s="4" t="s">
         <v>1017</v>
-      </c>
-      <c r="F140" s="5" t="s">
-        <v>1016</v>
-      </c>
-      <c r="G140" s="4" t="s">
-        <v>1018</v>
       </c>
       <c r="H140" s="1"/>
       <c r="I140" s="1"/>
@@ -62234,7 +62241,7 @@
       </c>
       <c r="L140" s="5"/>
       <c r="M140" s="4" t="s">
-        <v>1006</v>
+        <v>1005</v>
       </c>
     </row>
     <row r="141" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62339,16 +62346,16 @@
       </c>
       <c r="G144" s="1"/>
       <c r="H144" s="1" t="s">
+        <v>1021</v>
+      </c>
+      <c r="I144" s="5" t="s">
         <v>1022</v>
       </c>
-      <c r="I144" s="5" t="s">
-        <v>1023</v>
-      </c>
       <c r="J144" s="1" t="s">
+        <v>1019</v>
+      </c>
+      <c r="K144" s="5" t="s">
         <v>1020</v>
-      </c>
-      <c r="K144" s="5" t="s">
-        <v>1021</v>
       </c>
       <c r="L144" s="1"/>
       <c r="M144" s="4" t="s">
@@ -62382,7 +62389,7 @@
       <c r="K145" s="1"/>
       <c r="L145" s="1"/>
       <c r="M145" s="4" t="s">
-        <v>1043</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="146" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -62454,7 +62461,7 @@
       <c r="K148" s="5"/>
       <c r="L148" s="5"/>
       <c r="M148" s="4" t="s">
-        <v>1082</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="149" spans="1:13" ht="324" customHeight="1" x14ac:dyDescent="0.25">
@@ -62482,7 +62489,7 @@
       <c r="K149" s="5"/>
       <c r="L149" s="5"/>
       <c r="M149" s="4" t="s">
-        <v>1068</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="150" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62542,7 +62549,7 @@
       <c r="K151" s="1"/>
       <c r="L151" s="1"/>
       <c r="M151" s="4" t="s">
-        <v>1062</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="152" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -62568,7 +62575,7 @@
       <c r="K152" s="1"/>
       <c r="L152" s="1"/>
       <c r="M152" s="4" t="s">
-        <v>1011</v>
+        <v>1010</v>
       </c>
     </row>
     <row r="153" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -62627,7 +62634,7 @@
         <v>769</v>
       </c>
       <c r="L154" s="26" t="s">
-        <v>978</v>
+        <v>977</v>
       </c>
       <c r="M154" s="1"/>
     </row>
@@ -62643,7 +62650,7 @@
         <v>797</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>1074</v>
+        <v>1073</v>
       </c>
       <c r="E155" s="1"/>
       <c r="F155" s="1"/>
@@ -62654,7 +62661,7 @@
       <c r="K155" s="1"/>
       <c r="L155" s="1"/>
       <c r="M155" s="4" t="s">
-        <v>1061</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="156" spans="1:13" ht="255" x14ac:dyDescent="0.25">
@@ -62732,8 +62739,12 @@
       <c r="G158" s="1"/>
       <c r="H158" s="1"/>
       <c r="I158" s="5"/>
-      <c r="J158" s="1"/>
-      <c r="K158" s="1"/>
+      <c r="J158" s="4" t="s">
+        <v>1139</v>
+      </c>
+      <c r="K158" s="5" t="s">
+        <v>1140</v>
+      </c>
       <c r="L158" s="1"/>
       <c r="M158" s="10" t="s">
         <v>812</v>
@@ -62785,28 +62796,28 @@
         <v>825</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="E160" s="1" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F160" s="5" t="s">
         <v>1013</v>
       </c>
-      <c r="F160" s="5" t="s">
-        <v>1014</v>
-      </c>
       <c r="G160" s="4" t="s">
-        <v>1012</v>
+        <v>1011</v>
       </c>
       <c r="H160" s="1"/>
       <c r="I160" s="5"/>
       <c r="J160" s="1" t="s">
+        <v>1128</v>
+      </c>
+      <c r="K160" s="5" t="s">
         <v>1129</v>
-      </c>
-      <c r="K160" s="5" t="s">
-        <v>1130</v>
       </c>
       <c r="L160" s="1"/>
       <c r="M160" s="4" t="s">
-        <v>1019</v>
+        <v>1018</v>
       </c>
     </row>
     <row r="161" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -62818,7 +62829,7 @@
         <v>837</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>1084</v>
+        <v>1083</v>
       </c>
       <c r="D161" s="4"/>
       <c r="E161" s="1"/>
@@ -62830,7 +62841,7 @@
       <c r="K161" s="1"/>
       <c r="L161" s="1"/>
       <c r="M161" s="4" t="s">
-        <v>1085</v>
+        <v>1084</v>
       </c>
     </row>
     <row r="162" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -62872,7 +62883,7 @@
         <v>848</v>
       </c>
       <c r="E163" s="1" t="s">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="F163" s="5" t="s">
         <v>850</v>
@@ -62884,7 +62895,7 @@
       <c r="K163" s="1"/>
       <c r="L163" s="1"/>
       <c r="M163" s="4" t="s">
-        <v>969</v>
+        <v>968</v>
       </c>
     </row>
     <row r="164" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62934,13 +62945,13 @@
         <v>868</v>
       </c>
       <c r="E165" s="4" t="s">
+        <v>1023</v>
+      </c>
+      <c r="F165" s="5" t="s">
         <v>1024</v>
       </c>
-      <c r="F165" s="5" t="s">
+      <c r="G165" s="1" t="s">
         <v>1025</v>
-      </c>
-      <c r="G165" s="1" t="s">
-        <v>1026</v>
       </c>
       <c r="H165" s="1"/>
       <c r="I165" s="5"/>
@@ -62948,7 +62959,7 @@
       <c r="K165" s="1"/>
       <c r="L165" s="1"/>
       <c r="M165" s="4" t="s">
-        <v>983</v>
+        <v>982</v>
       </c>
     </row>
     <row r="166" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -63000,7 +63011,7 @@
       <c r="K167" s="1"/>
       <c r="L167" s="1"/>
       <c r="M167" s="4" t="s">
-        <v>1039</v>
+        <v>1038</v>
       </c>
     </row>
     <row r="168" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -63010,7 +63021,7 @@
       </c>
       <c r="B168" s="1"/>
       <c r="C168" s="4" t="s">
-        <v>996</v>
+        <v>995</v>
       </c>
       <c r="D168" s="4"/>
       <c r="E168" s="1"/>
@@ -63022,7 +63033,7 @@
       <c r="K168" s="1"/>
       <c r="L168" s="1"/>
       <c r="M168" s="4" t="s">
-        <v>1000</v>
+        <v>999</v>
       </c>
     </row>
     <row r="169" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -63038,21 +63049,21 @@
       </c>
       <c r="D169" s="4"/>
       <c r="E169" s="1" t="s">
+        <v>1104</v>
+      </c>
+      <c r="F169" s="5" t="s">
+        <v>1103</v>
+      </c>
+      <c r="G169" s="4" t="s">
         <v>1105</v>
-      </c>
-      <c r="F169" s="5" t="s">
-        <v>1104</v>
-      </c>
-      <c r="G169" s="4" t="s">
-        <v>1106</v>
       </c>
       <c r="H169" s="1"/>
       <c r="I169" s="5"/>
       <c r="J169" s="1" t="s">
-        <v>1111</v>
+        <v>1110</v>
       </c>
       <c r="K169" s="5" t="s">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="L169" s="1"/>
       <c r="M169" s="1"/>
@@ -63120,7 +63131,7 @@
       </c>
       <c r="B172" s="4"/>
       <c r="C172" s="4" t="s">
-        <v>1058</v>
+        <v>1057</v>
       </c>
       <c r="D172" s="4"/>
       <c r="E172" s="1"/>
@@ -63132,7 +63143,7 @@
       <c r="K172" s="1"/>
       <c r="L172" s="1"/>
       <c r="M172" s="4" t="s">
-        <v>1059</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="173" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -63152,7 +63163,7 @@
       <c r="K173" s="1"/>
       <c r="L173" s="1"/>
       <c r="M173" s="4" t="s">
-        <v>1079</v>
+        <v>1078</v>
       </c>
     </row>
     <row r="174" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -63161,7 +63172,7 @@
         <v>Campari Spritz</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="C174" s="4"/>
       <c r="D174" s="4"/>
@@ -63174,7 +63185,7 @@
       <c r="K174" s="1"/>
       <c r="L174" s="1"/>
       <c r="M174" s="4" t="s">
-        <v>1078</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="175" spans="1:13" ht="255" x14ac:dyDescent="0.25">
@@ -63183,10 +63194,10 @@
         <v>Hanky Panky</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>1138</v>
+        <v>1137</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="D175" s="4"/>
       <c r="E175" s="1"/>
@@ -63198,7 +63209,7 @@
       <c r="K175" s="1"/>
       <c r="L175" s="1"/>
       <c r="M175" s="4" t="s">
-        <v>1139</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="176" spans="1:13" x14ac:dyDescent="0.25">
@@ -64654,9 +64665,10 @@
     <hyperlink ref="K160" r:id="rId97" xr:uid="{94CE9F4F-36BE-4CCF-979C-57660D3F048C}"/>
     <hyperlink ref="F43" r:id="rId98" xr:uid="{8CF791BE-869A-4F43-9C91-AF8E24DC71C9}"/>
     <hyperlink ref="K125" r:id="rId99" xr:uid="{F4AC4FB8-FB91-4049-878D-BBEAAE2B5094}"/>
+    <hyperlink ref="K158" r:id="rId100" xr:uid="{C198DB91-C048-4B59-BF1D-EE0F56806A3D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId100"/>
+  <pageSetup orientation="portrait" r:id="rId101"/>
 </worksheet>
 </file>
 

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B8918B05-9EE5-4E6F-9CDD-B48765B0F414}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F29714D9-5901-41BF-8C9D-777EF728EA1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
@@ -3822,10 +3822,6 @@
     <t>Azúcar 2</t>
   </si>
   <si>
-    <t>vino-navegado_pati-aguilera.jpg
-Créditos: Ilustración de Pati Aguilera y Fito Holloway (AJíCOLOR) (https://festivaldelaji.blogspot.com/)</t>
-  </si>
-  <si>
     <t>Cascarita de Naranja</t>
   </si>
   <si>
@@ -4262,12 +4258,6 @@
 El Jerez Sour es una reinterpretación moderna dentro de la tradición de los cócteles sour, destacando por su elegancia, frescura y por poner en valor los matices aromáticos y la personalidad del jerez.</t>
   </si>
   <si>
-    <t>Constante_Gil2.jpg
-"Tertulias de café"
-Autor: Constante Gil
-Año: 1988</t>
-  </si>
-  <si>
     <t>Carmenere: historia de una botella echada al mar
 El Carmenere es un miembro de la familia Cabernet. Su nombre proviene de la palabra francesa carmin, en referencia al color carmín que adquiere su follaje antes de la caída de las hojas. Es considerada una de las seis uvas tintas originarias de Burdeos, junto con la Cabernet Sauvignon, la Cabernet Franc, la Merlot, la Malbec y la Petit Verdot. Sin embargo, hoy no es habitual encontrarla en Francia, y las mayores plantaciones de esta variedad se concentran en Chile.
 Antes de la década de 1860, en los viñedos de Burdeos, al sudoeste de Francia, el Carmenere era una uva más del paisaje: oscura y fragante, pero caprichosa. No era la favorita de los viticultores debido a que brotaba temprano, sufría con las lluvias de primavera y presentaba rendimientos irregulares. Aun así, cuando todo salía bien, aportaba color y un carácter especiado a los vinos producidos a partir de mezclas ceparias, habituales en esa época. La lógica de los monovarietales se impondría recién a partir del siglo XX.
@@ -4377,13 +4367,6 @@
 Antonio Miguel Ramón Ramón (1879 - 1924)</t>
   </si>
   <si>
-    <t>Trombe2.jpg
-Título: " Tormenta en el Mar”
-Autor: Gustave Courbet
-Técnica: Óleo sobre lienzo
-Año: 1865</t>
-  </si>
-  <si>
     <t>anita-bryant.jpg
 Anita Bryant, 1977.</t>
   </si>
@@ -4448,20 +4431,8 @@
 Portada del libro Floridita Cocktails, 1939.</t>
   </si>
   <si>
-    <t>mick-jagger.jpg
-Mick Jagger en el escenario, 1973. 
-Foto: Pictorial Press Ltd / Alamy Stock Photo.</t>
-  </si>
-  <si>
     <t>some-like-it-hot.jpg
 Afiche de la película Some Like It Hot (1959), dirigida por Billy Wilder y protagonizada por Marilyn Monroe, Tony Curtis y Jack Lemmon.</t>
-  </si>
-  <si>
-    <t>Lira_Pedro-Crepusculo.jpg
-Título: " Crepúsculo”
-Autor: Pedro Lira
-Técnica: Óleo sobre lienzo
-Año: Sin información precisa, antes de 1912</t>
   </si>
   <si>
     <t>Pizarnik.jpg
@@ -4525,9 +4496,6 @@
   <si>
     <t>Clicquot.jpg
 Anuncio publicitario de Veuve Clicquot, 1960.</t>
-  </si>
-  <si>
-    <t>cosmo2.jpg</t>
   </si>
   <si>
     <t>frangelico.jpg
@@ -4668,13 +4636,6 @@
 Con el paso de los años la relación se fue enfriando hasta desvanecerse, pero el cuadro permaneció colgado sobre la cama de Lorca en su habitación de la Residencia, como un vestigio silencioso de aquella amistad intensa, en la que la pintura, la poesía y hasta una botella de ron formaron parte del amor compartido. </t>
   </si>
   <si>
-    <t>naturaleza_ron.jpg
-Título: Naturaleza muerta con botella de ron (también conocida como Sifón y botella de ron)
-Autor: Salvador Dalí
-Técnica: Óleo sobre lienzo
-Año: 1924</t>
-  </si>
-  <si>
     <t>La_Bodeguita_Ernest_Hemingway.jpg
 Frase atribuida a Ernest Hemingway, escrita en una pared de La Bodeguita del Medio, en La Habana, Cuba.</t>
   </si>
@@ -4699,13 +4660,6 @@
   </si>
   <si>
     <t>Trepo por el/Tallo del lúpulo/Al cielo iré/Tu espuma en cúmulos/Atravesaré/Somos los tres/Junto a tu hermano pan/La agrupación/Perfecta, inmortal</t>
-  </si>
-  <si>
-    <t>Antonio_Machado_por_Leandro_Oroz_(1925).jpg
-Título: Retrato de Antonio Machado (1875 - 1939)
-Autor: Leandro Oroz Lacalle
-Técnica: Sanguina
-Año: 1925</t>
   </si>
   <si>
     <t>AlcProfSummerPenn19351.jpg
@@ -4758,13 +4712,6 @@
 En los años 50 y 60, la moda tropical y los bares tiki invitaron a beber paisajes, surgieron entonces cócteles como el Blue Hawaiian y el Laguna Azul. El cóctel podía ser una postal del trópico.
 Décadas más tarde, el cine reforzó ese imaginario. Películas como La laguna azul, estrenada en 1980, filmada en Fiyi, protagonizada con Brooke Shields y Christopher Atkins, terminaron por fijar la asociación entre el azul brillante y la idea de paraíso. El cóctel no nació de la película, de hecho es anterior, pero ambos compartían el mismo sueño: el de una isla lejana, suspendida en el tiempo.
 Posteriormente los tragos azules perdieron prestigio y popularidad, víctimas del exceso de azúcar y de la coctelería descuidada. Pero hoy han vuelto, redescubiertos con mejores técnicas y nuevos equilibrios, manteniendo su encanto original: la ilusión, breve y luminosa, de sostener el mar entre las manos.</t>
-  </si>
-  <si>
-    <t>pink.jpg
-Título: The Pink Panther 03
-Autora: Crys (Cristina Tichitoli)
-Técnica: Acrílico y técnica mixta sobre papel 
-Año: 2023</t>
   </si>
   <si>
     <t>En el jardín del edén/Suspira Santa Teresa/Con una copa en la mano,/Parece que de cerveza./De lejos sentía el amo/Fragancia de chicha cru'a,/Pa' sus adentros pensaba/"qué fiesta tan macanú'a".</t>
@@ -5240,6 +5187,56 @@
   <si>
     <t>espresso.jpg
 Ilustración contemporánea del cóctel Espresso Martini, inspirada en el estilo gráfico de los antiguos carteles y publicidades de bar.</t>
+  </si>
+  <si>
+    <t>vino-navegado_pati-aguilera.jpg
+Ilustración de Pati Aguilera y Fito Holloway (AJíCOLOR) (https://festivaldelaji.blogspot.com/)</t>
+  </si>
+  <si>
+    <t>Lira_Pedro-Crepusculo.jpg
+Título: "Crepúsculo”
+Autor: Pedro Lira
+Técnica: Óleo sobre lienzo
+Año: Sin información precisa, antes de 1912</t>
+  </si>
+  <si>
+    <t>Trombe2.jpg
+Título: "Tormenta en el Mar”
+Autor: Gustave Courbet
+Técnica: Óleo sobre lienzo
+Año: 1865</t>
+  </si>
+  <si>
+    <t>naturaleza_ron.jpg
+Título: "Naturaleza muerta con botella de ron" (también conocida como Sifón y botella de ron)
+Autor: Salvador Dalí
+Técnica: Óleo sobre lienzo
+Año: 1924</t>
+  </si>
+  <si>
+    <t>pink.jpg
+Título: "The Pink Panther 03"
+Autora: Crys (Cristina Tichitoli)
+Técnica: Acrílico y técnica mixta sobre papel 
+Año: 2023</t>
+  </si>
+  <si>
+    <t>mick-jagger.jpg
+Mick Jagger en el escenario, 1973. Foto: Pictorial Press Ltd / Alamy Stock Photo.</t>
+  </si>
+  <si>
+    <t>Constante_Gil2.jpg
+Título: "Tertulias de café"
+Autor: Constante Gil
+Año: 1988</t>
+  </si>
+  <si>
+    <t>cosmo2.jpg
+Ilustración contemporánea del cóctel Cosmopolitan, realizada en un estilo inspirado en los afiches publicitarios y pin-ups de mediados del siglo XX.</t>
+  </si>
+  <si>
+    <t>Antonio_Machado_por_Leandro_Oroz_(1925).jpg
+Retrato de Antonio Machado (1875 - 1939), sanguina de Leandro Oroz Lacalle,  1925.</t>
   </si>
 </sst>
 </file>
@@ -5917,7 +5914,7 @@
         <v>78</v>
       </c>
       <c r="O1" s="27" t="s">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="P1" s="27" t="s">
         <v>690</v>
@@ -5935,7 +5932,7 @@
         <v>564</v>
       </c>
       <c r="U1" s="27" t="s">
-        <v>863</v>
+        <v>862</v>
       </c>
       <c r="V1" s="27" t="s">
         <v>616</v>
@@ -5953,16 +5950,16 @@
         <v>196</v>
       </c>
       <c r="AA1" s="27" t="s">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="AB1" s="27" t="s">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="AC1" s="27" t="s">
+        <v>896</v>
+      </c>
+      <c r="AD1" s="27" t="s">
         <v>897</v>
-      </c>
-      <c r="AD1" s="27" t="s">
-        <v>898</v>
       </c>
       <c r="AE1" s="27" t="s">
         <v>82</v>
@@ -6016,7 +6013,7 @@
         <v>200</v>
       </c>
       <c r="AV1" s="27" t="s">
-        <v>852</v>
+        <v>851</v>
       </c>
       <c r="AW1" s="27" t="s">
         <v>209</v>
@@ -6115,7 +6112,7 @@
         <v>795</v>
       </c>
       <c r="CC1" s="8" t="s">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="CD1" s="7" t="s">
         <v>280</v>
@@ -6205,10 +6202,10 @@
         <v>664</v>
       </c>
       <c r="DG1" s="18" t="s">
+        <v>840</v>
+      </c>
+      <c r="DH1" s="18" t="s">
         <v>841</v>
-      </c>
-      <c r="DH1" s="18" t="s">
-        <v>842</v>
       </c>
       <c r="DI1" s="15" t="s">
         <v>136</v>
@@ -6235,7 +6232,7 @@
         <v>603</v>
       </c>
       <c r="DQ1" s="15" t="s">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="DR1" s="15" t="s">
         <v>604</v>
@@ -6271,13 +6268,13 @@
         <v>558</v>
       </c>
       <c r="EC1" s="21" t="s">
-        <v>844</v>
+        <v>843</v>
       </c>
       <c r="ED1" s="25" t="s">
         <v>811</v>
       </c>
       <c r="EE1" s="12" t="s">
-        <v>843</v>
+        <v>842</v>
       </c>
       <c r="EF1" s="14" t="s">
         <v>607</v>
@@ -6286,7 +6283,7 @@
         <v>234</v>
       </c>
       <c r="EH1" s="12" t="s">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="EI1" s="12" t="s">
         <v>286</v>
@@ -6301,10 +6298,10 @@
         <v>125</v>
       </c>
       <c r="EM1" s="17" t="s">
-        <v>831</v>
+        <v>830</v>
       </c>
       <c r="EN1" s="17" t="s">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="EO1" s="17" t="s">
         <v>557</v>
@@ -6328,7 +6325,7 @@
         <v>231</v>
       </c>
       <c r="EV1" s="20" t="s">
-        <v>845</v>
+        <v>844</v>
       </c>
       <c r="EW1" s="20" t="s">
         <v>232</v>
@@ -34323,7 +34320,7 @@
     </row>
     <row r="159" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>814</v>
+        <v>813</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>278</v>
@@ -34513,7 +34510,7 @@
     </row>
     <row r="160" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>197</v>
@@ -34685,7 +34682,7 @@
     </row>
     <row r="161" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>830</v>
+        <v>829</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>51</v>
@@ -34869,7 +34866,7 @@
     </row>
     <row r="162" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>51</v>
@@ -35045,7 +35042,7 @@
     </row>
     <row r="163" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>51</v>
@@ -35225,7 +35222,7 @@
     </row>
     <row r="164" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>53</v>
@@ -35403,7 +35400,7 @@
     </row>
     <row r="165" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>862</v>
+        <v>861</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>51</v>
@@ -35579,7 +35576,7 @@
     </row>
     <row r="166" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>872</v>
+        <v>871</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>50</v>
@@ -35761,7 +35758,7 @@
     </row>
     <row r="167" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>888</v>
+        <v>887</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>53</v>
@@ -35939,7 +35936,7 @@
     </row>
     <row r="168" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>886</v>
+        <v>885</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>55</v>
@@ -36113,7 +36110,7 @@
     </row>
     <row r="169" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>55</v>
@@ -36291,7 +36288,7 @@
     </row>
     <row r="170" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>53</v>
@@ -36467,7 +36464,7 @@
     </row>
     <row r="171" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>55</v>
@@ -36643,7 +36640,7 @@
     </row>
     <row r="172" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>1056</v>
+        <v>1047</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>53</v>
@@ -36821,7 +36818,7 @@
     </row>
     <row r="173" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>1075</v>
+        <v>1066</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>52</v>
@@ -36997,7 +36994,7 @@
     </row>
     <row r="174" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>1076</v>
+        <v>1067</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>49</v>
@@ -37175,7 +37172,7 @@
     </row>
     <row r="175" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>1135</v>
+        <v>1126</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>55</v>
@@ -49064,7 +49061,7 @@
         <v>579</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="P1" s="8" t="s">
         <v>132</v>
@@ -58537,7 +58534,7 @@
         <v>315</v>
       </c>
       <c r="G1" s="7" t="s">
-        <v>960</v>
+        <v>954</v>
       </c>
       <c r="H1" s="7" t="s">
         <v>316</v>
@@ -58552,7 +58549,7 @@
         <v>762</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>961</v>
+        <v>955</v>
       </c>
       <c r="M1" s="7" t="s">
         <v>810</v>
@@ -58583,7 +58580,7 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="4" t="s">
-        <v>902</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58629,7 +58626,7 @@
         <v>239</v>
       </c>
       <c r="G4" s="4" t="s">
-        <v>964</v>
+        <v>958</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="5"/>
@@ -58665,7 +58662,7 @@
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
       <c r="M5" s="4" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="270" x14ac:dyDescent="0.25">
@@ -58693,7 +58690,7 @@
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="4" t="s">
-        <v>949</v>
+        <v>944</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="270" x14ac:dyDescent="0.25">
@@ -58702,7 +58699,7 @@
         <v>Amaretto Spritz</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1079</v>
+        <v>1070</v>
       </c>
       <c r="C7" s="4" t="s">
         <v>351</v>
@@ -58721,7 +58718,7 @@
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="4" t="s">
-        <v>950</v>
+        <v>945</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="210" x14ac:dyDescent="0.25">
@@ -58747,7 +58744,7 @@
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="4" t="s">
-        <v>1037</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -58775,7 +58772,7 @@
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
       <c r="M9" s="1" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="210" x14ac:dyDescent="0.25">
@@ -58806,7 +58803,7 @@
         <v>Aperol Spritz</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1079</v>
+        <v>1070</v>
       </c>
       <c r="C11" s="4" t="s">
         <v>598</v>
@@ -58823,7 +58820,7 @@
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="4" t="s">
-        <v>1054</v>
+        <v>1045</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58871,7 +58868,7 @@
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="4" t="s">
-        <v>966</v>
+        <v>960</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58899,7 +58896,7 @@
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="4" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58923,7 +58920,7 @@
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="4" t="s">
-        <v>1036</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -58935,13 +58932,13 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>959</v>
+        <v>953</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>958</v>
+        <v>952</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>962</v>
+        <v>956</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -59027,7 +59024,7 @@
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="4" t="s">
-        <v>967</v>
+        <v>961</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59079,7 +59076,7 @@
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="4" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="375" x14ac:dyDescent="0.25">
@@ -59107,7 +59104,7 @@
       <c r="K22" s="5"/>
       <c r="L22" s="5"/>
       <c r="M22" s="4" t="s">
-        <v>1066</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -59129,7 +59126,7 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="4" t="s">
-        <v>980</v>
+        <v>974</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="345" x14ac:dyDescent="0.25">
@@ -59177,7 +59174,7 @@
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="4" t="s">
-        <v>969</v>
+        <v>963</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59205,7 +59202,7 @@
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="4" t="s">
-        <v>986</v>
+        <v>980</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="375" x14ac:dyDescent="0.25">
@@ -59223,23 +59220,23 @@
         <v>674</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1112</v>
+        <v>1103</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>1111</v>
+        <v>1102</v>
       </c>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1" t="s">
-        <v>1114</v>
+        <v>1105</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>1113</v>
+        <v>1104</v>
       </c>
       <c r="L27" s="1"/>
       <c r="M27" s="4" t="s">
-        <v>970</v>
+        <v>964</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59252,7 +59249,7 @@
         <v>457</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>1047</v>
+        <v>1038</v>
       </c>
       <c r="E28" s="1" t="s">
         <v>527</v>
@@ -59264,14 +59261,14 @@
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
       <c r="J28" s="1" t="s">
-        <v>1049</v>
+        <v>1040</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>1048</v>
+        <v>1039</v>
       </c>
       <c r="L28" s="5"/>
       <c r="M28" s="4" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="360" x14ac:dyDescent="0.25">
@@ -59297,7 +59294,7 @@
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="4" t="s">
-        <v>926</v>
+        <v>923</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59312,16 +59309,16 @@
         <v>666</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>1119</v>
+        <v>1110</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>1108</v>
+        <v>1099</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>1106</v>
+        <v>1097</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>1107</v>
+        <v>1098</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -59329,7 +59326,7 @@
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="4" t="s">
-        <v>927</v>
+        <v>924</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59347,13 +59344,13 @@
         <v>424</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>996</v>
+        <v>989</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>993</v>
+        <v>986</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>994</v>
+        <v>987</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -59361,7 +59358,7 @@
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="4" t="s">
-        <v>971</v>
+        <v>965</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -59377,7 +59374,7 @@
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1" t="s">
-        <v>1125</v>
+        <v>1116</v>
       </c>
       <c r="F32" s="5" t="s">
         <v>334</v>
@@ -59399,7 +59396,7 @@
         <v>724</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>838</v>
+        <v>837</v>
       </c>
       <c r="D33" s="4" t="s">
         <v>547</v>
@@ -59417,7 +59414,7 @@
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="4" t="s">
-        <v>878</v>
+        <v>877</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="255" x14ac:dyDescent="0.25">
@@ -59443,7 +59440,7 @@
       <c r="K34" s="5"/>
       <c r="L34" s="5"/>
       <c r="M34" s="4" t="s">
-        <v>972</v>
+        <v>966</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -59459,10 +59456,10 @@
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="1" t="s">
-        <v>1087</v>
+        <v>1078</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>1086</v>
+        <v>1077</v>
       </c>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
@@ -59490,8 +59487,8 @@
       <c r="J36" s="1"/>
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
-      <c r="M36" s="1" t="s">
-        <v>953</v>
+      <c r="M36" s="4" t="s">
+        <v>1140</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59519,7 +59516,7 @@
       <c r="K37" s="5"/>
       <c r="L37" s="5"/>
       <c r="M37" s="4" t="s">
-        <v>937</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="255" x14ac:dyDescent="0.25">
@@ -59545,7 +59542,7 @@
       <c r="K38" s="5"/>
       <c r="L38" s="5"/>
       <c r="M38" s="4" t="s">
-        <v>983</v>
+        <v>977</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -59554,7 +59551,7 @@
         <v>Cynar Spritz</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>1079</v>
+        <v>1070</v>
       </c>
       <c r="C39" s="4" t="s">
         <v>333</v>
@@ -59569,7 +59566,7 @@
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="4" t="s">
-        <v>1050</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -59590,16 +59587,16 @@
       </c>
       <c r="G40" s="5"/>
       <c r="H40" s="1" t="s">
-        <v>922</v>
+        <v>919</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>923</v>
+        <v>920</v>
       </c>
       <c r="J40" s="4"/>
       <c r="K40" s="5"/>
       <c r="L40" s="5"/>
       <c r="M40" s="4" t="s">
-        <v>934</v>
+        <v>931</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -59611,7 +59608,7 @@
         <v>724</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>1055</v>
+        <v>1046</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="1"/>
@@ -59623,7 +59620,7 @@
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
       <c r="M41" s="4" t="s">
-        <v>1053</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59649,7 +59646,7 @@
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="M42" s="4" t="s">
-        <v>918</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="270" x14ac:dyDescent="0.25">
@@ -59665,13 +59662,13 @@
         <v>590</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>1131</v>
+        <v>1122</v>
       </c>
       <c r="F43" s="5" t="s">
-        <v>1130</v>
+        <v>1121</v>
       </c>
       <c r="G43" s="4" t="s">
-        <v>1132</v>
+        <v>1123</v>
       </c>
       <c r="H43" s="1" t="s">
         <v>257</v>
@@ -59683,7 +59680,7 @@
       <c r="K43" s="5"/>
       <c r="L43" s="5"/>
       <c r="M43" s="4" t="s">
-        <v>919</v>
+        <v>916</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -59729,7 +59726,7 @@
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
       <c r="M45" s="4" t="s">
-        <v>1039</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="285" x14ac:dyDescent="0.25">
@@ -59742,7 +59739,7 @@
       </c>
       <c r="C46" s="4"/>
       <c r="D46" s="4" t="s">
-        <v>981</v>
+        <v>975</v>
       </c>
       <c r="E46" s="4" t="s">
         <v>185</v>
@@ -59754,16 +59751,16 @@
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
       <c r="J46" s="4" t="s">
-        <v>1027</v>
+        <v>1018</v>
       </c>
       <c r="K46" s="5" t="s">
-        <v>1026</v>
+        <v>1017</v>
       </c>
       <c r="L46" s="4" t="s">
-        <v>1028</v>
+        <v>1019</v>
       </c>
       <c r="M46" s="4" t="s">
-        <v>980</v>
+        <v>974</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -59791,7 +59788,7 @@
       <c r="K47" s="5"/>
       <c r="L47" s="5"/>
       <c r="M47" s="4" t="s">
-        <v>933</v>
+        <v>930</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="315" x14ac:dyDescent="0.25">
@@ -59839,7 +59836,7 @@
         <v>767</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>974</v>
+        <v>968</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -59847,7 +59844,7 @@
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
       <c r="M49" s="4" t="s">
-        <v>998</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="255" x14ac:dyDescent="0.25">
@@ -59867,7 +59864,7 @@
         <v>480</v>
       </c>
       <c r="G50" s="4" t="s">
-        <v>973</v>
+        <v>967</v>
       </c>
       <c r="H50" s="1" t="s">
         <v>326</v>
@@ -59879,7 +59876,7 @@
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
       <c r="M50" s="4" t="s">
-        <v>955</v>
+        <v>949</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59901,7 +59898,7 @@
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
       <c r="M51" s="4" t="s">
-        <v>1141</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="150" x14ac:dyDescent="0.25">
@@ -59933,7 +59930,7 @@
       </c>
       <c r="L52" s="1"/>
       <c r="M52" s="4" t="s">
-        <v>931</v>
+        <v>928</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="390" x14ac:dyDescent="0.25">
@@ -59955,7 +59952,7 @@
         <v>403</v>
       </c>
       <c r="G53" s="4" t="s">
-        <v>997</v>
+        <v>990</v>
       </c>
       <c r="H53" s="1" t="s">
         <v>383</v>
@@ -59964,16 +59961,16 @@
         <v>382</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>1099</v>
+        <v>1090</v>
       </c>
       <c r="K53" s="5" t="s">
-        <v>1098</v>
+        <v>1089</v>
       </c>
       <c r="L53" s="1" t="s">
-        <v>1100</v>
+        <v>1091</v>
       </c>
       <c r="M53" s="4" t="s">
-        <v>987</v>
+        <v>981</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59999,7 +59996,7 @@
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
       <c r="M54" s="4" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="55" spans="1:13" x14ac:dyDescent="0.25">
@@ -60045,7 +60042,7 @@
         <v>472</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>975</v>
+        <v>969</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -60053,7 +60050,7 @@
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
       <c r="M56" s="4" t="s">
-        <v>951</v>
+        <v>946</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -60081,7 +60078,7 @@
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
       <c r="M57" s="4" t="s">
-        <v>957</v>
+        <v>951</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="150" x14ac:dyDescent="0.25">
@@ -60105,7 +60102,7 @@
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="4" t="s">
-        <v>954</v>
+        <v>948</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60123,13 +60120,13 @@
         <v>357</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>1093</v>
+        <v>1084</v>
       </c>
       <c r="F59" s="5" t="s">
-        <v>1094</v>
+        <v>1085</v>
       </c>
       <c r="G59" s="4" t="s">
-        <v>1095</v>
+        <v>1086</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
@@ -60141,7 +60138,7 @@
       </c>
       <c r="L59" s="5"/>
       <c r="M59" s="4" t="s">
-        <v>952</v>
+        <v>947</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -60163,7 +60160,7 @@
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
       <c r="M60" s="4" t="s">
-        <v>976</v>
+        <v>970</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="165" x14ac:dyDescent="0.25">
@@ -60179,10 +60176,10 @@
         <v>387</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="4"/>
@@ -60191,7 +60188,7 @@
       <c r="K61" s="1"/>
       <c r="L61" s="1"/>
       <c r="M61" s="4" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="345" x14ac:dyDescent="0.25">
@@ -60217,7 +60214,7 @@
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
       <c r="M62" s="4" t="s">
-        <v>985</v>
+        <v>979</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60250,10 +60247,10 @@
         <v>764</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>963</v>
+        <v>957</v>
       </c>
       <c r="M63" s="4" t="s">
-        <v>925</v>
+        <v>922</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -60267,10 +60264,10 @@
       </c>
       <c r="D64" s="1"/>
       <c r="E64" s="1" t="s">
-        <v>1102</v>
+        <v>1093</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>1101</v>
+        <v>1092</v>
       </c>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
@@ -60279,7 +60276,7 @@
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
       <c r="M64" s="4" t="s">
-        <v>984</v>
+        <v>978</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60302,8 +60299,8 @@
       <c r="J65" s="1"/>
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
-      <c r="M65" s="1" t="s">
-        <v>921</v>
+      <c r="M65" s="4" t="s">
+        <v>918</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="375" x14ac:dyDescent="0.25">
@@ -60312,7 +60309,7 @@
         <v>Hugo</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>1080</v>
+        <v>1071</v>
       </c>
       <c r="C66" s="4" t="s">
         <v>731</v>
@@ -60329,7 +60326,7 @@
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
       <c r="M66" s="4" t="s">
-        <v>1051</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="67" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60355,7 +60352,7 @@
       <c r="K67" s="5"/>
       <c r="L67" s="5"/>
       <c r="M67" s="4" t="s">
-        <v>948</v>
+        <v>943</v>
       </c>
     </row>
     <row r="68" spans="1:13" ht="330" x14ac:dyDescent="0.25">
@@ -60365,7 +60362,7 @@
       </c>
       <c r="B68" s="1"/>
       <c r="C68" s="4" t="s">
-        <v>942</v>
+        <v>937</v>
       </c>
       <c r="D68" s="4" t="s">
         <v>592</v>
@@ -60380,16 +60377,16 @@
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
       <c r="J68" s="1" t="s">
-        <v>1121</v>
+        <v>1112</v>
       </c>
       <c r="K68" s="5" t="s">
-        <v>1120</v>
+        <v>1111</v>
       </c>
       <c r="L68" s="4" t="s">
-        <v>1122</v>
+        <v>1113</v>
       </c>
       <c r="M68" s="4" t="s">
-        <v>941</v>
+        <v>936</v>
       </c>
     </row>
     <row r="69" spans="1:13" ht="300" x14ac:dyDescent="0.25">
@@ -60417,7 +60414,7 @@
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
       <c r="M69" s="4" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -60445,7 +60442,7 @@
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
       <c r="M70" s="4" t="s">
-        <v>938</v>
+        <v>933</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -60471,7 +60468,7 @@
       <c r="K71" s="5"/>
       <c r="L71" s="5"/>
       <c r="M71" s="4" t="s">
-        <v>929</v>
+        <v>926</v>
       </c>
     </row>
     <row r="72" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60486,16 +60483,16 @@
         <v>632</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>866</v>
+        <v>865</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>1091</v>
+        <v>1082</v>
       </c>
       <c r="F72" s="5" t="s">
-        <v>1090</v>
+        <v>1081</v>
       </c>
       <c r="G72" s="4" t="s">
-        <v>1092</v>
+        <v>1083</v>
       </c>
       <c r="H72" s="1" t="s">
         <v>414</v>
@@ -60507,7 +60504,7 @@
       <c r="K72" s="5"/>
       <c r="L72" s="5"/>
       <c r="M72" s="4" t="s">
-        <v>867</v>
+        <v>866</v>
       </c>
     </row>
     <row r="73" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -60520,7 +60517,7 @@
       </c>
       <c r="C73" s="4"/>
       <c r="D73" s="4" t="s">
-        <v>1062</v>
+        <v>1053</v>
       </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
@@ -60531,7 +60528,7 @@
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
       <c r="M73" s="4" t="s">
-        <v>1063</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="74" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60585,7 +60582,7 @@
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
       <c r="M75" s="4" t="s">
-        <v>1052</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="76" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60621,10 +60618,10 @@
       </c>
       <c r="B77" s="1"/>
       <c r="C77" s="4" t="s">
-        <v>1008</v>
+        <v>1000</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>1009</v>
+        <v>1001</v>
       </c>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
@@ -60635,7 +60632,7 @@
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
       <c r="M77" s="4" t="s">
-        <v>1007</v>
+        <v>999</v>
       </c>
     </row>
     <row r="78" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -60675,10 +60672,10 @@
       <c r="C79" s="4"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1" t="s">
-        <v>1126</v>
+        <v>1117</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>1127</v>
+        <v>1118</v>
       </c>
       <c r="G79" s="1"/>
       <c r="H79" s="1"/>
@@ -60753,7 +60750,7 @@
       <c r="K82" s="1"/>
       <c r="L82" s="1"/>
       <c r="M82" s="4" t="s">
-        <v>1065</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60763,7 +60760,7 @@
       </c>
       <c r="B83" s="1"/>
       <c r="C83" s="4" t="s">
-        <v>880</v>
+        <v>879</v>
       </c>
       <c r="D83" s="4" t="s">
         <v>304</v>
@@ -60781,7 +60778,7 @@
       <c r="K83" s="5"/>
       <c r="L83" s="5"/>
       <c r="M83" s="4" t="s">
-        <v>879</v>
+        <v>878</v>
       </c>
     </row>
     <row r="84" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60796,7 +60793,7 @@
         <v>658</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
@@ -60811,7 +60808,7 @@
       <c r="K84" s="1"/>
       <c r="L84" s="1"/>
       <c r="M84" s="4" t="s">
-        <v>978</v>
+        <v>972</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -60826,7 +60823,7 @@
         <v>659</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>869</v>
+        <v>868</v>
       </c>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
@@ -60841,7 +60838,7 @@
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
       <c r="M85" s="4" t="s">
-        <v>979</v>
+        <v>973</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -60891,7 +60888,7 @@
       <c r="K87" s="5"/>
       <c r="L87" s="5"/>
       <c r="M87" s="4" t="s">
-        <v>936</v>
+        <v>932</v>
       </c>
     </row>
     <row r="88" spans="1:13" ht="360" x14ac:dyDescent="0.25">
@@ -60906,7 +60903,7 @@
         <v>634</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>1074</v>
+        <v>1065</v>
       </c>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
@@ -60917,7 +60914,7 @@
       <c r="K88" s="1"/>
       <c r="L88" s="1"/>
       <c r="M88" s="4" t="s">
-        <v>1064</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="89" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -60939,7 +60936,7 @@
         <v>180</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>1071</v>
+        <v>1062</v>
       </c>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
@@ -60947,7 +60944,7 @@
       <c r="K89" s="5"/>
       <c r="L89" s="5"/>
       <c r="M89" s="4" t="s">
-        <v>1069</v>
+        <v>1060</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
@@ -60968,10 +60965,10 @@
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
       <c r="J90" s="1" t="s">
-        <v>1116</v>
+        <v>1107</v>
       </c>
       <c r="K90" s="5" t="s">
-        <v>1115</v>
+        <v>1106</v>
       </c>
       <c r="L90" s="5"/>
       <c r="M90" s="1"/>
@@ -60989,7 +60986,7 @@
       </c>
       <c r="D91" s="1"/>
       <c r="E91" s="1" t="s">
-        <v>1125</v>
+        <v>1116</v>
       </c>
       <c r="F91" s="5" t="s">
         <v>334</v>
@@ -61008,10 +61005,10 @@
         <v>Michelada</v>
       </c>
       <c r="B92" s="4" t="s">
+        <v>838</v>
+      </c>
+      <c r="C92" s="4" t="s">
         <v>839</v>
-      </c>
-      <c r="C92" s="4" t="s">
-        <v>840</v>
       </c>
       <c r="D92" s="4" t="s">
         <v>400</v>
@@ -61026,10 +61023,10 @@
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
       <c r="J92" s="1" t="s">
-        <v>1097</v>
+        <v>1088</v>
       </c>
       <c r="K92" s="5" t="s">
-        <v>1096</v>
+        <v>1087</v>
       </c>
       <c r="L92" s="5"/>
       <c r="M92" s="1"/>
@@ -61053,7 +61050,7 @@
       <c r="K93" s="1"/>
       <c r="L93" s="1"/>
       <c r="M93" s="4" t="s">
-        <v>1041</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="94" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -61075,7 +61072,7 @@
       <c r="K94" s="1"/>
       <c r="L94" s="1"/>
       <c r="M94" s="4" t="s">
-        <v>1059</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="95" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -61099,7 +61096,7 @@
       <c r="K95" s="1"/>
       <c r="L95" s="1"/>
       <c r="M95" s="4" t="s">
-        <v>990</v>
+        <v>983</v>
       </c>
     </row>
     <row r="96" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -61132,13 +61129,13 @@
         <v>577</v>
       </c>
       <c r="D97" s="4" t="s">
-        <v>988</v>
+        <v>982</v>
       </c>
       <c r="E97" s="1" t="s">
-        <v>992</v>
+        <v>985</v>
       </c>
       <c r="F97" s="5" t="s">
-        <v>991</v>
+        <v>984</v>
       </c>
       <c r="G97" s="1"/>
       <c r="H97" s="4"/>
@@ -61147,7 +61144,7 @@
       <c r="K97" s="1"/>
       <c r="L97" s="1"/>
       <c r="M97" s="4" t="s">
-        <v>989</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="98" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -61156,7 +61153,7 @@
         <v>Mojito Spritz</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>1079</v>
+        <v>1070</v>
       </c>
       <c r="C98" s="4" t="s">
         <v>723</v>
@@ -61195,7 +61192,7 @@
       <c r="K99" s="5"/>
       <c r="L99" s="5"/>
       <c r="M99" s="4" t="s">
-        <v>924</v>
+        <v>921</v>
       </c>
     </row>
     <row r="100" spans="1:13" ht="150" x14ac:dyDescent="0.25">
@@ -61223,7 +61220,7 @@
       <c r="K100" s="5"/>
       <c r="L100" s="5"/>
       <c r="M100" s="4" t="s">
-        <v>1085</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="101" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -61271,7 +61268,7 @@
       <c r="K102" s="1"/>
       <c r="L102" s="1"/>
       <c r="M102" s="4" t="s">
-        <v>965</v>
+        <v>959</v>
       </c>
     </row>
     <row r="103" spans="1:13" ht="210" x14ac:dyDescent="0.25">
@@ -61293,7 +61290,7 @@
       <c r="K103" s="1"/>
       <c r="L103" s="1"/>
       <c r="M103" s="4" t="s">
-        <v>1035</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="104" spans="1:13" ht="345" x14ac:dyDescent="0.25">
@@ -61323,7 +61320,7 @@
       <c r="K104" s="5"/>
       <c r="L104" s="5"/>
       <c r="M104" s="4" t="s">
-        <v>1002</v>
+        <v>994</v>
       </c>
     </row>
     <row r="105" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -61349,7 +61346,7 @@
       <c r="K105" s="1"/>
       <c r="L105" s="1"/>
       <c r="M105" s="4" t="s">
-        <v>940</v>
+        <v>935</v>
       </c>
     </row>
     <row r="106" spans="1:13" ht="375" x14ac:dyDescent="0.25">
@@ -61365,25 +61362,25 @@
         <v>562</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>1033</v>
+        <v>1024</v>
       </c>
       <c r="F106" s="5" t="s">
+        <v>1025</v>
+      </c>
+      <c r="G106" s="4" t="s">
+        <v>1023</v>
+      </c>
+      <c r="H106" s="4" t="s">
+        <v>1037</v>
+      </c>
+      <c r="I106" s="5" t="s">
         <v>1034</v>
-      </c>
-      <c r="G106" s="4" t="s">
-        <v>1032</v>
-      </c>
-      <c r="H106" s="4" t="s">
-        <v>1046</v>
-      </c>
-      <c r="I106" s="5" t="s">
-        <v>1043</v>
       </c>
       <c r="J106" s="1"/>
       <c r="K106" s="1"/>
       <c r="L106" s="1"/>
       <c r="M106" s="4" t="s">
-        <v>1044</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="107" spans="1:13" ht="192" customHeight="1" x14ac:dyDescent="0.25">
@@ -61422,7 +61419,7 @@
       <c r="F108" s="1"/>
       <c r="G108" s="1"/>
       <c r="H108" s="1" t="s">
-        <v>956</v>
+        <v>950</v>
       </c>
       <c r="I108" s="5" t="s">
         <v>256</v>
@@ -61431,7 +61428,7 @@
       <c r="K108" s="1"/>
       <c r="L108" s="1"/>
       <c r="M108" s="4" t="s">
-        <v>1045</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="109" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -61466,7 +61463,7 @@
         <v>671</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>1000</v>
+        <v>992</v>
       </c>
       <c r="E110" s="4" t="s">
         <v>582</v>
@@ -61481,7 +61478,7 @@
       <c r="K110" s="5"/>
       <c r="L110" s="5"/>
       <c r="M110" s="4" t="s">
-        <v>1001</v>
+        <v>993</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.25">
@@ -61525,7 +61522,7 @@
         <v>482</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>1072</v>
+        <v>1063</v>
       </c>
       <c r="H112" s="1"/>
       <c r="I112" s="5"/>
@@ -61557,7 +61554,7 @@
       <c r="K113" s="5"/>
       <c r="L113" s="5"/>
       <c r="M113" s="4" t="s">
-        <v>1068</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.25">
@@ -61648,14 +61645,14 @@
       <c r="H117" s="1"/>
       <c r="I117" s="1"/>
       <c r="J117" s="4" t="s">
-        <v>1123</v>
+        <v>1114</v>
       </c>
       <c r="K117" s="5" t="s">
-        <v>1124</v>
+        <v>1115</v>
       </c>
       <c r="L117" s="5"/>
       <c r="M117" s="4" t="s">
-        <v>1006</v>
+        <v>998</v>
       </c>
     </row>
     <row r="118" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -61709,7 +61706,7 @@
       <c r="K119" s="5"/>
       <c r="L119" s="5"/>
       <c r="M119" s="4" t="s">
-        <v>1004</v>
+        <v>996</v>
       </c>
     </row>
     <row r="120" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -61718,7 +61715,7 @@
         <v>Ramazzotti Spritz</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>1079</v>
+        <v>1070</v>
       </c>
       <c r="C120" s="4" t="s">
         <v>352</v>
@@ -61744,17 +61741,17 @@
         <v>Ramazzotti Violetto Spritz</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>1079</v>
+        <v>1070</v>
       </c>
       <c r="C121" s="4" t="s">
         <v>745</v>
       </c>
       <c r="D121" s="1"/>
       <c r="E121" s="1" t="s">
-        <v>1089</v>
+        <v>1080</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>1088</v>
+        <v>1079</v>
       </c>
       <c r="G121" s="1"/>
       <c r="H121" s="1"/>
@@ -61813,7 +61810,7 @@
       <c r="K123" s="5"/>
       <c r="L123" s="5"/>
       <c r="M123" s="4" t="s">
-        <v>920</v>
+        <v>917</v>
       </c>
     </row>
     <row r="124" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -61862,10 +61859,10 @@
       <c r="H125" s="5"/>
       <c r="I125" s="1"/>
       <c r="J125" s="1" t="s">
-        <v>1134</v>
+        <v>1125</v>
       </c>
       <c r="K125" s="5" t="s">
-        <v>1133</v>
+        <v>1124</v>
       </c>
       <c r="L125" s="1"/>
       <c r="M125" s="1"/>
@@ -61933,7 +61930,7 @@
       <c r="K128" s="1"/>
       <c r="L128" s="1"/>
       <c r="M128" s="4" t="s">
-        <v>1003</v>
+        <v>995</v>
       </c>
     </row>
     <row r="129" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -61946,7 +61943,7 @@
         <v>368</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
       <c r="E129" s="1"/>
       <c r="F129" s="1"/>
@@ -61957,7 +61954,7 @@
       <c r="K129" s="1"/>
       <c r="L129" s="1"/>
       <c r="M129" s="4" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
     </row>
     <row r="130" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -61999,7 +61996,7 @@
       <c r="K131" s="1"/>
       <c r="L131" s="1"/>
       <c r="M131" s="4" t="s">
-        <v>1070</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="132" spans="1:13" ht="165" x14ac:dyDescent="0.25">
@@ -62025,7 +62022,7 @@
       <c r="K132" s="5"/>
       <c r="L132" s="5"/>
       <c r="M132" s="4" t="s">
-        <v>1040</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.25">
@@ -62061,10 +62058,10 @@
         <v>593</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>1118</v>
+        <v>1109</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>1117</v>
+        <v>1108</v>
       </c>
       <c r="G134" s="5"/>
       <c r="H134" s="4"/>
@@ -62077,7 +62074,7 @@
       </c>
       <c r="L134" s="5"/>
       <c r="M134" s="4" t="s">
-        <v>935</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="135" spans="1:13" ht="300" x14ac:dyDescent="0.25">
@@ -62089,25 +62086,25 @@
         <v>650</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>947</v>
+        <v>942</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>945</v>
+        <v>940</v>
       </c>
       <c r="E135" s="1"/>
       <c r="F135" s="1"/>
       <c r="G135" s="1"/>
       <c r="H135" s="1" t="s">
-        <v>944</v>
+        <v>939</v>
       </c>
       <c r="I135" s="5" t="s">
-        <v>943</v>
+        <v>938</v>
       </c>
       <c r="J135" s="1"/>
       <c r="K135" s="1"/>
       <c r="L135" s="1"/>
       <c r="M135" s="4" t="s">
-        <v>946</v>
+        <v>941</v>
       </c>
     </row>
     <row r="136" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -62147,13 +62144,13 @@
         <v>432</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>1030</v>
+        <v>1021</v>
       </c>
       <c r="F137" s="5" t="s">
-        <v>1029</v>
+        <v>1020</v>
       </c>
       <c r="G137" s="4" t="s">
-        <v>1031</v>
+        <v>1022</v>
       </c>
       <c r="H137" s="1"/>
       <c r="I137" s="1"/>
@@ -62181,7 +62178,7 @@
       <c r="K138" s="1"/>
       <c r="L138" s="1"/>
       <c r="M138" s="4" t="s">
-        <v>928</v>
+        <v>925</v>
       </c>
     </row>
     <row r="139" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -62223,13 +62220,13 @@
         <v>344</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>1016</v>
+        <v>1007</v>
       </c>
       <c r="F140" s="5" t="s">
-        <v>1015</v>
+        <v>1006</v>
       </c>
       <c r="G140" s="4" t="s">
-        <v>1017</v>
+        <v>1008</v>
       </c>
       <c r="H140" s="1"/>
       <c r="I140" s="1"/>
@@ -62241,7 +62238,7 @@
       </c>
       <c r="L140" s="5"/>
       <c r="M140" s="4" t="s">
-        <v>1005</v>
+        <v>997</v>
       </c>
     </row>
     <row r="141" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62256,7 +62253,7 @@
         <v>682</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="E141" s="4" t="s">
         <v>609</v>
@@ -62323,7 +62320,7 @@
       <c r="K143" s="1"/>
       <c r="L143" s="1"/>
       <c r="M143" s="4" t="s">
-        <v>932</v>
+        <v>929</v>
       </c>
     </row>
     <row r="144" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62346,20 +62343,20 @@
       </c>
       <c r="G144" s="1"/>
       <c r="H144" s="1" t="s">
-        <v>1021</v>
+        <v>1012</v>
       </c>
       <c r="I144" s="5" t="s">
-        <v>1022</v>
+        <v>1013</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>1019</v>
+        <v>1010</v>
       </c>
       <c r="K144" s="5" t="s">
-        <v>1020</v>
+        <v>1011</v>
       </c>
       <c r="L144" s="1"/>
       <c r="M144" s="4" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
     </row>
     <row r="145" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62389,7 +62386,7 @@
       <c r="K145" s="1"/>
       <c r="L145" s="1"/>
       <c r="M145" s="4" t="s">
-        <v>1042</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="146" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -62435,7 +62432,7 @@
       <c r="K147" s="5"/>
       <c r="L147" s="5"/>
       <c r="M147" s="4" t="s">
-        <v>939</v>
+        <v>934</v>
       </c>
     </row>
     <row r="148" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -62461,7 +62458,7 @@
       <c r="K148" s="5"/>
       <c r="L148" s="5"/>
       <c r="M148" s="4" t="s">
-        <v>1081</v>
+        <v>1072</v>
       </c>
     </row>
     <row r="149" spans="1:13" ht="324" customHeight="1" x14ac:dyDescent="0.25">
@@ -62489,7 +62486,7 @@
       <c r="K149" s="5"/>
       <c r="L149" s="5"/>
       <c r="M149" s="4" t="s">
-        <v>1067</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="150" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62519,7 +62516,7 @@
       <c r="K150" s="1"/>
       <c r="L150" s="1"/>
       <c r="M150" s="4" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
     </row>
     <row r="151" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -62549,7 +62546,7 @@
       <c r="K151" s="1"/>
       <c r="L151" s="1"/>
       <c r="M151" s="4" t="s">
-        <v>1061</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="152" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -62575,7 +62572,7 @@
       <c r="K152" s="1"/>
       <c r="L152" s="1"/>
       <c r="M152" s="4" t="s">
-        <v>1010</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="153" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -62616,7 +62613,7 @@
         <v>782</v>
       </c>
       <c r="D154" s="26" t="s">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>780</v>
@@ -62634,7 +62631,7 @@
         <v>769</v>
       </c>
       <c r="L154" s="26" t="s">
-        <v>977</v>
+        <v>971</v>
       </c>
       <c r="M154" s="1"/>
     </row>
@@ -62650,7 +62647,7 @@
         <v>797</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>1073</v>
+        <v>1064</v>
       </c>
       <c r="E155" s="1"/>
       <c r="F155" s="1"/>
@@ -62661,7 +62658,7 @@
       <c r="K155" s="1"/>
       <c r="L155" s="1"/>
       <c r="M155" s="4" t="s">
-        <v>1060</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="156" spans="1:13" ht="255" x14ac:dyDescent="0.25">
@@ -62724,30 +62721,30 @@
         <v>Vino Navegado</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="D158" s="10"/>
       <c r="E158" s="1" t="s">
-        <v>858</v>
+        <v>857</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="G158" s="1"/>
       <c r="H158" s="1"/>
       <c r="I158" s="5"/>
       <c r="J158" s="4" t="s">
-        <v>1139</v>
+        <v>1130</v>
       </c>
       <c r="K158" s="5" t="s">
-        <v>1140</v>
+        <v>1131</v>
       </c>
       <c r="L158" s="1"/>
-      <c r="M158" s="10" t="s">
-        <v>812</v>
+      <c r="M158" s="4" t="s">
+        <v>1133</v>
       </c>
     </row>
     <row r="159" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62756,32 +62753,32 @@
         <v>Cola de Mono</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>846</v>
+        <v>845</v>
       </c>
       <c r="C159" s="4" t="s">
-        <v>817</v>
+        <v>816</v>
       </c>
       <c r="D159" s="4" t="s">
-        <v>821</v>
+        <v>820</v>
       </c>
       <c r="E159" s="1" t="s">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="F159" s="5" t="s">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="G159" s="5"/>
       <c r="H159" s="1" t="s">
-        <v>828</v>
+        <v>827</v>
       </c>
       <c r="I159" s="10" t="s">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="J159" s="1"/>
       <c r="K159" s="1"/>
       <c r="L159" s="1"/>
       <c r="M159" s="4" t="s">
-        <v>930</v>
+        <v>927</v>
       </c>
     </row>
     <row r="160" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62790,34 +62787,34 @@
         <v>Chichón</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>825</v>
+        <v>824</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>1014</v>
+        <v>1005</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>1012</v>
+        <v>1003</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>1013</v>
+        <v>1004</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>1011</v>
+        <v>1002</v>
       </c>
       <c r="H160" s="1"/>
       <c r="I160" s="5"/>
       <c r="J160" s="1" t="s">
-        <v>1128</v>
+        <v>1119</v>
       </c>
       <c r="K160" s="5" t="s">
-        <v>1129</v>
+        <v>1120</v>
       </c>
       <c r="L160" s="1"/>
       <c r="M160" s="4" t="s">
-        <v>1018</v>
+        <v>1009</v>
       </c>
     </row>
     <row r="161" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -62826,10 +62823,10 @@
         <v>Ramos Fizz</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>837</v>
+        <v>836</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>1083</v>
+        <v>1074</v>
       </c>
       <c r="D161" s="4"/>
       <c r="E161" s="1"/>
@@ -62841,7 +62838,7 @@
       <c r="K161" s="1"/>
       <c r="L161" s="1"/>
       <c r="M161" s="4" t="s">
-        <v>1084</v>
+        <v>1075</v>
       </c>
     </row>
     <row r="162" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -62850,17 +62847,17 @@
         <v>Gin Fizz</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="D162" s="4"/>
       <c r="E162" s="1" t="s">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>834</v>
+        <v>833</v>
       </c>
       <c r="G162" s="5"/>
       <c r="H162" s="5"/>
@@ -62877,16 +62874,16 @@
       </c>
       <c r="B163" s="1"/>
       <c r="C163" s="4" t="s">
+        <v>848</v>
+      </c>
+      <c r="D163" s="4" t="s">
+        <v>847</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>1073</v>
+      </c>
+      <c r="F163" s="5" t="s">
         <v>849</v>
-      </c>
-      <c r="D163" s="4" t="s">
-        <v>848</v>
-      </c>
-      <c r="E163" s="1" t="s">
-        <v>1082</v>
-      </c>
-      <c r="F163" s="5" t="s">
-        <v>850</v>
       </c>
       <c r="G163" s="5"/>
       <c r="H163" s="1"/>
@@ -62895,7 +62892,7 @@
       <c r="K163" s="1"/>
       <c r="L163" s="1"/>
       <c r="M163" s="4" t="s">
-        <v>968</v>
+        <v>962</v>
       </c>
     </row>
     <row r="164" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62905,29 +62902,29 @@
       </c>
       <c r="B164" s="4"/>
       <c r="C164" s="4" t="s">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="G164" s="5"/>
       <c r="H164" s="1"/>
       <c r="I164" s="5"/>
       <c r="J164" s="1" t="s">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="K164" s="1" t="s">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="L164" s="1"/>
       <c r="M164" s="4" t="s">
-        <v>855</v>
+        <v>854</v>
       </c>
     </row>
     <row r="165" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62936,22 +62933,22 @@
         <v>Pihuelo</v>
       </c>
       <c r="B165" s="4" t="s">
+        <v>863</v>
+      </c>
+      <c r="C165" s="4" t="s">
         <v>864</v>
       </c>
-      <c r="C165" s="4" t="s">
-        <v>865</v>
-      </c>
       <c r="D165" s="4" t="s">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="E165" s="4" t="s">
-        <v>1023</v>
+        <v>1014</v>
       </c>
       <c r="F165" s="5" t="s">
-        <v>1024</v>
+        <v>1015</v>
       </c>
       <c r="G165" s="1" t="s">
-        <v>1025</v>
+        <v>1016</v>
       </c>
       <c r="H165" s="1"/>
       <c r="I165" s="5"/>
@@ -62959,7 +62956,7 @@
       <c r="K165" s="1"/>
       <c r="L165" s="1"/>
       <c r="M165" s="4" t="s">
-        <v>982</v>
+        <v>976</v>
       </c>
     </row>
     <row r="166" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62968,19 +62965,19 @@
         <v>Mojito Sandía</v>
       </c>
       <c r="B166" s="4" t="s">
+        <v>875</v>
+      </c>
+      <c r="C166" s="4" t="s">
         <v>876</v>
       </c>
-      <c r="C166" s="4" t="s">
-        <v>877</v>
-      </c>
       <c r="D166" s="4" t="s">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="E166" s="1" t="s">
+        <v>873</v>
+      </c>
+      <c r="F166" s="5" t="s">
         <v>874</v>
-      </c>
-      <c r="F166" s="5" t="s">
-        <v>875</v>
       </c>
       <c r="G166" s="5"/>
       <c r="H166" s="1"/>
@@ -62989,7 +62986,7 @@
       <c r="K166" s="1"/>
       <c r="L166" s="1"/>
       <c r="M166" s="4" t="s">
-        <v>882</v>
+        <v>881</v>
       </c>
     </row>
     <row r="167" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62999,7 +62996,7 @@
       </c>
       <c r="B167" s="1"/>
       <c r="C167" s="4" t="s">
-        <v>887</v>
+        <v>886</v>
       </c>
       <c r="D167" s="4"/>
       <c r="E167" s="1"/>
@@ -63011,7 +63008,7 @@
       <c r="K167" s="1"/>
       <c r="L167" s="1"/>
       <c r="M167" s="4" t="s">
-        <v>1038</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="168" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -63021,7 +63018,7 @@
       </c>
       <c r="B168" s="1"/>
       <c r="C168" s="4" t="s">
-        <v>995</v>
+        <v>988</v>
       </c>
       <c r="D168" s="4"/>
       <c r="E168" s="1"/>
@@ -63033,7 +63030,7 @@
       <c r="K168" s="1"/>
       <c r="L168" s="1"/>
       <c r="M168" s="4" t="s">
-        <v>999</v>
+        <v>991</v>
       </c>
     </row>
     <row r="169" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -63042,28 +63039,28 @@
         <v>Chardonnay Sour</v>
       </c>
       <c r="B169" s="4" t="s">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="C169" s="4" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="D169" s="4"/>
       <c r="E169" s="1" t="s">
-        <v>1104</v>
+        <v>1095</v>
       </c>
       <c r="F169" s="5" t="s">
-        <v>1103</v>
+        <v>1094</v>
       </c>
       <c r="G169" s="4" t="s">
-        <v>1105</v>
+        <v>1096</v>
       </c>
       <c r="H169" s="1"/>
       <c r="I169" s="5"/>
       <c r="J169" s="1" t="s">
-        <v>1110</v>
+        <v>1101</v>
       </c>
       <c r="K169" s="5" t="s">
-        <v>1109</v>
+        <v>1100</v>
       </c>
       <c r="L169" s="1"/>
       <c r="M169" s="1"/>
@@ -63074,13 +63071,13 @@
         <v>Carmenere Sour</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>469</v>
@@ -63095,7 +63092,7 @@
       <c r="K170" s="1"/>
       <c r="L170" s="1"/>
       <c r="M170" s="4" t="s">
-        <v>894</v>
+        <v>893</v>
       </c>
     </row>
     <row r="171" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -63104,13 +63101,13 @@
         <v>Jerez Sour</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="E171" s="1"/>
       <c r="F171" s="1"/>
@@ -63121,7 +63118,7 @@
       <c r="K171" s="1"/>
       <c r="L171" s="1"/>
       <c r="M171" s="4" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
     </row>
     <row r="172" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -63131,7 +63128,7 @@
       </c>
       <c r="B172" s="4"/>
       <c r="C172" s="4" t="s">
-        <v>1057</v>
+        <v>1048</v>
       </c>
       <c r="D172" s="4"/>
       <c r="E172" s="1"/>
@@ -63143,7 +63140,7 @@
       <c r="K172" s="1"/>
       <c r="L172" s="1"/>
       <c r="M172" s="4" t="s">
-        <v>1058</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="173" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -63163,7 +63160,7 @@
       <c r="K173" s="1"/>
       <c r="L173" s="1"/>
       <c r="M173" s="4" t="s">
-        <v>1078</v>
+        <v>1069</v>
       </c>
     </row>
     <row r="174" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -63172,7 +63169,7 @@
         <v>Campari Spritz</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>1079</v>
+        <v>1070</v>
       </c>
       <c r="C174" s="4"/>
       <c r="D174" s="4"/>
@@ -63185,7 +63182,7 @@
       <c r="K174" s="1"/>
       <c r="L174" s="1"/>
       <c r="M174" s="4" t="s">
-        <v>1077</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="175" spans="1:13" ht="255" x14ac:dyDescent="0.25">
@@ -63194,10 +63191,10 @@
         <v>Hanky Panky</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>1137</v>
+        <v>1128</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>1136</v>
+        <v>1127</v>
       </c>
       <c r="D175" s="4"/>
       <c r="E175" s="1"/>
@@ -63209,7 +63206,7 @@
       <c r="K175" s="1"/>
       <c r="L175" s="1"/>
       <c r="M175" s="4" t="s">
-        <v>1138</v>
+        <v>1129</v>
       </c>
     </row>
     <row r="176" spans="1:13" x14ac:dyDescent="0.25">

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F29714D9-5901-41BF-8C9D-777EF728EA1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1AC86AD-3E72-435A-B61E-2FA00316BB25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1703" uniqueCount="1142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1709" uniqueCount="1148">
   <si>
     <t>Ramazzotti Spritz</t>
   </si>
@@ -5237,6 +5237,30 @@
   <si>
     <t>Antonio_Machado_por_Leandro_Oroz_(1925).jpg
 Retrato de Antonio Machado (1875 - 1939), sanguina de Leandro Oroz Lacalle,  1925.</t>
+  </si>
+  <si>
+    <t>Frase célebre
+“Si bebes para olvidar, paga antes de empezar” 
+Refrán recopilado por J. V. Caruda en la sección El refranero hoy, dirigida por Julia Sevilla Muñoz, Paremia, Nº 5, Madrid, 1996.</t>
+  </si>
+  <si>
+    <t>feria_bretona.jpg
+Título: “Feria bretona”
+Autor: Pierre Vinit
+Técnica: Témpera sobre Papel
+Año: ?</t>
+  </si>
+  <si>
+    <t>Todos estos yanquis rojos/Son hijos de un camarón,/Y los parió una botella,/Una botella de ron./¿quién los llamó?/Ustedes viven,/Me muero yo,/Comen y beben,/Pero yo no,/Pero yo no.</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=xlBgXb2u4o0</t>
+  </si>
+  <si>
+    <t>Leo Maslíah - La Primera Sobriedad</t>
+  </si>
+  <si>
+    <t>Cerrame el ventanal que enfrente está/el bar que me dio esta cirrosis/no ves que estoy que me hago pis/por una copita de anis, o un Gin Fiss.</t>
   </si>
 </sst>
 </file>
@@ -59585,7 +59609,9 @@
       <c r="F40" s="5" t="s">
         <v>404</v>
       </c>
-      <c r="G40" s="5"/>
+      <c r="G40" s="4" t="s">
+        <v>1144</v>
+      </c>
       <c r="H40" s="1" t="s">
         <v>919</v>
       </c>
@@ -59999,7 +60025,7 @@
         <v>908</v>
       </c>
     </row>
-    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:13" ht="90" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="str">
         <f>IF(receta!A55="","",receta!A55)</f>
         <v>Feria Libre</v>
@@ -60008,7 +60034,9 @@
       <c r="C55" s="1" t="s">
         <v>370</v>
       </c>
-      <c r="D55" s="1"/>
+      <c r="D55" s="4" t="s">
+        <v>1142</v>
+      </c>
       <c r="E55" s="1" t="s">
         <v>183</v>
       </c>
@@ -60021,7 +60049,9 @@
       <c r="J55" s="1"/>
       <c r="K55" s="5"/>
       <c r="L55" s="5"/>
-      <c r="M55" s="1"/>
+      <c r="M55" s="4" t="s">
+        <v>1143</v>
+      </c>
     </row>
     <row r="56" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="str">
@@ -62862,9 +62892,15 @@
       <c r="G162" s="5"/>
       <c r="H162" s="5"/>
       <c r="I162" s="5"/>
-      <c r="J162" s="1"/>
-      <c r="K162" s="1"/>
-      <c r="L162" s="1"/>
+      <c r="J162" s="1" t="s">
+        <v>1146</v>
+      </c>
+      <c r="K162" s="5" t="s">
+        <v>1145</v>
+      </c>
+      <c r="L162" s="4" t="s">
+        <v>1147</v>
+      </c>
       <c r="M162" s="1"/>
     </row>
     <row r="163" spans="1:13" ht="255" x14ac:dyDescent="0.25">
@@ -64663,9 +64699,10 @@
     <hyperlink ref="F43" r:id="rId98" xr:uid="{8CF791BE-869A-4F43-9C91-AF8E24DC71C9}"/>
     <hyperlink ref="K125" r:id="rId99" xr:uid="{F4AC4FB8-FB91-4049-878D-BBEAAE2B5094}"/>
     <hyperlink ref="K158" r:id="rId100" xr:uid="{C198DB91-C048-4B59-BF1D-EE0F56806A3D}"/>
+    <hyperlink ref="K162" r:id="rId101" xr:uid="{13A99BFB-962B-44AF-937F-DBDFF58BD18C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId101"/>
+  <pageSetup orientation="portrait" r:id="rId102"/>
 </worksheet>
 </file>
 

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1AC86AD-3E72-435A-B61E-2FA00316BB25}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC8D022-961C-42C0-91B0-4E65FE3A386B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
@@ -21,7 +21,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">complementos!$A$1:$AE$250</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">receta!$A$1:$EW$174</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">receta!$A$1:$EW$175</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">recurso!$A$1:$M$250</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1709" uniqueCount="1148">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1711" uniqueCount="1150">
   <si>
     <t>Ramazzotti Spritz</t>
   </si>
@@ -489,9 +489,6 @@
   </si>
   <si>
     <t>Cimarrón</t>
-  </si>
-  <si>
-    <t>Destornillador</t>
   </si>
   <si>
     <t>Piña Colada</t>
@@ -2922,10 +2919,6 @@
     <t xml:space="preserve">The Champs - Tequila	</t>
   </si>
   <si>
-    <t>El Destornillador (en inglés Screwdriver), también conocido como Vodka con Naranja o simplemente Vodka Naranja, se cree que fue creado durante la Ley Seca estadounidense (1920–1933), época en la que el alcohol se disfrazaba como un inocente jugo de naranja.
-Otra teoría señala que, en los años 50, los obreros estadounidenses usaban un destornillador para remover la mezcla, ya que no contaban con cucharas a mano, lo que habría dado origen al nombre del cóctel.</t>
-  </si>
-  <si>
     <t>Anita Bryant.
 Existe una versión alternativa del cóctel Destornillador llamada Anita Bryant, en la que el jugo de naranja se reemplaza por jugo de manzana. El nombre hace referencia a Anita Bryant, cantante estadounidense y rostro de la Florida Citrus Commission (Comisión de Cítricos de Florida) durante las décadas de 1960 y 1970. A partir de 1977, Bryant se convirtió en una activa opositora de los derechos LGTB.
 Debido a su rol como imagen de los productores de naranjas, muchos bares gay en Estados Unidos dejaron de servir destornilladores y crearon esta nueva variante como forma de protesta.
@@ -5261,6 +5254,21 @@
   </si>
   <si>
     <t>Cerrame el ventanal que enfrente está/el bar que me dio esta cirrosis/no ves que estoy que me hago pis/por una copita de anis, o un Gin Fiss.</t>
+  </si>
+  <si>
+    <t>Beatles.jpg
+The Beatles en su última sesión fotográfica el 22 de agosto de 1969, en el parque Tittenhurst, propiedad de John Lennon, apenas unas semanas después de terminar Abbey Road.</t>
+  </si>
+  <si>
+    <t>Vodka Naranja</t>
+  </si>
+  <si>
+    <t>El Vodka Naranja o Destornillador (en inglés Screwdriver), se cree que fue creado durante la Ley Seca estadounidense (1920–1933), época en la que el alcohol se disfrazaba como un inocente jugo de naranja.
+Otra teoría señala que, en los años 50, los obreros estadounidenses usaban un destornillador para remover la mezcla, ya que no contaban con cucharas a mano, lo que habría dado origen al nombre en inglés del cóctel.</t>
+  </si>
+  <si>
+    <t>California_Clipper_500.jpg
+Pasaje de un barco clipper que muestra escenas de la Fiebre del Oro de California, alrededor de 1850, y resalta su papel en el transporte de buscadores de fortuna hacia San Francisco. Un clipper era un tipo de velero rápido del siglo XIX, diseñado para recorrer grandes distancias en el menor tiempo posible. La Fiebre del Oro de California comenzó en 1848, cuando se descubrió oro en Sutter’s Mill, cerca del río American. La noticia se difundió rápidamente y, entre 1849 y comienzos de la década de 1850, cientos de miles de personas viajaron a California para buscar fortuna. Como consecuencia, San Francisco pasó en pocos años de ser un pequeño puerto a convertirse en una ciudad importante.</t>
   </si>
 </sst>
 </file>
@@ -5829,6 +5837,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7FAA63B-DEDB-48F1-9CCA-3BF0BF1CD86F}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:EW250"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -5932,34 +5941,34 @@
         <v>77</v>
       </c>
       <c r="M1" s="27" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="N1" s="27" t="s">
         <v>78</v>
       </c>
       <c r="O1" s="27" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="P1" s="27" t="s">
-        <v>690</v>
+        <v>688</v>
       </c>
       <c r="Q1" s="27" t="s">
         <v>79</v>
       </c>
       <c r="R1" s="27" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="S1" s="27" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="T1" s="27" t="s">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="U1" s="27" t="s">
-        <v>862</v>
+        <v>860</v>
       </c>
       <c r="V1" s="27" t="s">
-        <v>616</v>
+        <v>614</v>
       </c>
       <c r="W1" s="27" t="s">
         <v>80</v>
@@ -5968,22 +5977,22 @@
         <v>81</v>
       </c>
       <c r="Y1" s="27" t="s">
+        <v>194</v>
+      </c>
+      <c r="Z1" s="27" t="s">
         <v>195</v>
       </c>
-      <c r="Z1" s="27" t="s">
-        <v>196</v>
-      </c>
       <c r="AA1" s="27" t="s">
-        <v>823</v>
+        <v>821</v>
       </c>
       <c r="AB1" s="27" t="s">
-        <v>822</v>
+        <v>820</v>
       </c>
       <c r="AC1" s="27" t="s">
-        <v>896</v>
+        <v>894</v>
       </c>
       <c r="AD1" s="27" t="s">
-        <v>897</v>
+        <v>895</v>
       </c>
       <c r="AE1" s="27" t="s">
         <v>82</v>
@@ -5992,7 +6001,7 @@
         <v>83</v>
       </c>
       <c r="AG1" s="27" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="AH1" s="27" t="s">
         <v>84</v>
@@ -6001,7 +6010,7 @@
         <v>85</v>
       </c>
       <c r="AJ1" s="27" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="AK1" s="27" t="s">
         <v>86</v>
@@ -6010,16 +6019,16 @@
         <v>87</v>
       </c>
       <c r="AM1" s="27" t="s">
-        <v>549</v>
+        <v>548</v>
       </c>
       <c r="AN1" s="27" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AO1" s="27" t="s">
         <v>88</v>
       </c>
       <c r="AP1" s="27" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="AQ1" s="27" t="s">
         <v>90</v>
@@ -6031,31 +6040,31 @@
         <v>92</v>
       </c>
       <c r="AT1" s="27" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="AU1" s="27" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AV1" s="27" t="s">
-        <v>851</v>
+        <v>849</v>
       </c>
       <c r="AW1" s="27" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="AX1" s="27" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="AY1" s="27" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="AZ1" s="27" t="s">
         <v>93</v>
       </c>
       <c r="BA1" s="27" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="BB1" s="27" t="s">
-        <v>301</v>
+        <v>300</v>
       </c>
       <c r="BC1" s="27" t="s">
         <v>94</v>
@@ -6085,22 +6094,22 @@
         <v>106</v>
       </c>
       <c r="BL1" s="8" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="BM1" s="8" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="BN1" s="8" t="s">
         <v>107</v>
       </c>
       <c r="BO1" s="8" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="BP1" s="8" t="s">
         <v>108</v>
       </c>
       <c r="BQ1" s="8" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="BR1" s="8" t="s">
         <v>109</v>
@@ -6115,13 +6124,13 @@
         <v>112</v>
       </c>
       <c r="BV1" s="8" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="BW1" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="BX1" s="8" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="BY1" s="8" t="s">
         <v>113</v>
@@ -6130,22 +6139,22 @@
         <v>114</v>
       </c>
       <c r="CA1" s="8" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="CB1" s="8" t="s">
-        <v>795</v>
+        <v>793</v>
       </c>
       <c r="CC1" s="8" t="s">
-        <v>815</v>
+        <v>813</v>
       </c>
       <c r="CD1" s="7" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="CE1" s="7" t="s">
-        <v>573</v>
+        <v>572</v>
       </c>
       <c r="CF1" s="8" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="CG1" s="8" t="s">
         <v>121</v>
@@ -6169,16 +6178,16 @@
         <v>120</v>
       </c>
       <c r="CN1" s="8" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="CO1" s="8" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="CP1" s="8" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="CQ1" s="8" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="CR1" s="7" t="s">
         <v>95</v>
@@ -6190,16 +6199,16 @@
         <v>97</v>
       </c>
       <c r="CU1" s="7" t="s">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="CV1" s="7" t="s">
-        <v>384</v>
+        <v>383</v>
       </c>
       <c r="CW1" s="7" t="s">
         <v>98</v>
       </c>
       <c r="CX1" s="7" t="s">
-        <v>485</v>
+        <v>484</v>
       </c>
       <c r="CY1" s="7" t="s">
         <v>99</v>
@@ -6208,28 +6217,28 @@
         <v>122</v>
       </c>
       <c r="DA1" s="7" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="DB1" s="7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="DC1" s="8" t="s">
-        <v>617</v>
+        <v>615</v>
       </c>
       <c r="DD1" s="18" t="s">
-        <v>665</v>
+        <v>663</v>
       </c>
       <c r="DE1" s="18" t="s">
-        <v>668</v>
+        <v>666</v>
       </c>
       <c r="DF1" s="18" t="s">
-        <v>664</v>
+        <v>662</v>
       </c>
       <c r="DG1" s="18" t="s">
-        <v>840</v>
+        <v>838</v>
       </c>
       <c r="DH1" s="18" t="s">
-        <v>841</v>
+        <v>839</v>
       </c>
       <c r="DI1" s="15" t="s">
         <v>136</v>
@@ -6238,79 +6247,79 @@
         <v>135</v>
       </c>
       <c r="DK1" s="15" t="s">
-        <v>670</v>
+        <v>668</v>
       </c>
       <c r="DL1" s="15" t="s">
+        <v>565</v>
+      </c>
+      <c r="DM1" s="15" t="s">
         <v>566</v>
       </c>
-      <c r="DM1" s="15" t="s">
-        <v>567</v>
-      </c>
       <c r="DN1" s="15" t="s">
-        <v>697</v>
+        <v>695</v>
       </c>
       <c r="DO1" s="15" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="DP1" s="15" t="s">
-        <v>603</v>
+        <v>601</v>
       </c>
       <c r="DQ1" s="15" t="s">
-        <v>812</v>
+        <v>810</v>
       </c>
       <c r="DR1" s="15" t="s">
-        <v>604</v>
+        <v>602</v>
       </c>
       <c r="DS1" s="15" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="DT1" s="15" t="s">
         <v>141</v>
       </c>
       <c r="DU1" s="15" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="DV1" s="15" t="s">
+        <v>603</v>
+      </c>
+      <c r="DW1" s="15" t="s">
+        <v>567</v>
+      </c>
+      <c r="DX1" s="15" t="s">
+        <v>807</v>
+      </c>
+      <c r="DY1" s="15" t="s">
+        <v>600</v>
+      </c>
+      <c r="DZ1" s="15" t="s">
+        <v>564</v>
+      </c>
+      <c r="EA1" s="15" t="s">
+        <v>554</v>
+      </c>
+      <c r="EB1" s="21" t="s">
+        <v>557</v>
+      </c>
+      <c r="EC1" s="21" t="s">
+        <v>841</v>
+      </c>
+      <c r="ED1" s="25" t="s">
+        <v>809</v>
+      </c>
+      <c r="EE1" s="12" t="s">
+        <v>840</v>
+      </c>
+      <c r="EF1" s="14" t="s">
         <v>605</v>
       </c>
-      <c r="DW1" s="15" t="s">
-        <v>568</v>
-      </c>
-      <c r="DX1" s="15" t="s">
-        <v>809</v>
-      </c>
-      <c r="DY1" s="15" t="s">
-        <v>602</v>
-      </c>
-      <c r="DZ1" s="15" t="s">
-        <v>565</v>
-      </c>
-      <c r="EA1" s="15" t="s">
-        <v>555</v>
-      </c>
-      <c r="EB1" s="21" t="s">
-        <v>558</v>
-      </c>
-      <c r="EC1" s="21" t="s">
-        <v>843</v>
-      </c>
-      <c r="ED1" s="25" t="s">
-        <v>811</v>
-      </c>
-      <c r="EE1" s="12" t="s">
-        <v>842</v>
-      </c>
-      <c r="EF1" s="14" t="s">
-        <v>607</v>
-      </c>
       <c r="EG1" s="12" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="EH1" s="12" t="s">
-        <v>814</v>
+        <v>812</v>
       </c>
       <c r="EI1" s="12" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="EJ1" s="16" t="s">
         <v>123</v>
@@ -6322,19 +6331,19 @@
         <v>125</v>
       </c>
       <c r="EM1" s="17" t="s">
-        <v>830</v>
+        <v>828</v>
       </c>
       <c r="EN1" s="17" t="s">
-        <v>817</v>
+        <v>815</v>
       </c>
       <c r="EO1" s="17" t="s">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="EP1" s="19" t="s">
-        <v>608</v>
+        <v>606</v>
       </c>
       <c r="EQ1" s="19" t="s">
-        <v>618</v>
+        <v>616</v>
       </c>
       <c r="ER1" s="19" t="s">
         <v>126</v>
@@ -6346,21 +6355,21 @@
         <v>128</v>
       </c>
       <c r="EU1" s="20" t="s">
+        <v>230</v>
+      </c>
+      <c r="EV1" s="20" t="s">
+        <v>842</v>
+      </c>
+      <c r="EW1" s="20" t="s">
         <v>231</v>
       </c>
-      <c r="EV1" s="20" t="s">
-        <v>844</v>
-      </c>
-      <c r="EW1" s="20" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="2" spans="1:153" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C2" s="2" t="s">
         <v>63</v>
@@ -6537,9 +6546,9 @@
       <c r="EV2" s="2"/>
       <c r="EW2" s="2"/>
     </row>
-    <row r="3" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>55</v>
@@ -6713,12 +6722,12 @@
       <c r="EV3" s="2"/>
       <c r="EW3" s="2"/>
     </row>
-    <row r="4" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C4" s="2" t="s">
         <v>63</v>
@@ -6893,9 +6902,9 @@
       <c r="EV4" s="2"/>
       <c r="EW4" s="2"/>
     </row>
-    <row r="5" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>55</v>
@@ -7069,7 +7078,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>42</v>
       </c>
@@ -7249,7 +7258,7 @@
       <c r="EV6" s="2"/>
       <c r="EW6" s="2"/>
     </row>
-    <row r="7" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>41</v>
       </c>
@@ -7427,7 +7436,7 @@
       <c r="EV7" s="2"/>
       <c r="EW7" s="2"/>
     </row>
-    <row r="8" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>31</v>
       </c>
@@ -7605,9 +7614,9 @@
       <c r="EV8" s="2"/>
       <c r="EW8" s="2"/>
     </row>
-    <row r="9" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>50</v>
@@ -7785,15 +7794,15 @@
       <c r="EV9" s="2"/>
       <c r="EW9" s="2"/>
     </row>
-    <row r="10" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
-        <v>572</v>
+        <v>571</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>51</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="D10" s="2">
         <v>300</v>
@@ -7967,7 +7976,7 @@
       <c r="EV10" s="2"/>
       <c r="EW10" s="2"/>
     </row>
-    <row r="11" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
@@ -8145,15 +8154,15 @@
       <c r="EV11" s="2"/>
       <c r="EW11" s="2"/>
     </row>
-    <row r="12" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>55</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="D12" s="2">
         <v>200</v>
@@ -8325,9 +8334,9 @@
       <c r="EV12" s="2"/>
       <c r="EW12" s="2"/>
     </row>
-    <row r="13" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>55</v>
@@ -8497,9 +8506,9 @@
       <c r="EV13" s="2"/>
       <c r="EW13" s="2"/>
     </row>
-    <row r="14" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>50</v>
@@ -8679,9 +8688,9 @@
       <c r="EV14" s="2"/>
       <c r="EW14" s="2"/>
     </row>
-    <row r="15" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>55</v>
@@ -8853,12 +8862,12 @@
       <c r="EV15" s="2"/>
       <c r="EW15" s="2"/>
     </row>
-    <row r="16" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
-        <v>600</v>
+        <v>598</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C16" s="2" t="s">
         <v>63</v>
@@ -9031,7 +9040,7 @@
       <c r="EV16" s="2"/>
       <c r="EW16" s="2"/>
     </row>
-    <row r="17" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>23</v>
       </c>
@@ -9217,9 +9226,9 @@
       <c r="EV17" s="2"/>
       <c r="EW17" s="2"/>
     </row>
-    <row r="18" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>50</v>
@@ -9403,12 +9412,12 @@
       <c r="EV18" s="2"/>
       <c r="EW18" s="2"/>
     </row>
-    <row r="19" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C19" s="2" t="s">
         <v>62</v>
@@ -9581,12 +9590,12 @@
       <c r="EV19" s="2"/>
       <c r="EW19" s="2"/>
     </row>
-    <row r="20" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>68</v>
@@ -9759,12 +9768,12 @@
       <c r="EV20" s="2"/>
       <c r="EW20" s="2"/>
     </row>
-    <row r="21" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C21" s="2" t="s">
         <v>63</v>
@@ -9937,9 +9946,9 @@
       <c r="EV21" s="2"/>
       <c r="EW21" s="2"/>
     </row>
-    <row r="22" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
-        <v>563</v>
+        <v>562</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>53</v>
@@ -10115,9 +10124,9 @@
       <c r="EV22" s="2"/>
       <c r="EW22" s="2"/>
     </row>
-    <row r="23" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>53</v>
@@ -10293,7 +10302,7 @@
       <c r="EV23" s="2"/>
       <c r="EW23" s="2"/>
     </row>
-    <row r="24" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>47</v>
       </c>
@@ -10465,7 +10474,7 @@
       <c r="EV24" s="2"/>
       <c r="EW24" s="2"/>
     </row>
-    <row r="25" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>27</v>
       </c>
@@ -10645,9 +10654,9 @@
       <c r="EV25" s="2"/>
       <c r="EW25" s="2"/>
     </row>
-    <row r="26" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
-        <v>484</v>
+        <v>483</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>50</v>
@@ -10823,9 +10832,9 @@
       <c r="EV26" s="2"/>
       <c r="EW26" s="2"/>
     </row>
-    <row r="27" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
-        <v>673</v>
+        <v>671</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>51</v>
@@ -11001,7 +11010,7 @@
       <c r="EV27" s="2"/>
       <c r="EW27" s="2"/>
     </row>
-    <row r="28" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>147</v>
       </c>
@@ -11179,7 +11188,7 @@
       <c r="EV28" s="2"/>
       <c r="EW28" s="2"/>
     </row>
-    <row r="29" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>38</v>
       </c>
@@ -11355,12 +11364,12 @@
       <c r="EV29" s="2"/>
       <c r="EW29" s="2"/>
     </row>
-    <row r="30" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>695</v>
+        <v>693</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C30" s="2" t="s">
         <v>63</v>
@@ -11533,12 +11542,12 @@
       <c r="EV30" s="2"/>
       <c r="EW30" s="2"/>
     </row>
-    <row r="31" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C31" s="2" t="s">
         <v>63</v>
@@ -11711,12 +11720,12 @@
       <c r="EV31" s="2"/>
       <c r="EW31" s="2"/>
     </row>
-    <row r="32" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
-        <v>696</v>
+        <v>694</v>
       </c>
       <c r="B32" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C32" s="2" t="s">
         <v>63</v>
@@ -11889,9 +11898,9 @@
       <c r="EV32" s="2"/>
       <c r="EW32" s="2"/>
     </row>
-    <row r="33" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
-        <v>513</v>
+        <v>512</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>55</v>
@@ -12065,9 +12074,9 @@
       <c r="EV33" s="2"/>
       <c r="EW33" s="2"/>
     </row>
-    <row r="34" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>51</v>
@@ -12247,9 +12256,9 @@
       <c r="EV34" s="2"/>
       <c r="EW34" s="2"/>
     </row>
-    <row r="35" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="B35" s="1" t="s">
         <v>54</v>
@@ -12423,9 +12432,9 @@
       <c r="EV35" s="2"/>
       <c r="EW35" s="2"/>
     </row>
-    <row r="36" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
-        <v>511</v>
+        <v>510</v>
       </c>
       <c r="B36" s="1" t="s">
         <v>54</v>
@@ -12599,15 +12608,15 @@
       <c r="EV36" s="2"/>
       <c r="EW36" s="2"/>
     </row>
-    <row r="37" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
-        <v>571</v>
+        <v>570</v>
       </c>
       <c r="B37" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="D37" s="2">
         <v>300</v>
@@ -12781,9 +12790,9 @@
       <c r="EV37" s="2"/>
       <c r="EW37" s="2"/>
     </row>
-    <row r="38" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
-        <v>505</v>
+        <v>504</v>
       </c>
       <c r="B38" s="1" t="s">
         <v>50</v>
@@ -12959,9 +12968,9 @@
       <c r="EV38" s="2"/>
       <c r="EW38" s="2"/>
     </row>
-    <row r="39" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="B39" s="1" t="s">
         <v>49</v>
@@ -13137,7 +13146,7 @@
       <c r="EV39" s="2"/>
       <c r="EW39" s="2"/>
     </row>
-    <row r="40" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>28</v>
       </c>
@@ -13311,9 +13320,9 @@
       <c r="EV40" s="2"/>
       <c r="EW40" s="2"/>
     </row>
-    <row r="41" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B41" s="1" t="s">
         <v>55</v>
@@ -13489,7 +13498,7 @@
       <c r="EV41" s="2"/>
       <c r="EW41" s="2"/>
     </row>
-    <row r="42" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>26</v>
       </c>
@@ -13669,7 +13678,7 @@
     </row>
     <row r="43" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="s">
-        <v>148</v>
+        <v>1147</v>
       </c>
       <c r="B43" s="1" t="s">
         <v>50</v>
@@ -13845,12 +13854,12 @@
       <c r="EV43" s="2"/>
       <c r="EW43" s="2"/>
     </row>
-    <row r="44" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="B44" s="1" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="C44" s="2" t="s">
         <v>63</v>
@@ -14017,9 +14026,9 @@
       <c r="EV44" s="2"/>
       <c r="EW44" s="2"/>
     </row>
-    <row r="45" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="B45" s="1" t="s">
         <v>54</v>
@@ -14189,7 +14198,7 @@
       <c r="EV45" s="2"/>
       <c r="EW45" s="2"/>
     </row>
-    <row r="46" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>46</v>
       </c>
@@ -14369,9 +14378,9 @@
       <c r="EV46" s="2"/>
       <c r="EW46" s="2"/>
     </row>
-    <row r="47" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="B47" s="1" t="s">
         <v>51</v>
@@ -14547,9 +14556,9 @@
       <c r="EV47" s="2"/>
       <c r="EW47" s="2"/>
     </row>
-    <row r="48" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="B48" s="1" t="s">
         <v>52</v>
@@ -14725,12 +14734,12 @@
       <c r="EV48" s="2"/>
       <c r="EW48" s="2"/>
     </row>
-    <row r="49" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
-        <v>294</v>
+        <v>293</v>
       </c>
       <c r="B49" s="1" t="s">
-        <v>297</v>
+        <v>296</v>
       </c>
       <c r="C49" s="2" t="s">
         <v>63</v>
@@ -14907,9 +14916,9 @@
       <c r="EV49" s="2"/>
       <c r="EW49" s="2"/>
     </row>
-    <row r="50" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
-        <v>478</v>
+        <v>477</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>53</v>
@@ -15087,9 +15096,9 @@
       <c r="EV50" s="2"/>
       <c r="EW50" s="2"/>
     </row>
-    <row r="51" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
-        <v>491</v>
+        <v>490</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>55</v>
@@ -15263,9 +15272,9 @@
       <c r="EV51" s="2"/>
       <c r="EW51" s="2"/>
     </row>
-    <row r="52" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B52" s="1" t="s">
         <v>51</v>
@@ -15447,9 +15456,9 @@
       <c r="EV52" s="2"/>
       <c r="EW52" s="2"/>
     </row>
-    <row r="53" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="B53" s="1" t="s">
         <v>56</v>
@@ -15619,9 +15628,9 @@
       <c r="EV53" s="2"/>
       <c r="EW53" s="2"/>
     </row>
-    <row r="54" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="B54" s="1" t="s">
         <v>50</v>
@@ -15799,7 +15808,7 @@
       <c r="EV54" s="2"/>
       <c r="EW54" s="2"/>
     </row>
-    <row r="55" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>14</v>
       </c>
@@ -15981,9 +15990,9 @@
       <c r="EV55" s="2"/>
       <c r="EW55" s="2"/>
     </row>
-    <row r="56" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
-        <v>393</v>
+        <v>392</v>
       </c>
       <c r="B56" s="1" t="s">
         <v>51</v>
@@ -16157,9 +16166,9 @@
       <c r="EV56" s="2"/>
       <c r="EW56" s="2"/>
     </row>
-    <row r="57" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="B57" s="1" t="s">
         <v>51</v>
@@ -16335,7 +16344,7 @@
       <c r="EV57" s="2"/>
       <c r="EW57" s="2"/>
     </row>
-    <row r="58" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>43</v>
       </c>
@@ -16515,9 +16524,9 @@
       <c r="EV58" s="2"/>
       <c r="EW58" s="2"/>
     </row>
-    <row r="59" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
-        <v>353</v>
+        <v>352</v>
       </c>
       <c r="B59" s="1" t="s">
         <v>55</v>
@@ -16691,9 +16700,9 @@
       <c r="EV59" s="2"/>
       <c r="EW59" s="2"/>
     </row>
-    <row r="60" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>51</v>
@@ -16869,7 +16878,7 @@
       <c r="EV60" s="2"/>
       <c r="EW60" s="2"/>
     </row>
-    <row r="61" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>20</v>
       </c>
@@ -17043,7 +17052,7 @@
       <c r="EV61" s="2"/>
       <c r="EW61" s="2"/>
     </row>
-    <row r="62" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>9</v>
       </c>
@@ -17219,7 +17228,7 @@
       <c r="EV62" s="2"/>
       <c r="EW62" s="2"/>
     </row>
-    <row r="63" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>4</v>
       </c>
@@ -17395,9 +17404,9 @@
       <c r="EV63" s="2"/>
       <c r="EW63" s="2"/>
     </row>
-    <row r="64" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
-        <v>689</v>
+        <v>687</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>50</v>
@@ -17573,7 +17582,7 @@
       <c r="EV64" s="2"/>
       <c r="EW64" s="2"/>
     </row>
-    <row r="65" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>29</v>
       </c>
@@ -17751,9 +17760,9 @@
       <c r="EV65" s="2"/>
       <c r="EW65" s="2"/>
     </row>
-    <row r="66" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>49</v>
@@ -17929,9 +17938,9 @@
       <c r="EV66" s="2"/>
       <c r="EW66" s="2"/>
     </row>
-    <row r="67" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="B67" s="1" t="s">
         <v>50</v>
@@ -18107,7 +18116,7 @@
       <c r="EV67" s="2"/>
       <c r="EW67" s="2"/>
     </row>
-    <row r="68" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>12</v>
       </c>
@@ -18287,9 +18296,9 @@
       <c r="EV68" s="2"/>
       <c r="EW68" s="2"/>
     </row>
-    <row r="69" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
-        <v>428</v>
+        <v>427</v>
       </c>
       <c r="B69" s="1" t="s">
         <v>55</v>
@@ -18463,9 +18472,9 @@
       <c r="EV69" s="2"/>
       <c r="EW69" s="2"/>
     </row>
-    <row r="70" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
-        <v>396</v>
+        <v>395</v>
       </c>
       <c r="B70" s="1" t="s">
         <v>51</v>
@@ -18645,9 +18654,9 @@
       <c r="EV70" s="2"/>
       <c r="EW70" s="2"/>
     </row>
-    <row r="71" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="B71" s="1" t="s">
         <v>50</v>
@@ -18825,9 +18834,9 @@
       <c r="EV71" s="2"/>
       <c r="EW71" s="2"/>
     </row>
-    <row r="72" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
-        <v>386</v>
+        <v>385</v>
       </c>
       <c r="B72" s="1" t="s">
         <v>50</v>
@@ -19001,12 +19010,12 @@
       <c r="EV72" s="2"/>
       <c r="EW72" s="2"/>
     </row>
-    <row r="73" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
+        <v>558</v>
+      </c>
+      <c r="B73" s="3" t="s">
         <v>559</v>
-      </c>
-      <c r="B73" s="3" t="s">
-        <v>560</v>
       </c>
       <c r="C73" s="1" t="s">
         <v>69</v>
@@ -19181,9 +19190,9 @@
       <c r="EV73" s="2"/>
       <c r="EW73" s="2"/>
     </row>
-    <row r="74" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
-        <v>698</v>
+        <v>696</v>
       </c>
       <c r="B74" s="1" t="s">
         <v>51</v>
@@ -19357,9 +19366,9 @@
       <c r="EV74" s="2"/>
       <c r="EW74" s="2"/>
     </row>
-    <row r="75" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="B75" s="1" t="s">
         <v>55</v>
@@ -19529,12 +19538,12 @@
       <c r="EV75" s="2"/>
       <c r="EW75" s="2"/>
     </row>
-    <row r="76" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="B76" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C76" s="2" t="s">
         <v>63</v>
@@ -19709,12 +19718,12 @@
       <c r="EV76" s="2"/>
       <c r="EW76" s="2"/>
     </row>
-    <row r="77" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="B77" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C77" s="2" t="s">
         <v>63</v>
@@ -19889,7 +19898,7 @@
       <c r="EV77" s="2"/>
       <c r="EW77" s="2"/>
     </row>
-    <row r="78" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>22</v>
       </c>
@@ -20067,7 +20076,7 @@
       <c r="EV78" s="2"/>
       <c r="EW78" s="2"/>
     </row>
-    <row r="79" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A79" s="11" t="s">
         <v>7</v>
       </c>
@@ -20251,9 +20260,9 @@
       <c r="EV79" s="2"/>
       <c r="EW79" s="2"/>
     </row>
-    <row r="80" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="B80" s="1" t="s">
         <v>50</v>
@@ -20433,9 +20442,9 @@
       <c r="EV80" s="2"/>
       <c r="EW80" s="2"/>
     </row>
-    <row r="81" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
-        <v>714</v>
+        <v>712</v>
       </c>
       <c r="B81" s="1" t="s">
         <v>51</v>
@@ -20611,9 +20620,9 @@
       <c r="EV81" s="2"/>
       <c r="EW81" s="2"/>
     </row>
-    <row r="82" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
-        <v>715</v>
+        <v>713</v>
       </c>
       <c r="B82" s="1" t="s">
         <v>50</v>
@@ -20795,9 +20804,9 @@
       <c r="EV82" s="2"/>
       <c r="EW82" s="2"/>
     </row>
-    <row r="83" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
-        <v>299</v>
+        <v>298</v>
       </c>
       <c r="B83" s="1" t="s">
         <v>53</v>
@@ -20975,9 +20984,9 @@
       <c r="EV83" s="2"/>
       <c r="EW83" s="2"/>
     </row>
-    <row r="84" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
-        <v>612</v>
+        <v>610</v>
       </c>
       <c r="B84" s="1" t="s">
         <v>51</v>
@@ -21151,9 +21160,9 @@
       <c r="EV84" s="2"/>
       <c r="EW84" s="2"/>
     </row>
-    <row r="85" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
-        <v>615</v>
+        <v>613</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>51</v>
@@ -21323,7 +21332,7 @@
       <c r="EV85" s="2"/>
       <c r="EW85" s="2"/>
     </row>
-    <row r="86" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>39</v>
       </c>
@@ -21499,7 +21508,7 @@
       <c r="EV86" s="2"/>
       <c r="EW86" s="2"/>
     </row>
-    <row r="87" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>32</v>
       </c>
@@ -21673,9 +21682,9 @@
       <c r="EV87" s="2"/>
       <c r="EW87" s="2"/>
     </row>
-    <row r="88" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>55</v>
@@ -21851,7 +21860,7 @@
       <c r="EV88" s="2"/>
       <c r="EW88" s="2"/>
     </row>
-    <row r="89" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>15</v>
       </c>
@@ -22027,7 +22036,7 @@
       <c r="EV89" s="2"/>
       <c r="EW89" s="2"/>
     </row>
-    <row r="90" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>16</v>
       </c>
@@ -22205,12 +22214,12 @@
       <c r="EV90" s="2"/>
       <c r="EW90" s="2"/>
     </row>
-    <row r="91" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
-        <v>677</v>
+        <v>675</v>
       </c>
       <c r="B91" s="1" t="s">
-        <v>678</v>
+        <v>676</v>
       </c>
       <c r="C91" s="2" t="s">
         <v>63</v>
@@ -22383,7 +22392,7 @@
       <c r="EV91" s="2"/>
       <c r="EW91" s="2"/>
     </row>
-    <row r="92" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>24</v>
       </c>
@@ -22565,9 +22574,9 @@
       <c r="EV92" s="2"/>
       <c r="EW92" s="2"/>
     </row>
-    <row r="93" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>53</v>
@@ -22741,9 +22750,9 @@
       <c r="EV93" s="2"/>
       <c r="EW93" s="2"/>
     </row>
-    <row r="94" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>55</v>
@@ -22913,7 +22922,7 @@
       <c r="EV94" s="2"/>
       <c r="EW94" s="2"/>
     </row>
-    <row r="95" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>17</v>
       </c>
@@ -23095,9 +23104,9 @@
       <c r="EV95" s="2"/>
       <c r="EW95" s="2"/>
     </row>
-    <row r="96" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>51</v>
@@ -23273,7 +23282,7 @@
       <c r="EV96" s="2"/>
       <c r="EW96" s="2"/>
     </row>
-    <row r="97" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>18</v>
       </c>
@@ -23455,9 +23464,9 @@
       <c r="EV97" s="2"/>
       <c r="EW97" s="2"/>
     </row>
-    <row r="98" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
-        <v>713</v>
+        <v>711</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>49</v>
@@ -23635,7 +23644,7 @@
       <c r="EV98" s="2"/>
       <c r="EW98" s="2"/>
     </row>
-    <row r="99" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>21</v>
       </c>
@@ -23813,7 +23822,7 @@
       <c r="EV99" s="2"/>
       <c r="EW99" s="2"/>
     </row>
-    <row r="100" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>73</v>
       </c>
@@ -23991,9 +24000,9 @@
       <c r="EV100" s="2"/>
       <c r="EW100" s="2"/>
     </row>
-    <row r="101" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>56</v>
@@ -24177,7 +24186,7 @@
       <c r="EV101" s="2"/>
       <c r="EW101" s="2"/>
     </row>
-    <row r="102" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>30</v>
       </c>
@@ -24355,7 +24364,7 @@
       <c r="EV102" s="2"/>
       <c r="EW102" s="2"/>
     </row>
-    <row r="103" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>35</v>
       </c>
@@ -24533,9 +24542,9 @@
       <c r="EV103" s="2"/>
       <c r="EW103" s="2"/>
     </row>
-    <row r="104" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>53</v>
@@ -24715,9 +24724,9 @@
       <c r="EV104" s="2"/>
       <c r="EW104" s="2"/>
     </row>
-    <row r="105" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>55</v>
@@ -24893,9 +24902,9 @@
       <c r="EV105" s="2"/>
       <c r="EW105" s="2"/>
     </row>
-    <row r="106" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
-        <v>556</v>
+        <v>555</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>53</v>
@@ -25073,7 +25082,7 @@
       <c r="EV106" s="2"/>
       <c r="EW106" s="2"/>
     </row>
-    <row r="107" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>34</v>
       </c>
@@ -25249,9 +25258,9 @@
       <c r="EV107" s="2"/>
       <c r="EW107" s="2"/>
     </row>
-    <row r="108" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>50</v>
@@ -25431,7 +25440,7 @@
       <c r="EV108" s="2"/>
       <c r="EW108" s="2"/>
     </row>
-    <row r="109" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>25</v>
       </c>
@@ -25617,15 +25626,15 @@
       <c r="EV109" s="2"/>
       <c r="EW109" s="2"/>
     </row>
-    <row r="110" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C110" s="2" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="D110" s="2">
         <v>300</v>
@@ -25797,9 +25806,9 @@
       <c r="EV110" s="2"/>
       <c r="EW110" s="2"/>
     </row>
-    <row r="111" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>50</v>
@@ -25977,7 +25986,7 @@
       <c r="EV111" s="2"/>
       <c r="EW111" s="2"/>
     </row>
-    <row r="112" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>33</v>
       </c>
@@ -26151,12 +26160,12 @@
       <c r="EV112" s="2"/>
       <c r="EW112" s="2"/>
     </row>
-    <row r="113" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="B113" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C113" s="3" t="s">
         <v>68</v>
@@ -26327,12 +26336,12 @@
       <c r="EV113" s="2"/>
       <c r="EW113" s="2"/>
     </row>
-    <row r="114" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B114" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C114" s="3" t="s">
         <v>68</v>
@@ -26503,7 +26512,7 @@
       <c r="EV114" s="2"/>
       <c r="EW114" s="2"/>
     </row>
-    <row r="115" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>10</v>
       </c>
@@ -26683,7 +26692,7 @@
       <c r="EV115" s="2"/>
       <c r="EW115" s="2"/>
     </row>
-    <row r="116" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>40</v>
       </c>
@@ -26861,7 +26870,7 @@
       <c r="EV116" s="2"/>
       <c r="EW116" s="2"/>
     </row>
-    <row r="117" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>5</v>
       </c>
@@ -27037,9 +27046,9 @@
       <c r="EV117" s="2"/>
       <c r="EW117" s="2"/>
     </row>
-    <row r="118" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>50</v>
@@ -27213,9 +27222,9 @@
       <c r="EV118" s="2"/>
       <c r="EW118" s="2"/>
     </row>
-    <row r="119" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>50</v>
@@ -27395,7 +27404,7 @@
       <c r="EV119" s="2"/>
       <c r="EW119" s="2"/>
     </row>
-    <row r="120" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>0</v>
       </c>
@@ -27573,7 +27582,7 @@
       <c r="EV120" s="2"/>
       <c r="EW120" s="2"/>
     </row>
-    <row r="121" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>140</v>
       </c>
@@ -27751,9 +27760,9 @@
       <c r="EV121" s="2"/>
       <c r="EW121" s="2"/>
     </row>
-    <row r="122" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>50</v>
@@ -27927,7 +27936,7 @@
       <c r="EV122" s="2"/>
       <c r="EW122" s="2"/>
     </row>
-    <row r="123" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>45</v>
       </c>
@@ -28105,9 +28114,9 @@
       <c r="EV123" s="2"/>
       <c r="EW123" s="2"/>
     </row>
-    <row r="124" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>53</v>
@@ -28281,12 +28290,12 @@
       <c r="EV124" s="2"/>
       <c r="EW124" s="2"/>
     </row>
-    <row r="125" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A125" s="13" t="s">
-        <v>601</v>
+        <v>599</v>
       </c>
       <c r="B125" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C125" s="2" t="s">
         <v>63</v>
@@ -28465,12 +28474,12 @@
       <c r="EV125" s="2"/>
       <c r="EW125" s="2"/>
     </row>
-    <row r="126" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
-        <v>531</v>
+        <v>530</v>
       </c>
       <c r="B126" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C126" s="2" t="s">
         <v>63</v>
@@ -28647,7 +28656,7 @@
       <c r="EV126" s="2"/>
       <c r="EW126" s="2"/>
     </row>
-    <row r="127" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>13</v>
       </c>
@@ -28825,7 +28834,7 @@
       <c r="EV127" s="2"/>
       <c r="EW127" s="2"/>
     </row>
-    <row r="128" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>11</v>
       </c>
@@ -29001,12 +29010,12 @@
       <c r="EV128" s="2"/>
       <c r="EW128" s="2"/>
     </row>
-    <row r="129" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="B129" s="11" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C129" s="2" t="s">
         <v>63</v>
@@ -29181,12 +29190,12 @@
       <c r="EV129" s="2"/>
       <c r="EW129" s="2"/>
     </row>
-    <row r="130" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
-        <v>576</v>
+        <v>575</v>
       </c>
       <c r="B130" s="1" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C130" s="2" t="s">
         <v>63</v>
@@ -29361,9 +29370,9 @@
       <c r="EV130" s="2"/>
       <c r="EW130" s="2"/>
     </row>
-    <row r="131" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>55</v>
@@ -29537,7 +29546,7 @@
       <c r="EV131" s="2"/>
       <c r="EW131" s="2"/>
     </row>
-    <row r="132" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>8</v>
       </c>
@@ -29717,9 +29726,9 @@
       <c r="EV132" s="2"/>
       <c r="EW132" s="2"/>
     </row>
-    <row r="133" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>55</v>
@@ -29893,7 +29902,7 @@
       <c r="EV133" s="2"/>
       <c r="EW133" s="2"/>
     </row>
-    <row r="134" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>36</v>
       </c>
@@ -30071,12 +30080,12 @@
       <c r="EV134" s="2"/>
       <c r="EW134" s="2"/>
     </row>
-    <row r="135" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="B135" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C135" s="2" t="s">
         <v>63</v>
@@ -30245,12 +30254,12 @@
       <c r="EV135" s="2"/>
       <c r="EW135" s="2"/>
     </row>
-    <row r="136" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="B136" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C136" s="22" t="s">
         <v>63</v>
@@ -30419,12 +30428,12 @@
       <c r="EV136" s="2"/>
       <c r="EW136" s="2"/>
     </row>
-    <row r="137" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A137" s="13" t="s">
-        <v>599</v>
+        <v>597</v>
       </c>
       <c r="B137" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C137" s="2" t="s">
         <v>63</v>
@@ -30597,7 +30606,7 @@
       <c r="EV137" s="2"/>
       <c r="EW137" s="2"/>
     </row>
-    <row r="138" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>19</v>
       </c>
@@ -30777,9 +30786,9 @@
       <c r="EV138" s="2"/>
       <c r="EW138" s="2"/>
     </row>
-    <row r="139" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
-        <v>580</v>
+        <v>579</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>52</v>
@@ -30957,9 +30966,9 @@
       <c r="EV139" s="2"/>
       <c r="EW139" s="2"/>
     </row>
-    <row r="140" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
-        <v>422</v>
+        <v>421</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>50</v>
@@ -31139,9 +31148,9 @@
       <c r="EV140" s="2"/>
       <c r="EW140" s="2"/>
     </row>
-    <row r="141" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
-        <v>606</v>
+        <v>604</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>55</v>
@@ -31317,9 +31326,9 @@
       <c r="EV141" s="2"/>
       <c r="EW141" s="2"/>
     </row>
-    <row r="142" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>53</v>
@@ -31497,9 +31506,9 @@
       <c r="EV142" s="2"/>
       <c r="EW142" s="2"/>
     </row>
-    <row r="143" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
-        <v>532</v>
+        <v>531</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>51</v>
@@ -31685,9 +31694,9 @@
       <c r="EV143" s="2"/>
       <c r="EW143" s="2"/>
     </row>
-    <row r="144" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>55</v>
@@ -31861,9 +31870,9 @@
       <c r="EV144" s="2"/>
       <c r="EW144" s="2"/>
     </row>
-    <row r="145" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
-        <v>490</v>
+        <v>489</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>53</v>
@@ -32037,7 +32046,7 @@
       <c r="EV145" s="2"/>
       <c r="EW145" s="2"/>
     </row>
-    <row r="146" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>142</v>
       </c>
@@ -32213,9 +32222,9 @@
       <c r="EV146" s="2"/>
       <c r="EW146" s="2"/>
     </row>
-    <row r="147" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
-        <v>709</v>
+        <v>707</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>51</v>
@@ -32389,9 +32398,9 @@
       <c r="EV147" s="2"/>
       <c r="EW147" s="2"/>
     </row>
-    <row r="148" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>51</v>
@@ -32565,9 +32574,9 @@
       <c r="EV148" s="2"/>
       <c r="EW148" s="2"/>
     </row>
-    <row r="149" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
-        <v>687</v>
+        <v>685</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>50</v>
@@ -32743,7 +32752,7 @@
       <c r="EV149" s="2"/>
       <c r="EW149" s="2"/>
     </row>
-    <row r="150" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>44</v>
       </c>
@@ -32919,15 +32928,15 @@
       <c r="EV150" s="2"/>
       <c r="EW150" s="2"/>
     </row>
-    <row r="151" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C151" s="2" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="D151" s="2">
         <v>300</v>
@@ -33099,9 +33108,9 @@
       <c r="EV151" s="2"/>
       <c r="EW151" s="2"/>
     </row>
-    <row r="152" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
-        <v>754</v>
+        <v>752</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>53</v>
@@ -33278,15 +33287,15 @@
       <c r="EV152" s="2"/>
       <c r="EW152" s="2"/>
     </row>
-    <row r="153" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>53</v>
       </c>
       <c r="C153" s="2" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="D153" s="2">
         <v>300</v>
@@ -33458,9 +33467,9 @@
       <c r="EV153" s="2"/>
       <c r="EW153" s="2"/>
     </row>
-    <row r="154" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>51</v>
@@ -33634,9 +33643,9 @@
       <c r="EV154" s="2"/>
       <c r="EW154" s="2"/>
     </row>
-    <row r="155" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
-        <v>794</v>
+        <v>792</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>54</v>
@@ -33810,9 +33819,9 @@
       <c r="EV155" s="2"/>
       <c r="EW155" s="2"/>
     </row>
-    <row r="156" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
-        <v>798</v>
+        <v>796</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>53</v>
@@ -33988,12 +33997,12 @@
       <c r="EV156" s="2"/>
       <c r="EW156" s="2"/>
     </row>
-    <row r="157" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
-        <v>802</v>
+        <v>800</v>
       </c>
       <c r="B157" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C157" s="3" t="s">
         <v>68</v>
@@ -34162,15 +34171,15 @@
       <c r="EV157" s="2"/>
       <c r="EW157" s="2"/>
     </row>
-    <row r="158" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
-        <v>808</v>
+        <v>806</v>
       </c>
       <c r="B158" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C158" s="2" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="D158" s="2">
         <v>1500</v>
@@ -34342,15 +34351,15 @@
       </c>
       <c r="EW158" s="2"/>
     </row>
-    <row r="159" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
-        <v>813</v>
+        <v>811</v>
       </c>
       <c r="B159" s="1" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="C159" s="2" t="s">
-        <v>805</v>
+        <v>803</v>
       </c>
       <c r="D159" s="2">
         <v>1500</v>
@@ -34532,12 +34541,12 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
-        <v>821</v>
+        <v>819</v>
       </c>
       <c r="B160" s="1" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C160" s="22" t="s">
         <v>63</v>
@@ -34704,9 +34713,9 @@
       <c r="EV160" s="2"/>
       <c r="EW160" s="2"/>
     </row>
-    <row r="161" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
-        <v>829</v>
+        <v>827</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>51</v>
@@ -34888,9 +34897,9 @@
       <c r="EV161" s="2"/>
       <c r="EW161" s="2"/>
     </row>
-    <row r="162" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
-        <v>831</v>
+        <v>829</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>51</v>
@@ -35064,9 +35073,9 @@
       <c r="EV162" s="2"/>
       <c r="EW162" s="2"/>
     </row>
-    <row r="163" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
-        <v>846</v>
+        <v>844</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>51</v>
@@ -35244,9 +35253,9 @@
       <c r="EV163" s="2"/>
       <c r="EW163" s="2"/>
     </row>
-    <row r="164" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
-        <v>850</v>
+        <v>848</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>53</v>
@@ -35422,9 +35431,9 @@
       <c r="EV164" s="2"/>
       <c r="EW164" s="2"/>
     </row>
-    <row r="165" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
-        <v>861</v>
+        <v>859</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>51</v>
@@ -35598,9 +35607,9 @@
       <c r="EV165" s="2"/>
       <c r="EW165" s="2"/>
     </row>
-    <row r="166" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
-        <v>871</v>
+        <v>869</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>50</v>
@@ -35780,9 +35789,9 @@
       <c r="EV166" s="2"/>
       <c r="EW166" s="2"/>
     </row>
-    <row r="167" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
-        <v>887</v>
+        <v>885</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>53</v>
@@ -35958,9 +35967,9 @@
       <c r="EV167" s="2"/>
       <c r="EW167" s="2"/>
     </row>
-    <row r="168" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
-        <v>885</v>
+        <v>883</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>55</v>
@@ -36132,9 +36141,9 @@
       <c r="EV168" s="2"/>
       <c r="EW168" s="2"/>
     </row>
-    <row r="169" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
-        <v>888</v>
+        <v>886</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>55</v>
@@ -36310,9 +36319,9 @@
       <c r="EV169" s="2"/>
       <c r="EW169" s="2"/>
     </row>
-    <row r="170" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
-        <v>889</v>
+        <v>887</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>53</v>
@@ -36486,9 +36495,9 @@
       <c r="EV170" s="2"/>
       <c r="EW170" s="2"/>
     </row>
-    <row r="171" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
-        <v>895</v>
+        <v>893</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>55</v>
@@ -36662,9 +36671,9 @@
       <c r="EV171" s="2"/>
       <c r="EW171" s="2"/>
     </row>
-    <row r="172" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
-        <v>1047</v>
+        <v>1045</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>53</v>
@@ -36840,9 +36849,9 @@
       <c r="EV172" s="2"/>
       <c r="EW172" s="2"/>
     </row>
-    <row r="173" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
-        <v>1066</v>
+        <v>1064</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>52</v>
@@ -37016,9 +37025,9 @@
       <c r="EV173" s="2"/>
       <c r="EW173" s="2"/>
     </row>
-    <row r="174" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
-        <v>1067</v>
+        <v>1065</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>49</v>
@@ -37194,9 +37203,9 @@
       <c r="EV174" s="2"/>
       <c r="EW174" s="2"/>
     </row>
-    <row r="175" spans="1:153" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
-        <v>1126</v>
+        <v>1124</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>55</v>
@@ -48994,7 +49003,12 @@
       <c r="EW250" s="2"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:EW174" xr:uid="{C7FAA63B-DEDB-48F1-9CCA-3BF0BF1CD86F}">
+  <autoFilter ref="A1:EW175" xr:uid="{C7FAA63B-DEDB-48F1-9CCA-3BF0BF1CD86F}">
+    <filterColumn colId="0">
+      <filters>
+        <filter val="Destornillador"/>
+      </filters>
+    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:EW150">
       <sortCondition ref="A1:A146"/>
     </sortState>
@@ -49052,25 +49066,25 @@
         <v>144</v>
       </c>
       <c r="D1" s="8" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="E1" s="8" t="s">
         <v>129</v>
       </c>
       <c r="F1" s="8" t="s">
-        <v>523</v>
+        <v>522</v>
       </c>
       <c r="G1" s="8" t="s">
-        <v>712</v>
+        <v>710</v>
       </c>
       <c r="H1" s="8" t="s">
         <v>141</v>
       </c>
       <c r="I1" s="8" t="s">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="J1" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="K1" s="8" t="s">
         <v>133</v>
@@ -49079,19 +49093,19 @@
         <v>134</v>
       </c>
       <c r="M1" s="8" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="N1" s="7" t="s">
-        <v>579</v>
+        <v>578</v>
       </c>
       <c r="O1" s="8" t="s">
-        <v>872</v>
+        <v>870</v>
       </c>
       <c r="P1" s="8" t="s">
         <v>132</v>
       </c>
       <c r="Q1" s="8" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="R1" s="8" t="s">
         <v>130</v>
@@ -49106,7 +49120,7 @@
         <v>137</v>
       </c>
       <c r="V1" s="7" t="s">
-        <v>342</v>
+        <v>341</v>
       </c>
       <c r="W1" s="7" t="s">
         <v>138</v>
@@ -49115,25 +49129,25 @@
         <v>139</v>
       </c>
       <c r="Y1" s="7" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="Z1" s="7" t="s">
         <v>131</v>
       </c>
       <c r="AA1" s="7" t="s">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="AB1" s="7" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AC1" s="7" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="AD1" s="7" t="s">
-        <v>286</v>
+        <v>285</v>
       </c>
       <c r="AE1" s="7" t="s">
-        <v>343</v>
+        <v>342</v>
       </c>
     </row>
     <row r="2" spans="1:31" x14ac:dyDescent="0.25">
@@ -50705,7 +50719,7 @@
     <row r="43" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="str">
         <f>IF(receta!A43="","",receta!A43)</f>
-        <v>Destornillador</v>
+        <v>Vodka Naranja</v>
       </c>
       <c r="B43" s="1"/>
       <c r="C43" s="1">
@@ -58543,40 +58557,40 @@
         <v>72</v>
       </c>
       <c r="B1" s="7" t="s">
-        <v>619</v>
+        <v>617</v>
       </c>
       <c r="C1" s="7" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="D1" s="7" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="E1" s="7" t="s">
+        <v>313</v>
+      </c>
+      <c r="F1" s="7" t="s">
         <v>314</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="G1" s="7" t="s">
+        <v>952</v>
+      </c>
+      <c r="H1" s="7" t="s">
         <v>315</v>
       </c>
-      <c r="G1" s="7" t="s">
-        <v>954</v>
-      </c>
-      <c r="H1" s="7" t="s">
+      <c r="I1" s="7" t="s">
         <v>316</v>
       </c>
-      <c r="I1" s="7" t="s">
-        <v>317</v>
-      </c>
       <c r="J1" s="7" t="s">
-        <v>761</v>
+        <v>759</v>
       </c>
       <c r="K1" s="7" t="s">
-        <v>762</v>
+        <v>760</v>
       </c>
       <c r="L1" s="7" t="s">
-        <v>955</v>
+        <v>953</v>
       </c>
       <c r="M1" s="7" t="s">
-        <v>810</v>
+        <v>808</v>
       </c>
     </row>
     <row r="2" spans="1:13" ht="270" x14ac:dyDescent="0.25">
@@ -58586,16 +58600,16 @@
       </c>
       <c r="B2" s="1"/>
       <c r="C2" s="4" t="s">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D2" s="4" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="E2" s="1" t="s">
-        <v>292</v>
+        <v>291</v>
       </c>
       <c r="F2" s="1" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1"/>
@@ -58604,7 +58618,7 @@
       <c r="K2" s="1"/>
       <c r="L2" s="1"/>
       <c r="M2" s="4" t="s">
-        <v>1139</v>
+        <v>1137</v>
       </c>
     </row>
     <row r="3" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58613,13 +58627,13 @@
         <v>Alejandra</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>662</v>
+        <v>660</v>
       </c>
       <c r="C3" s="4" t="s">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="E3" s="1"/>
       <c r="F3" s="1"/>
@@ -58638,19 +58652,19 @@
       </c>
       <c r="B4" s="1"/>
       <c r="C4" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>434</v>
+        <v>433</v>
       </c>
       <c r="E4" s="1" t="s">
+        <v>237</v>
+      </c>
+      <c r="F4" s="5" t="s">
         <v>238</v>
       </c>
-      <c r="F4" s="5" t="s">
-        <v>239</v>
-      </c>
       <c r="G4" s="4" t="s">
-        <v>958</v>
+        <v>956</v>
       </c>
       <c r="H4" s="1"/>
       <c r="I4" s="5"/>
@@ -58665,19 +58679,19 @@
         <v>Alexander</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>663</v>
+        <v>661</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>447</v>
+        <v>446</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>550</v>
+        <v>549</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="F5" s="5" t="s">
-        <v>363</v>
+        <v>362</v>
       </c>
       <c r="G5" s="5"/>
       <c r="H5" s="1"/>
@@ -58686,7 +58700,7 @@
       <c r="K5" s="5"/>
       <c r="L5" s="5"/>
       <c r="M5" s="4" t="s">
-        <v>910</v>
+        <v>908</v>
       </c>
     </row>
     <row r="6" spans="1:13" ht="270" x14ac:dyDescent="0.25">
@@ -58695,17 +58709,17 @@
         <v>Amaretto Sour</v>
       </c>
       <c r="B6" s="4" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C6" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D6" s="1"/>
       <c r="E6" s="1" t="s">
-        <v>437</v>
+        <v>436</v>
       </c>
       <c r="F6" s="1" t="s">
-        <v>436</v>
+        <v>435</v>
       </c>
       <c r="G6" s="1"/>
       <c r="H6" s="1"/>
@@ -58714,7 +58728,7 @@
       <c r="K6" s="1"/>
       <c r="L6" s="1"/>
       <c r="M6" s="4" t="s">
-        <v>944</v>
+        <v>942</v>
       </c>
     </row>
     <row r="7" spans="1:13" ht="270" x14ac:dyDescent="0.25">
@@ -58723,17 +58737,17 @@
         <v>Amaretto Spritz</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>351</v>
+        <v>350</v>
       </c>
       <c r="D7" s="1"/>
       <c r="E7" s="1" t="s">
-        <v>439</v>
+        <v>438</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
@@ -58742,7 +58756,7 @@
       <c r="K7" s="1"/>
       <c r="L7" s="1"/>
       <c r="M7" s="4" t="s">
-        <v>945</v>
+        <v>943</v>
       </c>
     </row>
     <row r="8" spans="1:13" ht="210" x14ac:dyDescent="0.25">
@@ -58752,14 +58766,14 @@
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="4" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="D8" s="1"/>
       <c r="E8" s="1" t="s">
+        <v>169</v>
+      </c>
+      <c r="F8" s="1" t="s">
         <v>170</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>171</v>
       </c>
       <c r="G8" s="1"/>
       <c r="H8" s="1"/>
@@ -58768,7 +58782,7 @@
       <c r="K8" s="1"/>
       <c r="L8" s="1"/>
       <c r="M8" s="4" t="s">
-        <v>1028</v>
+        <v>1026</v>
       </c>
     </row>
     <row r="9" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -58778,16 +58792,16 @@
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>423</v>
+        <v>422</v>
       </c>
       <c r="E9" s="1" t="s">
+        <v>187</v>
+      </c>
+      <c r="F9" s="5" t="s">
         <v>188</v>
-      </c>
-      <c r="F9" s="5" t="s">
-        <v>189</v>
       </c>
       <c r="G9" s="5"/>
       <c r="H9" s="1"/>
@@ -58796,7 +58810,7 @@
       <c r="K9" s="5"/>
       <c r="L9" s="5"/>
       <c r="M9" s="1" t="s">
-        <v>911</v>
+        <v>909</v>
       </c>
     </row>
     <row r="10" spans="1:13" ht="210" x14ac:dyDescent="0.25">
@@ -58805,10 +58819,10 @@
         <v>Andes Refresh</v>
       </c>
       <c r="B10" s="4" t="s">
-        <v>621</v>
+        <v>619</v>
       </c>
       <c r="C10" s="4" t="s">
-        <v>620</v>
+        <v>618</v>
       </c>
       <c r="D10" s="1"/>
       <c r="E10" s="11"/>
@@ -58827,13 +58841,13 @@
         <v>Aperol Spritz</v>
       </c>
       <c r="B11" s="4" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="C11" s="4" t="s">
-        <v>598</v>
+        <v>596</v>
       </c>
       <c r="D11" s="4" t="s">
-        <v>597</v>
+        <v>595</v>
       </c>
       <c r="E11" s="1"/>
       <c r="F11" s="1"/>
@@ -58844,7 +58858,7 @@
       <c r="K11" s="1"/>
       <c r="L11" s="1"/>
       <c r="M11" s="4" t="s">
-        <v>1045</v>
+        <v>1043</v>
       </c>
     </row>
     <row r="12" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58853,13 +58867,13 @@
         <v>Arándano Sour</v>
       </c>
       <c r="B12" s="4" t="s">
-        <v>667</v>
+        <v>665</v>
       </c>
       <c r="C12" s="4" t="s">
-        <v>622</v>
+        <v>620</v>
       </c>
       <c r="D12" s="4" t="s">
-        <v>552</v>
+        <v>551</v>
       </c>
       <c r="E12" s="1"/>
       <c r="F12" s="1"/>
@@ -58878,10 +58892,10 @@
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="4" t="s">
-        <v>448</v>
+        <v>447</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>419</v>
+        <v>418</v>
       </c>
       <c r="E13" s="1"/>
       <c r="F13" s="1"/>
@@ -58892,7 +58906,7 @@
       <c r="K13" s="1"/>
       <c r="L13" s="1"/>
       <c r="M13" s="4" t="s">
-        <v>960</v>
+        <v>958</v>
       </c>
     </row>
     <row r="14" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58902,25 +58916,25 @@
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D14" s="4" t="s">
-        <v>395</v>
+        <v>394</v>
       </c>
       <c r="E14" s="1"/>
       <c r="F14" s="1"/>
       <c r="G14" s="1"/>
       <c r="H14" s="1" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="I14" s="1" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="J14" s="1"/>
       <c r="K14" s="1"/>
       <c r="L14" s="1"/>
       <c r="M14" s="4" t="s">
-        <v>912</v>
+        <v>910</v>
       </c>
     </row>
     <row r="15" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -58930,10 +58944,10 @@
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="4" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D15" s="4" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="E15" s="1"/>
       <c r="F15" s="1"/>
@@ -58944,7 +58958,7 @@
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="4" t="s">
-        <v>1027</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="16" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -58956,13 +58970,13 @@
       <c r="C16" s="1"/>
       <c r="D16" s="1"/>
       <c r="E16" s="1" t="s">
-        <v>953</v>
+        <v>951</v>
       </c>
       <c r="F16" s="5" t="s">
-        <v>952</v>
+        <v>950</v>
       </c>
       <c r="G16" s="4" t="s">
-        <v>956</v>
+        <v>954</v>
       </c>
       <c r="H16" s="1"/>
       <c r="I16" s="1"/>
@@ -58978,23 +58992,23 @@
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="4" t="s">
+        <v>448</v>
+      </c>
+      <c r="D17" s="4" t="s">
+        <v>156</v>
+      </c>
+      <c r="E17" s="4" t="s">
+        <v>450</v>
+      </c>
+      <c r="F17" s="10" t="s">
         <v>449</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>157</v>
-      </c>
-      <c r="E17" s="4" t="s">
-        <v>451</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>450</v>
       </c>
       <c r="G17" s="10"/>
       <c r="H17" s="4" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>255</v>
+        <v>254</v>
       </c>
       <c r="J17" s="4"/>
       <c r="K17" s="10"/>
@@ -59008,14 +59022,14 @@
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D18" s="4"/>
       <c r="E18" s="1" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="F18" s="5" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="G18" s="5"/>
       <c r="H18" s="4"/>
@@ -59032,14 +59046,14 @@
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="4" t="s">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="1" t="s">
-        <v>442</v>
+        <v>441</v>
       </c>
       <c r="F19" s="1" t="s">
-        <v>441</v>
+        <v>440</v>
       </c>
       <c r="G19" s="1"/>
       <c r="H19" s="1"/>
@@ -59048,7 +59062,7 @@
       <c r="K19" s="1"/>
       <c r="L19" s="1"/>
       <c r="M19" s="4" t="s">
-        <v>961</v>
+        <v>959</v>
       </c>
     </row>
     <row r="20" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59058,14 +59072,14 @@
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="4" t="s">
-        <v>443</v>
+        <v>442</v>
       </c>
       <c r="D20" s="4"/>
       <c r="E20" s="1" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="G20" s="1"/>
       <c r="H20" s="1"/>
@@ -59081,26 +59095,26 @@
         <v>Borgoña</v>
       </c>
       <c r="B21" s="4" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="C21" s="4" t="s">
-        <v>694</v>
+        <v>692</v>
       </c>
       <c r="D21" s="4"/>
       <c r="E21" s="1"/>
       <c r="F21" s="1"/>
       <c r="G21" s="1"/>
       <c r="H21" s="1" t="s">
-        <v>453</v>
+        <v>452</v>
       </c>
       <c r="I21" s="1" t="s">
-        <v>452</v>
+        <v>451</v>
       </c>
       <c r="J21" s="1"/>
       <c r="K21" s="1"/>
       <c r="L21" s="1"/>
       <c r="M21" s="4" t="s">
-        <v>913</v>
+        <v>911</v>
       </c>
     </row>
     <row r="22" spans="1:13" ht="375" x14ac:dyDescent="0.25">
@@ -59109,17 +59123,17 @@
         <v>Caipiriña</v>
       </c>
       <c r="B22" s="4" t="s">
-        <v>623</v>
+        <v>621</v>
       </c>
       <c r="C22" s="4" t="s">
-        <v>732</v>
+        <v>730</v>
       </c>
       <c r="D22" s="1"/>
       <c r="E22" s="1" t="s">
+        <v>568</v>
+      </c>
+      <c r="F22" s="5" t="s">
         <v>569</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>570</v>
       </c>
       <c r="G22" s="5"/>
       <c r="H22" s="1"/>
@@ -59128,7 +59142,7 @@
       <c r="K22" s="5"/>
       <c r="L22" s="5"/>
       <c r="M22" s="4" t="s">
-        <v>1057</v>
+        <v>1055</v>
       </c>
     </row>
     <row r="23" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -59139,7 +59153,7 @@
       <c r="B23" s="3"/>
       <c r="C23" s="3"/>
       <c r="D23" s="4" t="s">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="E23" s="1"/>
       <c r="F23" s="1"/>
@@ -59150,7 +59164,7 @@
       <c r="K23" s="1"/>
       <c r="L23" s="1"/>
       <c r="M23" s="4" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
     </row>
     <row r="24" spans="1:13" ht="345" x14ac:dyDescent="0.25">
@@ -59160,14 +59174,14 @@
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="4" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="D24" s="1"/>
       <c r="E24" s="1" t="s">
+        <v>173</v>
+      </c>
+      <c r="F24" s="5" t="s">
         <v>174</v>
-      </c>
-      <c r="F24" s="5" t="s">
-        <v>175</v>
       </c>
       <c r="G24" s="5"/>
       <c r="H24" s="1"/>
@@ -59184,10 +59198,10 @@
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="4" t="s">
-        <v>454</v>
+        <v>453</v>
       </c>
       <c r="D25" s="4" t="s">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="E25" s="1"/>
       <c r="F25" s="1"/>
@@ -59198,7 +59212,7 @@
       <c r="K25" s="1"/>
       <c r="L25" s="1"/>
       <c r="M25" s="4" t="s">
-        <v>963</v>
+        <v>961</v>
       </c>
     </row>
     <row r="26" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59208,25 +59222,25 @@
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="4" t="s">
-        <v>489</v>
+        <v>488</v>
       </c>
       <c r="D26" s="4" t="s">
-        <v>488</v>
+        <v>487</v>
       </c>
       <c r="E26" s="1"/>
       <c r="F26" s="1"/>
       <c r="G26" s="1"/>
       <c r="H26" s="4" t="s">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="I26" s="1" t="s">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="J26" s="1"/>
       <c r="K26" s="1"/>
       <c r="L26" s="1"/>
       <c r="M26" s="4" t="s">
-        <v>980</v>
+        <v>978</v>
       </c>
     </row>
     <row r="27" spans="1:13" ht="375" x14ac:dyDescent="0.25">
@@ -59235,32 +59249,32 @@
         <v>Chupilca</v>
       </c>
       <c r="B27" s="4" t="s">
-        <v>692</v>
+        <v>690</v>
       </c>
       <c r="C27" s="4" t="s">
-        <v>676</v>
+        <v>674</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>674</v>
+        <v>672</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>1103</v>
+        <v>1101</v>
       </c>
       <c r="F27" s="5" t="s">
-        <v>1102</v>
+        <v>1100</v>
       </c>
       <c r="G27" s="1"/>
       <c r="H27" s="1"/>
       <c r="I27" s="1"/>
       <c r="J27" s="1" t="s">
-        <v>1105</v>
+        <v>1103</v>
       </c>
       <c r="K27" s="5" t="s">
-        <v>1104</v>
+        <v>1102</v>
       </c>
       <c r="L27" s="1"/>
       <c r="M27" s="4" t="s">
-        <v>964</v>
+        <v>962</v>
       </c>
     </row>
     <row r="28" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59270,29 +59284,29 @@
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="4" t="s">
-        <v>457</v>
+        <v>456</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>1038</v>
+        <v>1036</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
       <c r="I28" s="5"/>
       <c r="J28" s="1" t="s">
-        <v>1040</v>
+        <v>1038</v>
       </c>
       <c r="K28" s="5" t="s">
-        <v>1039</v>
+        <v>1037</v>
       </c>
       <c r="L28" s="5"/>
       <c r="M28" s="4" t="s">
-        <v>914</v>
+        <v>912</v>
       </c>
     </row>
     <row r="29" spans="1:13" ht="360" x14ac:dyDescent="0.25">
@@ -59302,14 +59316,14 @@
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="4" t="s">
-        <v>502</v>
+        <v>501</v>
       </c>
       <c r="D29" s="1"/>
       <c r="E29" s="1" t="s">
-        <v>494</v>
+        <v>493</v>
       </c>
       <c r="F29" s="1" t="s">
-        <v>493</v>
+        <v>492</v>
       </c>
       <c r="G29" s="1"/>
       <c r="H29" s="1"/>
@@ -59318,7 +59332,7 @@
       <c r="K29" s="1"/>
       <c r="L29" s="1"/>
       <c r="M29" s="4" t="s">
-        <v>923</v>
+        <v>921</v>
       </c>
     </row>
     <row r="30" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59327,22 +59341,22 @@
         <v>Cléry</v>
       </c>
       <c r="B30" s="4" t="s">
-        <v>736</v>
+        <v>734</v>
       </c>
       <c r="C30" s="4" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>1110</v>
+        <v>1108</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>1099</v>
+        <v>1097</v>
       </c>
       <c r="F30" s="5" t="s">
-        <v>1097</v>
+        <v>1095</v>
       </c>
       <c r="G30" s="4" t="s">
-        <v>1098</v>
+        <v>1096</v>
       </c>
       <c r="H30" s="1"/>
       <c r="I30" s="1"/>
@@ -59350,7 +59364,7 @@
       <c r="K30" s="1"/>
       <c r="L30" s="1"/>
       <c r="M30" s="4" t="s">
-        <v>924</v>
+        <v>922</v>
       </c>
     </row>
     <row r="31" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -59359,22 +59373,22 @@
         <v>Cléry Chirimoya</v>
       </c>
       <c r="B31" s="4" t="s">
-        <v>737</v>
+        <v>735</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>989</v>
+        <v>987</v>
       </c>
       <c r="F31" s="5" t="s">
-        <v>986</v>
+        <v>984</v>
       </c>
       <c r="G31" s="4" t="s">
-        <v>987</v>
+        <v>985</v>
       </c>
       <c r="H31" s="1"/>
       <c r="I31" s="1"/>
@@ -59382,7 +59396,7 @@
       <c r="K31" s="1"/>
       <c r="L31" s="1"/>
       <c r="M31" s="4" t="s">
-        <v>965</v>
+        <v>963</v>
       </c>
     </row>
     <row r="32" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -59391,17 +59405,17 @@
         <v>Cléry Durazno</v>
       </c>
       <c r="B32" s="4" t="s">
-        <v>738</v>
+        <v>736</v>
       </c>
       <c r="C32" s="4" t="s">
-        <v>666</v>
+        <v>664</v>
       </c>
       <c r="D32" s="1"/>
       <c r="E32" s="1" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="F32" s="5" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G32" s="5"/>
       <c r="H32" s="1"/>
@@ -59417,19 +59431,19 @@
         <v>Clover Club</v>
       </c>
       <c r="B33" s="4" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C33" s="4" t="s">
-        <v>837</v>
+        <v>835</v>
       </c>
       <c r="D33" s="4" t="s">
+        <v>546</v>
+      </c>
+      <c r="E33" s="4" t="s">
         <v>547</v>
       </c>
-      <c r="E33" s="4" t="s">
-        <v>548</v>
-      </c>
       <c r="F33" s="1" t="s">
-        <v>546</v>
+        <v>545</v>
       </c>
       <c r="G33" s="1"/>
       <c r="H33" s="1"/>
@@ -59438,7 +59452,7 @@
       <c r="K33" s="1"/>
       <c r="L33" s="1"/>
       <c r="M33" s="4" t="s">
-        <v>877</v>
+        <v>875</v>
       </c>
     </row>
     <row r="34" spans="1:13" ht="255" x14ac:dyDescent="0.25">
@@ -59448,14 +59462,14 @@
       </c>
       <c r="B34" s="1"/>
       <c r="C34" s="4" t="s">
-        <v>661</v>
+        <v>659</v>
       </c>
       <c r="D34" s="4"/>
       <c r="E34" s="1" t="s">
+        <v>243</v>
+      </c>
+      <c r="F34" s="5" t="s">
         <v>244</v>
-      </c>
-      <c r="F34" s="5" t="s">
-        <v>245</v>
       </c>
       <c r="G34" s="5"/>
       <c r="H34" s="1"/>
@@ -59464,7 +59478,7 @@
       <c r="K34" s="5"/>
       <c r="L34" s="5"/>
       <c r="M34" s="4" t="s">
-        <v>966</v>
+        <v>964</v>
       </c>
     </row>
     <row r="35" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -59473,17 +59487,17 @@
         <v>Cosmo Patagonia</v>
       </c>
       <c r="B35" s="4" t="s">
-        <v>730</v>
+        <v>728</v>
       </c>
       <c r="C35" s="4" t="s">
-        <v>624</v>
+        <v>622</v>
       </c>
       <c r="D35" s="4"/>
       <c r="E35" s="1" t="s">
-        <v>1078</v>
+        <v>1076</v>
       </c>
       <c r="F35" s="5" t="s">
-        <v>1077</v>
+        <v>1075</v>
       </c>
       <c r="G35" s="1"/>
       <c r="H35" s="1"/>
@@ -59500,7 +59514,7 @@
       </c>
       <c r="B36" s="1"/>
       <c r="C36" s="4" t="s">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D36" s="1"/>
       <c r="E36" s="1"/>
@@ -59512,7 +59526,7 @@
       <c r="K36" s="1"/>
       <c r="L36" s="1"/>
       <c r="M36" s="4" t="s">
-        <v>1140</v>
+        <v>1138</v>
       </c>
     </row>
     <row r="37" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59521,17 +59535,17 @@
         <v>Crepúsculo</v>
       </c>
       <c r="B37" s="4" t="s">
-        <v>626</v>
+        <v>624</v>
       </c>
       <c r="C37" s="4" t="s">
-        <v>625</v>
+        <v>623</v>
       </c>
       <c r="D37" s="1"/>
       <c r="E37" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F37" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G37" s="5"/>
       <c r="H37" s="1"/>
@@ -59540,7 +59554,7 @@
       <c r="K37" s="5"/>
       <c r="L37" s="5"/>
       <c r="M37" s="4" t="s">
-        <v>1134</v>
+        <v>1132</v>
       </c>
     </row>
     <row r="38" spans="1:13" ht="255" x14ac:dyDescent="0.25">
@@ -59550,14 +59564,14 @@
       </c>
       <c r="B38" s="1"/>
       <c r="C38" s="4" t="s">
-        <v>533</v>
+        <v>532</v>
       </c>
       <c r="D38" s="1"/>
       <c r="E38" s="1" t="s">
-        <v>510</v>
+        <v>509</v>
       </c>
       <c r="F38" s="5" t="s">
-        <v>509</v>
+        <v>508</v>
       </c>
       <c r="G38" s="5"/>
       <c r="H38" s="1"/>
@@ -59566,7 +59580,7 @@
       <c r="K38" s="5"/>
       <c r="L38" s="5"/>
       <c r="M38" s="4" t="s">
-        <v>977</v>
+        <v>975</v>
       </c>
     </row>
     <row r="39" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -59575,10 +59589,10 @@
         <v>Cynar Spritz</v>
       </c>
       <c r="B39" s="4" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="C39" s="4" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="D39" s="1"/>
       <c r="E39" s="1"/>
@@ -59590,7 +59604,7 @@
       <c r="K39" s="1"/>
       <c r="L39" s="1"/>
       <c r="M39" s="4" t="s">
-        <v>1041</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="40" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -59600,29 +59614,29 @@
       </c>
       <c r="B40" s="1"/>
       <c r="C40" s="4" t="s">
-        <v>345</v>
+        <v>344</v>
       </c>
       <c r="D40" s="1"/>
       <c r="E40" s="4" t="s">
-        <v>405</v>
+        <v>404</v>
       </c>
       <c r="F40" s="5" t="s">
-        <v>404</v>
+        <v>403</v>
       </c>
       <c r="G40" s="4" t="s">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="H40" s="1" t="s">
-        <v>919</v>
+        <v>917</v>
       </c>
       <c r="I40" s="5" t="s">
-        <v>920</v>
+        <v>918</v>
       </c>
       <c r="J40" s="4"/>
       <c r="K40" s="5"/>
       <c r="L40" s="5"/>
       <c r="M40" s="4" t="s">
-        <v>931</v>
+        <v>929</v>
       </c>
     </row>
     <row r="41" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -59631,10 +59645,10 @@
         <v>Dama Blanca</v>
       </c>
       <c r="B41" s="4" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C41" s="4" t="s">
-        <v>1046</v>
+        <v>1044</v>
       </c>
       <c r="D41" s="4"/>
       <c r="E41" s="1"/>
@@ -59646,7 +59660,7 @@
       <c r="K41" s="1"/>
       <c r="L41" s="1"/>
       <c r="M41" s="4" t="s">
-        <v>1044</v>
+        <v>1042</v>
       </c>
     </row>
     <row r="42" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59656,14 +59670,14 @@
       </c>
       <c r="B42" s="1"/>
       <c r="C42" s="4" t="s">
-        <v>458</v>
+        <v>457</v>
       </c>
       <c r="D42" s="1"/>
       <c r="E42" s="1" t="s">
-        <v>460</v>
+        <v>459</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>459</v>
+        <v>458</v>
       </c>
       <c r="G42" s="1"/>
       <c r="H42" s="1"/>
@@ -59672,41 +59686,41 @@
       <c r="K42" s="1"/>
       <c r="L42" s="1"/>
       <c r="M42" s="4" t="s">
-        <v>1135</v>
+        <v>1133</v>
       </c>
     </row>
     <row r="43" spans="1:13" ht="270" x14ac:dyDescent="0.25">
       <c r="A43" s="1" t="str">
         <f>IF(receta!A43="","",receta!A43)</f>
-        <v>Destornillador</v>
+        <v>Vodka Naranja</v>
       </c>
       <c r="B43" s="1"/>
       <c r="C43" s="4" t="s">
-        <v>589</v>
+        <v>1148</v>
       </c>
       <c r="D43" s="4" t="s">
-        <v>590</v>
+        <v>588</v>
       </c>
       <c r="E43" s="1" t="s">
-        <v>1122</v>
+        <v>1120</v>
       </c>
       <c r="F43" s="5" t="s">
+        <v>1119</v>
+      </c>
+      <c r="G43" s="4" t="s">
         <v>1121</v>
       </c>
-      <c r="G43" s="4" t="s">
-        <v>1123</v>
-      </c>
       <c r="H43" s="1" t="s">
+        <v>256</v>
+      </c>
+      <c r="I43" s="5" t="s">
         <v>257</v>
-      </c>
-      <c r="I43" s="5" t="s">
-        <v>258</v>
       </c>
       <c r="J43" s="1"/>
       <c r="K43" s="5"/>
       <c r="L43" s="5"/>
       <c r="M43" s="4" t="s">
-        <v>916</v>
+        <v>914</v>
       </c>
     </row>
     <row r="44" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -59716,7 +59730,7 @@
       </c>
       <c r="B44" s="1"/>
       <c r="C44" s="4" t="s">
-        <v>445</v>
+        <v>444</v>
       </c>
       <c r="D44" s="1"/>
       <c r="E44" s="1"/>
@@ -59735,13 +59749,13 @@
         <v>Dry Martini</v>
       </c>
       <c r="B45" s="4" t="s">
-        <v>627</v>
+        <v>625</v>
       </c>
       <c r="C45" s="4" t="s">
-        <v>693</v>
+        <v>691</v>
       </c>
       <c r="D45" s="4" t="s">
-        <v>391</v>
+        <v>390</v>
       </c>
       <c r="E45" s="1"/>
       <c r="F45" s="1"/>
@@ -59752,7 +59766,7 @@
       <c r="K45" s="1"/>
       <c r="L45" s="1"/>
       <c r="M45" s="4" t="s">
-        <v>1030</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="46" spans="1:13" ht="285" x14ac:dyDescent="0.25">
@@ -59761,32 +59775,32 @@
         <v>El Amor en los Tiempos del Covid</v>
       </c>
       <c r="B46" s="4" t="s">
-        <v>739</v>
+        <v>737</v>
       </c>
       <c r="C46" s="4"/>
       <c r="D46" s="4" t="s">
-        <v>975</v>
+        <v>973</v>
       </c>
       <c r="E46" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F46" s="5" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G46" s="5"/>
       <c r="H46" s="1"/>
       <c r="I46" s="1"/>
       <c r="J46" s="4" t="s">
-        <v>1018</v>
+        <v>1016</v>
       </c>
       <c r="K46" s="5" t="s">
+        <v>1015</v>
+      </c>
+      <c r="L46" s="4" t="s">
         <v>1017</v>
       </c>
-      <c r="L46" s="4" t="s">
-        <v>1019</v>
-      </c>
       <c r="M46" s="4" t="s">
-        <v>974</v>
+        <v>972</v>
       </c>
     </row>
     <row r="47" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -59796,16 +59810,16 @@
       </c>
       <c r="B47" s="1"/>
       <c r="C47" s="4" t="s">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D47" s="4" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="E47" s="1" t="s">
+        <v>301</v>
+      </c>
+      <c r="F47" s="5" t="s">
         <v>302</v>
-      </c>
-      <c r="F47" s="5" t="s">
-        <v>303</v>
       </c>
       <c r="G47" s="5"/>
       <c r="H47" s="4"/>
@@ -59814,7 +59828,7 @@
       <c r="K47" s="5"/>
       <c r="L47" s="5"/>
       <c r="M47" s="4" t="s">
-        <v>930</v>
+        <v>928</v>
       </c>
     </row>
     <row r="48" spans="1:13" ht="315" x14ac:dyDescent="0.25">
@@ -59824,16 +59838,16 @@
       </c>
       <c r="B48" s="1"/>
       <c r="C48" s="4" t="s">
-        <v>379</v>
+        <v>378</v>
       </c>
       <c r="D48" s="4" t="s">
-        <v>596</v>
+        <v>594</v>
       </c>
       <c r="E48" s="1" t="s">
-        <v>594</v>
+        <v>592</v>
       </c>
       <c r="F48" s="5" t="s">
-        <v>595</v>
+        <v>593</v>
       </c>
       <c r="G48" s="5"/>
       <c r="H48" s="1"/>
@@ -59841,7 +59855,9 @@
       <c r="J48" s="1"/>
       <c r="K48" s="5"/>
       <c r="L48" s="5"/>
-      <c r="M48" s="1"/>
+      <c r="M48" s="4" t="s">
+        <v>1146</v>
+      </c>
     </row>
     <row r="49" spans="1:13" ht="270" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="str">
@@ -59850,19 +59866,19 @@
       </c>
       <c r="B49" s="1"/>
       <c r="C49" s="4" t="s">
-        <v>628</v>
+        <v>626</v>
       </c>
       <c r="D49" s="4" t="s">
-        <v>371</v>
+        <v>370</v>
       </c>
       <c r="E49" s="1" t="s">
-        <v>766</v>
+        <v>764</v>
       </c>
       <c r="F49" s="5" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="G49" s="4" t="s">
-        <v>968</v>
+        <v>966</v>
       </c>
       <c r="H49" s="1"/>
       <c r="I49" s="1"/>
@@ -59870,7 +59886,7 @@
       <c r="K49" s="1"/>
       <c r="L49" s="1"/>
       <c r="M49" s="4" t="s">
-        <v>1141</v>
+        <v>1139</v>
       </c>
     </row>
     <row r="50" spans="1:13" ht="255" x14ac:dyDescent="0.25">
@@ -59880,29 +59896,29 @@
       </c>
       <c r="B50" s="1"/>
       <c r="C50" s="4" t="s">
-        <v>675</v>
+        <v>673</v>
       </c>
       <c r="D50" s="4"/>
       <c r="E50" s="4" t="s">
+        <v>478</v>
+      </c>
+      <c r="F50" s="5" t="s">
         <v>479</v>
       </c>
-      <c r="F50" s="5" t="s">
-        <v>480</v>
-      </c>
       <c r="G50" s="4" t="s">
-        <v>967</v>
+        <v>965</v>
       </c>
       <c r="H50" s="1" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="I50" s="5" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="J50" s="4"/>
       <c r="K50" s="5"/>
       <c r="L50" s="5"/>
       <c r="M50" s="4" t="s">
-        <v>949</v>
+        <v>947</v>
       </c>
     </row>
     <row r="51" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -59912,7 +59928,7 @@
       </c>
       <c r="B51" s="1"/>
       <c r="C51" s="4" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="D51" s="1"/>
       <c r="E51" s="1"/>
@@ -59924,7 +59940,7 @@
       <c r="K51" s="1"/>
       <c r="L51" s="1"/>
       <c r="M51" s="4" t="s">
-        <v>1132</v>
+        <v>1130</v>
       </c>
     </row>
     <row r="52" spans="1:13" ht="150" x14ac:dyDescent="0.25">
@@ -59934,29 +59950,29 @@
       </c>
       <c r="B52" s="1"/>
       <c r="C52" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D52" s="4" t="s">
-        <v>475</v>
+        <v>474</v>
       </c>
       <c r="E52" s="1" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F52" s="1" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="G52" s="1"/>
       <c r="H52" s="1"/>
       <c r="I52" s="1"/>
       <c r="J52" s="1" t="s">
-        <v>504</v>
+        <v>503</v>
       </c>
       <c r="K52" s="1" t="s">
-        <v>503</v>
+        <v>502</v>
       </c>
       <c r="L52" s="1"/>
       <c r="M52" s="4" t="s">
-        <v>928</v>
+        <v>926</v>
       </c>
     </row>
     <row r="53" spans="1:13" ht="390" x14ac:dyDescent="0.25">
@@ -59966,37 +59982,37 @@
       </c>
       <c r="B53" s="1"/>
       <c r="C53" s="4" t="s">
-        <v>385</v>
+        <v>384</v>
       </c>
       <c r="D53" s="4" t="s">
+        <v>400</v>
+      </c>
+      <c r="E53" s="1" t="s">
         <v>401</v>
       </c>
-      <c r="E53" s="1" t="s">
+      <c r="F53" s="1" t="s">
         <v>402</v>
       </c>
-      <c r="F53" s="1" t="s">
-        <v>403</v>
-      </c>
       <c r="G53" s="4" t="s">
-        <v>990</v>
+        <v>988</v>
       </c>
       <c r="H53" s="1" t="s">
-        <v>383</v>
+        <v>382</v>
       </c>
       <c r="I53" s="1" t="s">
-        <v>382</v>
+        <v>381</v>
       </c>
       <c r="J53" s="1" t="s">
-        <v>1090</v>
+        <v>1088</v>
       </c>
       <c r="K53" s="5" t="s">
+        <v>1087</v>
+      </c>
+      <c r="L53" s="1" t="s">
         <v>1089</v>
       </c>
-      <c r="L53" s="1" t="s">
-        <v>1091</v>
-      </c>
       <c r="M53" s="4" t="s">
-        <v>981</v>
+        <v>979</v>
       </c>
     </row>
     <row r="54" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -60006,23 +60022,23 @@
       </c>
       <c r="B54" s="1"/>
       <c r="C54" s="4" t="s">
-        <v>679</v>
+        <v>677</v>
       </c>
       <c r="D54" s="4"/>
       <c r="E54" s="1"/>
       <c r="F54" s="5"/>
       <c r="G54" s="4"/>
       <c r="H54" s="1" t="s">
-        <v>350</v>
+        <v>349</v>
       </c>
       <c r="I54" s="5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="J54" s="1"/>
       <c r="K54" s="5"/>
       <c r="L54" s="5"/>
       <c r="M54" s="4" t="s">
-        <v>908</v>
+        <v>906</v>
       </c>
     </row>
     <row r="55" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -60032,16 +60048,16 @@
       </c>
       <c r="B55" s="1"/>
       <c r="C55" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D55" s="4" t="s">
-        <v>1142</v>
+        <v>1140</v>
       </c>
       <c r="E55" s="1" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F55" s="5" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="G55" s="5"/>
       <c r="H55" s="1"/>
@@ -60050,7 +60066,7 @@
       <c r="K55" s="5"/>
       <c r="L55" s="5"/>
       <c r="M55" s="4" t="s">
-        <v>1143</v>
+        <v>1141</v>
       </c>
     </row>
     <row r="56" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60060,19 +60076,19 @@
       </c>
       <c r="B56" s="1"/>
       <c r="C56" s="4" t="s">
-        <v>474</v>
+        <v>473</v>
       </c>
       <c r="D56" s="4" t="s">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="E56" s="1" t="s">
-        <v>473</v>
+        <v>472</v>
       </c>
       <c r="F56" s="1" t="s">
-        <v>472</v>
+        <v>471</v>
       </c>
       <c r="G56" s="4" t="s">
-        <v>969</v>
+        <v>967</v>
       </c>
       <c r="H56" s="1"/>
       <c r="I56" s="1"/>
@@ -60080,7 +60096,7 @@
       <c r="K56" s="1"/>
       <c r="L56" s="1"/>
       <c r="M56" s="4" t="s">
-        <v>946</v>
+        <v>944</v>
       </c>
     </row>
     <row r="57" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -60090,16 +60106,16 @@
       </c>
       <c r="B57" s="1"/>
       <c r="C57" s="4" t="s">
-        <v>361</v>
+        <v>360</v>
       </c>
       <c r="D57" s="4" t="s">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="E57" s="11" t="s">
+        <v>171</v>
+      </c>
+      <c r="F57" s="5" t="s">
         <v>172</v>
-      </c>
-      <c r="F57" s="5" t="s">
-        <v>173</v>
       </c>
       <c r="G57" s="28"/>
       <c r="H57" s="11"/>
@@ -60108,7 +60124,7 @@
       <c r="K57" s="5"/>
       <c r="L57" s="5"/>
       <c r="M57" s="4" t="s">
-        <v>951</v>
+        <v>949</v>
       </c>
     </row>
     <row r="58" spans="1:13" ht="150" x14ac:dyDescent="0.25">
@@ -60117,10 +60133,10 @@
         <v>Frangelico Sour</v>
       </c>
       <c r="B58" s="4" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C58" s="4" t="s">
-        <v>337</v>
+        <v>336</v>
       </c>
       <c r="D58" s="1"/>
       <c r="E58" s="1"/>
@@ -60132,7 +60148,7 @@
       <c r="K58" s="1"/>
       <c r="L58" s="1"/>
       <c r="M58" s="4" t="s">
-        <v>948</v>
+        <v>946</v>
       </c>
     </row>
     <row r="59" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60141,34 +60157,34 @@
         <v>French 75</v>
       </c>
       <c r="B59" s="4" t="s">
-        <v>630</v>
+        <v>628</v>
       </c>
       <c r="C59" s="4" t="s">
-        <v>629</v>
+        <v>627</v>
       </c>
       <c r="D59" s="4" t="s">
-        <v>357</v>
+        <v>356</v>
       </c>
       <c r="E59" s="4" t="s">
+        <v>1082</v>
+      </c>
+      <c r="F59" s="5" t="s">
+        <v>1083</v>
+      </c>
+      <c r="G59" s="4" t="s">
         <v>1084</v>
-      </c>
-      <c r="F59" s="5" t="s">
-        <v>1085</v>
-      </c>
-      <c r="G59" s="4" t="s">
-        <v>1086</v>
       </c>
       <c r="H59" s="1"/>
       <c r="I59" s="1"/>
       <c r="J59" s="1" t="s">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="K59" s="5" t="s">
-        <v>410</v>
+        <v>409</v>
       </c>
       <c r="L59" s="5"/>
       <c r="M59" s="4" t="s">
-        <v>947</v>
+        <v>945</v>
       </c>
     </row>
     <row r="60" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -60178,7 +60194,7 @@
       </c>
       <c r="B60" s="1"/>
       <c r="C60" s="4" t="s">
-        <v>338</v>
+        <v>337</v>
       </c>
       <c r="D60" s="1"/>
       <c r="E60" s="1"/>
@@ -60190,7 +60206,7 @@
       <c r="K60" s="1"/>
       <c r="L60" s="1"/>
       <c r="M60" s="4" t="s">
-        <v>970</v>
+        <v>968</v>
       </c>
     </row>
     <row r="61" spans="1:13" ht="165" x14ac:dyDescent="0.25">
@@ -60200,16 +60216,16 @@
       </c>
       <c r="B61" s="1"/>
       <c r="C61" s="4" t="s">
-        <v>335</v>
+        <v>334</v>
       </c>
       <c r="D61" s="4" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>903</v>
+        <v>901</v>
       </c>
       <c r="F61" s="5" t="s">
-        <v>902</v>
+        <v>900</v>
       </c>
       <c r="G61" s="5"/>
       <c r="H61" s="4"/>
@@ -60218,7 +60234,7 @@
       <c r="K61" s="1"/>
       <c r="L61" s="1"/>
       <c r="M61" s="4" t="s">
-        <v>904</v>
+        <v>902</v>
       </c>
     </row>
     <row r="62" spans="1:13" ht="345" x14ac:dyDescent="0.25">
@@ -60228,14 +60244,14 @@
       </c>
       <c r="B62" s="1"/>
       <c r="C62" s="4" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="D62" s="1"/>
       <c r="E62" s="4" t="s">
+        <v>405</v>
+      </c>
+      <c r="F62" s="5" t="s">
         <v>406</v>
-      </c>
-      <c r="F62" s="5" t="s">
-        <v>407</v>
       </c>
       <c r="G62" s="5"/>
       <c r="H62" s="4"/>
@@ -60244,7 +60260,7 @@
       <c r="K62" s="5"/>
       <c r="L62" s="5"/>
       <c r="M62" s="4" t="s">
-        <v>979</v>
+        <v>977</v>
       </c>
     </row>
     <row r="63" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60255,32 +60271,32 @@
       <c r="B63" s="1"/>
       <c r="C63" s="1"/>
       <c r="D63" s="4" t="s">
-        <v>367</v>
+        <v>366</v>
       </c>
       <c r="E63" s="1" t="s">
+        <v>158</v>
+      </c>
+      <c r="F63" s="5" t="s">
         <v>159</v>
-      </c>
-      <c r="F63" s="5" t="s">
-        <v>160</v>
       </c>
       <c r="G63" s="4"/>
       <c r="H63" s="4" t="s">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="I63" s="5" t="s">
-        <v>336</v>
+        <v>335</v>
       </c>
       <c r="J63" s="1" t="s">
-        <v>763</v>
+        <v>761</v>
       </c>
       <c r="K63" s="5" t="s">
-        <v>764</v>
+        <v>762</v>
       </c>
       <c r="L63" s="4" t="s">
-        <v>957</v>
+        <v>955</v>
       </c>
       <c r="M63" s="4" t="s">
-        <v>922</v>
+        <v>920</v>
       </c>
     </row>
     <row r="64" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -60290,14 +60306,14 @@
       </c>
       <c r="B64" s="1"/>
       <c r="C64" s="4" t="s">
-        <v>691</v>
+        <v>689</v>
       </c>
       <c r="D64" s="1"/>
       <c r="E64" s="1" t="s">
-        <v>1093</v>
+        <v>1091</v>
       </c>
       <c r="F64" s="5" t="s">
-        <v>1092</v>
+        <v>1090</v>
       </c>
       <c r="G64" s="1"/>
       <c r="H64" s="1"/>
@@ -60306,7 +60322,7 @@
       <c r="K64" s="1"/>
       <c r="L64" s="1"/>
       <c r="M64" s="4" t="s">
-        <v>978</v>
+        <v>976</v>
       </c>
     </row>
     <row r="65" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60316,10 +60332,10 @@
       </c>
       <c r="B65" s="1"/>
       <c r="C65" s="4" t="s">
-        <v>631</v>
+        <v>629</v>
       </c>
       <c r="D65" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="E65" s="1"/>
       <c r="F65" s="1"/>
@@ -60330,7 +60346,7 @@
       <c r="K65" s="1"/>
       <c r="L65" s="1"/>
       <c r="M65" s="4" t="s">
-        <v>918</v>
+        <v>916</v>
       </c>
     </row>
     <row r="66" spans="1:13" ht="375" x14ac:dyDescent="0.25">
@@ -60339,13 +60355,13 @@
         <v>Hugo</v>
       </c>
       <c r="B66" s="1" t="s">
-        <v>1071</v>
+        <v>1069</v>
       </c>
       <c r="C66" s="4" t="s">
-        <v>731</v>
+        <v>729</v>
       </c>
       <c r="D66" s="4" t="s">
-        <v>744</v>
+        <v>742</v>
       </c>
       <c r="E66" s="1"/>
       <c r="F66" s="1"/>
@@ -60356,7 +60372,7 @@
       <c r="K66" s="1"/>
       <c r="L66" s="1"/>
       <c r="M66" s="4" t="s">
-        <v>1042</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="67" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60366,14 +60382,14 @@
       </c>
       <c r="B67" s="1"/>
       <c r="C67" s="4" t="s">
-        <v>380</v>
+        <v>379</v>
       </c>
       <c r="D67" s="4"/>
       <c r="E67" s="1" t="s">
+        <v>219</v>
+      </c>
+      <c r="F67" s="5" t="s">
         <v>220</v>
-      </c>
-      <c r="F67" s="5" t="s">
-        <v>221</v>
       </c>
       <c r="G67" s="5"/>
       <c r="H67" s="1"/>
@@ -60382,7 +60398,7 @@
       <c r="K67" s="5"/>
       <c r="L67" s="5"/>
       <c r="M67" s="4" t="s">
-        <v>943</v>
+        <v>941</v>
       </c>
     </row>
     <row r="68" spans="1:13" ht="330" x14ac:dyDescent="0.25">
@@ -60392,31 +60408,31 @@
       </c>
       <c r="B68" s="1"/>
       <c r="C68" s="4" t="s">
-        <v>937</v>
+        <v>935</v>
       </c>
       <c r="D68" s="4" t="s">
-        <v>592</v>
+        <v>590</v>
       </c>
       <c r="E68" s="1" t="s">
+        <v>164</v>
+      </c>
+      <c r="F68" s="5" t="s">
         <v>165</v>
-      </c>
-      <c r="F68" s="5" t="s">
-        <v>166</v>
       </c>
       <c r="G68" s="5"/>
       <c r="H68" s="1"/>
       <c r="I68" s="1"/>
       <c r="J68" s="1" t="s">
-        <v>1112</v>
+        <v>1110</v>
       </c>
       <c r="K68" s="5" t="s">
+        <v>1109</v>
+      </c>
+      <c r="L68" s="4" t="s">
         <v>1111</v>
       </c>
-      <c r="L68" s="4" t="s">
-        <v>1113</v>
-      </c>
       <c r="M68" s="4" t="s">
-        <v>936</v>
+        <v>934</v>
       </c>
     </row>
     <row r="69" spans="1:13" ht="300" x14ac:dyDescent="0.25">
@@ -60426,16 +60442,16 @@
       </c>
       <c r="B69" s="1"/>
       <c r="C69" s="4" t="s">
-        <v>435</v>
+        <v>434</v>
       </c>
       <c r="D69" s="4" t="s">
+        <v>428</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>430</v>
+      </c>
+      <c r="F69" s="1" t="s">
         <v>429</v>
-      </c>
-      <c r="E69" s="1" t="s">
-        <v>431</v>
-      </c>
-      <c r="F69" s="1" t="s">
-        <v>430</v>
       </c>
       <c r="G69" s="1"/>
       <c r="H69" s="1"/>
@@ -60444,7 +60460,7 @@
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
       <c r="M69" s="4" t="s">
-        <v>907</v>
+        <v>905</v>
       </c>
     </row>
     <row r="70" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -60454,16 +60470,16 @@
       </c>
       <c r="B70" s="1"/>
       <c r="C70" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D70" s="4" t="s">
-        <v>399</v>
+        <v>398</v>
       </c>
       <c r="E70" s="1" t="s">
+        <v>396</v>
+      </c>
+      <c r="F70" s="1" t="s">
         <v>397</v>
-      </c>
-      <c r="F70" s="1" t="s">
-        <v>398</v>
       </c>
       <c r="G70" s="1"/>
       <c r="H70" s="1"/>
@@ -60472,7 +60488,7 @@
       <c r="K70" s="1"/>
       <c r="L70" s="1"/>
       <c r="M70" s="4" t="s">
-        <v>933</v>
+        <v>931</v>
       </c>
     </row>
     <row r="71" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -60482,14 +60498,14 @@
       </c>
       <c r="B71" s="1"/>
       <c r="C71" s="4" t="s">
-        <v>461</v>
+        <v>460</v>
       </c>
       <c r="D71" s="1"/>
       <c r="E71" s="1" t="s">
-        <v>467</v>
+        <v>466</v>
       </c>
       <c r="F71" s="5" t="s">
-        <v>466</v>
+        <v>465</v>
       </c>
       <c r="G71" s="5"/>
       <c r="H71" s="1"/>
@@ -60498,7 +60514,7 @@
       <c r="K71" s="5"/>
       <c r="L71" s="5"/>
       <c r="M71" s="4" t="s">
-        <v>926</v>
+        <v>924</v>
       </c>
     </row>
     <row r="72" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60507,34 +60523,34 @@
         <v>Jote</v>
       </c>
       <c r="B72" s="4" t="s">
-        <v>633</v>
+        <v>631</v>
       </c>
       <c r="C72" s="4" t="s">
-        <v>632</v>
+        <v>630</v>
       </c>
       <c r="D72" s="4" t="s">
-        <v>865</v>
+        <v>863</v>
       </c>
       <c r="E72" s="1" t="s">
-        <v>1082</v>
+        <v>1080</v>
       </c>
       <c r="F72" s="5" t="s">
+        <v>1079</v>
+      </c>
+      <c r="G72" s="4" t="s">
         <v>1081</v>
       </c>
-      <c r="G72" s="4" t="s">
-        <v>1083</v>
-      </c>
       <c r="H72" s="1" t="s">
-        <v>414</v>
+        <v>413</v>
       </c>
       <c r="I72" s="5" t="s">
-        <v>390</v>
+        <v>389</v>
       </c>
       <c r="J72" s="1"/>
       <c r="K72" s="5"/>
       <c r="L72" s="5"/>
       <c r="M72" s="4" t="s">
-        <v>866</v>
+        <v>864</v>
       </c>
     </row>
     <row r="73" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -60543,11 +60559,11 @@
         <v>Julepe de Menta</v>
       </c>
       <c r="B73" s="4" t="s">
-        <v>561</v>
+        <v>560</v>
       </c>
       <c r="C73" s="4"/>
       <c r="D73" s="4" t="s">
-        <v>1053</v>
+        <v>1051</v>
       </c>
       <c r="E73" s="1"/>
       <c r="F73" s="1"/>
@@ -60558,7 +60574,7 @@
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
       <c r="M73" s="4" t="s">
-        <v>1054</v>
+        <v>1052</v>
       </c>
     </row>
     <row r="74" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60567,26 +60583,26 @@
         <v>Julieta Flowers</v>
       </c>
       <c r="B74" s="4" t="s">
-        <v>703</v>
+        <v>701</v>
       </c>
       <c r="C74" s="4" t="s">
-        <v>708</v>
+        <v>706</v>
       </c>
       <c r="D74" s="4" t="s">
-        <v>706</v>
+        <v>704</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="F74" s="5" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="G74" s="5"/>
       <c r="H74" s="1" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="I74" s="5" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="J74" s="1"/>
       <c r="K74" s="5"/>
@@ -60600,7 +60616,7 @@
       </c>
       <c r="B75" s="1"/>
       <c r="C75" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="D75" s="4"/>
       <c r="E75" s="1"/>
@@ -60612,7 +60628,7 @@
       <c r="K75" s="1"/>
       <c r="L75" s="1"/>
       <c r="M75" s="4" t="s">
-        <v>1043</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="76" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60622,16 +60638,16 @@
       </c>
       <c r="B76" s="1"/>
       <c r="C76" s="4" t="s">
-        <v>446</v>
+        <v>445</v>
       </c>
       <c r="D76" s="4" t="s">
+        <v>269</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>271</v>
+      </c>
+      <c r="F76" s="5" t="s">
         <v>270</v>
-      </c>
-      <c r="E76" s="1" t="s">
-        <v>272</v>
-      </c>
-      <c r="F76" s="5" t="s">
-        <v>271</v>
       </c>
       <c r="G76" s="5"/>
       <c r="H76" s="1"/>
@@ -60648,10 +60664,10 @@
       </c>
       <c r="B77" s="1"/>
       <c r="C77" s="4" t="s">
-        <v>1000</v>
+        <v>998</v>
       </c>
       <c r="D77" s="4" t="s">
-        <v>1001</v>
+        <v>999</v>
       </c>
       <c r="E77" s="1"/>
       <c r="F77" s="1"/>
@@ -60662,7 +60678,7 @@
       <c r="K77" s="1"/>
       <c r="L77" s="1"/>
       <c r="M77" s="4" t="s">
-        <v>999</v>
+        <v>997</v>
       </c>
     </row>
     <row r="78" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -60672,23 +60688,23 @@
       </c>
       <c r="B78" s="1"/>
       <c r="C78" s="4" t="s">
-        <v>462</v>
+        <v>461</v>
       </c>
       <c r="D78" s="1"/>
       <c r="E78" s="1" t="s">
-        <v>784</v>
+        <v>782</v>
       </c>
       <c r="F78" s="5" t="s">
-        <v>783</v>
+        <v>781</v>
       </c>
       <c r="G78" s="5"/>
       <c r="H78" s="1"/>
       <c r="I78" s="1"/>
       <c r="J78" s="1" t="s">
-        <v>786</v>
+        <v>784</v>
       </c>
       <c r="K78" s="5" t="s">
-        <v>785</v>
+        <v>783</v>
       </c>
       <c r="L78" s="5"/>
       <c r="M78" s="1"/>
@@ -60702,10 +60718,10 @@
       <c r="C79" s="4"/>
       <c r="D79" s="1"/>
       <c r="E79" s="1" t="s">
-        <v>1117</v>
+        <v>1115</v>
       </c>
       <c r="F79" s="5" t="s">
-        <v>1118</v>
+        <v>1116</v>
       </c>
       <c r="G79" s="1"/>
       <c r="H79" s="1"/>
@@ -60722,7 +60738,7 @@
       </c>
       <c r="B80" s="1"/>
       <c r="C80" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D80" s="4"/>
       <c r="E80" s="1"/>
@@ -60742,7 +60758,7 @@
       </c>
       <c r="B81" s="1"/>
       <c r="C81" s="4" t="s">
-        <v>722</v>
+        <v>720</v>
       </c>
       <c r="D81" s="4"/>
       <c r="E81" s="1"/>
@@ -60761,26 +60777,26 @@
         <v>Mai Tai Piña</v>
       </c>
       <c r="B82" s="4" t="s">
-        <v>717</v>
+        <v>715</v>
       </c>
       <c r="C82" s="4" t="s">
-        <v>720</v>
+        <v>718</v>
       </c>
       <c r="D82" s="4"/>
       <c r="E82" s="1"/>
       <c r="F82" s="1"/>
       <c r="G82" s="1"/>
       <c r="H82" s="1" t="s">
+        <v>717</v>
+      </c>
+      <c r="I82" s="5" t="s">
         <v>719</v>
-      </c>
-      <c r="I82" s="5" t="s">
-        <v>721</v>
       </c>
       <c r="J82" s="1"/>
       <c r="K82" s="1"/>
       <c r="L82" s="1"/>
       <c r="M82" s="4" t="s">
-        <v>1056</v>
+        <v>1054</v>
       </c>
     </row>
     <row r="83" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60790,16 +60806,16 @@
       </c>
       <c r="B83" s="1"/>
       <c r="C83" s="4" t="s">
-        <v>879</v>
+        <v>877</v>
       </c>
       <c r="D83" s="4" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>349</v>
+        <v>348</v>
       </c>
       <c r="F83" s="5" t="s">
-        <v>348</v>
+        <v>347</v>
       </c>
       <c r="G83" s="5"/>
       <c r="H83" s="1"/>
@@ -60808,7 +60824,7 @@
       <c r="K83" s="5"/>
       <c r="L83" s="5"/>
       <c r="M83" s="4" t="s">
-        <v>878</v>
+        <v>876</v>
       </c>
     </row>
     <row r="84" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -60817,28 +60833,28 @@
         <v>Malta con Huevo</v>
       </c>
       <c r="B84" s="4" t="s">
-        <v>657</v>
+        <v>655</v>
       </c>
       <c r="C84" s="4" t="s">
-        <v>658</v>
+        <v>656</v>
       </c>
       <c r="D84" s="4" t="s">
-        <v>869</v>
+        <v>867</v>
       </c>
       <c r="E84" s="1"/>
       <c r="F84" s="1"/>
       <c r="G84" s="1"/>
       <c r="H84" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="I84" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="J84" s="1"/>
       <c r="K84" s="1"/>
       <c r="L84" s="1"/>
       <c r="M84" s="4" t="s">
-        <v>972</v>
+        <v>970</v>
       </c>
     </row>
     <row r="85" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -60847,28 +60863,28 @@
         <v>Malta con Leche Condensada</v>
       </c>
       <c r="B85" s="4" t="s">
-        <v>660</v>
+        <v>658</v>
       </c>
       <c r="C85" s="4" t="s">
-        <v>659</v>
+        <v>657</v>
       </c>
       <c r="D85" s="4" t="s">
-        <v>868</v>
+        <v>866</v>
       </c>
       <c r="E85" s="1"/>
       <c r="F85" s="1"/>
       <c r="G85" s="1"/>
       <c r="H85" s="1" t="s">
-        <v>614</v>
+        <v>612</v>
       </c>
       <c r="I85" s="1" t="s">
-        <v>613</v>
+        <v>611</v>
       </c>
       <c r="J85" s="1"/>
       <c r="K85" s="1"/>
       <c r="L85" s="1"/>
       <c r="M85" s="4" t="s">
-        <v>973</v>
+        <v>971</v>
       </c>
     </row>
     <row r="86" spans="1:13" ht="30" x14ac:dyDescent="0.25">
@@ -60877,7 +60893,7 @@
         <v>Mango Sour</v>
       </c>
       <c r="B86" s="4" t="s">
-        <v>669</v>
+        <v>667</v>
       </c>
       <c r="C86" s="4"/>
       <c r="D86" s="1"/>
@@ -60898,27 +60914,27 @@
       </c>
       <c r="B87" s="1"/>
       <c r="C87" s="4" t="s">
-        <v>749</v>
+        <v>747</v>
       </c>
       <c r="D87" s="1"/>
       <c r="E87" s="1" t="s">
-        <v>748</v>
+        <v>746</v>
       </c>
       <c r="F87" s="5" t="s">
-        <v>747</v>
+        <v>745</v>
       </c>
       <c r="G87" s="5"/>
       <c r="H87" s="1" t="s">
-        <v>750</v>
+        <v>748</v>
       </c>
       <c r="I87" s="5" t="s">
-        <v>372</v>
+        <v>371</v>
       </c>
       <c r="J87" s="1"/>
       <c r="K87" s="5"/>
       <c r="L87" s="5"/>
       <c r="M87" s="4" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
     </row>
     <row r="88" spans="1:13" ht="360" x14ac:dyDescent="0.25">
@@ -60927,13 +60943,13 @@
         <v>Maqui Sour</v>
       </c>
       <c r="B88" s="4" t="s">
-        <v>740</v>
+        <v>738</v>
       </c>
       <c r="C88" s="4" t="s">
-        <v>634</v>
+        <v>632</v>
       </c>
       <c r="D88" s="4" t="s">
-        <v>1065</v>
+        <v>1063</v>
       </c>
       <c r="E88" s="1"/>
       <c r="F88" s="1"/>
@@ -60944,7 +60960,7 @@
       <c r="K88" s="1"/>
       <c r="L88" s="1"/>
       <c r="M88" s="4" t="s">
-        <v>1055</v>
+        <v>1053</v>
       </c>
     </row>
     <row r="89" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -60953,20 +60969,20 @@
         <v>Margarita</v>
       </c>
       <c r="B89" s="4" t="s">
-        <v>636</v>
+        <v>634</v>
       </c>
       <c r="C89" s="4" t="s">
-        <v>635</v>
+        <v>633</v>
       </c>
       <c r="D89" s="1"/>
       <c r="E89" s="1" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F89" s="5" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="G89" s="4" t="s">
-        <v>1062</v>
+        <v>1060</v>
       </c>
       <c r="H89" s="1"/>
       <c r="I89" s="1"/>
@@ -60974,7 +60990,7 @@
       <c r="K89" s="5"/>
       <c r="L89" s="5"/>
       <c r="M89" s="4" t="s">
-        <v>1060</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="90" spans="1:13" x14ac:dyDescent="0.25">
@@ -60986,19 +61002,19 @@
       <c r="C90" s="1"/>
       <c r="D90" s="1"/>
       <c r="E90" s="1" t="s">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="F90" s="5" t="s">
-        <v>409</v>
+        <v>408</v>
       </c>
       <c r="G90" s="5"/>
       <c r="H90" s="1"/>
       <c r="I90" s="1"/>
       <c r="J90" s="1" t="s">
-        <v>1107</v>
+        <v>1105</v>
       </c>
       <c r="K90" s="5" t="s">
-        <v>1106</v>
+        <v>1104</v>
       </c>
       <c r="L90" s="5"/>
       <c r="M90" s="1"/>
@@ -61009,17 +61025,17 @@
         <v>Melón con Vino</v>
       </c>
       <c r="B91" s="4" t="s">
-        <v>681</v>
+        <v>679</v>
       </c>
       <c r="C91" s="4" t="s">
-        <v>680</v>
+        <v>678</v>
       </c>
       <c r="D91" s="1"/>
       <c r="E91" s="1" t="s">
-        <v>1116</v>
+        <v>1114</v>
       </c>
       <c r="F91" s="5" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="G91" s="5"/>
       <c r="H91" s="1"/>
@@ -61035,28 +61051,28 @@
         <v>Michelada</v>
       </c>
       <c r="B92" s="4" t="s">
-        <v>838</v>
+        <v>836</v>
       </c>
       <c r="C92" s="4" t="s">
-        <v>839</v>
+        <v>837</v>
       </c>
       <c r="D92" s="4" t="s">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="E92" s="1" t="s">
+        <v>177</v>
+      </c>
+      <c r="F92" s="5" t="s">
         <v>178</v>
-      </c>
-      <c r="F92" s="5" t="s">
-        <v>179</v>
       </c>
       <c r="G92" s="5"/>
       <c r="H92" s="1"/>
       <c r="I92" s="1"/>
       <c r="J92" s="1" t="s">
-        <v>1088</v>
+        <v>1086</v>
       </c>
       <c r="K92" s="5" t="s">
-        <v>1087</v>
+        <v>1085</v>
       </c>
       <c r="L92" s="5"/>
       <c r="M92" s="1"/>
@@ -61068,7 +61084,7 @@
       </c>
       <c r="B93" s="1"/>
       <c r="C93" s="4" t="s">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="D93" s="1"/>
       <c r="E93" s="1"/>
@@ -61080,7 +61096,7 @@
       <c r="K93" s="1"/>
       <c r="L93" s="1"/>
       <c r="M93" s="4" t="s">
-        <v>1032</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="94" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -61090,7 +61106,7 @@
       </c>
       <c r="B94" s="1"/>
       <c r="C94" s="4" t="s">
-        <v>362</v>
+        <v>361</v>
       </c>
       <c r="D94" s="1"/>
       <c r="E94" s="1"/>
@@ -61102,7 +61118,7 @@
       <c r="K94" s="1"/>
       <c r="L94" s="1"/>
       <c r="M94" s="4" t="s">
-        <v>1050</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="95" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -61111,10 +61127,10 @@
         <v>Mojito</v>
       </c>
       <c r="B95" s="4" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="C95" s="4" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="D95" s="4"/>
       <c r="E95" s="1"/>
@@ -61126,7 +61142,7 @@
       <c r="K95" s="1"/>
       <c r="L95" s="1"/>
       <c r="M95" s="4" t="s">
-        <v>983</v>
+        <v>981</v>
       </c>
     </row>
     <row r="96" spans="1:13" ht="60" x14ac:dyDescent="0.25">
@@ -61136,7 +61152,7 @@
       </c>
       <c r="B96" s="1"/>
       <c r="C96" s="4" t="s">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="D96" s="4"/>
       <c r="E96" s="1"/>
@@ -61156,16 +61172,16 @@
       </c>
       <c r="B97" s="1"/>
       <c r="C97" s="4" t="s">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D97" s="4" t="s">
+        <v>980</v>
+      </c>
+      <c r="E97" s="1" t="s">
+        <v>983</v>
+      </c>
+      <c r="F97" s="5" t="s">
         <v>982</v>
-      </c>
-      <c r="E97" s="1" t="s">
-        <v>985</v>
-      </c>
-      <c r="F97" s="5" t="s">
-        <v>984</v>
       </c>
       <c r="G97" s="1"/>
       <c r="H97" s="4"/>
@@ -61174,7 +61190,7 @@
       <c r="K97" s="1"/>
       <c r="L97" s="1"/>
       <c r="M97" s="4" t="s">
-        <v>1136</v>
+        <v>1134</v>
       </c>
     </row>
     <row r="98" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -61183,10 +61199,10 @@
         <v>Mojito Spritz</v>
       </c>
       <c r="B98" s="4" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="C98" s="4" t="s">
-        <v>723</v>
+        <v>721</v>
       </c>
       <c r="D98" s="4"/>
       <c r="E98" s="1"/>
@@ -61206,14 +61222,14 @@
       </c>
       <c r="B99" s="1"/>
       <c r="C99" s="4" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="D99" s="4"/>
       <c r="E99" s="1" t="s">
+        <v>166</v>
+      </c>
+      <c r="F99" s="5" t="s">
         <v>167</v>
-      </c>
-      <c r="F99" s="5" t="s">
-        <v>168</v>
       </c>
       <c r="G99" s="5"/>
       <c r="H99" s="1"/>
@@ -61222,7 +61238,7 @@
       <c r="K99" s="5"/>
       <c r="L99" s="5"/>
       <c r="M99" s="4" t="s">
-        <v>921</v>
+        <v>919</v>
       </c>
     </row>
     <row r="100" spans="1:13" ht="150" x14ac:dyDescent="0.25">
@@ -61231,17 +61247,17 @@
         <v>Naranja Sour</v>
       </c>
       <c r="B100" s="4" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C100" s="4" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D100" s="4"/>
       <c r="E100" s="1" t="s">
-        <v>340</v>
+        <v>339</v>
       </c>
       <c r="F100" s="5" t="s">
-        <v>339</v>
+        <v>338</v>
       </c>
       <c r="G100" s="5"/>
       <c r="H100" s="1"/>
@@ -61250,7 +61266,7 @@
       <c r="K100" s="5"/>
       <c r="L100" s="5"/>
       <c r="M100" s="4" t="s">
-        <v>1076</v>
+        <v>1074</v>
       </c>
     </row>
     <row r="101" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -61260,17 +61276,17 @@
       </c>
       <c r="B101" s="1"/>
       <c r="C101" s="4" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="D101" s="4"/>
       <c r="E101" s="4"/>
       <c r="F101" s="1"/>
       <c r="G101" s="1"/>
       <c r="H101" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="I101" s="1" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="J101" s="4"/>
       <c r="K101" s="1"/>
@@ -61284,10 +61300,10 @@
       </c>
       <c r="B102" s="1"/>
       <c r="C102" s="4" t="s">
-        <v>373</v>
+        <v>372</v>
       </c>
       <c r="D102" s="4" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
       <c r="E102" s="1"/>
       <c r="F102" s="1"/>
@@ -61298,7 +61314,7 @@
       <c r="K102" s="1"/>
       <c r="L102" s="1"/>
       <c r="M102" s="4" t="s">
-        <v>959</v>
+        <v>957</v>
       </c>
     </row>
     <row r="103" spans="1:13" ht="210" x14ac:dyDescent="0.25">
@@ -61308,7 +61324,7 @@
       </c>
       <c r="B103" s="1"/>
       <c r="C103" s="4" t="s">
-        <v>591</v>
+        <v>589</v>
       </c>
       <c r="D103" s="1"/>
       <c r="E103" s="1"/>
@@ -61320,7 +61336,7 @@
       <c r="K103" s="1"/>
       <c r="L103" s="1"/>
       <c r="M103" s="4" t="s">
-        <v>1026</v>
+        <v>1024</v>
       </c>
     </row>
     <row r="104" spans="1:13" ht="345" x14ac:dyDescent="0.25">
@@ -61329,19 +61345,19 @@
         <v>New York Sour</v>
       </c>
       <c r="B104" s="4" t="s">
-        <v>741</v>
+        <v>739</v>
       </c>
       <c r="C104" s="4" t="s">
-        <v>639</v>
+        <v>637</v>
       </c>
       <c r="D104" s="4" t="s">
-        <v>481</v>
+        <v>480</v>
       </c>
       <c r="E104" s="1" t="s">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="F104" s="5" t="s">
-        <v>476</v>
+        <v>475</v>
       </c>
       <c r="G104" s="5"/>
       <c r="H104" s="1"/>
@@ -61350,7 +61366,7 @@
       <c r="K104" s="5"/>
       <c r="L104" s="5"/>
       <c r="M104" s="4" t="s">
-        <v>994</v>
+        <v>992</v>
       </c>
     </row>
     <row r="105" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -61360,14 +61376,14 @@
       </c>
       <c r="B105" s="1"/>
       <c r="C105" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D105" s="1"/>
       <c r="E105" s="1" t="s">
+        <v>204</v>
+      </c>
+      <c r="F105" s="1" t="s">
         <v>205</v>
-      </c>
-      <c r="F105" s="1" t="s">
-        <v>206</v>
       </c>
       <c r="G105" s="1"/>
       <c r="H105" s="1"/>
@@ -61376,7 +61392,7 @@
       <c r="K105" s="1"/>
       <c r="L105" s="1"/>
       <c r="M105" s="4" t="s">
-        <v>935</v>
+        <v>933</v>
       </c>
     </row>
     <row r="106" spans="1:13" ht="375" x14ac:dyDescent="0.25">
@@ -61385,32 +61401,32 @@
         <v>Old Fashioned</v>
       </c>
       <c r="B106" s="4" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="C106" s="4"/>
       <c r="D106" s="4" t="s">
-        <v>562</v>
+        <v>561</v>
       </c>
       <c r="E106" s="1" t="s">
-        <v>1024</v>
+        <v>1022</v>
       </c>
       <c r="F106" s="5" t="s">
-        <v>1025</v>
+        <v>1023</v>
       </c>
       <c r="G106" s="4" t="s">
-        <v>1023</v>
+        <v>1021</v>
       </c>
       <c r="H106" s="4" t="s">
-        <v>1037</v>
+        <v>1035</v>
       </c>
       <c r="I106" s="5" t="s">
-        <v>1034</v>
+        <v>1032</v>
       </c>
       <c r="J106" s="1"/>
       <c r="K106" s="1"/>
       <c r="L106" s="1"/>
       <c r="M106" s="4" t="s">
-        <v>1035</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="107" spans="1:13" ht="192" customHeight="1" x14ac:dyDescent="0.25">
@@ -61420,7 +61436,7 @@
       </c>
       <c r="B107" s="1"/>
       <c r="C107" s="4" t="s">
-        <v>346</v>
+        <v>345</v>
       </c>
       <c r="D107" s="1"/>
       <c r="E107" s="1"/>
@@ -61439,26 +61455,26 @@
         <v>Paloma</v>
       </c>
       <c r="B108" s="4" t="s">
-        <v>642</v>
+        <v>640</v>
       </c>
       <c r="C108" s="4" t="s">
-        <v>641</v>
+        <v>639</v>
       </c>
       <c r="D108" s="1"/>
       <c r="E108" s="1"/>
       <c r="F108" s="1"/>
       <c r="G108" s="1"/>
       <c r="H108" s="1" t="s">
-        <v>950</v>
+        <v>948</v>
       </c>
       <c r="I108" s="5" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="J108" s="1"/>
       <c r="K108" s="1"/>
       <c r="L108" s="1"/>
       <c r="M108" s="4" t="s">
-        <v>1036</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="109" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -61467,7 +61483,7 @@
         <v>Parrón</v>
       </c>
       <c r="B109" s="4" t="s">
-        <v>575</v>
+        <v>574</v>
       </c>
       <c r="C109" s="4"/>
       <c r="D109" s="4"/>
@@ -61487,19 +61503,19 @@
         <v>Penicilina</v>
       </c>
       <c r="B110" s="4" t="s">
-        <v>672</v>
+        <v>670</v>
       </c>
       <c r="C110" s="4" t="s">
-        <v>671</v>
+        <v>669</v>
       </c>
       <c r="D110" s="4" t="s">
-        <v>992</v>
+        <v>990</v>
       </c>
       <c r="E110" s="4" t="s">
-        <v>582</v>
+        <v>581</v>
       </c>
       <c r="F110" s="5" t="s">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="G110" s="5"/>
       <c r="H110" s="1"/>
@@ -61508,7 +61524,7 @@
       <c r="K110" s="5"/>
       <c r="L110" s="5"/>
       <c r="M110" s="4" t="s">
-        <v>993</v>
+        <v>991</v>
       </c>
     </row>
     <row r="111" spans="1:13" x14ac:dyDescent="0.25">
@@ -61518,14 +61534,14 @@
       </c>
       <c r="B111" s="1"/>
       <c r="C111" s="4" t="s">
-        <v>497</v>
+        <v>496</v>
       </c>
       <c r="D111" s="1"/>
       <c r="E111" s="1" t="s">
-        <v>498</v>
+        <v>497</v>
       </c>
       <c r="F111" s="5" t="s">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="G111" s="5"/>
       <c r="H111" s="1"/>
@@ -61542,17 +61558,17 @@
       </c>
       <c r="B112" s="1"/>
       <c r="C112" s="4" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="D112" s="1"/>
       <c r="E112" s="1" t="s">
-        <v>483</v>
+        <v>482</v>
       </c>
       <c r="F112" s="5" t="s">
-        <v>482</v>
+        <v>481</v>
       </c>
       <c r="G112" s="4" t="s">
-        <v>1063</v>
+        <v>1061</v>
       </c>
       <c r="H112" s="1"/>
       <c r="I112" s="5"/>
@@ -61568,14 +61584,14 @@
       </c>
       <c r="B113" s="1"/>
       <c r="C113" s="4" t="s">
-        <v>463</v>
+        <v>462</v>
       </c>
       <c r="D113" s="5"/>
       <c r="E113" s="1" t="s">
-        <v>415</v>
+        <v>414</v>
       </c>
       <c r="F113" s="5" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="G113" s="5"/>
       <c r="H113" s="6"/>
@@ -61584,7 +61600,7 @@
       <c r="K113" s="5"/>
       <c r="L113" s="5"/>
       <c r="M113" s="4" t="s">
-        <v>1059</v>
+        <v>1057</v>
       </c>
     </row>
     <row r="114" spans="1:13" x14ac:dyDescent="0.25">
@@ -61594,7 +61610,7 @@
       </c>
       <c r="B114" s="1"/>
       <c r="C114" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D114" s="1"/>
       <c r="E114" s="1"/>
@@ -61607,14 +61623,14 @@
       <c r="L114" s="1"/>
       <c r="M114" s="1"/>
     </row>
-    <row r="115" spans="1:13" ht="195" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="str">
         <f>IF(receta!A115="","",receta!A115)</f>
         <v>Pisco Punch</v>
       </c>
       <c r="B115" s="1"/>
       <c r="C115" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="D115" s="4"/>
       <c r="E115" s="1"/>
@@ -61625,7 +61641,9 @@
       <c r="J115" s="1"/>
       <c r="K115" s="1"/>
       <c r="L115" s="1"/>
-      <c r="M115" s="1"/>
+      <c r="M115" s="4" t="s">
+        <v>1149</v>
+      </c>
     </row>
     <row r="116" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="str">
@@ -61633,17 +61651,17 @@
         <v>Pisco Sour</v>
       </c>
       <c r="B116" s="4" t="s">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="C116" s="4"/>
       <c r="D116" s="4" t="s">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="E116" s="1" t="s">
+        <v>160</v>
+      </c>
+      <c r="F116" s="5" t="s">
         <v>161</v>
-      </c>
-      <c r="F116" s="5" t="s">
-        <v>162</v>
       </c>
       <c r="G116" s="5"/>
       <c r="H116" s="1"/>
@@ -61659,30 +61677,30 @@
         <v>Piscola</v>
       </c>
       <c r="B117" s="4" t="s">
-        <v>644</v>
+        <v>642</v>
       </c>
       <c r="C117" s="4" t="s">
-        <v>643</v>
+        <v>641</v>
       </c>
       <c r="D117" s="5"/>
       <c r="E117" s="1" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F117" s="5" t="s">
-        <v>416</v>
+        <v>415</v>
       </c>
       <c r="G117" s="5"/>
       <c r="H117" s="1"/>
       <c r="I117" s="1"/>
       <c r="J117" s="4" t="s">
-        <v>1114</v>
+        <v>1112</v>
       </c>
       <c r="K117" s="5" t="s">
-        <v>1115</v>
+        <v>1113</v>
       </c>
       <c r="L117" s="5"/>
       <c r="M117" s="4" t="s">
-        <v>998</v>
+        <v>996</v>
       </c>
     </row>
     <row r="118" spans="1:13" ht="90" x14ac:dyDescent="0.25">
@@ -61691,17 +61709,17 @@
         <v>Pistón</v>
       </c>
       <c r="B118" s="4" t="s">
-        <v>646</v>
+        <v>644</v>
       </c>
       <c r="C118" s="4" t="s">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="D118" s="1"/>
       <c r="E118" s="1" t="s">
+        <v>498</v>
+      </c>
+      <c r="F118" s="5" t="s">
         <v>499</v>
-      </c>
-      <c r="F118" s="5" t="s">
-        <v>500</v>
       </c>
       <c r="G118" s="5"/>
       <c r="H118" s="1"/>
@@ -61718,25 +61736,25 @@
       </c>
       <c r="B119" s="1"/>
       <c r="C119" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D119" s="4" t="s">
-        <v>455</v>
+        <v>454</v>
       </c>
       <c r="E119" s="1"/>
       <c r="F119" s="5"/>
       <c r="G119" s="5"/>
       <c r="H119" s="1" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="I119" s="5" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="J119" s="1"/>
       <c r="K119" s="5"/>
       <c r="L119" s="5"/>
       <c r="M119" s="4" t="s">
-        <v>996</v>
+        <v>994</v>
       </c>
     </row>
     <row r="120" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -61745,17 +61763,17 @@
         <v>Ramazzotti Spritz</v>
       </c>
       <c r="B120" s="4" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="C120" s="4" t="s">
-        <v>352</v>
+        <v>351</v>
       </c>
       <c r="D120" s="1"/>
       <c r="E120" s="1" t="s">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="F120" s="5" t="s">
-        <v>374</v>
+        <v>373</v>
       </c>
       <c r="G120" s="5"/>
       <c r="H120" s="1"/>
@@ -61771,17 +61789,17 @@
         <v>Ramazzotti Violetto Spritz</v>
       </c>
       <c r="B121" s="4" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="C121" s="4" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="D121" s="1"/>
       <c r="E121" s="1" t="s">
-        <v>1080</v>
+        <v>1078</v>
       </c>
       <c r="F121" s="5" t="s">
-        <v>1079</v>
+        <v>1077</v>
       </c>
       <c r="G121" s="1"/>
       <c r="H121" s="1"/>
@@ -61798,14 +61816,14 @@
       </c>
       <c r="B122" s="1"/>
       <c r="C122" s="4" t="s">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="D122" s="1"/>
       <c r="E122" s="1" t="s">
-        <v>508</v>
+        <v>507</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="G122" s="1"/>
       <c r="H122" s="1"/>
@@ -61822,25 +61840,25 @@
       </c>
       <c r="B123" s="1"/>
       <c r="C123" s="4" t="s">
-        <v>647</v>
+        <v>645</v>
       </c>
       <c r="D123" s="4" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="E123" s="1"/>
       <c r="F123" s="5"/>
       <c r="G123" s="5"/>
       <c r="H123" s="1" t="s">
-        <v>341</v>
+        <v>340</v>
       </c>
       <c r="I123" s="5" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="J123" s="1"/>
       <c r="K123" s="5"/>
       <c r="L123" s="5"/>
       <c r="M123" s="4" t="s">
-        <v>917</v>
+        <v>915</v>
       </c>
     </row>
     <row r="124" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -61850,10 +61868,10 @@
       </c>
       <c r="B124" s="1"/>
       <c r="C124" s="4" t="s">
-        <v>464</v>
+        <v>463</v>
       </c>
       <c r="D124" s="4" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="E124" s="1"/>
       <c r="F124" s="1"/>
@@ -61871,28 +61889,28 @@
         <v>Sangría</v>
       </c>
       <c r="B125" s="4" t="s">
-        <v>649</v>
+        <v>647</v>
       </c>
       <c r="C125" s="4" t="s">
-        <v>648</v>
+        <v>646</v>
       </c>
       <c r="D125" s="4" t="s">
-        <v>392</v>
+        <v>391</v>
       </c>
       <c r="E125" s="1" t="s">
-        <v>389</v>
+        <v>388</v>
       </c>
       <c r="F125" s="5" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="G125" s="5"/>
       <c r="H125" s="5"/>
       <c r="I125" s="1"/>
       <c r="J125" s="1" t="s">
-        <v>1125</v>
+        <v>1123</v>
       </c>
       <c r="K125" s="5" t="s">
-        <v>1124</v>
+        <v>1122</v>
       </c>
       <c r="L125" s="1"/>
       <c r="M125" s="1"/>
@@ -61904,7 +61922,7 @@
       </c>
       <c r="B126" s="1"/>
       <c r="C126" s="4" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="D126" s="1"/>
       <c r="E126" s="1"/>
@@ -61924,14 +61942,14 @@
       </c>
       <c r="B127" s="1"/>
       <c r="C127" s="4" t="s">
-        <v>718</v>
+        <v>716</v>
       </c>
       <c r="D127" s="1"/>
       <c r="E127" s="1" t="s">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>553</v>
+        <v>552</v>
       </c>
       <c r="G127" s="1"/>
       <c r="H127" s="1"/>
@@ -61948,7 +61966,7 @@
       </c>
       <c r="B128" s="1"/>
       <c r="C128" s="4" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="D128" s="4"/>
       <c r="E128" s="1"/>
@@ -61960,7 +61978,7 @@
       <c r="K128" s="1"/>
       <c r="L128" s="1"/>
       <c r="M128" s="4" t="s">
-        <v>995</v>
+        <v>993</v>
       </c>
     </row>
     <row r="129" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -61970,10 +61988,10 @@
       </c>
       <c r="B129" s="1"/>
       <c r="C129" s="4" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="D129" s="4" t="s">
-        <v>909</v>
+        <v>907</v>
       </c>
       <c r="E129" s="1"/>
       <c r="F129" s="1"/>
@@ -61984,7 +62002,7 @@
       <c r="K129" s="1"/>
       <c r="L129" s="1"/>
       <c r="M129" s="4" t="s">
-        <v>905</v>
+        <v>903</v>
       </c>
     </row>
     <row r="130" spans="1:13" ht="45" x14ac:dyDescent="0.25">
@@ -61994,7 +62012,7 @@
       </c>
       <c r="B130" s="1"/>
       <c r="C130" s="4" t="s">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D130" s="1"/>
       <c r="E130" s="1"/>
@@ -62014,7 +62032,7 @@
       </c>
       <c r="B131" s="1"/>
       <c r="C131" s="4" t="s">
-        <v>465</v>
+        <v>464</v>
       </c>
       <c r="D131" s="4"/>
       <c r="E131" s="1"/>
@@ -62026,7 +62044,7 @@
       <c r="K131" s="1"/>
       <c r="L131" s="1"/>
       <c r="M131" s="4" t="s">
-        <v>1061</v>
+        <v>1059</v>
       </c>
     </row>
     <row r="132" spans="1:13" ht="165" x14ac:dyDescent="0.25">
@@ -62036,14 +62054,14 @@
       </c>
       <c r="B132" s="1"/>
       <c r="C132" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D132" s="1"/>
       <c r="E132" s="1" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F132" s="5" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="G132" s="5"/>
       <c r="H132" s="1"/>
@@ -62052,7 +62070,7 @@
       <c r="K132" s="5"/>
       <c r="L132" s="5"/>
       <c r="M132" s="4" t="s">
-        <v>1031</v>
+        <v>1029</v>
       </c>
     </row>
     <row r="133" spans="1:13" x14ac:dyDescent="0.25">
@@ -62062,7 +62080,7 @@
       </c>
       <c r="B133" s="1"/>
       <c r="C133" s="4" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="D133" s="4"/>
       <c r="E133" s="1"/>
@@ -62082,29 +62100,29 @@
       </c>
       <c r="B134" s="1"/>
       <c r="C134" s="4" t="s">
-        <v>585</v>
+        <v>584</v>
       </c>
       <c r="D134" s="4" t="s">
-        <v>593</v>
+        <v>591</v>
       </c>
       <c r="E134" s="4" t="s">
-        <v>1109</v>
+        <v>1107</v>
       </c>
       <c r="F134" s="5" t="s">
-        <v>1108</v>
+        <v>1106</v>
       </c>
       <c r="G134" s="5"/>
       <c r="H134" s="4"/>
       <c r="I134" s="5"/>
       <c r="J134" s="4" t="s">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="K134" s="5" t="s">
-        <v>586</v>
+        <v>585</v>
       </c>
       <c r="L134" s="5"/>
       <c r="M134" s="4" t="s">
-        <v>1138</v>
+        <v>1136</v>
       </c>
     </row>
     <row r="135" spans="1:13" ht="300" x14ac:dyDescent="0.25">
@@ -62113,28 +62131,28 @@
         <v>Terremoto</v>
       </c>
       <c r="B135" s="4" t="s">
-        <v>650</v>
+        <v>648</v>
       </c>
       <c r="C135" s="4" t="s">
-        <v>942</v>
+        <v>940</v>
       </c>
       <c r="D135" s="4" t="s">
-        <v>940</v>
+        <v>938</v>
       </c>
       <c r="E135" s="1"/>
       <c r="F135" s="1"/>
       <c r="G135" s="1"/>
       <c r="H135" s="1" t="s">
-        <v>939</v>
+        <v>937</v>
       </c>
       <c r="I135" s="5" t="s">
-        <v>938</v>
+        <v>936</v>
       </c>
       <c r="J135" s="1"/>
       <c r="K135" s="1"/>
       <c r="L135" s="1"/>
       <c r="M135" s="4" t="s">
-        <v>941</v>
+        <v>939</v>
       </c>
     </row>
     <row r="136" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -62143,17 +62161,17 @@
         <v>Terremoto (Sin Alcohol)</v>
       </c>
       <c r="B136" s="4" t="s">
-        <v>652</v>
+        <v>650</v>
       </c>
       <c r="C136" s="4" t="s">
-        <v>651</v>
+        <v>649</v>
       </c>
       <c r="D136" s="4"/>
       <c r="E136" s="1" t="s">
+        <v>294</v>
+      </c>
+      <c r="F136" s="5" t="s">
         <v>295</v>
-      </c>
-      <c r="F136" s="5" t="s">
-        <v>296</v>
       </c>
       <c r="G136" s="5"/>
       <c r="H136" s="1"/>
@@ -62171,16 +62189,16 @@
       <c r="B137" s="13"/>
       <c r="C137" s="1"/>
       <c r="D137" s="4" t="s">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="E137" s="1" t="s">
-        <v>1021</v>
+        <v>1019</v>
       </c>
       <c r="F137" s="5" t="s">
+        <v>1018</v>
+      </c>
+      <c r="G137" s="4" t="s">
         <v>1020</v>
-      </c>
-      <c r="G137" s="4" t="s">
-        <v>1022</v>
       </c>
       <c r="H137" s="1"/>
       <c r="I137" s="1"/>
@@ -62196,7 +62214,7 @@
       </c>
       <c r="B138" s="4"/>
       <c r="C138" s="4" t="s">
-        <v>757</v>
+        <v>755</v>
       </c>
       <c r="D138" s="1"/>
       <c r="E138" s="1"/>
@@ -62208,7 +62226,7 @@
       <c r="K138" s="1"/>
       <c r="L138" s="1"/>
       <c r="M138" s="4" t="s">
-        <v>925</v>
+        <v>923</v>
       </c>
     </row>
     <row r="139" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -62218,17 +62236,17 @@
       </c>
       <c r="B139" s="1"/>
       <c r="C139" s="4" t="s">
-        <v>581</v>
+        <v>580</v>
       </c>
       <c r="D139" s="4"/>
       <c r="E139" s="1"/>
       <c r="F139" s="1"/>
       <c r="G139" s="1"/>
       <c r="H139" s="1" t="s">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="I139" s="1" t="s">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="J139" s="1"/>
       <c r="K139" s="1"/>
@@ -62241,34 +62259,34 @@
         <v>Tropezón</v>
       </c>
       <c r="B140" s="4" t="s">
-        <v>702</v>
+        <v>700</v>
       </c>
       <c r="C140" s="4" t="s">
-        <v>701</v>
+        <v>699</v>
       </c>
       <c r="D140" s="4" t="s">
-        <v>344</v>
+        <v>343</v>
       </c>
       <c r="E140" s="1" t="s">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="F140" s="5" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G140" s="4" t="s">
         <v>1006</v>
-      </c>
-      <c r="G140" s="4" t="s">
-        <v>1008</v>
       </c>
       <c r="H140" s="1"/>
       <c r="I140" s="1"/>
       <c r="J140" s="1" t="s">
-        <v>418</v>
+        <v>417</v>
       </c>
       <c r="K140" s="5" t="s">
-        <v>417</v>
+        <v>416</v>
       </c>
       <c r="L140" s="5"/>
       <c r="M140" s="4" t="s">
-        <v>997</v>
+        <v>995</v>
       </c>
     </row>
     <row r="141" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62277,19 +62295,19 @@
         <v>Vaina</v>
       </c>
       <c r="B141" s="4" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="C141" s="4" t="s">
-        <v>682</v>
+        <v>680</v>
       </c>
       <c r="D141" s="4" t="s">
-        <v>899</v>
+        <v>897</v>
       </c>
       <c r="E141" s="4" t="s">
-        <v>609</v>
+        <v>607</v>
       </c>
       <c r="F141" s="4" t="s">
-        <v>610</v>
+        <v>608</v>
       </c>
       <c r="G141" s="4"/>
       <c r="H141" s="1"/>
@@ -62306,14 +62324,14 @@
       </c>
       <c r="B142" s="1"/>
       <c r="C142" s="4" t="s">
-        <v>653</v>
+        <v>651</v>
       </c>
       <c r="D142" s="4"/>
       <c r="E142" s="4" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="F142" s="5" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G142" s="5"/>
       <c r="H142" s="1"/>
@@ -62329,19 +62347,19 @@
         <v>Vampiro</v>
       </c>
       <c r="B143" s="4" t="s">
-        <v>655</v>
+        <v>653</v>
       </c>
       <c r="C143" s="4" t="s">
-        <v>654</v>
+        <v>652</v>
       </c>
       <c r="D143" s="4" t="s">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="E143" s="1" t="s">
+        <v>536</v>
+      </c>
+      <c r="F143" s="1" t="s">
         <v>537</v>
-      </c>
-      <c r="F143" s="1" t="s">
-        <v>538</v>
       </c>
       <c r="G143" s="1"/>
       <c r="H143" s="1"/>
@@ -62350,7 +62368,7 @@
       <c r="K143" s="1"/>
       <c r="L143" s="1"/>
       <c r="M143" s="4" t="s">
-        <v>929</v>
+        <v>927</v>
       </c>
     </row>
     <row r="144" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62360,33 +62378,33 @@
       </c>
       <c r="B144" s="1"/>
       <c r="C144" s="1" t="s">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="D144" s="4" t="s">
-        <v>347</v>
+        <v>346</v>
       </c>
       <c r="E144" s="1" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="G144" s="1"/>
       <c r="H144" s="1" t="s">
-        <v>1012</v>
+        <v>1010</v>
       </c>
       <c r="I144" s="5" t="s">
-        <v>1013</v>
+        <v>1011</v>
       </c>
       <c r="J144" s="1" t="s">
-        <v>1010</v>
+        <v>1008</v>
       </c>
       <c r="K144" s="5" t="s">
-        <v>1011</v>
+        <v>1009</v>
       </c>
       <c r="L144" s="1"/>
       <c r="M144" s="4" t="s">
-        <v>915</v>
+        <v>913</v>
       </c>
     </row>
     <row r="145" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62395,19 +62413,19 @@
         <v>Vermouth con Soda</v>
       </c>
       <c r="B145" s="4" t="s">
-        <v>656</v>
+        <v>654</v>
       </c>
       <c r="C145" s="4" t="s">
-        <v>746</v>
+        <v>744</v>
       </c>
       <c r="D145" s="4" t="s">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="E145" s="1" t="s">
-        <v>545</v>
+        <v>544</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="G145" s="1"/>
       <c r="H145" s="1"/>
@@ -62416,7 +62434,7 @@
       <c r="K145" s="1"/>
       <c r="L145" s="1"/>
       <c r="M145" s="4" t="s">
-        <v>1033</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="146" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -62426,7 +62444,7 @@
       </c>
       <c r="B146" s="1"/>
       <c r="C146" s="4" t="s">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="D146" s="1"/>
       <c r="E146" s="1"/>
@@ -62446,14 +62464,14 @@
       </c>
       <c r="B147" s="1"/>
       <c r="C147" s="4" t="s">
-        <v>716</v>
+        <v>714</v>
       </c>
       <c r="D147" s="4"/>
       <c r="E147" s="1" t="s">
-        <v>710</v>
+        <v>708</v>
       </c>
       <c r="F147" s="5" t="s">
-        <v>711</v>
+        <v>709</v>
       </c>
       <c r="G147" s="5"/>
       <c r="H147" s="1"/>
@@ -62462,7 +62480,7 @@
       <c r="K147" s="5"/>
       <c r="L147" s="5"/>
       <c r="M147" s="4" t="s">
-        <v>934</v>
+        <v>932</v>
       </c>
     </row>
     <row r="148" spans="1:13" ht="225" x14ac:dyDescent="0.25">
@@ -62472,14 +62490,14 @@
       </c>
       <c r="B148" s="1"/>
       <c r="C148" s="4" t="s">
-        <v>684</v>
+        <v>682</v>
       </c>
       <c r="D148" s="1"/>
       <c r="E148" s="1" t="s">
-        <v>686</v>
+        <v>684</v>
       </c>
       <c r="F148" s="5" t="s">
-        <v>685</v>
+        <v>683</v>
       </c>
       <c r="G148" s="5"/>
       <c r="H148" s="1"/>
@@ -62488,7 +62506,7 @@
       <c r="K148" s="5"/>
       <c r="L148" s="5"/>
       <c r="M148" s="4" t="s">
-        <v>1072</v>
+        <v>1070</v>
       </c>
     </row>
     <row r="149" spans="1:13" ht="324" customHeight="1" x14ac:dyDescent="0.25">
@@ -62498,16 +62516,16 @@
       </c>
       <c r="B149" s="1"/>
       <c r="C149" s="4" t="s">
-        <v>688</v>
+        <v>686</v>
       </c>
       <c r="D149" s="4" t="s">
-        <v>707</v>
+        <v>705</v>
       </c>
       <c r="E149" s="1" t="s">
-        <v>704</v>
+        <v>702</v>
       </c>
       <c r="F149" s="5" t="s">
-        <v>705</v>
+        <v>703</v>
       </c>
       <c r="G149" s="5"/>
       <c r="H149" s="1"/>
@@ -62516,7 +62534,7 @@
       <c r="K149" s="5"/>
       <c r="L149" s="5"/>
       <c r="M149" s="4" t="s">
-        <v>1058</v>
+        <v>1056</v>
       </c>
     </row>
     <row r="150" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62525,19 +62543,19 @@
         <v>Whisky Sour</v>
       </c>
       <c r="B150" s="4" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C150" s="4" t="s">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D150" s="4" t="s">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="E150" s="1" t="s">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="G150" s="1"/>
       <c r="H150" s="1"/>
@@ -62546,7 +62564,7 @@
       <c r="K150" s="1"/>
       <c r="L150" s="1"/>
       <c r="M150" s="4" t="s">
-        <v>906</v>
+        <v>904</v>
       </c>
     </row>
     <row r="151" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -62555,19 +62573,19 @@
         <v>Bramble</v>
       </c>
       <c r="B151" s="4" t="s">
-        <v>753</v>
+        <v>751</v>
       </c>
       <c r="C151" s="4" t="s">
-        <v>752</v>
+        <v>750</v>
       </c>
       <c r="D151" s="4" t="s">
+        <v>785</v>
+      </c>
+      <c r="E151" s="1" t="s">
         <v>787</v>
       </c>
-      <c r="E151" s="1" t="s">
-        <v>789</v>
-      </c>
       <c r="F151" s="1" t="s">
-        <v>788</v>
+        <v>786</v>
       </c>
       <c r="G151" s="1"/>
       <c r="H151" s="1"/>
@@ -62576,7 +62594,7 @@
       <c r="K151" s="1"/>
       <c r="L151" s="1"/>
       <c r="M151" s="4" t="s">
-        <v>1052</v>
+        <v>1050</v>
       </c>
     </row>
     <row r="152" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -62586,14 +62604,14 @@
       </c>
       <c r="B152" s="1"/>
       <c r="C152" s="4" t="s">
-        <v>756</v>
+        <v>754</v>
       </c>
       <c r="D152" s="4"/>
       <c r="E152" s="1" t="s">
-        <v>790</v>
+        <v>788</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>755</v>
+        <v>753</v>
       </c>
       <c r="G152" s="1"/>
       <c r="H152" s="1"/>
@@ -62602,7 +62620,7 @@
       <c r="K152" s="1"/>
       <c r="L152" s="1"/>
       <c r="M152" s="4" t="s">
-        <v>1137</v>
+        <v>1135</v>
       </c>
     </row>
     <row r="153" spans="1:13" ht="240" x14ac:dyDescent="0.25">
@@ -62611,19 +62629,19 @@
         <v>Gin Basil Smash</v>
       </c>
       <c r="B153" s="4" t="s">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="C153" s="4" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="D153" s="4" t="s">
-        <v>793</v>
+        <v>791</v>
       </c>
       <c r="E153" s="4" t="s">
-        <v>791</v>
+        <v>789</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>792</v>
+        <v>790</v>
       </c>
       <c r="G153" s="1"/>
       <c r="H153" s="1"/>
@@ -62640,28 +62658,28 @@
       </c>
       <c r="B154" s="1"/>
       <c r="C154" s="4" t="s">
-        <v>782</v>
+        <v>780</v>
       </c>
       <c r="D154" s="26" t="s">
-        <v>882</v>
+        <v>880</v>
       </c>
       <c r="E154" s="1" t="s">
-        <v>780</v>
+        <v>778</v>
       </c>
       <c r="F154" s="5" t="s">
-        <v>781</v>
+        <v>779</v>
       </c>
       <c r="G154" s="5"/>
       <c r="H154" s="1"/>
       <c r="I154" s="5"/>
       <c r="J154" s="1" t="s">
-        <v>770</v>
+        <v>768</v>
       </c>
       <c r="K154" s="5" t="s">
-        <v>769</v>
+        <v>767</v>
       </c>
       <c r="L154" s="26" t="s">
-        <v>971</v>
+        <v>969</v>
       </c>
       <c r="M154" s="1"/>
     </row>
@@ -62671,13 +62689,13 @@
         <v>Medias de Seda</v>
       </c>
       <c r="B155" s="4" t="s">
-        <v>796</v>
+        <v>794</v>
       </c>
       <c r="C155" s="4" t="s">
-        <v>797</v>
+        <v>795</v>
       </c>
       <c r="D155" s="4" t="s">
-        <v>1064</v>
+        <v>1062</v>
       </c>
       <c r="E155" s="1"/>
       <c r="F155" s="1"/>
@@ -62688,7 +62706,7 @@
       <c r="K155" s="1"/>
       <c r="L155" s="1"/>
       <c r="M155" s="4" t="s">
-        <v>1051</v>
+        <v>1049</v>
       </c>
     </row>
     <row r="156" spans="1:13" ht="255" x14ac:dyDescent="0.25">
@@ -62697,17 +62715,17 @@
         <v>Brandy Sour</v>
       </c>
       <c r="B156" s="4" t="s">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="C156" s="4" t="s">
-        <v>799</v>
+        <v>797</v>
       </c>
       <c r="D156" s="4"/>
       <c r="E156" s="1" t="s">
-        <v>801</v>
+        <v>799</v>
       </c>
       <c r="F156" s="5" t="s">
-        <v>800</v>
+        <v>798</v>
       </c>
       <c r="G156" s="5"/>
       <c r="H156" s="1"/>
@@ -62723,19 +62741,19 @@
         <v>Juanito Rosado</v>
       </c>
       <c r="B157" s="4" t="s">
-        <v>804</v>
+        <v>802</v>
       </c>
       <c r="C157" s="4" t="s">
-        <v>803</v>
+        <v>801</v>
       </c>
       <c r="D157" s="4" t="s">
-        <v>433</v>
+        <v>432</v>
       </c>
       <c r="E157" s="1" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="G157" s="1"/>
       <c r="H157" s="1"/>
@@ -62751,30 +62769,30 @@
         <v>Vino Navegado</v>
       </c>
       <c r="B158" s="4" t="s">
-        <v>870</v>
+        <v>868</v>
       </c>
       <c r="C158" s="4" t="s">
-        <v>828</v>
+        <v>826</v>
       </c>
       <c r="D158" s="10"/>
       <c r="E158" s="1" t="s">
-        <v>857</v>
+        <v>855</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>856</v>
+        <v>854</v>
       </c>
       <c r="G158" s="1"/>
       <c r="H158" s="1"/>
       <c r="I158" s="5"/>
       <c r="J158" s="4" t="s">
-        <v>1130</v>
+        <v>1128</v>
       </c>
       <c r="K158" s="5" t="s">
-        <v>1131</v>
+        <v>1129</v>
       </c>
       <c r="L158" s="1"/>
       <c r="M158" s="4" t="s">
-        <v>1133</v>
+        <v>1131</v>
       </c>
     </row>
     <row r="159" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62783,32 +62801,32 @@
         <v>Cola de Mono</v>
       </c>
       <c r="B159" s="4" t="s">
-        <v>845</v>
+        <v>843</v>
       </c>
       <c r="C159" s="4" t="s">
+        <v>814</v>
+      </c>
+      <c r="D159" s="4" t="s">
+        <v>818</v>
+      </c>
+      <c r="E159" s="1" t="s">
+        <v>817</v>
+      </c>
+      <c r="F159" s="5" t="s">
         <v>816</v>
-      </c>
-      <c r="D159" s="4" t="s">
-        <v>820</v>
-      </c>
-      <c r="E159" s="1" t="s">
-        <v>819</v>
-      </c>
-      <c r="F159" s="5" t="s">
-        <v>818</v>
       </c>
       <c r="G159" s="5"/>
       <c r="H159" s="1" t="s">
-        <v>827</v>
+        <v>825</v>
       </c>
       <c r="I159" s="10" t="s">
-        <v>826</v>
+        <v>824</v>
       </c>
       <c r="J159" s="1"/>
       <c r="K159" s="1"/>
       <c r="L159" s="1"/>
       <c r="M159" s="4" t="s">
-        <v>927</v>
+        <v>925</v>
       </c>
     </row>
     <row r="160" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62817,34 +62835,34 @@
         <v>Chichón</v>
       </c>
       <c r="B160" s="4" t="s">
-        <v>825</v>
+        <v>823</v>
       </c>
       <c r="C160" s="4" t="s">
-        <v>824</v>
+        <v>822</v>
       </c>
       <c r="D160" s="4" t="s">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="E160" s="1" t="s">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="F160" s="5" t="s">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="G160" s="4" t="s">
-        <v>1002</v>
+        <v>1000</v>
       </c>
       <c r="H160" s="1"/>
       <c r="I160" s="5"/>
       <c r="J160" s="1" t="s">
-        <v>1119</v>
+        <v>1117</v>
       </c>
       <c r="K160" s="5" t="s">
-        <v>1120</v>
+        <v>1118</v>
       </c>
       <c r="L160" s="1"/>
       <c r="M160" s="4" t="s">
-        <v>1009</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="161" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -62853,10 +62871,10 @@
         <v>Ramos Fizz</v>
       </c>
       <c r="B161" s="4" t="s">
-        <v>836</v>
+        <v>834</v>
       </c>
       <c r="C161" s="4" t="s">
-        <v>1074</v>
+        <v>1072</v>
       </c>
       <c r="D161" s="4"/>
       <c r="E161" s="1"/>
@@ -62868,7 +62886,7 @@
       <c r="K161" s="1"/>
       <c r="L161" s="1"/>
       <c r="M161" s="4" t="s">
-        <v>1075</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="162" spans="1:13" ht="195" x14ac:dyDescent="0.25">
@@ -62877,29 +62895,29 @@
         <v>Gin Fizz</v>
       </c>
       <c r="B162" s="4" t="s">
-        <v>832</v>
+        <v>830</v>
       </c>
       <c r="C162" s="4" t="s">
-        <v>835</v>
+        <v>833</v>
       </c>
       <c r="D162" s="4"/>
       <c r="E162" s="1" t="s">
-        <v>834</v>
+        <v>832</v>
       </c>
       <c r="F162" s="5" t="s">
-        <v>833</v>
+        <v>831</v>
       </c>
       <c r="G162" s="5"/>
       <c r="H162" s="5"/>
       <c r="I162" s="5"/>
       <c r="J162" s="1" t="s">
-        <v>1146</v>
+        <v>1144</v>
       </c>
       <c r="K162" s="5" t="s">
+        <v>1143</v>
+      </c>
+      <c r="L162" s="4" t="s">
         <v>1145</v>
-      </c>
-      <c r="L162" s="4" t="s">
-        <v>1147</v>
       </c>
       <c r="M162" s="1"/>
     </row>
@@ -62910,16 +62928,16 @@
       </c>
       <c r="B163" s="1"/>
       <c r="C163" s="4" t="s">
-        <v>848</v>
+        <v>846</v>
       </c>
       <c r="D163" s="4" t="s">
+        <v>845</v>
+      </c>
+      <c r="E163" s="1" t="s">
+        <v>1071</v>
+      </c>
+      <c r="F163" s="5" t="s">
         <v>847</v>
-      </c>
-      <c r="E163" s="1" t="s">
-        <v>1073</v>
-      </c>
-      <c r="F163" s="5" t="s">
-        <v>849</v>
       </c>
       <c r="G163" s="5"/>
       <c r="H163" s="1"/>
@@ -62928,7 +62946,7 @@
       <c r="K163" s="1"/>
       <c r="L163" s="1"/>
       <c r="M163" s="4" t="s">
-        <v>962</v>
+        <v>960</v>
       </c>
     </row>
     <row r="164" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62938,29 +62956,29 @@
       </c>
       <c r="B164" s="4"/>
       <c r="C164" s="4" t="s">
-        <v>858</v>
+        <v>856</v>
       </c>
       <c r="D164" s="4" t="s">
-        <v>855</v>
+        <v>853</v>
       </c>
       <c r="E164" s="1" t="s">
-        <v>853</v>
+        <v>851</v>
       </c>
       <c r="F164" s="5" t="s">
-        <v>852</v>
+        <v>850</v>
       </c>
       <c r="G164" s="5"/>
       <c r="H164" s="1"/>
       <c r="I164" s="5"/>
       <c r="J164" s="1" t="s">
-        <v>860</v>
+        <v>858</v>
       </c>
       <c r="K164" s="1" t="s">
-        <v>859</v>
+        <v>857</v>
       </c>
       <c r="L164" s="1"/>
       <c r="M164" s="4" t="s">
-        <v>854</v>
+        <v>852</v>
       </c>
     </row>
     <row r="165" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -62969,22 +62987,22 @@
         <v>Pihuelo</v>
       </c>
       <c r="B165" s="4" t="s">
-        <v>863</v>
+        <v>861</v>
       </c>
       <c r="C165" s="4" t="s">
-        <v>864</v>
+        <v>862</v>
       </c>
       <c r="D165" s="4" t="s">
-        <v>867</v>
+        <v>865</v>
       </c>
       <c r="E165" s="4" t="s">
+        <v>1012</v>
+      </c>
+      <c r="F165" s="5" t="s">
+        <v>1013</v>
+      </c>
+      <c r="G165" s="1" t="s">
         <v>1014</v>
-      </c>
-      <c r="F165" s="5" t="s">
-        <v>1015</v>
-      </c>
-      <c r="G165" s="1" t="s">
-        <v>1016</v>
       </c>
       <c r="H165" s="1"/>
       <c r="I165" s="5"/>
@@ -62992,7 +63010,7 @@
       <c r="K165" s="1"/>
       <c r="L165" s="1"/>
       <c r="M165" s="4" t="s">
-        <v>976</v>
+        <v>974</v>
       </c>
     </row>
     <row r="166" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -63001,19 +63019,19 @@
         <v>Mojito Sandía</v>
       </c>
       <c r="B166" s="4" t="s">
-        <v>875</v>
+        <v>873</v>
       </c>
       <c r="C166" s="4" t="s">
-        <v>876</v>
+        <v>874</v>
       </c>
       <c r="D166" s="4" t="s">
-        <v>880</v>
+        <v>878</v>
       </c>
       <c r="E166" s="1" t="s">
-        <v>873</v>
+        <v>871</v>
       </c>
       <c r="F166" s="5" t="s">
-        <v>874</v>
+        <v>872</v>
       </c>
       <c r="G166" s="5"/>
       <c r="H166" s="1"/>
@@ -63022,7 +63040,7 @@
       <c r="K166" s="1"/>
       <c r="L166" s="1"/>
       <c r="M166" s="4" t="s">
-        <v>881</v>
+        <v>879</v>
       </c>
     </row>
     <row r="167" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -63032,7 +63050,7 @@
       </c>
       <c r="B167" s="1"/>
       <c r="C167" s="4" t="s">
-        <v>886</v>
+        <v>884</v>
       </c>
       <c r="D167" s="4"/>
       <c r="E167" s="1"/>
@@ -63044,7 +63062,7 @@
       <c r="K167" s="1"/>
       <c r="L167" s="1"/>
       <c r="M167" s="4" t="s">
-        <v>1029</v>
+        <v>1027</v>
       </c>
     </row>
     <row r="168" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -63054,7 +63072,7 @@
       </c>
       <c r="B168" s="1"/>
       <c r="C168" s="4" t="s">
-        <v>988</v>
+        <v>986</v>
       </c>
       <c r="D168" s="4"/>
       <c r="E168" s="1"/>
@@ -63066,7 +63084,7 @@
       <c r="K168" s="1"/>
       <c r="L168" s="1"/>
       <c r="M168" s="4" t="s">
-        <v>991</v>
+        <v>989</v>
       </c>
     </row>
     <row r="169" spans="1:13" ht="120" x14ac:dyDescent="0.25">
@@ -63075,28 +63093,28 @@
         <v>Chardonnay Sour</v>
       </c>
       <c r="B169" s="4" t="s">
+        <v>888</v>
+      </c>
+      <c r="C169" s="4" t="s">
         <v>890</v>
-      </c>
-      <c r="C169" s="4" t="s">
-        <v>892</v>
       </c>
       <c r="D169" s="4"/>
       <c r="E169" s="1" t="s">
-        <v>1095</v>
+        <v>1093</v>
       </c>
       <c r="F169" s="5" t="s">
+        <v>1092</v>
+      </c>
+      <c r="G169" s="4" t="s">
         <v>1094</v>
-      </c>
-      <c r="G169" s="4" t="s">
-        <v>1096</v>
       </c>
       <c r="H169" s="1"/>
       <c r="I169" s="5"/>
       <c r="J169" s="1" t="s">
-        <v>1101</v>
+        <v>1099</v>
       </c>
       <c r="K169" s="5" t="s">
-        <v>1100</v>
+        <v>1098</v>
       </c>
       <c r="L169" s="1"/>
       <c r="M169" s="1"/>
@@ -63107,19 +63125,19 @@
         <v>Carmenere Sour</v>
       </c>
       <c r="B170" s="4" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C170" s="4" t="s">
-        <v>894</v>
+        <v>892</v>
       </c>
       <c r="D170" s="4" t="s">
-        <v>901</v>
+        <v>899</v>
       </c>
       <c r="E170" s="1" t="s">
-        <v>469</v>
+        <v>468</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>468</v>
+        <v>467</v>
       </c>
       <c r="G170" s="1"/>
       <c r="H170" s="1"/>
@@ -63128,7 +63146,7 @@
       <c r="K170" s="1"/>
       <c r="L170" s="1"/>
       <c r="M170" s="4" t="s">
-        <v>893</v>
+        <v>891</v>
       </c>
     </row>
     <row r="171" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
@@ -63137,13 +63155,13 @@
         <v>Jerez Sour</v>
       </c>
       <c r="B171" s="4" t="s">
-        <v>891</v>
+        <v>889</v>
       </c>
       <c r="C171" s="4" t="s">
-        <v>900</v>
+        <v>898</v>
       </c>
       <c r="D171" s="4" t="s">
-        <v>883</v>
+        <v>881</v>
       </c>
       <c r="E171" s="1"/>
       <c r="F171" s="1"/>
@@ -63154,7 +63172,7 @@
       <c r="K171" s="1"/>
       <c r="L171" s="1"/>
       <c r="M171" s="4" t="s">
-        <v>898</v>
+        <v>896</v>
       </c>
     </row>
     <row r="172" spans="1:13" ht="180" x14ac:dyDescent="0.25">
@@ -63164,7 +63182,7 @@
       </c>
       <c r="B172" s="4"/>
       <c r="C172" s="4" t="s">
-        <v>1048</v>
+        <v>1046</v>
       </c>
       <c r="D172" s="4"/>
       <c r="E172" s="1"/>
@@ -63176,7 +63194,7 @@
       <c r="K172" s="1"/>
       <c r="L172" s="1"/>
       <c r="M172" s="4" t="s">
-        <v>1049</v>
+        <v>1047</v>
       </c>
     </row>
     <row r="173" spans="1:13" ht="105" x14ac:dyDescent="0.25">
@@ -63196,7 +63214,7 @@
       <c r="K173" s="1"/>
       <c r="L173" s="1"/>
       <c r="M173" s="4" t="s">
-        <v>1069</v>
+        <v>1067</v>
       </c>
     </row>
     <row r="174" spans="1:13" ht="135" x14ac:dyDescent="0.25">
@@ -63205,7 +63223,7 @@
         <v>Campari Spritz</v>
       </c>
       <c r="B174" s="4" t="s">
-        <v>1070</v>
+        <v>1068</v>
       </c>
       <c r="C174" s="4"/>
       <c r="D174" s="4"/>
@@ -63218,7 +63236,7 @@
       <c r="K174" s="1"/>
       <c r="L174" s="1"/>
       <c r="M174" s="4" t="s">
-        <v>1068</v>
+        <v>1066</v>
       </c>
     </row>
     <row r="175" spans="1:13" ht="255" x14ac:dyDescent="0.25">
@@ -63227,10 +63245,10 @@
         <v>Hanky Panky</v>
       </c>
       <c r="B175" s="4" t="s">
-        <v>1128</v>
+        <v>1126</v>
       </c>
       <c r="C175" s="4" t="s">
-        <v>1127</v>
+        <v>1125</v>
       </c>
       <c r="D175" s="4"/>
       <c r="E175" s="1"/>
@@ -63242,7 +63260,7 @@
       <c r="K175" s="1"/>
       <c r="L175" s="1"/>
       <c r="M175" s="4" t="s">
-        <v>1129</v>
+        <v>1127</v>
       </c>
     </row>
     <row r="176" spans="1:13" x14ac:dyDescent="0.25">
@@ -64731,10 +64749,10 @@
         <v>62</v>
       </c>
       <c r="B2" t="s">
-        <v>771</v>
+        <v>769</v>
       </c>
       <c r="C2" t="s">
-        <v>574</v>
+        <v>573</v>
       </c>
     </row>
     <row r="3" spans="1:3" x14ac:dyDescent="0.25">
@@ -64742,10 +64760,10 @@
         <v>67</v>
       </c>
       <c r="B3" t="s">
-        <v>772</v>
+        <v>770</v>
       </c>
       <c r="C3" t="s">
-        <v>202</v>
+        <v>201</v>
       </c>
     </row>
     <row r="4" spans="1:3" x14ac:dyDescent="0.25">
@@ -64753,10 +64771,10 @@
         <v>68</v>
       </c>
       <c r="B4" t="s">
-        <v>773</v>
+        <v>771</v>
       </c>
       <c r="C4" t="s">
-        <v>611</v>
+        <v>609</v>
       </c>
     </row>
     <row r="5" spans="1:3" x14ac:dyDescent="0.25">
@@ -64764,10 +64782,10 @@
         <v>63</v>
       </c>
       <c r="B5" t="s">
-        <v>774</v>
+        <v>772</v>
       </c>
       <c r="C5" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
     </row>
     <row r="6" spans="1:3" x14ac:dyDescent="0.25">
@@ -64775,10 +64793,10 @@
         <v>69</v>
       </c>
       <c r="B6" t="s">
+        <v>774</v>
+      </c>
+      <c r="C6" t="s">
         <v>776</v>
-      </c>
-      <c r="C6" t="s">
-        <v>778</v>
       </c>
     </row>
     <row r="7" spans="1:3" x14ac:dyDescent="0.25">
@@ -64786,7 +64804,7 @@
         <v>70</v>
       </c>
       <c r="B7" t="s">
-        <v>775</v>
+        <v>773</v>
       </c>
       <c r="C7" t="s">
         <v>71</v>
@@ -64794,24 +64812,24 @@
     </row>
     <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>729</v>
+        <v>727</v>
       </c>
       <c r="B8" t="s">
-        <v>779</v>
+        <v>777</v>
       </c>
       <c r="C8" t="s">
-        <v>777</v>
+        <v>775</v>
       </c>
     </row>
     <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
+        <v>803</v>
+      </c>
+      <c r="B9" t="s">
+        <v>804</v>
+      </c>
+      <c r="C9" t="s">
         <v>805</v>
-      </c>
-      <c r="B9" t="s">
-        <v>806</v>
-      </c>
-      <c r="C9" t="s">
-        <v>807</v>
       </c>
     </row>
   </sheetData>
@@ -64841,7 +64859,7 @@
         <v>115</v>
       </c>
       <c r="B2" s="23" t="s">
-        <v>515</v>
+        <v>514</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -64849,7 +64867,7 @@
         <v>116</v>
       </c>
       <c r="B3" s="23" t="s">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="90" x14ac:dyDescent="0.25">
@@ -64857,7 +64875,7 @@
         <v>117</v>
       </c>
       <c r="B4" s="23" t="s">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="5" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -64865,7 +64883,7 @@
         <v>118</v>
       </c>
       <c r="B5" s="23" t="s">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="6" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -64873,7 +64891,7 @@
         <v>119</v>
       </c>
       <c r="B6" s="23" t="s">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="7" spans="1:2" ht="75" x14ac:dyDescent="0.25">
@@ -64881,39 +64899,39 @@
         <v>120</v>
       </c>
       <c r="B7" s="23" t="s">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="8" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A8" s="23" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="B8" s="23" t="s">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="9" spans="1:2" ht="75" x14ac:dyDescent="0.25">
       <c r="A9" s="23" t="s">
-        <v>427</v>
+        <v>426</v>
       </c>
       <c r="B9" s="23" t="s">
-        <v>765</v>
+        <v>763</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A10" s="23" t="s">
-        <v>514</v>
+        <v>513</v>
       </c>
       <c r="B10" s="23" t="s">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="11" spans="1:2" ht="90" x14ac:dyDescent="0.25">
       <c r="A11" s="23" t="s">
-        <v>699</v>
+        <v>697</v>
       </c>
       <c r="B11" s="23" t="s">
-        <v>700</v>
+        <v>698</v>
       </c>
     </row>
   </sheetData>

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AC8D022-961C-42C0-91B0-4E65FE3A386B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3FC672B-ABEE-469B-ADB6-D47CCDE406F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
@@ -45,7 +45,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1711" uniqueCount="1150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1722" uniqueCount="1158">
   <si>
     <t>Ramazzotti Spritz</t>
   </si>
@@ -5269,6 +5269,37 @@
   <si>
     <t>California_Clipper_500.jpg
 Pasaje de un barco clipper que muestra escenas de la Fiebre del Oro de California, alrededor de 1850, y resalta su papel en el transporte de buscadores de fortuna hacia San Francisco. Un clipper era un tipo de velero rápido del siglo XIX, diseñado para recorrer grandes distancias en el menor tiempo posible. La Fiebre del Oro de California comenzó en 1848, cuando se descubrió oro en Sutter’s Mill, cerca del río American. La noticia se difundió rápidamente y, entre 1849 y comienzos de la década de 1850, cientos de miles de personas viajaron a California para buscar fortuna. Como consecuencia, San Francisco pasó en pocos años de ser un pequeño puerto a convertirse en una ciudad importante.</t>
+  </si>
+  <si>
+    <t>Bicicletta</t>
+  </si>
+  <si>
+    <t>Llena un vaso con hielo. Agrega el Campari y el vino blanco. Completa con agua con gas. Revuelve suavemente para integrar los ingredientes y decora con una rodaja de naranja.</t>
+  </si>
+  <si>
+    <t>Según la tradición popular, la Bicicletta, clásico aperitivo italiano, debe su nombre al tambaleante medio de transporte que utilizaban los ancianos tras una tarde, o una noche,  especialmente animada.</t>
+  </si>
+  <si>
+    <t>https://www.youtube.com/watch?v=XKcXwEAHkWM</t>
+  </si>
+  <si>
+    <t>León Gieco - El Angel De La Bicicleta</t>
+  </si>
+  <si>
+    <t>Pocho y la bicicleta
+Claudio “Pocho” Lepratti nació en 1966 en la provincia de Entre Ríos, Argentina, y desde joven manifestó una profunda vocación social. A fines de los años ochenta ingresó a la congregación salesiana, donde inició estudios de formación religiosa y trabajo comunitario. Esa experiencia consolidó su compromiso con los sectores más vulnerables. Aunque más tarde dejó la vida religiosa formal, mantuvo intacta su opción por el trabajo territorial y se radicó en Rosario, donde desarrolló tareas sociales en barrios populares de la zona sur.
+En Rosario trabajó con niños y jóvenes en situación de pobreza, participando en comedores comunitarios, espacios educativos y proyectos culturales. Quienes lo conocieron destacan su cercanía, su sencillez y su convicción de que la educación y la organización comunitaria eran herramientas fundamentales para la dignidad. En ese entramado barrial, la bicicleta fue parte esencial de su vida. Era su medio de transporte habitual: con ella recorría largas distancias entre escuelas, parroquias y comedores, llevando materiales, alimentos o simplemente su tiempo. La bicicleta simbolizaba su modo de estar en el mundo: cercano, austero y siempre en movimiento al servicio de los demás.
+A fines de 2001, Pocho trabajaba como auxiliar de cocina en el comedor de la Escuela Nº 756 José M. Serrano, del barrio Las Flores, en el sudoeste de Rosario. El 19 de diciembre, en medio de la crisis que culminaría con la renuncia del presidente Fernando de la Rúa, varios policías provenientes de Arroyo Seco comenzaron a disparar en las inmediaciones de la escuela. Lepratti subió al techo y, al asomarse, gritó: “¡Dejen de tirar, que hay chicos!”.
+El agente Esteban Velásquez abrió fuego con su escopeta y le dio en la tráquea, causándole la muerte casi instantánea. Pocho tenía 35 años.
+Los policías involucrados argumentaron que habían respondido a un supuesto ataque armado desde el techo. Sin embargo, las pericias demostraron que los impactos en el patrullero se habían realizado a nivel del suelo. Esteban Velásquez fue condenado a 14 años de prisión por homicidio, y otros cinco policías, fueron condenados por falsedad ideológica y encubrimiento agravado, al comprobarse que habían baleado el vehículo policial para simular un enfrentamiento.
+La figura de Pocho quedó asociada para siempre a la bicicleta, especialmente tras la canción “El ángel de la bicicleta” de León Gieco, que transformó ese objeto cotidiano en símbolo de compromiso, ternura y resistencia. Pero el nombre de Pocho nombre también permanece ligado al activismo social y a la militancia territorial en los barrios populares de Rosario: a un compromiso profundo con la justicia social, hecha de presencia, trabajo comunitario y defensa de la vida. Desde entonces, la bicicleta no es solo el medio con el que recorría los barrios, sino también la imagen de una ética solidaria que eligió ponerse delante de las balas para proteger a los demás.</t>
+  </si>
+  <si>
+    <t>Pocho.jpg
+Claudio “Pocho” Lepratti (27 de febrero de 1966 - 19 de diciembre de 2001)</t>
+  </si>
+  <si>
+    <t>Existe una variante interesante que reemplaza la gaseosa de limón por gaseosa de pomelo. El resultado es un Tinto de Verano con un amargor cítrico que realza el carácter del vino tinto y sorprende.</t>
   </si>
 </sst>
 </file>
@@ -5837,7 +5868,6 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C7FAA63B-DEDB-48F1-9CCA-3BF0BF1CD86F}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:EW250"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
@@ -6364,7 +6394,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="2" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A2" s="1" t="s">
         <v>275</v>
       </c>
@@ -6546,7 +6576,7 @@
       <c r="EV2" s="2"/>
       <c r="EW2" s="2"/>
     </row>
-    <row r="3" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>225</v>
       </c>
@@ -6722,7 +6752,7 @@
       <c r="EV3" s="2"/>
       <c r="EW3" s="2"/>
     </row>
-    <row r="4" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>235</v>
       </c>
@@ -6902,7 +6932,7 @@
       <c r="EV4" s="2"/>
       <c r="EW4" s="2"/>
     </row>
-    <row r="5" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>226</v>
       </c>
@@ -7078,7 +7108,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
         <v>42</v>
       </c>
@@ -7258,7 +7288,7 @@
       <c r="EV6" s="2"/>
       <c r="EW6" s="2"/>
     </row>
-    <row r="7" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>41</v>
       </c>
@@ -7436,7 +7466,7 @@
       <c r="EV7" s="2"/>
       <c r="EW7" s="2"/>
     </row>
-    <row r="8" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
         <v>31</v>
       </c>
@@ -7614,7 +7644,7 @@
       <c r="EV8" s="2"/>
       <c r="EW8" s="2"/>
     </row>
-    <row r="9" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
         <v>186</v>
       </c>
@@ -7794,7 +7824,7 @@
       <c r="EV9" s="2"/>
       <c r="EW9" s="2"/>
     </row>
-    <row r="10" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A10" s="1" t="s">
         <v>571</v>
       </c>
@@ -7976,7 +8006,7 @@
       <c r="EV10" s="2"/>
       <c r="EW10" s="2"/>
     </row>
-    <row r="11" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
         <v>1</v>
       </c>
@@ -8154,7 +8184,7 @@
       <c r="EV11" s="2"/>
       <c r="EW11" s="2"/>
     </row>
-    <row r="12" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A12" s="1" t="s">
         <v>550</v>
       </c>
@@ -8334,7 +8364,7 @@
       <c r="EV12" s="2"/>
       <c r="EW12" s="2"/>
     </row>
-    <row r="13" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A13" s="1" t="s">
         <v>210</v>
       </c>
@@ -8506,7 +8536,7 @@
       <c r="EV13" s="2"/>
       <c r="EW13" s="2"/>
     </row>
-    <row r="14" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
         <v>176</v>
       </c>
@@ -8688,7 +8718,7 @@
       <c r="EV14" s="2"/>
       <c r="EW14" s="2"/>
     </row>
-    <row r="15" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
         <v>227</v>
       </c>
@@ -8862,7 +8892,7 @@
       <c r="EV15" s="2"/>
       <c r="EW15" s="2"/>
     </row>
-    <row r="16" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A16" s="13" t="s">
         <v>598</v>
       </c>
@@ -9040,7 +9070,7 @@
       <c r="EV16" s="2"/>
       <c r="EW16" s="2"/>
     </row>
-    <row r="17" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
         <v>23</v>
       </c>
@@ -9226,7 +9256,7 @@
       <c r="EV17" s="2"/>
       <c r="EW17" s="2"/>
     </row>
-    <row r="18" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A18" s="1" t="s">
         <v>212</v>
       </c>
@@ -9412,7 +9442,7 @@
       <c r="EV18" s="2"/>
       <c r="EW18" s="2"/>
     </row>
-    <row r="19" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A19" s="1" t="s">
         <v>258</v>
       </c>
@@ -9590,7 +9620,7 @@
       <c r="EV19" s="2"/>
       <c r="EW19" s="2"/>
     </row>
-    <row r="20" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
         <v>439</v>
       </c>
@@ -9768,7 +9798,7 @@
       <c r="EV20" s="2"/>
       <c r="EW20" s="2"/>
     </row>
-    <row r="21" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
         <v>278</v>
       </c>
@@ -9946,7 +9976,7 @@
       <c r="EV21" s="2"/>
       <c r="EW21" s="2"/>
     </row>
-    <row r="22" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A22" s="1" t="s">
         <v>562</v>
       </c>
@@ -10124,7 +10154,7 @@
       <c r="EV22" s="2"/>
       <c r="EW22" s="2"/>
     </row>
-    <row r="23" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A23" s="3" t="s">
         <v>240</v>
       </c>
@@ -10302,7 +10332,7 @@
       <c r="EV23" s="2"/>
       <c r="EW23" s="2"/>
     </row>
-    <row r="24" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A24" s="1" t="s">
         <v>47</v>
       </c>
@@ -10474,7 +10504,7 @@
       <c r="EV24" s="2"/>
       <c r="EW24" s="2"/>
     </row>
-    <row r="25" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A25" s="1" t="s">
         <v>27</v>
       </c>
@@ -10654,7 +10684,7 @@
       <c r="EV25" s="2"/>
       <c r="EW25" s="2"/>
     </row>
-    <row r="26" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A26" s="1" t="s">
         <v>483</v>
       </c>
@@ -10832,7 +10862,7 @@
       <c r="EV26" s="2"/>
       <c r="EW26" s="2"/>
     </row>
-    <row r="27" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A27" s="1" t="s">
         <v>671</v>
       </c>
@@ -11010,7 +11040,7 @@
       <c r="EV27" s="2"/>
       <c r="EW27" s="2"/>
     </row>
-    <row r="28" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
         <v>147</v>
       </c>
@@ -11188,7 +11218,7 @@
       <c r="EV28" s="2"/>
       <c r="EW28" s="2"/>
     </row>
-    <row r="29" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
         <v>38</v>
       </c>
@@ -11364,7 +11394,7 @@
       <c r="EV29" s="2"/>
       <c r="EW29" s="2"/>
     </row>
-    <row r="30" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
         <v>693</v>
       </c>
@@ -11542,7 +11572,7 @@
       <c r="EV30" s="2"/>
       <c r="EW30" s="2"/>
     </row>
-    <row r="31" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
         <v>582</v>
       </c>
@@ -11720,7 +11750,7 @@
       <c r="EV31" s="2"/>
       <c r="EW31" s="2"/>
     </row>
-    <row r="32" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A32" s="1" t="s">
         <v>694</v>
       </c>
@@ -11898,7 +11928,7 @@
       <c r="EV32" s="2"/>
       <c r="EW32" s="2"/>
     </row>
-    <row r="33" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A33" s="1" t="s">
         <v>512</v>
       </c>
@@ -12074,7 +12104,7 @@
       <c r="EV33" s="2"/>
       <c r="EW33" s="2"/>
     </row>
-    <row r="34" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A34" s="1" t="s">
         <v>185</v>
       </c>
@@ -12256,7 +12286,7 @@
       <c r="EV34" s="2"/>
       <c r="EW34" s="2"/>
     </row>
-    <row r="35" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A35" s="1" t="s">
         <v>241</v>
       </c>
@@ -12432,7 +12462,7 @@
       <c r="EV35" s="2"/>
       <c r="EW35" s="2"/>
     </row>
-    <row r="36" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A36" s="1" t="s">
         <v>510</v>
       </c>
@@ -12608,7 +12638,7 @@
       <c r="EV36" s="2"/>
       <c r="EW36" s="2"/>
     </row>
-    <row r="37" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A37" s="1" t="s">
         <v>570</v>
       </c>
@@ -12790,7 +12820,7 @@
       <c r="EV37" s="2"/>
       <c r="EW37" s="2"/>
     </row>
-    <row r="38" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A38" s="1" t="s">
         <v>504</v>
       </c>
@@ -12968,7 +12998,7 @@
       <c r="EV38" s="2"/>
       <c r="EW38" s="2"/>
     </row>
-    <row r="39" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A39" s="1" t="s">
         <v>200</v>
       </c>
@@ -13146,7 +13176,7 @@
       <c r="EV39" s="2"/>
       <c r="EW39" s="2"/>
     </row>
-    <row r="40" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A40" s="1" t="s">
         <v>28</v>
       </c>
@@ -13320,7 +13350,7 @@
       <c r="EV40" s="2"/>
       <c r="EW40" s="2"/>
     </row>
-    <row r="41" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A41" s="1" t="s">
         <v>306</v>
       </c>
@@ -13498,7 +13528,7 @@
       <c r="EV41" s="2"/>
       <c r="EW41" s="2"/>
     </row>
-    <row r="42" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A42" s="1" t="s">
         <v>26</v>
       </c>
@@ -13854,7 +13884,7 @@
       <c r="EV43" s="2"/>
       <c r="EW43" s="2"/>
     </row>
-    <row r="44" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A44" s="1" t="s">
         <v>265</v>
       </c>
@@ -14026,7 +14056,7 @@
       <c r="EV44" s="2"/>
       <c r="EW44" s="2"/>
     </row>
-    <row r="45" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A45" s="1" t="s">
         <v>247</v>
       </c>
@@ -14198,7 +14228,7 @@
       <c r="EV45" s="2"/>
       <c r="EW45" s="2"/>
     </row>
-    <row r="46" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A46" s="1" t="s">
         <v>46</v>
       </c>
@@ -14378,7 +14408,7 @@
       <c r="EV46" s="2"/>
       <c r="EW46" s="2"/>
     </row>
-    <row r="47" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A47" s="1" t="s">
         <v>299</v>
       </c>
@@ -14556,7 +14586,7 @@
       <c r="EV47" s="2"/>
       <c r="EW47" s="2"/>
     </row>
-    <row r="48" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A48" s="1" t="s">
         <v>224</v>
       </c>
@@ -14734,7 +14764,7 @@
       <c r="EV48" s="2"/>
       <c r="EW48" s="2"/>
     </row>
-    <row r="49" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A49" s="1" t="s">
         <v>293</v>
       </c>
@@ -14916,7 +14946,7 @@
       <c r="EV49" s="2"/>
       <c r="EW49" s="2"/>
     </row>
-    <row r="50" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A50" s="1" t="s">
         <v>477</v>
       </c>
@@ -15096,7 +15126,7 @@
       <c r="EV50" s="2"/>
       <c r="EW50" s="2"/>
     </row>
-    <row r="51" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A51" s="1" t="s">
         <v>490</v>
       </c>
@@ -15272,7 +15302,7 @@
       <c r="EV51" s="2"/>
       <c r="EW51" s="2"/>
     </row>
-    <row r="52" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A52" s="1" t="s">
         <v>190</v>
       </c>
@@ -15456,7 +15486,7 @@
       <c r="EV52" s="2"/>
       <c r="EW52" s="2"/>
     </row>
-    <row r="53" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A53" s="1" t="s">
         <v>380</v>
       </c>
@@ -15628,7 +15658,7 @@
       <c r="EV53" s="2"/>
       <c r="EW53" s="2"/>
     </row>
-    <row r="54" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A54" s="1" t="s">
         <v>276</v>
       </c>
@@ -15808,7 +15838,7 @@
       <c r="EV54" s="2"/>
       <c r="EW54" s="2"/>
     </row>
-    <row r="55" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A55" s="1" t="s">
         <v>14</v>
       </c>
@@ -15990,7 +16020,7 @@
       <c r="EV55" s="2"/>
       <c r="EW55" s="2"/>
     </row>
-    <row r="56" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A56" s="1" t="s">
         <v>392</v>
       </c>
@@ -16166,7 +16196,7 @@
       <c r="EV56" s="2"/>
       <c r="EW56" s="2"/>
     </row>
-    <row r="57" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A57" s="1" t="s">
         <v>149</v>
       </c>
@@ -16344,7 +16374,7 @@
       <c r="EV57" s="2"/>
       <c r="EW57" s="2"/>
     </row>
-    <row r="58" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A58" s="1" t="s">
         <v>43</v>
       </c>
@@ -16524,7 +16554,7 @@
       <c r="EV58" s="2"/>
       <c r="EW58" s="2"/>
     </row>
-    <row r="59" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A59" s="1" t="s">
         <v>352</v>
       </c>
@@ -16700,7 +16730,7 @@
       <c r="EV59" s="2"/>
       <c r="EW59" s="2"/>
     </row>
-    <row r="60" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A60" s="1" t="s">
         <v>239</v>
       </c>
@@ -16878,7 +16908,7 @@
       <c r="EV60" s="2"/>
       <c r="EW60" s="2"/>
     </row>
-    <row r="61" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A61" s="1" t="s">
         <v>20</v>
       </c>
@@ -17052,7 +17082,7 @@
       <c r="EV61" s="2"/>
       <c r="EW61" s="2"/>
     </row>
-    <row r="62" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A62" s="1" t="s">
         <v>9</v>
       </c>
@@ -17228,7 +17258,7 @@
       <c r="EV62" s="2"/>
       <c r="EW62" s="2"/>
     </row>
-    <row r="63" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A63" s="1" t="s">
         <v>4</v>
       </c>
@@ -17404,7 +17434,7 @@
       <c r="EV63" s="2"/>
       <c r="EW63" s="2"/>
     </row>
-    <row r="64" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A64" s="1" t="s">
         <v>687</v>
       </c>
@@ -17582,7 +17612,7 @@
       <c r="EV64" s="2"/>
       <c r="EW64" s="2"/>
     </row>
-    <row r="65" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A65" s="1" t="s">
         <v>29</v>
       </c>
@@ -17760,7 +17790,7 @@
       <c r="EV65" s="2"/>
       <c r="EW65" s="2"/>
     </row>
-    <row r="66" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A66" s="1" t="s">
         <v>527</v>
       </c>
@@ -17938,7 +17968,7 @@
       <c r="EV66" s="2"/>
       <c r="EW66" s="2"/>
     </row>
-    <row r="67" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A67" s="1" t="s">
         <v>218</v>
       </c>
@@ -18116,7 +18146,7 @@
       <c r="EV67" s="2"/>
       <c r="EW67" s="2"/>
     </row>
-    <row r="68" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A68" s="1" t="s">
         <v>12</v>
       </c>
@@ -18296,7 +18326,7 @@
       <c r="EV68" s="2"/>
       <c r="EW68" s="2"/>
     </row>
-    <row r="69" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A69" s="1" t="s">
         <v>427</v>
       </c>
@@ -18472,7 +18502,7 @@
       <c r="EV69" s="2"/>
       <c r="EW69" s="2"/>
     </row>
-    <row r="70" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A70" s="1" t="s">
         <v>395</v>
       </c>
@@ -18654,7 +18684,7 @@
       <c r="EV70" s="2"/>
       <c r="EW70" s="2"/>
     </row>
-    <row r="71" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A71" s="1" t="s">
         <v>221</v>
       </c>
@@ -18834,7 +18864,7 @@
       <c r="EV71" s="2"/>
       <c r="EW71" s="2"/>
     </row>
-    <row r="72" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A72" s="1" t="s">
         <v>385</v>
       </c>
@@ -19010,7 +19040,7 @@
       <c r="EV72" s="2"/>
       <c r="EW72" s="2"/>
     </row>
-    <row r="73" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A73" s="1" t="s">
         <v>558</v>
       </c>
@@ -19190,7 +19220,7 @@
       <c r="EV73" s="2"/>
       <c r="EW73" s="2"/>
     </row>
-    <row r="74" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A74" s="1" t="s">
         <v>696</v>
       </c>
@@ -19366,7 +19396,7 @@
       <c r="EV74" s="2"/>
       <c r="EW74" s="2"/>
     </row>
-    <row r="75" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A75" s="1" t="s">
         <v>206</v>
       </c>
@@ -19538,7 +19568,7 @@
       <c r="EV75" s="2"/>
       <c r="EW75" s="2"/>
     </row>
-    <row r="76" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A76" s="1" t="s">
         <v>267</v>
       </c>
@@ -19718,7 +19748,7 @@
       <c r="EV76" s="2"/>
       <c r="EW76" s="2"/>
     </row>
-    <row r="77" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A77" s="1" t="s">
         <v>261</v>
       </c>
@@ -19898,7 +19928,7 @@
       <c r="EV77" s="2"/>
       <c r="EW77" s="2"/>
     </row>
-    <row r="78" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A78" s="1" t="s">
         <v>22</v>
       </c>
@@ -20076,7 +20106,7 @@
       <c r="EV78" s="2"/>
       <c r="EW78" s="2"/>
     </row>
-    <row r="79" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A79" s="11" t="s">
         <v>7</v>
       </c>
@@ -20260,7 +20290,7 @@
       <c r="EV79" s="2"/>
       <c r="EW79" s="2"/>
     </row>
-    <row r="80" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A80" s="1" t="s">
         <v>215</v>
       </c>
@@ -20442,7 +20472,7 @@
       <c r="EV80" s="2"/>
       <c r="EW80" s="2"/>
     </row>
-    <row r="81" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A81" s="1" t="s">
         <v>712</v>
       </c>
@@ -20620,7 +20650,7 @@
       <c r="EV81" s="2"/>
       <c r="EW81" s="2"/>
     </row>
-    <row r="82" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A82" s="1" t="s">
         <v>713</v>
       </c>
@@ -20804,7 +20834,7 @@
       <c r="EV82" s="2"/>
       <c r="EW82" s="2"/>
     </row>
-    <row r="83" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A83" s="1" t="s">
         <v>298</v>
       </c>
@@ -20984,7 +21014,7 @@
       <c r="EV83" s="2"/>
       <c r="EW83" s="2"/>
     </row>
-    <row r="84" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A84" s="1" t="s">
         <v>610</v>
       </c>
@@ -21160,7 +21190,7 @@
       <c r="EV84" s="2"/>
       <c r="EW84" s="2"/>
     </row>
-    <row r="85" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A85" s="1" t="s">
         <v>613</v>
       </c>
@@ -21332,7 +21362,7 @@
       <c r="EV85" s="2"/>
       <c r="EW85" s="2"/>
     </row>
-    <row r="86" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A86" s="1" t="s">
         <v>39</v>
       </c>
@@ -21508,7 +21538,7 @@
       <c r="EV86" s="2"/>
       <c r="EW86" s="2"/>
     </row>
-    <row r="87" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A87" s="1" t="s">
         <v>32</v>
       </c>
@@ -21682,7 +21712,7 @@
       <c r="EV87" s="2"/>
       <c r="EW87" s="2"/>
     </row>
-    <row r="88" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A88" s="1" t="s">
         <v>274</v>
       </c>
@@ -21860,7 +21890,7 @@
       <c r="EV88" s="2"/>
       <c r="EW88" s="2"/>
     </row>
-    <row r="89" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A89" s="1" t="s">
         <v>15</v>
       </c>
@@ -22036,7 +22066,7 @@
       <c r="EV89" s="2"/>
       <c r="EW89" s="2"/>
     </row>
-    <row r="90" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A90" s="1" t="s">
         <v>16</v>
       </c>
@@ -22214,7 +22244,7 @@
       <c r="EV90" s="2"/>
       <c r="EW90" s="2"/>
     </row>
-    <row r="91" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A91" s="1" t="s">
         <v>675</v>
       </c>
@@ -22392,7 +22422,7 @@
       <c r="EV91" s="2"/>
       <c r="EW91" s="2"/>
     </row>
-    <row r="92" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A92" s="1" t="s">
         <v>24</v>
       </c>
@@ -22574,7 +22604,7 @@
       <c r="EV92" s="2"/>
       <c r="EW92" s="2"/>
     </row>
-    <row r="93" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A93" s="1" t="s">
         <v>511</v>
       </c>
@@ -22750,7 +22780,7 @@
       <c r="EV93" s="2"/>
       <c r="EW93" s="2"/>
     </row>
-    <row r="94" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A94" s="1" t="s">
         <v>207</v>
       </c>
@@ -22922,7 +22952,7 @@
       <c r="EV94" s="2"/>
       <c r="EW94" s="2"/>
     </row>
-    <row r="95" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A95" s="1" t="s">
         <v>17</v>
       </c>
@@ -23104,7 +23134,7 @@
       <c r="EV95" s="2"/>
       <c r="EW95" s="2"/>
     </row>
-    <row r="96" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A96" s="1" t="s">
         <v>211</v>
       </c>
@@ -23282,7 +23312,7 @@
       <c r="EV96" s="2"/>
       <c r="EW96" s="2"/>
     </row>
-    <row r="97" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A97" s="1" t="s">
         <v>18</v>
       </c>
@@ -23464,7 +23494,7 @@
       <c r="EV97" s="2"/>
       <c r="EW97" s="2"/>
     </row>
-    <row r="98" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="98" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A98" s="1" t="s">
         <v>711</v>
       </c>
@@ -23644,7 +23674,7 @@
       <c r="EV98" s="2"/>
       <c r="EW98" s="2"/>
     </row>
-    <row r="99" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="99" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A99" s="1" t="s">
         <v>21</v>
       </c>
@@ -23822,7 +23852,7 @@
       <c r="EV99" s="2"/>
       <c r="EW99" s="2"/>
     </row>
-    <row r="100" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="100" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A100" s="1" t="s">
         <v>73</v>
       </c>
@@ -24000,7 +24030,7 @@
       <c r="EV100" s="2"/>
       <c r="EW100" s="2"/>
     </row>
-    <row r="101" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="101" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A101" s="1" t="s">
         <v>268</v>
       </c>
@@ -24186,7 +24216,7 @@
       <c r="EV101" s="2"/>
       <c r="EW101" s="2"/>
     </row>
-    <row r="102" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="102" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A102" s="1" t="s">
         <v>30</v>
       </c>
@@ -24364,7 +24394,7 @@
       <c r="EV102" s="2"/>
       <c r="EW102" s="2"/>
     </row>
-    <row r="103" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="103" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A103" s="1" t="s">
         <v>35</v>
       </c>
@@ -24542,7 +24572,7 @@
       <c r="EV103" s="2"/>
       <c r="EW103" s="2"/>
     </row>
-    <row r="104" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="104" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A104" s="1" t="s">
         <v>273</v>
       </c>
@@ -24724,7 +24754,7 @@
       <c r="EV104" s="2"/>
       <c r="EW104" s="2"/>
     </row>
-    <row r="105" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="105" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A105" s="1" t="s">
         <v>203</v>
       </c>
@@ -24902,7 +24932,7 @@
       <c r="EV105" s="2"/>
       <c r="EW105" s="2"/>
     </row>
-    <row r="106" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="106" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A106" s="1" t="s">
         <v>555</v>
       </c>
@@ -25082,7 +25112,7 @@
       <c r="EV106" s="2"/>
       <c r="EW106" s="2"/>
     </row>
-    <row r="107" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="107" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A107" s="1" t="s">
         <v>34</v>
       </c>
@@ -25258,7 +25288,7 @@
       <c r="EV107" s="2"/>
       <c r="EW107" s="2"/>
     </row>
-    <row r="108" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="108" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A108" s="1" t="s">
         <v>523</v>
       </c>
@@ -25440,7 +25470,7 @@
       <c r="EV108" s="2"/>
       <c r="EW108" s="2"/>
     </row>
-    <row r="109" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="109" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A109" s="1" t="s">
         <v>25</v>
       </c>
@@ -25626,7 +25656,7 @@
       <c r="EV109" s="2"/>
       <c r="EW109" s="2"/>
     </row>
-    <row r="110" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="110" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A110" s="1" t="s">
         <v>528</v>
       </c>
@@ -25806,7 +25836,7 @@
       <c r="EV110" s="2"/>
       <c r="EW110" s="2"/>
     </row>
-    <row r="111" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="111" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A111" s="1" t="s">
         <v>494</v>
       </c>
@@ -25986,7 +26016,7 @@
       <c r="EV111" s="2"/>
       <c r="EW111" s="2"/>
     </row>
-    <row r="112" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="112" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A112" s="1" t="s">
         <v>33</v>
       </c>
@@ -26160,7 +26190,7 @@
       <c r="EV112" s="2"/>
       <c r="EW112" s="2"/>
     </row>
-    <row r="113" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="113" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A113" s="1" t="s">
         <v>148</v>
       </c>
@@ -26336,7 +26366,7 @@
       <c r="EV113" s="2"/>
       <c r="EW113" s="2"/>
     </row>
-    <row r="114" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="114" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A114" s="1" t="s">
         <v>312</v>
       </c>
@@ -26512,7 +26542,7 @@
       <c r="EV114" s="2"/>
       <c r="EW114" s="2"/>
     </row>
-    <row r="115" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="115" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A115" s="1" t="s">
         <v>10</v>
       </c>
@@ -26692,7 +26722,7 @@
       <c r="EV115" s="2"/>
       <c r="EW115" s="2"/>
     </row>
-    <row r="116" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="116" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A116" s="1" t="s">
         <v>40</v>
       </c>
@@ -26870,7 +26900,7 @@
       <c r="EV116" s="2"/>
       <c r="EW116" s="2"/>
     </row>
-    <row r="117" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="117" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A117" s="1" t="s">
         <v>5</v>
       </c>
@@ -27046,7 +27076,7 @@
       <c r="EV117" s="2"/>
       <c r="EW117" s="2"/>
     </row>
-    <row r="118" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="118" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A118" s="1" t="s">
         <v>495</v>
       </c>
@@ -27222,7 +27252,7 @@
       <c r="EV118" s="2"/>
       <c r="EW118" s="2"/>
     </row>
-    <row r="119" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="119" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A119" s="1" t="s">
         <v>272</v>
       </c>
@@ -27404,7 +27434,7 @@
       <c r="EV119" s="2"/>
       <c r="EW119" s="2"/>
     </row>
-    <row r="120" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="120" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A120" s="1" t="s">
         <v>0</v>
       </c>
@@ -27582,7 +27612,7 @@
       <c r="EV120" s="2"/>
       <c r="EW120" s="2"/>
     </row>
-    <row r="121" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="121" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A121" s="1" t="s">
         <v>140</v>
       </c>
@@ -27760,7 +27790,7 @@
       <c r="EV121" s="2"/>
       <c r="EW121" s="2"/>
     </row>
-    <row r="122" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A122" s="1" t="s">
         <v>505</v>
       </c>
@@ -27936,7 +27966,7 @@
       <c r="EV122" s="2"/>
       <c r="EW122" s="2"/>
     </row>
-    <row r="123" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A123" s="1" t="s">
         <v>45</v>
       </c>
@@ -28114,7 +28144,7 @@
       <c r="EV123" s="2"/>
       <c r="EW123" s="2"/>
     </row>
-    <row r="124" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A124" s="1" t="s">
         <v>252</v>
       </c>
@@ -28290,7 +28320,7 @@
       <c r="EV124" s="2"/>
       <c r="EW124" s="2"/>
     </row>
-    <row r="125" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A125" s="13" t="s">
         <v>599</v>
       </c>
@@ -28474,7 +28504,7 @@
       <c r="EV125" s="2"/>
       <c r="EW125" s="2"/>
     </row>
-    <row r="126" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A126" s="1" t="s">
         <v>530</v>
       </c>
@@ -28656,7 +28686,7 @@
       <c r="EV126" s="2"/>
       <c r="EW126" s="2"/>
     </row>
-    <row r="127" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A127" s="1" t="s">
         <v>13</v>
       </c>
@@ -28834,7 +28864,7 @@
       <c r="EV127" s="2"/>
       <c r="EW127" s="2"/>
     </row>
-    <row r="128" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A128" s="1" t="s">
         <v>11</v>
       </c>
@@ -29010,7 +29040,7 @@
       <c r="EV128" s="2"/>
       <c r="EW128" s="2"/>
     </row>
-    <row r="129" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="129" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A129" s="1" t="s">
         <v>259</v>
       </c>
@@ -29190,7 +29220,7 @@
       <c r="EV129" s="2"/>
       <c r="EW129" s="2"/>
     </row>
-    <row r="130" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="130" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A130" s="1" t="s">
         <v>575</v>
       </c>
@@ -29370,7 +29400,7 @@
       <c r="EV130" s="2"/>
       <c r="EW130" s="2"/>
     </row>
-    <row r="131" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="131" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A131" s="1" t="s">
         <v>307</v>
       </c>
@@ -29546,7 +29576,7 @@
       <c r="EV131" s="2"/>
       <c r="EW131" s="2"/>
     </row>
-    <row r="132" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="132" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A132" s="1" t="s">
         <v>8</v>
       </c>
@@ -29726,7 +29756,7 @@
       <c r="EV132" s="2"/>
       <c r="EW132" s="2"/>
     </row>
-    <row r="133" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="133" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A133" s="1" t="s">
         <v>216</v>
       </c>
@@ -29902,7 +29932,7 @@
       <c r="EV133" s="2"/>
       <c r="EW133" s="2"/>
     </row>
-    <row r="134" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="134" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A134" s="1" t="s">
         <v>36</v>
       </c>
@@ -30080,7 +30110,7 @@
       <c r="EV134" s="2"/>
       <c r="EW134" s="2"/>
     </row>
-    <row r="135" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="135" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A135" s="1" t="s">
         <v>193</v>
       </c>
@@ -30254,7 +30284,7 @@
       <c r="EV135" s="2"/>
       <c r="EW135" s="2"/>
     </row>
-    <row r="136" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="136" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A136" s="1" t="s">
         <v>292</v>
       </c>
@@ -30428,7 +30458,7 @@
       <c r="EV136" s="2"/>
       <c r="EW136" s="2"/>
     </row>
-    <row r="137" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="137" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A137" s="13" t="s">
         <v>597</v>
       </c>
@@ -30606,7 +30636,7 @@
       <c r="EV137" s="2"/>
       <c r="EW137" s="2"/>
     </row>
-    <row r="138" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="138" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A138" s="1" t="s">
         <v>19</v>
       </c>
@@ -30786,7 +30816,7 @@
       <c r="EV138" s="2"/>
       <c r="EW138" s="2"/>
     </row>
-    <row r="139" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="139" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A139" s="1" t="s">
         <v>579</v>
       </c>
@@ -30966,7 +30996,7 @@
       <c r="EV139" s="2"/>
       <c r="EW139" s="2"/>
     </row>
-    <row r="140" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="140" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A140" s="1" t="s">
         <v>421</v>
       </c>
@@ -31148,7 +31178,7 @@
       <c r="EV140" s="2"/>
       <c r="EW140" s="2"/>
     </row>
-    <row r="141" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="141" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A141" s="1" t="s">
         <v>604</v>
       </c>
@@ -31326,7 +31356,7 @@
       <c r="EV141" s="2"/>
       <c r="EW141" s="2"/>
     </row>
-    <row r="142" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="142" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A142" s="1" t="s">
         <v>189</v>
       </c>
@@ -31506,7 +31536,7 @@
       <c r="EV142" s="2"/>
       <c r="EW142" s="2"/>
     </row>
-    <row r="143" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="143" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A143" s="1" t="s">
         <v>531</v>
       </c>
@@ -31694,7 +31724,7 @@
       <c r="EV143" s="2"/>
       <c r="EW143" s="2"/>
     </row>
-    <row r="144" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="144" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A144" s="1" t="s">
         <v>318</v>
       </c>
@@ -31870,7 +31900,7 @@
       <c r="EV144" s="2"/>
       <c r="EW144" s="2"/>
     </row>
-    <row r="145" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="145" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A145" s="1" t="s">
         <v>489</v>
       </c>
@@ -32046,7 +32076,7 @@
       <c r="EV145" s="2"/>
       <c r="EW145" s="2"/>
     </row>
-    <row r="146" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="146" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A146" s="1" t="s">
         <v>142</v>
       </c>
@@ -32222,7 +32252,7 @@
       <c r="EV146" s="2"/>
       <c r="EW146" s="2"/>
     </row>
-    <row r="147" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="147" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A147" s="1" t="s">
         <v>707</v>
       </c>
@@ -32398,7 +32428,7 @@
       <c r="EV147" s="2"/>
       <c r="EW147" s="2"/>
     </row>
-    <row r="148" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="148" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A148" s="1" t="s">
         <v>681</v>
       </c>
@@ -32574,7 +32604,7 @@
       <c r="EV148" s="2"/>
       <c r="EW148" s="2"/>
     </row>
-    <row r="149" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="149" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A149" s="1" t="s">
         <v>685</v>
       </c>
@@ -32752,7 +32782,7 @@
       <c r="EV149" s="2"/>
       <c r="EW149" s="2"/>
     </row>
-    <row r="150" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="150" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A150" s="1" t="s">
         <v>44</v>
       </c>
@@ -32928,7 +32958,7 @@
       <c r="EV150" s="2"/>
       <c r="EW150" s="2"/>
     </row>
-    <row r="151" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="151" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A151" s="1" t="s">
         <v>749</v>
       </c>
@@ -33108,7 +33138,7 @@
       <c r="EV151" s="2"/>
       <c r="EW151" s="2"/>
     </row>
-    <row r="152" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="152" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A152" s="1" t="s">
         <v>752</v>
       </c>
@@ -33287,7 +33317,7 @@
       <c r="EV152" s="2"/>
       <c r="EW152" s="2"/>
     </row>
-    <row r="153" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="153" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A153" s="1" t="s">
         <v>756</v>
       </c>
@@ -33467,7 +33497,7 @@
       <c r="EV153" s="2"/>
       <c r="EW153" s="2"/>
     </row>
-    <row r="154" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="154" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A154" s="1" t="s">
         <v>766</v>
       </c>
@@ -33643,7 +33673,7 @@
       <c r="EV154" s="2"/>
       <c r="EW154" s="2"/>
     </row>
-    <row r="155" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="155" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A155" s="1" t="s">
         <v>792</v>
       </c>
@@ -33819,7 +33849,7 @@
       <c r="EV155" s="2"/>
       <c r="EW155" s="2"/>
     </row>
-    <row r="156" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="156" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A156" s="1" t="s">
         <v>796</v>
       </c>
@@ -33997,7 +34027,7 @@
       <c r="EV156" s="2"/>
       <c r="EW156" s="2"/>
     </row>
-    <row r="157" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="157" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A157" s="1" t="s">
         <v>800</v>
       </c>
@@ -34171,7 +34201,7 @@
       <c r="EV157" s="2"/>
       <c r="EW157" s="2"/>
     </row>
-    <row r="158" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="158" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A158" s="1" t="s">
         <v>806</v>
       </c>
@@ -34351,7 +34381,7 @@
       </c>
       <c r="EW158" s="2"/>
     </row>
-    <row r="159" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="159" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A159" s="1" t="s">
         <v>811</v>
       </c>
@@ -34541,7 +34571,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="160" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="160" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A160" s="1" t="s">
         <v>819</v>
       </c>
@@ -34713,7 +34743,7 @@
       <c r="EV160" s="2"/>
       <c r="EW160" s="2"/>
     </row>
-    <row r="161" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="161" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A161" s="1" t="s">
         <v>827</v>
       </c>
@@ -34897,7 +34927,7 @@
       <c r="EV161" s="2"/>
       <c r="EW161" s="2"/>
     </row>
-    <row r="162" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="162" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A162" s="1" t="s">
         <v>829</v>
       </c>
@@ -35073,7 +35103,7 @@
       <c r="EV162" s="2"/>
       <c r="EW162" s="2"/>
     </row>
-    <row r="163" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="163" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A163" s="1" t="s">
         <v>844</v>
       </c>
@@ -35253,7 +35283,7 @@
       <c r="EV163" s="2"/>
       <c r="EW163" s="2"/>
     </row>
-    <row r="164" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="164" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A164" s="1" t="s">
         <v>848</v>
       </c>
@@ -35431,7 +35461,7 @@
       <c r="EV164" s="2"/>
       <c r="EW164" s="2"/>
     </row>
-    <row r="165" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="165" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A165" s="1" t="s">
         <v>859</v>
       </c>
@@ -35607,7 +35637,7 @@
       <c r="EV165" s="2"/>
       <c r="EW165" s="2"/>
     </row>
-    <row r="166" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="166" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A166" s="1" t="s">
         <v>869</v>
       </c>
@@ -35789,7 +35819,7 @@
       <c r="EV166" s="2"/>
       <c r="EW166" s="2"/>
     </row>
-    <row r="167" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="167" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A167" s="1" t="s">
         <v>885</v>
       </c>
@@ -35967,7 +35997,7 @@
       <c r="EV167" s="2"/>
       <c r="EW167" s="2"/>
     </row>
-    <row r="168" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="168" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A168" s="1" t="s">
         <v>883</v>
       </c>
@@ -36141,7 +36171,7 @@
       <c r="EV168" s="2"/>
       <c r="EW168" s="2"/>
     </row>
-    <row r="169" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="169" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A169" s="1" t="s">
         <v>886</v>
       </c>
@@ -36319,7 +36349,7 @@
       <c r="EV169" s="2"/>
       <c r="EW169" s="2"/>
     </row>
-    <row r="170" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="170" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A170" s="1" t="s">
         <v>887</v>
       </c>
@@ -36495,7 +36525,7 @@
       <c r="EV170" s="2"/>
       <c r="EW170" s="2"/>
     </row>
-    <row r="171" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="171" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A171" s="1" t="s">
         <v>893</v>
       </c>
@@ -36671,7 +36701,7 @@
       <c r="EV171" s="2"/>
       <c r="EW171" s="2"/>
     </row>
-    <row r="172" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="172" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A172" s="1" t="s">
         <v>1045</v>
       </c>
@@ -36849,7 +36879,7 @@
       <c r="EV172" s="2"/>
       <c r="EW172" s="2"/>
     </row>
-    <row r="173" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="173" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A173" s="1" t="s">
         <v>1064</v>
       </c>
@@ -37025,7 +37055,7 @@
       <c r="EV173" s="2"/>
       <c r="EW173" s="2"/>
     </row>
-    <row r="174" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="174" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A174" s="1" t="s">
         <v>1065</v>
       </c>
@@ -37048,7 +37078,7 @@
         <v>300</v>
       </c>
       <c r="H174" s="2">
-        <f t="shared" ref="H174:H175" si="8">SUM(I174:DF174)</f>
+        <f t="shared" ref="H174:H176" si="8">SUM(I174:DF174)</f>
         <v>180</v>
       </c>
       <c r="I174" s="2"/>
@@ -37203,7 +37233,7 @@
       <c r="EV174" s="2"/>
       <c r="EW174" s="2"/>
     </row>
-    <row r="175" spans="1:153" hidden="1" x14ac:dyDescent="0.25">
+    <row r="175" spans="1:153" x14ac:dyDescent="0.25">
       <c r="A175" s="1" t="s">
         <v>1124</v>
       </c>
@@ -37378,14 +37408,31 @@
       <c r="EW175" s="2"/>
     </row>
     <row r="176" spans="1:153" x14ac:dyDescent="0.25">
-      <c r="A176" s="1"/>
-      <c r="B176" s="1"/>
-      <c r="C176" s="2"/>
-      <c r="D176" s="2"/>
-      <c r="E176" s="2"/>
-      <c r="F176" s="2"/>
-      <c r="G176" s="2"/>
-      <c r="H176" s="2"/>
+      <c r="A176" s="1" t="s">
+        <v>1150</v>
+      </c>
+      <c r="B176" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="C176" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="D176" s="2">
+        <v>300</v>
+      </c>
+      <c r="E176" s="2">
+        <v>120</v>
+      </c>
+      <c r="F176" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="G176" s="2">
+        <v>180</v>
+      </c>
+      <c r="H176" s="2">
+        <f t="shared" si="8"/>
+        <v>180</v>
+      </c>
       <c r="I176" s="2"/>
       <c r="J176" s="2"/>
       <c r="K176" s="2"/>
@@ -37402,7 +37449,9 @@
       <c r="V176" s="2"/>
       <c r="W176" s="2"/>
       <c r="X176" s="2"/>
-      <c r="Y176" s="2"/>
+      <c r="Y176" s="2">
+        <v>90</v>
+      </c>
       <c r="Z176" s="2"/>
       <c r="AA176" s="2"/>
       <c r="AB176" s="2"/>
@@ -37414,7 +37463,9 @@
       <c r="AH176" s="2"/>
       <c r="AI176" s="2"/>
       <c r="AJ176" s="2"/>
-      <c r="AK176" s="2"/>
+      <c r="AK176" s="2">
+        <v>60</v>
+      </c>
       <c r="AL176" s="2"/>
       <c r="AM176" s="2"/>
       <c r="AN176" s="2"/>
@@ -37483,7 +37534,9 @@
       <c r="CY176" s="2"/>
       <c r="CZ176" s="2"/>
       <c r="DA176" s="2"/>
-      <c r="DB176" s="2"/>
+      <c r="DB176" s="2">
+        <v>30</v>
+      </c>
       <c r="DC176" s="2"/>
       <c r="DD176" s="2"/>
       <c r="DE176" s="2"/>
@@ -49004,11 +49057,6 @@
     </row>
   </sheetData>
   <autoFilter ref="A1:EW175" xr:uid="{C7FAA63B-DEDB-48F1-9CCA-3BF0BF1CD86F}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="Destornillador"/>
-      </filters>
-    </filterColumn>
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:EW150">
       <sortCondition ref="A1:A146"/>
     </sortState>
@@ -55825,10 +55873,12 @@
     <row r="176" spans="1:31" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="str">
         <f>IF(receta!A176="","",receta!A176)</f>
-        <v/>
+        <v>Bicicletta</v>
       </c>
       <c r="B176" s="2"/>
-      <c r="C176" s="2"/>
+      <c r="C176" s="2">
+        <v>1</v>
+      </c>
       <c r="D176" s="2"/>
       <c r="E176" s="2"/>
       <c r="F176" s="2"/>
@@ -62187,7 +62237,9 @@
         <v>Tinto de Verano</v>
       </c>
       <c r="B137" s="13"/>
-      <c r="C137" s="1"/>
+      <c r="C137" s="4" t="s">
+        <v>1157</v>
+      </c>
       <c r="D137" s="4" t="s">
         <v>431</v>
       </c>
@@ -63263,23 +63315,35 @@
         <v>1127</v>
       </c>
     </row>
-    <row r="176" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="176" spans="1:13" ht="409.5" x14ac:dyDescent="0.25">
       <c r="A176" s="1" t="str">
         <f>IF(receta!A176="","",receta!A176)</f>
-        <v/>
-      </c>
-      <c r="B176" s="1"/>
-      <c r="C176" s="4"/>
-      <c r="D176" s="4"/>
-      <c r="E176" s="1"/>
-      <c r="F176" s="1"/>
+        <v>Bicicletta</v>
+      </c>
+      <c r="B176" s="4" t="s">
+        <v>1151</v>
+      </c>
+      <c r="C176" s="4" t="s">
+        <v>1152</v>
+      </c>
+      <c r="D176" s="4" t="s">
+        <v>1155</v>
+      </c>
+      <c r="E176" s="1" t="s">
+        <v>1154</v>
+      </c>
+      <c r="F176" s="5" t="s">
+        <v>1153</v>
+      </c>
       <c r="G176" s="1"/>
       <c r="H176" s="1"/>
       <c r="I176" s="5"/>
       <c r="J176" s="1"/>
       <c r="K176" s="1"/>
       <c r="L176" s="1"/>
-      <c r="M176" s="1"/>
+      <c r="M176" s="4" t="s">
+        <v>1156</v>
+      </c>
     </row>
     <row r="177" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A177" s="1" t="str">
@@ -64718,9 +64782,10 @@
     <hyperlink ref="K125" r:id="rId99" xr:uid="{F4AC4FB8-FB91-4049-878D-BBEAAE2B5094}"/>
     <hyperlink ref="K158" r:id="rId100" xr:uid="{C198DB91-C048-4B59-BF1D-EE0F56806A3D}"/>
     <hyperlink ref="K162" r:id="rId101" xr:uid="{13A99BFB-962B-44AF-937F-DBDFF58BD18C}"/>
+    <hyperlink ref="F176" r:id="rId102" xr:uid="{266B0E4F-3A83-474D-9ADC-710DA8B25FB8}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId102"/>
+  <pageSetup orientation="portrait" r:id="rId103"/>
 </worksheet>
 </file>
 

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3FC672B-ABEE-469B-ADB6-D47CCDE406F9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C627817C-2D92-405C-87FD-D31A7E639B9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
@@ -5295,11 +5295,11 @@
 La figura de Pocho quedó asociada para siempre a la bicicleta, especialmente tras la canción “El ángel de la bicicleta” de León Gieco, que transformó ese objeto cotidiano en símbolo de compromiso, ternura y resistencia. Pero el nombre de Pocho nombre también permanece ligado al activismo social y a la militancia territorial en los barrios populares de Rosario: a un compromiso profundo con la justicia social, hecha de presencia, trabajo comunitario y defensa de la vida. Desde entonces, la bicicleta no es solo el medio con el que recorría los barrios, sino también la imagen de una ética solidaria que eligió ponerse delante de las balas para proteger a los demás.</t>
   </si>
   <si>
-    <t>Pocho.jpg
+    <t>Existe una variante interesante que reemplaza la gaseosa de limón por gaseosa de pomelo. El resultado es un Tinto de Verano con un amargor cítrico que realza el carácter del vino tinto y sorprende.</t>
+  </si>
+  <si>
+    <t>Pocho2.jpg
 Claudio “Pocho” Lepratti (27 de febrero de 1966 - 19 de diciembre de 2001)</t>
-  </si>
-  <si>
-    <t>Existe una variante interesante que reemplaza la gaseosa de limón por gaseosa de pomelo. El resultado es un Tinto de Verano con un amargor cítrico que realza el carácter del vino tinto y sorprende.</t>
   </si>
 </sst>
 </file>
@@ -62238,7 +62238,7 @@
       </c>
       <c r="B137" s="13"/>
       <c r="C137" s="4" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="D137" s="4" t="s">
         <v>431</v>
@@ -63342,7 +63342,7 @@
       <c r="K176" s="1"/>
       <c r="L176" s="1"/>
       <c r="M176" s="4" t="s">
-        <v>1156</v>
+        <v>1157</v>
       </c>
     </row>
     <row r="177" spans="1:13" x14ac:dyDescent="0.25">

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C627817C-2D92-405C-87FD-D31A7E639B9F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B90236DA-4C48-402F-BB5C-C32BAE0E8846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
@@ -5299,7 +5299,7 @@
   </si>
   <si>
     <t>Pocho2.jpg
-Claudio “Pocho” Lepratti (27 de febrero de 1966 - 19 de diciembre de 2001)</t>
+Graffitis dedicados a "Pocho" Lepratti, militante social asesinado por la policía argentina en 2001.</t>
   </si>
 </sst>
 </file>

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B90236DA-4C48-402F-BB5C-C32BAE0E8846}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A47501-885F-404A-89C6-273772854ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
@@ -5299,7 +5299,7 @@
   </si>
   <si>
     <t>Pocho2.jpg
-Graffitis dedicados a "Pocho" Lepratti, militante social asesinado por la policía argentina en 2001.</t>
+Grafitis dedicados a "Pocho" Lepratti, militante social asesinado por la policía argentina en 2001.</t>
   </si>
 </sst>
 </file>

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{67A47501-885F-404A-89C6-273772854ED6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BF4BC30-ABC5-4E9A-B435-BC70F2D99D4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
@@ -5286,20 +5286,22 @@
     <t>León Gieco - El Angel De La Bicicleta</t>
   </si>
   <si>
-    <t>Pocho y la bicicleta
+    <t>Existe una variante interesante que reemplaza la gaseosa de limón por gaseosa de pomelo. El resultado es un Tinto de Verano con un amargor cítrico que realza el carácter del vino tinto y sorprende.</t>
+  </si>
+  <si>
+    <t>Pocho2.jpg
+Grafitis dedicados a "Pocho" Lepratti, militante social asesinado por la policía argentina en 2001.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Pocho y la bicicleta
 Claudio “Pocho” Lepratti nació en 1966 en la provincia de Entre Ríos, Argentina, y desde joven manifestó una profunda vocación social. A fines de los años ochenta ingresó a la congregación salesiana, donde inició estudios de formación religiosa y trabajo comunitario. Esa experiencia consolidó su compromiso con los sectores más vulnerables. Aunque más tarde dejó la vida religiosa formal, mantuvo intacta su opción por el trabajo territorial y se radicó en Rosario, donde desarrolló tareas sociales en barrios populares de la zona sur.
 En Rosario trabajó con niños y jóvenes en situación de pobreza, participando en comedores comunitarios, espacios educativos y proyectos culturales. Quienes lo conocieron destacan su cercanía, su sencillez y su convicción de que la educación y la organización comunitaria eran herramientas fundamentales para la dignidad. En ese entramado barrial, la bicicleta fue parte esencial de su vida. Era su medio de transporte habitual: con ella recorría largas distancias entre escuelas, parroquias y comedores, llevando materiales, alimentos o simplemente su tiempo. La bicicleta simbolizaba su modo de estar en el mundo: cercano, austero y siempre en movimiento al servicio de los demás.
 A fines de 2001, Pocho trabajaba como auxiliar de cocina en el comedor de la Escuela Nº 756 José M. Serrano, del barrio Las Flores, en el sudoeste de Rosario. El 19 de diciembre, en medio de la crisis que culminaría con la renuncia del presidente Fernando de la Rúa, varios policías provenientes de Arroyo Seco comenzaron a disparar en las inmediaciones de la escuela. Lepratti subió al techo y, al asomarse, gritó: “¡Dejen de tirar, que hay chicos!”.
 El agente Esteban Velásquez abrió fuego con su escopeta y le dio en la tráquea, causándole la muerte casi instantánea. Pocho tenía 35 años.
 Los policías involucrados argumentaron que habían respondido a un supuesto ataque armado desde el techo. Sin embargo, las pericias demostraron que los impactos en el patrullero se habían realizado a nivel del suelo. Esteban Velásquez fue condenado a 14 años de prisión por homicidio, y otros cinco policías, fueron condenados por falsedad ideológica y encubrimiento agravado, al comprobarse que habían baleado el vehículo policial para simular un enfrentamiento.
-La figura de Pocho quedó asociada para siempre a la bicicleta, especialmente tras la canción “El ángel de la bicicleta” de León Gieco, que transformó ese objeto cotidiano en símbolo de compromiso, ternura y resistencia. Pero el nombre de Pocho nombre también permanece ligado al activismo social y a la militancia territorial en los barrios populares de Rosario: a un compromiso profundo con la justicia social, hecha de presencia, trabajo comunitario y defensa de la vida. Desde entonces, la bicicleta no es solo el medio con el que recorría los barrios, sino también la imagen de una ética solidaria que eligió ponerse delante de las balas para proteger a los demás.</t>
-  </si>
-  <si>
-    <t>Existe una variante interesante que reemplaza la gaseosa de limón por gaseosa de pomelo. El resultado es un Tinto de Verano con un amargor cítrico que realza el carácter del vino tinto y sorprende.</t>
-  </si>
-  <si>
-    <t>Pocho2.jpg
-Grafitis dedicados a "Pocho" Lepratti, militante social asesinado por la policía argentina en 2001.</t>
+La figura de Pocho quedó asociada para siempre a la bicicleta, especialmente tras la canción “El ángel de la bicicleta”, popularizada por León Gieco, que transformó ese objeto cotidiano en símbolo de compromiso, ternura y resistencia. La canción, una cumbia compuesta por el pianista Luis Gurevich en homenaje a Pocho, fue grabada por Gieco junto a músicos del grupo Los Pibes Chorros, incorporando el teclado característico de la cumbia villera y el bajo que le dan su identidad sonora, ligada a los barrios populares en los que Pocho desarrollaba su trabajo comunitario.
+Pero el nombre de Pocho también permanece ligado al activismo social y a la militancia territorial en los barrios populares de Rosario: a un compromiso profundo con la justicia social, hecho de presencia, trabajo comunitario y defensa de la vida. Desde entonces, la bicicleta no es solo el medio con el que recorría los barrios, sino también la imagen de una ética solidaria que eligió ponerse delante de las balas para proteger a los demás.
+</t>
   </si>
 </sst>
 </file>
@@ -62238,7 +62240,7 @@
       </c>
       <c r="B137" s="13"/>
       <c r="C137" s="4" t="s">
-        <v>1156</v>
+        <v>1155</v>
       </c>
       <c r="D137" s="4" t="s">
         <v>431</v>
@@ -63327,7 +63329,7 @@
         <v>1152</v>
       </c>
       <c r="D176" s="4" t="s">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>1154</v>
@@ -63342,7 +63344,7 @@
       <c r="K176" s="1"/>
       <c r="L176" s="1"/>
       <c r="M176" s="4" t="s">
-        <v>1157</v>
+        <v>1156</v>
       </c>
     </row>
     <row r="177" spans="1:13" x14ac:dyDescent="0.25">

--- a/data/recetas.xlsx
+++ b/data/recetas.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vamon\Documents\Aplicación coctelería\coctel_app\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9BF4BC30-ABC5-4E9A-B435-BC70F2D99D4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70922254-0DA1-42A7-8308-3402D2AC478A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" activeTab="2" xr2:uid="{732455C0-6376-41B9-84D1-84E385ACD0F1}"/>
   </bookViews>
@@ -5293,15 +5293,14 @@
 Grafitis dedicados a "Pocho" Lepratti, militante social asesinado por la policía argentina en 2001.</t>
   </si>
   <si>
-    <t xml:space="preserve">Pocho y la bicicleta
+    <t>Pocho y la bicicleta
 Claudio “Pocho” Lepratti nació en 1966 en la provincia de Entre Ríos, Argentina, y desde joven manifestó una profunda vocación social. A fines de los años ochenta ingresó a la congregación salesiana, donde inició estudios de formación religiosa y trabajo comunitario. Esa experiencia consolidó su compromiso con los sectores más vulnerables. Aunque más tarde dejó la vida religiosa formal, mantuvo intacta su opción por el trabajo territorial y se radicó en Rosario, donde desarrolló tareas sociales en barrios populares de la zona sur.
 En Rosario trabajó con niños y jóvenes en situación de pobreza, participando en comedores comunitarios, espacios educativos y proyectos culturales. Quienes lo conocieron destacan su cercanía, su sencillez y su convicción de que la educación y la organización comunitaria eran herramientas fundamentales para la dignidad. En ese entramado barrial, la bicicleta fue parte esencial de su vida. Era su medio de transporte habitual: con ella recorría largas distancias entre escuelas, parroquias y comedores, llevando materiales, alimentos o simplemente su tiempo. La bicicleta simbolizaba su modo de estar en el mundo: cercano, austero y siempre en movimiento al servicio de los demás.
-A fines de 2001, Pocho trabajaba como auxiliar de cocina en el comedor de la Escuela Nº 756 José M. Serrano, del barrio Las Flores, en el sudoeste de Rosario. El 19 de diciembre, en medio de la crisis que culminaría con la renuncia del presidente Fernando de la Rúa, varios policías provenientes de Arroyo Seco comenzaron a disparar en las inmediaciones de la escuela. Lepratti subió al techo y, al asomarse, gritó: “¡Dejen de tirar, que hay chicos!”.
+A fines de 2001, Pocho trabajaba como auxiliar de cocina en el comedor de la Escuela Nº 756 "José M. Serrano", del barrio Las Flores, en el sudoeste de Rosario. El 19 de diciembre, en medio de la crisis que culminaría con la renuncia del presidente Fernando de la Rúa, varios policías provenientes de Arroyo Seco comenzaron a disparar en las inmediaciones de la escuela. Lepratti subió al techo y, al asomarse, gritó: “¡Dejen de tirar, que hay chicos!”.
 El agente Esteban Velásquez abrió fuego con su escopeta y le dio en la tráquea, causándole la muerte casi instantánea. Pocho tenía 35 años.
-Los policías involucrados argumentaron que habían respondido a un supuesto ataque armado desde el techo. Sin embargo, las pericias demostraron que los impactos en el patrullero se habían realizado a nivel del suelo. Esteban Velásquez fue condenado a 14 años de prisión por homicidio, y otros cinco policías, fueron condenados por falsedad ideológica y encubrimiento agravado, al comprobarse que habían baleado el vehículo policial para simular un enfrentamiento.
-La figura de Pocho quedó asociada para siempre a la bicicleta, especialmente tras la canción “El ángel de la bicicleta”, popularizada por León Gieco, que transformó ese objeto cotidiano en símbolo de compromiso, ternura y resistencia. La canción, una cumbia compuesta por el pianista Luis Gurevich en homenaje a Pocho, fue grabada por Gieco junto a músicos del grupo Los Pibes Chorros, incorporando el teclado característico de la cumbia villera y el bajo que le dan su identidad sonora, ligada a los barrios populares en los que Pocho desarrollaba su trabajo comunitario.
-Pero el nombre de Pocho también permanece ligado al activismo social y a la militancia territorial en los barrios populares de Rosario: a un compromiso profundo con la justicia social, hecho de presencia, trabajo comunitario y defensa de la vida. Desde entonces, la bicicleta no es solo el medio con el que recorría los barrios, sino también la imagen de una ética solidaria que eligió ponerse delante de las balas para proteger a los demás.
-</t>
+Los policías involucrados argumentaron que habían respondido a un supuesto ataque armado desde el techo. Sin embargo, las pericias demostraron que los impactos en el patrullero se habían realizado a nivel del suelo. Esteban Velásquez fue condenado a 14 años de prisión por homicidio, y otros cinco policías fueron condenados por falsedad ideológica y encubrimiento agravado, al comprobarse que habían baleado el vehículo policial para simular un enfrentamiento.
+La figura de Pocho quedó asociada para siempre a la bicicleta, especialmente tras la canción “El ángel de la bicicleta”, popularizada por León Gieco. La canción, una cumbia compuesta por el pianista Luis Gurevich en homenaje a Pocho, fue grabada por Gieco junto a músicos del grupo Los Pibes Chorros, incorporando el teclado característico de la cumbia villera y percusiones que le dan una identidad sonora ligada a los barrios populares en los que Pocho desarrollaba su trabajo comunitario.
+Pero el nombre de Pocho también permanece ligado al activismo social y a un compromiso profundo con la justicia social. Por ello, la bicicleta no es solo el medio con el que recorría los barrios, sino también el símbolo de su trabajo incansable, de su ética solidaria y de su entrega permanente.</t>
   </si>
 </sst>
 </file>
